--- a/output/cta-index-crime-full-year.xlsx
+++ b/output/cta-index-crime-full-year.xlsx
@@ -19,18 +19,18 @@
     <sheet name="Rogers Park" sheetId="10" r:id="rId10"/>
     <sheet name="Douglas" sheetId="11" r:id="rId11"/>
     <sheet name="Jefferson Park" sheetId="12" r:id="rId12"/>
-    <sheet name="Grand Crossing" sheetId="13" r:id="rId13"/>
-    <sheet name="Chatham" sheetId="14" r:id="rId14"/>
-    <sheet name="Austin" sheetId="15" r:id="rId15"/>
-    <sheet name="Albany Park" sheetId="16" r:id="rId16"/>
-    <sheet name="Grand Boulevard" sheetId="17" r:id="rId17"/>
-    <sheet name="Belmont Cragin" sheetId="18" r:id="rId18"/>
-    <sheet name="West Ridge" sheetId="19" r:id="rId19"/>
-    <sheet name="Loop" sheetId="20" r:id="rId20"/>
-    <sheet name="Lake View" sheetId="21" r:id="rId21"/>
-    <sheet name="South Shore" sheetId="22" r:id="rId22"/>
-    <sheet name="Mount Greenwood" sheetId="23" r:id="rId23"/>
-    <sheet name="Gage Park" sheetId="24" r:id="rId24"/>
+    <sheet name="Chatham" sheetId="13" r:id="rId13"/>
+    <sheet name="Albany Park" sheetId="14" r:id="rId14"/>
+    <sheet name="Grand Boulevard" sheetId="15" r:id="rId15"/>
+    <sheet name="Belmont Cragin" sheetId="16" r:id="rId16"/>
+    <sheet name="West Ridge" sheetId="17" r:id="rId17"/>
+    <sheet name="Loop" sheetId="18" r:id="rId18"/>
+    <sheet name="Lake View" sheetId="19" r:id="rId19"/>
+    <sheet name="Austin" sheetId="20" r:id="rId20"/>
+    <sheet name="South Shore" sheetId="21" r:id="rId21"/>
+    <sheet name="Mount Greenwood" sheetId="22" r:id="rId22"/>
+    <sheet name="Gage Park" sheetId="23" r:id="rId23"/>
+    <sheet name="Grand Crossing" sheetId="24" r:id="rId24"/>
     <sheet name="West Loop" sheetId="25" r:id="rId25"/>
     <sheet name="Rush &amp; Division" sheetId="26" r:id="rId26"/>
     <sheet name="North Lawndale" sheetId="27" r:id="rId27"/>
@@ -50,9 +50,9 @@
     <sheet name="Roseland" sheetId="41" r:id="rId41"/>
     <sheet name="Woodlawn" sheetId="42" r:id="rId42"/>
     <sheet name="Fuller Park" sheetId="43" r:id="rId43"/>
-    <sheet name="O'Hare" sheetId="44" r:id="rId44"/>
-    <sheet name="Little Italy, UIC" sheetId="45" r:id="rId45"/>
-    <sheet name="Hyde Park" sheetId="46" r:id="rId46"/>
+    <sheet name="Little Italy, UIC" sheetId="44" r:id="rId44"/>
+    <sheet name="Hyde Park" sheetId="45" r:id="rId45"/>
+    <sheet name="O'Hare" sheetId="46" r:id="rId46"/>
     <sheet name="Bucktown" sheetId="47" r:id="rId47"/>
     <sheet name="Calumet Heights" sheetId="48" r:id="rId48"/>
     <sheet name="Edgewater" sheetId="49" r:id="rId49"/>
@@ -2146,41 +2146,38 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2">
-        <v>5</v>
-      </c>
       <c r="C2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D2">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H2">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J2">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K2">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M2">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -2188,56 +2185,56 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D3">
+        <v>7</v>
+      </c>
+      <c r="E3">
+        <v>3</v>
+      </c>
+      <c r="F3">
+        <v>4</v>
+      </c>
+      <c r="G3">
         <v>8</v>
       </c>
-      <c r="E3">
-        <v>9</v>
-      </c>
-      <c r="F3">
-        <v>19</v>
-      </c>
-      <c r="G3">
-        <v>9</v>
-      </c>
       <c r="H3">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="I3">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="J3">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="K3">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="L3">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="M3">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="I4">
-        <v>1</v>
-      </c>
-      <c r="M4">
+      <c r="H4">
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="B5">
+        <v>1</v>
       </c>
       <c r="K5">
         <v>1</v>
@@ -2245,36 +2242,30 @@
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="E6">
-        <v>1</v>
-      </c>
-      <c r="F6">
-        <v>2</v>
-      </c>
-      <c r="J6">
-        <v>2</v>
-      </c>
-      <c r="M6">
+        <v>6</v>
+      </c>
+      <c r="G6">
+        <v>1</v>
+      </c>
+      <c r="H6">
+        <v>1</v>
+      </c>
+      <c r="I6">
         <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="D7">
+        <v>1</v>
       </c>
       <c r="E7">
         <v>1</v>
       </c>
-      <c r="I7">
-        <v>1</v>
-      </c>
-      <c r="K7">
-        <v>1</v>
-      </c>
-      <c r="L7">
-        <v>1</v>
+      <c r="J7">
+        <v>2</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -2282,40 +2273,40 @@
         <v>8</v>
       </c>
       <c r="B8">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="C8">
-        <v>37</v>
+        <v>9</v>
       </c>
       <c r="D8">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="E8">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="F8">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="G8">
         <v>15</v>
       </c>
       <c r="H8">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="I8">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="J8">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="K8">
-        <v>49</v>
+        <v>18</v>
       </c>
       <c r="L8">
-        <v>44</v>
+        <v>19</v>
       </c>
       <c r="M8">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -2323,40 +2314,40 @@
         <v>9</v>
       </c>
       <c r="B9">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C9">
-        <v>64</v>
+        <v>46</v>
       </c>
       <c r="D9">
-        <v>46</v>
+        <v>32</v>
       </c>
       <c r="E9">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="F9">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="G9">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="H9">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="I9">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="J9">
         <v>20</v>
       </c>
       <c r="K9">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="L9">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="M9">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -2364,40 +2355,40 @@
         <v>10</v>
       </c>
       <c r="B10">
-        <v>77</v>
+        <v>51</v>
       </c>
       <c r="C10">
-        <v>106</v>
+        <v>57</v>
       </c>
       <c r="D10">
-        <v>82</v>
+        <v>62</v>
       </c>
       <c r="E10">
-        <v>88</v>
+        <v>48</v>
       </c>
       <c r="F10">
-        <v>91</v>
+        <v>60</v>
       </c>
       <c r="G10">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="H10">
-        <v>66</v>
+        <v>31</v>
       </c>
       <c r="I10">
-        <v>77</v>
+        <v>44</v>
       </c>
       <c r="J10">
-        <v>67</v>
+        <v>43</v>
       </c>
       <c r="K10">
-        <v>110</v>
+        <v>57</v>
       </c>
       <c r="L10">
-        <v>98</v>
+        <v>40</v>
       </c>
       <c r="M10">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
   </sheetData>
@@ -2407,7 +2398,7 @@
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M10"/>
+  <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="23.7109375" customWidth="1"/>
@@ -2470,38 +2461,29 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C2">
-        <v>1</v>
-      </c>
       <c r="D2">
-        <v>5</v>
-      </c>
-      <c r="E2">
         <v>1</v>
       </c>
       <c r="F2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G2">
         <v>1</v>
       </c>
-      <c r="H2">
-        <v>3</v>
-      </c>
       <c r="I2">
         <v>2</v>
       </c>
       <c r="J2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K2">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="L2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M2">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -2509,210 +2491,153 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C3">
         <v>1</v>
       </c>
-      <c r="D3">
-        <v>7</v>
-      </c>
-      <c r="E3">
-        <v>3</v>
-      </c>
-      <c r="F3">
-        <v>4</v>
-      </c>
       <c r="G3">
-        <v>8</v>
-      </c>
-      <c r="H3">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I3">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="J3">
-        <v>4</v>
-      </c>
-      <c r="K3">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="L3">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="M3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="H4">
+        <v>5</v>
+      </c>
+      <c r="E4">
+        <v>2</v>
+      </c>
+      <c r="J4">
+        <v>1</v>
+      </c>
+      <c r="K4">
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B5">
         <v>1</v>
       </c>
+      <c r="C5">
+        <v>1</v>
+      </c>
+      <c r="D5">
+        <v>2</v>
+      </c>
+      <c r="E5">
+        <v>2</v>
+      </c>
+      <c r="G5">
+        <v>1</v>
+      </c>
+      <c r="I5">
+        <v>1</v>
+      </c>
+      <c r="J5">
+        <v>3</v>
+      </c>
       <c r="K5">
+        <v>4</v>
+      </c>
+      <c r="M5">
         <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
-        <v>6</v>
+        <v>9</v>
+      </c>
+      <c r="B6">
+        <v>8</v>
+      </c>
+      <c r="C6">
+        <v>13</v>
+      </c>
+      <c r="D6">
+        <v>10</v>
+      </c>
+      <c r="E6">
+        <v>9</v>
+      </c>
+      <c r="F6">
+        <v>9</v>
       </c>
       <c r="G6">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="H6">
         <v>1</v>
       </c>
       <c r="I6">
-        <v>1</v>
+        <v>4</v>
+      </c>
+      <c r="J6">
+        <v>5</v>
+      </c>
+      <c r="K6">
+        <v>8</v>
+      </c>
+      <c r="L6">
+        <v>3</v>
+      </c>
+      <c r="M6">
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="1" t="s">
-        <v>7</v>
+        <v>10</v>
+      </c>
+      <c r="B7">
+        <v>10</v>
+      </c>
+      <c r="C7">
+        <v>15</v>
       </c>
       <c r="D7">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="E7">
-        <v>1</v>
+        <v>13</v>
+      </c>
+      <c r="F7">
+        <v>10</v>
+      </c>
+      <c r="G7">
+        <v>12</v>
+      </c>
+      <c r="H7">
+        <v>1</v>
+      </c>
+      <c r="I7">
+        <v>8</v>
       </c>
       <c r="J7">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13">
-      <c r="A8" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B8">
-        <v>5</v>
-      </c>
-      <c r="C8">
-        <v>9</v>
-      </c>
-      <c r="D8">
-        <v>17</v>
-      </c>
-      <c r="E8">
-        <v>13</v>
-      </c>
-      <c r="F8">
-        <v>19</v>
-      </c>
-      <c r="G8">
+        <v>14</v>
+      </c>
+      <c r="K7">
         <v>15</v>
       </c>
-      <c r="H8">
-        <v>5</v>
-      </c>
-      <c r="I8">
-        <v>15</v>
-      </c>
-      <c r="J8">
-        <v>12</v>
-      </c>
-      <c r="K8">
-        <v>18</v>
-      </c>
-      <c r="L8">
-        <v>19</v>
-      </c>
-      <c r="M8">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13">
-      <c r="A9" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B9">
-        <v>43</v>
-      </c>
-      <c r="C9">
-        <v>46</v>
-      </c>
-      <c r="D9">
-        <v>32</v>
-      </c>
-      <c r="E9">
-        <v>30</v>
-      </c>
-      <c r="F9">
-        <v>34</v>
-      </c>
-      <c r="G9">
-        <v>15</v>
-      </c>
-      <c r="H9">
-        <v>17</v>
-      </c>
-      <c r="I9">
-        <v>20</v>
-      </c>
-      <c r="J9">
-        <v>20</v>
-      </c>
-      <c r="K9">
-        <v>20</v>
-      </c>
-      <c r="L9">
-        <v>13</v>
-      </c>
-      <c r="M9">
+      <c r="L7">
         <v>6</v>
       </c>
-    </row>
-    <row r="10" spans="1:13">
-      <c r="A10" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B10">
-        <v>51</v>
-      </c>
-      <c r="C10">
-        <v>57</v>
-      </c>
-      <c r="D10">
-        <v>62</v>
-      </c>
-      <c r="E10">
-        <v>48</v>
-      </c>
-      <c r="F10">
-        <v>60</v>
-      </c>
-      <c r="G10">
-        <v>40</v>
-      </c>
-      <c r="H10">
-        <v>31</v>
-      </c>
-      <c r="I10">
-        <v>44</v>
-      </c>
-      <c r="J10">
-        <v>43</v>
-      </c>
-      <c r="K10">
-        <v>57</v>
-      </c>
-      <c r="L10">
-        <v>40</v>
-      </c>
-      <c r="M10">
-        <v>17</v>
+      <c r="M7">
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -2722,10 +2647,10 @@
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M10"/>
+  <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="1" max="1" width="18.7109375" customWidth="1"/>
     <col min="2" max="2" width="4.7109375" customWidth="1"/>
     <col min="3" max="3" width="4.7109375" customWidth="1"/>
     <col min="4" max="4" width="4.7109375" customWidth="1"/>
@@ -2785,41 +2710,29 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2">
-        <v>4</v>
-      </c>
       <c r="C2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E2">
-        <v>5</v>
-      </c>
-      <c r="F2">
-        <v>9</v>
-      </c>
-      <c r="G2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H2">
-        <v>5</v>
-      </c>
-      <c r="I2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J2">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="K2">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="L2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="M2">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -2827,210 +2740,162 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C3">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D3">
-        <v>6</v>
-      </c>
-      <c r="E3">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="F3">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G3">
-        <v>7</v>
-      </c>
-      <c r="H3">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="I3">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J3">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="K3">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="L3">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="M3">
-        <v>10</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="I4">
+        <v>6</v>
+      </c>
+      <c r="H4">
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B5">
-        <v>1</v>
+        <v>7</v>
+      </c>
+      <c r="C5">
+        <v>11</v>
       </c>
       <c r="D5">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E5">
-        <v>1</v>
+        <v>5</v>
+      </c>
+      <c r="F5">
+        <v>5</v>
+      </c>
+      <c r="G5">
+        <v>6</v>
+      </c>
+      <c r="H5">
+        <v>2</v>
+      </c>
+      <c r="I5">
+        <v>2</v>
       </c>
       <c r="J5">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K5">
-        <v>2</v>
-      </c>
-      <c r="M5">
-        <v>1</v>
+        <v>6</v>
+      </c>
+      <c r="L5">
+        <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6">
+        <v>15</v>
+      </c>
+      <c r="C6">
+        <v>16</v>
+      </c>
+      <c r="D6">
+        <v>15</v>
+      </c>
+      <c r="E6">
+        <v>16</v>
+      </c>
+      <c r="F6">
+        <v>11</v>
+      </c>
+      <c r="G6">
+        <v>9</v>
+      </c>
+      <c r="H6">
+        <v>5</v>
+      </c>
+      <c r="I6">
+        <v>5</v>
+      </c>
+      <c r="J6">
+        <v>12</v>
+      </c>
+      <c r="K6">
         <v>6</v>
       </c>
-      <c r="K6">
-        <v>1</v>
+      <c r="L6">
+        <v>4</v>
+      </c>
+      <c r="M6">
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="1" t="s">
-        <v>7</v>
+        <v>10</v>
+      </c>
+      <c r="B7">
+        <v>24</v>
+      </c>
+      <c r="C7">
+        <v>29</v>
+      </c>
+      <c r="D7">
+        <v>25</v>
+      </c>
+      <c r="E7">
+        <v>22</v>
+      </c>
+      <c r="F7">
+        <v>19</v>
+      </c>
+      <c r="G7">
+        <v>16</v>
+      </c>
+      <c r="H7">
+        <v>10</v>
+      </c>
+      <c r="I7">
+        <v>11</v>
+      </c>
+      <c r="J7">
+        <v>20</v>
+      </c>
+      <c r="K7">
+        <v>15</v>
       </c>
       <c r="L7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13">
-      <c r="A8" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B8">
-        <v>23</v>
-      </c>
-      <c r="C8">
-        <v>31</v>
-      </c>
-      <c r="D8">
-        <v>22</v>
-      </c>
-      <c r="E8">
-        <v>44</v>
-      </c>
-      <c r="F8">
-        <v>38</v>
-      </c>
-      <c r="G8">
-        <v>24</v>
-      </c>
-      <c r="H8">
-        <v>50</v>
-      </c>
-      <c r="I8">
-        <v>34</v>
-      </c>
-      <c r="J8">
-        <v>26</v>
-      </c>
-      <c r="K8">
-        <v>24</v>
-      </c>
-      <c r="L8">
-        <v>14</v>
-      </c>
-      <c r="M8">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13">
-      <c r="A9" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B9">
-        <v>46</v>
-      </c>
-      <c r="C9">
-        <v>59</v>
-      </c>
-      <c r="D9">
-        <v>33</v>
-      </c>
-      <c r="E9">
-        <v>73</v>
-      </c>
-      <c r="F9">
-        <v>114</v>
-      </c>
-      <c r="G9">
-        <v>58</v>
-      </c>
-      <c r="H9">
-        <v>41</v>
-      </c>
-      <c r="I9">
-        <v>44</v>
-      </c>
-      <c r="J9">
-        <v>20</v>
-      </c>
-      <c r="K9">
-        <v>25</v>
-      </c>
-      <c r="L9">
-        <v>27</v>
-      </c>
-      <c r="M9">
         <v>16</v>
       </c>
-    </row>
-    <row r="10" spans="1:13">
-      <c r="A10" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B10">
-        <v>78</v>
-      </c>
-      <c r="C10">
-        <v>99</v>
-      </c>
-      <c r="D10">
-        <v>65</v>
-      </c>
-      <c r="E10">
-        <v>130</v>
-      </c>
-      <c r="F10">
-        <v>167</v>
-      </c>
-      <c r="G10">
-        <v>92</v>
-      </c>
-      <c r="H10">
-        <v>104</v>
-      </c>
-      <c r="I10">
-        <v>89</v>
-      </c>
-      <c r="J10">
-        <v>67</v>
-      </c>
-      <c r="K10">
-        <v>71</v>
-      </c>
-      <c r="L10">
-        <v>61</v>
-      </c>
-      <c r="M10">
-        <v>50</v>
+      <c r="M7">
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -3106,25 +2971,7 @@
       <c r="D2">
         <v>1</v>
       </c>
-      <c r="F2">
-        <v>1</v>
-      </c>
-      <c r="G2">
-        <v>1</v>
-      </c>
-      <c r="I2">
-        <v>2</v>
-      </c>
       <c r="J2">
-        <v>4</v>
-      </c>
-      <c r="K2">
-        <v>2</v>
-      </c>
-      <c r="L2">
-        <v>2</v>
-      </c>
-      <c r="M2">
         <v>1</v>
       </c>
     </row>
@@ -3132,25 +2979,16 @@
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B3">
-        <v>1</v>
-      </c>
-      <c r="C3">
-        <v>1</v>
+      <c r="E3">
+        <v>2</v>
       </c>
       <c r="G3">
-        <v>2</v>
-      </c>
-      <c r="I3">
         <v>1</v>
       </c>
       <c r="J3">
         <v>1</v>
       </c>
       <c r="L3">
-        <v>1</v>
-      </c>
-      <c r="M3">
         <v>1</v>
       </c>
     </row>
@@ -3158,13 +2996,7 @@
       <c r="A4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="E4">
-        <v>2</v>
-      </c>
-      <c r="J4">
-        <v>1</v>
-      </c>
-      <c r="K4">
+      <c r="C4">
         <v>1</v>
       </c>
     </row>
@@ -3173,28 +3005,22 @@
         <v>8</v>
       </c>
       <c r="B5">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C5">
-        <v>1</v>
-      </c>
-      <c r="D5">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E5">
-        <v>2</v>
-      </c>
-      <c r="G5">
-        <v>1</v>
-      </c>
-      <c r="I5">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="H5">
+        <v>2</v>
       </c>
       <c r="J5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M5">
         <v>1</v>
@@ -3205,40 +3031,40 @@
         <v>9</v>
       </c>
       <c r="B6">
+        <v>6</v>
+      </c>
+      <c r="C6">
+        <v>2</v>
+      </c>
+      <c r="D6">
+        <v>6</v>
+      </c>
+      <c r="E6">
         <v>8</v>
       </c>
-      <c r="C6">
-        <v>13</v>
-      </c>
-      <c r="D6">
-        <v>10</v>
-      </c>
-      <c r="E6">
-        <v>9</v>
-      </c>
       <c r="F6">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G6">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="H6">
         <v>1</v>
       </c>
       <c r="I6">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J6">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K6">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="L6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -3246,40 +3072,40 @@
         <v>10</v>
       </c>
       <c r="B7">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C7">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="D7">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="E7">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F7">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G7">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="H7">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I7">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="J7">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="K7">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="L7">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="M7">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -3288,474 +3114,6 @@
 </file>
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M7"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="18.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" customWidth="1"/>
-    <col min="13" max="13" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="M1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2">
-        <v>1</v>
-      </c>
-      <c r="D2">
-        <v>1</v>
-      </c>
-      <c r="E2">
-        <v>1</v>
-      </c>
-      <c r="H2">
-        <v>2</v>
-      </c>
-      <c r="J2">
-        <v>1</v>
-      </c>
-      <c r="K2">
-        <v>2</v>
-      </c>
-      <c r="L2">
-        <v>2</v>
-      </c>
-      <c r="M2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3">
-        <v>2</v>
-      </c>
-      <c r="C3">
-        <v>1</v>
-      </c>
-      <c r="D3">
-        <v>1</v>
-      </c>
-      <c r="F3">
-        <v>3</v>
-      </c>
-      <c r="G3">
-        <v>1</v>
-      </c>
-      <c r="I3">
-        <v>4</v>
-      </c>
-      <c r="J3">
-        <v>2</v>
-      </c>
-      <c r="K3">
-        <v>1</v>
-      </c>
-      <c r="L3">
-        <v>4</v>
-      </c>
-      <c r="M3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5">
-        <v>7</v>
-      </c>
-      <c r="C5">
-        <v>11</v>
-      </c>
-      <c r="D5">
-        <v>8</v>
-      </c>
-      <c r="E5">
-        <v>5</v>
-      </c>
-      <c r="F5">
-        <v>5</v>
-      </c>
-      <c r="G5">
-        <v>6</v>
-      </c>
-      <c r="H5">
-        <v>2</v>
-      </c>
-      <c r="I5">
-        <v>2</v>
-      </c>
-      <c r="J5">
-        <v>5</v>
-      </c>
-      <c r="K5">
-        <v>6</v>
-      </c>
-      <c r="L5">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B6">
-        <v>15</v>
-      </c>
-      <c r="C6">
-        <v>16</v>
-      </c>
-      <c r="D6">
-        <v>15</v>
-      </c>
-      <c r="E6">
-        <v>16</v>
-      </c>
-      <c r="F6">
-        <v>11</v>
-      </c>
-      <c r="G6">
-        <v>9</v>
-      </c>
-      <c r="H6">
-        <v>5</v>
-      </c>
-      <c r="I6">
-        <v>5</v>
-      </c>
-      <c r="J6">
-        <v>12</v>
-      </c>
-      <c r="K6">
-        <v>6</v>
-      </c>
-      <c r="L6">
-        <v>4</v>
-      </c>
-      <c r="M6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
-      <c r="A7" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B7">
-        <v>24</v>
-      </c>
-      <c r="C7">
-        <v>29</v>
-      </c>
-      <c r="D7">
-        <v>25</v>
-      </c>
-      <c r="E7">
-        <v>22</v>
-      </c>
-      <c r="F7">
-        <v>19</v>
-      </c>
-      <c r="G7">
-        <v>16</v>
-      </c>
-      <c r="H7">
-        <v>10</v>
-      </c>
-      <c r="I7">
-        <v>11</v>
-      </c>
-      <c r="J7">
-        <v>20</v>
-      </c>
-      <c r="K7">
-        <v>15</v>
-      </c>
-      <c r="L7">
-        <v>16</v>
-      </c>
-      <c r="M7">
-        <v>6</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M7"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" customWidth="1"/>
-    <col min="13" max="13" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="M1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D2">
-        <v>1</v>
-      </c>
-      <c r="J2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="E3">
-        <v>2</v>
-      </c>
-      <c r="G3">
-        <v>1</v>
-      </c>
-      <c r="J3">
-        <v>1</v>
-      </c>
-      <c r="L3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5">
-        <v>5</v>
-      </c>
-      <c r="C5">
-        <v>6</v>
-      </c>
-      <c r="E5">
-        <v>1</v>
-      </c>
-      <c r="H5">
-        <v>2</v>
-      </c>
-      <c r="J5">
-        <v>4</v>
-      </c>
-      <c r="K5">
-        <v>2</v>
-      </c>
-      <c r="M5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B6">
-        <v>6</v>
-      </c>
-      <c r="C6">
-        <v>2</v>
-      </c>
-      <c r="D6">
-        <v>6</v>
-      </c>
-      <c r="E6">
-        <v>8</v>
-      </c>
-      <c r="F6">
-        <v>7</v>
-      </c>
-      <c r="G6">
-        <v>2</v>
-      </c>
-      <c r="H6">
-        <v>1</v>
-      </c>
-      <c r="I6">
-        <v>1</v>
-      </c>
-      <c r="J6">
-        <v>3</v>
-      </c>
-      <c r="K6">
-        <v>1</v>
-      </c>
-      <c r="L6">
-        <v>2</v>
-      </c>
-      <c r="M6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
-      <c r="A7" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B7">
-        <v>11</v>
-      </c>
-      <c r="C7">
-        <v>9</v>
-      </c>
-      <c r="D7">
-        <v>7</v>
-      </c>
-      <c r="E7">
-        <v>11</v>
-      </c>
-      <c r="F7">
-        <v>7</v>
-      </c>
-      <c r="G7">
-        <v>3</v>
-      </c>
-      <c r="H7">
-        <v>3</v>
-      </c>
-      <c r="I7">
-        <v>1</v>
-      </c>
-      <c r="J7">
-        <v>9</v>
-      </c>
-      <c r="K7">
-        <v>3</v>
-      </c>
-      <c r="L7">
-        <v>3</v>
-      </c>
-      <c r="M7">
-        <v>2</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:L8"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -3926,6 +3284,656 @@
       </c>
       <c r="L8">
         <v>2</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:M10"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+    <col min="13" max="13" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="M1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>6</v>
+      </c>
+      <c r="C2">
+        <v>3</v>
+      </c>
+      <c r="D2">
+        <v>12</v>
+      </c>
+      <c r="E2">
+        <v>5</v>
+      </c>
+      <c r="F2">
+        <v>8</v>
+      </c>
+      <c r="G2">
+        <v>4</v>
+      </c>
+      <c r="H2">
+        <v>13</v>
+      </c>
+      <c r="I2">
+        <v>14</v>
+      </c>
+      <c r="J2">
+        <v>22</v>
+      </c>
+      <c r="K2">
+        <v>15</v>
+      </c>
+      <c r="L2">
+        <v>15</v>
+      </c>
+      <c r="M2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>13</v>
+      </c>
+      <c r="C3">
+        <v>13</v>
+      </c>
+      <c r="D3">
+        <v>17</v>
+      </c>
+      <c r="E3">
+        <v>18</v>
+      </c>
+      <c r="F3">
+        <v>14</v>
+      </c>
+      <c r="G3">
+        <v>26</v>
+      </c>
+      <c r="H3">
+        <v>23</v>
+      </c>
+      <c r="I3">
+        <v>32</v>
+      </c>
+      <c r="J3">
+        <v>40</v>
+      </c>
+      <c r="K3">
+        <v>26</v>
+      </c>
+      <c r="L3">
+        <v>34</v>
+      </c>
+      <c r="M3">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G4">
+        <v>1</v>
+      </c>
+      <c r="J4">
+        <v>2</v>
+      </c>
+      <c r="K4">
+        <v>1</v>
+      </c>
+      <c r="L4">
+        <v>1</v>
+      </c>
+      <c r="M4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C5">
+        <v>2</v>
+      </c>
+      <c r="D5">
+        <v>1</v>
+      </c>
+      <c r="E5">
+        <v>2</v>
+      </c>
+      <c r="F5">
+        <v>1</v>
+      </c>
+      <c r="H5">
+        <v>2</v>
+      </c>
+      <c r="I5">
+        <v>4</v>
+      </c>
+      <c r="J5">
+        <v>3</v>
+      </c>
+      <c r="K5">
+        <v>2</v>
+      </c>
+      <c r="L5">
+        <v>5</v>
+      </c>
+      <c r="M5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G6">
+        <v>1</v>
+      </c>
+      <c r="H6">
+        <v>2</v>
+      </c>
+      <c r="J6">
+        <v>2</v>
+      </c>
+      <c r="L6">
+        <v>2</v>
+      </c>
+      <c r="M6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="K7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13">
+      <c r="A8" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8">
+        <v>30</v>
+      </c>
+      <c r="C8">
+        <v>44</v>
+      </c>
+      <c r="D8">
+        <v>49</v>
+      </c>
+      <c r="E8">
+        <v>67</v>
+      </c>
+      <c r="F8">
+        <v>69</v>
+      </c>
+      <c r="G8">
+        <v>57</v>
+      </c>
+      <c r="H8">
+        <v>80</v>
+      </c>
+      <c r="I8">
+        <v>80</v>
+      </c>
+      <c r="J8">
+        <v>64</v>
+      </c>
+      <c r="K8">
+        <v>48</v>
+      </c>
+      <c r="L8">
+        <v>44</v>
+      </c>
+      <c r="M8">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13">
+      <c r="A9" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B9">
+        <v>233</v>
+      </c>
+      <c r="C9">
+        <v>354</v>
+      </c>
+      <c r="D9">
+        <v>538</v>
+      </c>
+      <c r="E9">
+        <v>705</v>
+      </c>
+      <c r="F9">
+        <v>568</v>
+      </c>
+      <c r="G9">
+        <v>168</v>
+      </c>
+      <c r="H9">
+        <v>116</v>
+      </c>
+      <c r="I9">
+        <v>194</v>
+      </c>
+      <c r="J9">
+        <v>122</v>
+      </c>
+      <c r="K9">
+        <v>114</v>
+      </c>
+      <c r="L9">
+        <v>95</v>
+      </c>
+      <c r="M9">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13">
+      <c r="A10" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B10">
+        <v>282</v>
+      </c>
+      <c r="C10">
+        <v>416</v>
+      </c>
+      <c r="D10">
+        <v>617</v>
+      </c>
+      <c r="E10">
+        <v>797</v>
+      </c>
+      <c r="F10">
+        <v>660</v>
+      </c>
+      <c r="G10">
+        <v>257</v>
+      </c>
+      <c r="H10">
+        <v>236</v>
+      </c>
+      <c r="I10">
+        <v>324</v>
+      </c>
+      <c r="J10">
+        <v>255</v>
+      </c>
+      <c r="K10">
+        <v>207</v>
+      </c>
+      <c r="L10">
+        <v>196</v>
+      </c>
+      <c r="M10">
+        <v>88</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:M8"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+    <col min="13" max="13" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="M1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>4</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="E2">
+        <v>4</v>
+      </c>
+      <c r="F2">
+        <v>2</v>
+      </c>
+      <c r="G2">
+        <v>4</v>
+      </c>
+      <c r="H2">
+        <v>2</v>
+      </c>
+      <c r="I2">
+        <v>3</v>
+      </c>
+      <c r="J2">
+        <v>2</v>
+      </c>
+      <c r="K2">
+        <v>6</v>
+      </c>
+      <c r="L2">
+        <v>6</v>
+      </c>
+      <c r="M2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>2</v>
+      </c>
+      <c r="C3">
+        <v>4</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
+      <c r="E3">
+        <v>4</v>
+      </c>
+      <c r="F3">
+        <v>5</v>
+      </c>
+      <c r="G3">
+        <v>4</v>
+      </c>
+      <c r="H3">
+        <v>7</v>
+      </c>
+      <c r="I3">
+        <v>2</v>
+      </c>
+      <c r="J3">
+        <v>11</v>
+      </c>
+      <c r="K3">
+        <v>5</v>
+      </c>
+      <c r="L3">
+        <v>7</v>
+      </c>
+      <c r="M3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="H4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C5">
+        <v>1</v>
+      </c>
+      <c r="H5">
+        <v>1</v>
+      </c>
+      <c r="I5">
+        <v>1</v>
+      </c>
+      <c r="K5">
+        <v>3</v>
+      </c>
+      <c r="L5">
+        <v>2</v>
+      </c>
+      <c r="M5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C6">
+        <v>14</v>
+      </c>
+      <c r="D6">
+        <v>12</v>
+      </c>
+      <c r="E6">
+        <v>10</v>
+      </c>
+      <c r="F6">
+        <v>11</v>
+      </c>
+      <c r="G6">
+        <v>11</v>
+      </c>
+      <c r="H6">
+        <v>17</v>
+      </c>
+      <c r="I6">
+        <v>20</v>
+      </c>
+      <c r="J6">
+        <v>3</v>
+      </c>
+      <c r="K6">
+        <v>10</v>
+      </c>
+      <c r="L6">
+        <v>5</v>
+      </c>
+      <c r="M6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7">
+        <v>58</v>
+      </c>
+      <c r="C7">
+        <v>53</v>
+      </c>
+      <c r="D7">
+        <v>43</v>
+      </c>
+      <c r="E7">
+        <v>56</v>
+      </c>
+      <c r="F7">
+        <v>53</v>
+      </c>
+      <c r="G7">
+        <v>33</v>
+      </c>
+      <c r="H7">
+        <v>23</v>
+      </c>
+      <c r="I7">
+        <v>26</v>
+      </c>
+      <c r="J7">
+        <v>27</v>
+      </c>
+      <c r="K7">
+        <v>17</v>
+      </c>
+      <c r="L7">
+        <v>19</v>
+      </c>
+      <c r="M7">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13">
+      <c r="A8" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B8">
+        <v>60</v>
+      </c>
+      <c r="C8">
+        <v>76</v>
+      </c>
+      <c r="D8">
+        <v>57</v>
+      </c>
+      <c r="E8">
+        <v>74</v>
+      </c>
+      <c r="F8">
+        <v>71</v>
+      </c>
+      <c r="G8">
+        <v>52</v>
+      </c>
+      <c r="H8">
+        <v>51</v>
+      </c>
+      <c r="I8">
+        <v>52</v>
+      </c>
+      <c r="J8">
+        <v>43</v>
+      </c>
+      <c r="K8">
+        <v>41</v>
+      </c>
+      <c r="L8">
+        <v>39</v>
+      </c>
+      <c r="M8">
+        <v>25</v>
       </c>
     </row>
   </sheetData>
@@ -7892,40 +7900,40 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D2">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="E2">
         <v>5</v>
       </c>
       <c r="F2">
+        <v>9</v>
+      </c>
+      <c r="G2">
+        <v>3</v>
+      </c>
+      <c r="H2">
+        <v>5</v>
+      </c>
+      <c r="I2">
+        <v>4</v>
+      </c>
+      <c r="J2">
         <v>8</v>
       </c>
-      <c r="G2">
-        <v>4</v>
-      </c>
-      <c r="H2">
-        <v>13</v>
-      </c>
-      <c r="I2">
-        <v>14</v>
-      </c>
-      <c r="J2">
-        <v>22</v>
-      </c>
       <c r="K2">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="L2">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="M2">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -7933,59 +7941,47 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="C3">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="D3">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="E3">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="F3">
+        <v>6</v>
+      </c>
+      <c r="G3">
+        <v>7</v>
+      </c>
+      <c r="H3">
+        <v>8</v>
+      </c>
+      <c r="I3">
+        <v>6</v>
+      </c>
+      <c r="J3">
+        <v>10</v>
+      </c>
+      <c r="K3">
+        <v>12</v>
+      </c>
+      <c r="L3">
         <v>14</v>
       </c>
-      <c r="G3">
-        <v>26</v>
-      </c>
-      <c r="H3">
-        <v>23</v>
-      </c>
-      <c r="I3">
-        <v>32</v>
-      </c>
-      <c r="J3">
-        <v>40</v>
-      </c>
-      <c r="K3">
-        <v>26</v>
-      </c>
-      <c r="L3">
-        <v>34</v>
-      </c>
       <c r="M3">
-        <v>16</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="G4">
-        <v>1</v>
-      </c>
-      <c r="J4">
-        <v>2</v>
-      </c>
-      <c r="K4">
-        <v>1</v>
-      </c>
-      <c r="L4">
-        <v>1</v>
-      </c>
-      <c r="M4">
+      <c r="I4">
         <v>1</v>
       </c>
     </row>
@@ -7993,23 +7989,14 @@
       <c r="A5" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C5">
-        <v>2</v>
+      <c r="B5">
+        <v>1</v>
       </c>
       <c r="D5">
         <v>1</v>
       </c>
       <c r="E5">
-        <v>2</v>
-      </c>
-      <c r="F5">
-        <v>1</v>
-      </c>
-      <c r="H5">
-        <v>2</v>
-      </c>
-      <c r="I5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J5">
         <v>3</v>
@@ -8017,30 +8004,15 @@
       <c r="K5">
         <v>2</v>
       </c>
-      <c r="L5">
-        <v>5</v>
-      </c>
       <c r="M5">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="G6">
-        <v>1</v>
-      </c>
-      <c r="H6">
-        <v>2</v>
-      </c>
-      <c r="J6">
-        <v>2</v>
-      </c>
-      <c r="L6">
-        <v>2</v>
-      </c>
-      <c r="M6">
+      <c r="K6">
         <v>1</v>
       </c>
     </row>
@@ -8048,7 +8020,7 @@
       <c r="A7" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="K7">
+      <c r="L7">
         <v>1</v>
       </c>
     </row>
@@ -8057,40 +8029,40 @@
         <v>8</v>
       </c>
       <c r="B8">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="C8">
+        <v>31</v>
+      </c>
+      <c r="D8">
+        <v>22</v>
+      </c>
+      <c r="E8">
         <v>44</v>
       </c>
-      <c r="D8">
-        <v>49</v>
-      </c>
-      <c r="E8">
-        <v>67</v>
-      </c>
       <c r="F8">
-        <v>69</v>
+        <v>38</v>
       </c>
       <c r="G8">
-        <v>57</v>
+        <v>24</v>
       </c>
       <c r="H8">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="I8">
-        <v>80</v>
+        <v>34</v>
       </c>
       <c r="J8">
-        <v>64</v>
+        <v>26</v>
       </c>
       <c r="K8">
-        <v>48</v>
+        <v>24</v>
       </c>
       <c r="L8">
-        <v>44</v>
+        <v>14</v>
       </c>
       <c r="M8">
-        <v>19</v>
+        <v>14</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -8098,40 +8070,40 @@
         <v>9</v>
       </c>
       <c r="B9">
-        <v>233</v>
+        <v>46</v>
       </c>
       <c r="C9">
-        <v>354</v>
+        <v>59</v>
       </c>
       <c r="D9">
-        <v>538</v>
+        <v>33</v>
       </c>
       <c r="E9">
-        <v>705</v>
+        <v>73</v>
       </c>
       <c r="F9">
-        <v>568</v>
+        <v>114</v>
       </c>
       <c r="G9">
-        <v>168</v>
+        <v>58</v>
       </c>
       <c r="H9">
-        <v>116</v>
+        <v>41</v>
       </c>
       <c r="I9">
-        <v>194</v>
+        <v>44</v>
       </c>
       <c r="J9">
-        <v>122</v>
+        <v>20</v>
       </c>
       <c r="K9">
-        <v>114</v>
+        <v>25</v>
       </c>
       <c r="L9">
-        <v>95</v>
+        <v>27</v>
       </c>
       <c r="M9">
-        <v>45</v>
+        <v>16</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -8139,40 +8111,40 @@
         <v>10</v>
       </c>
       <c r="B10">
-        <v>282</v>
+        <v>78</v>
       </c>
       <c r="C10">
-        <v>416</v>
+        <v>99</v>
       </c>
       <c r="D10">
-        <v>617</v>
+        <v>65</v>
       </c>
       <c r="E10">
-        <v>797</v>
+        <v>130</v>
       </c>
       <c r="F10">
-        <v>660</v>
+        <v>167</v>
       </c>
       <c r="G10">
-        <v>257</v>
+        <v>92</v>
       </c>
       <c r="H10">
-        <v>236</v>
+        <v>104</v>
       </c>
       <c r="I10">
-        <v>324</v>
+        <v>89</v>
       </c>
       <c r="J10">
-        <v>255</v>
+        <v>67</v>
       </c>
       <c r="K10">
-        <v>207</v>
+        <v>71</v>
       </c>
       <c r="L10">
-        <v>196</v>
+        <v>61</v>
       </c>
       <c r="M10">
-        <v>88</v>
+        <v>50</v>
       </c>
     </row>
   </sheetData>
@@ -8181,302 +8153,6 @@
 </file>
 
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M8"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" customWidth="1"/>
-    <col min="13" max="13" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="M1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2">
-        <v>4</v>
-      </c>
-      <c r="D2">
-        <v>1</v>
-      </c>
-      <c r="E2">
-        <v>4</v>
-      </c>
-      <c r="F2">
-        <v>2</v>
-      </c>
-      <c r="G2">
-        <v>4</v>
-      </c>
-      <c r="H2">
-        <v>2</v>
-      </c>
-      <c r="I2">
-        <v>3</v>
-      </c>
-      <c r="J2">
-        <v>2</v>
-      </c>
-      <c r="K2">
-        <v>6</v>
-      </c>
-      <c r="L2">
-        <v>6</v>
-      </c>
-      <c r="M2">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3">
-        <v>2</v>
-      </c>
-      <c r="C3">
-        <v>4</v>
-      </c>
-      <c r="D3">
-        <v>1</v>
-      </c>
-      <c r="E3">
-        <v>4</v>
-      </c>
-      <c r="F3">
-        <v>5</v>
-      </c>
-      <c r="G3">
-        <v>4</v>
-      </c>
-      <c r="H3">
-        <v>7</v>
-      </c>
-      <c r="I3">
-        <v>2</v>
-      </c>
-      <c r="J3">
-        <v>11</v>
-      </c>
-      <c r="K3">
-        <v>5</v>
-      </c>
-      <c r="L3">
-        <v>7</v>
-      </c>
-      <c r="M3">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="H4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C5">
-        <v>1</v>
-      </c>
-      <c r="H5">
-        <v>1</v>
-      </c>
-      <c r="I5">
-        <v>1</v>
-      </c>
-      <c r="K5">
-        <v>3</v>
-      </c>
-      <c r="L5">
-        <v>2</v>
-      </c>
-      <c r="M5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C6">
-        <v>14</v>
-      </c>
-      <c r="D6">
-        <v>12</v>
-      </c>
-      <c r="E6">
-        <v>10</v>
-      </c>
-      <c r="F6">
-        <v>11</v>
-      </c>
-      <c r="G6">
-        <v>11</v>
-      </c>
-      <c r="H6">
-        <v>17</v>
-      </c>
-      <c r="I6">
-        <v>20</v>
-      </c>
-      <c r="J6">
-        <v>3</v>
-      </c>
-      <c r="K6">
-        <v>10</v>
-      </c>
-      <c r="L6">
-        <v>5</v>
-      </c>
-      <c r="M6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
-      <c r="A7" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B7">
-        <v>58</v>
-      </c>
-      <c r="C7">
-        <v>53</v>
-      </c>
-      <c r="D7">
-        <v>43</v>
-      </c>
-      <c r="E7">
-        <v>56</v>
-      </c>
-      <c r="F7">
-        <v>53</v>
-      </c>
-      <c r="G7">
-        <v>33</v>
-      </c>
-      <c r="H7">
-        <v>23</v>
-      </c>
-      <c r="I7">
-        <v>26</v>
-      </c>
-      <c r="J7">
-        <v>27</v>
-      </c>
-      <c r="K7">
-        <v>17</v>
-      </c>
-      <c r="L7">
-        <v>19</v>
-      </c>
-      <c r="M7">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13">
-      <c r="A8" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B8">
-        <v>60</v>
-      </c>
-      <c r="C8">
-        <v>76</v>
-      </c>
-      <c r="D8">
-        <v>57</v>
-      </c>
-      <c r="E8">
-        <v>74</v>
-      </c>
-      <c r="F8">
-        <v>71</v>
-      </c>
-      <c r="G8">
-        <v>52</v>
-      </c>
-      <c r="H8">
-        <v>51</v>
-      </c>
-      <c r="I8">
-        <v>52</v>
-      </c>
-      <c r="J8">
-        <v>43</v>
-      </c>
-      <c r="K8">
-        <v>41</v>
-      </c>
-      <c r="L8">
-        <v>39</v>
-      </c>
-      <c r="M8">
-        <v>25</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -8747,7 +8423,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:D4"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -8810,7 +8486,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M9"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -9077,6 +8753,330 @@
       </c>
       <c r="M9">
         <v>7</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:M10"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+    <col min="13" max="13" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="M1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>5</v>
+      </c>
+      <c r="C2">
+        <v>3</v>
+      </c>
+      <c r="D2">
+        <v>7</v>
+      </c>
+      <c r="E2">
+        <v>5</v>
+      </c>
+      <c r="F2">
+        <v>5</v>
+      </c>
+      <c r="G2">
+        <v>4</v>
+      </c>
+      <c r="H2">
+        <v>6</v>
+      </c>
+      <c r="I2">
+        <v>4</v>
+      </c>
+      <c r="J2">
+        <v>7</v>
+      </c>
+      <c r="K2">
+        <v>7</v>
+      </c>
+      <c r="L2">
+        <v>5</v>
+      </c>
+      <c r="M2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>3</v>
+      </c>
+      <c r="C3">
+        <v>2</v>
+      </c>
+      <c r="D3">
+        <v>8</v>
+      </c>
+      <c r="E3">
+        <v>9</v>
+      </c>
+      <c r="F3">
+        <v>19</v>
+      </c>
+      <c r="G3">
+        <v>9</v>
+      </c>
+      <c r="H3">
+        <v>8</v>
+      </c>
+      <c r="I3">
+        <v>13</v>
+      </c>
+      <c r="J3">
+        <v>12</v>
+      </c>
+      <c r="K3">
+        <v>17</v>
+      </c>
+      <c r="L3">
+        <v>13</v>
+      </c>
+      <c r="M3">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="I4">
+        <v>1</v>
+      </c>
+      <c r="M4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="K5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="E6">
+        <v>1</v>
+      </c>
+      <c r="F6">
+        <v>2</v>
+      </c>
+      <c r="J6">
+        <v>2</v>
+      </c>
+      <c r="M6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E7">
+        <v>1</v>
+      </c>
+      <c r="I7">
+        <v>1</v>
+      </c>
+      <c r="K7">
+        <v>1</v>
+      </c>
+      <c r="L7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13">
+      <c r="A8" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8">
+        <v>24</v>
+      </c>
+      <c r="C8">
+        <v>37</v>
+      </c>
+      <c r="D8">
+        <v>21</v>
+      </c>
+      <c r="E8">
+        <v>22</v>
+      </c>
+      <c r="F8">
+        <v>27</v>
+      </c>
+      <c r="G8">
+        <v>15</v>
+      </c>
+      <c r="H8">
+        <v>25</v>
+      </c>
+      <c r="I8">
+        <v>21</v>
+      </c>
+      <c r="J8">
+        <v>26</v>
+      </c>
+      <c r="K8">
+        <v>49</v>
+      </c>
+      <c r="L8">
+        <v>44</v>
+      </c>
+      <c r="M8">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13">
+      <c r="A9" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B9">
+        <v>45</v>
+      </c>
+      <c r="C9">
+        <v>64</v>
+      </c>
+      <c r="D9">
+        <v>46</v>
+      </c>
+      <c r="E9">
+        <v>50</v>
+      </c>
+      <c r="F9">
+        <v>38</v>
+      </c>
+      <c r="G9">
+        <v>19</v>
+      </c>
+      <c r="H9">
+        <v>27</v>
+      </c>
+      <c r="I9">
+        <v>37</v>
+      </c>
+      <c r="J9">
+        <v>20</v>
+      </c>
+      <c r="K9">
+        <v>35</v>
+      </c>
+      <c r="L9">
+        <v>35</v>
+      </c>
+      <c r="M9">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13">
+      <c r="A10" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B10">
+        <v>77</v>
+      </c>
+      <c r="C10">
+        <v>106</v>
+      </c>
+      <c r="D10">
+        <v>82</v>
+      </c>
+      <c r="E10">
+        <v>88</v>
+      </c>
+      <c r="F10">
+        <v>91</v>
+      </c>
+      <c r="G10">
+        <v>47</v>
+      </c>
+      <c r="H10">
+        <v>66</v>
+      </c>
+      <c r="I10">
+        <v>77</v>
+      </c>
+      <c r="J10">
+        <v>67</v>
+      </c>
+      <c r="K10">
+        <v>110</v>
+      </c>
+      <c r="L10">
+        <v>98</v>
+      </c>
+      <c r="M10">
+        <v>36</v>
       </c>
     </row>
   </sheetData>
@@ -14580,257 +14580,6 @@
 
 <file path=xl/worksheets/sheet44.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M8"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" customWidth="1"/>
-    <col min="13" max="13" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="M1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2">
-        <v>1</v>
-      </c>
-      <c r="D2">
-        <v>2</v>
-      </c>
-      <c r="F2">
-        <v>2</v>
-      </c>
-      <c r="I2">
-        <v>3</v>
-      </c>
-      <c r="J2">
-        <v>2</v>
-      </c>
-      <c r="K2">
-        <v>1</v>
-      </c>
-      <c r="L2">
-        <v>5</v>
-      </c>
-      <c r="M2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C3">
-        <v>1</v>
-      </c>
-      <c r="E3">
-        <v>1</v>
-      </c>
-      <c r="H3">
-        <v>2</v>
-      </c>
-      <c r="I3">
-        <v>1</v>
-      </c>
-      <c r="J3">
-        <v>1</v>
-      </c>
-      <c r="K3">
-        <v>2</v>
-      </c>
-      <c r="L3">
-        <v>2</v>
-      </c>
-      <c r="M3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C4">
-        <v>1</v>
-      </c>
-      <c r="I4">
-        <v>1</v>
-      </c>
-      <c r="K4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="L5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B6">
-        <v>1</v>
-      </c>
-      <c r="F6">
-        <v>4</v>
-      </c>
-      <c r="H6">
-        <v>1</v>
-      </c>
-      <c r="I6">
-        <v>2</v>
-      </c>
-      <c r="K6">
-        <v>1</v>
-      </c>
-      <c r="M6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
-      <c r="A7" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B7">
-        <v>10</v>
-      </c>
-      <c r="C7">
-        <v>20</v>
-      </c>
-      <c r="D7">
-        <v>25</v>
-      </c>
-      <c r="E7">
-        <v>30</v>
-      </c>
-      <c r="F7">
-        <v>41</v>
-      </c>
-      <c r="G7">
-        <v>10</v>
-      </c>
-      <c r="H7">
-        <v>5</v>
-      </c>
-      <c r="I7">
-        <v>5</v>
-      </c>
-      <c r="J7">
-        <v>15</v>
-      </c>
-      <c r="K7">
-        <v>17</v>
-      </c>
-      <c r="L7">
-        <v>12</v>
-      </c>
-      <c r="M7">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13">
-      <c r="A8" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B8">
-        <v>12</v>
-      </c>
-      <c r="C8">
-        <v>22</v>
-      </c>
-      <c r="D8">
-        <v>27</v>
-      </c>
-      <c r="E8">
-        <v>31</v>
-      </c>
-      <c r="F8">
-        <v>47</v>
-      </c>
-      <c r="G8">
-        <v>10</v>
-      </c>
-      <c r="H8">
-        <v>8</v>
-      </c>
-      <c r="I8">
-        <v>12</v>
-      </c>
-      <c r="J8">
-        <v>18</v>
-      </c>
-      <c r="K8">
-        <v>22</v>
-      </c>
-      <c r="L8">
-        <v>21</v>
-      </c>
-      <c r="M8">
-        <v>16</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet45.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -15108,7 +14857,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet46.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet45.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -15324,6 +15073,257 @@
       </c>
       <c r="M6">
         <v>3</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet46.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:M8"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+    <col min="13" max="13" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="M1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>2</v>
+      </c>
+      <c r="F2">
+        <v>2</v>
+      </c>
+      <c r="I2">
+        <v>3</v>
+      </c>
+      <c r="J2">
+        <v>2</v>
+      </c>
+      <c r="K2">
+        <v>1</v>
+      </c>
+      <c r="L2">
+        <v>5</v>
+      </c>
+      <c r="M2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
+      <c r="E3">
+        <v>1</v>
+      </c>
+      <c r="H3">
+        <v>2</v>
+      </c>
+      <c r="I3">
+        <v>1</v>
+      </c>
+      <c r="J3">
+        <v>1</v>
+      </c>
+      <c r="K3">
+        <v>2</v>
+      </c>
+      <c r="L3">
+        <v>2</v>
+      </c>
+      <c r="M3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
+      <c r="I4">
+        <v>1</v>
+      </c>
+      <c r="K4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="L5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6">
+        <v>1</v>
+      </c>
+      <c r="F6">
+        <v>4</v>
+      </c>
+      <c r="H6">
+        <v>1</v>
+      </c>
+      <c r="I6">
+        <v>2</v>
+      </c>
+      <c r="K6">
+        <v>1</v>
+      </c>
+      <c r="M6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7">
+        <v>10</v>
+      </c>
+      <c r="C7">
+        <v>20</v>
+      </c>
+      <c r="D7">
+        <v>25</v>
+      </c>
+      <c r="E7">
+        <v>30</v>
+      </c>
+      <c r="F7">
+        <v>41</v>
+      </c>
+      <c r="G7">
+        <v>10</v>
+      </c>
+      <c r="H7">
+        <v>5</v>
+      </c>
+      <c r="I7">
+        <v>5</v>
+      </c>
+      <c r="J7">
+        <v>15</v>
+      </c>
+      <c r="K7">
+        <v>17</v>
+      </c>
+      <c r="L7">
+        <v>12</v>
+      </c>
+      <c r="M7">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13">
+      <c r="A8" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B8">
+        <v>12</v>
+      </c>
+      <c r="C8">
+        <v>22</v>
+      </c>
+      <c r="D8">
+        <v>27</v>
+      </c>
+      <c r="E8">
+        <v>31</v>
+      </c>
+      <c r="F8">
+        <v>47</v>
+      </c>
+      <c r="G8">
+        <v>10</v>
+      </c>
+      <c r="H8">
+        <v>8</v>
+      </c>
+      <c r="I8">
+        <v>12</v>
+      </c>
+      <c r="J8">
+        <v>18</v>
+      </c>
+      <c r="K8">
+        <v>22</v>
+      </c>
+      <c r="L8">
+        <v>21</v>
+      </c>
+      <c r="M8">
+        <v>16</v>
       </c>
     </row>
   </sheetData>

--- a/output/cta-index-crime-full-year.xlsx
+++ b/output/cta-index-crime-full-year.xlsx
@@ -19,18 +19,18 @@
     <sheet name="Rogers Park" sheetId="10" r:id="rId10"/>
     <sheet name="Douglas" sheetId="11" r:id="rId11"/>
     <sheet name="Jefferson Park" sheetId="12" r:id="rId12"/>
-    <sheet name="Chatham" sheetId="13" r:id="rId13"/>
-    <sheet name="Albany Park" sheetId="14" r:id="rId14"/>
-    <sheet name="Grand Boulevard" sheetId="15" r:id="rId15"/>
-    <sheet name="Belmont Cragin" sheetId="16" r:id="rId16"/>
-    <sheet name="West Ridge" sheetId="17" r:id="rId17"/>
-    <sheet name="Loop" sheetId="18" r:id="rId18"/>
-    <sheet name="Lake View" sheetId="19" r:id="rId19"/>
-    <sheet name="Austin" sheetId="20" r:id="rId20"/>
-    <sheet name="South Shore" sheetId="21" r:id="rId21"/>
-    <sheet name="Mount Greenwood" sheetId="22" r:id="rId22"/>
-    <sheet name="Gage Park" sheetId="23" r:id="rId23"/>
-    <sheet name="Grand Crossing" sheetId="24" r:id="rId24"/>
+    <sheet name="Grand Crossing" sheetId="13" r:id="rId13"/>
+    <sheet name="Chatham" sheetId="14" r:id="rId14"/>
+    <sheet name="Austin" sheetId="15" r:id="rId15"/>
+    <sheet name="Albany Park" sheetId="16" r:id="rId16"/>
+    <sheet name="Grand Boulevard" sheetId="17" r:id="rId17"/>
+    <sheet name="Belmont Cragin" sheetId="18" r:id="rId18"/>
+    <sheet name="West Ridge" sheetId="19" r:id="rId19"/>
+    <sheet name="Loop" sheetId="20" r:id="rId20"/>
+    <sheet name="Lake View" sheetId="21" r:id="rId21"/>
+    <sheet name="South Shore" sheetId="22" r:id="rId22"/>
+    <sheet name="Mount Greenwood" sheetId="23" r:id="rId23"/>
+    <sheet name="Gage Park" sheetId="24" r:id="rId24"/>
     <sheet name="West Loop" sheetId="25" r:id="rId25"/>
     <sheet name="Rush &amp; Division" sheetId="26" r:id="rId26"/>
     <sheet name="North Lawndale" sheetId="27" r:id="rId27"/>
@@ -50,9 +50,9 @@
     <sheet name="Roseland" sheetId="41" r:id="rId41"/>
     <sheet name="Woodlawn" sheetId="42" r:id="rId42"/>
     <sheet name="Fuller Park" sheetId="43" r:id="rId43"/>
-    <sheet name="Little Italy, UIC" sheetId="44" r:id="rId44"/>
-    <sheet name="Hyde Park" sheetId="45" r:id="rId45"/>
-    <sheet name="O'Hare" sheetId="46" r:id="rId46"/>
+    <sheet name="O'Hare" sheetId="44" r:id="rId44"/>
+    <sheet name="Little Italy, UIC" sheetId="45" r:id="rId45"/>
+    <sheet name="Hyde Park" sheetId="46" r:id="rId46"/>
     <sheet name="Bucktown" sheetId="47" r:id="rId47"/>
     <sheet name="Calumet Heights" sheetId="48" r:id="rId48"/>
     <sheet name="Edgewater" sheetId="49" r:id="rId49"/>
@@ -71,28 +71,28 @@
     <sheet name="Avalon Park" sheetId="62" r:id="rId62"/>
     <sheet name="Brighton Park" sheetId="63" r:id="rId63"/>
     <sheet name="Lincoln Park" sheetId="64" r:id="rId64"/>
-    <sheet name="West Pullman" sheetId="65" r:id="rId65"/>
-    <sheet name="West Lawn" sheetId="66" r:id="rId66"/>
-    <sheet name="Little Village" sheetId="67" r:id="rId67"/>
-    <sheet name="Ukrainian Village" sheetId="68" r:id="rId68"/>
-    <sheet name="Archer Heights" sheetId="69" r:id="rId69"/>
-    <sheet name="Montclare" sheetId="70" r:id="rId70"/>
-    <sheet name="Old Town" sheetId="71" r:id="rId71"/>
-    <sheet name="Grant Park" sheetId="72" r:id="rId72"/>
-    <sheet name="West Elsdon" sheetId="73" r:id="rId73"/>
-    <sheet name="East Side" sheetId="74" r:id="rId74"/>
-    <sheet name="South Deering" sheetId="75" r:id="rId75"/>
-    <sheet name="Hermosa" sheetId="76" r:id="rId76"/>
-    <sheet name="Morgan Park" sheetId="77" r:id="rId77"/>
-    <sheet name="Boystown" sheetId="78" r:id="rId78"/>
-    <sheet name="Streeterville" sheetId="79" r:id="rId79"/>
-    <sheet name="Portage Park" sheetId="80" r:id="rId80"/>
-    <sheet name="Irving Park" sheetId="81" r:id="rId81"/>
-    <sheet name="Dunning" sheetId="82" r:id="rId82"/>
-    <sheet name="Clearing" sheetId="83" r:id="rId83"/>
-    <sheet name="Millenium Park" sheetId="84" r:id="rId84"/>
-    <sheet name="North Park" sheetId="85" r:id="rId85"/>
-    <sheet name="Printers Row" sheetId="86" r:id="rId86"/>
+    <sheet name="Printers Row" sheetId="65" r:id="rId65"/>
+    <sheet name="West Pullman" sheetId="66" r:id="rId66"/>
+    <sheet name="West Lawn" sheetId="67" r:id="rId67"/>
+    <sheet name="Little Village" sheetId="68" r:id="rId68"/>
+    <sheet name="Ukrainian Village" sheetId="69" r:id="rId69"/>
+    <sheet name="Archer Heights" sheetId="70" r:id="rId70"/>
+    <sheet name="Montclare" sheetId="71" r:id="rId71"/>
+    <sheet name="Old Town" sheetId="72" r:id="rId72"/>
+    <sheet name="Grant Park" sheetId="73" r:id="rId73"/>
+    <sheet name="West Elsdon" sheetId="74" r:id="rId74"/>
+    <sheet name="East Side" sheetId="75" r:id="rId75"/>
+    <sheet name="South Deering" sheetId="76" r:id="rId76"/>
+    <sheet name="Hermosa" sheetId="77" r:id="rId77"/>
+    <sheet name="Morgan Park" sheetId="78" r:id="rId78"/>
+    <sheet name="Boystown" sheetId="79" r:id="rId79"/>
+    <sheet name="Streeterville" sheetId="80" r:id="rId80"/>
+    <sheet name="Portage Park" sheetId="81" r:id="rId81"/>
+    <sheet name="Irving Park" sheetId="82" r:id="rId82"/>
+    <sheet name="Dunning" sheetId="83" r:id="rId83"/>
+    <sheet name="Clearing" sheetId="84" r:id="rId84"/>
+    <sheet name="Millenium Park" sheetId="85" r:id="rId85"/>
+    <sheet name="North Park" sheetId="86" r:id="rId86"/>
     <sheet name="Riverdale" sheetId="87" r:id="rId87"/>
     <sheet name="Gold Coast" sheetId="88" r:id="rId88"/>
     <sheet name="East Village" sheetId="89" r:id="rId89"/>
@@ -1156,7 +1156,7 @@
         <v>467</v>
       </c>
       <c r="M9">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -1197,7 +1197,7 @@
         <v>703</v>
       </c>
       <c r="M10">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -1238,7 +1238,7 @@
         <v>1604</v>
       </c>
       <c r="M11">
-        <v>791</v>
+        <v>793</v>
       </c>
     </row>
   </sheetData>
@@ -2146,38 +2146,41 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
+      <c r="B2">
+        <v>5</v>
+      </c>
       <c r="C2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D2">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H2">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J2">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="L2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M2">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -2185,56 +2188,56 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D3">
+        <v>8</v>
+      </c>
+      <c r="E3">
+        <v>9</v>
+      </c>
+      <c r="F3">
+        <v>19</v>
+      </c>
+      <c r="G3">
+        <v>9</v>
+      </c>
+      <c r="H3">
+        <v>8</v>
+      </c>
+      <c r="I3">
+        <v>13</v>
+      </c>
+      <c r="J3">
+        <v>12</v>
+      </c>
+      <c r="K3">
+        <v>17</v>
+      </c>
+      <c r="L3">
+        <v>13</v>
+      </c>
+      <c r="M3">
         <v>7</v>
-      </c>
-      <c r="E3">
-        <v>3</v>
-      </c>
-      <c r="F3">
-        <v>4</v>
-      </c>
-      <c r="G3">
-        <v>8</v>
-      </c>
-      <c r="H3">
-        <v>4</v>
-      </c>
-      <c r="I3">
-        <v>6</v>
-      </c>
-      <c r="J3">
-        <v>4</v>
-      </c>
-      <c r="K3">
-        <v>10</v>
-      </c>
-      <c r="L3">
-        <v>5</v>
-      </c>
-      <c r="M3">
-        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="H4">
+      <c r="I4">
+        <v>1</v>
+      </c>
+      <c r="M4">
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K5">
         <v>1</v>
@@ -2242,30 +2245,36 @@
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="G6">
-        <v>1</v>
-      </c>
-      <c r="H6">
-        <v>1</v>
-      </c>
-      <c r="I6">
+        <v>5</v>
+      </c>
+      <c r="E6">
+        <v>1</v>
+      </c>
+      <c r="F6">
+        <v>2</v>
+      </c>
+      <c r="J6">
+        <v>2</v>
+      </c>
+      <c r="M6">
         <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D7">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E7">
         <v>1</v>
       </c>
-      <c r="J7">
-        <v>2</v>
+      <c r="I7">
+        <v>1</v>
+      </c>
+      <c r="K7">
+        <v>1</v>
+      </c>
+      <c r="L7">
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -2273,40 +2282,40 @@
         <v>8</v>
       </c>
       <c r="B8">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="C8">
-        <v>9</v>
+        <v>37</v>
       </c>
       <c r="D8">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E8">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="F8">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="G8">
         <v>15</v>
       </c>
       <c r="H8">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="I8">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="J8">
+        <v>26</v>
+      </c>
+      <c r="K8">
+        <v>49</v>
+      </c>
+      <c r="L8">
+        <v>44</v>
+      </c>
+      <c r="M8">
         <v>12</v>
-      </c>
-      <c r="K8">
-        <v>18</v>
-      </c>
-      <c r="L8">
-        <v>19</v>
-      </c>
-      <c r="M8">
-        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -2314,40 +2323,40 @@
         <v>9</v>
       </c>
       <c r="B9">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C9">
+        <v>64</v>
+      </c>
+      <c r="D9">
         <v>46</v>
       </c>
-      <c r="D9">
-        <v>32</v>
-      </c>
       <c r="E9">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="F9">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="G9">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="H9">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="I9">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="J9">
         <v>20</v>
       </c>
       <c r="K9">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="L9">
-        <v>13</v>
+        <v>35</v>
       </c>
       <c r="M9">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -2355,40 +2364,40 @@
         <v>10</v>
       </c>
       <c r="B10">
-        <v>51</v>
+        <v>77</v>
       </c>
       <c r="C10">
-        <v>57</v>
+        <v>106</v>
       </c>
       <c r="D10">
-        <v>62</v>
+        <v>82</v>
       </c>
       <c r="E10">
-        <v>48</v>
+        <v>88</v>
       </c>
       <c r="F10">
-        <v>60</v>
+        <v>91</v>
       </c>
       <c r="G10">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="H10">
-        <v>31</v>
+        <v>66</v>
       </c>
       <c r="I10">
-        <v>44</v>
+        <v>77</v>
       </c>
       <c r="J10">
-        <v>43</v>
+        <v>67</v>
       </c>
       <c r="K10">
-        <v>57</v>
+        <v>110</v>
       </c>
       <c r="L10">
-        <v>40</v>
+        <v>98</v>
       </c>
       <c r="M10">
-        <v>17</v>
+        <v>36</v>
       </c>
     </row>
   </sheetData>
@@ -2398,7 +2407,7 @@
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M7"/>
+  <dimension ref="A1:M10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="23.7109375" customWidth="1"/>
@@ -2461,29 +2470,38 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
       <c r="D2">
+        <v>5</v>
+      </c>
+      <c r="E2">
         <v>1</v>
       </c>
       <c r="F2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G2">
         <v>1</v>
       </c>
+      <c r="H2">
+        <v>3</v>
+      </c>
       <c r="I2">
         <v>2</v>
       </c>
       <c r="J2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K2">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="L2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M2">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -2491,153 +2509,210 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C3">
         <v>1</v>
       </c>
+      <c r="D3">
+        <v>7</v>
+      </c>
+      <c r="E3">
+        <v>3</v>
+      </c>
+      <c r="F3">
+        <v>4</v>
+      </c>
       <c r="G3">
-        <v>2</v>
+        <v>8</v>
+      </c>
+      <c r="H3">
+        <v>4</v>
       </c>
       <c r="I3">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="J3">
-        <v>1</v>
+        <v>4</v>
+      </c>
+      <c r="K3">
+        <v>10</v>
       </c>
       <c r="L3">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="E4">
-        <v>2</v>
-      </c>
-      <c r="J4">
-        <v>1</v>
-      </c>
-      <c r="K4">
+        <v>3</v>
+      </c>
+      <c r="H4">
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B5">
         <v>1</v>
       </c>
-      <c r="C5">
-        <v>1</v>
-      </c>
-      <c r="D5">
-        <v>2</v>
-      </c>
-      <c r="E5">
-        <v>2</v>
-      </c>
-      <c r="G5">
-        <v>1</v>
-      </c>
-      <c r="I5">
-        <v>1</v>
-      </c>
-      <c r="J5">
-        <v>3</v>
-      </c>
       <c r="K5">
-        <v>4</v>
-      </c>
-      <c r="M5">
         <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B6">
-        <v>8</v>
-      </c>
-      <c r="C6">
-        <v>13</v>
-      </c>
-      <c r="D6">
-        <v>10</v>
-      </c>
-      <c r="E6">
-        <v>9</v>
-      </c>
-      <c r="F6">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G6">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="H6">
         <v>1</v>
       </c>
       <c r="I6">
-        <v>4</v>
-      </c>
-      <c r="J6">
-        <v>5</v>
-      </c>
-      <c r="K6">
-        <v>8</v>
-      </c>
-      <c r="L6">
-        <v>3</v>
-      </c>
-      <c r="M6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D7">
+        <v>1</v>
+      </c>
+      <c r="E7">
+        <v>1</v>
+      </c>
+      <c r="J7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13">
+      <c r="A8" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8">
+        <v>5</v>
+      </c>
+      <c r="C8">
+        <v>9</v>
+      </c>
+      <c r="D8">
+        <v>17</v>
+      </c>
+      <c r="E8">
+        <v>13</v>
+      </c>
+      <c r="F8">
+        <v>19</v>
+      </c>
+      <c r="G8">
+        <v>15</v>
+      </c>
+      <c r="H8">
+        <v>5</v>
+      </c>
+      <c r="I8">
+        <v>15</v>
+      </c>
+      <c r="J8">
+        <v>12</v>
+      </c>
+      <c r="K8">
+        <v>18</v>
+      </c>
+      <c r="L8">
+        <v>19</v>
+      </c>
+      <c r="M8">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13">
+      <c r="A9" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B9">
+        <v>43</v>
+      </c>
+      <c r="C9">
+        <v>46</v>
+      </c>
+      <c r="D9">
+        <v>32</v>
+      </c>
+      <c r="E9">
+        <v>30</v>
+      </c>
+      <c r="F9">
+        <v>34</v>
+      </c>
+      <c r="G9">
+        <v>15</v>
+      </c>
+      <c r="H9">
+        <v>17</v>
+      </c>
+      <c r="I9">
+        <v>20</v>
+      </c>
+      <c r="J9">
+        <v>20</v>
+      </c>
+      <c r="K9">
+        <v>20</v>
+      </c>
+      <c r="L9">
+        <v>13</v>
+      </c>
+      <c r="M9">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13">
+      <c r="A10" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B7">
-        <v>10</v>
-      </c>
-      <c r="C7">
-        <v>15</v>
-      </c>
-      <c r="D7">
-        <v>13</v>
-      </c>
-      <c r="E7">
-        <v>13</v>
-      </c>
-      <c r="F7">
-        <v>10</v>
-      </c>
-      <c r="G7">
-        <v>12</v>
-      </c>
-      <c r="H7">
-        <v>1</v>
-      </c>
-      <c r="I7">
-        <v>8</v>
-      </c>
-      <c r="J7">
-        <v>14</v>
-      </c>
-      <c r="K7">
-        <v>15</v>
-      </c>
-      <c r="L7">
-        <v>6</v>
-      </c>
-      <c r="M7">
-        <v>5</v>
+      <c r="B10">
+        <v>51</v>
+      </c>
+      <c r="C10">
+        <v>57</v>
+      </c>
+      <c r="D10">
+        <v>62</v>
+      </c>
+      <c r="E10">
+        <v>48</v>
+      </c>
+      <c r="F10">
+        <v>60</v>
+      </c>
+      <c r="G10">
+        <v>40</v>
+      </c>
+      <c r="H10">
+        <v>31</v>
+      </c>
+      <c r="I10">
+        <v>44</v>
+      </c>
+      <c r="J10">
+        <v>43</v>
+      </c>
+      <c r="K10">
+        <v>57</v>
+      </c>
+      <c r="L10">
+        <v>40</v>
+      </c>
+      <c r="M10">
+        <v>17</v>
       </c>
     </row>
   </sheetData>
@@ -2647,10 +2722,10 @@
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M7"/>
+  <dimension ref="A1:M10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="18.7109375" customWidth="1"/>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
     <col min="2" max="2" width="4.7109375" customWidth="1"/>
     <col min="3" max="3" width="4.7109375" customWidth="1"/>
     <col min="4" max="4" width="4.7109375" customWidth="1"/>
@@ -2710,29 +2785,41 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
+      <c r="B2">
+        <v>4</v>
+      </c>
       <c r="C2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E2">
-        <v>1</v>
+        <v>5</v>
+      </c>
+      <c r="F2">
+        <v>9</v>
+      </c>
+      <c r="G2">
+        <v>3</v>
       </c>
       <c r="H2">
-        <v>2</v>
+        <v>5</v>
+      </c>
+      <c r="I2">
+        <v>4</v>
       </c>
       <c r="J2">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="K2">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="L2">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="M2">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -2740,162 +2827,210 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C3">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D3">
-        <v>1</v>
+        <v>6</v>
+      </c>
+      <c r="E3">
+        <v>7</v>
       </c>
       <c r="F3">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G3">
-        <v>1</v>
+        <v>7</v>
+      </c>
+      <c r="H3">
+        <v>8</v>
       </c>
       <c r="I3">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J3">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="K3">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="L3">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="M3">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H4">
+        <v>3</v>
+      </c>
+      <c r="I4">
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B5">
-        <v>7</v>
-      </c>
-      <c r="C5">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="D5">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E5">
-        <v>5</v>
-      </c>
-      <c r="F5">
-        <v>5</v>
-      </c>
-      <c r="G5">
-        <v>6</v>
-      </c>
-      <c r="H5">
-        <v>2</v>
-      </c>
-      <c r="I5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J5">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K5">
-        <v>6</v>
-      </c>
-      <c r="L5">
-        <v>6</v>
+        <v>2</v>
+      </c>
+      <c r="M5">
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B6">
-        <v>15</v>
-      </c>
-      <c r="C6">
-        <v>16</v>
-      </c>
-      <c r="D6">
-        <v>15</v>
-      </c>
-      <c r="E6">
-        <v>16</v>
-      </c>
-      <c r="F6">
-        <v>11</v>
-      </c>
-      <c r="G6">
-        <v>9</v>
-      </c>
-      <c r="H6">
-        <v>5</v>
-      </c>
-      <c r="I6">
-        <v>5</v>
-      </c>
-      <c r="J6">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="K6">
-        <v>6</v>
-      </c>
-      <c r="L6">
-        <v>4</v>
-      </c>
-      <c r="M6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="L7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13">
+      <c r="A8" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8">
+        <v>23</v>
+      </c>
+      <c r="C8">
+        <v>31</v>
+      </c>
+      <c r="D8">
+        <v>22</v>
+      </c>
+      <c r="E8">
+        <v>44</v>
+      </c>
+      <c r="F8">
+        <v>38</v>
+      </c>
+      <c r="G8">
+        <v>24</v>
+      </c>
+      <c r="H8">
+        <v>50</v>
+      </c>
+      <c r="I8">
+        <v>34</v>
+      </c>
+      <c r="J8">
+        <v>26</v>
+      </c>
+      <c r="K8">
+        <v>24</v>
+      </c>
+      <c r="L8">
+        <v>14</v>
+      </c>
+      <c r="M8">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13">
+      <c r="A9" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B9">
+        <v>46</v>
+      </c>
+      <c r="C9">
+        <v>59</v>
+      </c>
+      <c r="D9">
+        <v>33</v>
+      </c>
+      <c r="E9">
+        <v>73</v>
+      </c>
+      <c r="F9">
+        <v>114</v>
+      </c>
+      <c r="G9">
+        <v>58</v>
+      </c>
+      <c r="H9">
+        <v>41</v>
+      </c>
+      <c r="I9">
+        <v>44</v>
+      </c>
+      <c r="J9">
+        <v>20</v>
+      </c>
+      <c r="K9">
+        <v>25</v>
+      </c>
+      <c r="L9">
+        <v>27</v>
+      </c>
+      <c r="M9">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13">
+      <c r="A10" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B7">
-        <v>24</v>
-      </c>
-      <c r="C7">
-        <v>29</v>
-      </c>
-      <c r="D7">
-        <v>25</v>
-      </c>
-      <c r="E7">
-        <v>22</v>
-      </c>
-      <c r="F7">
-        <v>19</v>
-      </c>
-      <c r="G7">
-        <v>16</v>
-      </c>
-      <c r="H7">
-        <v>10</v>
-      </c>
-      <c r="I7">
-        <v>11</v>
-      </c>
-      <c r="J7">
-        <v>20</v>
-      </c>
-      <c r="K7">
-        <v>15</v>
-      </c>
-      <c r="L7">
-        <v>16</v>
-      </c>
-      <c r="M7">
-        <v>6</v>
+      <c r="B10">
+        <v>78</v>
+      </c>
+      <c r="C10">
+        <v>99</v>
+      </c>
+      <c r="D10">
+        <v>65</v>
+      </c>
+      <c r="E10">
+        <v>130</v>
+      </c>
+      <c r="F10">
+        <v>167</v>
+      </c>
+      <c r="G10">
+        <v>92</v>
+      </c>
+      <c r="H10">
+        <v>104</v>
+      </c>
+      <c r="I10">
+        <v>89</v>
+      </c>
+      <c r="J10">
+        <v>67</v>
+      </c>
+      <c r="K10">
+        <v>71</v>
+      </c>
+      <c r="L10">
+        <v>61</v>
+      </c>
+      <c r="M10">
+        <v>50</v>
       </c>
     </row>
   </sheetData>
@@ -2971,7 +3106,25 @@
       <c r="D2">
         <v>1</v>
       </c>
+      <c r="F2">
+        <v>1</v>
+      </c>
+      <c r="G2">
+        <v>1</v>
+      </c>
+      <c r="I2">
+        <v>2</v>
+      </c>
       <c r="J2">
+        <v>4</v>
+      </c>
+      <c r="K2">
+        <v>2</v>
+      </c>
+      <c r="L2">
+        <v>2</v>
+      </c>
+      <c r="M2">
         <v>1</v>
       </c>
     </row>
@@ -2979,16 +3132,25 @@
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="E3">
-        <v>2</v>
+      <c r="B3">
+        <v>1</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
       </c>
       <c r="G3">
+        <v>2</v>
+      </c>
+      <c r="I3">
         <v>1</v>
       </c>
       <c r="J3">
         <v>1</v>
       </c>
       <c r="L3">
+        <v>1</v>
+      </c>
+      <c r="M3">
         <v>1</v>
       </c>
     </row>
@@ -2996,7 +3158,13 @@
       <c r="A4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C4">
+      <c r="E4">
+        <v>2</v>
+      </c>
+      <c r="J4">
+        <v>1</v>
+      </c>
+      <c r="K4">
         <v>1</v>
       </c>
     </row>
@@ -3005,22 +3173,28 @@
         <v>8</v>
       </c>
       <c r="B5">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C5">
-        <v>6</v>
+        <v>1</v>
+      </c>
+      <c r="D5">
+        <v>2</v>
       </c>
       <c r="E5">
-        <v>1</v>
-      </c>
-      <c r="H5">
-        <v>2</v>
+        <v>2</v>
+      </c>
+      <c r="G5">
+        <v>1</v>
+      </c>
+      <c r="I5">
+        <v>1</v>
       </c>
       <c r="J5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M5">
         <v>1</v>
@@ -3031,40 +3205,40 @@
         <v>9</v>
       </c>
       <c r="B6">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C6">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="D6">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E6">
+        <v>9</v>
+      </c>
+      <c r="F6">
+        <v>9</v>
+      </c>
+      <c r="G6">
         <v>8</v>
       </c>
-      <c r="F6">
-        <v>7</v>
-      </c>
-      <c r="G6">
-        <v>2</v>
-      </c>
       <c r="H6">
         <v>1</v>
       </c>
       <c r="I6">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J6">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K6">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="L6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -3072,40 +3246,40 @@
         <v>10</v>
       </c>
       <c r="B7">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C7">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D7">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="E7">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F7">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G7">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="H7">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I7">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="J7">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="K7">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="L7">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="M7">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -3114,6 +3288,474 @@
 </file>
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:M7"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="18.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+    <col min="13" max="13" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="M1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
+      <c r="H2">
+        <v>2</v>
+      </c>
+      <c r="J2">
+        <v>1</v>
+      </c>
+      <c r="K2">
+        <v>2</v>
+      </c>
+      <c r="L2">
+        <v>2</v>
+      </c>
+      <c r="M2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>2</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
+      <c r="F3">
+        <v>3</v>
+      </c>
+      <c r="G3">
+        <v>1</v>
+      </c>
+      <c r="I3">
+        <v>4</v>
+      </c>
+      <c r="J3">
+        <v>2</v>
+      </c>
+      <c r="K3">
+        <v>1</v>
+      </c>
+      <c r="L3">
+        <v>4</v>
+      </c>
+      <c r="M3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5">
+        <v>7</v>
+      </c>
+      <c r="C5">
+        <v>11</v>
+      </c>
+      <c r="D5">
+        <v>8</v>
+      </c>
+      <c r="E5">
+        <v>5</v>
+      </c>
+      <c r="F5">
+        <v>5</v>
+      </c>
+      <c r="G5">
+        <v>6</v>
+      </c>
+      <c r="H5">
+        <v>2</v>
+      </c>
+      <c r="I5">
+        <v>2</v>
+      </c>
+      <c r="J5">
+        <v>5</v>
+      </c>
+      <c r="K5">
+        <v>6</v>
+      </c>
+      <c r="L5">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6">
+        <v>15</v>
+      </c>
+      <c r="C6">
+        <v>16</v>
+      </c>
+      <c r="D6">
+        <v>15</v>
+      </c>
+      <c r="E6">
+        <v>16</v>
+      </c>
+      <c r="F6">
+        <v>11</v>
+      </c>
+      <c r="G6">
+        <v>9</v>
+      </c>
+      <c r="H6">
+        <v>5</v>
+      </c>
+      <c r="I6">
+        <v>5</v>
+      </c>
+      <c r="J6">
+        <v>12</v>
+      </c>
+      <c r="K6">
+        <v>6</v>
+      </c>
+      <c r="L6">
+        <v>4</v>
+      </c>
+      <c r="M6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7">
+        <v>24</v>
+      </c>
+      <c r="C7">
+        <v>29</v>
+      </c>
+      <c r="D7">
+        <v>25</v>
+      </c>
+      <c r="E7">
+        <v>22</v>
+      </c>
+      <c r="F7">
+        <v>19</v>
+      </c>
+      <c r="G7">
+        <v>16</v>
+      </c>
+      <c r="H7">
+        <v>10</v>
+      </c>
+      <c r="I7">
+        <v>11</v>
+      </c>
+      <c r="J7">
+        <v>20</v>
+      </c>
+      <c r="K7">
+        <v>15</v>
+      </c>
+      <c r="L7">
+        <v>16</v>
+      </c>
+      <c r="M7">
+        <v>6</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:M7"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+    <col min="13" max="13" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="M1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="J2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E3">
+        <v>2</v>
+      </c>
+      <c r="G3">
+        <v>1</v>
+      </c>
+      <c r="J3">
+        <v>1</v>
+      </c>
+      <c r="L3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5">
+        <v>5</v>
+      </c>
+      <c r="C5">
+        <v>6</v>
+      </c>
+      <c r="E5">
+        <v>1</v>
+      </c>
+      <c r="H5">
+        <v>2</v>
+      </c>
+      <c r="J5">
+        <v>4</v>
+      </c>
+      <c r="K5">
+        <v>2</v>
+      </c>
+      <c r="M5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6">
+        <v>6</v>
+      </c>
+      <c r="C6">
+        <v>2</v>
+      </c>
+      <c r="D6">
+        <v>6</v>
+      </c>
+      <c r="E6">
+        <v>8</v>
+      </c>
+      <c r="F6">
+        <v>7</v>
+      </c>
+      <c r="G6">
+        <v>2</v>
+      </c>
+      <c r="H6">
+        <v>1</v>
+      </c>
+      <c r="I6">
+        <v>1</v>
+      </c>
+      <c r="J6">
+        <v>3</v>
+      </c>
+      <c r="K6">
+        <v>1</v>
+      </c>
+      <c r="L6">
+        <v>2</v>
+      </c>
+      <c r="M6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7">
+        <v>11</v>
+      </c>
+      <c r="C7">
+        <v>9</v>
+      </c>
+      <c r="D7">
+        <v>7</v>
+      </c>
+      <c r="E7">
+        <v>11</v>
+      </c>
+      <c r="F7">
+        <v>7</v>
+      </c>
+      <c r="G7">
+        <v>3</v>
+      </c>
+      <c r="H7">
+        <v>3</v>
+      </c>
+      <c r="I7">
+        <v>1</v>
+      </c>
+      <c r="J7">
+        <v>9</v>
+      </c>
+      <c r="K7">
+        <v>3</v>
+      </c>
+      <c r="L7">
+        <v>3</v>
+      </c>
+      <c r="M7">
+        <v>2</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:L8"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -3284,656 +3926,6 @@
       </c>
       <c r="L8">
         <v>2</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M10"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" customWidth="1"/>
-    <col min="13" max="13" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="M1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2">
-        <v>6</v>
-      </c>
-      <c r="C2">
-        <v>3</v>
-      </c>
-      <c r="D2">
-        <v>12</v>
-      </c>
-      <c r="E2">
-        <v>5</v>
-      </c>
-      <c r="F2">
-        <v>8</v>
-      </c>
-      <c r="G2">
-        <v>4</v>
-      </c>
-      <c r="H2">
-        <v>13</v>
-      </c>
-      <c r="I2">
-        <v>14</v>
-      </c>
-      <c r="J2">
-        <v>22</v>
-      </c>
-      <c r="K2">
-        <v>15</v>
-      </c>
-      <c r="L2">
-        <v>15</v>
-      </c>
-      <c r="M2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3">
-        <v>13</v>
-      </c>
-      <c r="C3">
-        <v>13</v>
-      </c>
-      <c r="D3">
-        <v>17</v>
-      </c>
-      <c r="E3">
-        <v>18</v>
-      </c>
-      <c r="F3">
-        <v>14</v>
-      </c>
-      <c r="G3">
-        <v>26</v>
-      </c>
-      <c r="H3">
-        <v>23</v>
-      </c>
-      <c r="I3">
-        <v>32</v>
-      </c>
-      <c r="J3">
-        <v>40</v>
-      </c>
-      <c r="K3">
-        <v>26</v>
-      </c>
-      <c r="L3">
-        <v>34</v>
-      </c>
-      <c r="M3">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="G4">
-        <v>1</v>
-      </c>
-      <c r="J4">
-        <v>2</v>
-      </c>
-      <c r="K4">
-        <v>1</v>
-      </c>
-      <c r="L4">
-        <v>1</v>
-      </c>
-      <c r="M4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C5">
-        <v>2</v>
-      </c>
-      <c r="D5">
-        <v>1</v>
-      </c>
-      <c r="E5">
-        <v>2</v>
-      </c>
-      <c r="F5">
-        <v>1</v>
-      </c>
-      <c r="H5">
-        <v>2</v>
-      </c>
-      <c r="I5">
-        <v>4</v>
-      </c>
-      <c r="J5">
-        <v>3</v>
-      </c>
-      <c r="K5">
-        <v>2</v>
-      </c>
-      <c r="L5">
-        <v>5</v>
-      </c>
-      <c r="M5">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="G6">
-        <v>1</v>
-      </c>
-      <c r="H6">
-        <v>2</v>
-      </c>
-      <c r="J6">
-        <v>2</v>
-      </c>
-      <c r="L6">
-        <v>2</v>
-      </c>
-      <c r="M6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
-      <c r="A7" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="K7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13">
-      <c r="A8" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B8">
-        <v>30</v>
-      </c>
-      <c r="C8">
-        <v>44</v>
-      </c>
-      <c r="D8">
-        <v>49</v>
-      </c>
-      <c r="E8">
-        <v>67</v>
-      </c>
-      <c r="F8">
-        <v>69</v>
-      </c>
-      <c r="G8">
-        <v>57</v>
-      </c>
-      <c r="H8">
-        <v>80</v>
-      </c>
-      <c r="I8">
-        <v>80</v>
-      </c>
-      <c r="J8">
-        <v>64</v>
-      </c>
-      <c r="K8">
-        <v>48</v>
-      </c>
-      <c r="L8">
-        <v>44</v>
-      </c>
-      <c r="M8">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13">
-      <c r="A9" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B9">
-        <v>233</v>
-      </c>
-      <c r="C9">
-        <v>354</v>
-      </c>
-      <c r="D9">
-        <v>538</v>
-      </c>
-      <c r="E9">
-        <v>705</v>
-      </c>
-      <c r="F9">
-        <v>568</v>
-      </c>
-      <c r="G9">
-        <v>168</v>
-      </c>
-      <c r="H9">
-        <v>116</v>
-      </c>
-      <c r="I9">
-        <v>194</v>
-      </c>
-      <c r="J9">
-        <v>122</v>
-      </c>
-      <c r="K9">
-        <v>114</v>
-      </c>
-      <c r="L9">
-        <v>95</v>
-      </c>
-      <c r="M9">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13">
-      <c r="A10" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B10">
-        <v>282</v>
-      </c>
-      <c r="C10">
-        <v>416</v>
-      </c>
-      <c r="D10">
-        <v>617</v>
-      </c>
-      <c r="E10">
-        <v>797</v>
-      </c>
-      <c r="F10">
-        <v>660</v>
-      </c>
-      <c r="G10">
-        <v>257</v>
-      </c>
-      <c r="H10">
-        <v>236</v>
-      </c>
-      <c r="I10">
-        <v>324</v>
-      </c>
-      <c r="J10">
-        <v>255</v>
-      </c>
-      <c r="K10">
-        <v>207</v>
-      </c>
-      <c r="L10">
-        <v>196</v>
-      </c>
-      <c r="M10">
-        <v>88</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M8"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" customWidth="1"/>
-    <col min="13" max="13" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="M1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2">
-        <v>4</v>
-      </c>
-      <c r="D2">
-        <v>1</v>
-      </c>
-      <c r="E2">
-        <v>4</v>
-      </c>
-      <c r="F2">
-        <v>2</v>
-      </c>
-      <c r="G2">
-        <v>4</v>
-      </c>
-      <c r="H2">
-        <v>2</v>
-      </c>
-      <c r="I2">
-        <v>3</v>
-      </c>
-      <c r="J2">
-        <v>2</v>
-      </c>
-      <c r="K2">
-        <v>6</v>
-      </c>
-      <c r="L2">
-        <v>6</v>
-      </c>
-      <c r="M2">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3">
-        <v>2</v>
-      </c>
-      <c r="C3">
-        <v>4</v>
-      </c>
-      <c r="D3">
-        <v>1</v>
-      </c>
-      <c r="E3">
-        <v>4</v>
-      </c>
-      <c r="F3">
-        <v>5</v>
-      </c>
-      <c r="G3">
-        <v>4</v>
-      </c>
-      <c r="H3">
-        <v>7</v>
-      </c>
-      <c r="I3">
-        <v>2</v>
-      </c>
-      <c r="J3">
-        <v>11</v>
-      </c>
-      <c r="K3">
-        <v>5</v>
-      </c>
-      <c r="L3">
-        <v>7</v>
-      </c>
-      <c r="M3">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="H4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C5">
-        <v>1</v>
-      </c>
-      <c r="H5">
-        <v>1</v>
-      </c>
-      <c r="I5">
-        <v>1</v>
-      </c>
-      <c r="K5">
-        <v>3</v>
-      </c>
-      <c r="L5">
-        <v>2</v>
-      </c>
-      <c r="M5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C6">
-        <v>14</v>
-      </c>
-      <c r="D6">
-        <v>12</v>
-      </c>
-      <c r="E6">
-        <v>10</v>
-      </c>
-      <c r="F6">
-        <v>11</v>
-      </c>
-      <c r="G6">
-        <v>11</v>
-      </c>
-      <c r="H6">
-        <v>17</v>
-      </c>
-      <c r="I6">
-        <v>20</v>
-      </c>
-      <c r="J6">
-        <v>3</v>
-      </c>
-      <c r="K6">
-        <v>10</v>
-      </c>
-      <c r="L6">
-        <v>5</v>
-      </c>
-      <c r="M6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
-      <c r="A7" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B7">
-        <v>58</v>
-      </c>
-      <c r="C7">
-        <v>53</v>
-      </c>
-      <c r="D7">
-        <v>43</v>
-      </c>
-      <c r="E7">
-        <v>56</v>
-      </c>
-      <c r="F7">
-        <v>53</v>
-      </c>
-      <c r="G7">
-        <v>33</v>
-      </c>
-      <c r="H7">
-        <v>23</v>
-      </c>
-      <c r="I7">
-        <v>26</v>
-      </c>
-      <c r="J7">
-        <v>27</v>
-      </c>
-      <c r="K7">
-        <v>17</v>
-      </c>
-      <c r="L7">
-        <v>19</v>
-      </c>
-      <c r="M7">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13">
-      <c r="A8" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B8">
-        <v>60</v>
-      </c>
-      <c r="C8">
-        <v>76</v>
-      </c>
-      <c r="D8">
-        <v>57</v>
-      </c>
-      <c r="E8">
-        <v>74</v>
-      </c>
-      <c r="F8">
-        <v>71</v>
-      </c>
-      <c r="G8">
-        <v>52</v>
-      </c>
-      <c r="H8">
-        <v>51</v>
-      </c>
-      <c r="I8">
-        <v>52</v>
-      </c>
-      <c r="J8">
-        <v>43</v>
-      </c>
-      <c r="K8">
-        <v>41</v>
-      </c>
-      <c r="L8">
-        <v>39</v>
-      </c>
-      <c r="M8">
-        <v>25</v>
       </c>
     </row>
   </sheetData>
@@ -5954,7 +5946,7 @@
         <v>196</v>
       </c>
       <c r="M53">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="54" spans="1:13">
@@ -6673,7 +6665,7 @@
         <v>7</v>
       </c>
       <c r="M72">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="73" spans="1:13">
@@ -7726,7 +7718,7 @@
         <v>1604</v>
       </c>
       <c r="M99">
-        <v>791</v>
+        <v>793</v>
       </c>
     </row>
   </sheetData>
@@ -7900,40 +7892,40 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D2">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="E2">
         <v>5</v>
       </c>
       <c r="F2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H2">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="I2">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="J2">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="K2">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="L2">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="M2">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -7941,47 +7933,59 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="C3">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="D3">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="E3">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="F3">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="G3">
-        <v>7</v>
+        <v>26</v>
       </c>
       <c r="H3">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="I3">
-        <v>6</v>
+        <v>32</v>
       </c>
       <c r="J3">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="K3">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="L3">
-        <v>14</v>
+        <v>34</v>
       </c>
       <c r="M3">
-        <v>10</v>
+        <v>16</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="I4">
+      <c r="G4">
+        <v>1</v>
+      </c>
+      <c r="J4">
+        <v>2</v>
+      </c>
+      <c r="K4">
+        <v>1</v>
+      </c>
+      <c r="L4">
+        <v>1</v>
+      </c>
+      <c r="M4">
         <v>1</v>
       </c>
     </row>
@@ -7989,14 +7993,23 @@
       <c r="A5" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B5">
-        <v>1</v>
+      <c r="C5">
+        <v>2</v>
       </c>
       <c r="D5">
         <v>1</v>
       </c>
       <c r="E5">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="F5">
+        <v>1</v>
+      </c>
+      <c r="H5">
+        <v>2</v>
+      </c>
+      <c r="I5">
+        <v>4</v>
       </c>
       <c r="J5">
         <v>3</v>
@@ -8004,15 +8017,30 @@
       <c r="K5">
         <v>2</v>
       </c>
+      <c r="L5">
+        <v>5</v>
+      </c>
       <c r="M5">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="K6">
+      <c r="G6">
+        <v>1</v>
+      </c>
+      <c r="H6">
+        <v>2</v>
+      </c>
+      <c r="J6">
+        <v>2</v>
+      </c>
+      <c r="L6">
+        <v>2</v>
+      </c>
+      <c r="M6">
         <v>1</v>
       </c>
     </row>
@@ -8020,7 +8048,7 @@
       <c r="A7" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="L7">
+      <c r="K7">
         <v>1</v>
       </c>
     </row>
@@ -8029,40 +8057,40 @@
         <v>8</v>
       </c>
       <c r="B8">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="C8">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="D8">
-        <v>22</v>
+        <v>49</v>
       </c>
       <c r="E8">
+        <v>67</v>
+      </c>
+      <c r="F8">
+        <v>69</v>
+      </c>
+      <c r="G8">
+        <v>57</v>
+      </c>
+      <c r="H8">
+        <v>80</v>
+      </c>
+      <c r="I8">
+        <v>80</v>
+      </c>
+      <c r="J8">
+        <v>64</v>
+      </c>
+      <c r="K8">
+        <v>48</v>
+      </c>
+      <c r="L8">
         <v>44</v>
       </c>
-      <c r="F8">
-        <v>38</v>
-      </c>
-      <c r="G8">
-        <v>24</v>
-      </c>
-      <c r="H8">
-        <v>50</v>
-      </c>
-      <c r="I8">
-        <v>34</v>
-      </c>
-      <c r="J8">
-        <v>26</v>
-      </c>
-      <c r="K8">
-        <v>24</v>
-      </c>
-      <c r="L8">
-        <v>14</v>
-      </c>
       <c r="M8">
-        <v>14</v>
+        <v>20</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -8070,40 +8098,40 @@
         <v>9</v>
       </c>
       <c r="B9">
-        <v>46</v>
+        <v>233</v>
       </c>
       <c r="C9">
-        <v>59</v>
+        <v>354</v>
       </c>
       <c r="D9">
-        <v>33</v>
+        <v>538</v>
       </c>
       <c r="E9">
-        <v>73</v>
+        <v>705</v>
       </c>
       <c r="F9">
+        <v>568</v>
+      </c>
+      <c r="G9">
+        <v>168</v>
+      </c>
+      <c r="H9">
+        <v>116</v>
+      </c>
+      <c r="I9">
+        <v>194</v>
+      </c>
+      <c r="J9">
+        <v>122</v>
+      </c>
+      <c r="K9">
         <v>114</v>
       </c>
-      <c r="G9">
-        <v>58</v>
-      </c>
-      <c r="H9">
-        <v>41</v>
-      </c>
-      <c r="I9">
-        <v>44</v>
-      </c>
-      <c r="J9">
-        <v>20</v>
-      </c>
-      <c r="K9">
-        <v>25</v>
-      </c>
       <c r="L9">
-        <v>27</v>
+        <v>95</v>
       </c>
       <c r="M9">
-        <v>16</v>
+        <v>45</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -8111,40 +8139,40 @@
         <v>10</v>
       </c>
       <c r="B10">
-        <v>78</v>
+        <v>282</v>
       </c>
       <c r="C10">
-        <v>99</v>
+        <v>416</v>
       </c>
       <c r="D10">
-        <v>65</v>
+        <v>617</v>
       </c>
       <c r="E10">
-        <v>130</v>
+        <v>797</v>
       </c>
       <c r="F10">
-        <v>167</v>
+        <v>660</v>
       </c>
       <c r="G10">
-        <v>92</v>
+        <v>257</v>
       </c>
       <c r="H10">
-        <v>104</v>
+        <v>236</v>
       </c>
       <c r="I10">
+        <v>324</v>
+      </c>
+      <c r="J10">
+        <v>255</v>
+      </c>
+      <c r="K10">
+        <v>207</v>
+      </c>
+      <c r="L10">
+        <v>196</v>
+      </c>
+      <c r="M10">
         <v>89</v>
-      </c>
-      <c r="J10">
-        <v>67</v>
-      </c>
-      <c r="K10">
-        <v>71</v>
-      </c>
-      <c r="L10">
-        <v>61</v>
-      </c>
-      <c r="M10">
-        <v>50</v>
       </c>
     </row>
   </sheetData>
@@ -8153,6 +8181,302 @@
 </file>
 
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:M8"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+    <col min="13" max="13" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="M1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>4</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="E2">
+        <v>4</v>
+      </c>
+      <c r="F2">
+        <v>2</v>
+      </c>
+      <c r="G2">
+        <v>4</v>
+      </c>
+      <c r="H2">
+        <v>2</v>
+      </c>
+      <c r="I2">
+        <v>3</v>
+      </c>
+      <c r="J2">
+        <v>2</v>
+      </c>
+      <c r="K2">
+        <v>6</v>
+      </c>
+      <c r="L2">
+        <v>6</v>
+      </c>
+      <c r="M2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>2</v>
+      </c>
+      <c r="C3">
+        <v>4</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
+      <c r="E3">
+        <v>4</v>
+      </c>
+      <c r="F3">
+        <v>5</v>
+      </c>
+      <c r="G3">
+        <v>4</v>
+      </c>
+      <c r="H3">
+        <v>7</v>
+      </c>
+      <c r="I3">
+        <v>2</v>
+      </c>
+      <c r="J3">
+        <v>11</v>
+      </c>
+      <c r="K3">
+        <v>5</v>
+      </c>
+      <c r="L3">
+        <v>7</v>
+      </c>
+      <c r="M3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="H4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C5">
+        <v>1</v>
+      </c>
+      <c r="H5">
+        <v>1</v>
+      </c>
+      <c r="I5">
+        <v>1</v>
+      </c>
+      <c r="K5">
+        <v>3</v>
+      </c>
+      <c r="L5">
+        <v>2</v>
+      </c>
+      <c r="M5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C6">
+        <v>14</v>
+      </c>
+      <c r="D6">
+        <v>12</v>
+      </c>
+      <c r="E6">
+        <v>10</v>
+      </c>
+      <c r="F6">
+        <v>11</v>
+      </c>
+      <c r="G6">
+        <v>11</v>
+      </c>
+      <c r="H6">
+        <v>17</v>
+      </c>
+      <c r="I6">
+        <v>20</v>
+      </c>
+      <c r="J6">
+        <v>3</v>
+      </c>
+      <c r="K6">
+        <v>10</v>
+      </c>
+      <c r="L6">
+        <v>5</v>
+      </c>
+      <c r="M6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7">
+        <v>58</v>
+      </c>
+      <c r="C7">
+        <v>53</v>
+      </c>
+      <c r="D7">
+        <v>43</v>
+      </c>
+      <c r="E7">
+        <v>56</v>
+      </c>
+      <c r="F7">
+        <v>53</v>
+      </c>
+      <c r="G7">
+        <v>33</v>
+      </c>
+      <c r="H7">
+        <v>23</v>
+      </c>
+      <c r="I7">
+        <v>26</v>
+      </c>
+      <c r="J7">
+        <v>27</v>
+      </c>
+      <c r="K7">
+        <v>17</v>
+      </c>
+      <c r="L7">
+        <v>19</v>
+      </c>
+      <c r="M7">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13">
+      <c r="A8" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B8">
+        <v>60</v>
+      </c>
+      <c r="C8">
+        <v>76</v>
+      </c>
+      <c r="D8">
+        <v>57</v>
+      </c>
+      <c r="E8">
+        <v>74</v>
+      </c>
+      <c r="F8">
+        <v>71</v>
+      </c>
+      <c r="G8">
+        <v>52</v>
+      </c>
+      <c r="H8">
+        <v>51</v>
+      </c>
+      <c r="I8">
+        <v>52</v>
+      </c>
+      <c r="J8">
+        <v>43</v>
+      </c>
+      <c r="K8">
+        <v>41</v>
+      </c>
+      <c r="L8">
+        <v>39</v>
+      </c>
+      <c r="M8">
+        <v>25</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -8423,7 +8747,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:D4"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -8486,7 +8810,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M9"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -8753,330 +9077,6 @@
       </c>
       <c r="M9">
         <v>7</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M10"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" customWidth="1"/>
-    <col min="13" max="13" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="M1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2">
-        <v>5</v>
-      </c>
-      <c r="C2">
-        <v>3</v>
-      </c>
-      <c r="D2">
-        <v>7</v>
-      </c>
-      <c r="E2">
-        <v>5</v>
-      </c>
-      <c r="F2">
-        <v>5</v>
-      </c>
-      <c r="G2">
-        <v>4</v>
-      </c>
-      <c r="H2">
-        <v>6</v>
-      </c>
-      <c r="I2">
-        <v>4</v>
-      </c>
-      <c r="J2">
-        <v>7</v>
-      </c>
-      <c r="K2">
-        <v>7</v>
-      </c>
-      <c r="L2">
-        <v>5</v>
-      </c>
-      <c r="M2">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3">
-        <v>3</v>
-      </c>
-      <c r="C3">
-        <v>2</v>
-      </c>
-      <c r="D3">
-        <v>8</v>
-      </c>
-      <c r="E3">
-        <v>9</v>
-      </c>
-      <c r="F3">
-        <v>19</v>
-      </c>
-      <c r="G3">
-        <v>9</v>
-      </c>
-      <c r="H3">
-        <v>8</v>
-      </c>
-      <c r="I3">
-        <v>13</v>
-      </c>
-      <c r="J3">
-        <v>12</v>
-      </c>
-      <c r="K3">
-        <v>17</v>
-      </c>
-      <c r="L3">
-        <v>13</v>
-      </c>
-      <c r="M3">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="I4">
-        <v>1</v>
-      </c>
-      <c r="M4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="K5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="E6">
-        <v>1</v>
-      </c>
-      <c r="F6">
-        <v>2</v>
-      </c>
-      <c r="J6">
-        <v>2</v>
-      </c>
-      <c r="M6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
-      <c r="A7" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E7">
-        <v>1</v>
-      </c>
-      <c r="I7">
-        <v>1</v>
-      </c>
-      <c r="K7">
-        <v>1</v>
-      </c>
-      <c r="L7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13">
-      <c r="A8" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B8">
-        <v>24</v>
-      </c>
-      <c r="C8">
-        <v>37</v>
-      </c>
-      <c r="D8">
-        <v>21</v>
-      </c>
-      <c r="E8">
-        <v>22</v>
-      </c>
-      <c r="F8">
-        <v>27</v>
-      </c>
-      <c r="G8">
-        <v>15</v>
-      </c>
-      <c r="H8">
-        <v>25</v>
-      </c>
-      <c r="I8">
-        <v>21</v>
-      </c>
-      <c r="J8">
-        <v>26</v>
-      </c>
-      <c r="K8">
-        <v>49</v>
-      </c>
-      <c r="L8">
-        <v>44</v>
-      </c>
-      <c r="M8">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13">
-      <c r="A9" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B9">
-        <v>45</v>
-      </c>
-      <c r="C9">
-        <v>64</v>
-      </c>
-      <c r="D9">
-        <v>46</v>
-      </c>
-      <c r="E9">
-        <v>50</v>
-      </c>
-      <c r="F9">
-        <v>38</v>
-      </c>
-      <c r="G9">
-        <v>19</v>
-      </c>
-      <c r="H9">
-        <v>27</v>
-      </c>
-      <c r="I9">
-        <v>37</v>
-      </c>
-      <c r="J9">
-        <v>20</v>
-      </c>
-      <c r="K9">
-        <v>35</v>
-      </c>
-      <c r="L9">
-        <v>35</v>
-      </c>
-      <c r="M9">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13">
-      <c r="A10" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B10">
-        <v>77</v>
-      </c>
-      <c r="C10">
-        <v>106</v>
-      </c>
-      <c r="D10">
-        <v>82</v>
-      </c>
-      <c r="E10">
-        <v>88</v>
-      </c>
-      <c r="F10">
-        <v>91</v>
-      </c>
-      <c r="G10">
-        <v>47</v>
-      </c>
-      <c r="H10">
-        <v>66</v>
-      </c>
-      <c r="I10">
-        <v>77</v>
-      </c>
-      <c r="J10">
-        <v>67</v>
-      </c>
-      <c r="K10">
-        <v>110</v>
-      </c>
-      <c r="L10">
-        <v>98</v>
-      </c>
-      <c r="M10">
-        <v>36</v>
       </c>
     </row>
   </sheetData>
@@ -14580,6 +14580,257 @@
 
 <file path=xl/worksheets/sheet44.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:M8"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+    <col min="13" max="13" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="M1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>2</v>
+      </c>
+      <c r="F2">
+        <v>2</v>
+      </c>
+      <c r="I2">
+        <v>3</v>
+      </c>
+      <c r="J2">
+        <v>2</v>
+      </c>
+      <c r="K2">
+        <v>1</v>
+      </c>
+      <c r="L2">
+        <v>5</v>
+      </c>
+      <c r="M2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
+      <c r="E3">
+        <v>1</v>
+      </c>
+      <c r="H3">
+        <v>2</v>
+      </c>
+      <c r="I3">
+        <v>1</v>
+      </c>
+      <c r="J3">
+        <v>1</v>
+      </c>
+      <c r="K3">
+        <v>2</v>
+      </c>
+      <c r="L3">
+        <v>2</v>
+      </c>
+      <c r="M3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
+      <c r="I4">
+        <v>1</v>
+      </c>
+      <c r="K4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="L5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6">
+        <v>1</v>
+      </c>
+      <c r="F6">
+        <v>4</v>
+      </c>
+      <c r="H6">
+        <v>1</v>
+      </c>
+      <c r="I6">
+        <v>2</v>
+      </c>
+      <c r="K6">
+        <v>1</v>
+      </c>
+      <c r="M6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7">
+        <v>10</v>
+      </c>
+      <c r="C7">
+        <v>20</v>
+      </c>
+      <c r="D7">
+        <v>25</v>
+      </c>
+      <c r="E7">
+        <v>30</v>
+      </c>
+      <c r="F7">
+        <v>41</v>
+      </c>
+      <c r="G7">
+        <v>10</v>
+      </c>
+      <c r="H7">
+        <v>5</v>
+      </c>
+      <c r="I7">
+        <v>5</v>
+      </c>
+      <c r="J7">
+        <v>15</v>
+      </c>
+      <c r="K7">
+        <v>17</v>
+      </c>
+      <c r="L7">
+        <v>12</v>
+      </c>
+      <c r="M7">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13">
+      <c r="A8" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B8">
+        <v>12</v>
+      </c>
+      <c r="C8">
+        <v>22</v>
+      </c>
+      <c r="D8">
+        <v>27</v>
+      </c>
+      <c r="E8">
+        <v>31</v>
+      </c>
+      <c r="F8">
+        <v>47</v>
+      </c>
+      <c r="G8">
+        <v>10</v>
+      </c>
+      <c r="H8">
+        <v>8</v>
+      </c>
+      <c r="I8">
+        <v>12</v>
+      </c>
+      <c r="J8">
+        <v>18</v>
+      </c>
+      <c r="K8">
+        <v>22</v>
+      </c>
+      <c r="L8">
+        <v>21</v>
+      </c>
+      <c r="M8">
+        <v>16</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet45.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -14857,7 +15108,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet45.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet46.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -15073,257 +15324,6 @@
       </c>
       <c r="M6">
         <v>3</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet46.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M8"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" customWidth="1"/>
-    <col min="13" max="13" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="M1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2">
-        <v>1</v>
-      </c>
-      <c r="D2">
-        <v>2</v>
-      </c>
-      <c r="F2">
-        <v>2</v>
-      </c>
-      <c r="I2">
-        <v>3</v>
-      </c>
-      <c r="J2">
-        <v>2</v>
-      </c>
-      <c r="K2">
-        <v>1</v>
-      </c>
-      <c r="L2">
-        <v>5</v>
-      </c>
-      <c r="M2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C3">
-        <v>1</v>
-      </c>
-      <c r="E3">
-        <v>1</v>
-      </c>
-      <c r="H3">
-        <v>2</v>
-      </c>
-      <c r="I3">
-        <v>1</v>
-      </c>
-      <c r="J3">
-        <v>1</v>
-      </c>
-      <c r="K3">
-        <v>2</v>
-      </c>
-      <c r="L3">
-        <v>2</v>
-      </c>
-      <c r="M3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C4">
-        <v>1</v>
-      </c>
-      <c r="I4">
-        <v>1</v>
-      </c>
-      <c r="K4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="L5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B6">
-        <v>1</v>
-      </c>
-      <c r="F6">
-        <v>4</v>
-      </c>
-      <c r="H6">
-        <v>1</v>
-      </c>
-      <c r="I6">
-        <v>2</v>
-      </c>
-      <c r="K6">
-        <v>1</v>
-      </c>
-      <c r="M6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
-      <c r="A7" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B7">
-        <v>10</v>
-      </c>
-      <c r="C7">
-        <v>20</v>
-      </c>
-      <c r="D7">
-        <v>25</v>
-      </c>
-      <c r="E7">
-        <v>30</v>
-      </c>
-      <c r="F7">
-        <v>41</v>
-      </c>
-      <c r="G7">
-        <v>10</v>
-      </c>
-      <c r="H7">
-        <v>5</v>
-      </c>
-      <c r="I7">
-        <v>5</v>
-      </c>
-      <c r="J7">
-        <v>15</v>
-      </c>
-      <c r="K7">
-        <v>17</v>
-      </c>
-      <c r="L7">
-        <v>12</v>
-      </c>
-      <c r="M7">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13">
-      <c r="A8" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B8">
-        <v>12</v>
-      </c>
-      <c r="C8">
-        <v>22</v>
-      </c>
-      <c r="D8">
-        <v>27</v>
-      </c>
-      <c r="E8">
-        <v>31</v>
-      </c>
-      <c r="F8">
-        <v>47</v>
-      </c>
-      <c r="G8">
-        <v>10</v>
-      </c>
-      <c r="H8">
-        <v>8</v>
-      </c>
-      <c r="I8">
-        <v>12</v>
-      </c>
-      <c r="J8">
-        <v>18</v>
-      </c>
-      <c r="K8">
-        <v>22</v>
-      </c>
-      <c r="L8">
-        <v>21</v>
-      </c>
-      <c r="M8">
-        <v>16</v>
       </c>
     </row>
   </sheetData>
@@ -20106,14 +20106,20 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="H2">
+      <c r="C2">
+        <v>2</v>
+      </c>
+      <c r="G2">
         <v>1</v>
       </c>
       <c r="I2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J2">
         <v>1</v>
+      </c>
+      <c r="L2">
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -20121,21 +20127,18 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>2</v>
-      </c>
-      <c r="E3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F3">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="H3">
+        <v>1</v>
       </c>
       <c r="J3">
-        <v>4</v>
-      </c>
-      <c r="K3">
-        <v>1</v>
-      </c>
-      <c r="M3">
+        <v>1</v>
+      </c>
+      <c r="L3">
         <v>1</v>
       </c>
     </row>
@@ -20144,37 +20147,37 @@
         <v>8</v>
       </c>
       <c r="B4">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="C4">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D4">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E4">
         <v>2</v>
       </c>
       <c r="F4">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G4">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I4">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="J4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M4">
         <v>1</v>
@@ -20185,34 +20188,40 @@
         <v>9</v>
       </c>
       <c r="B5">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C5">
+        <v>9</v>
+      </c>
+      <c r="D5">
+        <v>8</v>
+      </c>
+      <c r="E5">
+        <v>16</v>
+      </c>
+      <c r="F5">
+        <v>26</v>
+      </c>
+      <c r="G5">
+        <v>3</v>
+      </c>
+      <c r="H5">
         <v>6</v>
       </c>
-      <c r="D5">
-        <v>4</v>
-      </c>
-      <c r="E5">
-        <v>3</v>
-      </c>
-      <c r="F5">
-        <v>4</v>
-      </c>
-      <c r="G5">
-        <v>1</v>
-      </c>
-      <c r="H5">
-        <v>1</v>
+      <c r="I5">
+        <v>5</v>
+      </c>
+      <c r="J5">
+        <v>6</v>
       </c>
       <c r="K5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M5">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -20220,40 +20229,40 @@
         <v>10</v>
       </c>
       <c r="B6">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="C6">
+        <v>16</v>
+      </c>
+      <c r="D6">
+        <v>14</v>
+      </c>
+      <c r="E6">
+        <v>18</v>
+      </c>
+      <c r="F6">
+        <v>34</v>
+      </c>
+      <c r="G6">
+        <v>8</v>
+      </c>
+      <c r="H6">
+        <v>8</v>
+      </c>
+      <c r="I6">
+        <v>16</v>
+      </c>
+      <c r="J6">
+        <v>11</v>
+      </c>
+      <c r="K6">
         <v>10</v>
       </c>
-      <c r="D6">
-        <v>5</v>
-      </c>
-      <c r="E6">
+      <c r="L6">
         <v>7</v>
       </c>
-      <c r="F6">
-        <v>10</v>
-      </c>
-      <c r="G6">
-        <v>3</v>
-      </c>
-      <c r="H6">
-        <v>5</v>
-      </c>
-      <c r="I6">
-        <v>3</v>
-      </c>
-      <c r="J6">
-        <v>6</v>
-      </c>
-      <c r="K6">
-        <v>8</v>
-      </c>
-      <c r="L6">
-        <v>4</v>
-      </c>
       <c r="M6">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -20262,6 +20271,226 @@
 </file>
 
 <file path=xl/worksheets/sheet66.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:M6"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="18.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+    <col min="13" max="13" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="M1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="H2">
+        <v>1</v>
+      </c>
+      <c r="I2">
+        <v>2</v>
+      </c>
+      <c r="J2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>2</v>
+      </c>
+      <c r="E3">
+        <v>2</v>
+      </c>
+      <c r="F3">
+        <v>2</v>
+      </c>
+      <c r="J3">
+        <v>4</v>
+      </c>
+      <c r="K3">
+        <v>1</v>
+      </c>
+      <c r="M3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4">
+        <v>8</v>
+      </c>
+      <c r="C4">
+        <v>4</v>
+      </c>
+      <c r="D4">
+        <v>1</v>
+      </c>
+      <c r="E4">
+        <v>2</v>
+      </c>
+      <c r="F4">
+        <v>4</v>
+      </c>
+      <c r="G4">
+        <v>2</v>
+      </c>
+      <c r="H4">
+        <v>3</v>
+      </c>
+      <c r="I4">
+        <v>1</v>
+      </c>
+      <c r="J4">
+        <v>1</v>
+      </c>
+      <c r="K4">
+        <v>5</v>
+      </c>
+      <c r="L4">
+        <v>2</v>
+      </c>
+      <c r="M4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5">
+        <v>7</v>
+      </c>
+      <c r="C5">
+        <v>6</v>
+      </c>
+      <c r="D5">
+        <v>4</v>
+      </c>
+      <c r="E5">
+        <v>3</v>
+      </c>
+      <c r="F5">
+        <v>4</v>
+      </c>
+      <c r="G5">
+        <v>1</v>
+      </c>
+      <c r="H5">
+        <v>1</v>
+      </c>
+      <c r="K5">
+        <v>2</v>
+      </c>
+      <c r="L5">
+        <v>2</v>
+      </c>
+      <c r="M5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6">
+        <v>17</v>
+      </c>
+      <c r="C6">
+        <v>10</v>
+      </c>
+      <c r="D6">
+        <v>5</v>
+      </c>
+      <c r="E6">
+        <v>7</v>
+      </c>
+      <c r="F6">
+        <v>10</v>
+      </c>
+      <c r="G6">
+        <v>3</v>
+      </c>
+      <c r="H6">
+        <v>5</v>
+      </c>
+      <c r="I6">
+        <v>3</v>
+      </c>
+      <c r="J6">
+        <v>6</v>
+      </c>
+      <c r="K6">
+        <v>8</v>
+      </c>
+      <c r="L6">
+        <v>4</v>
+      </c>
+      <c r="M6">
+        <v>3</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet67.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:J6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -20403,7 +20632,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet67.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet68.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -20646,7 +20875,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet68.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet69.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -20823,168 +21052,6 @@
       </c>
       <c r="M6">
         <v>4</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet69.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J7"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="19.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:10">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="E2">
-        <v>1</v>
-      </c>
-      <c r="H2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C3">
-        <v>1</v>
-      </c>
-      <c r="I3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10">
-      <c r="A4" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10">
-      <c r="A5" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5">
-        <v>1</v>
-      </c>
-      <c r="C5">
-        <v>1</v>
-      </c>
-      <c r="F5">
-        <v>1</v>
-      </c>
-      <c r="H5">
-        <v>1</v>
-      </c>
-      <c r="I5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10">
-      <c r="A6" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B6">
-        <v>2</v>
-      </c>
-      <c r="C6">
-        <v>2</v>
-      </c>
-      <c r="D6">
-        <v>1</v>
-      </c>
-      <c r="F6">
-        <v>1</v>
-      </c>
-      <c r="G6">
-        <v>3</v>
-      </c>
-      <c r="H6">
-        <v>1</v>
-      </c>
-      <c r="J6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10">
-      <c r="A7" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B7">
-        <v>4</v>
-      </c>
-      <c r="C7">
-        <v>4</v>
-      </c>
-      <c r="D7">
-        <v>1</v>
-      </c>
-      <c r="E7">
-        <v>1</v>
-      </c>
-      <c r="F7">
-        <v>2</v>
-      </c>
-      <c r="G7">
-        <v>3</v>
-      </c>
-      <c r="H7">
-        <v>3</v>
-      </c>
-      <c r="I7">
-        <v>2</v>
-      </c>
-      <c r="J7">
-        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -21310,6 +21377,168 @@
 
 <file path=xl/worksheets/sheet70.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:J7"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="19.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
+      <c r="H2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
+      <c r="I3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10">
+      <c r="A4" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10">
+      <c r="A5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5">
+        <v>1</v>
+      </c>
+      <c r="C5">
+        <v>1</v>
+      </c>
+      <c r="F5">
+        <v>1</v>
+      </c>
+      <c r="H5">
+        <v>1</v>
+      </c>
+      <c r="I5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10">
+      <c r="A6" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6">
+        <v>2</v>
+      </c>
+      <c r="C6">
+        <v>2</v>
+      </c>
+      <c r="D6">
+        <v>1</v>
+      </c>
+      <c r="F6">
+        <v>1</v>
+      </c>
+      <c r="G6">
+        <v>3</v>
+      </c>
+      <c r="H6">
+        <v>1</v>
+      </c>
+      <c r="J6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10">
+      <c r="A7" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7">
+        <v>4</v>
+      </c>
+      <c r="C7">
+        <v>4</v>
+      </c>
+      <c r="D7">
+        <v>1</v>
+      </c>
+      <c r="E7">
+        <v>1</v>
+      </c>
+      <c r="F7">
+        <v>2</v>
+      </c>
+      <c r="G7">
+        <v>3</v>
+      </c>
+      <c r="H7">
+        <v>3</v>
+      </c>
+      <c r="I7">
+        <v>2</v>
+      </c>
+      <c r="J7">
+        <v>2</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet71.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:G5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -21418,7 +21647,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet71.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet72.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M8"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -21684,7 +21913,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet72.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet73.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:L6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -21849,7 +22078,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet73.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet74.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -22048,7 +22277,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet74.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet75.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:I6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -22186,7 +22415,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet75.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet76.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -22411,7 +22640,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet76.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet77.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:I5"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -22553,7 +22782,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet77.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet78.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -22749,7 +22978,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet78.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet79.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:H5"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -22853,195 +23082,6 @@
       </c>
       <c r="H5">
         <v>3</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet79.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M7"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" customWidth="1"/>
-    <col min="13" max="13" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="M1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2">
-        <v>1</v>
-      </c>
-      <c r="G2">
-        <v>1</v>
-      </c>
-      <c r="L2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="E3">
-        <v>1</v>
-      </c>
-      <c r="L3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="I4">
-        <v>1</v>
-      </c>
-      <c r="J4">
-        <v>1</v>
-      </c>
-      <c r="M4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5">
-        <v>3</v>
-      </c>
-      <c r="D5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B6">
-        <v>3</v>
-      </c>
-      <c r="C6">
-        <v>4</v>
-      </c>
-      <c r="D6">
-        <v>4</v>
-      </c>
-      <c r="E6">
-        <v>1</v>
-      </c>
-      <c r="F6">
-        <v>3</v>
-      </c>
-      <c r="H6">
-        <v>1</v>
-      </c>
-      <c r="J6">
-        <v>1</v>
-      </c>
-      <c r="K6">
-        <v>4</v>
-      </c>
-      <c r="L6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
-      <c r="A7" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B7">
-        <v>7</v>
-      </c>
-      <c r="C7">
-        <v>4</v>
-      </c>
-      <c r="D7">
-        <v>5</v>
-      </c>
-      <c r="E7">
-        <v>2</v>
-      </c>
-      <c r="F7">
-        <v>3</v>
-      </c>
-      <c r="G7">
-        <v>1</v>
-      </c>
-      <c r="H7">
-        <v>1</v>
-      </c>
-      <c r="I7">
-        <v>1</v>
-      </c>
-      <c r="J7">
-        <v>2</v>
-      </c>
-      <c r="K7">
-        <v>4</v>
-      </c>
-      <c r="L7">
-        <v>4</v>
-      </c>
-      <c r="M7">
-        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -23381,13 +23421,10 @@
       <c r="B2">
         <v>1</v>
       </c>
-      <c r="H2">
-        <v>1</v>
-      </c>
-      <c r="I2">
-        <v>1</v>
-      </c>
-      <c r="K2">
+      <c r="G2">
+        <v>1</v>
+      </c>
+      <c r="L2">
         <v>1</v>
       </c>
     </row>
@@ -23395,16 +23432,7 @@
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B3">
-        <v>1</v>
-      </c>
       <c r="E3">
-        <v>1</v>
-      </c>
-      <c r="J3">
-        <v>1</v>
-      </c>
-      <c r="K3">
         <v>1</v>
       </c>
       <c r="L3">
@@ -23415,7 +23443,13 @@
       <c r="A4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="H4">
+      <c r="I4">
+        <v>1</v>
+      </c>
+      <c r="J4">
+        <v>1</v>
+      </c>
+      <c r="M4">
         <v>1</v>
       </c>
     </row>
@@ -23424,15 +23458,9 @@
         <v>8</v>
       </c>
       <c r="B5">
-        <v>1</v>
-      </c>
-      <c r="C5">
-        <v>2</v>
-      </c>
-      <c r="J5">
-        <v>2</v>
-      </c>
-      <c r="K5">
+        <v>3</v>
+      </c>
+      <c r="D5">
         <v>1</v>
       </c>
     </row>
@@ -23444,34 +23472,28 @@
         <v>3</v>
       </c>
       <c r="C6">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D6">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E6">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="F6">
-        <v>2</v>
-      </c>
-      <c r="G6">
         <v>3</v>
       </c>
       <c r="H6">
-        <v>3</v>
-      </c>
-      <c r="I6">
         <v>1</v>
       </c>
       <c r="J6">
         <v>1</v>
       </c>
+      <c r="K6">
+        <v>4</v>
+      </c>
       <c r="L6">
         <v>2</v>
-      </c>
-      <c r="M6">
-        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -23479,37 +23501,37 @@
         <v>10</v>
       </c>
       <c r="B7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D7">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E7">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="F7">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G7">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H7">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J7">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M7">
         <v>1</v>
@@ -23585,34 +23607,16 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C2">
-        <v>1</v>
-      </c>
-      <c r="D2">
-        <v>1</v>
-      </c>
-      <c r="E2">
-        <v>1</v>
-      </c>
-      <c r="F2">
-        <v>2</v>
+      <c r="B2">
+        <v>1</v>
       </c>
       <c r="H2">
         <v>1</v>
       </c>
       <c r="I2">
-        <v>2</v>
-      </c>
-      <c r="J2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K2">
-        <v>2</v>
-      </c>
-      <c r="L2">
-        <v>2</v>
-      </c>
-      <c r="M2">
         <v>1</v>
       </c>
     </row>
@@ -23623,31 +23627,16 @@
       <c r="B3">
         <v>1</v>
       </c>
-      <c r="C3">
-        <v>1</v>
-      </c>
-      <c r="D3">
-        <v>1</v>
-      </c>
       <c r="E3">
         <v>1</v>
       </c>
-      <c r="G3">
-        <v>2</v>
-      </c>
-      <c r="H3">
-        <v>1</v>
-      </c>
-      <c r="I3">
-        <v>2</v>
+      <c r="J3">
+        <v>1</v>
       </c>
       <c r="K3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L3">
-        <v>3</v>
-      </c>
-      <c r="M3">
         <v>1</v>
       </c>
     </row>
@@ -23655,7 +23644,7 @@
       <c r="A4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C4">
+      <c r="H4">
         <v>1</v>
       </c>
     </row>
@@ -23669,34 +23658,10 @@
       <c r="C5">
         <v>2</v>
       </c>
-      <c r="D5">
-        <v>5</v>
-      </c>
-      <c r="E5">
-        <v>1</v>
-      </c>
-      <c r="F5">
-        <v>1</v>
-      </c>
-      <c r="G5">
-        <v>2</v>
-      </c>
-      <c r="H5">
-        <v>3</v>
-      </c>
-      <c r="I5">
-        <v>2</v>
-      </c>
       <c r="J5">
         <v>2</v>
       </c>
       <c r="K5">
-        <v>2</v>
-      </c>
-      <c r="L5">
-        <v>1</v>
-      </c>
-      <c r="M5">
         <v>1</v>
       </c>
     </row>
@@ -23705,40 +23670,37 @@
         <v>9</v>
       </c>
       <c r="B6">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="C6">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="D6">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="E6">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F6">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="G6">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="H6">
         <v>3</v>
       </c>
       <c r="I6">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="J6">
-        <v>7</v>
-      </c>
-      <c r="K6">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L6">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="M6">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -23746,40 +23708,40 @@
         <v>10</v>
       </c>
       <c r="B7">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="C7">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="D7">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="E7">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="F7">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="G7">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="H7">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="I7">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="J7">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="K7">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="L7">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="M7">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -23788,6 +23750,273 @@
 </file>
 
 <file path=xl/worksheets/sheet82.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:M7"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+    <col min="13" max="13" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="M1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
+      <c r="F2">
+        <v>2</v>
+      </c>
+      <c r="H2">
+        <v>1</v>
+      </c>
+      <c r="I2">
+        <v>2</v>
+      </c>
+      <c r="J2">
+        <v>4</v>
+      </c>
+      <c r="K2">
+        <v>2</v>
+      </c>
+      <c r="L2">
+        <v>2</v>
+      </c>
+      <c r="M2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>1</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
+      <c r="E3">
+        <v>1</v>
+      </c>
+      <c r="G3">
+        <v>2</v>
+      </c>
+      <c r="H3">
+        <v>1</v>
+      </c>
+      <c r="I3">
+        <v>2</v>
+      </c>
+      <c r="K3">
+        <v>2</v>
+      </c>
+      <c r="L3">
+        <v>3</v>
+      </c>
+      <c r="M3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5">
+        <v>1</v>
+      </c>
+      <c r="C5">
+        <v>2</v>
+      </c>
+      <c r="D5">
+        <v>5</v>
+      </c>
+      <c r="E5">
+        <v>1</v>
+      </c>
+      <c r="F5">
+        <v>1</v>
+      </c>
+      <c r="G5">
+        <v>2</v>
+      </c>
+      <c r="H5">
+        <v>3</v>
+      </c>
+      <c r="I5">
+        <v>2</v>
+      </c>
+      <c r="J5">
+        <v>2</v>
+      </c>
+      <c r="K5">
+        <v>2</v>
+      </c>
+      <c r="L5">
+        <v>1</v>
+      </c>
+      <c r="M5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6">
+        <v>14</v>
+      </c>
+      <c r="C6">
+        <v>12</v>
+      </c>
+      <c r="D6">
+        <v>14</v>
+      </c>
+      <c r="E6">
+        <v>14</v>
+      </c>
+      <c r="F6">
+        <v>15</v>
+      </c>
+      <c r="G6">
+        <v>9</v>
+      </c>
+      <c r="H6">
+        <v>3</v>
+      </c>
+      <c r="I6">
+        <v>6</v>
+      </c>
+      <c r="J6">
+        <v>7</v>
+      </c>
+      <c r="K6">
+        <v>5</v>
+      </c>
+      <c r="L6">
+        <v>11</v>
+      </c>
+      <c r="M6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7">
+        <v>16</v>
+      </c>
+      <c r="C7">
+        <v>17</v>
+      </c>
+      <c r="D7">
+        <v>21</v>
+      </c>
+      <c r="E7">
+        <v>17</v>
+      </c>
+      <c r="F7">
+        <v>18</v>
+      </c>
+      <c r="G7">
+        <v>13</v>
+      </c>
+      <c r="H7">
+        <v>8</v>
+      </c>
+      <c r="I7">
+        <v>12</v>
+      </c>
+      <c r="J7">
+        <v>13</v>
+      </c>
+      <c r="K7">
+        <v>11</v>
+      </c>
+      <c r="L7">
+        <v>17</v>
+      </c>
+      <c r="M7">
+        <v>8</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet83.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:H6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -23903,7 +24132,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet83.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet84.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M8"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -24130,7 +24359,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet84.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet85.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:K5"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -24283,7 +24512,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet85.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet86.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -24460,235 +24689,6 @@
       </c>
       <c r="M6">
         <v>2</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet86.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M6"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="18.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" customWidth="1"/>
-    <col min="13" max="13" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="M1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2">
-        <v>2</v>
-      </c>
-      <c r="G2">
-        <v>1</v>
-      </c>
-      <c r="I2">
-        <v>1</v>
-      </c>
-      <c r="J2">
-        <v>1</v>
-      </c>
-      <c r="L2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3">
-        <v>1</v>
-      </c>
-      <c r="F3">
-        <v>1</v>
-      </c>
-      <c r="H3">
-        <v>1</v>
-      </c>
-      <c r="J3">
-        <v>1</v>
-      </c>
-      <c r="L3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4">
-        <v>3</v>
-      </c>
-      <c r="C4">
-        <v>5</v>
-      </c>
-      <c r="D4">
-        <v>6</v>
-      </c>
-      <c r="E4">
-        <v>2</v>
-      </c>
-      <c r="F4">
-        <v>7</v>
-      </c>
-      <c r="G4">
-        <v>4</v>
-      </c>
-      <c r="H4">
-        <v>1</v>
-      </c>
-      <c r="I4">
-        <v>10</v>
-      </c>
-      <c r="J4">
-        <v>3</v>
-      </c>
-      <c r="K4">
-        <v>6</v>
-      </c>
-      <c r="L4">
-        <v>3</v>
-      </c>
-      <c r="M4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B5">
-        <v>5</v>
-      </c>
-      <c r="C5">
-        <v>9</v>
-      </c>
-      <c r="D5">
-        <v>8</v>
-      </c>
-      <c r="E5">
-        <v>16</v>
-      </c>
-      <c r="F5">
-        <v>26</v>
-      </c>
-      <c r="G5">
-        <v>3</v>
-      </c>
-      <c r="H5">
-        <v>6</v>
-      </c>
-      <c r="I5">
-        <v>5</v>
-      </c>
-      <c r="J5">
-        <v>6</v>
-      </c>
-      <c r="K5">
-        <v>4</v>
-      </c>
-      <c r="L5">
-        <v>1</v>
-      </c>
-      <c r="M5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B6">
-        <v>9</v>
-      </c>
-      <c r="C6">
-        <v>16</v>
-      </c>
-      <c r="D6">
-        <v>14</v>
-      </c>
-      <c r="E6">
-        <v>18</v>
-      </c>
-      <c r="F6">
-        <v>34</v>
-      </c>
-      <c r="G6">
-        <v>8</v>
-      </c>
-      <c r="H6">
-        <v>8</v>
-      </c>
-      <c r="I6">
-        <v>16</v>
-      </c>
-      <c r="J6">
-        <v>11</v>
-      </c>
-      <c r="K6">
-        <v>10</v>
-      </c>
-      <c r="L6">
-        <v>7</v>
-      </c>
-      <c r="M6">
-        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/output/cta-index-crime-full-year.xlsx
+++ b/output/cta-index-crime-full-year.xlsx
@@ -19,18 +19,18 @@
     <sheet name="Rogers Park" sheetId="10" r:id="rId10"/>
     <sheet name="Douglas" sheetId="11" r:id="rId11"/>
     <sheet name="Jefferson Park" sheetId="12" r:id="rId12"/>
-    <sheet name="Grand Crossing" sheetId="13" r:id="rId13"/>
-    <sheet name="Chatham" sheetId="14" r:id="rId14"/>
-    <sheet name="Austin" sheetId="15" r:id="rId15"/>
-    <sheet name="Albany Park" sheetId="16" r:id="rId16"/>
-    <sheet name="Grand Boulevard" sheetId="17" r:id="rId17"/>
-    <sheet name="Belmont Cragin" sheetId="18" r:id="rId18"/>
-    <sheet name="West Ridge" sheetId="19" r:id="rId19"/>
-    <sheet name="Loop" sheetId="20" r:id="rId20"/>
-    <sheet name="Lake View" sheetId="21" r:id="rId21"/>
-    <sheet name="South Shore" sheetId="22" r:id="rId22"/>
-    <sheet name="Mount Greenwood" sheetId="23" r:id="rId23"/>
-    <sheet name="Gage Park" sheetId="24" r:id="rId24"/>
+    <sheet name="Chatham" sheetId="13" r:id="rId13"/>
+    <sheet name="Albany Park" sheetId="14" r:id="rId14"/>
+    <sheet name="Grand Boulevard" sheetId="15" r:id="rId15"/>
+    <sheet name="Belmont Cragin" sheetId="16" r:id="rId16"/>
+    <sheet name="West Ridge" sheetId="17" r:id="rId17"/>
+    <sheet name="Loop" sheetId="18" r:id="rId18"/>
+    <sheet name="Lake View" sheetId="19" r:id="rId19"/>
+    <sheet name="Austin" sheetId="20" r:id="rId20"/>
+    <sheet name="South Shore" sheetId="21" r:id="rId21"/>
+    <sheet name="Mount Greenwood" sheetId="22" r:id="rId22"/>
+    <sheet name="Gage Park" sheetId="23" r:id="rId23"/>
+    <sheet name="Grand Crossing" sheetId="24" r:id="rId24"/>
     <sheet name="West Loop" sheetId="25" r:id="rId25"/>
     <sheet name="Rush &amp; Division" sheetId="26" r:id="rId26"/>
     <sheet name="North Lawndale" sheetId="27" r:id="rId27"/>
@@ -50,9 +50,9 @@
     <sheet name="Roseland" sheetId="41" r:id="rId41"/>
     <sheet name="Woodlawn" sheetId="42" r:id="rId42"/>
     <sheet name="Fuller Park" sheetId="43" r:id="rId43"/>
-    <sheet name="O'Hare" sheetId="44" r:id="rId44"/>
-    <sheet name="Little Italy, UIC" sheetId="45" r:id="rId45"/>
-    <sheet name="Hyde Park" sheetId="46" r:id="rId46"/>
+    <sheet name="Little Italy, UIC" sheetId="44" r:id="rId44"/>
+    <sheet name="Hyde Park" sheetId="45" r:id="rId45"/>
+    <sheet name="O'Hare" sheetId="46" r:id="rId46"/>
     <sheet name="Bucktown" sheetId="47" r:id="rId47"/>
     <sheet name="Calumet Heights" sheetId="48" r:id="rId48"/>
     <sheet name="Edgewater" sheetId="49" r:id="rId49"/>
@@ -2146,41 +2146,38 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2">
-        <v>5</v>
-      </c>
       <c r="C2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D2">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H2">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J2">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K2">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M2">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -2188,56 +2185,56 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D3">
+        <v>7</v>
+      </c>
+      <c r="E3">
+        <v>3</v>
+      </c>
+      <c r="F3">
+        <v>4</v>
+      </c>
+      <c r="G3">
         <v>8</v>
       </c>
-      <c r="E3">
-        <v>9</v>
-      </c>
-      <c r="F3">
-        <v>19</v>
-      </c>
-      <c r="G3">
-        <v>9</v>
-      </c>
       <c r="H3">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="I3">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="J3">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="K3">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="L3">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="M3">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="I4">
-        <v>1</v>
-      </c>
-      <c r="M4">
+      <c r="H4">
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="B5">
+        <v>1</v>
       </c>
       <c r="K5">
         <v>1</v>
@@ -2245,36 +2242,30 @@
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="E6">
-        <v>1</v>
-      </c>
-      <c r="F6">
-        <v>2</v>
-      </c>
-      <c r="J6">
-        <v>2</v>
-      </c>
-      <c r="M6">
+        <v>6</v>
+      </c>
+      <c r="G6">
+        <v>1</v>
+      </c>
+      <c r="H6">
+        <v>1</v>
+      </c>
+      <c r="I6">
         <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="D7">
+        <v>1</v>
       </c>
       <c r="E7">
         <v>1</v>
       </c>
-      <c r="I7">
-        <v>1</v>
-      </c>
-      <c r="K7">
-        <v>1</v>
-      </c>
-      <c r="L7">
-        <v>1</v>
+      <c r="J7">
+        <v>2</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -2282,40 +2273,40 @@
         <v>8</v>
       </c>
       <c r="B8">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="C8">
-        <v>37</v>
+        <v>9</v>
       </c>
       <c r="D8">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="E8">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="F8">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="G8">
         <v>15</v>
       </c>
       <c r="H8">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="I8">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="J8">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="K8">
-        <v>49</v>
+        <v>18</v>
       </c>
       <c r="L8">
-        <v>44</v>
+        <v>19</v>
       </c>
       <c r="M8">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -2323,40 +2314,40 @@
         <v>9</v>
       </c>
       <c r="B9">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C9">
-        <v>64</v>
+        <v>46</v>
       </c>
       <c r="D9">
-        <v>46</v>
+        <v>32</v>
       </c>
       <c r="E9">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="F9">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="G9">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="H9">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="I9">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="J9">
         <v>20</v>
       </c>
       <c r="K9">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="L9">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="M9">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -2364,40 +2355,40 @@
         <v>10</v>
       </c>
       <c r="B10">
-        <v>77</v>
+        <v>51</v>
       </c>
       <c r="C10">
-        <v>106</v>
+        <v>57</v>
       </c>
       <c r="D10">
-        <v>82</v>
+        <v>62</v>
       </c>
       <c r="E10">
-        <v>88</v>
+        <v>48</v>
       </c>
       <c r="F10">
-        <v>91</v>
+        <v>60</v>
       </c>
       <c r="G10">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="H10">
-        <v>66</v>
+        <v>31</v>
       </c>
       <c r="I10">
-        <v>77</v>
+        <v>44</v>
       </c>
       <c r="J10">
-        <v>67</v>
+        <v>43</v>
       </c>
       <c r="K10">
-        <v>110</v>
+        <v>57</v>
       </c>
       <c r="L10">
-        <v>98</v>
+        <v>40</v>
       </c>
       <c r="M10">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
   </sheetData>
@@ -2407,7 +2398,7 @@
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M10"/>
+  <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="23.7109375" customWidth="1"/>
@@ -2470,38 +2461,29 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C2">
-        <v>1</v>
-      </c>
       <c r="D2">
-        <v>5</v>
-      </c>
-      <c r="E2">
         <v>1</v>
       </c>
       <c r="F2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G2">
         <v>1</v>
       </c>
-      <c r="H2">
-        <v>3</v>
-      </c>
       <c r="I2">
         <v>2</v>
       </c>
       <c r="J2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K2">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="L2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M2">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -2509,210 +2491,153 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C3">
         <v>1</v>
       </c>
-      <c r="D3">
-        <v>7</v>
-      </c>
-      <c r="E3">
-        <v>3</v>
-      </c>
-      <c r="F3">
-        <v>4</v>
-      </c>
       <c r="G3">
-        <v>8</v>
-      </c>
-      <c r="H3">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I3">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="J3">
-        <v>4</v>
-      </c>
-      <c r="K3">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="L3">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="M3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="H4">
+        <v>5</v>
+      </c>
+      <c r="E4">
+        <v>2</v>
+      </c>
+      <c r="J4">
+        <v>1</v>
+      </c>
+      <c r="K4">
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B5">
         <v>1</v>
       </c>
+      <c r="C5">
+        <v>1</v>
+      </c>
+      <c r="D5">
+        <v>2</v>
+      </c>
+      <c r="E5">
+        <v>2</v>
+      </c>
+      <c r="G5">
+        <v>1</v>
+      </c>
+      <c r="I5">
+        <v>1</v>
+      </c>
+      <c r="J5">
+        <v>3</v>
+      </c>
       <c r="K5">
+        <v>4</v>
+      </c>
+      <c r="M5">
         <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
-        <v>6</v>
+        <v>9</v>
+      </c>
+      <c r="B6">
+        <v>8</v>
+      </c>
+      <c r="C6">
+        <v>13</v>
+      </c>
+      <c r="D6">
+        <v>10</v>
+      </c>
+      <c r="E6">
+        <v>9</v>
+      </c>
+      <c r="F6">
+        <v>9</v>
       </c>
       <c r="G6">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="H6">
         <v>1</v>
       </c>
       <c r="I6">
-        <v>1</v>
+        <v>4</v>
+      </c>
+      <c r="J6">
+        <v>5</v>
+      </c>
+      <c r="K6">
+        <v>8</v>
+      </c>
+      <c r="L6">
+        <v>3</v>
+      </c>
+      <c r="M6">
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="1" t="s">
-        <v>7</v>
+        <v>10</v>
+      </c>
+      <c r="B7">
+        <v>10</v>
+      </c>
+      <c r="C7">
+        <v>15</v>
       </c>
       <c r="D7">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="E7">
-        <v>1</v>
+        <v>13</v>
+      </c>
+      <c r="F7">
+        <v>10</v>
+      </c>
+      <c r="G7">
+        <v>12</v>
+      </c>
+      <c r="H7">
+        <v>1</v>
+      </c>
+      <c r="I7">
+        <v>8</v>
       </c>
       <c r="J7">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13">
-      <c r="A8" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B8">
-        <v>5</v>
-      </c>
-      <c r="C8">
-        <v>9</v>
-      </c>
-      <c r="D8">
-        <v>17</v>
-      </c>
-      <c r="E8">
-        <v>13</v>
-      </c>
-      <c r="F8">
-        <v>19</v>
-      </c>
-      <c r="G8">
+        <v>14</v>
+      </c>
+      <c r="K7">
         <v>15</v>
       </c>
-      <c r="H8">
-        <v>5</v>
-      </c>
-      <c r="I8">
-        <v>15</v>
-      </c>
-      <c r="J8">
-        <v>12</v>
-      </c>
-      <c r="K8">
-        <v>18</v>
-      </c>
-      <c r="L8">
-        <v>19</v>
-      </c>
-      <c r="M8">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13">
-      <c r="A9" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B9">
-        <v>43</v>
-      </c>
-      <c r="C9">
-        <v>46</v>
-      </c>
-      <c r="D9">
-        <v>32</v>
-      </c>
-      <c r="E9">
-        <v>30</v>
-      </c>
-      <c r="F9">
-        <v>34</v>
-      </c>
-      <c r="G9">
-        <v>15</v>
-      </c>
-      <c r="H9">
-        <v>17</v>
-      </c>
-      <c r="I9">
-        <v>20</v>
-      </c>
-      <c r="J9">
-        <v>20</v>
-      </c>
-      <c r="K9">
-        <v>20</v>
-      </c>
-      <c r="L9">
-        <v>13</v>
-      </c>
-      <c r="M9">
+      <c r="L7">
         <v>6</v>
       </c>
-    </row>
-    <row r="10" spans="1:13">
-      <c r="A10" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B10">
-        <v>51</v>
-      </c>
-      <c r="C10">
-        <v>57</v>
-      </c>
-      <c r="D10">
-        <v>62</v>
-      </c>
-      <c r="E10">
-        <v>48</v>
-      </c>
-      <c r="F10">
-        <v>60</v>
-      </c>
-      <c r="G10">
-        <v>40</v>
-      </c>
-      <c r="H10">
-        <v>31</v>
-      </c>
-      <c r="I10">
-        <v>44</v>
-      </c>
-      <c r="J10">
-        <v>43</v>
-      </c>
-      <c r="K10">
-        <v>57</v>
-      </c>
-      <c r="L10">
-        <v>40</v>
-      </c>
-      <c r="M10">
-        <v>17</v>
+      <c r="M7">
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -2722,10 +2647,10 @@
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M10"/>
+  <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="1" max="1" width="18.7109375" customWidth="1"/>
     <col min="2" max="2" width="4.7109375" customWidth="1"/>
     <col min="3" max="3" width="4.7109375" customWidth="1"/>
     <col min="4" max="4" width="4.7109375" customWidth="1"/>
@@ -2785,41 +2710,29 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2">
-        <v>4</v>
-      </c>
       <c r="C2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E2">
-        <v>5</v>
-      </c>
-      <c r="F2">
-        <v>9</v>
-      </c>
-      <c r="G2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H2">
-        <v>5</v>
-      </c>
-      <c r="I2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J2">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="K2">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="L2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="M2">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -2827,210 +2740,162 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C3">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D3">
-        <v>6</v>
-      </c>
-      <c r="E3">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="F3">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G3">
-        <v>7</v>
-      </c>
-      <c r="H3">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="I3">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J3">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="K3">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="L3">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="M3">
-        <v>10</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="I4">
+        <v>6</v>
+      </c>
+      <c r="H4">
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B5">
-        <v>1</v>
+        <v>7</v>
+      </c>
+      <c r="C5">
+        <v>11</v>
       </c>
       <c r="D5">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E5">
-        <v>1</v>
+        <v>5</v>
+      </c>
+      <c r="F5">
+        <v>5</v>
+      </c>
+      <c r="G5">
+        <v>6</v>
+      </c>
+      <c r="H5">
+        <v>2</v>
+      </c>
+      <c r="I5">
+        <v>2</v>
       </c>
       <c r="J5">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K5">
-        <v>2</v>
-      </c>
-      <c r="M5">
-        <v>1</v>
+        <v>6</v>
+      </c>
+      <c r="L5">
+        <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6">
+        <v>15</v>
+      </c>
+      <c r="C6">
+        <v>16</v>
+      </c>
+      <c r="D6">
+        <v>15</v>
+      </c>
+      <c r="E6">
+        <v>16</v>
+      </c>
+      <c r="F6">
+        <v>11</v>
+      </c>
+      <c r="G6">
+        <v>9</v>
+      </c>
+      <c r="H6">
+        <v>5</v>
+      </c>
+      <c r="I6">
+        <v>5</v>
+      </c>
+      <c r="J6">
+        <v>12</v>
+      </c>
+      <c r="K6">
         <v>6</v>
       </c>
-      <c r="K6">
-        <v>1</v>
+      <c r="L6">
+        <v>4</v>
+      </c>
+      <c r="M6">
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="1" t="s">
-        <v>7</v>
+        <v>10</v>
+      </c>
+      <c r="B7">
+        <v>24</v>
+      </c>
+      <c r="C7">
+        <v>29</v>
+      </c>
+      <c r="D7">
+        <v>25</v>
+      </c>
+      <c r="E7">
+        <v>22</v>
+      </c>
+      <c r="F7">
+        <v>19</v>
+      </c>
+      <c r="G7">
+        <v>16</v>
+      </c>
+      <c r="H7">
+        <v>10</v>
+      </c>
+      <c r="I7">
+        <v>11</v>
+      </c>
+      <c r="J7">
+        <v>20</v>
+      </c>
+      <c r="K7">
+        <v>15</v>
       </c>
       <c r="L7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13">
-      <c r="A8" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B8">
-        <v>23</v>
-      </c>
-      <c r="C8">
-        <v>31</v>
-      </c>
-      <c r="D8">
-        <v>22</v>
-      </c>
-      <c r="E8">
-        <v>44</v>
-      </c>
-      <c r="F8">
-        <v>38</v>
-      </c>
-      <c r="G8">
-        <v>24</v>
-      </c>
-      <c r="H8">
-        <v>50</v>
-      </c>
-      <c r="I8">
-        <v>34</v>
-      </c>
-      <c r="J8">
-        <v>26</v>
-      </c>
-      <c r="K8">
-        <v>24</v>
-      </c>
-      <c r="L8">
-        <v>14</v>
-      </c>
-      <c r="M8">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13">
-      <c r="A9" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B9">
-        <v>46</v>
-      </c>
-      <c r="C9">
-        <v>59</v>
-      </c>
-      <c r="D9">
-        <v>33</v>
-      </c>
-      <c r="E9">
-        <v>73</v>
-      </c>
-      <c r="F9">
-        <v>114</v>
-      </c>
-      <c r="G9">
-        <v>58</v>
-      </c>
-      <c r="H9">
-        <v>41</v>
-      </c>
-      <c r="I9">
-        <v>44</v>
-      </c>
-      <c r="J9">
-        <v>20</v>
-      </c>
-      <c r="K9">
-        <v>25</v>
-      </c>
-      <c r="L9">
-        <v>27</v>
-      </c>
-      <c r="M9">
         <v>16</v>
       </c>
-    </row>
-    <row r="10" spans="1:13">
-      <c r="A10" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B10">
-        <v>78</v>
-      </c>
-      <c r="C10">
-        <v>99</v>
-      </c>
-      <c r="D10">
-        <v>65</v>
-      </c>
-      <c r="E10">
-        <v>130</v>
-      </c>
-      <c r="F10">
-        <v>167</v>
-      </c>
-      <c r="G10">
-        <v>92</v>
-      </c>
-      <c r="H10">
-        <v>104</v>
-      </c>
-      <c r="I10">
-        <v>89</v>
-      </c>
-      <c r="J10">
-        <v>67</v>
-      </c>
-      <c r="K10">
-        <v>71</v>
-      </c>
-      <c r="L10">
-        <v>61</v>
-      </c>
-      <c r="M10">
-        <v>50</v>
+      <c r="M7">
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -3106,25 +2971,7 @@
       <c r="D2">
         <v>1</v>
       </c>
-      <c r="F2">
-        <v>1</v>
-      </c>
-      <c r="G2">
-        <v>1</v>
-      </c>
-      <c r="I2">
-        <v>2</v>
-      </c>
       <c r="J2">
-        <v>4</v>
-      </c>
-      <c r="K2">
-        <v>2</v>
-      </c>
-      <c r="L2">
-        <v>2</v>
-      </c>
-      <c r="M2">
         <v>1</v>
       </c>
     </row>
@@ -3132,25 +2979,16 @@
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B3">
-        <v>1</v>
-      </c>
-      <c r="C3">
-        <v>1</v>
+      <c r="E3">
+        <v>2</v>
       </c>
       <c r="G3">
-        <v>2</v>
-      </c>
-      <c r="I3">
         <v>1</v>
       </c>
       <c r="J3">
         <v>1</v>
       </c>
       <c r="L3">
-        <v>1</v>
-      </c>
-      <c r="M3">
         <v>1</v>
       </c>
     </row>
@@ -3158,13 +2996,7 @@
       <c r="A4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="E4">
-        <v>2</v>
-      </c>
-      <c r="J4">
-        <v>1</v>
-      </c>
-      <c r="K4">
+      <c r="C4">
         <v>1</v>
       </c>
     </row>
@@ -3173,28 +3005,22 @@
         <v>8</v>
       </c>
       <c r="B5">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C5">
-        <v>1</v>
-      </c>
-      <c r="D5">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E5">
-        <v>2</v>
-      </c>
-      <c r="G5">
-        <v>1</v>
-      </c>
-      <c r="I5">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="H5">
+        <v>2</v>
       </c>
       <c r="J5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M5">
         <v>1</v>
@@ -3205,40 +3031,40 @@
         <v>9</v>
       </c>
       <c r="B6">
+        <v>6</v>
+      </c>
+      <c r="C6">
+        <v>2</v>
+      </c>
+      <c r="D6">
+        <v>6</v>
+      </c>
+      <c r="E6">
         <v>8</v>
       </c>
-      <c r="C6">
-        <v>13</v>
-      </c>
-      <c r="D6">
-        <v>10</v>
-      </c>
-      <c r="E6">
-        <v>9</v>
-      </c>
       <c r="F6">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G6">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="H6">
         <v>1</v>
       </c>
       <c r="I6">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J6">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K6">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="L6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -3246,40 +3072,40 @@
         <v>10</v>
       </c>
       <c r="B7">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C7">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="D7">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="E7">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F7">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G7">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="H7">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I7">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="J7">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="K7">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="L7">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="M7">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -3288,474 +3114,6 @@
 </file>
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M7"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="18.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" customWidth="1"/>
-    <col min="13" max="13" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="M1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2">
-        <v>1</v>
-      </c>
-      <c r="D2">
-        <v>1</v>
-      </c>
-      <c r="E2">
-        <v>1</v>
-      </c>
-      <c r="H2">
-        <v>2</v>
-      </c>
-      <c r="J2">
-        <v>1</v>
-      </c>
-      <c r="K2">
-        <v>2</v>
-      </c>
-      <c r="L2">
-        <v>2</v>
-      </c>
-      <c r="M2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3">
-        <v>2</v>
-      </c>
-      <c r="C3">
-        <v>1</v>
-      </c>
-      <c r="D3">
-        <v>1</v>
-      </c>
-      <c r="F3">
-        <v>3</v>
-      </c>
-      <c r="G3">
-        <v>1</v>
-      </c>
-      <c r="I3">
-        <v>4</v>
-      </c>
-      <c r="J3">
-        <v>2</v>
-      </c>
-      <c r="K3">
-        <v>1</v>
-      </c>
-      <c r="L3">
-        <v>4</v>
-      </c>
-      <c r="M3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5">
-        <v>7</v>
-      </c>
-      <c r="C5">
-        <v>11</v>
-      </c>
-      <c r="D5">
-        <v>8</v>
-      </c>
-      <c r="E5">
-        <v>5</v>
-      </c>
-      <c r="F5">
-        <v>5</v>
-      </c>
-      <c r="G5">
-        <v>6</v>
-      </c>
-      <c r="H5">
-        <v>2</v>
-      </c>
-      <c r="I5">
-        <v>2</v>
-      </c>
-      <c r="J5">
-        <v>5</v>
-      </c>
-      <c r="K5">
-        <v>6</v>
-      </c>
-      <c r="L5">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B6">
-        <v>15</v>
-      </c>
-      <c r="C6">
-        <v>16</v>
-      </c>
-      <c r="D6">
-        <v>15</v>
-      </c>
-      <c r="E6">
-        <v>16</v>
-      </c>
-      <c r="F6">
-        <v>11</v>
-      </c>
-      <c r="G6">
-        <v>9</v>
-      </c>
-      <c r="H6">
-        <v>5</v>
-      </c>
-      <c r="I6">
-        <v>5</v>
-      </c>
-      <c r="J6">
-        <v>12</v>
-      </c>
-      <c r="K6">
-        <v>6</v>
-      </c>
-      <c r="L6">
-        <v>4</v>
-      </c>
-      <c r="M6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
-      <c r="A7" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B7">
-        <v>24</v>
-      </c>
-      <c r="C7">
-        <v>29</v>
-      </c>
-      <c r="D7">
-        <v>25</v>
-      </c>
-      <c r="E7">
-        <v>22</v>
-      </c>
-      <c r="F7">
-        <v>19</v>
-      </c>
-      <c r="G7">
-        <v>16</v>
-      </c>
-      <c r="H7">
-        <v>10</v>
-      </c>
-      <c r="I7">
-        <v>11</v>
-      </c>
-      <c r="J7">
-        <v>20</v>
-      </c>
-      <c r="K7">
-        <v>15</v>
-      </c>
-      <c r="L7">
-        <v>16</v>
-      </c>
-      <c r="M7">
-        <v>6</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M7"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" customWidth="1"/>
-    <col min="13" max="13" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="M1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D2">
-        <v>1</v>
-      </c>
-      <c r="J2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="E3">
-        <v>2</v>
-      </c>
-      <c r="G3">
-        <v>1</v>
-      </c>
-      <c r="J3">
-        <v>1</v>
-      </c>
-      <c r="L3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5">
-        <v>5</v>
-      </c>
-      <c r="C5">
-        <v>6</v>
-      </c>
-      <c r="E5">
-        <v>1</v>
-      </c>
-      <c r="H5">
-        <v>2</v>
-      </c>
-      <c r="J5">
-        <v>4</v>
-      </c>
-      <c r="K5">
-        <v>2</v>
-      </c>
-      <c r="M5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B6">
-        <v>6</v>
-      </c>
-      <c r="C6">
-        <v>2</v>
-      </c>
-      <c r="D6">
-        <v>6</v>
-      </c>
-      <c r="E6">
-        <v>8</v>
-      </c>
-      <c r="F6">
-        <v>7</v>
-      </c>
-      <c r="G6">
-        <v>2</v>
-      </c>
-      <c r="H6">
-        <v>1</v>
-      </c>
-      <c r="I6">
-        <v>1</v>
-      </c>
-      <c r="J6">
-        <v>3</v>
-      </c>
-      <c r="K6">
-        <v>1</v>
-      </c>
-      <c r="L6">
-        <v>2</v>
-      </c>
-      <c r="M6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
-      <c r="A7" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B7">
-        <v>11</v>
-      </c>
-      <c r="C7">
-        <v>9</v>
-      </c>
-      <c r="D7">
-        <v>7</v>
-      </c>
-      <c r="E7">
-        <v>11</v>
-      </c>
-      <c r="F7">
-        <v>7</v>
-      </c>
-      <c r="G7">
-        <v>3</v>
-      </c>
-      <c r="H7">
-        <v>3</v>
-      </c>
-      <c r="I7">
-        <v>1</v>
-      </c>
-      <c r="J7">
-        <v>9</v>
-      </c>
-      <c r="K7">
-        <v>3</v>
-      </c>
-      <c r="L7">
-        <v>3</v>
-      </c>
-      <c r="M7">
-        <v>2</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:L8"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -3926,6 +3284,656 @@
       </c>
       <c r="L8">
         <v>2</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:M10"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+    <col min="13" max="13" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="M1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>6</v>
+      </c>
+      <c r="C2">
+        <v>3</v>
+      </c>
+      <c r="D2">
+        <v>12</v>
+      </c>
+      <c r="E2">
+        <v>5</v>
+      </c>
+      <c r="F2">
+        <v>8</v>
+      </c>
+      <c r="G2">
+        <v>4</v>
+      </c>
+      <c r="H2">
+        <v>13</v>
+      </c>
+      <c r="I2">
+        <v>14</v>
+      </c>
+      <c r="J2">
+        <v>22</v>
+      </c>
+      <c r="K2">
+        <v>15</v>
+      </c>
+      <c r="L2">
+        <v>15</v>
+      </c>
+      <c r="M2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>13</v>
+      </c>
+      <c r="C3">
+        <v>13</v>
+      </c>
+      <c r="D3">
+        <v>17</v>
+      </c>
+      <c r="E3">
+        <v>18</v>
+      </c>
+      <c r="F3">
+        <v>14</v>
+      </c>
+      <c r="G3">
+        <v>26</v>
+      </c>
+      <c r="H3">
+        <v>23</v>
+      </c>
+      <c r="I3">
+        <v>32</v>
+      </c>
+      <c r="J3">
+        <v>40</v>
+      </c>
+      <c r="K3">
+        <v>26</v>
+      </c>
+      <c r="L3">
+        <v>34</v>
+      </c>
+      <c r="M3">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G4">
+        <v>1</v>
+      </c>
+      <c r="J4">
+        <v>2</v>
+      </c>
+      <c r="K4">
+        <v>1</v>
+      </c>
+      <c r="L4">
+        <v>1</v>
+      </c>
+      <c r="M4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C5">
+        <v>2</v>
+      </c>
+      <c r="D5">
+        <v>1</v>
+      </c>
+      <c r="E5">
+        <v>2</v>
+      </c>
+      <c r="F5">
+        <v>1</v>
+      </c>
+      <c r="H5">
+        <v>2</v>
+      </c>
+      <c r="I5">
+        <v>4</v>
+      </c>
+      <c r="J5">
+        <v>3</v>
+      </c>
+      <c r="K5">
+        <v>2</v>
+      </c>
+      <c r="L5">
+        <v>5</v>
+      </c>
+      <c r="M5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G6">
+        <v>1</v>
+      </c>
+      <c r="H6">
+        <v>2</v>
+      </c>
+      <c r="J6">
+        <v>2</v>
+      </c>
+      <c r="L6">
+        <v>2</v>
+      </c>
+      <c r="M6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="K7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13">
+      <c r="A8" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8">
+        <v>30</v>
+      </c>
+      <c r="C8">
+        <v>44</v>
+      </c>
+      <c r="D8">
+        <v>49</v>
+      </c>
+      <c r="E8">
+        <v>67</v>
+      </c>
+      <c r="F8">
+        <v>69</v>
+      </c>
+      <c r="G8">
+        <v>57</v>
+      </c>
+      <c r="H8">
+        <v>80</v>
+      </c>
+      <c r="I8">
+        <v>80</v>
+      </c>
+      <c r="J8">
+        <v>64</v>
+      </c>
+      <c r="K8">
+        <v>48</v>
+      </c>
+      <c r="L8">
+        <v>44</v>
+      </c>
+      <c r="M8">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13">
+      <c r="A9" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B9">
+        <v>233</v>
+      </c>
+      <c r="C9">
+        <v>354</v>
+      </c>
+      <c r="D9">
+        <v>538</v>
+      </c>
+      <c r="E9">
+        <v>705</v>
+      </c>
+      <c r="F9">
+        <v>568</v>
+      </c>
+      <c r="G9">
+        <v>168</v>
+      </c>
+      <c r="H9">
+        <v>116</v>
+      </c>
+      <c r="I9">
+        <v>194</v>
+      </c>
+      <c r="J9">
+        <v>122</v>
+      </c>
+      <c r="K9">
+        <v>114</v>
+      </c>
+      <c r="L9">
+        <v>95</v>
+      </c>
+      <c r="M9">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13">
+      <c r="A10" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B10">
+        <v>282</v>
+      </c>
+      <c r="C10">
+        <v>416</v>
+      </c>
+      <c r="D10">
+        <v>617</v>
+      </c>
+      <c r="E10">
+        <v>797</v>
+      </c>
+      <c r="F10">
+        <v>660</v>
+      </c>
+      <c r="G10">
+        <v>257</v>
+      </c>
+      <c r="H10">
+        <v>236</v>
+      </c>
+      <c r="I10">
+        <v>324</v>
+      </c>
+      <c r="J10">
+        <v>255</v>
+      </c>
+      <c r="K10">
+        <v>207</v>
+      </c>
+      <c r="L10">
+        <v>196</v>
+      </c>
+      <c r="M10">
+        <v>89</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:M8"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+    <col min="13" max="13" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="M1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>4</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="E2">
+        <v>4</v>
+      </c>
+      <c r="F2">
+        <v>2</v>
+      </c>
+      <c r="G2">
+        <v>4</v>
+      </c>
+      <c r="H2">
+        <v>2</v>
+      </c>
+      <c r="I2">
+        <v>3</v>
+      </c>
+      <c r="J2">
+        <v>2</v>
+      </c>
+      <c r="K2">
+        <v>6</v>
+      </c>
+      <c r="L2">
+        <v>6</v>
+      </c>
+      <c r="M2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>2</v>
+      </c>
+      <c r="C3">
+        <v>4</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
+      <c r="E3">
+        <v>4</v>
+      </c>
+      <c r="F3">
+        <v>5</v>
+      </c>
+      <c r="G3">
+        <v>4</v>
+      </c>
+      <c r="H3">
+        <v>7</v>
+      </c>
+      <c r="I3">
+        <v>2</v>
+      </c>
+      <c r="J3">
+        <v>11</v>
+      </c>
+      <c r="K3">
+        <v>5</v>
+      </c>
+      <c r="L3">
+        <v>7</v>
+      </c>
+      <c r="M3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="H4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C5">
+        <v>1</v>
+      </c>
+      <c r="H5">
+        <v>1</v>
+      </c>
+      <c r="I5">
+        <v>1</v>
+      </c>
+      <c r="K5">
+        <v>3</v>
+      </c>
+      <c r="L5">
+        <v>2</v>
+      </c>
+      <c r="M5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C6">
+        <v>14</v>
+      </c>
+      <c r="D6">
+        <v>12</v>
+      </c>
+      <c r="E6">
+        <v>10</v>
+      </c>
+      <c r="F6">
+        <v>11</v>
+      </c>
+      <c r="G6">
+        <v>11</v>
+      </c>
+      <c r="H6">
+        <v>17</v>
+      </c>
+      <c r="I6">
+        <v>20</v>
+      </c>
+      <c r="J6">
+        <v>3</v>
+      </c>
+      <c r="K6">
+        <v>10</v>
+      </c>
+      <c r="L6">
+        <v>5</v>
+      </c>
+      <c r="M6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7">
+        <v>58</v>
+      </c>
+      <c r="C7">
+        <v>53</v>
+      </c>
+      <c r="D7">
+        <v>43</v>
+      </c>
+      <c r="E7">
+        <v>56</v>
+      </c>
+      <c r="F7">
+        <v>53</v>
+      </c>
+      <c r="G7">
+        <v>33</v>
+      </c>
+      <c r="H7">
+        <v>23</v>
+      </c>
+      <c r="I7">
+        <v>26</v>
+      </c>
+      <c r="J7">
+        <v>27</v>
+      </c>
+      <c r="K7">
+        <v>17</v>
+      </c>
+      <c r="L7">
+        <v>19</v>
+      </c>
+      <c r="M7">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13">
+      <c r="A8" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B8">
+        <v>60</v>
+      </c>
+      <c r="C8">
+        <v>76</v>
+      </c>
+      <c r="D8">
+        <v>57</v>
+      </c>
+      <c r="E8">
+        <v>74</v>
+      </c>
+      <c r="F8">
+        <v>71</v>
+      </c>
+      <c r="G8">
+        <v>52</v>
+      </c>
+      <c r="H8">
+        <v>51</v>
+      </c>
+      <c r="I8">
+        <v>52</v>
+      </c>
+      <c r="J8">
+        <v>43</v>
+      </c>
+      <c r="K8">
+        <v>41</v>
+      </c>
+      <c r="L8">
+        <v>39</v>
+      </c>
+      <c r="M8">
+        <v>25</v>
       </c>
     </row>
   </sheetData>
@@ -7892,40 +7900,40 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D2">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="E2">
         <v>5</v>
       </c>
       <c r="F2">
+        <v>9</v>
+      </c>
+      <c r="G2">
+        <v>3</v>
+      </c>
+      <c r="H2">
+        <v>5</v>
+      </c>
+      <c r="I2">
+        <v>4</v>
+      </c>
+      <c r="J2">
         <v>8</v>
       </c>
-      <c r="G2">
-        <v>4</v>
-      </c>
-      <c r="H2">
-        <v>13</v>
-      </c>
-      <c r="I2">
-        <v>14</v>
-      </c>
-      <c r="J2">
-        <v>22</v>
-      </c>
       <c r="K2">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="L2">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="M2">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -7933,59 +7941,47 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="C3">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="D3">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="E3">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="F3">
+        <v>6</v>
+      </c>
+      <c r="G3">
+        <v>7</v>
+      </c>
+      <c r="H3">
+        <v>8</v>
+      </c>
+      <c r="I3">
+        <v>6</v>
+      </c>
+      <c r="J3">
+        <v>10</v>
+      </c>
+      <c r="K3">
+        <v>12</v>
+      </c>
+      <c r="L3">
         <v>14</v>
       </c>
-      <c r="G3">
-        <v>26</v>
-      </c>
-      <c r="H3">
-        <v>23</v>
-      </c>
-      <c r="I3">
-        <v>32</v>
-      </c>
-      <c r="J3">
-        <v>40</v>
-      </c>
-      <c r="K3">
-        <v>26</v>
-      </c>
-      <c r="L3">
-        <v>34</v>
-      </c>
       <c r="M3">
-        <v>16</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="G4">
-        <v>1</v>
-      </c>
-      <c r="J4">
-        <v>2</v>
-      </c>
-      <c r="K4">
-        <v>1</v>
-      </c>
-      <c r="L4">
-        <v>1</v>
-      </c>
-      <c r="M4">
+      <c r="I4">
         <v>1</v>
       </c>
     </row>
@@ -7993,23 +7989,14 @@
       <c r="A5" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C5">
-        <v>2</v>
+      <c r="B5">
+        <v>1</v>
       </c>
       <c r="D5">
         <v>1</v>
       </c>
       <c r="E5">
-        <v>2</v>
-      </c>
-      <c r="F5">
-        <v>1</v>
-      </c>
-      <c r="H5">
-        <v>2</v>
-      </c>
-      <c r="I5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J5">
         <v>3</v>
@@ -8017,30 +8004,15 @@
       <c r="K5">
         <v>2</v>
       </c>
-      <c r="L5">
-        <v>5</v>
-      </c>
       <c r="M5">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="G6">
-        <v>1</v>
-      </c>
-      <c r="H6">
-        <v>2</v>
-      </c>
-      <c r="J6">
-        <v>2</v>
-      </c>
-      <c r="L6">
-        <v>2</v>
-      </c>
-      <c r="M6">
+      <c r="K6">
         <v>1</v>
       </c>
     </row>
@@ -8048,7 +8020,7 @@
       <c r="A7" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="K7">
+      <c r="L7">
         <v>1</v>
       </c>
     </row>
@@ -8057,40 +8029,40 @@
         <v>8</v>
       </c>
       <c r="B8">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="C8">
+        <v>31</v>
+      </c>
+      <c r="D8">
+        <v>22</v>
+      </c>
+      <c r="E8">
         <v>44</v>
       </c>
-      <c r="D8">
-        <v>49</v>
-      </c>
-      <c r="E8">
-        <v>67</v>
-      </c>
       <c r="F8">
-        <v>69</v>
+        <v>38</v>
       </c>
       <c r="G8">
-        <v>57</v>
+        <v>24</v>
       </c>
       <c r="H8">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="I8">
-        <v>80</v>
+        <v>34</v>
       </c>
       <c r="J8">
-        <v>64</v>
+        <v>26</v>
       </c>
       <c r="K8">
-        <v>48</v>
+        <v>24</v>
       </c>
       <c r="L8">
-        <v>44</v>
+        <v>14</v>
       </c>
       <c r="M8">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -8098,40 +8070,40 @@
         <v>9</v>
       </c>
       <c r="B9">
-        <v>233</v>
+        <v>46</v>
       </c>
       <c r="C9">
-        <v>354</v>
+        <v>59</v>
       </c>
       <c r="D9">
-        <v>538</v>
+        <v>33</v>
       </c>
       <c r="E9">
-        <v>705</v>
+        <v>73</v>
       </c>
       <c r="F9">
-        <v>568</v>
+        <v>114</v>
       </c>
       <c r="G9">
-        <v>168</v>
+        <v>58</v>
       </c>
       <c r="H9">
-        <v>116</v>
+        <v>41</v>
       </c>
       <c r="I9">
-        <v>194</v>
+        <v>44</v>
       </c>
       <c r="J9">
-        <v>122</v>
+        <v>20</v>
       </c>
       <c r="K9">
-        <v>114</v>
+        <v>25</v>
       </c>
       <c r="L9">
-        <v>95</v>
+        <v>27</v>
       </c>
       <c r="M9">
-        <v>45</v>
+        <v>16</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -8139,40 +8111,40 @@
         <v>10</v>
       </c>
       <c r="B10">
-        <v>282</v>
+        <v>78</v>
       </c>
       <c r="C10">
-        <v>416</v>
+        <v>99</v>
       </c>
       <c r="D10">
-        <v>617</v>
+        <v>65</v>
       </c>
       <c r="E10">
-        <v>797</v>
+        <v>130</v>
       </c>
       <c r="F10">
-        <v>660</v>
+        <v>167</v>
       </c>
       <c r="G10">
-        <v>257</v>
+        <v>92</v>
       </c>
       <c r="H10">
-        <v>236</v>
+        <v>104</v>
       </c>
       <c r="I10">
-        <v>324</v>
+        <v>89</v>
       </c>
       <c r="J10">
-        <v>255</v>
+        <v>67</v>
       </c>
       <c r="K10">
-        <v>207</v>
+        <v>71</v>
       </c>
       <c r="L10">
-        <v>196</v>
+        <v>61</v>
       </c>
       <c r="M10">
-        <v>89</v>
+        <v>50</v>
       </c>
     </row>
   </sheetData>
@@ -8181,302 +8153,6 @@
 </file>
 
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M8"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" customWidth="1"/>
-    <col min="13" max="13" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="M1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2">
-        <v>4</v>
-      </c>
-      <c r="D2">
-        <v>1</v>
-      </c>
-      <c r="E2">
-        <v>4</v>
-      </c>
-      <c r="F2">
-        <v>2</v>
-      </c>
-      <c r="G2">
-        <v>4</v>
-      </c>
-      <c r="H2">
-        <v>2</v>
-      </c>
-      <c r="I2">
-        <v>3</v>
-      </c>
-      <c r="J2">
-        <v>2</v>
-      </c>
-      <c r="K2">
-        <v>6</v>
-      </c>
-      <c r="L2">
-        <v>6</v>
-      </c>
-      <c r="M2">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3">
-        <v>2</v>
-      </c>
-      <c r="C3">
-        <v>4</v>
-      </c>
-      <c r="D3">
-        <v>1</v>
-      </c>
-      <c r="E3">
-        <v>4</v>
-      </c>
-      <c r="F3">
-        <v>5</v>
-      </c>
-      <c r="G3">
-        <v>4</v>
-      </c>
-      <c r="H3">
-        <v>7</v>
-      </c>
-      <c r="I3">
-        <v>2</v>
-      </c>
-      <c r="J3">
-        <v>11</v>
-      </c>
-      <c r="K3">
-        <v>5</v>
-      </c>
-      <c r="L3">
-        <v>7</v>
-      </c>
-      <c r="M3">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="H4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C5">
-        <v>1</v>
-      </c>
-      <c r="H5">
-        <v>1</v>
-      </c>
-      <c r="I5">
-        <v>1</v>
-      </c>
-      <c r="K5">
-        <v>3</v>
-      </c>
-      <c r="L5">
-        <v>2</v>
-      </c>
-      <c r="M5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C6">
-        <v>14</v>
-      </c>
-      <c r="D6">
-        <v>12</v>
-      </c>
-      <c r="E6">
-        <v>10</v>
-      </c>
-      <c r="F6">
-        <v>11</v>
-      </c>
-      <c r="G6">
-        <v>11</v>
-      </c>
-      <c r="H6">
-        <v>17</v>
-      </c>
-      <c r="I6">
-        <v>20</v>
-      </c>
-      <c r="J6">
-        <v>3</v>
-      </c>
-      <c r="K6">
-        <v>10</v>
-      </c>
-      <c r="L6">
-        <v>5</v>
-      </c>
-      <c r="M6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
-      <c r="A7" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B7">
-        <v>58</v>
-      </c>
-      <c r="C7">
-        <v>53</v>
-      </c>
-      <c r="D7">
-        <v>43</v>
-      </c>
-      <c r="E7">
-        <v>56</v>
-      </c>
-      <c r="F7">
-        <v>53</v>
-      </c>
-      <c r="G7">
-        <v>33</v>
-      </c>
-      <c r="H7">
-        <v>23</v>
-      </c>
-      <c r="I7">
-        <v>26</v>
-      </c>
-      <c r="J7">
-        <v>27</v>
-      </c>
-      <c r="K7">
-        <v>17</v>
-      </c>
-      <c r="L7">
-        <v>19</v>
-      </c>
-      <c r="M7">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13">
-      <c r="A8" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B8">
-        <v>60</v>
-      </c>
-      <c r="C8">
-        <v>76</v>
-      </c>
-      <c r="D8">
-        <v>57</v>
-      </c>
-      <c r="E8">
-        <v>74</v>
-      </c>
-      <c r="F8">
-        <v>71</v>
-      </c>
-      <c r="G8">
-        <v>52</v>
-      </c>
-      <c r="H8">
-        <v>51</v>
-      </c>
-      <c r="I8">
-        <v>52</v>
-      </c>
-      <c r="J8">
-        <v>43</v>
-      </c>
-      <c r="K8">
-        <v>41</v>
-      </c>
-      <c r="L8">
-        <v>39</v>
-      </c>
-      <c r="M8">
-        <v>25</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -8747,7 +8423,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:D4"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -8810,7 +8486,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M9"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -9077,6 +8753,330 @@
       </c>
       <c r="M9">
         <v>7</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:M10"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+    <col min="13" max="13" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="M1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>5</v>
+      </c>
+      <c r="C2">
+        <v>3</v>
+      </c>
+      <c r="D2">
+        <v>7</v>
+      </c>
+      <c r="E2">
+        <v>5</v>
+      </c>
+      <c r="F2">
+        <v>5</v>
+      </c>
+      <c r="G2">
+        <v>4</v>
+      </c>
+      <c r="H2">
+        <v>6</v>
+      </c>
+      <c r="I2">
+        <v>4</v>
+      </c>
+      <c r="J2">
+        <v>7</v>
+      </c>
+      <c r="K2">
+        <v>7</v>
+      </c>
+      <c r="L2">
+        <v>5</v>
+      </c>
+      <c r="M2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>3</v>
+      </c>
+      <c r="C3">
+        <v>2</v>
+      </c>
+      <c r="D3">
+        <v>8</v>
+      </c>
+      <c r="E3">
+        <v>9</v>
+      </c>
+      <c r="F3">
+        <v>19</v>
+      </c>
+      <c r="G3">
+        <v>9</v>
+      </c>
+      <c r="H3">
+        <v>8</v>
+      </c>
+      <c r="I3">
+        <v>13</v>
+      </c>
+      <c r="J3">
+        <v>12</v>
+      </c>
+      <c r="K3">
+        <v>17</v>
+      </c>
+      <c r="L3">
+        <v>13</v>
+      </c>
+      <c r="M3">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="I4">
+        <v>1</v>
+      </c>
+      <c r="M4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="K5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="E6">
+        <v>1</v>
+      </c>
+      <c r="F6">
+        <v>2</v>
+      </c>
+      <c r="J6">
+        <v>2</v>
+      </c>
+      <c r="M6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E7">
+        <v>1</v>
+      </c>
+      <c r="I7">
+        <v>1</v>
+      </c>
+      <c r="K7">
+        <v>1</v>
+      </c>
+      <c r="L7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13">
+      <c r="A8" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8">
+        <v>24</v>
+      </c>
+      <c r="C8">
+        <v>37</v>
+      </c>
+      <c r="D8">
+        <v>21</v>
+      </c>
+      <c r="E8">
+        <v>22</v>
+      </c>
+      <c r="F8">
+        <v>27</v>
+      </c>
+      <c r="G8">
+        <v>15</v>
+      </c>
+      <c r="H8">
+        <v>25</v>
+      </c>
+      <c r="I8">
+        <v>21</v>
+      </c>
+      <c r="J8">
+        <v>26</v>
+      </c>
+      <c r="K8">
+        <v>49</v>
+      </c>
+      <c r="L8">
+        <v>44</v>
+      </c>
+      <c r="M8">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13">
+      <c r="A9" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B9">
+        <v>45</v>
+      </c>
+      <c r="C9">
+        <v>64</v>
+      </c>
+      <c r="D9">
+        <v>46</v>
+      </c>
+      <c r="E9">
+        <v>50</v>
+      </c>
+      <c r="F9">
+        <v>38</v>
+      </c>
+      <c r="G9">
+        <v>19</v>
+      </c>
+      <c r="H9">
+        <v>27</v>
+      </c>
+      <c r="I9">
+        <v>37</v>
+      </c>
+      <c r="J9">
+        <v>20</v>
+      </c>
+      <c r="K9">
+        <v>35</v>
+      </c>
+      <c r="L9">
+        <v>35</v>
+      </c>
+      <c r="M9">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13">
+      <c r="A10" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B10">
+        <v>77</v>
+      </c>
+      <c r="C10">
+        <v>106</v>
+      </c>
+      <c r="D10">
+        <v>82</v>
+      </c>
+      <c r="E10">
+        <v>88</v>
+      </c>
+      <c r="F10">
+        <v>91</v>
+      </c>
+      <c r="G10">
+        <v>47</v>
+      </c>
+      <c r="H10">
+        <v>66</v>
+      </c>
+      <c r="I10">
+        <v>77</v>
+      </c>
+      <c r="J10">
+        <v>67</v>
+      </c>
+      <c r="K10">
+        <v>110</v>
+      </c>
+      <c r="L10">
+        <v>98</v>
+      </c>
+      <c r="M10">
+        <v>36</v>
       </c>
     </row>
   </sheetData>
@@ -14580,257 +14580,6 @@
 
 <file path=xl/worksheets/sheet44.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M8"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" customWidth="1"/>
-    <col min="13" max="13" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="M1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2">
-        <v>1</v>
-      </c>
-      <c r="D2">
-        <v>2</v>
-      </c>
-      <c r="F2">
-        <v>2</v>
-      </c>
-      <c r="I2">
-        <v>3</v>
-      </c>
-      <c r="J2">
-        <v>2</v>
-      </c>
-      <c r="K2">
-        <v>1</v>
-      </c>
-      <c r="L2">
-        <v>5</v>
-      </c>
-      <c r="M2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C3">
-        <v>1</v>
-      </c>
-      <c r="E3">
-        <v>1</v>
-      </c>
-      <c r="H3">
-        <v>2</v>
-      </c>
-      <c r="I3">
-        <v>1</v>
-      </c>
-      <c r="J3">
-        <v>1</v>
-      </c>
-      <c r="K3">
-        <v>2</v>
-      </c>
-      <c r="L3">
-        <v>2</v>
-      </c>
-      <c r="M3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C4">
-        <v>1</v>
-      </c>
-      <c r="I4">
-        <v>1</v>
-      </c>
-      <c r="K4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="L5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B6">
-        <v>1</v>
-      </c>
-      <c r="F6">
-        <v>4</v>
-      </c>
-      <c r="H6">
-        <v>1</v>
-      </c>
-      <c r="I6">
-        <v>2</v>
-      </c>
-      <c r="K6">
-        <v>1</v>
-      </c>
-      <c r="M6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
-      <c r="A7" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B7">
-        <v>10</v>
-      </c>
-      <c r="C7">
-        <v>20</v>
-      </c>
-      <c r="D7">
-        <v>25</v>
-      </c>
-      <c r="E7">
-        <v>30</v>
-      </c>
-      <c r="F7">
-        <v>41</v>
-      </c>
-      <c r="G7">
-        <v>10</v>
-      </c>
-      <c r="H7">
-        <v>5</v>
-      </c>
-      <c r="I7">
-        <v>5</v>
-      </c>
-      <c r="J7">
-        <v>15</v>
-      </c>
-      <c r="K7">
-        <v>17</v>
-      </c>
-      <c r="L7">
-        <v>12</v>
-      </c>
-      <c r="M7">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13">
-      <c r="A8" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B8">
-        <v>12</v>
-      </c>
-      <c r="C8">
-        <v>22</v>
-      </c>
-      <c r="D8">
-        <v>27</v>
-      </c>
-      <c r="E8">
-        <v>31</v>
-      </c>
-      <c r="F8">
-        <v>47</v>
-      </c>
-      <c r="G8">
-        <v>10</v>
-      </c>
-      <c r="H8">
-        <v>8</v>
-      </c>
-      <c r="I8">
-        <v>12</v>
-      </c>
-      <c r="J8">
-        <v>18</v>
-      </c>
-      <c r="K8">
-        <v>22</v>
-      </c>
-      <c r="L8">
-        <v>21</v>
-      </c>
-      <c r="M8">
-        <v>16</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet45.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -15108,7 +14857,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet46.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet45.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -15324,6 +15073,257 @@
       </c>
       <c r="M6">
         <v>3</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet46.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:M8"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+    <col min="13" max="13" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="M1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>2</v>
+      </c>
+      <c r="F2">
+        <v>2</v>
+      </c>
+      <c r="I2">
+        <v>3</v>
+      </c>
+      <c r="J2">
+        <v>2</v>
+      </c>
+      <c r="K2">
+        <v>1</v>
+      </c>
+      <c r="L2">
+        <v>5</v>
+      </c>
+      <c r="M2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
+      <c r="E3">
+        <v>1</v>
+      </c>
+      <c r="H3">
+        <v>2</v>
+      </c>
+      <c r="I3">
+        <v>1</v>
+      </c>
+      <c r="J3">
+        <v>1</v>
+      </c>
+      <c r="K3">
+        <v>2</v>
+      </c>
+      <c r="L3">
+        <v>2</v>
+      </c>
+      <c r="M3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
+      <c r="I4">
+        <v>1</v>
+      </c>
+      <c r="K4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="L5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6">
+        <v>1</v>
+      </c>
+      <c r="F6">
+        <v>4</v>
+      </c>
+      <c r="H6">
+        <v>1</v>
+      </c>
+      <c r="I6">
+        <v>2</v>
+      </c>
+      <c r="K6">
+        <v>1</v>
+      </c>
+      <c r="M6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7">
+        <v>10</v>
+      </c>
+      <c r="C7">
+        <v>20</v>
+      </c>
+      <c r="D7">
+        <v>25</v>
+      </c>
+      <c r="E7">
+        <v>30</v>
+      </c>
+      <c r="F7">
+        <v>41</v>
+      </c>
+      <c r="G7">
+        <v>10</v>
+      </c>
+      <c r="H7">
+        <v>5</v>
+      </c>
+      <c r="I7">
+        <v>5</v>
+      </c>
+      <c r="J7">
+        <v>15</v>
+      </c>
+      <c r="K7">
+        <v>17</v>
+      </c>
+      <c r="L7">
+        <v>12</v>
+      </c>
+      <c r="M7">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13">
+      <c r="A8" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B8">
+        <v>12</v>
+      </c>
+      <c r="C8">
+        <v>22</v>
+      </c>
+      <c r="D8">
+        <v>27</v>
+      </c>
+      <c r="E8">
+        <v>31</v>
+      </c>
+      <c r="F8">
+        <v>47</v>
+      </c>
+      <c r="G8">
+        <v>10</v>
+      </c>
+      <c r="H8">
+        <v>8</v>
+      </c>
+      <c r="I8">
+        <v>12</v>
+      </c>
+      <c r="J8">
+        <v>18</v>
+      </c>
+      <c r="K8">
+        <v>22</v>
+      </c>
+      <c r="L8">
+        <v>21</v>
+      </c>
+      <c r="M8">
+        <v>16</v>
       </c>
     </row>
   </sheetData>

--- a/output/cta-index-crime-full-year.xlsx
+++ b/output/cta-index-crime-full-year.xlsx
@@ -19,18 +19,18 @@
     <sheet name="Rogers Park" sheetId="10" r:id="rId10"/>
     <sheet name="Douglas" sheetId="11" r:id="rId11"/>
     <sheet name="Jefferson Park" sheetId="12" r:id="rId12"/>
-    <sheet name="Chatham" sheetId="13" r:id="rId13"/>
-    <sheet name="Albany Park" sheetId="14" r:id="rId14"/>
-    <sheet name="Grand Boulevard" sheetId="15" r:id="rId15"/>
-    <sheet name="Belmont Cragin" sheetId="16" r:id="rId16"/>
-    <sheet name="West Ridge" sheetId="17" r:id="rId17"/>
-    <sheet name="Loop" sheetId="18" r:id="rId18"/>
-    <sheet name="Lake View" sheetId="19" r:id="rId19"/>
-    <sheet name="Austin" sheetId="20" r:id="rId20"/>
-    <sheet name="South Shore" sheetId="21" r:id="rId21"/>
-    <sheet name="Mount Greenwood" sheetId="22" r:id="rId22"/>
-    <sheet name="Gage Park" sheetId="23" r:id="rId23"/>
-    <sheet name="Grand Crossing" sheetId="24" r:id="rId24"/>
+    <sheet name="Grand Crossing" sheetId="13" r:id="rId13"/>
+    <sheet name="Chatham" sheetId="14" r:id="rId14"/>
+    <sheet name="Austin" sheetId="15" r:id="rId15"/>
+    <sheet name="Albany Park" sheetId="16" r:id="rId16"/>
+    <sheet name="Grand Boulevard" sheetId="17" r:id="rId17"/>
+    <sheet name="Belmont Cragin" sheetId="18" r:id="rId18"/>
+    <sheet name="West Ridge" sheetId="19" r:id="rId19"/>
+    <sheet name="Loop" sheetId="20" r:id="rId20"/>
+    <sheet name="Lake View" sheetId="21" r:id="rId21"/>
+    <sheet name="South Shore" sheetId="22" r:id="rId22"/>
+    <sheet name="Mount Greenwood" sheetId="23" r:id="rId23"/>
+    <sheet name="Gage Park" sheetId="24" r:id="rId24"/>
     <sheet name="West Loop" sheetId="25" r:id="rId25"/>
     <sheet name="Rush &amp; Division" sheetId="26" r:id="rId26"/>
     <sheet name="North Lawndale" sheetId="27" r:id="rId27"/>
@@ -50,9 +50,9 @@
     <sheet name="Roseland" sheetId="41" r:id="rId41"/>
     <sheet name="Woodlawn" sheetId="42" r:id="rId42"/>
     <sheet name="Fuller Park" sheetId="43" r:id="rId43"/>
-    <sheet name="Little Italy, UIC" sheetId="44" r:id="rId44"/>
-    <sheet name="Hyde Park" sheetId="45" r:id="rId45"/>
-    <sheet name="O'Hare" sheetId="46" r:id="rId46"/>
+    <sheet name="O'Hare" sheetId="44" r:id="rId44"/>
+    <sheet name="Little Italy, UIC" sheetId="45" r:id="rId45"/>
+    <sheet name="Hyde Park" sheetId="46" r:id="rId46"/>
     <sheet name="Bucktown" sheetId="47" r:id="rId47"/>
     <sheet name="Calumet Heights" sheetId="48" r:id="rId48"/>
     <sheet name="Edgewater" sheetId="49" r:id="rId49"/>
@@ -2146,38 +2146,41 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
+      <c r="B2">
+        <v>5</v>
+      </c>
       <c r="C2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D2">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H2">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J2">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="L2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M2">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -2185,56 +2188,56 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D3">
+        <v>8</v>
+      </c>
+      <c r="E3">
+        <v>9</v>
+      </c>
+      <c r="F3">
+        <v>19</v>
+      </c>
+      <c r="G3">
+        <v>9</v>
+      </c>
+      <c r="H3">
+        <v>8</v>
+      </c>
+      <c r="I3">
+        <v>13</v>
+      </c>
+      <c r="J3">
+        <v>12</v>
+      </c>
+      <c r="K3">
+        <v>17</v>
+      </c>
+      <c r="L3">
+        <v>13</v>
+      </c>
+      <c r="M3">
         <v>7</v>
-      </c>
-      <c r="E3">
-        <v>3</v>
-      </c>
-      <c r="F3">
-        <v>4</v>
-      </c>
-      <c r="G3">
-        <v>8</v>
-      </c>
-      <c r="H3">
-        <v>4</v>
-      </c>
-      <c r="I3">
-        <v>6</v>
-      </c>
-      <c r="J3">
-        <v>4</v>
-      </c>
-      <c r="K3">
-        <v>10</v>
-      </c>
-      <c r="L3">
-        <v>5</v>
-      </c>
-      <c r="M3">
-        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="H4">
+      <c r="I4">
+        <v>1</v>
+      </c>
+      <c r="M4">
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K5">
         <v>1</v>
@@ -2242,30 +2245,36 @@
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="G6">
-        <v>1</v>
-      </c>
-      <c r="H6">
-        <v>1</v>
-      </c>
-      <c r="I6">
+        <v>5</v>
+      </c>
+      <c r="E6">
+        <v>1</v>
+      </c>
+      <c r="F6">
+        <v>2</v>
+      </c>
+      <c r="J6">
+        <v>2</v>
+      </c>
+      <c r="M6">
         <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D7">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E7">
         <v>1</v>
       </c>
-      <c r="J7">
-        <v>2</v>
+      <c r="I7">
+        <v>1</v>
+      </c>
+      <c r="K7">
+        <v>1</v>
+      </c>
+      <c r="L7">
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -2273,40 +2282,40 @@
         <v>8</v>
       </c>
       <c r="B8">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="C8">
-        <v>9</v>
+        <v>37</v>
       </c>
       <c r="D8">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E8">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="F8">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="G8">
         <v>15</v>
       </c>
       <c r="H8">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="I8">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="J8">
+        <v>26</v>
+      </c>
+      <c r="K8">
+        <v>49</v>
+      </c>
+      <c r="L8">
+        <v>44</v>
+      </c>
+      <c r="M8">
         <v>12</v>
-      </c>
-      <c r="K8">
-        <v>18</v>
-      </c>
-      <c r="L8">
-        <v>19</v>
-      </c>
-      <c r="M8">
-        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -2314,40 +2323,40 @@
         <v>9</v>
       </c>
       <c r="B9">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C9">
+        <v>64</v>
+      </c>
+      <c r="D9">
         <v>46</v>
       </c>
-      <c r="D9">
-        <v>32</v>
-      </c>
       <c r="E9">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="F9">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="G9">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="H9">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="I9">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="J9">
         <v>20</v>
       </c>
       <c r="K9">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="L9">
-        <v>13</v>
+        <v>35</v>
       </c>
       <c r="M9">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -2355,40 +2364,40 @@
         <v>10</v>
       </c>
       <c r="B10">
-        <v>51</v>
+        <v>77</v>
       </c>
       <c r="C10">
-        <v>57</v>
+        <v>106</v>
       </c>
       <c r="D10">
-        <v>62</v>
+        <v>82</v>
       </c>
       <c r="E10">
-        <v>48</v>
+        <v>88</v>
       </c>
       <c r="F10">
-        <v>60</v>
+        <v>91</v>
       </c>
       <c r="G10">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="H10">
-        <v>31</v>
+        <v>66</v>
       </c>
       <c r="I10">
-        <v>44</v>
+        <v>77</v>
       </c>
       <c r="J10">
-        <v>43</v>
+        <v>67</v>
       </c>
       <c r="K10">
-        <v>57</v>
+        <v>110</v>
       </c>
       <c r="L10">
-        <v>40</v>
+        <v>98</v>
       </c>
       <c r="M10">
-        <v>17</v>
+        <v>36</v>
       </c>
     </row>
   </sheetData>
@@ -2398,7 +2407,7 @@
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M7"/>
+  <dimension ref="A1:M10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="23.7109375" customWidth="1"/>
@@ -2461,29 +2470,38 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
       <c r="D2">
+        <v>5</v>
+      </c>
+      <c r="E2">
         <v>1</v>
       </c>
       <c r="F2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G2">
         <v>1</v>
       </c>
+      <c r="H2">
+        <v>3</v>
+      </c>
       <c r="I2">
         <v>2</v>
       </c>
       <c r="J2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K2">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="L2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M2">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -2491,153 +2509,210 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C3">
         <v>1</v>
       </c>
+      <c r="D3">
+        <v>7</v>
+      </c>
+      <c r="E3">
+        <v>3</v>
+      </c>
+      <c r="F3">
+        <v>4</v>
+      </c>
       <c r="G3">
-        <v>2</v>
+        <v>8</v>
+      </c>
+      <c r="H3">
+        <v>4</v>
       </c>
       <c r="I3">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="J3">
-        <v>1</v>
+        <v>4</v>
+      </c>
+      <c r="K3">
+        <v>10</v>
       </c>
       <c r="L3">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="E4">
-        <v>2</v>
-      </c>
-      <c r="J4">
-        <v>1</v>
-      </c>
-      <c r="K4">
+        <v>3</v>
+      </c>
+      <c r="H4">
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B5">
         <v>1</v>
       </c>
-      <c r="C5">
-        <v>1</v>
-      </c>
-      <c r="D5">
-        <v>2</v>
-      </c>
-      <c r="E5">
-        <v>2</v>
-      </c>
-      <c r="G5">
-        <v>1</v>
-      </c>
-      <c r="I5">
-        <v>1</v>
-      </c>
-      <c r="J5">
-        <v>3</v>
-      </c>
       <c r="K5">
-        <v>4</v>
-      </c>
-      <c r="M5">
         <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B6">
-        <v>8</v>
-      </c>
-      <c r="C6">
-        <v>13</v>
-      </c>
-      <c r="D6">
-        <v>10</v>
-      </c>
-      <c r="E6">
-        <v>9</v>
-      </c>
-      <c r="F6">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G6">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="H6">
         <v>1</v>
       </c>
       <c r="I6">
-        <v>4</v>
-      </c>
-      <c r="J6">
-        <v>5</v>
-      </c>
-      <c r="K6">
-        <v>8</v>
-      </c>
-      <c r="L6">
-        <v>3</v>
-      </c>
-      <c r="M6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D7">
+        <v>1</v>
+      </c>
+      <c r="E7">
+        <v>1</v>
+      </c>
+      <c r="J7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13">
+      <c r="A8" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8">
+        <v>5</v>
+      </c>
+      <c r="C8">
+        <v>9</v>
+      </c>
+      <c r="D8">
+        <v>17</v>
+      </c>
+      <c r="E8">
+        <v>13</v>
+      </c>
+      <c r="F8">
+        <v>19</v>
+      </c>
+      <c r="G8">
+        <v>15</v>
+      </c>
+      <c r="H8">
+        <v>5</v>
+      </c>
+      <c r="I8">
+        <v>15</v>
+      </c>
+      <c r="J8">
+        <v>12</v>
+      </c>
+      <c r="K8">
+        <v>18</v>
+      </c>
+      <c r="L8">
+        <v>19</v>
+      </c>
+      <c r="M8">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13">
+      <c r="A9" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B9">
+        <v>43</v>
+      </c>
+      <c r="C9">
+        <v>46</v>
+      </c>
+      <c r="D9">
+        <v>32</v>
+      </c>
+      <c r="E9">
+        <v>30</v>
+      </c>
+      <c r="F9">
+        <v>34</v>
+      </c>
+      <c r="G9">
+        <v>15</v>
+      </c>
+      <c r="H9">
+        <v>17</v>
+      </c>
+      <c r="I9">
+        <v>20</v>
+      </c>
+      <c r="J9">
+        <v>20</v>
+      </c>
+      <c r="K9">
+        <v>20</v>
+      </c>
+      <c r="L9">
+        <v>13</v>
+      </c>
+      <c r="M9">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13">
+      <c r="A10" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B7">
-        <v>10</v>
-      </c>
-      <c r="C7">
-        <v>15</v>
-      </c>
-      <c r="D7">
-        <v>13</v>
-      </c>
-      <c r="E7">
-        <v>13</v>
-      </c>
-      <c r="F7">
-        <v>10</v>
-      </c>
-      <c r="G7">
-        <v>12</v>
-      </c>
-      <c r="H7">
-        <v>1</v>
-      </c>
-      <c r="I7">
-        <v>8</v>
-      </c>
-      <c r="J7">
-        <v>14</v>
-      </c>
-      <c r="K7">
-        <v>15</v>
-      </c>
-      <c r="L7">
-        <v>6</v>
-      </c>
-      <c r="M7">
-        <v>5</v>
+      <c r="B10">
+        <v>51</v>
+      </c>
+      <c r="C10">
+        <v>57</v>
+      </c>
+      <c r="D10">
+        <v>62</v>
+      </c>
+      <c r="E10">
+        <v>48</v>
+      </c>
+      <c r="F10">
+        <v>60</v>
+      </c>
+      <c r="G10">
+        <v>40</v>
+      </c>
+      <c r="H10">
+        <v>31</v>
+      </c>
+      <c r="I10">
+        <v>44</v>
+      </c>
+      <c r="J10">
+        <v>43</v>
+      </c>
+      <c r="K10">
+        <v>57</v>
+      </c>
+      <c r="L10">
+        <v>40</v>
+      </c>
+      <c r="M10">
+        <v>17</v>
       </c>
     </row>
   </sheetData>
@@ -2647,10 +2722,10 @@
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M7"/>
+  <dimension ref="A1:M10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="18.7109375" customWidth="1"/>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
     <col min="2" max="2" width="4.7109375" customWidth="1"/>
     <col min="3" max="3" width="4.7109375" customWidth="1"/>
     <col min="4" max="4" width="4.7109375" customWidth="1"/>
@@ -2710,29 +2785,41 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
+      <c r="B2">
+        <v>4</v>
+      </c>
       <c r="C2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E2">
-        <v>1</v>
+        <v>5</v>
+      </c>
+      <c r="F2">
+        <v>9</v>
+      </c>
+      <c r="G2">
+        <v>3</v>
       </c>
       <c r="H2">
-        <v>2</v>
+        <v>5</v>
+      </c>
+      <c r="I2">
+        <v>4</v>
       </c>
       <c r="J2">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="K2">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="L2">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="M2">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -2740,162 +2827,210 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C3">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D3">
-        <v>1</v>
+        <v>6</v>
+      </c>
+      <c r="E3">
+        <v>7</v>
       </c>
       <c r="F3">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G3">
-        <v>1</v>
+        <v>7</v>
+      </c>
+      <c r="H3">
+        <v>8</v>
       </c>
       <c r="I3">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J3">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="K3">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="L3">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="M3">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H4">
+        <v>3</v>
+      </c>
+      <c r="I4">
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B5">
-        <v>7</v>
-      </c>
-      <c r="C5">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="D5">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E5">
-        <v>5</v>
-      </c>
-      <c r="F5">
-        <v>5</v>
-      </c>
-      <c r="G5">
-        <v>6</v>
-      </c>
-      <c r="H5">
-        <v>2</v>
-      </c>
-      <c r="I5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J5">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K5">
-        <v>6</v>
-      </c>
-      <c r="L5">
-        <v>6</v>
+        <v>2</v>
+      </c>
+      <c r="M5">
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B6">
-        <v>15</v>
-      </c>
-      <c r="C6">
-        <v>16</v>
-      </c>
-      <c r="D6">
-        <v>15</v>
-      </c>
-      <c r="E6">
-        <v>16</v>
-      </c>
-      <c r="F6">
-        <v>11</v>
-      </c>
-      <c r="G6">
-        <v>9</v>
-      </c>
-      <c r="H6">
-        <v>5</v>
-      </c>
-      <c r="I6">
-        <v>5</v>
-      </c>
-      <c r="J6">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="K6">
-        <v>6</v>
-      </c>
-      <c r="L6">
-        <v>4</v>
-      </c>
-      <c r="M6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="L7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13">
+      <c r="A8" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8">
+        <v>23</v>
+      </c>
+      <c r="C8">
+        <v>31</v>
+      </c>
+      <c r="D8">
+        <v>22</v>
+      </c>
+      <c r="E8">
+        <v>44</v>
+      </c>
+      <c r="F8">
+        <v>38</v>
+      </c>
+      <c r="G8">
+        <v>24</v>
+      </c>
+      <c r="H8">
+        <v>50</v>
+      </c>
+      <c r="I8">
+        <v>34</v>
+      </c>
+      <c r="J8">
+        <v>26</v>
+      </c>
+      <c r="K8">
+        <v>24</v>
+      </c>
+      <c r="L8">
+        <v>14</v>
+      </c>
+      <c r="M8">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13">
+      <c r="A9" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B9">
+        <v>46</v>
+      </c>
+      <c r="C9">
+        <v>59</v>
+      </c>
+      <c r="D9">
+        <v>33</v>
+      </c>
+      <c r="E9">
+        <v>73</v>
+      </c>
+      <c r="F9">
+        <v>114</v>
+      </c>
+      <c r="G9">
+        <v>58</v>
+      </c>
+      <c r="H9">
+        <v>41</v>
+      </c>
+      <c r="I9">
+        <v>44</v>
+      </c>
+      <c r="J9">
+        <v>20</v>
+      </c>
+      <c r="K9">
+        <v>25</v>
+      </c>
+      <c r="L9">
+        <v>27</v>
+      </c>
+      <c r="M9">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13">
+      <c r="A10" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B7">
-        <v>24</v>
-      </c>
-      <c r="C7">
-        <v>29</v>
-      </c>
-      <c r="D7">
-        <v>25</v>
-      </c>
-      <c r="E7">
-        <v>22</v>
-      </c>
-      <c r="F7">
-        <v>19</v>
-      </c>
-      <c r="G7">
-        <v>16</v>
-      </c>
-      <c r="H7">
-        <v>10</v>
-      </c>
-      <c r="I7">
-        <v>11</v>
-      </c>
-      <c r="J7">
-        <v>20</v>
-      </c>
-      <c r="K7">
-        <v>15</v>
-      </c>
-      <c r="L7">
-        <v>16</v>
-      </c>
-      <c r="M7">
-        <v>6</v>
+      <c r="B10">
+        <v>78</v>
+      </c>
+      <c r="C10">
+        <v>99</v>
+      </c>
+      <c r="D10">
+        <v>65</v>
+      </c>
+      <c r="E10">
+        <v>130</v>
+      </c>
+      <c r="F10">
+        <v>167</v>
+      </c>
+      <c r="G10">
+        <v>92</v>
+      </c>
+      <c r="H10">
+        <v>104</v>
+      </c>
+      <c r="I10">
+        <v>89</v>
+      </c>
+      <c r="J10">
+        <v>67</v>
+      </c>
+      <c r="K10">
+        <v>71</v>
+      </c>
+      <c r="L10">
+        <v>61</v>
+      </c>
+      <c r="M10">
+        <v>50</v>
       </c>
     </row>
   </sheetData>
@@ -2971,7 +3106,25 @@
       <c r="D2">
         <v>1</v>
       </c>
+      <c r="F2">
+        <v>1</v>
+      </c>
+      <c r="G2">
+        <v>1</v>
+      </c>
+      <c r="I2">
+        <v>2</v>
+      </c>
       <c r="J2">
+        <v>4</v>
+      </c>
+      <c r="K2">
+        <v>2</v>
+      </c>
+      <c r="L2">
+        <v>2</v>
+      </c>
+      <c r="M2">
         <v>1</v>
       </c>
     </row>
@@ -2979,16 +3132,25 @@
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="E3">
-        <v>2</v>
+      <c r="B3">
+        <v>1</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
       </c>
       <c r="G3">
+        <v>2</v>
+      </c>
+      <c r="I3">
         <v>1</v>
       </c>
       <c r="J3">
         <v>1</v>
       </c>
       <c r="L3">
+        <v>1</v>
+      </c>
+      <c r="M3">
         <v>1</v>
       </c>
     </row>
@@ -2996,7 +3158,13 @@
       <c r="A4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C4">
+      <c r="E4">
+        <v>2</v>
+      </c>
+      <c r="J4">
+        <v>1</v>
+      </c>
+      <c r="K4">
         <v>1</v>
       </c>
     </row>
@@ -3005,22 +3173,28 @@
         <v>8</v>
       </c>
       <c r="B5">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C5">
-        <v>6</v>
+        <v>1</v>
+      </c>
+      <c r="D5">
+        <v>2</v>
       </c>
       <c r="E5">
-        <v>1</v>
-      </c>
-      <c r="H5">
-        <v>2</v>
+        <v>2</v>
+      </c>
+      <c r="G5">
+        <v>1</v>
+      </c>
+      <c r="I5">
+        <v>1</v>
       </c>
       <c r="J5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M5">
         <v>1</v>
@@ -3031,40 +3205,40 @@
         <v>9</v>
       </c>
       <c r="B6">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C6">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="D6">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E6">
+        <v>9</v>
+      </c>
+      <c r="F6">
+        <v>9</v>
+      </c>
+      <c r="G6">
         <v>8</v>
       </c>
-      <c r="F6">
-        <v>7</v>
-      </c>
-      <c r="G6">
-        <v>2</v>
-      </c>
       <c r="H6">
         <v>1</v>
       </c>
       <c r="I6">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J6">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K6">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="L6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -3072,40 +3246,40 @@
         <v>10</v>
       </c>
       <c r="B7">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C7">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D7">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="E7">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F7">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G7">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="H7">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I7">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="J7">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="K7">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="L7">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="M7">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -3114,6 +3288,474 @@
 </file>
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:M7"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="18.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+    <col min="13" max="13" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="M1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
+      <c r="H2">
+        <v>2</v>
+      </c>
+      <c r="J2">
+        <v>1</v>
+      </c>
+      <c r="K2">
+        <v>2</v>
+      </c>
+      <c r="L2">
+        <v>2</v>
+      </c>
+      <c r="M2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>2</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
+      <c r="F3">
+        <v>3</v>
+      </c>
+      <c r="G3">
+        <v>1</v>
+      </c>
+      <c r="I3">
+        <v>4</v>
+      </c>
+      <c r="J3">
+        <v>2</v>
+      </c>
+      <c r="K3">
+        <v>1</v>
+      </c>
+      <c r="L3">
+        <v>4</v>
+      </c>
+      <c r="M3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5">
+        <v>7</v>
+      </c>
+      <c r="C5">
+        <v>11</v>
+      </c>
+      <c r="D5">
+        <v>8</v>
+      </c>
+      <c r="E5">
+        <v>5</v>
+      </c>
+      <c r="F5">
+        <v>5</v>
+      </c>
+      <c r="G5">
+        <v>6</v>
+      </c>
+      <c r="H5">
+        <v>2</v>
+      </c>
+      <c r="I5">
+        <v>2</v>
+      </c>
+      <c r="J5">
+        <v>5</v>
+      </c>
+      <c r="K5">
+        <v>6</v>
+      </c>
+      <c r="L5">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6">
+        <v>15</v>
+      </c>
+      <c r="C6">
+        <v>16</v>
+      </c>
+      <c r="D6">
+        <v>15</v>
+      </c>
+      <c r="E6">
+        <v>16</v>
+      </c>
+      <c r="F6">
+        <v>11</v>
+      </c>
+      <c r="G6">
+        <v>9</v>
+      </c>
+      <c r="H6">
+        <v>5</v>
+      </c>
+      <c r="I6">
+        <v>5</v>
+      </c>
+      <c r="J6">
+        <v>12</v>
+      </c>
+      <c r="K6">
+        <v>6</v>
+      </c>
+      <c r="L6">
+        <v>4</v>
+      </c>
+      <c r="M6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7">
+        <v>24</v>
+      </c>
+      <c r="C7">
+        <v>29</v>
+      </c>
+      <c r="D7">
+        <v>25</v>
+      </c>
+      <c r="E7">
+        <v>22</v>
+      </c>
+      <c r="F7">
+        <v>19</v>
+      </c>
+      <c r="G7">
+        <v>16</v>
+      </c>
+      <c r="H7">
+        <v>10</v>
+      </c>
+      <c r="I7">
+        <v>11</v>
+      </c>
+      <c r="J7">
+        <v>20</v>
+      </c>
+      <c r="K7">
+        <v>15</v>
+      </c>
+      <c r="L7">
+        <v>16</v>
+      </c>
+      <c r="M7">
+        <v>6</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:M7"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+    <col min="13" max="13" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="M1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="J2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E3">
+        <v>2</v>
+      </c>
+      <c r="G3">
+        <v>1</v>
+      </c>
+      <c r="J3">
+        <v>1</v>
+      </c>
+      <c r="L3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5">
+        <v>5</v>
+      </c>
+      <c r="C5">
+        <v>6</v>
+      </c>
+      <c r="E5">
+        <v>1</v>
+      </c>
+      <c r="H5">
+        <v>2</v>
+      </c>
+      <c r="J5">
+        <v>4</v>
+      </c>
+      <c r="K5">
+        <v>2</v>
+      </c>
+      <c r="M5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6">
+        <v>6</v>
+      </c>
+      <c r="C6">
+        <v>2</v>
+      </c>
+      <c r="D6">
+        <v>6</v>
+      </c>
+      <c r="E6">
+        <v>8</v>
+      </c>
+      <c r="F6">
+        <v>7</v>
+      </c>
+      <c r="G6">
+        <v>2</v>
+      </c>
+      <c r="H6">
+        <v>1</v>
+      </c>
+      <c r="I6">
+        <v>1</v>
+      </c>
+      <c r="J6">
+        <v>3</v>
+      </c>
+      <c r="K6">
+        <v>1</v>
+      </c>
+      <c r="L6">
+        <v>2</v>
+      </c>
+      <c r="M6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7">
+        <v>11</v>
+      </c>
+      <c r="C7">
+        <v>9</v>
+      </c>
+      <c r="D7">
+        <v>7</v>
+      </c>
+      <c r="E7">
+        <v>11</v>
+      </c>
+      <c r="F7">
+        <v>7</v>
+      </c>
+      <c r="G7">
+        <v>3</v>
+      </c>
+      <c r="H7">
+        <v>3</v>
+      </c>
+      <c r="I7">
+        <v>1</v>
+      </c>
+      <c r="J7">
+        <v>9</v>
+      </c>
+      <c r="K7">
+        <v>3</v>
+      </c>
+      <c r="L7">
+        <v>3</v>
+      </c>
+      <c r="M7">
+        <v>2</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:L8"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -3284,656 +3926,6 @@
       </c>
       <c r="L8">
         <v>2</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M10"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" customWidth="1"/>
-    <col min="13" max="13" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="M1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2">
-        <v>6</v>
-      </c>
-      <c r="C2">
-        <v>3</v>
-      </c>
-      <c r="D2">
-        <v>12</v>
-      </c>
-      <c r="E2">
-        <v>5</v>
-      </c>
-      <c r="F2">
-        <v>8</v>
-      </c>
-      <c r="G2">
-        <v>4</v>
-      </c>
-      <c r="H2">
-        <v>13</v>
-      </c>
-      <c r="I2">
-        <v>14</v>
-      </c>
-      <c r="J2">
-        <v>22</v>
-      </c>
-      <c r="K2">
-        <v>15</v>
-      </c>
-      <c r="L2">
-        <v>15</v>
-      </c>
-      <c r="M2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3">
-        <v>13</v>
-      </c>
-      <c r="C3">
-        <v>13</v>
-      </c>
-      <c r="D3">
-        <v>17</v>
-      </c>
-      <c r="E3">
-        <v>18</v>
-      </c>
-      <c r="F3">
-        <v>14</v>
-      </c>
-      <c r="G3">
-        <v>26</v>
-      </c>
-      <c r="H3">
-        <v>23</v>
-      </c>
-      <c r="I3">
-        <v>32</v>
-      </c>
-      <c r="J3">
-        <v>40</v>
-      </c>
-      <c r="K3">
-        <v>26</v>
-      </c>
-      <c r="L3">
-        <v>34</v>
-      </c>
-      <c r="M3">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="G4">
-        <v>1</v>
-      </c>
-      <c r="J4">
-        <v>2</v>
-      </c>
-      <c r="K4">
-        <v>1</v>
-      </c>
-      <c r="L4">
-        <v>1</v>
-      </c>
-      <c r="M4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C5">
-        <v>2</v>
-      </c>
-      <c r="D5">
-        <v>1</v>
-      </c>
-      <c r="E5">
-        <v>2</v>
-      </c>
-      <c r="F5">
-        <v>1</v>
-      </c>
-      <c r="H5">
-        <v>2</v>
-      </c>
-      <c r="I5">
-        <v>4</v>
-      </c>
-      <c r="J5">
-        <v>3</v>
-      </c>
-      <c r="K5">
-        <v>2</v>
-      </c>
-      <c r="L5">
-        <v>5</v>
-      </c>
-      <c r="M5">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="G6">
-        <v>1</v>
-      </c>
-      <c r="H6">
-        <v>2</v>
-      </c>
-      <c r="J6">
-        <v>2</v>
-      </c>
-      <c r="L6">
-        <v>2</v>
-      </c>
-      <c r="M6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
-      <c r="A7" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="K7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13">
-      <c r="A8" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B8">
-        <v>30</v>
-      </c>
-      <c r="C8">
-        <v>44</v>
-      </c>
-      <c r="D8">
-        <v>49</v>
-      </c>
-      <c r="E8">
-        <v>67</v>
-      </c>
-      <c r="F8">
-        <v>69</v>
-      </c>
-      <c r="G8">
-        <v>57</v>
-      </c>
-      <c r="H8">
-        <v>80</v>
-      </c>
-      <c r="I8">
-        <v>80</v>
-      </c>
-      <c r="J8">
-        <v>64</v>
-      </c>
-      <c r="K8">
-        <v>48</v>
-      </c>
-      <c r="L8">
-        <v>44</v>
-      </c>
-      <c r="M8">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13">
-      <c r="A9" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B9">
-        <v>233</v>
-      </c>
-      <c r="C9">
-        <v>354</v>
-      </c>
-      <c r="D9">
-        <v>538</v>
-      </c>
-      <c r="E9">
-        <v>705</v>
-      </c>
-      <c r="F9">
-        <v>568</v>
-      </c>
-      <c r="G9">
-        <v>168</v>
-      </c>
-      <c r="H9">
-        <v>116</v>
-      </c>
-      <c r="I9">
-        <v>194</v>
-      </c>
-      <c r="J9">
-        <v>122</v>
-      </c>
-      <c r="K9">
-        <v>114</v>
-      </c>
-      <c r="L9">
-        <v>95</v>
-      </c>
-      <c r="M9">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13">
-      <c r="A10" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B10">
-        <v>282</v>
-      </c>
-      <c r="C10">
-        <v>416</v>
-      </c>
-      <c r="D10">
-        <v>617</v>
-      </c>
-      <c r="E10">
-        <v>797</v>
-      </c>
-      <c r="F10">
-        <v>660</v>
-      </c>
-      <c r="G10">
-        <v>257</v>
-      </c>
-      <c r="H10">
-        <v>236</v>
-      </c>
-      <c r="I10">
-        <v>324</v>
-      </c>
-      <c r="J10">
-        <v>255</v>
-      </c>
-      <c r="K10">
-        <v>207</v>
-      </c>
-      <c r="L10">
-        <v>196</v>
-      </c>
-      <c r="M10">
-        <v>89</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M8"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" customWidth="1"/>
-    <col min="13" max="13" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="M1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2">
-        <v>4</v>
-      </c>
-      <c r="D2">
-        <v>1</v>
-      </c>
-      <c r="E2">
-        <v>4</v>
-      </c>
-      <c r="F2">
-        <v>2</v>
-      </c>
-      <c r="G2">
-        <v>4</v>
-      </c>
-      <c r="H2">
-        <v>2</v>
-      </c>
-      <c r="I2">
-        <v>3</v>
-      </c>
-      <c r="J2">
-        <v>2</v>
-      </c>
-      <c r="K2">
-        <v>6</v>
-      </c>
-      <c r="L2">
-        <v>6</v>
-      </c>
-      <c r="M2">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3">
-        <v>2</v>
-      </c>
-      <c r="C3">
-        <v>4</v>
-      </c>
-      <c r="D3">
-        <v>1</v>
-      </c>
-      <c r="E3">
-        <v>4</v>
-      </c>
-      <c r="F3">
-        <v>5</v>
-      </c>
-      <c r="G3">
-        <v>4</v>
-      </c>
-      <c r="H3">
-        <v>7</v>
-      </c>
-      <c r="I3">
-        <v>2</v>
-      </c>
-      <c r="J3">
-        <v>11</v>
-      </c>
-      <c r="K3">
-        <v>5</v>
-      </c>
-      <c r="L3">
-        <v>7</v>
-      </c>
-      <c r="M3">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="H4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C5">
-        <v>1</v>
-      </c>
-      <c r="H5">
-        <v>1</v>
-      </c>
-      <c r="I5">
-        <v>1</v>
-      </c>
-      <c r="K5">
-        <v>3</v>
-      </c>
-      <c r="L5">
-        <v>2</v>
-      </c>
-      <c r="M5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C6">
-        <v>14</v>
-      </c>
-      <c r="D6">
-        <v>12</v>
-      </c>
-      <c r="E6">
-        <v>10</v>
-      </c>
-      <c r="F6">
-        <v>11</v>
-      </c>
-      <c r="G6">
-        <v>11</v>
-      </c>
-      <c r="H6">
-        <v>17</v>
-      </c>
-      <c r="I6">
-        <v>20</v>
-      </c>
-      <c r="J6">
-        <v>3</v>
-      </c>
-      <c r="K6">
-        <v>10</v>
-      </c>
-      <c r="L6">
-        <v>5</v>
-      </c>
-      <c r="M6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
-      <c r="A7" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B7">
-        <v>58</v>
-      </c>
-      <c r="C7">
-        <v>53</v>
-      </c>
-      <c r="D7">
-        <v>43</v>
-      </c>
-      <c r="E7">
-        <v>56</v>
-      </c>
-      <c r="F7">
-        <v>53</v>
-      </c>
-      <c r="G7">
-        <v>33</v>
-      </c>
-      <c r="H7">
-        <v>23</v>
-      </c>
-      <c r="I7">
-        <v>26</v>
-      </c>
-      <c r="J7">
-        <v>27</v>
-      </c>
-      <c r="K7">
-        <v>17</v>
-      </c>
-      <c r="L7">
-        <v>19</v>
-      </c>
-      <c r="M7">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13">
-      <c r="A8" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B8">
-        <v>60</v>
-      </c>
-      <c r="C8">
-        <v>76</v>
-      </c>
-      <c r="D8">
-        <v>57</v>
-      </c>
-      <c r="E8">
-        <v>74</v>
-      </c>
-      <c r="F8">
-        <v>71</v>
-      </c>
-      <c r="G8">
-        <v>52</v>
-      </c>
-      <c r="H8">
-        <v>51</v>
-      </c>
-      <c r="I8">
-        <v>52</v>
-      </c>
-      <c r="J8">
-        <v>43</v>
-      </c>
-      <c r="K8">
-        <v>41</v>
-      </c>
-      <c r="L8">
-        <v>39</v>
-      </c>
-      <c r="M8">
-        <v>25</v>
       </c>
     </row>
   </sheetData>
@@ -7900,40 +7892,40 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D2">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="E2">
         <v>5</v>
       </c>
       <c r="F2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H2">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="I2">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="J2">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="K2">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="L2">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="M2">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -7941,47 +7933,59 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="C3">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="D3">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="E3">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="F3">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="G3">
-        <v>7</v>
+        <v>26</v>
       </c>
       <c r="H3">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="I3">
-        <v>6</v>
+        <v>32</v>
       </c>
       <c r="J3">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="K3">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="L3">
-        <v>14</v>
+        <v>34</v>
       </c>
       <c r="M3">
-        <v>10</v>
+        <v>16</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="I4">
+      <c r="G4">
+        <v>1</v>
+      </c>
+      <c r="J4">
+        <v>2</v>
+      </c>
+      <c r="K4">
+        <v>1</v>
+      </c>
+      <c r="L4">
+        <v>1</v>
+      </c>
+      <c r="M4">
         <v>1</v>
       </c>
     </row>
@@ -7989,14 +7993,23 @@
       <c r="A5" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B5">
-        <v>1</v>
+      <c r="C5">
+        <v>2</v>
       </c>
       <c r="D5">
         <v>1</v>
       </c>
       <c r="E5">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="F5">
+        <v>1</v>
+      </c>
+      <c r="H5">
+        <v>2</v>
+      </c>
+      <c r="I5">
+        <v>4</v>
       </c>
       <c r="J5">
         <v>3</v>
@@ -8004,15 +8017,30 @@
       <c r="K5">
         <v>2</v>
       </c>
+      <c r="L5">
+        <v>5</v>
+      </c>
       <c r="M5">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="K6">
+      <c r="G6">
+        <v>1</v>
+      </c>
+      <c r="H6">
+        <v>2</v>
+      </c>
+      <c r="J6">
+        <v>2</v>
+      </c>
+      <c r="L6">
+        <v>2</v>
+      </c>
+      <c r="M6">
         <v>1</v>
       </c>
     </row>
@@ -8020,7 +8048,7 @@
       <c r="A7" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="L7">
+      <c r="K7">
         <v>1</v>
       </c>
     </row>
@@ -8029,40 +8057,40 @@
         <v>8</v>
       </c>
       <c r="B8">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="C8">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="D8">
-        <v>22</v>
+        <v>49</v>
       </c>
       <c r="E8">
+        <v>67</v>
+      </c>
+      <c r="F8">
+        <v>69</v>
+      </c>
+      <c r="G8">
+        <v>57</v>
+      </c>
+      <c r="H8">
+        <v>80</v>
+      </c>
+      <c r="I8">
+        <v>80</v>
+      </c>
+      <c r="J8">
+        <v>64</v>
+      </c>
+      <c r="K8">
+        <v>48</v>
+      </c>
+      <c r="L8">
         <v>44</v>
       </c>
-      <c r="F8">
-        <v>38</v>
-      </c>
-      <c r="G8">
-        <v>24</v>
-      </c>
-      <c r="H8">
-        <v>50</v>
-      </c>
-      <c r="I8">
-        <v>34</v>
-      </c>
-      <c r="J8">
-        <v>26</v>
-      </c>
-      <c r="K8">
-        <v>24</v>
-      </c>
-      <c r="L8">
-        <v>14</v>
-      </c>
       <c r="M8">
-        <v>14</v>
+        <v>20</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -8070,40 +8098,40 @@
         <v>9</v>
       </c>
       <c r="B9">
-        <v>46</v>
+        <v>233</v>
       </c>
       <c r="C9">
-        <v>59</v>
+        <v>354</v>
       </c>
       <c r="D9">
-        <v>33</v>
+        <v>538</v>
       </c>
       <c r="E9">
-        <v>73</v>
+        <v>705</v>
       </c>
       <c r="F9">
+        <v>568</v>
+      </c>
+      <c r="G9">
+        <v>168</v>
+      </c>
+      <c r="H9">
+        <v>116</v>
+      </c>
+      <c r="I9">
+        <v>194</v>
+      </c>
+      <c r="J9">
+        <v>122</v>
+      </c>
+      <c r="K9">
         <v>114</v>
       </c>
-      <c r="G9">
-        <v>58</v>
-      </c>
-      <c r="H9">
-        <v>41</v>
-      </c>
-      <c r="I9">
-        <v>44</v>
-      </c>
-      <c r="J9">
-        <v>20</v>
-      </c>
-      <c r="K9">
-        <v>25</v>
-      </c>
       <c r="L9">
-        <v>27</v>
+        <v>95</v>
       </c>
       <c r="M9">
-        <v>16</v>
+        <v>45</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -8111,40 +8139,40 @@
         <v>10</v>
       </c>
       <c r="B10">
-        <v>78</v>
+        <v>282</v>
       </c>
       <c r="C10">
-        <v>99</v>
+        <v>416</v>
       </c>
       <c r="D10">
-        <v>65</v>
+        <v>617</v>
       </c>
       <c r="E10">
-        <v>130</v>
+        <v>797</v>
       </c>
       <c r="F10">
-        <v>167</v>
+        <v>660</v>
       </c>
       <c r="G10">
-        <v>92</v>
+        <v>257</v>
       </c>
       <c r="H10">
-        <v>104</v>
+        <v>236</v>
       </c>
       <c r="I10">
+        <v>324</v>
+      </c>
+      <c r="J10">
+        <v>255</v>
+      </c>
+      <c r="K10">
+        <v>207</v>
+      </c>
+      <c r="L10">
+        <v>196</v>
+      </c>
+      <c r="M10">
         <v>89</v>
-      </c>
-      <c r="J10">
-        <v>67</v>
-      </c>
-      <c r="K10">
-        <v>71</v>
-      </c>
-      <c r="L10">
-        <v>61</v>
-      </c>
-      <c r="M10">
-        <v>50</v>
       </c>
     </row>
   </sheetData>
@@ -8153,6 +8181,302 @@
 </file>
 
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:M8"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+    <col min="13" max="13" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="M1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>4</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="E2">
+        <v>4</v>
+      </c>
+      <c r="F2">
+        <v>2</v>
+      </c>
+      <c r="G2">
+        <v>4</v>
+      </c>
+      <c r="H2">
+        <v>2</v>
+      </c>
+      <c r="I2">
+        <v>3</v>
+      </c>
+      <c r="J2">
+        <v>2</v>
+      </c>
+      <c r="K2">
+        <v>6</v>
+      </c>
+      <c r="L2">
+        <v>6</v>
+      </c>
+      <c r="M2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>2</v>
+      </c>
+      <c r="C3">
+        <v>4</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
+      <c r="E3">
+        <v>4</v>
+      </c>
+      <c r="F3">
+        <v>5</v>
+      </c>
+      <c r="G3">
+        <v>4</v>
+      </c>
+      <c r="H3">
+        <v>7</v>
+      </c>
+      <c r="I3">
+        <v>2</v>
+      </c>
+      <c r="J3">
+        <v>11</v>
+      </c>
+      <c r="K3">
+        <v>5</v>
+      </c>
+      <c r="L3">
+        <v>7</v>
+      </c>
+      <c r="M3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="H4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C5">
+        <v>1</v>
+      </c>
+      <c r="H5">
+        <v>1</v>
+      </c>
+      <c r="I5">
+        <v>1</v>
+      </c>
+      <c r="K5">
+        <v>3</v>
+      </c>
+      <c r="L5">
+        <v>2</v>
+      </c>
+      <c r="M5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C6">
+        <v>14</v>
+      </c>
+      <c r="D6">
+        <v>12</v>
+      </c>
+      <c r="E6">
+        <v>10</v>
+      </c>
+      <c r="F6">
+        <v>11</v>
+      </c>
+      <c r="G6">
+        <v>11</v>
+      </c>
+      <c r="H6">
+        <v>17</v>
+      </c>
+      <c r="I6">
+        <v>20</v>
+      </c>
+      <c r="J6">
+        <v>3</v>
+      </c>
+      <c r="K6">
+        <v>10</v>
+      </c>
+      <c r="L6">
+        <v>5</v>
+      </c>
+      <c r="M6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7">
+        <v>58</v>
+      </c>
+      <c r="C7">
+        <v>53</v>
+      </c>
+      <c r="D7">
+        <v>43</v>
+      </c>
+      <c r="E7">
+        <v>56</v>
+      </c>
+      <c r="F7">
+        <v>53</v>
+      </c>
+      <c r="G7">
+        <v>33</v>
+      </c>
+      <c r="H7">
+        <v>23</v>
+      </c>
+      <c r="I7">
+        <v>26</v>
+      </c>
+      <c r="J7">
+        <v>27</v>
+      </c>
+      <c r="K7">
+        <v>17</v>
+      </c>
+      <c r="L7">
+        <v>19</v>
+      </c>
+      <c r="M7">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13">
+      <c r="A8" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B8">
+        <v>60</v>
+      </c>
+      <c r="C8">
+        <v>76</v>
+      </c>
+      <c r="D8">
+        <v>57</v>
+      </c>
+      <c r="E8">
+        <v>74</v>
+      </c>
+      <c r="F8">
+        <v>71</v>
+      </c>
+      <c r="G8">
+        <v>52</v>
+      </c>
+      <c r="H8">
+        <v>51</v>
+      </c>
+      <c r="I8">
+        <v>52</v>
+      </c>
+      <c r="J8">
+        <v>43</v>
+      </c>
+      <c r="K8">
+        <v>41</v>
+      </c>
+      <c r="L8">
+        <v>39</v>
+      </c>
+      <c r="M8">
+        <v>25</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -8423,7 +8747,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:D4"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -8486,7 +8810,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M9"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -8753,330 +9077,6 @@
       </c>
       <c r="M9">
         <v>7</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M10"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" customWidth="1"/>
-    <col min="13" max="13" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="M1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2">
-        <v>5</v>
-      </c>
-      <c r="C2">
-        <v>3</v>
-      </c>
-      <c r="D2">
-        <v>7</v>
-      </c>
-      <c r="E2">
-        <v>5</v>
-      </c>
-      <c r="F2">
-        <v>5</v>
-      </c>
-      <c r="G2">
-        <v>4</v>
-      </c>
-      <c r="H2">
-        <v>6</v>
-      </c>
-      <c r="I2">
-        <v>4</v>
-      </c>
-      <c r="J2">
-        <v>7</v>
-      </c>
-      <c r="K2">
-        <v>7</v>
-      </c>
-      <c r="L2">
-        <v>5</v>
-      </c>
-      <c r="M2">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3">
-        <v>3</v>
-      </c>
-      <c r="C3">
-        <v>2</v>
-      </c>
-      <c r="D3">
-        <v>8</v>
-      </c>
-      <c r="E3">
-        <v>9</v>
-      </c>
-      <c r="F3">
-        <v>19</v>
-      </c>
-      <c r="G3">
-        <v>9</v>
-      </c>
-      <c r="H3">
-        <v>8</v>
-      </c>
-      <c r="I3">
-        <v>13</v>
-      </c>
-      <c r="J3">
-        <v>12</v>
-      </c>
-      <c r="K3">
-        <v>17</v>
-      </c>
-      <c r="L3">
-        <v>13</v>
-      </c>
-      <c r="M3">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="I4">
-        <v>1</v>
-      </c>
-      <c r="M4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="K5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="E6">
-        <v>1</v>
-      </c>
-      <c r="F6">
-        <v>2</v>
-      </c>
-      <c r="J6">
-        <v>2</v>
-      </c>
-      <c r="M6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
-      <c r="A7" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E7">
-        <v>1</v>
-      </c>
-      <c r="I7">
-        <v>1</v>
-      </c>
-      <c r="K7">
-        <v>1</v>
-      </c>
-      <c r="L7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13">
-      <c r="A8" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B8">
-        <v>24</v>
-      </c>
-      <c r="C8">
-        <v>37</v>
-      </c>
-      <c r="D8">
-        <v>21</v>
-      </c>
-      <c r="E8">
-        <v>22</v>
-      </c>
-      <c r="F8">
-        <v>27</v>
-      </c>
-      <c r="G8">
-        <v>15</v>
-      </c>
-      <c r="H8">
-        <v>25</v>
-      </c>
-      <c r="I8">
-        <v>21</v>
-      </c>
-      <c r="J8">
-        <v>26</v>
-      </c>
-      <c r="K8">
-        <v>49</v>
-      </c>
-      <c r="L8">
-        <v>44</v>
-      </c>
-      <c r="M8">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13">
-      <c r="A9" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B9">
-        <v>45</v>
-      </c>
-      <c r="C9">
-        <v>64</v>
-      </c>
-      <c r="D9">
-        <v>46</v>
-      </c>
-      <c r="E9">
-        <v>50</v>
-      </c>
-      <c r="F9">
-        <v>38</v>
-      </c>
-      <c r="G9">
-        <v>19</v>
-      </c>
-      <c r="H9">
-        <v>27</v>
-      </c>
-      <c r="I9">
-        <v>37</v>
-      </c>
-      <c r="J9">
-        <v>20</v>
-      </c>
-      <c r="K9">
-        <v>35</v>
-      </c>
-      <c r="L9">
-        <v>35</v>
-      </c>
-      <c r="M9">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13">
-      <c r="A10" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B10">
-        <v>77</v>
-      </c>
-      <c r="C10">
-        <v>106</v>
-      </c>
-      <c r="D10">
-        <v>82</v>
-      </c>
-      <c r="E10">
-        <v>88</v>
-      </c>
-      <c r="F10">
-        <v>91</v>
-      </c>
-      <c r="G10">
-        <v>47</v>
-      </c>
-      <c r="H10">
-        <v>66</v>
-      </c>
-      <c r="I10">
-        <v>77</v>
-      </c>
-      <c r="J10">
-        <v>67</v>
-      </c>
-      <c r="K10">
-        <v>110</v>
-      </c>
-      <c r="L10">
-        <v>98</v>
-      </c>
-      <c r="M10">
-        <v>36</v>
       </c>
     </row>
   </sheetData>
@@ -14580,6 +14580,257 @@
 
 <file path=xl/worksheets/sheet44.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:M8"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+    <col min="13" max="13" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="M1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>2</v>
+      </c>
+      <c r="F2">
+        <v>2</v>
+      </c>
+      <c r="I2">
+        <v>3</v>
+      </c>
+      <c r="J2">
+        <v>2</v>
+      </c>
+      <c r="K2">
+        <v>1</v>
+      </c>
+      <c r="L2">
+        <v>5</v>
+      </c>
+      <c r="M2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
+      <c r="E3">
+        <v>1</v>
+      </c>
+      <c r="H3">
+        <v>2</v>
+      </c>
+      <c r="I3">
+        <v>1</v>
+      </c>
+      <c r="J3">
+        <v>1</v>
+      </c>
+      <c r="K3">
+        <v>2</v>
+      </c>
+      <c r="L3">
+        <v>2</v>
+      </c>
+      <c r="M3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
+      <c r="I4">
+        <v>1</v>
+      </c>
+      <c r="K4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="L5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6">
+        <v>1</v>
+      </c>
+      <c r="F6">
+        <v>4</v>
+      </c>
+      <c r="H6">
+        <v>1</v>
+      </c>
+      <c r="I6">
+        <v>2</v>
+      </c>
+      <c r="K6">
+        <v>1</v>
+      </c>
+      <c r="M6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7">
+        <v>10</v>
+      </c>
+      <c r="C7">
+        <v>20</v>
+      </c>
+      <c r="D7">
+        <v>25</v>
+      </c>
+      <c r="E7">
+        <v>30</v>
+      </c>
+      <c r="F7">
+        <v>41</v>
+      </c>
+      <c r="G7">
+        <v>10</v>
+      </c>
+      <c r="H7">
+        <v>5</v>
+      </c>
+      <c r="I7">
+        <v>5</v>
+      </c>
+      <c r="J7">
+        <v>15</v>
+      </c>
+      <c r="K7">
+        <v>17</v>
+      </c>
+      <c r="L7">
+        <v>12</v>
+      </c>
+      <c r="M7">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13">
+      <c r="A8" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B8">
+        <v>12</v>
+      </c>
+      <c r="C8">
+        <v>22</v>
+      </c>
+      <c r="D8">
+        <v>27</v>
+      </c>
+      <c r="E8">
+        <v>31</v>
+      </c>
+      <c r="F8">
+        <v>47</v>
+      </c>
+      <c r="G8">
+        <v>10</v>
+      </c>
+      <c r="H8">
+        <v>8</v>
+      </c>
+      <c r="I8">
+        <v>12</v>
+      </c>
+      <c r="J8">
+        <v>18</v>
+      </c>
+      <c r="K8">
+        <v>22</v>
+      </c>
+      <c r="L8">
+        <v>21</v>
+      </c>
+      <c r="M8">
+        <v>16</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet45.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -14857,7 +15108,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet45.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet46.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -15073,257 +15324,6 @@
       </c>
       <c r="M6">
         <v>3</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet46.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M8"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" customWidth="1"/>
-    <col min="13" max="13" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="M1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2">
-        <v>1</v>
-      </c>
-      <c r="D2">
-        <v>2</v>
-      </c>
-      <c r="F2">
-        <v>2</v>
-      </c>
-      <c r="I2">
-        <v>3</v>
-      </c>
-      <c r="J2">
-        <v>2</v>
-      </c>
-      <c r="K2">
-        <v>1</v>
-      </c>
-      <c r="L2">
-        <v>5</v>
-      </c>
-      <c r="M2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C3">
-        <v>1</v>
-      </c>
-      <c r="E3">
-        <v>1</v>
-      </c>
-      <c r="H3">
-        <v>2</v>
-      </c>
-      <c r="I3">
-        <v>1</v>
-      </c>
-      <c r="J3">
-        <v>1</v>
-      </c>
-      <c r="K3">
-        <v>2</v>
-      </c>
-      <c r="L3">
-        <v>2</v>
-      </c>
-      <c r="M3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C4">
-        <v>1</v>
-      </c>
-      <c r="I4">
-        <v>1</v>
-      </c>
-      <c r="K4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="L5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B6">
-        <v>1</v>
-      </c>
-      <c r="F6">
-        <v>4</v>
-      </c>
-      <c r="H6">
-        <v>1</v>
-      </c>
-      <c r="I6">
-        <v>2</v>
-      </c>
-      <c r="K6">
-        <v>1</v>
-      </c>
-      <c r="M6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
-      <c r="A7" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B7">
-        <v>10</v>
-      </c>
-      <c r="C7">
-        <v>20</v>
-      </c>
-      <c r="D7">
-        <v>25</v>
-      </c>
-      <c r="E7">
-        <v>30</v>
-      </c>
-      <c r="F7">
-        <v>41</v>
-      </c>
-      <c r="G7">
-        <v>10</v>
-      </c>
-      <c r="H7">
-        <v>5</v>
-      </c>
-      <c r="I7">
-        <v>5</v>
-      </c>
-      <c r="J7">
-        <v>15</v>
-      </c>
-      <c r="K7">
-        <v>17</v>
-      </c>
-      <c r="L7">
-        <v>12</v>
-      </c>
-      <c r="M7">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13">
-      <c r="A8" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B8">
-        <v>12</v>
-      </c>
-      <c r="C8">
-        <v>22</v>
-      </c>
-      <c r="D8">
-        <v>27</v>
-      </c>
-      <c r="E8">
-        <v>31</v>
-      </c>
-      <c r="F8">
-        <v>47</v>
-      </c>
-      <c r="G8">
-        <v>10</v>
-      </c>
-      <c r="H8">
-        <v>8</v>
-      </c>
-      <c r="I8">
-        <v>12</v>
-      </c>
-      <c r="J8">
-        <v>18</v>
-      </c>
-      <c r="K8">
-        <v>22</v>
-      </c>
-      <c r="L8">
-        <v>21</v>
-      </c>
-      <c r="M8">
-        <v>16</v>
       </c>
     </row>
   </sheetData>

--- a/output/cta-index-crime-full-year.xlsx
+++ b/output/cta-index-crime-full-year.xlsx
@@ -19,18 +19,18 @@
     <sheet name="Rogers Park" sheetId="10" r:id="rId10"/>
     <sheet name="Douglas" sheetId="11" r:id="rId11"/>
     <sheet name="Jefferson Park" sheetId="12" r:id="rId12"/>
-    <sheet name="Chatham" sheetId="13" r:id="rId13"/>
-    <sheet name="Albany Park" sheetId="14" r:id="rId14"/>
-    <sheet name="Grand Boulevard" sheetId="15" r:id="rId15"/>
-    <sheet name="Belmont Cragin" sheetId="16" r:id="rId16"/>
-    <sheet name="West Ridge" sheetId="17" r:id="rId17"/>
-    <sheet name="Loop" sheetId="18" r:id="rId18"/>
-    <sheet name="Lake View" sheetId="19" r:id="rId19"/>
-    <sheet name="Austin" sheetId="20" r:id="rId20"/>
-    <sheet name="South Shore" sheetId="21" r:id="rId21"/>
-    <sheet name="Mount Greenwood" sheetId="22" r:id="rId22"/>
-    <sheet name="Gage Park" sheetId="23" r:id="rId23"/>
-    <sheet name="Grand Crossing" sheetId="24" r:id="rId24"/>
+    <sheet name="Grand Crossing" sheetId="13" r:id="rId13"/>
+    <sheet name="Chatham" sheetId="14" r:id="rId14"/>
+    <sheet name="Austin" sheetId="15" r:id="rId15"/>
+    <sheet name="Albany Park" sheetId="16" r:id="rId16"/>
+    <sheet name="Grand Boulevard" sheetId="17" r:id="rId17"/>
+    <sheet name="Belmont Cragin" sheetId="18" r:id="rId18"/>
+    <sheet name="West Ridge" sheetId="19" r:id="rId19"/>
+    <sheet name="Loop" sheetId="20" r:id="rId20"/>
+    <sheet name="Lake View" sheetId="21" r:id="rId21"/>
+    <sheet name="South Shore" sheetId="22" r:id="rId22"/>
+    <sheet name="Mount Greenwood" sheetId="23" r:id="rId23"/>
+    <sheet name="Gage Park" sheetId="24" r:id="rId24"/>
     <sheet name="West Loop" sheetId="25" r:id="rId25"/>
     <sheet name="Rush &amp; Division" sheetId="26" r:id="rId26"/>
     <sheet name="North Lawndale" sheetId="27" r:id="rId27"/>
@@ -50,9 +50,9 @@
     <sheet name="Roseland" sheetId="41" r:id="rId41"/>
     <sheet name="Woodlawn" sheetId="42" r:id="rId42"/>
     <sheet name="Fuller Park" sheetId="43" r:id="rId43"/>
-    <sheet name="Little Italy, UIC" sheetId="44" r:id="rId44"/>
-    <sheet name="Hyde Park" sheetId="45" r:id="rId45"/>
-    <sheet name="O'Hare" sheetId="46" r:id="rId46"/>
+    <sheet name="O'Hare" sheetId="44" r:id="rId44"/>
+    <sheet name="Little Italy, UIC" sheetId="45" r:id="rId45"/>
+    <sheet name="Hyde Park" sheetId="46" r:id="rId46"/>
     <sheet name="Bucktown" sheetId="47" r:id="rId47"/>
     <sheet name="Calumet Heights" sheetId="48" r:id="rId48"/>
     <sheet name="Edgewater" sheetId="49" r:id="rId49"/>
@@ -905,7 +905,7 @@
         <v>137</v>
       </c>
       <c r="M2">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -1156,7 +1156,7 @@
         <v>467</v>
       </c>
       <c r="M9">
-        <v>181</v>
+        <v>183</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -1238,7 +1238,7 @@
         <v>1604</v>
       </c>
       <c r="M11">
-        <v>793</v>
+        <v>796</v>
       </c>
     </row>
   </sheetData>
@@ -2146,38 +2146,41 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
+      <c r="B2">
+        <v>5</v>
+      </c>
       <c r="C2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D2">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H2">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J2">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="L2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M2">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -2185,56 +2188,56 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D3">
+        <v>8</v>
+      </c>
+      <c r="E3">
+        <v>9</v>
+      </c>
+      <c r="F3">
+        <v>19</v>
+      </c>
+      <c r="G3">
+        <v>9</v>
+      </c>
+      <c r="H3">
+        <v>8</v>
+      </c>
+      <c r="I3">
+        <v>13</v>
+      </c>
+      <c r="J3">
+        <v>12</v>
+      </c>
+      <c r="K3">
+        <v>17</v>
+      </c>
+      <c r="L3">
+        <v>13</v>
+      </c>
+      <c r="M3">
         <v>7</v>
-      </c>
-      <c r="E3">
-        <v>3</v>
-      </c>
-      <c r="F3">
-        <v>4</v>
-      </c>
-      <c r="G3">
-        <v>8</v>
-      </c>
-      <c r="H3">
-        <v>4</v>
-      </c>
-      <c r="I3">
-        <v>6</v>
-      </c>
-      <c r="J3">
-        <v>4</v>
-      </c>
-      <c r="K3">
-        <v>10</v>
-      </c>
-      <c r="L3">
-        <v>5</v>
-      </c>
-      <c r="M3">
-        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="H4">
+      <c r="I4">
+        <v>1</v>
+      </c>
+      <c r="M4">
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K5">
         <v>1</v>
@@ -2242,30 +2245,36 @@
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="G6">
-        <v>1</v>
-      </c>
-      <c r="H6">
-        <v>1</v>
-      </c>
-      <c r="I6">
+        <v>5</v>
+      </c>
+      <c r="E6">
+        <v>1</v>
+      </c>
+      <c r="F6">
+        <v>2</v>
+      </c>
+      <c r="J6">
+        <v>2</v>
+      </c>
+      <c r="M6">
         <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D7">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E7">
         <v>1</v>
       </c>
-      <c r="J7">
-        <v>2</v>
+      <c r="I7">
+        <v>1</v>
+      </c>
+      <c r="K7">
+        <v>1</v>
+      </c>
+      <c r="L7">
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -2273,40 +2282,40 @@
         <v>8</v>
       </c>
       <c r="B8">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="C8">
-        <v>9</v>
+        <v>37</v>
       </c>
       <c r="D8">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E8">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="F8">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="G8">
         <v>15</v>
       </c>
       <c r="H8">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="I8">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="J8">
+        <v>26</v>
+      </c>
+      <c r="K8">
+        <v>49</v>
+      </c>
+      <c r="L8">
+        <v>44</v>
+      </c>
+      <c r="M8">
         <v>12</v>
-      </c>
-      <c r="K8">
-        <v>18</v>
-      </c>
-      <c r="L8">
-        <v>19</v>
-      </c>
-      <c r="M8">
-        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -2314,40 +2323,40 @@
         <v>9</v>
       </c>
       <c r="B9">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C9">
+        <v>64</v>
+      </c>
+      <c r="D9">
         <v>46</v>
       </c>
-      <c r="D9">
-        <v>32</v>
-      </c>
       <c r="E9">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="F9">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="G9">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="H9">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="I9">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="J9">
         <v>20</v>
       </c>
       <c r="K9">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="L9">
-        <v>13</v>
+        <v>35</v>
       </c>
       <c r="M9">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -2355,40 +2364,40 @@
         <v>10</v>
       </c>
       <c r="B10">
-        <v>51</v>
+        <v>77</v>
       </c>
       <c r="C10">
-        <v>57</v>
+        <v>106</v>
       </c>
       <c r="D10">
-        <v>62</v>
+        <v>82</v>
       </c>
       <c r="E10">
-        <v>48</v>
+        <v>88</v>
       </c>
       <c r="F10">
-        <v>60</v>
+        <v>91</v>
       </c>
       <c r="G10">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="H10">
-        <v>31</v>
+        <v>66</v>
       </c>
       <c r="I10">
-        <v>44</v>
+        <v>77</v>
       </c>
       <c r="J10">
-        <v>43</v>
+        <v>67</v>
       </c>
       <c r="K10">
-        <v>57</v>
+        <v>110</v>
       </c>
       <c r="L10">
-        <v>40</v>
+        <v>98</v>
       </c>
       <c r="M10">
-        <v>17</v>
+        <v>36</v>
       </c>
     </row>
   </sheetData>
@@ -2398,7 +2407,7 @@
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M7"/>
+  <dimension ref="A1:M10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="23.7109375" customWidth="1"/>
@@ -2461,29 +2470,38 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
       <c r="D2">
+        <v>5</v>
+      </c>
+      <c r="E2">
         <v>1</v>
       </c>
       <c r="F2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G2">
         <v>1</v>
       </c>
+      <c r="H2">
+        <v>3</v>
+      </c>
       <c r="I2">
         <v>2</v>
       </c>
       <c r="J2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K2">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="L2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M2">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -2491,153 +2509,210 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C3">
         <v>1</v>
       </c>
+      <c r="D3">
+        <v>7</v>
+      </c>
+      <c r="E3">
+        <v>3</v>
+      </c>
+      <c r="F3">
+        <v>4</v>
+      </c>
       <c r="G3">
-        <v>2</v>
+        <v>8</v>
+      </c>
+      <c r="H3">
+        <v>4</v>
       </c>
       <c r="I3">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="J3">
-        <v>1</v>
+        <v>4</v>
+      </c>
+      <c r="K3">
+        <v>10</v>
       </c>
       <c r="L3">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="E4">
-        <v>2</v>
-      </c>
-      <c r="J4">
-        <v>1</v>
-      </c>
-      <c r="K4">
+        <v>3</v>
+      </c>
+      <c r="H4">
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B5">
         <v>1</v>
       </c>
-      <c r="C5">
-        <v>1</v>
-      </c>
-      <c r="D5">
-        <v>2</v>
-      </c>
-      <c r="E5">
-        <v>2</v>
-      </c>
-      <c r="G5">
-        <v>1</v>
-      </c>
-      <c r="I5">
-        <v>1</v>
-      </c>
-      <c r="J5">
-        <v>3</v>
-      </c>
       <c r="K5">
-        <v>4</v>
-      </c>
-      <c r="M5">
         <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B6">
-        <v>8</v>
-      </c>
-      <c r="C6">
-        <v>13</v>
-      </c>
-      <c r="D6">
-        <v>10</v>
-      </c>
-      <c r="E6">
-        <v>9</v>
-      </c>
-      <c r="F6">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G6">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="H6">
         <v>1</v>
       </c>
       <c r="I6">
-        <v>4</v>
-      </c>
-      <c r="J6">
-        <v>5</v>
-      </c>
-      <c r="K6">
-        <v>8</v>
-      </c>
-      <c r="L6">
-        <v>3</v>
-      </c>
-      <c r="M6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D7">
+        <v>1</v>
+      </c>
+      <c r="E7">
+        <v>1</v>
+      </c>
+      <c r="J7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13">
+      <c r="A8" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8">
+        <v>5</v>
+      </c>
+      <c r="C8">
+        <v>9</v>
+      </c>
+      <c r="D8">
+        <v>17</v>
+      </c>
+      <c r="E8">
+        <v>13</v>
+      </c>
+      <c r="F8">
+        <v>19</v>
+      </c>
+      <c r="G8">
+        <v>15</v>
+      </c>
+      <c r="H8">
+        <v>5</v>
+      </c>
+      <c r="I8">
+        <v>15</v>
+      </c>
+      <c r="J8">
+        <v>12</v>
+      </c>
+      <c r="K8">
+        <v>18</v>
+      </c>
+      <c r="L8">
+        <v>19</v>
+      </c>
+      <c r="M8">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13">
+      <c r="A9" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B9">
+        <v>43</v>
+      </c>
+      <c r="C9">
+        <v>46</v>
+      </c>
+      <c r="D9">
+        <v>32</v>
+      </c>
+      <c r="E9">
+        <v>30</v>
+      </c>
+      <c r="F9">
+        <v>34</v>
+      </c>
+      <c r="G9">
+        <v>15</v>
+      </c>
+      <c r="H9">
+        <v>17</v>
+      </c>
+      <c r="I9">
+        <v>20</v>
+      </c>
+      <c r="J9">
+        <v>20</v>
+      </c>
+      <c r="K9">
+        <v>20</v>
+      </c>
+      <c r="L9">
+        <v>13</v>
+      </c>
+      <c r="M9">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13">
+      <c r="A10" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B7">
-        <v>10</v>
-      </c>
-      <c r="C7">
-        <v>15</v>
-      </c>
-      <c r="D7">
-        <v>13</v>
-      </c>
-      <c r="E7">
-        <v>13</v>
-      </c>
-      <c r="F7">
-        <v>10</v>
-      </c>
-      <c r="G7">
-        <v>12</v>
-      </c>
-      <c r="H7">
-        <v>1</v>
-      </c>
-      <c r="I7">
-        <v>8</v>
-      </c>
-      <c r="J7">
-        <v>14</v>
-      </c>
-      <c r="K7">
-        <v>15</v>
-      </c>
-      <c r="L7">
-        <v>6</v>
-      </c>
-      <c r="M7">
-        <v>5</v>
+      <c r="B10">
+        <v>51</v>
+      </c>
+      <c r="C10">
+        <v>57</v>
+      </c>
+      <c r="D10">
+        <v>62</v>
+      </c>
+      <c r="E10">
+        <v>48</v>
+      </c>
+      <c r="F10">
+        <v>60</v>
+      </c>
+      <c r="G10">
+        <v>40</v>
+      </c>
+      <c r="H10">
+        <v>31</v>
+      </c>
+      <c r="I10">
+        <v>44</v>
+      </c>
+      <c r="J10">
+        <v>43</v>
+      </c>
+      <c r="K10">
+        <v>57</v>
+      </c>
+      <c r="L10">
+        <v>40</v>
+      </c>
+      <c r="M10">
+        <v>17</v>
       </c>
     </row>
   </sheetData>
@@ -2647,10 +2722,10 @@
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M7"/>
+  <dimension ref="A1:M10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="18.7109375" customWidth="1"/>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
     <col min="2" max="2" width="4.7109375" customWidth="1"/>
     <col min="3" max="3" width="4.7109375" customWidth="1"/>
     <col min="4" max="4" width="4.7109375" customWidth="1"/>
@@ -2710,29 +2785,41 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
+      <c r="B2">
+        <v>4</v>
+      </c>
       <c r="C2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E2">
-        <v>1</v>
+        <v>5</v>
+      </c>
+      <c r="F2">
+        <v>9</v>
+      </c>
+      <c r="G2">
+        <v>3</v>
       </c>
       <c r="H2">
-        <v>2</v>
+        <v>5</v>
+      </c>
+      <c r="I2">
+        <v>4</v>
       </c>
       <c r="J2">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="K2">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="L2">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="M2">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -2740,162 +2827,210 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C3">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D3">
-        <v>1</v>
+        <v>6</v>
+      </c>
+      <c r="E3">
+        <v>7</v>
       </c>
       <c r="F3">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G3">
-        <v>1</v>
+        <v>7</v>
+      </c>
+      <c r="H3">
+        <v>8</v>
       </c>
       <c r="I3">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J3">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="K3">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="L3">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="M3">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H4">
+        <v>3</v>
+      </c>
+      <c r="I4">
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B5">
-        <v>7</v>
-      </c>
-      <c r="C5">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="D5">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E5">
-        <v>5</v>
-      </c>
-      <c r="F5">
-        <v>5</v>
-      </c>
-      <c r="G5">
-        <v>6</v>
-      </c>
-      <c r="H5">
-        <v>2</v>
-      </c>
-      <c r="I5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J5">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K5">
-        <v>6</v>
-      </c>
-      <c r="L5">
-        <v>6</v>
+        <v>2</v>
+      </c>
+      <c r="M5">
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B6">
-        <v>15</v>
-      </c>
-      <c r="C6">
-        <v>16</v>
-      </c>
-      <c r="D6">
-        <v>15</v>
-      </c>
-      <c r="E6">
-        <v>16</v>
-      </c>
-      <c r="F6">
-        <v>11</v>
-      </c>
-      <c r="G6">
-        <v>9</v>
-      </c>
-      <c r="H6">
-        <v>5</v>
-      </c>
-      <c r="I6">
-        <v>5</v>
-      </c>
-      <c r="J6">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="K6">
-        <v>6</v>
-      </c>
-      <c r="L6">
-        <v>4</v>
-      </c>
-      <c r="M6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="L7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13">
+      <c r="A8" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8">
+        <v>23</v>
+      </c>
+      <c r="C8">
+        <v>31</v>
+      </c>
+      <c r="D8">
+        <v>22</v>
+      </c>
+      <c r="E8">
+        <v>44</v>
+      </c>
+      <c r="F8">
+        <v>38</v>
+      </c>
+      <c r="G8">
+        <v>24</v>
+      </c>
+      <c r="H8">
+        <v>50</v>
+      </c>
+      <c r="I8">
+        <v>34</v>
+      </c>
+      <c r="J8">
+        <v>26</v>
+      </c>
+      <c r="K8">
+        <v>24</v>
+      </c>
+      <c r="L8">
+        <v>14</v>
+      </c>
+      <c r="M8">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13">
+      <c r="A9" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B9">
+        <v>46</v>
+      </c>
+      <c r="C9">
+        <v>59</v>
+      </c>
+      <c r="D9">
+        <v>33</v>
+      </c>
+      <c r="E9">
+        <v>73</v>
+      </c>
+      <c r="F9">
+        <v>114</v>
+      </c>
+      <c r="G9">
+        <v>58</v>
+      </c>
+      <c r="H9">
+        <v>41</v>
+      </c>
+      <c r="I9">
+        <v>44</v>
+      </c>
+      <c r="J9">
+        <v>20</v>
+      </c>
+      <c r="K9">
+        <v>25</v>
+      </c>
+      <c r="L9">
+        <v>27</v>
+      </c>
+      <c r="M9">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13">
+      <c r="A10" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B7">
-        <v>24</v>
-      </c>
-      <c r="C7">
-        <v>29</v>
-      </c>
-      <c r="D7">
-        <v>25</v>
-      </c>
-      <c r="E7">
-        <v>22</v>
-      </c>
-      <c r="F7">
-        <v>19</v>
-      </c>
-      <c r="G7">
-        <v>16</v>
-      </c>
-      <c r="H7">
-        <v>10</v>
-      </c>
-      <c r="I7">
-        <v>11</v>
-      </c>
-      <c r="J7">
-        <v>20</v>
-      </c>
-      <c r="K7">
-        <v>15</v>
-      </c>
-      <c r="L7">
-        <v>16</v>
-      </c>
-      <c r="M7">
-        <v>6</v>
+      <c r="B10">
+        <v>78</v>
+      </c>
+      <c r="C10">
+        <v>99</v>
+      </c>
+      <c r="D10">
+        <v>65</v>
+      </c>
+      <c r="E10">
+        <v>130</v>
+      </c>
+      <c r="F10">
+        <v>167</v>
+      </c>
+      <c r="G10">
+        <v>92</v>
+      </c>
+      <c r="H10">
+        <v>104</v>
+      </c>
+      <c r="I10">
+        <v>89</v>
+      </c>
+      <c r="J10">
+        <v>67</v>
+      </c>
+      <c r="K10">
+        <v>71</v>
+      </c>
+      <c r="L10">
+        <v>61</v>
+      </c>
+      <c r="M10">
+        <v>50</v>
       </c>
     </row>
   </sheetData>
@@ -2971,7 +3106,25 @@
       <c r="D2">
         <v>1</v>
       </c>
+      <c r="F2">
+        <v>1</v>
+      </c>
+      <c r="G2">
+        <v>1</v>
+      </c>
+      <c r="I2">
+        <v>2</v>
+      </c>
       <c r="J2">
+        <v>4</v>
+      </c>
+      <c r="K2">
+        <v>2</v>
+      </c>
+      <c r="L2">
+        <v>2</v>
+      </c>
+      <c r="M2">
         <v>1</v>
       </c>
     </row>
@@ -2979,16 +3132,25 @@
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="E3">
-        <v>2</v>
+      <c r="B3">
+        <v>1</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
       </c>
       <c r="G3">
+        <v>2</v>
+      </c>
+      <c r="I3">
         <v>1</v>
       </c>
       <c r="J3">
         <v>1</v>
       </c>
       <c r="L3">
+        <v>1</v>
+      </c>
+      <c r="M3">
         <v>1</v>
       </c>
     </row>
@@ -2996,7 +3158,13 @@
       <c r="A4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C4">
+      <c r="E4">
+        <v>2</v>
+      </c>
+      <c r="J4">
+        <v>1</v>
+      </c>
+      <c r="K4">
         <v>1</v>
       </c>
     </row>
@@ -3005,22 +3173,28 @@
         <v>8</v>
       </c>
       <c r="B5">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C5">
-        <v>6</v>
+        <v>1</v>
+      </c>
+      <c r="D5">
+        <v>2</v>
       </c>
       <c r="E5">
-        <v>1</v>
-      </c>
-      <c r="H5">
-        <v>2</v>
+        <v>2</v>
+      </c>
+      <c r="G5">
+        <v>1</v>
+      </c>
+      <c r="I5">
+        <v>1</v>
       </c>
       <c r="J5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M5">
         <v>1</v>
@@ -3031,40 +3205,40 @@
         <v>9</v>
       </c>
       <c r="B6">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C6">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="D6">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E6">
+        <v>9</v>
+      </c>
+      <c r="F6">
+        <v>9</v>
+      </c>
+      <c r="G6">
         <v>8</v>
       </c>
-      <c r="F6">
-        <v>7</v>
-      </c>
-      <c r="G6">
-        <v>2</v>
-      </c>
       <c r="H6">
         <v>1</v>
       </c>
       <c r="I6">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J6">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K6">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="L6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -3072,40 +3246,40 @@
         <v>10</v>
       </c>
       <c r="B7">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C7">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D7">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="E7">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F7">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G7">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="H7">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I7">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="J7">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="K7">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="L7">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="M7">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -3114,6 +3288,477 @@
 </file>
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:M7"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="18.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+    <col min="13" max="13" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="M1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
+      <c r="H2">
+        <v>2</v>
+      </c>
+      <c r="J2">
+        <v>1</v>
+      </c>
+      <c r="K2">
+        <v>2</v>
+      </c>
+      <c r="L2">
+        <v>2</v>
+      </c>
+      <c r="M2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>2</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
+      <c r="F3">
+        <v>3</v>
+      </c>
+      <c r="G3">
+        <v>1</v>
+      </c>
+      <c r="I3">
+        <v>4</v>
+      </c>
+      <c r="J3">
+        <v>2</v>
+      </c>
+      <c r="K3">
+        <v>1</v>
+      </c>
+      <c r="L3">
+        <v>4</v>
+      </c>
+      <c r="M3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5">
+        <v>7</v>
+      </c>
+      <c r="C5">
+        <v>11</v>
+      </c>
+      <c r="D5">
+        <v>8</v>
+      </c>
+      <c r="E5">
+        <v>5</v>
+      </c>
+      <c r="F5">
+        <v>5</v>
+      </c>
+      <c r="G5">
+        <v>6</v>
+      </c>
+      <c r="H5">
+        <v>2</v>
+      </c>
+      <c r="I5">
+        <v>2</v>
+      </c>
+      <c r="J5">
+        <v>5</v>
+      </c>
+      <c r="K5">
+        <v>6</v>
+      </c>
+      <c r="L5">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6">
+        <v>15</v>
+      </c>
+      <c r="C6">
+        <v>16</v>
+      </c>
+      <c r="D6">
+        <v>15</v>
+      </c>
+      <c r="E6">
+        <v>16</v>
+      </c>
+      <c r="F6">
+        <v>11</v>
+      </c>
+      <c r="G6">
+        <v>9</v>
+      </c>
+      <c r="H6">
+        <v>5</v>
+      </c>
+      <c r="I6">
+        <v>5</v>
+      </c>
+      <c r="J6">
+        <v>12</v>
+      </c>
+      <c r="K6">
+        <v>6</v>
+      </c>
+      <c r="L6">
+        <v>4</v>
+      </c>
+      <c r="M6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7">
+        <v>24</v>
+      </c>
+      <c r="C7">
+        <v>29</v>
+      </c>
+      <c r="D7">
+        <v>25</v>
+      </c>
+      <c r="E7">
+        <v>22</v>
+      </c>
+      <c r="F7">
+        <v>19</v>
+      </c>
+      <c r="G7">
+        <v>16</v>
+      </c>
+      <c r="H7">
+        <v>10</v>
+      </c>
+      <c r="I7">
+        <v>11</v>
+      </c>
+      <c r="J7">
+        <v>20</v>
+      </c>
+      <c r="K7">
+        <v>15</v>
+      </c>
+      <c r="L7">
+        <v>16</v>
+      </c>
+      <c r="M7">
+        <v>6</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:M7"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+    <col min="13" max="13" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="M1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="J2">
+        <v>1</v>
+      </c>
+      <c r="M2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E3">
+        <v>2</v>
+      </c>
+      <c r="G3">
+        <v>1</v>
+      </c>
+      <c r="J3">
+        <v>1</v>
+      </c>
+      <c r="L3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5">
+        <v>5</v>
+      </c>
+      <c r="C5">
+        <v>6</v>
+      </c>
+      <c r="E5">
+        <v>1</v>
+      </c>
+      <c r="H5">
+        <v>2</v>
+      </c>
+      <c r="J5">
+        <v>4</v>
+      </c>
+      <c r="K5">
+        <v>2</v>
+      </c>
+      <c r="M5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6">
+        <v>6</v>
+      </c>
+      <c r="C6">
+        <v>2</v>
+      </c>
+      <c r="D6">
+        <v>6</v>
+      </c>
+      <c r="E6">
+        <v>8</v>
+      </c>
+      <c r="F6">
+        <v>7</v>
+      </c>
+      <c r="G6">
+        <v>2</v>
+      </c>
+      <c r="H6">
+        <v>1</v>
+      </c>
+      <c r="I6">
+        <v>1</v>
+      </c>
+      <c r="J6">
+        <v>3</v>
+      </c>
+      <c r="K6">
+        <v>1</v>
+      </c>
+      <c r="L6">
+        <v>2</v>
+      </c>
+      <c r="M6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7">
+        <v>11</v>
+      </c>
+      <c r="C7">
+        <v>9</v>
+      </c>
+      <c r="D7">
+        <v>7</v>
+      </c>
+      <c r="E7">
+        <v>11</v>
+      </c>
+      <c r="F7">
+        <v>7</v>
+      </c>
+      <c r="G7">
+        <v>3</v>
+      </c>
+      <c r="H7">
+        <v>3</v>
+      </c>
+      <c r="I7">
+        <v>1</v>
+      </c>
+      <c r="J7">
+        <v>9</v>
+      </c>
+      <c r="K7">
+        <v>3</v>
+      </c>
+      <c r="L7">
+        <v>3</v>
+      </c>
+      <c r="M7">
+        <v>3</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:L8"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -3284,656 +3929,6 @@
       </c>
       <c r="L8">
         <v>2</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M10"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" customWidth="1"/>
-    <col min="13" max="13" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="M1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2">
-        <v>6</v>
-      </c>
-      <c r="C2">
-        <v>3</v>
-      </c>
-      <c r="D2">
-        <v>12</v>
-      </c>
-      <c r="E2">
-        <v>5</v>
-      </c>
-      <c r="F2">
-        <v>8</v>
-      </c>
-      <c r="G2">
-        <v>4</v>
-      </c>
-      <c r="H2">
-        <v>13</v>
-      </c>
-      <c r="I2">
-        <v>14</v>
-      </c>
-      <c r="J2">
-        <v>22</v>
-      </c>
-      <c r="K2">
-        <v>15</v>
-      </c>
-      <c r="L2">
-        <v>15</v>
-      </c>
-      <c r="M2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3">
-        <v>13</v>
-      </c>
-      <c r="C3">
-        <v>13</v>
-      </c>
-      <c r="D3">
-        <v>17</v>
-      </c>
-      <c r="E3">
-        <v>18</v>
-      </c>
-      <c r="F3">
-        <v>14</v>
-      </c>
-      <c r="G3">
-        <v>26</v>
-      </c>
-      <c r="H3">
-        <v>23</v>
-      </c>
-      <c r="I3">
-        <v>32</v>
-      </c>
-      <c r="J3">
-        <v>40</v>
-      </c>
-      <c r="K3">
-        <v>26</v>
-      </c>
-      <c r="L3">
-        <v>34</v>
-      </c>
-      <c r="M3">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="G4">
-        <v>1</v>
-      </c>
-      <c r="J4">
-        <v>2</v>
-      </c>
-      <c r="K4">
-        <v>1</v>
-      </c>
-      <c r="L4">
-        <v>1</v>
-      </c>
-      <c r="M4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C5">
-        <v>2</v>
-      </c>
-      <c r="D5">
-        <v>1</v>
-      </c>
-      <c r="E5">
-        <v>2</v>
-      </c>
-      <c r="F5">
-        <v>1</v>
-      </c>
-      <c r="H5">
-        <v>2</v>
-      </c>
-      <c r="I5">
-        <v>4</v>
-      </c>
-      <c r="J5">
-        <v>3</v>
-      </c>
-      <c r="K5">
-        <v>2</v>
-      </c>
-      <c r="L5">
-        <v>5</v>
-      </c>
-      <c r="M5">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="G6">
-        <v>1</v>
-      </c>
-      <c r="H6">
-        <v>2</v>
-      </c>
-      <c r="J6">
-        <v>2</v>
-      </c>
-      <c r="L6">
-        <v>2</v>
-      </c>
-      <c r="M6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
-      <c r="A7" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="K7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13">
-      <c r="A8" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B8">
-        <v>30</v>
-      </c>
-      <c r="C8">
-        <v>44</v>
-      </c>
-      <c r="D8">
-        <v>49</v>
-      </c>
-      <c r="E8">
-        <v>67</v>
-      </c>
-      <c r="F8">
-        <v>69</v>
-      </c>
-      <c r="G8">
-        <v>57</v>
-      </c>
-      <c r="H8">
-        <v>80</v>
-      </c>
-      <c r="I8">
-        <v>80</v>
-      </c>
-      <c r="J8">
-        <v>64</v>
-      </c>
-      <c r="K8">
-        <v>48</v>
-      </c>
-      <c r="L8">
-        <v>44</v>
-      </c>
-      <c r="M8">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13">
-      <c r="A9" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B9">
-        <v>233</v>
-      </c>
-      <c r="C9">
-        <v>354</v>
-      </c>
-      <c r="D9">
-        <v>538</v>
-      </c>
-      <c r="E9">
-        <v>705</v>
-      </c>
-      <c r="F9">
-        <v>568</v>
-      </c>
-      <c r="G9">
-        <v>168</v>
-      </c>
-      <c r="H9">
-        <v>116</v>
-      </c>
-      <c r="I9">
-        <v>194</v>
-      </c>
-      <c r="J9">
-        <v>122</v>
-      </c>
-      <c r="K9">
-        <v>114</v>
-      </c>
-      <c r="L9">
-        <v>95</v>
-      </c>
-      <c r="M9">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13">
-      <c r="A10" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B10">
-        <v>282</v>
-      </c>
-      <c r="C10">
-        <v>416</v>
-      </c>
-      <c r="D10">
-        <v>617</v>
-      </c>
-      <c r="E10">
-        <v>797</v>
-      </c>
-      <c r="F10">
-        <v>660</v>
-      </c>
-      <c r="G10">
-        <v>257</v>
-      </c>
-      <c r="H10">
-        <v>236</v>
-      </c>
-      <c r="I10">
-        <v>324</v>
-      </c>
-      <c r="J10">
-        <v>255</v>
-      </c>
-      <c r="K10">
-        <v>207</v>
-      </c>
-      <c r="L10">
-        <v>196</v>
-      </c>
-      <c r="M10">
-        <v>89</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M8"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" customWidth="1"/>
-    <col min="13" max="13" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="M1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2">
-        <v>4</v>
-      </c>
-      <c r="D2">
-        <v>1</v>
-      </c>
-      <c r="E2">
-        <v>4</v>
-      </c>
-      <c r="F2">
-        <v>2</v>
-      </c>
-      <c r="G2">
-        <v>4</v>
-      </c>
-      <c r="H2">
-        <v>2</v>
-      </c>
-      <c r="I2">
-        <v>3</v>
-      </c>
-      <c r="J2">
-        <v>2</v>
-      </c>
-      <c r="K2">
-        <v>6</v>
-      </c>
-      <c r="L2">
-        <v>6</v>
-      </c>
-      <c r="M2">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3">
-        <v>2</v>
-      </c>
-      <c r="C3">
-        <v>4</v>
-      </c>
-      <c r="D3">
-        <v>1</v>
-      </c>
-      <c r="E3">
-        <v>4</v>
-      </c>
-      <c r="F3">
-        <v>5</v>
-      </c>
-      <c r="G3">
-        <v>4</v>
-      </c>
-      <c r="H3">
-        <v>7</v>
-      </c>
-      <c r="I3">
-        <v>2</v>
-      </c>
-      <c r="J3">
-        <v>11</v>
-      </c>
-      <c r="K3">
-        <v>5</v>
-      </c>
-      <c r="L3">
-        <v>7</v>
-      </c>
-      <c r="M3">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="H4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C5">
-        <v>1</v>
-      </c>
-      <c r="H5">
-        <v>1</v>
-      </c>
-      <c r="I5">
-        <v>1</v>
-      </c>
-      <c r="K5">
-        <v>3</v>
-      </c>
-      <c r="L5">
-        <v>2</v>
-      </c>
-      <c r="M5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C6">
-        <v>14</v>
-      </c>
-      <c r="D6">
-        <v>12</v>
-      </c>
-      <c r="E6">
-        <v>10</v>
-      </c>
-      <c r="F6">
-        <v>11</v>
-      </c>
-      <c r="G6">
-        <v>11</v>
-      </c>
-      <c r="H6">
-        <v>17</v>
-      </c>
-      <c r="I6">
-        <v>20</v>
-      </c>
-      <c r="J6">
-        <v>3</v>
-      </c>
-      <c r="K6">
-        <v>10</v>
-      </c>
-      <c r="L6">
-        <v>5</v>
-      </c>
-      <c r="M6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
-      <c r="A7" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B7">
-        <v>58</v>
-      </c>
-      <c r="C7">
-        <v>53</v>
-      </c>
-      <c r="D7">
-        <v>43</v>
-      </c>
-      <c r="E7">
-        <v>56</v>
-      </c>
-      <c r="F7">
-        <v>53</v>
-      </c>
-      <c r="G7">
-        <v>33</v>
-      </c>
-      <c r="H7">
-        <v>23</v>
-      </c>
-      <c r="I7">
-        <v>26</v>
-      </c>
-      <c r="J7">
-        <v>27</v>
-      </c>
-      <c r="K7">
-        <v>17</v>
-      </c>
-      <c r="L7">
-        <v>19</v>
-      </c>
-      <c r="M7">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13">
-      <c r="A8" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B8">
-        <v>60</v>
-      </c>
-      <c r="C8">
-        <v>76</v>
-      </c>
-      <c r="D8">
-        <v>57</v>
-      </c>
-      <c r="E8">
-        <v>74</v>
-      </c>
-      <c r="F8">
-        <v>71</v>
-      </c>
-      <c r="G8">
-        <v>52</v>
-      </c>
-      <c r="H8">
-        <v>51</v>
-      </c>
-      <c r="I8">
-        <v>52</v>
-      </c>
-      <c r="J8">
-        <v>43</v>
-      </c>
-      <c r="K8">
-        <v>41</v>
-      </c>
-      <c r="L8">
-        <v>39</v>
-      </c>
-      <c r="M8">
-        <v>25</v>
       </c>
     </row>
   </sheetData>
@@ -4382,7 +4377,7 @@
         <v>3</v>
       </c>
       <c r="M11">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12" spans="1:13">
@@ -6313,7 +6308,7 @@
         <v>4</v>
       </c>
       <c r="M63">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="64" spans="1:13">
@@ -7287,7 +7282,7 @@
         <v>2</v>
       </c>
       <c r="M88">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="89" spans="1:13">
@@ -7442,7 +7437,7 @@
         <v>26</v>
       </c>
       <c r="M92">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="93" spans="1:13">
@@ -7644,7 +7639,7 @@
         <v>6</v>
       </c>
       <c r="M97">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="98" spans="1:13">
@@ -7726,7 +7721,7 @@
         <v>1604</v>
       </c>
       <c r="M99">
-        <v>793</v>
+        <v>796</v>
       </c>
     </row>
   </sheetData>
@@ -7900,40 +7895,40 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D2">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="E2">
         <v>5</v>
       </c>
       <c r="F2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H2">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="I2">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="J2">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="K2">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="L2">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="M2">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -7941,47 +7936,59 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="C3">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="D3">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="E3">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="F3">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="G3">
-        <v>7</v>
+        <v>26</v>
       </c>
       <c r="H3">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="I3">
-        <v>6</v>
+        <v>32</v>
       </c>
       <c r="J3">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="K3">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="L3">
-        <v>14</v>
+        <v>34</v>
       </c>
       <c r="M3">
-        <v>10</v>
+        <v>16</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="I4">
+      <c r="G4">
+        <v>1</v>
+      </c>
+      <c r="J4">
+        <v>2</v>
+      </c>
+      <c r="K4">
+        <v>1</v>
+      </c>
+      <c r="L4">
+        <v>1</v>
+      </c>
+      <c r="M4">
         <v>1</v>
       </c>
     </row>
@@ -7989,14 +7996,23 @@
       <c r="A5" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B5">
-        <v>1</v>
+      <c r="C5">
+        <v>2</v>
       </c>
       <c r="D5">
         <v>1</v>
       </c>
       <c r="E5">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="F5">
+        <v>1</v>
+      </c>
+      <c r="H5">
+        <v>2</v>
+      </c>
+      <c r="I5">
+        <v>4</v>
       </c>
       <c r="J5">
         <v>3</v>
@@ -8004,15 +8020,30 @@
       <c r="K5">
         <v>2</v>
       </c>
+      <c r="L5">
+        <v>5</v>
+      </c>
       <c r="M5">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="K6">
+      <c r="G6">
+        <v>1</v>
+      </c>
+      <c r="H6">
+        <v>2</v>
+      </c>
+      <c r="J6">
+        <v>2</v>
+      </c>
+      <c r="L6">
+        <v>2</v>
+      </c>
+      <c r="M6">
         <v>1</v>
       </c>
     </row>
@@ -8020,7 +8051,7 @@
       <c r="A7" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="L7">
+      <c r="K7">
         <v>1</v>
       </c>
     </row>
@@ -8029,40 +8060,40 @@
         <v>8</v>
       </c>
       <c r="B8">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="C8">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="D8">
-        <v>22</v>
+        <v>49</v>
       </c>
       <c r="E8">
+        <v>67</v>
+      </c>
+      <c r="F8">
+        <v>69</v>
+      </c>
+      <c r="G8">
+        <v>57</v>
+      </c>
+      <c r="H8">
+        <v>80</v>
+      </c>
+      <c r="I8">
+        <v>80</v>
+      </c>
+      <c r="J8">
+        <v>64</v>
+      </c>
+      <c r="K8">
+        <v>48</v>
+      </c>
+      <c r="L8">
         <v>44</v>
       </c>
-      <c r="F8">
-        <v>38</v>
-      </c>
-      <c r="G8">
-        <v>24</v>
-      </c>
-      <c r="H8">
-        <v>50</v>
-      </c>
-      <c r="I8">
-        <v>34</v>
-      </c>
-      <c r="J8">
-        <v>26</v>
-      </c>
-      <c r="K8">
-        <v>24</v>
-      </c>
-      <c r="L8">
-        <v>14</v>
-      </c>
       <c r="M8">
-        <v>14</v>
+        <v>20</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -8070,40 +8101,40 @@
         <v>9</v>
       </c>
       <c r="B9">
-        <v>46</v>
+        <v>233</v>
       </c>
       <c r="C9">
-        <v>59</v>
+        <v>354</v>
       </c>
       <c r="D9">
-        <v>33</v>
+        <v>538</v>
       </c>
       <c r="E9">
-        <v>73</v>
+        <v>705</v>
       </c>
       <c r="F9">
+        <v>568</v>
+      </c>
+      <c r="G9">
+        <v>168</v>
+      </c>
+      <c r="H9">
+        <v>116</v>
+      </c>
+      <c r="I9">
+        <v>194</v>
+      </c>
+      <c r="J9">
+        <v>122</v>
+      </c>
+      <c r="K9">
         <v>114</v>
       </c>
-      <c r="G9">
-        <v>58</v>
-      </c>
-      <c r="H9">
-        <v>41</v>
-      </c>
-      <c r="I9">
-        <v>44</v>
-      </c>
-      <c r="J9">
-        <v>20</v>
-      </c>
-      <c r="K9">
-        <v>25</v>
-      </c>
       <c r="L9">
-        <v>27</v>
+        <v>95</v>
       </c>
       <c r="M9">
-        <v>16</v>
+        <v>45</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -8111,40 +8142,40 @@
         <v>10</v>
       </c>
       <c r="B10">
-        <v>78</v>
+        <v>282</v>
       </c>
       <c r="C10">
-        <v>99</v>
+        <v>416</v>
       </c>
       <c r="D10">
-        <v>65</v>
+        <v>617</v>
       </c>
       <c r="E10">
-        <v>130</v>
+        <v>797</v>
       </c>
       <c r="F10">
-        <v>167</v>
+        <v>660</v>
       </c>
       <c r="G10">
-        <v>92</v>
+        <v>257</v>
       </c>
       <c r="H10">
-        <v>104</v>
+        <v>236</v>
       </c>
       <c r="I10">
+        <v>324</v>
+      </c>
+      <c r="J10">
+        <v>255</v>
+      </c>
+      <c r="K10">
+        <v>207</v>
+      </c>
+      <c r="L10">
+        <v>196</v>
+      </c>
+      <c r="M10">
         <v>89</v>
-      </c>
-      <c r="J10">
-        <v>67</v>
-      </c>
-      <c r="K10">
-        <v>71</v>
-      </c>
-      <c r="L10">
-        <v>61</v>
-      </c>
-      <c r="M10">
-        <v>50</v>
       </c>
     </row>
   </sheetData>
@@ -8153,6 +8184,302 @@
 </file>
 
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:M8"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+    <col min="13" max="13" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="M1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>4</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="E2">
+        <v>4</v>
+      </c>
+      <c r="F2">
+        <v>2</v>
+      </c>
+      <c r="G2">
+        <v>4</v>
+      </c>
+      <c r="H2">
+        <v>2</v>
+      </c>
+      <c r="I2">
+        <v>3</v>
+      </c>
+      <c r="J2">
+        <v>2</v>
+      </c>
+      <c r="K2">
+        <v>6</v>
+      </c>
+      <c r="L2">
+        <v>6</v>
+      </c>
+      <c r="M2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>2</v>
+      </c>
+      <c r="C3">
+        <v>4</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
+      <c r="E3">
+        <v>4</v>
+      </c>
+      <c r="F3">
+        <v>5</v>
+      </c>
+      <c r="G3">
+        <v>4</v>
+      </c>
+      <c r="H3">
+        <v>7</v>
+      </c>
+      <c r="I3">
+        <v>2</v>
+      </c>
+      <c r="J3">
+        <v>11</v>
+      </c>
+      <c r="K3">
+        <v>5</v>
+      </c>
+      <c r="L3">
+        <v>7</v>
+      </c>
+      <c r="M3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="H4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C5">
+        <v>1</v>
+      </c>
+      <c r="H5">
+        <v>1</v>
+      </c>
+      <c r="I5">
+        <v>1</v>
+      </c>
+      <c r="K5">
+        <v>3</v>
+      </c>
+      <c r="L5">
+        <v>2</v>
+      </c>
+      <c r="M5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C6">
+        <v>14</v>
+      </c>
+      <c r="D6">
+        <v>12</v>
+      </c>
+      <c r="E6">
+        <v>10</v>
+      </c>
+      <c r="F6">
+        <v>11</v>
+      </c>
+      <c r="G6">
+        <v>11</v>
+      </c>
+      <c r="H6">
+        <v>17</v>
+      </c>
+      <c r="I6">
+        <v>20</v>
+      </c>
+      <c r="J6">
+        <v>3</v>
+      </c>
+      <c r="K6">
+        <v>10</v>
+      </c>
+      <c r="L6">
+        <v>5</v>
+      </c>
+      <c r="M6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7">
+        <v>58</v>
+      </c>
+      <c r="C7">
+        <v>53</v>
+      </c>
+      <c r="D7">
+        <v>43</v>
+      </c>
+      <c r="E7">
+        <v>56</v>
+      </c>
+      <c r="F7">
+        <v>53</v>
+      </c>
+      <c r="G7">
+        <v>33</v>
+      </c>
+      <c r="H7">
+        <v>23</v>
+      </c>
+      <c r="I7">
+        <v>26</v>
+      </c>
+      <c r="J7">
+        <v>27</v>
+      </c>
+      <c r="K7">
+        <v>17</v>
+      </c>
+      <c r="L7">
+        <v>19</v>
+      </c>
+      <c r="M7">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13">
+      <c r="A8" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B8">
+        <v>60</v>
+      </c>
+      <c r="C8">
+        <v>76</v>
+      </c>
+      <c r="D8">
+        <v>57</v>
+      </c>
+      <c r="E8">
+        <v>74</v>
+      </c>
+      <c r="F8">
+        <v>71</v>
+      </c>
+      <c r="G8">
+        <v>52</v>
+      </c>
+      <c r="H8">
+        <v>51</v>
+      </c>
+      <c r="I8">
+        <v>52</v>
+      </c>
+      <c r="J8">
+        <v>43</v>
+      </c>
+      <c r="K8">
+        <v>41</v>
+      </c>
+      <c r="L8">
+        <v>39</v>
+      </c>
+      <c r="M8">
+        <v>25</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -8423,7 +8750,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:D4"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -8486,7 +8813,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M9"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -8753,330 +9080,6 @@
       </c>
       <c r="M9">
         <v>7</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M10"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" customWidth="1"/>
-    <col min="13" max="13" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="M1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2">
-        <v>5</v>
-      </c>
-      <c r="C2">
-        <v>3</v>
-      </c>
-      <c r="D2">
-        <v>7</v>
-      </c>
-      <c r="E2">
-        <v>5</v>
-      </c>
-      <c r="F2">
-        <v>5</v>
-      </c>
-      <c r="G2">
-        <v>4</v>
-      </c>
-      <c r="H2">
-        <v>6</v>
-      </c>
-      <c r="I2">
-        <v>4</v>
-      </c>
-      <c r="J2">
-        <v>7</v>
-      </c>
-      <c r="K2">
-        <v>7</v>
-      </c>
-      <c r="L2">
-        <v>5</v>
-      </c>
-      <c r="M2">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3">
-        <v>3</v>
-      </c>
-      <c r="C3">
-        <v>2</v>
-      </c>
-      <c r="D3">
-        <v>8</v>
-      </c>
-      <c r="E3">
-        <v>9</v>
-      </c>
-      <c r="F3">
-        <v>19</v>
-      </c>
-      <c r="G3">
-        <v>9</v>
-      </c>
-      <c r="H3">
-        <v>8</v>
-      </c>
-      <c r="I3">
-        <v>13</v>
-      </c>
-      <c r="J3">
-        <v>12</v>
-      </c>
-      <c r="K3">
-        <v>17</v>
-      </c>
-      <c r="L3">
-        <v>13</v>
-      </c>
-      <c r="M3">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="I4">
-        <v>1</v>
-      </c>
-      <c r="M4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="K5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="E6">
-        <v>1</v>
-      </c>
-      <c r="F6">
-        <v>2</v>
-      </c>
-      <c r="J6">
-        <v>2</v>
-      </c>
-      <c r="M6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
-      <c r="A7" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E7">
-        <v>1</v>
-      </c>
-      <c r="I7">
-        <v>1</v>
-      </c>
-      <c r="K7">
-        <v>1</v>
-      </c>
-      <c r="L7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13">
-      <c r="A8" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B8">
-        <v>24</v>
-      </c>
-      <c r="C8">
-        <v>37</v>
-      </c>
-      <c r="D8">
-        <v>21</v>
-      </c>
-      <c r="E8">
-        <v>22</v>
-      </c>
-      <c r="F8">
-        <v>27</v>
-      </c>
-      <c r="G8">
-        <v>15</v>
-      </c>
-      <c r="H8">
-        <v>25</v>
-      </c>
-      <c r="I8">
-        <v>21</v>
-      </c>
-      <c r="J8">
-        <v>26</v>
-      </c>
-      <c r="K8">
-        <v>49</v>
-      </c>
-      <c r="L8">
-        <v>44</v>
-      </c>
-      <c r="M8">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13">
-      <c r="A9" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B9">
-        <v>45</v>
-      </c>
-      <c r="C9">
-        <v>64</v>
-      </c>
-      <c r="D9">
-        <v>46</v>
-      </c>
-      <c r="E9">
-        <v>50</v>
-      </c>
-      <c r="F9">
-        <v>38</v>
-      </c>
-      <c r="G9">
-        <v>19</v>
-      </c>
-      <c r="H9">
-        <v>27</v>
-      </c>
-      <c r="I9">
-        <v>37</v>
-      </c>
-      <c r="J9">
-        <v>20</v>
-      </c>
-      <c r="K9">
-        <v>35</v>
-      </c>
-      <c r="L9">
-        <v>35</v>
-      </c>
-      <c r="M9">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13">
-      <c r="A10" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B10">
-        <v>77</v>
-      </c>
-      <c r="C10">
-        <v>106</v>
-      </c>
-      <c r="D10">
-        <v>82</v>
-      </c>
-      <c r="E10">
-        <v>88</v>
-      </c>
-      <c r="F10">
-        <v>91</v>
-      </c>
-      <c r="G10">
-        <v>47</v>
-      </c>
-      <c r="H10">
-        <v>66</v>
-      </c>
-      <c r="I10">
-        <v>77</v>
-      </c>
-      <c r="J10">
-        <v>67</v>
-      </c>
-      <c r="K10">
-        <v>110</v>
-      </c>
-      <c r="L10">
-        <v>98</v>
-      </c>
-      <c r="M10">
-        <v>36</v>
       </c>
     </row>
   </sheetData>
@@ -9280,7 +9283,7 @@
         <v>5</v>
       </c>
       <c r="M7">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -9362,7 +9365,7 @@
         <v>26</v>
       </c>
       <c r="M9">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
   </sheetData>
@@ -11325,6 +11328,9 @@
       <c r="K4">
         <v>2</v>
       </c>
+      <c r="M4">
+        <v>1</v>
+      </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
@@ -11405,7 +11411,7 @@
         <v>4</v>
       </c>
       <c r="M6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -14156,7 +14162,7 @@
         <v>5</v>
       </c>
       <c r="M3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -14290,7 +14296,7 @@
         <v>6</v>
       </c>
       <c r="M7">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -14580,6 +14586,257 @@
 
 <file path=xl/worksheets/sheet44.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:M8"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+    <col min="13" max="13" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="M1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>2</v>
+      </c>
+      <c r="F2">
+        <v>2</v>
+      </c>
+      <c r="I2">
+        <v>3</v>
+      </c>
+      <c r="J2">
+        <v>2</v>
+      </c>
+      <c r="K2">
+        <v>1</v>
+      </c>
+      <c r="L2">
+        <v>5</v>
+      </c>
+      <c r="M2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
+      <c r="E3">
+        <v>1</v>
+      </c>
+      <c r="H3">
+        <v>2</v>
+      </c>
+      <c r="I3">
+        <v>1</v>
+      </c>
+      <c r="J3">
+        <v>1</v>
+      </c>
+      <c r="K3">
+        <v>2</v>
+      </c>
+      <c r="L3">
+        <v>2</v>
+      </c>
+      <c r="M3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
+      <c r="I4">
+        <v>1</v>
+      </c>
+      <c r="K4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="L5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6">
+        <v>1</v>
+      </c>
+      <c r="F6">
+        <v>4</v>
+      </c>
+      <c r="H6">
+        <v>1</v>
+      </c>
+      <c r="I6">
+        <v>2</v>
+      </c>
+      <c r="K6">
+        <v>1</v>
+      </c>
+      <c r="M6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7">
+        <v>10</v>
+      </c>
+      <c r="C7">
+        <v>20</v>
+      </c>
+      <c r="D7">
+        <v>25</v>
+      </c>
+      <c r="E7">
+        <v>30</v>
+      </c>
+      <c r="F7">
+        <v>41</v>
+      </c>
+      <c r="G7">
+        <v>10</v>
+      </c>
+      <c r="H7">
+        <v>5</v>
+      </c>
+      <c r="I7">
+        <v>5</v>
+      </c>
+      <c r="J7">
+        <v>15</v>
+      </c>
+      <c r="K7">
+        <v>17</v>
+      </c>
+      <c r="L7">
+        <v>12</v>
+      </c>
+      <c r="M7">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13">
+      <c r="A8" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B8">
+        <v>12</v>
+      </c>
+      <c r="C8">
+        <v>22</v>
+      </c>
+      <c r="D8">
+        <v>27</v>
+      </c>
+      <c r="E8">
+        <v>31</v>
+      </c>
+      <c r="F8">
+        <v>47</v>
+      </c>
+      <c r="G8">
+        <v>10</v>
+      </c>
+      <c r="H8">
+        <v>8</v>
+      </c>
+      <c r="I8">
+        <v>12</v>
+      </c>
+      <c r="J8">
+        <v>18</v>
+      </c>
+      <c r="K8">
+        <v>22</v>
+      </c>
+      <c r="L8">
+        <v>21</v>
+      </c>
+      <c r="M8">
+        <v>16</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet45.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -14857,7 +15114,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet45.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet46.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -15073,257 +15330,6 @@
       </c>
       <c r="M6">
         <v>3</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet46.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M8"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" customWidth="1"/>
-    <col min="13" max="13" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="M1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2">
-        <v>1</v>
-      </c>
-      <c r="D2">
-        <v>2</v>
-      </c>
-      <c r="F2">
-        <v>2</v>
-      </c>
-      <c r="I2">
-        <v>3</v>
-      </c>
-      <c r="J2">
-        <v>2</v>
-      </c>
-      <c r="K2">
-        <v>1</v>
-      </c>
-      <c r="L2">
-        <v>5</v>
-      </c>
-      <c r="M2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C3">
-        <v>1</v>
-      </c>
-      <c r="E3">
-        <v>1</v>
-      </c>
-      <c r="H3">
-        <v>2</v>
-      </c>
-      <c r="I3">
-        <v>1</v>
-      </c>
-      <c r="J3">
-        <v>1</v>
-      </c>
-      <c r="K3">
-        <v>2</v>
-      </c>
-      <c r="L3">
-        <v>2</v>
-      </c>
-      <c r="M3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C4">
-        <v>1</v>
-      </c>
-      <c r="I4">
-        <v>1</v>
-      </c>
-      <c r="K4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="L5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B6">
-        <v>1</v>
-      </c>
-      <c r="F6">
-        <v>4</v>
-      </c>
-      <c r="H6">
-        <v>1</v>
-      </c>
-      <c r="I6">
-        <v>2</v>
-      </c>
-      <c r="K6">
-        <v>1</v>
-      </c>
-      <c r="M6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
-      <c r="A7" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B7">
-        <v>10</v>
-      </c>
-      <c r="C7">
-        <v>20</v>
-      </c>
-      <c r="D7">
-        <v>25</v>
-      </c>
-      <c r="E7">
-        <v>30</v>
-      </c>
-      <c r="F7">
-        <v>41</v>
-      </c>
-      <c r="G7">
-        <v>10</v>
-      </c>
-      <c r="H7">
-        <v>5</v>
-      </c>
-      <c r="I7">
-        <v>5</v>
-      </c>
-      <c r="J7">
-        <v>15</v>
-      </c>
-      <c r="K7">
-        <v>17</v>
-      </c>
-      <c r="L7">
-        <v>12</v>
-      </c>
-      <c r="M7">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13">
-      <c r="A8" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B8">
-        <v>12</v>
-      </c>
-      <c r="C8">
-        <v>22</v>
-      </c>
-      <c r="D8">
-        <v>27</v>
-      </c>
-      <c r="E8">
-        <v>31</v>
-      </c>
-      <c r="F8">
-        <v>47</v>
-      </c>
-      <c r="G8">
-        <v>10</v>
-      </c>
-      <c r="H8">
-        <v>8</v>
-      </c>
-      <c r="I8">
-        <v>12</v>
-      </c>
-      <c r="J8">
-        <v>18</v>
-      </c>
-      <c r="K8">
-        <v>22</v>
-      </c>
-      <c r="L8">
-        <v>21</v>
-      </c>
-      <c r="M8">
-        <v>16</v>
       </c>
     </row>
   </sheetData>
@@ -19262,7 +19268,7 @@
         <v>1</v>
       </c>
       <c r="M3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -19375,7 +19381,7 @@
         <v>2</v>
       </c>
       <c r="M7">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/output/cta-index-crime-full-year.xlsx
+++ b/output/cta-index-crime-full-year.xlsx
@@ -19,18 +19,18 @@
     <sheet name="Rogers Park" sheetId="10" r:id="rId10"/>
     <sheet name="Douglas" sheetId="11" r:id="rId11"/>
     <sheet name="Jefferson Park" sheetId="12" r:id="rId12"/>
-    <sheet name="Grand Crossing" sheetId="13" r:id="rId13"/>
-    <sheet name="Chatham" sheetId="14" r:id="rId14"/>
-    <sheet name="Austin" sheetId="15" r:id="rId15"/>
-    <sheet name="Albany Park" sheetId="16" r:id="rId16"/>
-    <sheet name="Grand Boulevard" sheetId="17" r:id="rId17"/>
-    <sheet name="Belmont Cragin" sheetId="18" r:id="rId18"/>
-    <sheet name="West Ridge" sheetId="19" r:id="rId19"/>
-    <sheet name="Loop" sheetId="20" r:id="rId20"/>
-    <sheet name="Lake View" sheetId="21" r:id="rId21"/>
-    <sheet name="South Shore" sheetId="22" r:id="rId22"/>
-    <sheet name="Mount Greenwood" sheetId="23" r:id="rId23"/>
-    <sheet name="Gage Park" sheetId="24" r:id="rId24"/>
+    <sheet name="Chatham" sheetId="13" r:id="rId13"/>
+    <sheet name="Albany Park" sheetId="14" r:id="rId14"/>
+    <sheet name="Grand Boulevard" sheetId="15" r:id="rId15"/>
+    <sheet name="Belmont Cragin" sheetId="16" r:id="rId16"/>
+    <sheet name="West Ridge" sheetId="17" r:id="rId17"/>
+    <sheet name="Loop" sheetId="18" r:id="rId18"/>
+    <sheet name="Lake View" sheetId="19" r:id="rId19"/>
+    <sheet name="Austin" sheetId="20" r:id="rId20"/>
+    <sheet name="South Shore" sheetId="21" r:id="rId21"/>
+    <sheet name="Mount Greenwood" sheetId="22" r:id="rId22"/>
+    <sheet name="Gage Park" sheetId="23" r:id="rId23"/>
+    <sheet name="Grand Crossing" sheetId="24" r:id="rId24"/>
     <sheet name="West Loop" sheetId="25" r:id="rId25"/>
     <sheet name="Rush &amp; Division" sheetId="26" r:id="rId26"/>
     <sheet name="North Lawndale" sheetId="27" r:id="rId27"/>
@@ -50,9 +50,9 @@
     <sheet name="Roseland" sheetId="41" r:id="rId41"/>
     <sheet name="Woodlawn" sheetId="42" r:id="rId42"/>
     <sheet name="Fuller Park" sheetId="43" r:id="rId43"/>
-    <sheet name="O'Hare" sheetId="44" r:id="rId44"/>
-    <sheet name="Little Italy, UIC" sheetId="45" r:id="rId45"/>
-    <sheet name="Hyde Park" sheetId="46" r:id="rId46"/>
+    <sheet name="Little Italy, UIC" sheetId="44" r:id="rId44"/>
+    <sheet name="Hyde Park" sheetId="45" r:id="rId45"/>
+    <sheet name="O'Hare" sheetId="46" r:id="rId46"/>
     <sheet name="Bucktown" sheetId="47" r:id="rId47"/>
     <sheet name="Calumet Heights" sheetId="48" r:id="rId48"/>
     <sheet name="Edgewater" sheetId="49" r:id="rId49"/>
@@ -2146,41 +2146,38 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2">
-        <v>5</v>
-      </c>
       <c r="C2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D2">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H2">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J2">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K2">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M2">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -2188,56 +2185,56 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D3">
+        <v>7</v>
+      </c>
+      <c r="E3">
+        <v>3</v>
+      </c>
+      <c r="F3">
+        <v>4</v>
+      </c>
+      <c r="G3">
         <v>8</v>
       </c>
-      <c r="E3">
-        <v>9</v>
-      </c>
-      <c r="F3">
-        <v>19</v>
-      </c>
-      <c r="G3">
-        <v>9</v>
-      </c>
       <c r="H3">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="I3">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="J3">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="K3">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="L3">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="M3">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="I4">
-        <v>1</v>
-      </c>
-      <c r="M4">
+      <c r="H4">
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="B5">
+        <v>1</v>
       </c>
       <c r="K5">
         <v>1</v>
@@ -2245,36 +2242,30 @@
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="E6">
-        <v>1</v>
-      </c>
-      <c r="F6">
-        <v>2</v>
-      </c>
-      <c r="J6">
-        <v>2</v>
-      </c>
-      <c r="M6">
+        <v>6</v>
+      </c>
+      <c r="G6">
+        <v>1</v>
+      </c>
+      <c r="H6">
+        <v>1</v>
+      </c>
+      <c r="I6">
         <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="D7">
+        <v>1</v>
       </c>
       <c r="E7">
         <v>1</v>
       </c>
-      <c r="I7">
-        <v>1</v>
-      </c>
-      <c r="K7">
-        <v>1</v>
-      </c>
-      <c r="L7">
-        <v>1</v>
+      <c r="J7">
+        <v>2</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -2282,40 +2273,40 @@
         <v>8</v>
       </c>
       <c r="B8">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="C8">
-        <v>37</v>
+        <v>9</v>
       </c>
       <c r="D8">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="E8">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="F8">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="G8">
         <v>15</v>
       </c>
       <c r="H8">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="I8">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="J8">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="K8">
-        <v>49</v>
+        <v>18</v>
       </c>
       <c r="L8">
-        <v>44</v>
+        <v>19</v>
       </c>
       <c r="M8">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -2323,40 +2314,40 @@
         <v>9</v>
       </c>
       <c r="B9">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C9">
-        <v>64</v>
+        <v>46</v>
       </c>
       <c r="D9">
-        <v>46</v>
+        <v>32</v>
       </c>
       <c r="E9">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="F9">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="G9">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="H9">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="I9">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="J9">
         <v>20</v>
       </c>
       <c r="K9">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="L9">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="M9">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -2364,40 +2355,40 @@
         <v>10</v>
       </c>
       <c r="B10">
-        <v>77</v>
+        <v>51</v>
       </c>
       <c r="C10">
-        <v>106</v>
+        <v>57</v>
       </c>
       <c r="D10">
-        <v>82</v>
+        <v>62</v>
       </c>
       <c r="E10">
-        <v>88</v>
+        <v>48</v>
       </c>
       <c r="F10">
-        <v>91</v>
+        <v>60</v>
       </c>
       <c r="G10">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="H10">
-        <v>66</v>
+        <v>31</v>
       </c>
       <c r="I10">
-        <v>77</v>
+        <v>44</v>
       </c>
       <c r="J10">
-        <v>67</v>
+        <v>43</v>
       </c>
       <c r="K10">
-        <v>110</v>
+        <v>57</v>
       </c>
       <c r="L10">
-        <v>98</v>
+        <v>40</v>
       </c>
       <c r="M10">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
   </sheetData>
@@ -2407,7 +2398,7 @@
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M10"/>
+  <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="23.7109375" customWidth="1"/>
@@ -2470,38 +2461,29 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C2">
-        <v>1</v>
-      </c>
       <c r="D2">
-        <v>5</v>
-      </c>
-      <c r="E2">
         <v>1</v>
       </c>
       <c r="F2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G2">
         <v>1</v>
       </c>
-      <c r="H2">
-        <v>3</v>
-      </c>
       <c r="I2">
         <v>2</v>
       </c>
       <c r="J2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K2">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="L2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M2">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -2509,210 +2491,153 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C3">
         <v>1</v>
       </c>
-      <c r="D3">
-        <v>7</v>
-      </c>
-      <c r="E3">
-        <v>3</v>
-      </c>
-      <c r="F3">
-        <v>4</v>
-      </c>
       <c r="G3">
-        <v>8</v>
-      </c>
-      <c r="H3">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I3">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="J3">
-        <v>4</v>
-      </c>
-      <c r="K3">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="L3">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="M3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="H4">
+        <v>5</v>
+      </c>
+      <c r="E4">
+        <v>2</v>
+      </c>
+      <c r="J4">
+        <v>1</v>
+      </c>
+      <c r="K4">
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B5">
         <v>1</v>
       </c>
+      <c r="C5">
+        <v>1</v>
+      </c>
+      <c r="D5">
+        <v>2</v>
+      </c>
+      <c r="E5">
+        <v>2</v>
+      </c>
+      <c r="G5">
+        <v>1</v>
+      </c>
+      <c r="I5">
+        <v>1</v>
+      </c>
+      <c r="J5">
+        <v>3</v>
+      </c>
       <c r="K5">
+        <v>4</v>
+      </c>
+      <c r="M5">
         <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
-        <v>6</v>
+        <v>9</v>
+      </c>
+      <c r="B6">
+        <v>8</v>
+      </c>
+      <c r="C6">
+        <v>13</v>
+      </c>
+      <c r="D6">
+        <v>10</v>
+      </c>
+      <c r="E6">
+        <v>9</v>
+      </c>
+      <c r="F6">
+        <v>9</v>
       </c>
       <c r="G6">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="H6">
         <v>1</v>
       </c>
       <c r="I6">
-        <v>1</v>
+        <v>4</v>
+      </c>
+      <c r="J6">
+        <v>5</v>
+      </c>
+      <c r="K6">
+        <v>8</v>
+      </c>
+      <c r="L6">
+        <v>3</v>
+      </c>
+      <c r="M6">
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="1" t="s">
-        <v>7</v>
+        <v>10</v>
+      </c>
+      <c r="B7">
+        <v>10</v>
+      </c>
+      <c r="C7">
+        <v>15</v>
       </c>
       <c r="D7">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="E7">
-        <v>1</v>
+        <v>13</v>
+      </c>
+      <c r="F7">
+        <v>10</v>
+      </c>
+      <c r="G7">
+        <v>12</v>
+      </c>
+      <c r="H7">
+        <v>1</v>
+      </c>
+      <c r="I7">
+        <v>8</v>
       </c>
       <c r="J7">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13">
-      <c r="A8" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B8">
-        <v>5</v>
-      </c>
-      <c r="C8">
-        <v>9</v>
-      </c>
-      <c r="D8">
-        <v>17</v>
-      </c>
-      <c r="E8">
-        <v>13</v>
-      </c>
-      <c r="F8">
-        <v>19</v>
-      </c>
-      <c r="G8">
+        <v>14</v>
+      </c>
+      <c r="K7">
         <v>15</v>
       </c>
-      <c r="H8">
-        <v>5</v>
-      </c>
-      <c r="I8">
-        <v>15</v>
-      </c>
-      <c r="J8">
-        <v>12</v>
-      </c>
-      <c r="K8">
-        <v>18</v>
-      </c>
-      <c r="L8">
-        <v>19</v>
-      </c>
-      <c r="M8">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13">
-      <c r="A9" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B9">
-        <v>43</v>
-      </c>
-      <c r="C9">
-        <v>46</v>
-      </c>
-      <c r="D9">
-        <v>32</v>
-      </c>
-      <c r="E9">
-        <v>30</v>
-      </c>
-      <c r="F9">
-        <v>34</v>
-      </c>
-      <c r="G9">
-        <v>15</v>
-      </c>
-      <c r="H9">
-        <v>17</v>
-      </c>
-      <c r="I9">
-        <v>20</v>
-      </c>
-      <c r="J9">
-        <v>20</v>
-      </c>
-      <c r="K9">
-        <v>20</v>
-      </c>
-      <c r="L9">
-        <v>13</v>
-      </c>
-      <c r="M9">
+      <c r="L7">
         <v>6</v>
       </c>
-    </row>
-    <row r="10" spans="1:13">
-      <c r="A10" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B10">
-        <v>51</v>
-      </c>
-      <c r="C10">
-        <v>57</v>
-      </c>
-      <c r="D10">
-        <v>62</v>
-      </c>
-      <c r="E10">
-        <v>48</v>
-      </c>
-      <c r="F10">
-        <v>60</v>
-      </c>
-      <c r="G10">
-        <v>40</v>
-      </c>
-      <c r="H10">
-        <v>31</v>
-      </c>
-      <c r="I10">
-        <v>44</v>
-      </c>
-      <c r="J10">
-        <v>43</v>
-      </c>
-      <c r="K10">
-        <v>57</v>
-      </c>
-      <c r="L10">
-        <v>40</v>
-      </c>
-      <c r="M10">
-        <v>17</v>
+      <c r="M7">
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -2722,10 +2647,10 @@
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M10"/>
+  <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="1" max="1" width="18.7109375" customWidth="1"/>
     <col min="2" max="2" width="4.7109375" customWidth="1"/>
     <col min="3" max="3" width="4.7109375" customWidth="1"/>
     <col min="4" max="4" width="4.7109375" customWidth="1"/>
@@ -2785,41 +2710,29 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2">
-        <v>4</v>
-      </c>
       <c r="C2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E2">
-        <v>5</v>
-      </c>
-      <c r="F2">
-        <v>9</v>
-      </c>
-      <c r="G2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H2">
-        <v>5</v>
-      </c>
-      <c r="I2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J2">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="K2">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="L2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="M2">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -2827,210 +2740,162 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C3">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D3">
-        <v>6</v>
-      </c>
-      <c r="E3">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="F3">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G3">
-        <v>7</v>
-      </c>
-      <c r="H3">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="I3">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J3">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="K3">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="L3">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="M3">
-        <v>10</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="I4">
+        <v>6</v>
+      </c>
+      <c r="H4">
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B5">
-        <v>1</v>
+        <v>7</v>
+      </c>
+      <c r="C5">
+        <v>11</v>
       </c>
       <c r="D5">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E5">
-        <v>1</v>
+        <v>5</v>
+      </c>
+      <c r="F5">
+        <v>5</v>
+      </c>
+      <c r="G5">
+        <v>6</v>
+      </c>
+      <c r="H5">
+        <v>2</v>
+      </c>
+      <c r="I5">
+        <v>2</v>
       </c>
       <c r="J5">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K5">
-        <v>2</v>
-      </c>
-      <c r="M5">
-        <v>1</v>
+        <v>6</v>
+      </c>
+      <c r="L5">
+        <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6">
+        <v>15</v>
+      </c>
+      <c r="C6">
+        <v>16</v>
+      </c>
+      <c r="D6">
+        <v>15</v>
+      </c>
+      <c r="E6">
+        <v>16</v>
+      </c>
+      <c r="F6">
+        <v>11</v>
+      </c>
+      <c r="G6">
+        <v>9</v>
+      </c>
+      <c r="H6">
+        <v>5</v>
+      </c>
+      <c r="I6">
+        <v>5</v>
+      </c>
+      <c r="J6">
+        <v>12</v>
+      </c>
+      <c r="K6">
         <v>6</v>
       </c>
-      <c r="K6">
-        <v>1</v>
+      <c r="L6">
+        <v>4</v>
+      </c>
+      <c r="M6">
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="1" t="s">
-        <v>7</v>
+        <v>10</v>
+      </c>
+      <c r="B7">
+        <v>24</v>
+      </c>
+      <c r="C7">
+        <v>29</v>
+      </c>
+      <c r="D7">
+        <v>25</v>
+      </c>
+      <c r="E7">
+        <v>22</v>
+      </c>
+      <c r="F7">
+        <v>19</v>
+      </c>
+      <c r="G7">
+        <v>16</v>
+      </c>
+      <c r="H7">
+        <v>10</v>
+      </c>
+      <c r="I7">
+        <v>11</v>
+      </c>
+      <c r="J7">
+        <v>20</v>
+      </c>
+      <c r="K7">
+        <v>15</v>
       </c>
       <c r="L7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13">
-      <c r="A8" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B8">
-        <v>23</v>
-      </c>
-      <c r="C8">
-        <v>31</v>
-      </c>
-      <c r="D8">
-        <v>22</v>
-      </c>
-      <c r="E8">
-        <v>44</v>
-      </c>
-      <c r="F8">
-        <v>38</v>
-      </c>
-      <c r="G8">
-        <v>24</v>
-      </c>
-      <c r="H8">
-        <v>50</v>
-      </c>
-      <c r="I8">
-        <v>34</v>
-      </c>
-      <c r="J8">
-        <v>26</v>
-      </c>
-      <c r="K8">
-        <v>24</v>
-      </c>
-      <c r="L8">
-        <v>14</v>
-      </c>
-      <c r="M8">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13">
-      <c r="A9" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B9">
-        <v>46</v>
-      </c>
-      <c r="C9">
-        <v>59</v>
-      </c>
-      <c r="D9">
-        <v>33</v>
-      </c>
-      <c r="E9">
-        <v>73</v>
-      </c>
-      <c r="F9">
-        <v>114</v>
-      </c>
-      <c r="G9">
-        <v>58</v>
-      </c>
-      <c r="H9">
-        <v>41</v>
-      </c>
-      <c r="I9">
-        <v>44</v>
-      </c>
-      <c r="J9">
-        <v>20</v>
-      </c>
-      <c r="K9">
-        <v>25</v>
-      </c>
-      <c r="L9">
-        <v>27</v>
-      </c>
-      <c r="M9">
         <v>16</v>
       </c>
-    </row>
-    <row r="10" spans="1:13">
-      <c r="A10" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B10">
-        <v>78</v>
-      </c>
-      <c r="C10">
-        <v>99</v>
-      </c>
-      <c r="D10">
-        <v>65</v>
-      </c>
-      <c r="E10">
-        <v>130</v>
-      </c>
-      <c r="F10">
-        <v>167</v>
-      </c>
-      <c r="G10">
-        <v>92</v>
-      </c>
-      <c r="H10">
-        <v>104</v>
-      </c>
-      <c r="I10">
-        <v>89</v>
-      </c>
-      <c r="J10">
-        <v>67</v>
-      </c>
-      <c r="K10">
-        <v>71</v>
-      </c>
-      <c r="L10">
-        <v>61</v>
-      </c>
-      <c r="M10">
-        <v>50</v>
+      <c r="M7">
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -3106,23 +2971,8 @@
       <c r="D2">
         <v>1</v>
       </c>
-      <c r="F2">
-        <v>1</v>
-      </c>
-      <c r="G2">
-        <v>1</v>
-      </c>
-      <c r="I2">
-        <v>2</v>
-      </c>
       <c r="J2">
-        <v>4</v>
-      </c>
-      <c r="K2">
-        <v>2</v>
-      </c>
-      <c r="L2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M2">
         <v>1</v>
@@ -3132,25 +2982,16 @@
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B3">
-        <v>1</v>
-      </c>
-      <c r="C3">
-        <v>1</v>
+      <c r="E3">
+        <v>2</v>
       </c>
       <c r="G3">
-        <v>2</v>
-      </c>
-      <c r="I3">
         <v>1</v>
       </c>
       <c r="J3">
         <v>1</v>
       </c>
       <c r="L3">
-        <v>1</v>
-      </c>
-      <c r="M3">
         <v>1</v>
       </c>
     </row>
@@ -3158,13 +2999,7 @@
       <c r="A4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="E4">
-        <v>2</v>
-      </c>
-      <c r="J4">
-        <v>1</v>
-      </c>
-      <c r="K4">
+      <c r="C4">
         <v>1</v>
       </c>
     </row>
@@ -3173,28 +3008,22 @@
         <v>8</v>
       </c>
       <c r="B5">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C5">
-        <v>1</v>
-      </c>
-      <c r="D5">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E5">
-        <v>2</v>
-      </c>
-      <c r="G5">
-        <v>1</v>
-      </c>
-      <c r="I5">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="H5">
+        <v>2</v>
       </c>
       <c r="J5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M5">
         <v>1</v>
@@ -3205,40 +3034,40 @@
         <v>9</v>
       </c>
       <c r="B6">
+        <v>6</v>
+      </c>
+      <c r="C6">
+        <v>2</v>
+      </c>
+      <c r="D6">
+        <v>6</v>
+      </c>
+      <c r="E6">
         <v>8</v>
       </c>
-      <c r="C6">
-        <v>13</v>
-      </c>
-      <c r="D6">
-        <v>10</v>
-      </c>
-      <c r="E6">
-        <v>9</v>
-      </c>
       <c r="F6">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G6">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="H6">
         <v>1</v>
       </c>
       <c r="I6">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J6">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K6">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="L6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -3246,40 +3075,40 @@
         <v>10</v>
       </c>
       <c r="B7">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C7">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="D7">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="E7">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F7">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G7">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="H7">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I7">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="J7">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="K7">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="L7">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="M7">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -3288,477 +3117,6 @@
 </file>
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M7"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="18.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" customWidth="1"/>
-    <col min="13" max="13" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="M1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2">
-        <v>1</v>
-      </c>
-      <c r="D2">
-        <v>1</v>
-      </c>
-      <c r="E2">
-        <v>1</v>
-      </c>
-      <c r="H2">
-        <v>2</v>
-      </c>
-      <c r="J2">
-        <v>1</v>
-      </c>
-      <c r="K2">
-        <v>2</v>
-      </c>
-      <c r="L2">
-        <v>2</v>
-      </c>
-      <c r="M2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3">
-        <v>2</v>
-      </c>
-      <c r="C3">
-        <v>1</v>
-      </c>
-      <c r="D3">
-        <v>1</v>
-      </c>
-      <c r="F3">
-        <v>3</v>
-      </c>
-      <c r="G3">
-        <v>1</v>
-      </c>
-      <c r="I3">
-        <v>4</v>
-      </c>
-      <c r="J3">
-        <v>2</v>
-      </c>
-      <c r="K3">
-        <v>1</v>
-      </c>
-      <c r="L3">
-        <v>4</v>
-      </c>
-      <c r="M3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5">
-        <v>7</v>
-      </c>
-      <c r="C5">
-        <v>11</v>
-      </c>
-      <c r="D5">
-        <v>8</v>
-      </c>
-      <c r="E5">
-        <v>5</v>
-      </c>
-      <c r="F5">
-        <v>5</v>
-      </c>
-      <c r="G5">
-        <v>6</v>
-      </c>
-      <c r="H5">
-        <v>2</v>
-      </c>
-      <c r="I5">
-        <v>2</v>
-      </c>
-      <c r="J5">
-        <v>5</v>
-      </c>
-      <c r="K5">
-        <v>6</v>
-      </c>
-      <c r="L5">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B6">
-        <v>15</v>
-      </c>
-      <c r="C6">
-        <v>16</v>
-      </c>
-      <c r="D6">
-        <v>15</v>
-      </c>
-      <c r="E6">
-        <v>16</v>
-      </c>
-      <c r="F6">
-        <v>11</v>
-      </c>
-      <c r="G6">
-        <v>9</v>
-      </c>
-      <c r="H6">
-        <v>5</v>
-      </c>
-      <c r="I6">
-        <v>5</v>
-      </c>
-      <c r="J6">
-        <v>12</v>
-      </c>
-      <c r="K6">
-        <v>6</v>
-      </c>
-      <c r="L6">
-        <v>4</v>
-      </c>
-      <c r="M6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
-      <c r="A7" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B7">
-        <v>24</v>
-      </c>
-      <c r="C7">
-        <v>29</v>
-      </c>
-      <c r="D7">
-        <v>25</v>
-      </c>
-      <c r="E7">
-        <v>22</v>
-      </c>
-      <c r="F7">
-        <v>19</v>
-      </c>
-      <c r="G7">
-        <v>16</v>
-      </c>
-      <c r="H7">
-        <v>10</v>
-      </c>
-      <c r="I7">
-        <v>11</v>
-      </c>
-      <c r="J7">
-        <v>20</v>
-      </c>
-      <c r="K7">
-        <v>15</v>
-      </c>
-      <c r="L7">
-        <v>16</v>
-      </c>
-      <c r="M7">
-        <v>6</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M7"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" customWidth="1"/>
-    <col min="13" max="13" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="M1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D2">
-        <v>1</v>
-      </c>
-      <c r="J2">
-        <v>1</v>
-      </c>
-      <c r="M2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="E3">
-        <v>2</v>
-      </c>
-      <c r="G3">
-        <v>1</v>
-      </c>
-      <c r="J3">
-        <v>1</v>
-      </c>
-      <c r="L3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5">
-        <v>5</v>
-      </c>
-      <c r="C5">
-        <v>6</v>
-      </c>
-      <c r="E5">
-        <v>1</v>
-      </c>
-      <c r="H5">
-        <v>2</v>
-      </c>
-      <c r="J5">
-        <v>4</v>
-      </c>
-      <c r="K5">
-        <v>2</v>
-      </c>
-      <c r="M5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B6">
-        <v>6</v>
-      </c>
-      <c r="C6">
-        <v>2</v>
-      </c>
-      <c r="D6">
-        <v>6</v>
-      </c>
-      <c r="E6">
-        <v>8</v>
-      </c>
-      <c r="F6">
-        <v>7</v>
-      </c>
-      <c r="G6">
-        <v>2</v>
-      </c>
-      <c r="H6">
-        <v>1</v>
-      </c>
-      <c r="I6">
-        <v>1</v>
-      </c>
-      <c r="J6">
-        <v>3</v>
-      </c>
-      <c r="K6">
-        <v>1</v>
-      </c>
-      <c r="L6">
-        <v>2</v>
-      </c>
-      <c r="M6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
-      <c r="A7" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B7">
-        <v>11</v>
-      </c>
-      <c r="C7">
-        <v>9</v>
-      </c>
-      <c r="D7">
-        <v>7</v>
-      </c>
-      <c r="E7">
-        <v>11</v>
-      </c>
-      <c r="F7">
-        <v>7</v>
-      </c>
-      <c r="G7">
-        <v>3</v>
-      </c>
-      <c r="H7">
-        <v>3</v>
-      </c>
-      <c r="I7">
-        <v>1</v>
-      </c>
-      <c r="J7">
-        <v>9</v>
-      </c>
-      <c r="K7">
-        <v>3</v>
-      </c>
-      <c r="L7">
-        <v>3</v>
-      </c>
-      <c r="M7">
-        <v>3</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:L8"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -3929,6 +3287,656 @@
       </c>
       <c r="L8">
         <v>2</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:M10"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+    <col min="13" max="13" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="M1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>6</v>
+      </c>
+      <c r="C2">
+        <v>3</v>
+      </c>
+      <c r="D2">
+        <v>12</v>
+      </c>
+      <c r="E2">
+        <v>5</v>
+      </c>
+      <c r="F2">
+        <v>8</v>
+      </c>
+      <c r="G2">
+        <v>4</v>
+      </c>
+      <c r="H2">
+        <v>13</v>
+      </c>
+      <c r="I2">
+        <v>14</v>
+      </c>
+      <c r="J2">
+        <v>22</v>
+      </c>
+      <c r="K2">
+        <v>15</v>
+      </c>
+      <c r="L2">
+        <v>15</v>
+      </c>
+      <c r="M2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>13</v>
+      </c>
+      <c r="C3">
+        <v>13</v>
+      </c>
+      <c r="D3">
+        <v>17</v>
+      </c>
+      <c r="E3">
+        <v>18</v>
+      </c>
+      <c r="F3">
+        <v>14</v>
+      </c>
+      <c r="G3">
+        <v>26</v>
+      </c>
+      <c r="H3">
+        <v>23</v>
+      </c>
+      <c r="I3">
+        <v>32</v>
+      </c>
+      <c r="J3">
+        <v>40</v>
+      </c>
+      <c r="K3">
+        <v>26</v>
+      </c>
+      <c r="L3">
+        <v>34</v>
+      </c>
+      <c r="M3">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G4">
+        <v>1</v>
+      </c>
+      <c r="J4">
+        <v>2</v>
+      </c>
+      <c r="K4">
+        <v>1</v>
+      </c>
+      <c r="L4">
+        <v>1</v>
+      </c>
+      <c r="M4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C5">
+        <v>2</v>
+      </c>
+      <c r="D5">
+        <v>1</v>
+      </c>
+      <c r="E5">
+        <v>2</v>
+      </c>
+      <c r="F5">
+        <v>1</v>
+      </c>
+      <c r="H5">
+        <v>2</v>
+      </c>
+      <c r="I5">
+        <v>4</v>
+      </c>
+      <c r="J5">
+        <v>3</v>
+      </c>
+      <c r="K5">
+        <v>2</v>
+      </c>
+      <c r="L5">
+        <v>5</v>
+      </c>
+      <c r="M5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G6">
+        <v>1</v>
+      </c>
+      <c r="H6">
+        <v>2</v>
+      </c>
+      <c r="J6">
+        <v>2</v>
+      </c>
+      <c r="L6">
+        <v>2</v>
+      </c>
+      <c r="M6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="K7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13">
+      <c r="A8" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8">
+        <v>30</v>
+      </c>
+      <c r="C8">
+        <v>44</v>
+      </c>
+      <c r="D8">
+        <v>49</v>
+      </c>
+      <c r="E8">
+        <v>67</v>
+      </c>
+      <c r="F8">
+        <v>69</v>
+      </c>
+      <c r="G8">
+        <v>57</v>
+      </c>
+      <c r="H8">
+        <v>80</v>
+      </c>
+      <c r="I8">
+        <v>80</v>
+      </c>
+      <c r="J8">
+        <v>64</v>
+      </c>
+      <c r="K8">
+        <v>48</v>
+      </c>
+      <c r="L8">
+        <v>44</v>
+      </c>
+      <c r="M8">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13">
+      <c r="A9" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B9">
+        <v>233</v>
+      </c>
+      <c r="C9">
+        <v>354</v>
+      </c>
+      <c r="D9">
+        <v>538</v>
+      </c>
+      <c r="E9">
+        <v>705</v>
+      </c>
+      <c r="F9">
+        <v>568</v>
+      </c>
+      <c r="G9">
+        <v>168</v>
+      </c>
+      <c r="H9">
+        <v>116</v>
+      </c>
+      <c r="I9">
+        <v>194</v>
+      </c>
+      <c r="J9">
+        <v>122</v>
+      </c>
+      <c r="K9">
+        <v>114</v>
+      </c>
+      <c r="L9">
+        <v>95</v>
+      </c>
+      <c r="M9">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13">
+      <c r="A10" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B10">
+        <v>282</v>
+      </c>
+      <c r="C10">
+        <v>416</v>
+      </c>
+      <c r="D10">
+        <v>617</v>
+      </c>
+      <c r="E10">
+        <v>797</v>
+      </c>
+      <c r="F10">
+        <v>660</v>
+      </c>
+      <c r="G10">
+        <v>257</v>
+      </c>
+      <c r="H10">
+        <v>236</v>
+      </c>
+      <c r="I10">
+        <v>324</v>
+      </c>
+      <c r="J10">
+        <v>255</v>
+      </c>
+      <c r="K10">
+        <v>207</v>
+      </c>
+      <c r="L10">
+        <v>196</v>
+      </c>
+      <c r="M10">
+        <v>89</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:M8"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+    <col min="13" max="13" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="M1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>4</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="E2">
+        <v>4</v>
+      </c>
+      <c r="F2">
+        <v>2</v>
+      </c>
+      <c r="G2">
+        <v>4</v>
+      </c>
+      <c r="H2">
+        <v>2</v>
+      </c>
+      <c r="I2">
+        <v>3</v>
+      </c>
+      <c r="J2">
+        <v>2</v>
+      </c>
+      <c r="K2">
+        <v>6</v>
+      </c>
+      <c r="L2">
+        <v>6</v>
+      </c>
+      <c r="M2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>2</v>
+      </c>
+      <c r="C3">
+        <v>4</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
+      <c r="E3">
+        <v>4</v>
+      </c>
+      <c r="F3">
+        <v>5</v>
+      </c>
+      <c r="G3">
+        <v>4</v>
+      </c>
+      <c r="H3">
+        <v>7</v>
+      </c>
+      <c r="I3">
+        <v>2</v>
+      </c>
+      <c r="J3">
+        <v>11</v>
+      </c>
+      <c r="K3">
+        <v>5</v>
+      </c>
+      <c r="L3">
+        <v>7</v>
+      </c>
+      <c r="M3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="H4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C5">
+        <v>1</v>
+      </c>
+      <c r="H5">
+        <v>1</v>
+      </c>
+      <c r="I5">
+        <v>1</v>
+      </c>
+      <c r="K5">
+        <v>3</v>
+      </c>
+      <c r="L5">
+        <v>2</v>
+      </c>
+      <c r="M5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C6">
+        <v>14</v>
+      </c>
+      <c r="D6">
+        <v>12</v>
+      </c>
+      <c r="E6">
+        <v>10</v>
+      </c>
+      <c r="F6">
+        <v>11</v>
+      </c>
+      <c r="G6">
+        <v>11</v>
+      </c>
+      <c r="H6">
+        <v>17</v>
+      </c>
+      <c r="I6">
+        <v>20</v>
+      </c>
+      <c r="J6">
+        <v>3</v>
+      </c>
+      <c r="K6">
+        <v>10</v>
+      </c>
+      <c r="L6">
+        <v>5</v>
+      </c>
+      <c r="M6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7">
+        <v>58</v>
+      </c>
+      <c r="C7">
+        <v>53</v>
+      </c>
+      <c r="D7">
+        <v>43</v>
+      </c>
+      <c r="E7">
+        <v>56</v>
+      </c>
+      <c r="F7">
+        <v>53</v>
+      </c>
+      <c r="G7">
+        <v>33</v>
+      </c>
+      <c r="H7">
+        <v>23</v>
+      </c>
+      <c r="I7">
+        <v>26</v>
+      </c>
+      <c r="J7">
+        <v>27</v>
+      </c>
+      <c r="K7">
+        <v>17</v>
+      </c>
+      <c r="L7">
+        <v>19</v>
+      </c>
+      <c r="M7">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13">
+      <c r="A8" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B8">
+        <v>60</v>
+      </c>
+      <c r="C8">
+        <v>76</v>
+      </c>
+      <c r="D8">
+        <v>57</v>
+      </c>
+      <c r="E8">
+        <v>74</v>
+      </c>
+      <c r="F8">
+        <v>71</v>
+      </c>
+      <c r="G8">
+        <v>52</v>
+      </c>
+      <c r="H8">
+        <v>51</v>
+      </c>
+      <c r="I8">
+        <v>52</v>
+      </c>
+      <c r="J8">
+        <v>43</v>
+      </c>
+      <c r="K8">
+        <v>41</v>
+      </c>
+      <c r="L8">
+        <v>39</v>
+      </c>
+      <c r="M8">
+        <v>25</v>
       </c>
     </row>
   </sheetData>
@@ -7895,40 +7903,40 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D2">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="E2">
         <v>5</v>
       </c>
       <c r="F2">
+        <v>9</v>
+      </c>
+      <c r="G2">
+        <v>3</v>
+      </c>
+      <c r="H2">
+        <v>5</v>
+      </c>
+      <c r="I2">
+        <v>4</v>
+      </c>
+      <c r="J2">
         <v>8</v>
       </c>
-      <c r="G2">
-        <v>4</v>
-      </c>
-      <c r="H2">
-        <v>13</v>
-      </c>
-      <c r="I2">
-        <v>14</v>
-      </c>
-      <c r="J2">
-        <v>22</v>
-      </c>
       <c r="K2">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="L2">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="M2">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -7936,59 +7944,47 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="C3">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="D3">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="E3">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="F3">
+        <v>6</v>
+      </c>
+      <c r="G3">
+        <v>7</v>
+      </c>
+      <c r="H3">
+        <v>8</v>
+      </c>
+      <c r="I3">
+        <v>6</v>
+      </c>
+      <c r="J3">
+        <v>10</v>
+      </c>
+      <c r="K3">
+        <v>12</v>
+      </c>
+      <c r="L3">
         <v>14</v>
       </c>
-      <c r="G3">
-        <v>26</v>
-      </c>
-      <c r="H3">
-        <v>23</v>
-      </c>
-      <c r="I3">
-        <v>32</v>
-      </c>
-      <c r="J3">
-        <v>40</v>
-      </c>
-      <c r="K3">
-        <v>26</v>
-      </c>
-      <c r="L3">
-        <v>34</v>
-      </c>
       <c r="M3">
-        <v>16</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="G4">
-        <v>1</v>
-      </c>
-      <c r="J4">
-        <v>2</v>
-      </c>
-      <c r="K4">
-        <v>1</v>
-      </c>
-      <c r="L4">
-        <v>1</v>
-      </c>
-      <c r="M4">
+      <c r="I4">
         <v>1</v>
       </c>
     </row>
@@ -7996,23 +7992,14 @@
       <c r="A5" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C5">
-        <v>2</v>
+      <c r="B5">
+        <v>1</v>
       </c>
       <c r="D5">
         <v>1</v>
       </c>
       <c r="E5">
-        <v>2</v>
-      </c>
-      <c r="F5">
-        <v>1</v>
-      </c>
-      <c r="H5">
-        <v>2</v>
-      </c>
-      <c r="I5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J5">
         <v>3</v>
@@ -8020,30 +8007,15 @@
       <c r="K5">
         <v>2</v>
       </c>
-      <c r="L5">
-        <v>5</v>
-      </c>
       <c r="M5">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="G6">
-        <v>1</v>
-      </c>
-      <c r="H6">
-        <v>2</v>
-      </c>
-      <c r="J6">
-        <v>2</v>
-      </c>
-      <c r="L6">
-        <v>2</v>
-      </c>
-      <c r="M6">
+      <c r="K6">
         <v>1</v>
       </c>
     </row>
@@ -8051,7 +8023,7 @@
       <c r="A7" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="K7">
+      <c r="L7">
         <v>1</v>
       </c>
     </row>
@@ -8060,40 +8032,40 @@
         <v>8</v>
       </c>
       <c r="B8">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="C8">
+        <v>31</v>
+      </c>
+      <c r="D8">
+        <v>22</v>
+      </c>
+      <c r="E8">
         <v>44</v>
       </c>
-      <c r="D8">
-        <v>49</v>
-      </c>
-      <c r="E8">
-        <v>67</v>
-      </c>
       <c r="F8">
-        <v>69</v>
+        <v>38</v>
       </c>
       <c r="G8">
-        <v>57</v>
+        <v>24</v>
       </c>
       <c r="H8">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="I8">
-        <v>80</v>
+        <v>34</v>
       </c>
       <c r="J8">
-        <v>64</v>
+        <v>26</v>
       </c>
       <c r="K8">
-        <v>48</v>
+        <v>24</v>
       </c>
       <c r="L8">
-        <v>44</v>
+        <v>14</v>
       </c>
       <c r="M8">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -8101,40 +8073,40 @@
         <v>9</v>
       </c>
       <c r="B9">
-        <v>233</v>
+        <v>46</v>
       </c>
       <c r="C9">
-        <v>354</v>
+        <v>59</v>
       </c>
       <c r="D9">
-        <v>538</v>
+        <v>33</v>
       </c>
       <c r="E9">
-        <v>705</v>
+        <v>73</v>
       </c>
       <c r="F9">
-        <v>568</v>
+        <v>114</v>
       </c>
       <c r="G9">
-        <v>168</v>
+        <v>58</v>
       </c>
       <c r="H9">
-        <v>116</v>
+        <v>41</v>
       </c>
       <c r="I9">
-        <v>194</v>
+        <v>44</v>
       </c>
       <c r="J9">
-        <v>122</v>
+        <v>20</v>
       </c>
       <c r="K9">
-        <v>114</v>
+        <v>25</v>
       </c>
       <c r="L9">
-        <v>95</v>
+        <v>27</v>
       </c>
       <c r="M9">
-        <v>45</v>
+        <v>16</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -8142,40 +8114,40 @@
         <v>10</v>
       </c>
       <c r="B10">
-        <v>282</v>
+        <v>78</v>
       </c>
       <c r="C10">
-        <v>416</v>
+        <v>99</v>
       </c>
       <c r="D10">
-        <v>617</v>
+        <v>65</v>
       </c>
       <c r="E10">
-        <v>797</v>
+        <v>130</v>
       </c>
       <c r="F10">
-        <v>660</v>
+        <v>167</v>
       </c>
       <c r="G10">
-        <v>257</v>
+        <v>92</v>
       </c>
       <c r="H10">
-        <v>236</v>
+        <v>104</v>
       </c>
       <c r="I10">
-        <v>324</v>
+        <v>89</v>
       </c>
       <c r="J10">
-        <v>255</v>
+        <v>67</v>
       </c>
       <c r="K10">
-        <v>207</v>
+        <v>71</v>
       </c>
       <c r="L10">
-        <v>196</v>
+        <v>61</v>
       </c>
       <c r="M10">
-        <v>89</v>
+        <v>50</v>
       </c>
     </row>
   </sheetData>
@@ -8184,302 +8156,6 @@
 </file>
 
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M8"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" customWidth="1"/>
-    <col min="13" max="13" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="M1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2">
-        <v>4</v>
-      </c>
-      <c r="D2">
-        <v>1</v>
-      </c>
-      <c r="E2">
-        <v>4</v>
-      </c>
-      <c r="F2">
-        <v>2</v>
-      </c>
-      <c r="G2">
-        <v>4</v>
-      </c>
-      <c r="H2">
-        <v>2</v>
-      </c>
-      <c r="I2">
-        <v>3</v>
-      </c>
-      <c r="J2">
-        <v>2</v>
-      </c>
-      <c r="K2">
-        <v>6</v>
-      </c>
-      <c r="L2">
-        <v>6</v>
-      </c>
-      <c r="M2">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3">
-        <v>2</v>
-      </c>
-      <c r="C3">
-        <v>4</v>
-      </c>
-      <c r="D3">
-        <v>1</v>
-      </c>
-      <c r="E3">
-        <v>4</v>
-      </c>
-      <c r="F3">
-        <v>5</v>
-      </c>
-      <c r="G3">
-        <v>4</v>
-      </c>
-      <c r="H3">
-        <v>7</v>
-      </c>
-      <c r="I3">
-        <v>2</v>
-      </c>
-      <c r="J3">
-        <v>11</v>
-      </c>
-      <c r="K3">
-        <v>5</v>
-      </c>
-      <c r="L3">
-        <v>7</v>
-      </c>
-      <c r="M3">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="H4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C5">
-        <v>1</v>
-      </c>
-      <c r="H5">
-        <v>1</v>
-      </c>
-      <c r="I5">
-        <v>1</v>
-      </c>
-      <c r="K5">
-        <v>3</v>
-      </c>
-      <c r="L5">
-        <v>2</v>
-      </c>
-      <c r="M5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C6">
-        <v>14</v>
-      </c>
-      <c r="D6">
-        <v>12</v>
-      </c>
-      <c r="E6">
-        <v>10</v>
-      </c>
-      <c r="F6">
-        <v>11</v>
-      </c>
-      <c r="G6">
-        <v>11</v>
-      </c>
-      <c r="H6">
-        <v>17</v>
-      </c>
-      <c r="I6">
-        <v>20</v>
-      </c>
-      <c r="J6">
-        <v>3</v>
-      </c>
-      <c r="K6">
-        <v>10</v>
-      </c>
-      <c r="L6">
-        <v>5</v>
-      </c>
-      <c r="M6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
-      <c r="A7" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B7">
-        <v>58</v>
-      </c>
-      <c r="C7">
-        <v>53</v>
-      </c>
-      <c r="D7">
-        <v>43</v>
-      </c>
-      <c r="E7">
-        <v>56</v>
-      </c>
-      <c r="F7">
-        <v>53</v>
-      </c>
-      <c r="G7">
-        <v>33</v>
-      </c>
-      <c r="H7">
-        <v>23</v>
-      </c>
-      <c r="I7">
-        <v>26</v>
-      </c>
-      <c r="J7">
-        <v>27</v>
-      </c>
-      <c r="K7">
-        <v>17</v>
-      </c>
-      <c r="L7">
-        <v>19</v>
-      </c>
-      <c r="M7">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13">
-      <c r="A8" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B8">
-        <v>60</v>
-      </c>
-      <c r="C8">
-        <v>76</v>
-      </c>
-      <c r="D8">
-        <v>57</v>
-      </c>
-      <c r="E8">
-        <v>74</v>
-      </c>
-      <c r="F8">
-        <v>71</v>
-      </c>
-      <c r="G8">
-        <v>52</v>
-      </c>
-      <c r="H8">
-        <v>51</v>
-      </c>
-      <c r="I8">
-        <v>52</v>
-      </c>
-      <c r="J8">
-        <v>43</v>
-      </c>
-      <c r="K8">
-        <v>41</v>
-      </c>
-      <c r="L8">
-        <v>39</v>
-      </c>
-      <c r="M8">
-        <v>25</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -8750,7 +8426,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:D4"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -8813,7 +8489,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M9"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -9080,6 +8756,330 @@
       </c>
       <c r="M9">
         <v>7</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:M10"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+    <col min="13" max="13" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="M1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>5</v>
+      </c>
+      <c r="C2">
+        <v>3</v>
+      </c>
+      <c r="D2">
+        <v>7</v>
+      </c>
+      <c r="E2">
+        <v>5</v>
+      </c>
+      <c r="F2">
+        <v>5</v>
+      </c>
+      <c r="G2">
+        <v>4</v>
+      </c>
+      <c r="H2">
+        <v>6</v>
+      </c>
+      <c r="I2">
+        <v>4</v>
+      </c>
+      <c r="J2">
+        <v>7</v>
+      </c>
+      <c r="K2">
+        <v>7</v>
+      </c>
+      <c r="L2">
+        <v>5</v>
+      </c>
+      <c r="M2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>3</v>
+      </c>
+      <c r="C3">
+        <v>2</v>
+      </c>
+      <c r="D3">
+        <v>8</v>
+      </c>
+      <c r="E3">
+        <v>9</v>
+      </c>
+      <c r="F3">
+        <v>19</v>
+      </c>
+      <c r="G3">
+        <v>9</v>
+      </c>
+      <c r="H3">
+        <v>8</v>
+      </c>
+      <c r="I3">
+        <v>13</v>
+      </c>
+      <c r="J3">
+        <v>12</v>
+      </c>
+      <c r="K3">
+        <v>17</v>
+      </c>
+      <c r="L3">
+        <v>13</v>
+      </c>
+      <c r="M3">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="I4">
+        <v>1</v>
+      </c>
+      <c r="M4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="K5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="E6">
+        <v>1</v>
+      </c>
+      <c r="F6">
+        <v>2</v>
+      </c>
+      <c r="J6">
+        <v>2</v>
+      </c>
+      <c r="M6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E7">
+        <v>1</v>
+      </c>
+      <c r="I7">
+        <v>1</v>
+      </c>
+      <c r="K7">
+        <v>1</v>
+      </c>
+      <c r="L7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13">
+      <c r="A8" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8">
+        <v>24</v>
+      </c>
+      <c r="C8">
+        <v>37</v>
+      </c>
+      <c r="D8">
+        <v>21</v>
+      </c>
+      <c r="E8">
+        <v>22</v>
+      </c>
+      <c r="F8">
+        <v>27</v>
+      </c>
+      <c r="G8">
+        <v>15</v>
+      </c>
+      <c r="H8">
+        <v>25</v>
+      </c>
+      <c r="I8">
+        <v>21</v>
+      </c>
+      <c r="J8">
+        <v>26</v>
+      </c>
+      <c r="K8">
+        <v>49</v>
+      </c>
+      <c r="L8">
+        <v>44</v>
+      </c>
+      <c r="M8">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13">
+      <c r="A9" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B9">
+        <v>45</v>
+      </c>
+      <c r="C9">
+        <v>64</v>
+      </c>
+      <c r="D9">
+        <v>46</v>
+      </c>
+      <c r="E9">
+        <v>50</v>
+      </c>
+      <c r="F9">
+        <v>38</v>
+      </c>
+      <c r="G9">
+        <v>19</v>
+      </c>
+      <c r="H9">
+        <v>27</v>
+      </c>
+      <c r="I9">
+        <v>37</v>
+      </c>
+      <c r="J9">
+        <v>20</v>
+      </c>
+      <c r="K9">
+        <v>35</v>
+      </c>
+      <c r="L9">
+        <v>35</v>
+      </c>
+      <c r="M9">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13">
+      <c r="A10" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B10">
+        <v>77</v>
+      </c>
+      <c r="C10">
+        <v>106</v>
+      </c>
+      <c r="D10">
+        <v>82</v>
+      </c>
+      <c r="E10">
+        <v>88</v>
+      </c>
+      <c r="F10">
+        <v>91</v>
+      </c>
+      <c r="G10">
+        <v>47</v>
+      </c>
+      <c r="H10">
+        <v>66</v>
+      </c>
+      <c r="I10">
+        <v>77</v>
+      </c>
+      <c r="J10">
+        <v>67</v>
+      </c>
+      <c r="K10">
+        <v>110</v>
+      </c>
+      <c r="L10">
+        <v>98</v>
+      </c>
+      <c r="M10">
+        <v>36</v>
       </c>
     </row>
   </sheetData>
@@ -14586,257 +14586,6 @@
 
 <file path=xl/worksheets/sheet44.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M8"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" customWidth="1"/>
-    <col min="13" max="13" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="M1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2">
-        <v>1</v>
-      </c>
-      <c r="D2">
-        <v>2</v>
-      </c>
-      <c r="F2">
-        <v>2</v>
-      </c>
-      <c r="I2">
-        <v>3</v>
-      </c>
-      <c r="J2">
-        <v>2</v>
-      </c>
-      <c r="K2">
-        <v>1</v>
-      </c>
-      <c r="L2">
-        <v>5</v>
-      </c>
-      <c r="M2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C3">
-        <v>1</v>
-      </c>
-      <c r="E3">
-        <v>1</v>
-      </c>
-      <c r="H3">
-        <v>2</v>
-      </c>
-      <c r="I3">
-        <v>1</v>
-      </c>
-      <c r="J3">
-        <v>1</v>
-      </c>
-      <c r="K3">
-        <v>2</v>
-      </c>
-      <c r="L3">
-        <v>2</v>
-      </c>
-      <c r="M3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C4">
-        <v>1</v>
-      </c>
-      <c r="I4">
-        <v>1</v>
-      </c>
-      <c r="K4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="L5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B6">
-        <v>1</v>
-      </c>
-      <c r="F6">
-        <v>4</v>
-      </c>
-      <c r="H6">
-        <v>1</v>
-      </c>
-      <c r="I6">
-        <v>2</v>
-      </c>
-      <c r="K6">
-        <v>1</v>
-      </c>
-      <c r="M6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
-      <c r="A7" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B7">
-        <v>10</v>
-      </c>
-      <c r="C7">
-        <v>20</v>
-      </c>
-      <c r="D7">
-        <v>25</v>
-      </c>
-      <c r="E7">
-        <v>30</v>
-      </c>
-      <c r="F7">
-        <v>41</v>
-      </c>
-      <c r="G7">
-        <v>10</v>
-      </c>
-      <c r="H7">
-        <v>5</v>
-      </c>
-      <c r="I7">
-        <v>5</v>
-      </c>
-      <c r="J7">
-        <v>15</v>
-      </c>
-      <c r="K7">
-        <v>17</v>
-      </c>
-      <c r="L7">
-        <v>12</v>
-      </c>
-      <c r="M7">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13">
-      <c r="A8" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B8">
-        <v>12</v>
-      </c>
-      <c r="C8">
-        <v>22</v>
-      </c>
-      <c r="D8">
-        <v>27</v>
-      </c>
-      <c r="E8">
-        <v>31</v>
-      </c>
-      <c r="F8">
-        <v>47</v>
-      </c>
-      <c r="G8">
-        <v>10</v>
-      </c>
-      <c r="H8">
-        <v>8</v>
-      </c>
-      <c r="I8">
-        <v>12</v>
-      </c>
-      <c r="J8">
-        <v>18</v>
-      </c>
-      <c r="K8">
-        <v>22</v>
-      </c>
-      <c r="L8">
-        <v>21</v>
-      </c>
-      <c r="M8">
-        <v>16</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet45.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -15114,7 +14863,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet46.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet45.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -15330,6 +15079,257 @@
       </c>
       <c r="M6">
         <v>3</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet46.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:M8"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+    <col min="13" max="13" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="M1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>2</v>
+      </c>
+      <c r="F2">
+        <v>2</v>
+      </c>
+      <c r="I2">
+        <v>3</v>
+      </c>
+      <c r="J2">
+        <v>2</v>
+      </c>
+      <c r="K2">
+        <v>1</v>
+      </c>
+      <c r="L2">
+        <v>5</v>
+      </c>
+      <c r="M2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
+      <c r="E3">
+        <v>1</v>
+      </c>
+      <c r="H3">
+        <v>2</v>
+      </c>
+      <c r="I3">
+        <v>1</v>
+      </c>
+      <c r="J3">
+        <v>1</v>
+      </c>
+      <c r="K3">
+        <v>2</v>
+      </c>
+      <c r="L3">
+        <v>2</v>
+      </c>
+      <c r="M3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
+      <c r="I4">
+        <v>1</v>
+      </c>
+      <c r="K4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="L5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6">
+        <v>1</v>
+      </c>
+      <c r="F6">
+        <v>4</v>
+      </c>
+      <c r="H6">
+        <v>1</v>
+      </c>
+      <c r="I6">
+        <v>2</v>
+      </c>
+      <c r="K6">
+        <v>1</v>
+      </c>
+      <c r="M6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7">
+        <v>10</v>
+      </c>
+      <c r="C7">
+        <v>20</v>
+      </c>
+      <c r="D7">
+        <v>25</v>
+      </c>
+      <c r="E7">
+        <v>30</v>
+      </c>
+      <c r="F7">
+        <v>41</v>
+      </c>
+      <c r="G7">
+        <v>10</v>
+      </c>
+      <c r="H7">
+        <v>5</v>
+      </c>
+      <c r="I7">
+        <v>5</v>
+      </c>
+      <c r="J7">
+        <v>15</v>
+      </c>
+      <c r="K7">
+        <v>17</v>
+      </c>
+      <c r="L7">
+        <v>12</v>
+      </c>
+      <c r="M7">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13">
+      <c r="A8" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B8">
+        <v>12</v>
+      </c>
+      <c r="C8">
+        <v>22</v>
+      </c>
+      <c r="D8">
+        <v>27</v>
+      </c>
+      <c r="E8">
+        <v>31</v>
+      </c>
+      <c r="F8">
+        <v>47</v>
+      </c>
+      <c r="G8">
+        <v>10</v>
+      </c>
+      <c r="H8">
+        <v>8</v>
+      </c>
+      <c r="I8">
+        <v>12</v>
+      </c>
+      <c r="J8">
+        <v>18</v>
+      </c>
+      <c r="K8">
+        <v>22</v>
+      </c>
+      <c r="L8">
+        <v>21</v>
+      </c>
+      <c r="M8">
+        <v>16</v>
       </c>
     </row>
   </sheetData>

--- a/output/cta-index-crime-full-year.xlsx
+++ b/output/cta-index-crime-full-year.xlsx
@@ -72,13 +72,13 @@
     <sheet name="Brighton Park" sheetId="63" r:id="rId63"/>
     <sheet name="Lincoln Park" sheetId="64" r:id="rId64"/>
     <sheet name="Printers Row" sheetId="65" r:id="rId65"/>
-    <sheet name="West Pullman" sheetId="66" r:id="rId66"/>
-    <sheet name="West Lawn" sheetId="67" r:id="rId67"/>
-    <sheet name="Little Village" sheetId="68" r:id="rId68"/>
-    <sheet name="Ukrainian Village" sheetId="69" r:id="rId69"/>
-    <sheet name="Archer Heights" sheetId="70" r:id="rId70"/>
-    <sheet name="Montclare" sheetId="71" r:id="rId71"/>
-    <sheet name="Old Town" sheetId="72" r:id="rId72"/>
+    <sheet name="Old Town" sheetId="66" r:id="rId66"/>
+    <sheet name="West Pullman" sheetId="67" r:id="rId67"/>
+    <sheet name="West Lawn" sheetId="68" r:id="rId68"/>
+    <sheet name="Little Village" sheetId="69" r:id="rId69"/>
+    <sheet name="Ukrainian Village" sheetId="70" r:id="rId70"/>
+    <sheet name="Archer Heights" sheetId="71" r:id="rId71"/>
+    <sheet name="Montclare" sheetId="72" r:id="rId72"/>
     <sheet name="Grant Park" sheetId="73" r:id="rId73"/>
     <sheet name="West Elsdon" sheetId="74" r:id="rId74"/>
     <sheet name="East Side" sheetId="75" r:id="rId75"/>
@@ -946,7 +946,7 @@
         <v>262</v>
       </c>
       <c r="M3">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -1156,7 +1156,7 @@
         <v>467</v>
       </c>
       <c r="M9">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -1197,7 +1197,7 @@
         <v>703</v>
       </c>
       <c r="M10">
-        <v>356</v>
+        <v>358</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -1238,7 +1238,7 @@
         <v>1604</v>
       </c>
       <c r="M11">
-        <v>796</v>
+        <v>800</v>
       </c>
     </row>
   </sheetData>
@@ -2306,7 +2306,7 @@
         <v>19</v>
       </c>
       <c r="M8">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -2388,7 +2388,7 @@
         <v>40</v>
       </c>
       <c r="M10">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
   </sheetData>
@@ -3599,7 +3599,7 @@
         <v>95</v>
       </c>
       <c r="M9">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -3640,7 +3640,7 @@
         <v>196</v>
       </c>
       <c r="M10">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
   </sheetData>
@@ -4265,7 +4265,7 @@
         <v>61</v>
       </c>
       <c r="M8">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -4665,7 +4665,7 @@
         <v>40</v>
       </c>
       <c r="M19">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="20" spans="1:13">
@@ -5957,7 +5957,7 @@
         <v>196</v>
       </c>
       <c r="M53">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="54" spans="1:13">
@@ -6594,7 +6594,7 @@
         <v>17</v>
       </c>
       <c r="M70">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="71" spans="1:13">
@@ -7729,7 +7729,7 @@
         <v>1604</v>
       </c>
       <c r="M99">
-        <v>796</v>
+        <v>800</v>
       </c>
     </row>
   </sheetData>
@@ -7977,7 +7977,7 @@
         <v>14</v>
       </c>
       <c r="M3">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -8147,7 +8147,7 @@
         <v>61</v>
       </c>
       <c r="M10">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
   </sheetData>
@@ -20278,6 +20278,272 @@
 
 <file path=xl/worksheets/sheet66.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:M8"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+    <col min="13" max="13" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="M1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>2</v>
+      </c>
+      <c r="F2">
+        <v>2</v>
+      </c>
+      <c r="G2">
+        <v>2</v>
+      </c>
+      <c r="H2">
+        <v>1</v>
+      </c>
+      <c r="J2">
+        <v>1</v>
+      </c>
+      <c r="K2">
+        <v>4</v>
+      </c>
+      <c r="L2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>1</v>
+      </c>
+      <c r="D3">
+        <v>3</v>
+      </c>
+      <c r="E3">
+        <v>2</v>
+      </c>
+      <c r="F3">
+        <v>4</v>
+      </c>
+      <c r="G3">
+        <v>1</v>
+      </c>
+      <c r="H3">
+        <v>4</v>
+      </c>
+      <c r="I3">
+        <v>2</v>
+      </c>
+      <c r="J3">
+        <v>6</v>
+      </c>
+      <c r="K3">
+        <v>3</v>
+      </c>
+      <c r="L3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="J5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6">
+        <v>1</v>
+      </c>
+      <c r="C6">
+        <v>11</v>
+      </c>
+      <c r="D6">
+        <v>4</v>
+      </c>
+      <c r="E6">
+        <v>17</v>
+      </c>
+      <c r="F6">
+        <v>18</v>
+      </c>
+      <c r="G6">
+        <v>12</v>
+      </c>
+      <c r="H6">
+        <v>12</v>
+      </c>
+      <c r="I6">
+        <v>17</v>
+      </c>
+      <c r="J6">
+        <v>6</v>
+      </c>
+      <c r="K6">
+        <v>17</v>
+      </c>
+      <c r="L6">
+        <v>5</v>
+      </c>
+      <c r="M6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7">
+        <v>24</v>
+      </c>
+      <c r="C7">
+        <v>26</v>
+      </c>
+      <c r="D7">
+        <v>44</v>
+      </c>
+      <c r="E7">
+        <v>57</v>
+      </c>
+      <c r="F7">
+        <v>79</v>
+      </c>
+      <c r="G7">
+        <v>24</v>
+      </c>
+      <c r="H7">
+        <v>13</v>
+      </c>
+      <c r="I7">
+        <v>15</v>
+      </c>
+      <c r="J7">
+        <v>15</v>
+      </c>
+      <c r="K7">
+        <v>9</v>
+      </c>
+      <c r="L7">
+        <v>7</v>
+      </c>
+      <c r="M7">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13">
+      <c r="A8" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B8">
+        <v>27</v>
+      </c>
+      <c r="C8">
+        <v>37</v>
+      </c>
+      <c r="D8">
+        <v>53</v>
+      </c>
+      <c r="E8">
+        <v>76</v>
+      </c>
+      <c r="F8">
+        <v>103</v>
+      </c>
+      <c r="G8">
+        <v>39</v>
+      </c>
+      <c r="H8">
+        <v>30</v>
+      </c>
+      <c r="I8">
+        <v>34</v>
+      </c>
+      <c r="J8">
+        <v>29</v>
+      </c>
+      <c r="K8">
+        <v>33</v>
+      </c>
+      <c r="L8">
+        <v>17</v>
+      </c>
+      <c r="M8">
+        <v>7</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet67.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -20496,7 +20762,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet67.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet68.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:J6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -20638,7 +20904,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet68.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet69.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -20874,190 +21140,6 @@
       </c>
       <c r="M7">
         <v>9</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet69.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M6"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="18.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" customWidth="1"/>
-    <col min="13" max="13" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="M1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="H2">
-        <v>1</v>
-      </c>
-      <c r="J2">
-        <v>1</v>
-      </c>
-      <c r="L2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="L3">
-        <v>2</v>
-      </c>
-      <c r="M3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E4">
-        <v>1</v>
-      </c>
-      <c r="I4">
-        <v>2</v>
-      </c>
-      <c r="L4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B5">
-        <v>3</v>
-      </c>
-      <c r="C5">
-        <v>2</v>
-      </c>
-      <c r="D5">
-        <v>1</v>
-      </c>
-      <c r="E5">
-        <v>2</v>
-      </c>
-      <c r="F5">
-        <v>2</v>
-      </c>
-      <c r="G5">
-        <v>1</v>
-      </c>
-      <c r="H5">
-        <v>2</v>
-      </c>
-      <c r="I5">
-        <v>2</v>
-      </c>
-      <c r="K5">
-        <v>4</v>
-      </c>
-      <c r="L5">
-        <v>1</v>
-      </c>
-      <c r="M5">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B6">
-        <v>3</v>
-      </c>
-      <c r="C6">
-        <v>2</v>
-      </c>
-      <c r="D6">
-        <v>1</v>
-      </c>
-      <c r="E6">
-        <v>3</v>
-      </c>
-      <c r="F6">
-        <v>2</v>
-      </c>
-      <c r="G6">
-        <v>1</v>
-      </c>
-      <c r="H6">
-        <v>3</v>
-      </c>
-      <c r="I6">
-        <v>4</v>
-      </c>
-      <c r="J6">
-        <v>1</v>
-      </c>
-      <c r="K6">
-        <v>4</v>
-      </c>
-      <c r="L6">
-        <v>5</v>
-      </c>
-      <c r="M6">
-        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -21383,6 +21465,190 @@
 
 <file path=xl/worksheets/sheet70.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:M6"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="18.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+    <col min="13" max="13" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="M1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="H2">
+        <v>1</v>
+      </c>
+      <c r="J2">
+        <v>1</v>
+      </c>
+      <c r="L2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="L3">
+        <v>2</v>
+      </c>
+      <c r="M3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E4">
+        <v>1</v>
+      </c>
+      <c r="I4">
+        <v>2</v>
+      </c>
+      <c r="L4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5">
+        <v>3</v>
+      </c>
+      <c r="C5">
+        <v>2</v>
+      </c>
+      <c r="D5">
+        <v>1</v>
+      </c>
+      <c r="E5">
+        <v>2</v>
+      </c>
+      <c r="F5">
+        <v>2</v>
+      </c>
+      <c r="G5">
+        <v>1</v>
+      </c>
+      <c r="H5">
+        <v>2</v>
+      </c>
+      <c r="I5">
+        <v>2</v>
+      </c>
+      <c r="K5">
+        <v>4</v>
+      </c>
+      <c r="L5">
+        <v>1</v>
+      </c>
+      <c r="M5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6">
+        <v>3</v>
+      </c>
+      <c r="C6">
+        <v>2</v>
+      </c>
+      <c r="D6">
+        <v>1</v>
+      </c>
+      <c r="E6">
+        <v>3</v>
+      </c>
+      <c r="F6">
+        <v>2</v>
+      </c>
+      <c r="G6">
+        <v>1</v>
+      </c>
+      <c r="H6">
+        <v>3</v>
+      </c>
+      <c r="I6">
+        <v>4</v>
+      </c>
+      <c r="J6">
+        <v>1</v>
+      </c>
+      <c r="K6">
+        <v>4</v>
+      </c>
+      <c r="L6">
+        <v>5</v>
+      </c>
+      <c r="M6">
+        <v>4</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet71.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:J7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -21543,7 +21809,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet71.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet72.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:G5"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -21646,272 +21912,6 @@
       </c>
       <c r="G5">
         <v>2</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet72.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M8"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" customWidth="1"/>
-    <col min="13" max="13" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="M1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D2">
-        <v>2</v>
-      </c>
-      <c r="F2">
-        <v>2</v>
-      </c>
-      <c r="G2">
-        <v>2</v>
-      </c>
-      <c r="H2">
-        <v>1</v>
-      </c>
-      <c r="J2">
-        <v>1</v>
-      </c>
-      <c r="K2">
-        <v>4</v>
-      </c>
-      <c r="L2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3">
-        <v>1</v>
-      </c>
-      <c r="D3">
-        <v>3</v>
-      </c>
-      <c r="E3">
-        <v>2</v>
-      </c>
-      <c r="F3">
-        <v>4</v>
-      </c>
-      <c r="G3">
-        <v>1</v>
-      </c>
-      <c r="H3">
-        <v>4</v>
-      </c>
-      <c r="I3">
-        <v>2</v>
-      </c>
-      <c r="J3">
-        <v>6</v>
-      </c>
-      <c r="K3">
-        <v>3</v>
-      </c>
-      <c r="L3">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="J5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B6">
-        <v>1</v>
-      </c>
-      <c r="C6">
-        <v>11</v>
-      </c>
-      <c r="D6">
-        <v>4</v>
-      </c>
-      <c r="E6">
-        <v>17</v>
-      </c>
-      <c r="F6">
-        <v>18</v>
-      </c>
-      <c r="G6">
-        <v>12</v>
-      </c>
-      <c r="H6">
-        <v>12</v>
-      </c>
-      <c r="I6">
-        <v>17</v>
-      </c>
-      <c r="J6">
-        <v>6</v>
-      </c>
-      <c r="K6">
-        <v>17</v>
-      </c>
-      <c r="L6">
-        <v>5</v>
-      </c>
-      <c r="M6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
-      <c r="A7" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B7">
-        <v>24</v>
-      </c>
-      <c r="C7">
-        <v>26</v>
-      </c>
-      <c r="D7">
-        <v>44</v>
-      </c>
-      <c r="E7">
-        <v>57</v>
-      </c>
-      <c r="F7">
-        <v>79</v>
-      </c>
-      <c r="G7">
-        <v>24</v>
-      </c>
-      <c r="H7">
-        <v>13</v>
-      </c>
-      <c r="I7">
-        <v>15</v>
-      </c>
-      <c r="J7">
-        <v>15</v>
-      </c>
-      <c r="K7">
-        <v>9</v>
-      </c>
-      <c r="L7">
-        <v>7</v>
-      </c>
-      <c r="M7">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13">
-      <c r="A8" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B8">
-        <v>27</v>
-      </c>
-      <c r="C8">
-        <v>37</v>
-      </c>
-      <c r="D8">
-        <v>53</v>
-      </c>
-      <c r="E8">
-        <v>76</v>
-      </c>
-      <c r="F8">
-        <v>103</v>
-      </c>
-      <c r="G8">
-        <v>39</v>
-      </c>
-      <c r="H8">
-        <v>30</v>
-      </c>
-      <c r="I8">
-        <v>34</v>
-      </c>
-      <c r="J8">
-        <v>29</v>
-      </c>
-      <c r="K8">
-        <v>33</v>
-      </c>
-      <c r="L8">
-        <v>17</v>
-      </c>
-      <c r="M8">
-        <v>6</v>
       </c>
     </row>
   </sheetData>

--- a/output/cta-index-crime-full-year.xlsx
+++ b/output/cta-index-crime-full-year.xlsx
@@ -19,18 +19,18 @@
     <sheet name="Rogers Park" sheetId="10" r:id="rId10"/>
     <sheet name="Douglas" sheetId="11" r:id="rId11"/>
     <sheet name="Jefferson Park" sheetId="12" r:id="rId12"/>
-    <sheet name="Chatham" sheetId="13" r:id="rId13"/>
-    <sheet name="Albany Park" sheetId="14" r:id="rId14"/>
-    <sheet name="Grand Boulevard" sheetId="15" r:id="rId15"/>
-    <sheet name="Belmont Cragin" sheetId="16" r:id="rId16"/>
-    <sheet name="West Ridge" sheetId="17" r:id="rId17"/>
-    <sheet name="Loop" sheetId="18" r:id="rId18"/>
-    <sheet name="Lake View" sheetId="19" r:id="rId19"/>
-    <sheet name="Austin" sheetId="20" r:id="rId20"/>
-    <sheet name="South Shore" sheetId="21" r:id="rId21"/>
-    <sheet name="Mount Greenwood" sheetId="22" r:id="rId22"/>
-    <sheet name="Gage Park" sheetId="23" r:id="rId23"/>
-    <sheet name="Grand Crossing" sheetId="24" r:id="rId24"/>
+    <sheet name="Grand Crossing" sheetId="13" r:id="rId13"/>
+    <sheet name="Chatham" sheetId="14" r:id="rId14"/>
+    <sheet name="Austin" sheetId="15" r:id="rId15"/>
+    <sheet name="Albany Park" sheetId="16" r:id="rId16"/>
+    <sheet name="Grand Boulevard" sheetId="17" r:id="rId17"/>
+    <sheet name="Belmont Cragin" sheetId="18" r:id="rId18"/>
+    <sheet name="West Ridge" sheetId="19" r:id="rId19"/>
+    <sheet name="Loop" sheetId="20" r:id="rId20"/>
+    <sheet name="Lake View" sheetId="21" r:id="rId21"/>
+    <sheet name="South Shore" sheetId="22" r:id="rId22"/>
+    <sheet name="Mount Greenwood" sheetId="23" r:id="rId23"/>
+    <sheet name="Gage Park" sheetId="24" r:id="rId24"/>
     <sheet name="West Loop" sheetId="25" r:id="rId25"/>
     <sheet name="Rush &amp; Division" sheetId="26" r:id="rId26"/>
     <sheet name="North Lawndale" sheetId="27" r:id="rId27"/>
@@ -50,9 +50,9 @@
     <sheet name="Roseland" sheetId="41" r:id="rId41"/>
     <sheet name="Woodlawn" sheetId="42" r:id="rId42"/>
     <sheet name="Fuller Park" sheetId="43" r:id="rId43"/>
-    <sheet name="Little Italy, UIC" sheetId="44" r:id="rId44"/>
-    <sheet name="Hyde Park" sheetId="45" r:id="rId45"/>
-    <sheet name="O'Hare" sheetId="46" r:id="rId46"/>
+    <sheet name="O'Hare" sheetId="44" r:id="rId44"/>
+    <sheet name="Little Italy, UIC" sheetId="45" r:id="rId45"/>
+    <sheet name="Hyde Park" sheetId="46" r:id="rId46"/>
     <sheet name="Bucktown" sheetId="47" r:id="rId47"/>
     <sheet name="Calumet Heights" sheetId="48" r:id="rId48"/>
     <sheet name="Edgewater" sheetId="49" r:id="rId49"/>
@@ -2146,38 +2146,41 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
+      <c r="B2">
+        <v>5</v>
+      </c>
       <c r="C2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D2">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H2">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J2">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="L2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M2">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -2185,56 +2188,56 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D3">
+        <v>8</v>
+      </c>
+      <c r="E3">
+        <v>9</v>
+      </c>
+      <c r="F3">
+        <v>19</v>
+      </c>
+      <c r="G3">
+        <v>9</v>
+      </c>
+      <c r="H3">
+        <v>8</v>
+      </c>
+      <c r="I3">
+        <v>13</v>
+      </c>
+      <c r="J3">
+        <v>12</v>
+      </c>
+      <c r="K3">
+        <v>17</v>
+      </c>
+      <c r="L3">
+        <v>13</v>
+      </c>
+      <c r="M3">
         <v>7</v>
-      </c>
-      <c r="E3">
-        <v>3</v>
-      </c>
-      <c r="F3">
-        <v>4</v>
-      </c>
-      <c r="G3">
-        <v>8</v>
-      </c>
-      <c r="H3">
-        <v>4</v>
-      </c>
-      <c r="I3">
-        <v>6</v>
-      </c>
-      <c r="J3">
-        <v>4</v>
-      </c>
-      <c r="K3">
-        <v>10</v>
-      </c>
-      <c r="L3">
-        <v>5</v>
-      </c>
-      <c r="M3">
-        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="H4">
+      <c r="I4">
+        <v>1</v>
+      </c>
+      <c r="M4">
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K5">
         <v>1</v>
@@ -2242,30 +2245,36 @@
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="G6">
-        <v>1</v>
-      </c>
-      <c r="H6">
-        <v>1</v>
-      </c>
-      <c r="I6">
+        <v>5</v>
+      </c>
+      <c r="E6">
+        <v>1</v>
+      </c>
+      <c r="F6">
+        <v>2</v>
+      </c>
+      <c r="J6">
+        <v>2</v>
+      </c>
+      <c r="M6">
         <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D7">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E7">
         <v>1</v>
       </c>
-      <c r="J7">
-        <v>2</v>
+      <c r="I7">
+        <v>1</v>
+      </c>
+      <c r="K7">
+        <v>1</v>
+      </c>
+      <c r="L7">
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -2273,40 +2282,40 @@
         <v>8</v>
       </c>
       <c r="B8">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="C8">
-        <v>9</v>
+        <v>37</v>
       </c>
       <c r="D8">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E8">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="F8">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="G8">
         <v>15</v>
       </c>
       <c r="H8">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="I8">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="J8">
+        <v>26</v>
+      </c>
+      <c r="K8">
+        <v>49</v>
+      </c>
+      <c r="L8">
+        <v>44</v>
+      </c>
+      <c r="M8">
         <v>12</v>
-      </c>
-      <c r="K8">
-        <v>18</v>
-      </c>
-      <c r="L8">
-        <v>19</v>
-      </c>
-      <c r="M8">
-        <v>6</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -2314,40 +2323,40 @@
         <v>9</v>
       </c>
       <c r="B9">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C9">
+        <v>64</v>
+      </c>
+      <c r="D9">
         <v>46</v>
       </c>
-      <c r="D9">
-        <v>32</v>
-      </c>
       <c r="E9">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="F9">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="G9">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="H9">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="I9">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="J9">
         <v>20</v>
       </c>
       <c r="K9">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="L9">
-        <v>13</v>
+        <v>35</v>
       </c>
       <c r="M9">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -2355,40 +2364,40 @@
         <v>10</v>
       </c>
       <c r="B10">
-        <v>51</v>
+        <v>77</v>
       </c>
       <c r="C10">
-        <v>57</v>
+        <v>106</v>
       </c>
       <c r="D10">
-        <v>62</v>
+        <v>82</v>
       </c>
       <c r="E10">
-        <v>48</v>
+        <v>88</v>
       </c>
       <c r="F10">
-        <v>60</v>
+        <v>91</v>
       </c>
       <c r="G10">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="H10">
-        <v>31</v>
+        <v>66</v>
       </c>
       <c r="I10">
-        <v>44</v>
+        <v>77</v>
       </c>
       <c r="J10">
-        <v>43</v>
+        <v>67</v>
       </c>
       <c r="K10">
-        <v>57</v>
+        <v>110</v>
       </c>
       <c r="L10">
-        <v>40</v>
+        <v>98</v>
       </c>
       <c r="M10">
-        <v>18</v>
+        <v>36</v>
       </c>
     </row>
   </sheetData>
@@ -2398,7 +2407,7 @@
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M7"/>
+  <dimension ref="A1:M10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="23.7109375" customWidth="1"/>
@@ -2461,29 +2470,38 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
       <c r="D2">
+        <v>5</v>
+      </c>
+      <c r="E2">
         <v>1</v>
       </c>
       <c r="F2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G2">
         <v>1</v>
       </c>
+      <c r="H2">
+        <v>3</v>
+      </c>
       <c r="I2">
         <v>2</v>
       </c>
       <c r="J2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K2">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="L2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M2">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -2491,153 +2509,210 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C3">
         <v>1</v>
       </c>
+      <c r="D3">
+        <v>7</v>
+      </c>
+      <c r="E3">
+        <v>3</v>
+      </c>
+      <c r="F3">
+        <v>4</v>
+      </c>
       <c r="G3">
-        <v>2</v>
+        <v>8</v>
+      </c>
+      <c r="H3">
+        <v>4</v>
       </c>
       <c r="I3">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="J3">
-        <v>1</v>
+        <v>4</v>
+      </c>
+      <c r="K3">
+        <v>10</v>
       </c>
       <c r="L3">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="E4">
-        <v>2</v>
-      </c>
-      <c r="J4">
-        <v>1</v>
-      </c>
-      <c r="K4">
+        <v>3</v>
+      </c>
+      <c r="H4">
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B5">
         <v>1</v>
       </c>
-      <c r="C5">
-        <v>1</v>
-      </c>
-      <c r="D5">
-        <v>2</v>
-      </c>
-      <c r="E5">
-        <v>2</v>
-      </c>
-      <c r="G5">
-        <v>1</v>
-      </c>
-      <c r="I5">
-        <v>1</v>
-      </c>
-      <c r="J5">
-        <v>3</v>
-      </c>
       <c r="K5">
-        <v>4</v>
-      </c>
-      <c r="M5">
         <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B6">
-        <v>8</v>
-      </c>
-      <c r="C6">
-        <v>13</v>
-      </c>
-      <c r="D6">
-        <v>10</v>
-      </c>
-      <c r="E6">
-        <v>9</v>
-      </c>
-      <c r="F6">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G6">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="H6">
         <v>1</v>
       </c>
       <c r="I6">
-        <v>4</v>
-      </c>
-      <c r="J6">
-        <v>5</v>
-      </c>
-      <c r="K6">
-        <v>8</v>
-      </c>
-      <c r="L6">
-        <v>3</v>
-      </c>
-      <c r="M6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D7">
+        <v>1</v>
+      </c>
+      <c r="E7">
+        <v>1</v>
+      </c>
+      <c r="J7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13">
+      <c r="A8" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8">
+        <v>5</v>
+      </c>
+      <c r="C8">
+        <v>9</v>
+      </c>
+      <c r="D8">
+        <v>17</v>
+      </c>
+      <c r="E8">
+        <v>13</v>
+      </c>
+      <c r="F8">
+        <v>19</v>
+      </c>
+      <c r="G8">
+        <v>15</v>
+      </c>
+      <c r="H8">
+        <v>5</v>
+      </c>
+      <c r="I8">
+        <v>15</v>
+      </c>
+      <c r="J8">
+        <v>12</v>
+      </c>
+      <c r="K8">
+        <v>18</v>
+      </c>
+      <c r="L8">
+        <v>19</v>
+      </c>
+      <c r="M8">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13">
+      <c r="A9" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B9">
+        <v>43</v>
+      </c>
+      <c r="C9">
+        <v>46</v>
+      </c>
+      <c r="D9">
+        <v>32</v>
+      </c>
+      <c r="E9">
+        <v>30</v>
+      </c>
+      <c r="F9">
+        <v>34</v>
+      </c>
+      <c r="G9">
+        <v>15</v>
+      </c>
+      <c r="H9">
+        <v>17</v>
+      </c>
+      <c r="I9">
+        <v>20</v>
+      </c>
+      <c r="J9">
+        <v>20</v>
+      </c>
+      <c r="K9">
+        <v>20</v>
+      </c>
+      <c r="L9">
+        <v>13</v>
+      </c>
+      <c r="M9">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13">
+      <c r="A10" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B7">
-        <v>10</v>
-      </c>
-      <c r="C7">
-        <v>15</v>
-      </c>
-      <c r="D7">
-        <v>13</v>
-      </c>
-      <c r="E7">
-        <v>13</v>
-      </c>
-      <c r="F7">
-        <v>10</v>
-      </c>
-      <c r="G7">
-        <v>12</v>
-      </c>
-      <c r="H7">
-        <v>1</v>
-      </c>
-      <c r="I7">
-        <v>8</v>
-      </c>
-      <c r="J7">
-        <v>14</v>
-      </c>
-      <c r="K7">
-        <v>15</v>
-      </c>
-      <c r="L7">
-        <v>6</v>
-      </c>
-      <c r="M7">
-        <v>5</v>
+      <c r="B10">
+        <v>51</v>
+      </c>
+      <c r="C10">
+        <v>57</v>
+      </c>
+      <c r="D10">
+        <v>62</v>
+      </c>
+      <c r="E10">
+        <v>48</v>
+      </c>
+      <c r="F10">
+        <v>60</v>
+      </c>
+      <c r="G10">
+        <v>40</v>
+      </c>
+      <c r="H10">
+        <v>31</v>
+      </c>
+      <c r="I10">
+        <v>44</v>
+      </c>
+      <c r="J10">
+        <v>43</v>
+      </c>
+      <c r="K10">
+        <v>57</v>
+      </c>
+      <c r="L10">
+        <v>40</v>
+      </c>
+      <c r="M10">
+        <v>18</v>
       </c>
     </row>
   </sheetData>
@@ -2647,10 +2722,10 @@
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M7"/>
+  <dimension ref="A1:M10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="18.7109375" customWidth="1"/>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
     <col min="2" max="2" width="4.7109375" customWidth="1"/>
     <col min="3" max="3" width="4.7109375" customWidth="1"/>
     <col min="4" max="4" width="4.7109375" customWidth="1"/>
@@ -2710,29 +2785,41 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
+      <c r="B2">
+        <v>4</v>
+      </c>
       <c r="C2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E2">
-        <v>1</v>
+        <v>5</v>
+      </c>
+      <c r="F2">
+        <v>9</v>
+      </c>
+      <c r="G2">
+        <v>3</v>
       </c>
       <c r="H2">
-        <v>2</v>
+        <v>5</v>
+      </c>
+      <c r="I2">
+        <v>4</v>
       </c>
       <c r="J2">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="K2">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="L2">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="M2">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -2740,162 +2827,210 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C3">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D3">
-        <v>1</v>
+        <v>6</v>
+      </c>
+      <c r="E3">
+        <v>7</v>
       </c>
       <c r="F3">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G3">
-        <v>1</v>
+        <v>7</v>
+      </c>
+      <c r="H3">
+        <v>8</v>
       </c>
       <c r="I3">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J3">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="K3">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="L3">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="M3">
-        <v>2</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H4">
+        <v>3</v>
+      </c>
+      <c r="I4">
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B5">
-        <v>7</v>
-      </c>
-      <c r="C5">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="D5">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E5">
-        <v>5</v>
-      </c>
-      <c r="F5">
-        <v>5</v>
-      </c>
-      <c r="G5">
-        <v>6</v>
-      </c>
-      <c r="H5">
-        <v>2</v>
-      </c>
-      <c r="I5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J5">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K5">
-        <v>6</v>
-      </c>
-      <c r="L5">
-        <v>6</v>
+        <v>2</v>
+      </c>
+      <c r="M5">
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B6">
-        <v>15</v>
-      </c>
-      <c r="C6">
-        <v>16</v>
-      </c>
-      <c r="D6">
-        <v>15</v>
-      </c>
-      <c r="E6">
-        <v>16</v>
-      </c>
-      <c r="F6">
-        <v>11</v>
-      </c>
-      <c r="G6">
-        <v>9</v>
-      </c>
-      <c r="H6">
-        <v>5</v>
-      </c>
-      <c r="I6">
-        <v>5</v>
-      </c>
-      <c r="J6">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="K6">
-        <v>6</v>
-      </c>
-      <c r="L6">
-        <v>4</v>
-      </c>
-      <c r="M6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="L7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13">
+      <c r="A8" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8">
+        <v>23</v>
+      </c>
+      <c r="C8">
+        <v>31</v>
+      </c>
+      <c r="D8">
+        <v>22</v>
+      </c>
+      <c r="E8">
+        <v>44</v>
+      </c>
+      <c r="F8">
+        <v>38</v>
+      </c>
+      <c r="G8">
+        <v>24</v>
+      </c>
+      <c r="H8">
+        <v>50</v>
+      </c>
+      <c r="I8">
+        <v>34</v>
+      </c>
+      <c r="J8">
+        <v>26</v>
+      </c>
+      <c r="K8">
+        <v>24</v>
+      </c>
+      <c r="L8">
+        <v>14</v>
+      </c>
+      <c r="M8">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13">
+      <c r="A9" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B9">
+        <v>46</v>
+      </c>
+      <c r="C9">
+        <v>59</v>
+      </c>
+      <c r="D9">
+        <v>33</v>
+      </c>
+      <c r="E9">
+        <v>73</v>
+      </c>
+      <c r="F9">
+        <v>114</v>
+      </c>
+      <c r="G9">
+        <v>58</v>
+      </c>
+      <c r="H9">
+        <v>41</v>
+      </c>
+      <c r="I9">
+        <v>44</v>
+      </c>
+      <c r="J9">
+        <v>20</v>
+      </c>
+      <c r="K9">
+        <v>25</v>
+      </c>
+      <c r="L9">
+        <v>27</v>
+      </c>
+      <c r="M9">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13">
+      <c r="A10" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B7">
-        <v>24</v>
-      </c>
-      <c r="C7">
-        <v>29</v>
-      </c>
-      <c r="D7">
-        <v>25</v>
-      </c>
-      <c r="E7">
-        <v>22</v>
-      </c>
-      <c r="F7">
-        <v>19</v>
-      </c>
-      <c r="G7">
-        <v>16</v>
-      </c>
-      <c r="H7">
-        <v>10</v>
-      </c>
-      <c r="I7">
-        <v>11</v>
-      </c>
-      <c r="J7">
-        <v>20</v>
-      </c>
-      <c r="K7">
-        <v>15</v>
-      </c>
-      <c r="L7">
-        <v>16</v>
-      </c>
-      <c r="M7">
-        <v>6</v>
+      <c r="B10">
+        <v>78</v>
+      </c>
+      <c r="C10">
+        <v>99</v>
+      </c>
+      <c r="D10">
+        <v>65</v>
+      </c>
+      <c r="E10">
+        <v>130</v>
+      </c>
+      <c r="F10">
+        <v>167</v>
+      </c>
+      <c r="G10">
+        <v>92</v>
+      </c>
+      <c r="H10">
+        <v>104</v>
+      </c>
+      <c r="I10">
+        <v>89</v>
+      </c>
+      <c r="J10">
+        <v>67</v>
+      </c>
+      <c r="K10">
+        <v>71</v>
+      </c>
+      <c r="L10">
+        <v>61</v>
+      </c>
+      <c r="M10">
+        <v>51</v>
       </c>
     </row>
   </sheetData>
@@ -2971,8 +3106,23 @@
       <c r="D2">
         <v>1</v>
       </c>
+      <c r="F2">
+        <v>1</v>
+      </c>
+      <c r="G2">
+        <v>1</v>
+      </c>
+      <c r="I2">
+        <v>2</v>
+      </c>
       <c r="J2">
-        <v>1</v>
+        <v>4</v>
+      </c>
+      <c r="K2">
+        <v>2</v>
+      </c>
+      <c r="L2">
+        <v>2</v>
       </c>
       <c r="M2">
         <v>1</v>
@@ -2982,16 +3132,25 @@
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="E3">
-        <v>2</v>
+      <c r="B3">
+        <v>1</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
       </c>
       <c r="G3">
+        <v>2</v>
+      </c>
+      <c r="I3">
         <v>1</v>
       </c>
       <c r="J3">
         <v>1</v>
       </c>
       <c r="L3">
+        <v>1</v>
+      </c>
+      <c r="M3">
         <v>1</v>
       </c>
     </row>
@@ -2999,7 +3158,13 @@
       <c r="A4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C4">
+      <c r="E4">
+        <v>2</v>
+      </c>
+      <c r="J4">
+        <v>1</v>
+      </c>
+      <c r="K4">
         <v>1</v>
       </c>
     </row>
@@ -3008,22 +3173,28 @@
         <v>8</v>
       </c>
       <c r="B5">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C5">
-        <v>6</v>
+        <v>1</v>
+      </c>
+      <c r="D5">
+        <v>2</v>
       </c>
       <c r="E5">
-        <v>1</v>
-      </c>
-      <c r="H5">
-        <v>2</v>
+        <v>2</v>
+      </c>
+      <c r="G5">
+        <v>1</v>
+      </c>
+      <c r="I5">
+        <v>1</v>
       </c>
       <c r="J5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M5">
         <v>1</v>
@@ -3034,40 +3205,40 @@
         <v>9</v>
       </c>
       <c r="B6">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C6">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="D6">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E6">
+        <v>9</v>
+      </c>
+      <c r="F6">
+        <v>9</v>
+      </c>
+      <c r="G6">
         <v>8</v>
       </c>
-      <c r="F6">
-        <v>7</v>
-      </c>
-      <c r="G6">
-        <v>2</v>
-      </c>
       <c r="H6">
         <v>1</v>
       </c>
       <c r="I6">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J6">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K6">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="L6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -3075,40 +3246,40 @@
         <v>10</v>
       </c>
       <c r="B7">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C7">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D7">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="E7">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F7">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G7">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="H7">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I7">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="J7">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="K7">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="L7">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="M7">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -3117,6 +3288,477 @@
 </file>
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:M7"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="18.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+    <col min="13" max="13" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="M1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
+      <c r="H2">
+        <v>2</v>
+      </c>
+      <c r="J2">
+        <v>1</v>
+      </c>
+      <c r="K2">
+        <v>2</v>
+      </c>
+      <c r="L2">
+        <v>2</v>
+      </c>
+      <c r="M2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>2</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
+      <c r="F3">
+        <v>3</v>
+      </c>
+      <c r="G3">
+        <v>1</v>
+      </c>
+      <c r="I3">
+        <v>4</v>
+      </c>
+      <c r="J3">
+        <v>2</v>
+      </c>
+      <c r="K3">
+        <v>1</v>
+      </c>
+      <c r="L3">
+        <v>4</v>
+      </c>
+      <c r="M3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5">
+        <v>7</v>
+      </c>
+      <c r="C5">
+        <v>11</v>
+      </c>
+      <c r="D5">
+        <v>8</v>
+      </c>
+      <c r="E5">
+        <v>5</v>
+      </c>
+      <c r="F5">
+        <v>5</v>
+      </c>
+      <c r="G5">
+        <v>6</v>
+      </c>
+      <c r="H5">
+        <v>2</v>
+      </c>
+      <c r="I5">
+        <v>2</v>
+      </c>
+      <c r="J5">
+        <v>5</v>
+      </c>
+      <c r="K5">
+        <v>6</v>
+      </c>
+      <c r="L5">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6">
+        <v>15</v>
+      </c>
+      <c r="C6">
+        <v>16</v>
+      </c>
+      <c r="D6">
+        <v>15</v>
+      </c>
+      <c r="E6">
+        <v>16</v>
+      </c>
+      <c r="F6">
+        <v>11</v>
+      </c>
+      <c r="G6">
+        <v>9</v>
+      </c>
+      <c r="H6">
+        <v>5</v>
+      </c>
+      <c r="I6">
+        <v>5</v>
+      </c>
+      <c r="J6">
+        <v>12</v>
+      </c>
+      <c r="K6">
+        <v>6</v>
+      </c>
+      <c r="L6">
+        <v>4</v>
+      </c>
+      <c r="M6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7">
+        <v>24</v>
+      </c>
+      <c r="C7">
+        <v>29</v>
+      </c>
+      <c r="D7">
+        <v>25</v>
+      </c>
+      <c r="E7">
+        <v>22</v>
+      </c>
+      <c r="F7">
+        <v>19</v>
+      </c>
+      <c r="G7">
+        <v>16</v>
+      </c>
+      <c r="H7">
+        <v>10</v>
+      </c>
+      <c r="I7">
+        <v>11</v>
+      </c>
+      <c r="J7">
+        <v>20</v>
+      </c>
+      <c r="K7">
+        <v>15</v>
+      </c>
+      <c r="L7">
+        <v>16</v>
+      </c>
+      <c r="M7">
+        <v>6</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:M7"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+    <col min="13" max="13" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="M1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="J2">
+        <v>1</v>
+      </c>
+      <c r="M2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E3">
+        <v>2</v>
+      </c>
+      <c r="G3">
+        <v>1</v>
+      </c>
+      <c r="J3">
+        <v>1</v>
+      </c>
+      <c r="L3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5">
+        <v>5</v>
+      </c>
+      <c r="C5">
+        <v>6</v>
+      </c>
+      <c r="E5">
+        <v>1</v>
+      </c>
+      <c r="H5">
+        <v>2</v>
+      </c>
+      <c r="J5">
+        <v>4</v>
+      </c>
+      <c r="K5">
+        <v>2</v>
+      </c>
+      <c r="M5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6">
+        <v>6</v>
+      </c>
+      <c r="C6">
+        <v>2</v>
+      </c>
+      <c r="D6">
+        <v>6</v>
+      </c>
+      <c r="E6">
+        <v>8</v>
+      </c>
+      <c r="F6">
+        <v>7</v>
+      </c>
+      <c r="G6">
+        <v>2</v>
+      </c>
+      <c r="H6">
+        <v>1</v>
+      </c>
+      <c r="I6">
+        <v>1</v>
+      </c>
+      <c r="J6">
+        <v>3</v>
+      </c>
+      <c r="K6">
+        <v>1</v>
+      </c>
+      <c r="L6">
+        <v>2</v>
+      </c>
+      <c r="M6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7">
+        <v>11</v>
+      </c>
+      <c r="C7">
+        <v>9</v>
+      </c>
+      <c r="D7">
+        <v>7</v>
+      </c>
+      <c r="E7">
+        <v>11</v>
+      </c>
+      <c r="F7">
+        <v>7</v>
+      </c>
+      <c r="G7">
+        <v>3</v>
+      </c>
+      <c r="H7">
+        <v>3</v>
+      </c>
+      <c r="I7">
+        <v>1</v>
+      </c>
+      <c r="J7">
+        <v>9</v>
+      </c>
+      <c r="K7">
+        <v>3</v>
+      </c>
+      <c r="L7">
+        <v>3</v>
+      </c>
+      <c r="M7">
+        <v>3</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:L8"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -3287,656 +3929,6 @@
       </c>
       <c r="L8">
         <v>2</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M10"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" customWidth="1"/>
-    <col min="13" max="13" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="M1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2">
-        <v>6</v>
-      </c>
-      <c r="C2">
-        <v>3</v>
-      </c>
-      <c r="D2">
-        <v>12</v>
-      </c>
-      <c r="E2">
-        <v>5</v>
-      </c>
-      <c r="F2">
-        <v>8</v>
-      </c>
-      <c r="G2">
-        <v>4</v>
-      </c>
-      <c r="H2">
-        <v>13</v>
-      </c>
-      <c r="I2">
-        <v>14</v>
-      </c>
-      <c r="J2">
-        <v>22</v>
-      </c>
-      <c r="K2">
-        <v>15</v>
-      </c>
-      <c r="L2">
-        <v>15</v>
-      </c>
-      <c r="M2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3">
-        <v>13</v>
-      </c>
-      <c r="C3">
-        <v>13</v>
-      </c>
-      <c r="D3">
-        <v>17</v>
-      </c>
-      <c r="E3">
-        <v>18</v>
-      </c>
-      <c r="F3">
-        <v>14</v>
-      </c>
-      <c r="G3">
-        <v>26</v>
-      </c>
-      <c r="H3">
-        <v>23</v>
-      </c>
-      <c r="I3">
-        <v>32</v>
-      </c>
-      <c r="J3">
-        <v>40</v>
-      </c>
-      <c r="K3">
-        <v>26</v>
-      </c>
-      <c r="L3">
-        <v>34</v>
-      </c>
-      <c r="M3">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="G4">
-        <v>1</v>
-      </c>
-      <c r="J4">
-        <v>2</v>
-      </c>
-      <c r="K4">
-        <v>1</v>
-      </c>
-      <c r="L4">
-        <v>1</v>
-      </c>
-      <c r="M4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C5">
-        <v>2</v>
-      </c>
-      <c r="D5">
-        <v>1</v>
-      </c>
-      <c r="E5">
-        <v>2</v>
-      </c>
-      <c r="F5">
-        <v>1</v>
-      </c>
-      <c r="H5">
-        <v>2</v>
-      </c>
-      <c r="I5">
-        <v>4</v>
-      </c>
-      <c r="J5">
-        <v>3</v>
-      </c>
-      <c r="K5">
-        <v>2</v>
-      </c>
-      <c r="L5">
-        <v>5</v>
-      </c>
-      <c r="M5">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="G6">
-        <v>1</v>
-      </c>
-      <c r="H6">
-        <v>2</v>
-      </c>
-      <c r="J6">
-        <v>2</v>
-      </c>
-      <c r="L6">
-        <v>2</v>
-      </c>
-      <c r="M6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
-      <c r="A7" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="K7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13">
-      <c r="A8" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B8">
-        <v>30</v>
-      </c>
-      <c r="C8">
-        <v>44</v>
-      </c>
-      <c r="D8">
-        <v>49</v>
-      </c>
-      <c r="E8">
-        <v>67</v>
-      </c>
-      <c r="F8">
-        <v>69</v>
-      </c>
-      <c r="G8">
-        <v>57</v>
-      </c>
-      <c r="H8">
-        <v>80</v>
-      </c>
-      <c r="I8">
-        <v>80</v>
-      </c>
-      <c r="J8">
-        <v>64</v>
-      </c>
-      <c r="K8">
-        <v>48</v>
-      </c>
-      <c r="L8">
-        <v>44</v>
-      </c>
-      <c r="M8">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13">
-      <c r="A9" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B9">
-        <v>233</v>
-      </c>
-      <c r="C9">
-        <v>354</v>
-      </c>
-      <c r="D9">
-        <v>538</v>
-      </c>
-      <c r="E9">
-        <v>705</v>
-      </c>
-      <c r="F9">
-        <v>568</v>
-      </c>
-      <c r="G9">
-        <v>168</v>
-      </c>
-      <c r="H9">
-        <v>116</v>
-      </c>
-      <c r="I9">
-        <v>194</v>
-      </c>
-      <c r="J9">
-        <v>122</v>
-      </c>
-      <c r="K9">
-        <v>114</v>
-      </c>
-      <c r="L9">
-        <v>95</v>
-      </c>
-      <c r="M9">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13">
-      <c r="A10" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B10">
-        <v>282</v>
-      </c>
-      <c r="C10">
-        <v>416</v>
-      </c>
-      <c r="D10">
-        <v>617</v>
-      </c>
-      <c r="E10">
-        <v>797</v>
-      </c>
-      <c r="F10">
-        <v>660</v>
-      </c>
-      <c r="G10">
-        <v>257</v>
-      </c>
-      <c r="H10">
-        <v>236</v>
-      </c>
-      <c r="I10">
-        <v>324</v>
-      </c>
-      <c r="J10">
-        <v>255</v>
-      </c>
-      <c r="K10">
-        <v>207</v>
-      </c>
-      <c r="L10">
-        <v>196</v>
-      </c>
-      <c r="M10">
-        <v>90</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M8"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" customWidth="1"/>
-    <col min="13" max="13" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="M1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2">
-        <v>4</v>
-      </c>
-      <c r="D2">
-        <v>1</v>
-      </c>
-      <c r="E2">
-        <v>4</v>
-      </c>
-      <c r="F2">
-        <v>2</v>
-      </c>
-      <c r="G2">
-        <v>4</v>
-      </c>
-      <c r="H2">
-        <v>2</v>
-      </c>
-      <c r="I2">
-        <v>3</v>
-      </c>
-      <c r="J2">
-        <v>2</v>
-      </c>
-      <c r="K2">
-        <v>6</v>
-      </c>
-      <c r="L2">
-        <v>6</v>
-      </c>
-      <c r="M2">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3">
-        <v>2</v>
-      </c>
-      <c r="C3">
-        <v>4</v>
-      </c>
-      <c r="D3">
-        <v>1</v>
-      </c>
-      <c r="E3">
-        <v>4</v>
-      </c>
-      <c r="F3">
-        <v>5</v>
-      </c>
-      <c r="G3">
-        <v>4</v>
-      </c>
-      <c r="H3">
-        <v>7</v>
-      </c>
-      <c r="I3">
-        <v>2</v>
-      </c>
-      <c r="J3">
-        <v>11</v>
-      </c>
-      <c r="K3">
-        <v>5</v>
-      </c>
-      <c r="L3">
-        <v>7</v>
-      </c>
-      <c r="M3">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="H4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C5">
-        <v>1</v>
-      </c>
-      <c r="H5">
-        <v>1</v>
-      </c>
-      <c r="I5">
-        <v>1</v>
-      </c>
-      <c r="K5">
-        <v>3</v>
-      </c>
-      <c r="L5">
-        <v>2</v>
-      </c>
-      <c r="M5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C6">
-        <v>14</v>
-      </c>
-      <c r="D6">
-        <v>12</v>
-      </c>
-      <c r="E6">
-        <v>10</v>
-      </c>
-      <c r="F6">
-        <v>11</v>
-      </c>
-      <c r="G6">
-        <v>11</v>
-      </c>
-      <c r="H6">
-        <v>17</v>
-      </c>
-      <c r="I6">
-        <v>20</v>
-      </c>
-      <c r="J6">
-        <v>3</v>
-      </c>
-      <c r="K6">
-        <v>10</v>
-      </c>
-      <c r="L6">
-        <v>5</v>
-      </c>
-      <c r="M6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
-      <c r="A7" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B7">
-        <v>58</v>
-      </c>
-      <c r="C7">
-        <v>53</v>
-      </c>
-      <c r="D7">
-        <v>43</v>
-      </c>
-      <c r="E7">
-        <v>56</v>
-      </c>
-      <c r="F7">
-        <v>53</v>
-      </c>
-      <c r="G7">
-        <v>33</v>
-      </c>
-      <c r="H7">
-        <v>23</v>
-      </c>
-      <c r="I7">
-        <v>26</v>
-      </c>
-      <c r="J7">
-        <v>27</v>
-      </c>
-      <c r="K7">
-        <v>17</v>
-      </c>
-      <c r="L7">
-        <v>19</v>
-      </c>
-      <c r="M7">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13">
-      <c r="A8" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B8">
-        <v>60</v>
-      </c>
-      <c r="C8">
-        <v>76</v>
-      </c>
-      <c r="D8">
-        <v>57</v>
-      </c>
-      <c r="E8">
-        <v>74</v>
-      </c>
-      <c r="F8">
-        <v>71</v>
-      </c>
-      <c r="G8">
-        <v>52</v>
-      </c>
-      <c r="H8">
-        <v>51</v>
-      </c>
-      <c r="I8">
-        <v>52</v>
-      </c>
-      <c r="J8">
-        <v>43</v>
-      </c>
-      <c r="K8">
-        <v>41</v>
-      </c>
-      <c r="L8">
-        <v>39</v>
-      </c>
-      <c r="M8">
-        <v>25</v>
       </c>
     </row>
   </sheetData>
@@ -7903,40 +7895,40 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D2">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="E2">
         <v>5</v>
       </c>
       <c r="F2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H2">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="I2">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="J2">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="K2">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="L2">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="M2">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -7944,47 +7936,59 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="C3">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="D3">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="E3">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="F3">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="G3">
-        <v>7</v>
+        <v>26</v>
       </c>
       <c r="H3">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="I3">
-        <v>6</v>
+        <v>32</v>
       </c>
       <c r="J3">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="K3">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="L3">
-        <v>14</v>
+        <v>34</v>
       </c>
       <c r="M3">
-        <v>11</v>
+        <v>16</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="I4">
+      <c r="G4">
+        <v>1</v>
+      </c>
+      <c r="J4">
+        <v>2</v>
+      </c>
+      <c r="K4">
+        <v>1</v>
+      </c>
+      <c r="L4">
+        <v>1</v>
+      </c>
+      <c r="M4">
         <v>1</v>
       </c>
     </row>
@@ -7992,14 +7996,23 @@
       <c r="A5" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B5">
-        <v>1</v>
+      <c r="C5">
+        <v>2</v>
       </c>
       <c r="D5">
         <v>1</v>
       </c>
       <c r="E5">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="F5">
+        <v>1</v>
+      </c>
+      <c r="H5">
+        <v>2</v>
+      </c>
+      <c r="I5">
+        <v>4</v>
       </c>
       <c r="J5">
         <v>3</v>
@@ -8007,15 +8020,30 @@
       <c r="K5">
         <v>2</v>
       </c>
+      <c r="L5">
+        <v>5</v>
+      </c>
       <c r="M5">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="K6">
+      <c r="G6">
+        <v>1</v>
+      </c>
+      <c r="H6">
+        <v>2</v>
+      </c>
+      <c r="J6">
+        <v>2</v>
+      </c>
+      <c r="L6">
+        <v>2</v>
+      </c>
+      <c r="M6">
         <v>1</v>
       </c>
     </row>
@@ -8023,7 +8051,7 @@
       <c r="A7" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="L7">
+      <c r="K7">
         <v>1</v>
       </c>
     </row>
@@ -8032,40 +8060,40 @@
         <v>8</v>
       </c>
       <c r="B8">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="C8">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="D8">
-        <v>22</v>
+        <v>49</v>
       </c>
       <c r="E8">
+        <v>67</v>
+      </c>
+      <c r="F8">
+        <v>69</v>
+      </c>
+      <c r="G8">
+        <v>57</v>
+      </c>
+      <c r="H8">
+        <v>80</v>
+      </c>
+      <c r="I8">
+        <v>80</v>
+      </c>
+      <c r="J8">
+        <v>64</v>
+      </c>
+      <c r="K8">
+        <v>48</v>
+      </c>
+      <c r="L8">
         <v>44</v>
       </c>
-      <c r="F8">
-        <v>38</v>
-      </c>
-      <c r="G8">
-        <v>24</v>
-      </c>
-      <c r="H8">
-        <v>50</v>
-      </c>
-      <c r="I8">
-        <v>34</v>
-      </c>
-      <c r="J8">
-        <v>26</v>
-      </c>
-      <c r="K8">
-        <v>24</v>
-      </c>
-      <c r="L8">
-        <v>14</v>
-      </c>
       <c r="M8">
-        <v>14</v>
+        <v>20</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -8073,40 +8101,40 @@
         <v>9</v>
       </c>
       <c r="B9">
+        <v>233</v>
+      </c>
+      <c r="C9">
+        <v>354</v>
+      </c>
+      <c r="D9">
+        <v>538</v>
+      </c>
+      <c r="E9">
+        <v>705</v>
+      </c>
+      <c r="F9">
+        <v>568</v>
+      </c>
+      <c r="G9">
+        <v>168</v>
+      </c>
+      <c r="H9">
+        <v>116</v>
+      </c>
+      <c r="I9">
+        <v>194</v>
+      </c>
+      <c r="J9">
+        <v>122</v>
+      </c>
+      <c r="K9">
+        <v>114</v>
+      </c>
+      <c r="L9">
+        <v>95</v>
+      </c>
+      <c r="M9">
         <v>46</v>
-      </c>
-      <c r="C9">
-        <v>59</v>
-      </c>
-      <c r="D9">
-        <v>33</v>
-      </c>
-      <c r="E9">
-        <v>73</v>
-      </c>
-      <c r="F9">
-        <v>114</v>
-      </c>
-      <c r="G9">
-        <v>58</v>
-      </c>
-      <c r="H9">
-        <v>41</v>
-      </c>
-      <c r="I9">
-        <v>44</v>
-      </c>
-      <c r="J9">
-        <v>20</v>
-      </c>
-      <c r="K9">
-        <v>25</v>
-      </c>
-      <c r="L9">
-        <v>27</v>
-      </c>
-      <c r="M9">
-        <v>16</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -8114,40 +8142,40 @@
         <v>10</v>
       </c>
       <c r="B10">
-        <v>78</v>
+        <v>282</v>
       </c>
       <c r="C10">
-        <v>99</v>
+        <v>416</v>
       </c>
       <c r="D10">
-        <v>65</v>
+        <v>617</v>
       </c>
       <c r="E10">
-        <v>130</v>
+        <v>797</v>
       </c>
       <c r="F10">
-        <v>167</v>
+        <v>660</v>
       </c>
       <c r="G10">
-        <v>92</v>
+        <v>257</v>
       </c>
       <c r="H10">
-        <v>104</v>
+        <v>236</v>
       </c>
       <c r="I10">
-        <v>89</v>
+        <v>324</v>
       </c>
       <c r="J10">
-        <v>67</v>
+        <v>255</v>
       </c>
       <c r="K10">
-        <v>71</v>
+        <v>207</v>
       </c>
       <c r="L10">
-        <v>61</v>
+        <v>196</v>
       </c>
       <c r="M10">
-        <v>51</v>
+        <v>90</v>
       </c>
     </row>
   </sheetData>
@@ -8156,6 +8184,302 @@
 </file>
 
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:M8"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+    <col min="13" max="13" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="M1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>4</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="E2">
+        <v>4</v>
+      </c>
+      <c r="F2">
+        <v>2</v>
+      </c>
+      <c r="G2">
+        <v>4</v>
+      </c>
+      <c r="H2">
+        <v>2</v>
+      </c>
+      <c r="I2">
+        <v>3</v>
+      </c>
+      <c r="J2">
+        <v>2</v>
+      </c>
+      <c r="K2">
+        <v>6</v>
+      </c>
+      <c r="L2">
+        <v>6</v>
+      </c>
+      <c r="M2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>2</v>
+      </c>
+      <c r="C3">
+        <v>4</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
+      <c r="E3">
+        <v>4</v>
+      </c>
+      <c r="F3">
+        <v>5</v>
+      </c>
+      <c r="G3">
+        <v>4</v>
+      </c>
+      <c r="H3">
+        <v>7</v>
+      </c>
+      <c r="I3">
+        <v>2</v>
+      </c>
+      <c r="J3">
+        <v>11</v>
+      </c>
+      <c r="K3">
+        <v>5</v>
+      </c>
+      <c r="L3">
+        <v>7</v>
+      </c>
+      <c r="M3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="H4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C5">
+        <v>1</v>
+      </c>
+      <c r="H5">
+        <v>1</v>
+      </c>
+      <c r="I5">
+        <v>1</v>
+      </c>
+      <c r="K5">
+        <v>3</v>
+      </c>
+      <c r="L5">
+        <v>2</v>
+      </c>
+      <c r="M5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C6">
+        <v>14</v>
+      </c>
+      <c r="D6">
+        <v>12</v>
+      </c>
+      <c r="E6">
+        <v>10</v>
+      </c>
+      <c r="F6">
+        <v>11</v>
+      </c>
+      <c r="G6">
+        <v>11</v>
+      </c>
+      <c r="H6">
+        <v>17</v>
+      </c>
+      <c r="I6">
+        <v>20</v>
+      </c>
+      <c r="J6">
+        <v>3</v>
+      </c>
+      <c r="K6">
+        <v>10</v>
+      </c>
+      <c r="L6">
+        <v>5</v>
+      </c>
+      <c r="M6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7">
+        <v>58</v>
+      </c>
+      <c r="C7">
+        <v>53</v>
+      </c>
+      <c r="D7">
+        <v>43</v>
+      </c>
+      <c r="E7">
+        <v>56</v>
+      </c>
+      <c r="F7">
+        <v>53</v>
+      </c>
+      <c r="G7">
+        <v>33</v>
+      </c>
+      <c r="H7">
+        <v>23</v>
+      </c>
+      <c r="I7">
+        <v>26</v>
+      </c>
+      <c r="J7">
+        <v>27</v>
+      </c>
+      <c r="K7">
+        <v>17</v>
+      </c>
+      <c r="L7">
+        <v>19</v>
+      </c>
+      <c r="M7">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13">
+      <c r="A8" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B8">
+        <v>60</v>
+      </c>
+      <c r="C8">
+        <v>76</v>
+      </c>
+      <c r="D8">
+        <v>57</v>
+      </c>
+      <c r="E8">
+        <v>74</v>
+      </c>
+      <c r="F8">
+        <v>71</v>
+      </c>
+      <c r="G8">
+        <v>52</v>
+      </c>
+      <c r="H8">
+        <v>51</v>
+      </c>
+      <c r="I8">
+        <v>52</v>
+      </c>
+      <c r="J8">
+        <v>43</v>
+      </c>
+      <c r="K8">
+        <v>41</v>
+      </c>
+      <c r="L8">
+        <v>39</v>
+      </c>
+      <c r="M8">
+        <v>25</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -8426,7 +8750,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:D4"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -8489,7 +8813,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M9"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -8756,330 +9080,6 @@
       </c>
       <c r="M9">
         <v>7</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M10"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" customWidth="1"/>
-    <col min="13" max="13" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="M1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2">
-        <v>5</v>
-      </c>
-      <c r="C2">
-        <v>3</v>
-      </c>
-      <c r="D2">
-        <v>7</v>
-      </c>
-      <c r="E2">
-        <v>5</v>
-      </c>
-      <c r="F2">
-        <v>5</v>
-      </c>
-      <c r="G2">
-        <v>4</v>
-      </c>
-      <c r="H2">
-        <v>6</v>
-      </c>
-      <c r="I2">
-        <v>4</v>
-      </c>
-      <c r="J2">
-        <v>7</v>
-      </c>
-      <c r="K2">
-        <v>7</v>
-      </c>
-      <c r="L2">
-        <v>5</v>
-      </c>
-      <c r="M2">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3">
-        <v>3</v>
-      </c>
-      <c r="C3">
-        <v>2</v>
-      </c>
-      <c r="D3">
-        <v>8</v>
-      </c>
-      <c r="E3">
-        <v>9</v>
-      </c>
-      <c r="F3">
-        <v>19</v>
-      </c>
-      <c r="G3">
-        <v>9</v>
-      </c>
-      <c r="H3">
-        <v>8</v>
-      </c>
-      <c r="I3">
-        <v>13</v>
-      </c>
-      <c r="J3">
-        <v>12</v>
-      </c>
-      <c r="K3">
-        <v>17</v>
-      </c>
-      <c r="L3">
-        <v>13</v>
-      </c>
-      <c r="M3">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="I4">
-        <v>1</v>
-      </c>
-      <c r="M4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="K5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="E6">
-        <v>1</v>
-      </c>
-      <c r="F6">
-        <v>2</v>
-      </c>
-      <c r="J6">
-        <v>2</v>
-      </c>
-      <c r="M6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
-      <c r="A7" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E7">
-        <v>1</v>
-      </c>
-      <c r="I7">
-        <v>1</v>
-      </c>
-      <c r="K7">
-        <v>1</v>
-      </c>
-      <c r="L7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13">
-      <c r="A8" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B8">
-        <v>24</v>
-      </c>
-      <c r="C8">
-        <v>37</v>
-      </c>
-      <c r="D8">
-        <v>21</v>
-      </c>
-      <c r="E8">
-        <v>22</v>
-      </c>
-      <c r="F8">
-        <v>27</v>
-      </c>
-      <c r="G8">
-        <v>15</v>
-      </c>
-      <c r="H8">
-        <v>25</v>
-      </c>
-      <c r="I8">
-        <v>21</v>
-      </c>
-      <c r="J8">
-        <v>26</v>
-      </c>
-      <c r="K8">
-        <v>49</v>
-      </c>
-      <c r="L8">
-        <v>44</v>
-      </c>
-      <c r="M8">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13">
-      <c r="A9" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B9">
-        <v>45</v>
-      </c>
-      <c r="C9">
-        <v>64</v>
-      </c>
-      <c r="D9">
-        <v>46</v>
-      </c>
-      <c r="E9">
-        <v>50</v>
-      </c>
-      <c r="F9">
-        <v>38</v>
-      </c>
-      <c r="G9">
-        <v>19</v>
-      </c>
-      <c r="H9">
-        <v>27</v>
-      </c>
-      <c r="I9">
-        <v>37</v>
-      </c>
-      <c r="J9">
-        <v>20</v>
-      </c>
-      <c r="K9">
-        <v>35</v>
-      </c>
-      <c r="L9">
-        <v>35</v>
-      </c>
-      <c r="M9">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13">
-      <c r="A10" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B10">
-        <v>77</v>
-      </c>
-      <c r="C10">
-        <v>106</v>
-      </c>
-      <c r="D10">
-        <v>82</v>
-      </c>
-      <c r="E10">
-        <v>88</v>
-      </c>
-      <c r="F10">
-        <v>91</v>
-      </c>
-      <c r="G10">
-        <v>47</v>
-      </c>
-      <c r="H10">
-        <v>66</v>
-      </c>
-      <c r="I10">
-        <v>77</v>
-      </c>
-      <c r="J10">
-        <v>67</v>
-      </c>
-      <c r="K10">
-        <v>110</v>
-      </c>
-      <c r="L10">
-        <v>98</v>
-      </c>
-      <c r="M10">
-        <v>36</v>
       </c>
     </row>
   </sheetData>
@@ -14586,6 +14586,257 @@
 
 <file path=xl/worksheets/sheet44.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:M8"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+    <col min="13" max="13" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="M1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>2</v>
+      </c>
+      <c r="F2">
+        <v>2</v>
+      </c>
+      <c r="I2">
+        <v>3</v>
+      </c>
+      <c r="J2">
+        <v>2</v>
+      </c>
+      <c r="K2">
+        <v>1</v>
+      </c>
+      <c r="L2">
+        <v>5</v>
+      </c>
+      <c r="M2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
+      <c r="E3">
+        <v>1</v>
+      </c>
+      <c r="H3">
+        <v>2</v>
+      </c>
+      <c r="I3">
+        <v>1</v>
+      </c>
+      <c r="J3">
+        <v>1</v>
+      </c>
+      <c r="K3">
+        <v>2</v>
+      </c>
+      <c r="L3">
+        <v>2</v>
+      </c>
+      <c r="M3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
+      <c r="I4">
+        <v>1</v>
+      </c>
+      <c r="K4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="L5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6">
+        <v>1</v>
+      </c>
+      <c r="F6">
+        <v>4</v>
+      </c>
+      <c r="H6">
+        <v>1</v>
+      </c>
+      <c r="I6">
+        <v>2</v>
+      </c>
+      <c r="K6">
+        <v>1</v>
+      </c>
+      <c r="M6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7">
+        <v>10</v>
+      </c>
+      <c r="C7">
+        <v>20</v>
+      </c>
+      <c r="D7">
+        <v>25</v>
+      </c>
+      <c r="E7">
+        <v>30</v>
+      </c>
+      <c r="F7">
+        <v>41</v>
+      </c>
+      <c r="G7">
+        <v>10</v>
+      </c>
+      <c r="H7">
+        <v>5</v>
+      </c>
+      <c r="I7">
+        <v>5</v>
+      </c>
+      <c r="J7">
+        <v>15</v>
+      </c>
+      <c r="K7">
+        <v>17</v>
+      </c>
+      <c r="L7">
+        <v>12</v>
+      </c>
+      <c r="M7">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13">
+      <c r="A8" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B8">
+        <v>12</v>
+      </c>
+      <c r="C8">
+        <v>22</v>
+      </c>
+      <c r="D8">
+        <v>27</v>
+      </c>
+      <c r="E8">
+        <v>31</v>
+      </c>
+      <c r="F8">
+        <v>47</v>
+      </c>
+      <c r="G8">
+        <v>10</v>
+      </c>
+      <c r="H8">
+        <v>8</v>
+      </c>
+      <c r="I8">
+        <v>12</v>
+      </c>
+      <c r="J8">
+        <v>18</v>
+      </c>
+      <c r="K8">
+        <v>22</v>
+      </c>
+      <c r="L8">
+        <v>21</v>
+      </c>
+      <c r="M8">
+        <v>16</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet45.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -14863,7 +15114,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet45.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet46.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -15079,257 +15330,6 @@
       </c>
       <c r="M6">
         <v>3</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet46.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M8"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" customWidth="1"/>
-    <col min="13" max="13" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="M1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2">
-        <v>1</v>
-      </c>
-      <c r="D2">
-        <v>2</v>
-      </c>
-      <c r="F2">
-        <v>2</v>
-      </c>
-      <c r="I2">
-        <v>3</v>
-      </c>
-      <c r="J2">
-        <v>2</v>
-      </c>
-      <c r="K2">
-        <v>1</v>
-      </c>
-      <c r="L2">
-        <v>5</v>
-      </c>
-      <c r="M2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C3">
-        <v>1</v>
-      </c>
-      <c r="E3">
-        <v>1</v>
-      </c>
-      <c r="H3">
-        <v>2</v>
-      </c>
-      <c r="I3">
-        <v>1</v>
-      </c>
-      <c r="J3">
-        <v>1</v>
-      </c>
-      <c r="K3">
-        <v>2</v>
-      </c>
-      <c r="L3">
-        <v>2</v>
-      </c>
-      <c r="M3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C4">
-        <v>1</v>
-      </c>
-      <c r="I4">
-        <v>1</v>
-      </c>
-      <c r="K4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="L5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B6">
-        <v>1</v>
-      </c>
-      <c r="F6">
-        <v>4</v>
-      </c>
-      <c r="H6">
-        <v>1</v>
-      </c>
-      <c r="I6">
-        <v>2</v>
-      </c>
-      <c r="K6">
-        <v>1</v>
-      </c>
-      <c r="M6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
-      <c r="A7" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B7">
-        <v>10</v>
-      </c>
-      <c r="C7">
-        <v>20</v>
-      </c>
-      <c r="D7">
-        <v>25</v>
-      </c>
-      <c r="E7">
-        <v>30</v>
-      </c>
-      <c r="F7">
-        <v>41</v>
-      </c>
-      <c r="G7">
-        <v>10</v>
-      </c>
-      <c r="H7">
-        <v>5</v>
-      </c>
-      <c r="I7">
-        <v>5</v>
-      </c>
-      <c r="J7">
-        <v>15</v>
-      </c>
-      <c r="K7">
-        <v>17</v>
-      </c>
-      <c r="L7">
-        <v>12</v>
-      </c>
-      <c r="M7">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13">
-      <c r="A8" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B8">
-        <v>12</v>
-      </c>
-      <c r="C8">
-        <v>22</v>
-      </c>
-      <c r="D8">
-        <v>27</v>
-      </c>
-      <c r="E8">
-        <v>31</v>
-      </c>
-      <c r="F8">
-        <v>47</v>
-      </c>
-      <c r="G8">
-        <v>10</v>
-      </c>
-      <c r="H8">
-        <v>8</v>
-      </c>
-      <c r="I8">
-        <v>12</v>
-      </c>
-      <c r="J8">
-        <v>18</v>
-      </c>
-      <c r="K8">
-        <v>22</v>
-      </c>
-      <c r="L8">
-        <v>21</v>
-      </c>
-      <c r="M8">
-        <v>16</v>
       </c>
     </row>
   </sheetData>

--- a/output/cta-index-crime-full-year.xlsx
+++ b/output/cta-index-crime-full-year.xlsx
@@ -9,10 +9,10 @@
   <sheets>
     <sheet name="Citywide Totals" sheetId="1" r:id="rId1"/>
     <sheet name="By Neighborhood" sheetId="2" r:id="rId2"/>
-    <sheet name="Austin" sheetId="3" r:id="rId3"/>
-    <sheet name="Loop" sheetId="4" r:id="rId4"/>
-    <sheet name="Old Town" sheetId="5" r:id="rId5"/>
-    <sheet name="Chatham" sheetId="6" r:id="rId6"/>
+    <sheet name="Chatham" sheetId="3" r:id="rId3"/>
+    <sheet name="Austin" sheetId="4" r:id="rId4"/>
+    <sheet name="Loop" sheetId="5" r:id="rId5"/>
+    <sheet name="Old Town" sheetId="6" r:id="rId6"/>
     <sheet name="New City" sheetId="7" r:id="rId7"/>
     <sheet name="Belmont Cragin" sheetId="8" r:id="rId8"/>
     <sheet name="Woodlawn" sheetId="9" r:id="rId9"/>
@@ -1077,7 +1077,7 @@
         <v>5</v>
       </c>
       <c r="M7">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -1197,7 +1197,7 @@
         <v>703</v>
       </c>
       <c r="M10">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -1238,7 +1238,7 @@
         <v>1604</v>
       </c>
       <c r="M11">
-        <v>800</v>
+        <v>802</v>
       </c>
     </row>
   </sheetData>
@@ -4617,7 +4617,7 @@
         <v>40</v>
       </c>
       <c r="M19">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="20" spans="1:13">
@@ -5251,7 +5251,7 @@
         <v>98</v>
       </c>
       <c r="M36">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="37" spans="1:13">
@@ -7681,7 +7681,7 @@
         <v>1604</v>
       </c>
       <c r="M99">
-        <v>800</v>
+        <v>802</v>
       </c>
     </row>
   </sheetData>
@@ -10595,41 +10595,38 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2">
-        <v>4</v>
-      </c>
       <c r="C2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F2">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="G2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J2">
+        <v>5</v>
+      </c>
+      <c r="K2">
         <v>8</v>
       </c>
-      <c r="K2">
-        <v>7</v>
-      </c>
       <c r="L2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M2">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -10637,47 +10634,47 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C3">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E3">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="F3">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G3">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H3">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="I3">
         <v>6</v>
       </c>
       <c r="J3">
+        <v>4</v>
+      </c>
+      <c r="K3">
         <v>10</v>
       </c>
-      <c r="K3">
-        <v>12</v>
-      </c>
       <c r="L3">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="M3">
-        <v>11</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="I4">
+      <c r="H4">
         <v>1</v>
       </c>
     </row>
@@ -10688,19 +10685,7 @@
       <c r="B5">
         <v>1</v>
       </c>
-      <c r="D5">
-        <v>1</v>
-      </c>
-      <c r="E5">
-        <v>1</v>
-      </c>
-      <c r="J5">
-        <v>3</v>
-      </c>
       <c r="K5">
-        <v>2</v>
-      </c>
-      <c r="M5">
         <v>1</v>
       </c>
     </row>
@@ -10708,7 +10693,13 @@
       <c r="A6" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="K6">
+      <c r="G6">
+        <v>1</v>
+      </c>
+      <c r="H6">
+        <v>1</v>
+      </c>
+      <c r="I6">
         <v>1</v>
       </c>
     </row>
@@ -10716,8 +10707,14 @@
       <c r="A7" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="L7">
-        <v>1</v>
+      <c r="D7">
+        <v>1</v>
+      </c>
+      <c r="E7">
+        <v>1</v>
+      </c>
+      <c r="J7">
+        <v>2</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -10725,40 +10722,40 @@
         <v>8</v>
       </c>
       <c r="B8">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="C8">
-        <v>31</v>
+        <v>9</v>
       </c>
       <c r="D8">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="E8">
-        <v>44</v>
+        <v>13</v>
       </c>
       <c r="F8">
-        <v>38</v>
+        <v>19</v>
       </c>
       <c r="G8">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="H8">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="I8">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="J8">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="K8">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="L8">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="M8">
-        <v>14</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -10766,40 +10763,40 @@
         <v>9</v>
       </c>
       <c r="B9">
+        <v>43</v>
+      </c>
+      <c r="C9">
         <v>46</v>
       </c>
-      <c r="C9">
-        <v>59</v>
-      </c>
       <c r="D9">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E9">
-        <v>73</v>
+        <v>30</v>
       </c>
       <c r="F9">
-        <v>114</v>
+        <v>34</v>
       </c>
       <c r="G9">
-        <v>58</v>
+        <v>15</v>
       </c>
       <c r="H9">
-        <v>41</v>
+        <v>17</v>
       </c>
       <c r="I9">
-        <v>44</v>
+        <v>20</v>
       </c>
       <c r="J9">
         <v>20</v>
       </c>
       <c r="K9">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="L9">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="M9">
-        <v>16</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -10807,40 +10804,40 @@
         <v>10</v>
       </c>
       <c r="B10">
-        <v>78</v>
+        <v>51</v>
       </c>
       <c r="C10">
-        <v>99</v>
+        <v>57</v>
       </c>
       <c r="D10">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="E10">
-        <v>130</v>
+        <v>48</v>
       </c>
       <c r="F10">
-        <v>167</v>
+        <v>60</v>
       </c>
       <c r="G10">
-        <v>92</v>
+        <v>40</v>
       </c>
       <c r="H10">
-        <v>104</v>
+        <v>31</v>
       </c>
       <c r="I10">
-        <v>89</v>
+        <v>44</v>
       </c>
       <c r="J10">
-        <v>67</v>
+        <v>43</v>
       </c>
       <c r="K10">
-        <v>71</v>
+        <v>57</v>
       </c>
       <c r="L10">
-        <v>61</v>
+        <v>40</v>
       </c>
       <c r="M10">
-        <v>51</v>
+        <v>19</v>
       </c>
     </row>
   </sheetData>
@@ -11848,6 +11845,9 @@
       <c r="L7">
         <v>1</v>
       </c>
+      <c r="M7">
+        <v>1</v>
+      </c>
     </row>
     <row r="8" spans="1:13">
       <c r="A8" s="1" t="s">
@@ -11969,7 +11969,7 @@
         <v>98</v>
       </c>
       <c r="M10">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
   </sheetData>
@@ -13481,40 +13481,40 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D2">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="E2">
         <v>5</v>
       </c>
       <c r="F2">
+        <v>9</v>
+      </c>
+      <c r="G2">
+        <v>3</v>
+      </c>
+      <c r="H2">
+        <v>5</v>
+      </c>
+      <c r="I2">
+        <v>4</v>
+      </c>
+      <c r="J2">
         <v>8</v>
       </c>
-      <c r="G2">
-        <v>4</v>
-      </c>
-      <c r="H2">
-        <v>13</v>
-      </c>
-      <c r="I2">
-        <v>14</v>
-      </c>
-      <c r="J2">
-        <v>22</v>
-      </c>
       <c r="K2">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="L2">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="M2">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -13522,59 +13522,47 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="C3">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="D3">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="E3">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="F3">
+        <v>6</v>
+      </c>
+      <c r="G3">
+        <v>7</v>
+      </c>
+      <c r="H3">
+        <v>8</v>
+      </c>
+      <c r="I3">
+        <v>6</v>
+      </c>
+      <c r="J3">
+        <v>10</v>
+      </c>
+      <c r="K3">
+        <v>12</v>
+      </c>
+      <c r="L3">
         <v>14</v>
       </c>
-      <c r="G3">
-        <v>26</v>
-      </c>
-      <c r="H3">
-        <v>23</v>
-      </c>
-      <c r="I3">
-        <v>32</v>
-      </c>
-      <c r="J3">
-        <v>40</v>
-      </c>
-      <c r="K3">
-        <v>26</v>
-      </c>
-      <c r="L3">
-        <v>34</v>
-      </c>
       <c r="M3">
-        <v>16</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="G4">
-        <v>1</v>
-      </c>
-      <c r="J4">
-        <v>2</v>
-      </c>
-      <c r="K4">
-        <v>1</v>
-      </c>
-      <c r="L4">
-        <v>1</v>
-      </c>
-      <c r="M4">
+      <c r="I4">
         <v>1</v>
       </c>
     </row>
@@ -13582,23 +13570,14 @@
       <c r="A5" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C5">
-        <v>2</v>
+      <c r="B5">
+        <v>1</v>
       </c>
       <c r="D5">
         <v>1</v>
       </c>
       <c r="E5">
-        <v>2</v>
-      </c>
-      <c r="F5">
-        <v>1</v>
-      </c>
-      <c r="H5">
-        <v>2</v>
-      </c>
-      <c r="I5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J5">
         <v>3</v>
@@ -13606,30 +13585,15 @@
       <c r="K5">
         <v>2</v>
       </c>
-      <c r="L5">
-        <v>5</v>
-      </c>
       <c r="M5">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="G6">
-        <v>1</v>
-      </c>
-      <c r="H6">
-        <v>2</v>
-      </c>
-      <c r="J6">
-        <v>2</v>
-      </c>
-      <c r="L6">
-        <v>2</v>
-      </c>
-      <c r="M6">
+      <c r="K6">
         <v>1</v>
       </c>
     </row>
@@ -13637,7 +13601,7 @@
       <c r="A7" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="K7">
+      <c r="L7">
         <v>1</v>
       </c>
     </row>
@@ -13646,40 +13610,40 @@
         <v>8</v>
       </c>
       <c r="B8">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="C8">
+        <v>31</v>
+      </c>
+      <c r="D8">
+        <v>22</v>
+      </c>
+      <c r="E8">
         <v>44</v>
       </c>
-      <c r="D8">
-        <v>49</v>
-      </c>
-      <c r="E8">
-        <v>67</v>
-      </c>
       <c r="F8">
-        <v>69</v>
+        <v>38</v>
       </c>
       <c r="G8">
-        <v>57</v>
+        <v>24</v>
       </c>
       <c r="H8">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="I8">
-        <v>80</v>
+        <v>34</v>
       </c>
       <c r="J8">
-        <v>64</v>
+        <v>26</v>
       </c>
       <c r="K8">
-        <v>48</v>
+        <v>24</v>
       </c>
       <c r="L8">
-        <v>44</v>
+        <v>14</v>
       </c>
       <c r="M8">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -13687,40 +13651,40 @@
         <v>9</v>
       </c>
       <c r="B9">
-        <v>233</v>
+        <v>46</v>
       </c>
       <c r="C9">
-        <v>354</v>
+        <v>59</v>
       </c>
       <c r="D9">
-        <v>538</v>
+        <v>33</v>
       </c>
       <c r="E9">
-        <v>705</v>
+        <v>73</v>
       </c>
       <c r="F9">
-        <v>568</v>
+        <v>114</v>
       </c>
       <c r="G9">
-        <v>168</v>
+        <v>58</v>
       </c>
       <c r="H9">
-        <v>116</v>
+        <v>41</v>
       </c>
       <c r="I9">
-        <v>194</v>
+        <v>44</v>
       </c>
       <c r="J9">
-        <v>122</v>
+        <v>20</v>
       </c>
       <c r="K9">
-        <v>114</v>
+        <v>25</v>
       </c>
       <c r="L9">
-        <v>95</v>
+        <v>27</v>
       </c>
       <c r="M9">
-        <v>46</v>
+        <v>16</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -13728,40 +13692,40 @@
         <v>10</v>
       </c>
       <c r="B10">
-        <v>282</v>
+        <v>78</v>
       </c>
       <c r="C10">
-        <v>416</v>
+        <v>99</v>
       </c>
       <c r="D10">
-        <v>617</v>
+        <v>65</v>
       </c>
       <c r="E10">
-        <v>797</v>
+        <v>130</v>
       </c>
       <c r="F10">
-        <v>660</v>
+        <v>167</v>
       </c>
       <c r="G10">
-        <v>257</v>
+        <v>92</v>
       </c>
       <c r="H10">
-        <v>236</v>
+        <v>104</v>
       </c>
       <c r="I10">
-        <v>324</v>
+        <v>89</v>
       </c>
       <c r="J10">
-        <v>255</v>
+        <v>67</v>
       </c>
       <c r="K10">
-        <v>207</v>
+        <v>71</v>
       </c>
       <c r="L10">
-        <v>196</v>
+        <v>61</v>
       </c>
       <c r="M10">
-        <v>90</v>
+        <v>51</v>
       </c>
     </row>
   </sheetData>
@@ -16239,7 +16203,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M8"/>
+  <dimension ref="A1:M10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="23.7109375" customWidth="1"/>
@@ -16302,25 +16266,40 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
+      <c r="B2">
+        <v>6</v>
+      </c>
+      <c r="C2">
+        <v>3</v>
+      </c>
       <c r="D2">
-        <v>2</v>
+        <v>12</v>
+      </c>
+      <c r="E2">
+        <v>5</v>
       </c>
       <c r="F2">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="G2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H2">
-        <v>1</v>
+        <v>13</v>
+      </c>
+      <c r="I2">
+        <v>14</v>
       </c>
       <c r="J2">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="K2">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="L2">
+        <v>15</v>
+      </c>
+      <c r="M2">
         <v>2</v>
       </c>
     </row>
@@ -16329,41 +16308,59 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>1</v>
+        <v>13</v>
+      </c>
+      <c r="C3">
+        <v>13</v>
       </c>
       <c r="D3">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="E3">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="F3">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="G3">
-        <v>1</v>
+        <v>26</v>
       </c>
       <c r="H3">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="I3">
-        <v>2</v>
+        <v>32</v>
       </c>
       <c r="J3">
-        <v>6</v>
+        <v>40</v>
       </c>
       <c r="K3">
-        <v>3</v>
+        <v>26</v>
       </c>
       <c r="L3">
-        <v>3</v>
+        <v>34</v>
+      </c>
+      <c r="M3">
+        <v>16</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B4">
+      <c r="G4">
+        <v>1</v>
+      </c>
+      <c r="J4">
+        <v>2</v>
+      </c>
+      <c r="K4">
+        <v>1</v>
+      </c>
+      <c r="L4">
+        <v>1</v>
+      </c>
+      <c r="M4">
         <v>1</v>
       </c>
     </row>
@@ -16371,131 +16368,186 @@
       <c r="A5" s="1" t="s">
         <v>5</v>
       </c>
+      <c r="C5">
+        <v>2</v>
+      </c>
+      <c r="D5">
+        <v>1</v>
+      </c>
+      <c r="E5">
+        <v>2</v>
+      </c>
+      <c r="F5">
+        <v>1</v>
+      </c>
+      <c r="H5">
+        <v>2</v>
+      </c>
+      <c r="I5">
+        <v>4</v>
+      </c>
       <c r="J5">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="K5">
+        <v>2</v>
+      </c>
+      <c r="L5">
+        <v>5</v>
+      </c>
+      <c r="M5">
+        <v>4</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B6">
-        <v>1</v>
-      </c>
-      <c r="C6">
-        <v>11</v>
-      </c>
-      <c r="D6">
-        <v>4</v>
-      </c>
-      <c r="E6">
-        <v>17</v>
-      </c>
-      <c r="F6">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="G6">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="H6">
-        <v>12</v>
-      </c>
-      <c r="I6">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="J6">
-        <v>6</v>
-      </c>
-      <c r="K6">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="L6">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="M6">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B7">
-        <v>24</v>
-      </c>
-      <c r="C7">
-        <v>26</v>
-      </c>
-      <c r="D7">
-        <v>44</v>
-      </c>
-      <c r="E7">
-        <v>57</v>
-      </c>
-      <c r="F7">
-        <v>79</v>
-      </c>
-      <c r="G7">
-        <v>24</v>
-      </c>
-      <c r="H7">
-        <v>13</v>
-      </c>
-      <c r="I7">
-        <v>15</v>
-      </c>
-      <c r="J7">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="K7">
-        <v>9</v>
-      </c>
-      <c r="L7">
-        <v>7</v>
-      </c>
-      <c r="M7">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:13">
       <c r="A8" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8">
+        <v>30</v>
+      </c>
+      <c r="C8">
+        <v>44</v>
+      </c>
+      <c r="D8">
+        <v>49</v>
+      </c>
+      <c r="E8">
+        <v>67</v>
+      </c>
+      <c r="F8">
+        <v>69</v>
+      </c>
+      <c r="G8">
+        <v>57</v>
+      </c>
+      <c r="H8">
+        <v>80</v>
+      </c>
+      <c r="I8">
+        <v>80</v>
+      </c>
+      <c r="J8">
+        <v>64</v>
+      </c>
+      <c r="K8">
+        <v>48</v>
+      </c>
+      <c r="L8">
+        <v>44</v>
+      </c>
+      <c r="M8">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13">
+      <c r="A9" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B9">
+        <v>233</v>
+      </c>
+      <c r="C9">
+        <v>354</v>
+      </c>
+      <c r="D9">
+        <v>538</v>
+      </c>
+      <c r="E9">
+        <v>705</v>
+      </c>
+      <c r="F9">
+        <v>568</v>
+      </c>
+      <c r="G9">
+        <v>168</v>
+      </c>
+      <c r="H9">
+        <v>116</v>
+      </c>
+      <c r="I9">
+        <v>194</v>
+      </c>
+      <c r="J9">
+        <v>122</v>
+      </c>
+      <c r="K9">
+        <v>114</v>
+      </c>
+      <c r="L9">
+        <v>95</v>
+      </c>
+      <c r="M9">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13">
+      <c r="A10" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B8">
-        <v>27</v>
-      </c>
-      <c r="C8">
-        <v>37</v>
-      </c>
-      <c r="D8">
-        <v>53</v>
-      </c>
-      <c r="E8">
-        <v>76</v>
-      </c>
-      <c r="F8">
-        <v>103</v>
-      </c>
-      <c r="G8">
-        <v>39</v>
-      </c>
-      <c r="H8">
-        <v>30</v>
-      </c>
-      <c r="I8">
-        <v>34</v>
-      </c>
-      <c r="J8">
-        <v>29</v>
-      </c>
-      <c r="K8">
-        <v>33</v>
-      </c>
-      <c r="L8">
-        <v>17</v>
-      </c>
-      <c r="M8">
-        <v>7</v>
+      <c r="B10">
+        <v>282</v>
+      </c>
+      <c r="C10">
+        <v>416</v>
+      </c>
+      <c r="D10">
+        <v>617</v>
+      </c>
+      <c r="E10">
+        <v>797</v>
+      </c>
+      <c r="F10">
+        <v>660</v>
+      </c>
+      <c r="G10">
+        <v>257</v>
+      </c>
+      <c r="H10">
+        <v>236</v>
+      </c>
+      <c r="I10">
+        <v>324</v>
+      </c>
+      <c r="J10">
+        <v>255</v>
+      </c>
+      <c r="K10">
+        <v>207</v>
+      </c>
+      <c r="L10">
+        <v>196</v>
+      </c>
+      <c r="M10">
+        <v>90</v>
       </c>
     </row>
   </sheetData>
@@ -18921,7 +18973,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M10"/>
+  <dimension ref="A1:M8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="23.7109375" customWidth="1"/>
@@ -18984,38 +19036,26 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C2">
-        <v>1</v>
-      </c>
       <c r="D2">
-        <v>5</v>
-      </c>
-      <c r="E2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H2">
-        <v>3</v>
-      </c>
-      <c r="I2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K2">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="L2">
-        <v>3</v>
-      </c>
-      <c r="M2">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -19023,47 +19063,41 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>2</v>
-      </c>
-      <c r="C3">
         <v>1</v>
       </c>
       <c r="D3">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F3">
         <v>4</v>
       </c>
       <c r="G3">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="H3">
         <v>4</v>
       </c>
       <c r="I3">
+        <v>2</v>
+      </c>
+      <c r="J3">
         <v>6</v>
       </c>
-      <c r="J3">
-        <v>4</v>
-      </c>
       <c r="K3">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="L3">
-        <v>5</v>
-      </c>
-      <c r="M3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="H4">
+      <c r="B4">
         <v>1</v>
       </c>
     </row>
@@ -19071,162 +19105,131 @@
       <c r="A5" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B5">
-        <v>1</v>
-      </c>
-      <c r="K5">
+      <c r="J5">
         <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6">
+        <v>1</v>
+      </c>
+      <c r="C6">
+        <v>11</v>
+      </c>
+      <c r="D6">
+        <v>4</v>
+      </c>
+      <c r="E6">
+        <v>17</v>
+      </c>
+      <c r="F6">
+        <v>18</v>
+      </c>
+      <c r="G6">
+        <v>12</v>
+      </c>
+      <c r="H6">
+        <v>12</v>
+      </c>
+      <c r="I6">
+        <v>17</v>
+      </c>
+      <c r="J6">
         <v>6</v>
       </c>
-      <c r="G6">
-        <v>1</v>
-      </c>
-      <c r="H6">
-        <v>1</v>
-      </c>
-      <c r="I6">
-        <v>1</v>
+      <c r="K6">
+        <v>17</v>
+      </c>
+      <c r="L6">
+        <v>5</v>
+      </c>
+      <c r="M6">
+        <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7">
+        <v>24</v>
+      </c>
+      <c r="C7">
+        <v>26</v>
+      </c>
+      <c r="D7">
+        <v>44</v>
+      </c>
+      <c r="E7">
+        <v>57</v>
+      </c>
+      <c r="F7">
+        <v>79</v>
+      </c>
+      <c r="G7">
+        <v>24</v>
+      </c>
+      <c r="H7">
+        <v>13</v>
+      </c>
+      <c r="I7">
+        <v>15</v>
+      </c>
+      <c r="J7">
+        <v>15</v>
+      </c>
+      <c r="K7">
+        <v>9</v>
+      </c>
+      <c r="L7">
         <v>7</v>
       </c>
-      <c r="D7">
-        <v>1</v>
-      </c>
-      <c r="E7">
-        <v>1</v>
-      </c>
-      <c r="J7">
-        <v>2</v>
+      <c r="M7">
+        <v>4</v>
       </c>
     </row>
     <row r="8" spans="1:13">
       <c r="A8" s="1" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B8">
-        <v>5</v>
+        <v>27</v>
       </c>
       <c r="C8">
-        <v>9</v>
+        <v>37</v>
       </c>
       <c r="D8">
+        <v>53</v>
+      </c>
+      <c r="E8">
+        <v>76</v>
+      </c>
+      <c r="F8">
+        <v>103</v>
+      </c>
+      <c r="G8">
+        <v>39</v>
+      </c>
+      <c r="H8">
+        <v>30</v>
+      </c>
+      <c r="I8">
+        <v>34</v>
+      </c>
+      <c r="J8">
+        <v>29</v>
+      </c>
+      <c r="K8">
+        <v>33</v>
+      </c>
+      <c r="L8">
         <v>17</v>
       </c>
-      <c r="E8">
-        <v>13</v>
-      </c>
-      <c r="F8">
-        <v>19</v>
-      </c>
-      <c r="G8">
-        <v>15</v>
-      </c>
-      <c r="H8">
-        <v>5</v>
-      </c>
-      <c r="I8">
-        <v>15</v>
-      </c>
-      <c r="J8">
-        <v>12</v>
-      </c>
-      <c r="K8">
-        <v>18</v>
-      </c>
-      <c r="L8">
-        <v>19</v>
-      </c>
       <c r="M8">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13">
-      <c r="A9" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B9">
-        <v>43</v>
-      </c>
-      <c r="C9">
-        <v>46</v>
-      </c>
-      <c r="D9">
-        <v>32</v>
-      </c>
-      <c r="E9">
-        <v>30</v>
-      </c>
-      <c r="F9">
-        <v>34</v>
-      </c>
-      <c r="G9">
-        <v>15</v>
-      </c>
-      <c r="H9">
-        <v>17</v>
-      </c>
-      <c r="I9">
-        <v>20</v>
-      </c>
-      <c r="J9">
-        <v>20</v>
-      </c>
-      <c r="K9">
-        <v>20</v>
-      </c>
-      <c r="L9">
-        <v>13</v>
-      </c>
-      <c r="M9">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13">
-      <c r="A10" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B10">
-        <v>51</v>
-      </c>
-      <c r="C10">
-        <v>57</v>
-      </c>
-      <c r="D10">
-        <v>62</v>
-      </c>
-      <c r="E10">
-        <v>48</v>
-      </c>
-      <c r="F10">
-        <v>60</v>
-      </c>
-      <c r="G10">
-        <v>40</v>
-      </c>
-      <c r="H10">
-        <v>31</v>
-      </c>
-      <c r="I10">
-        <v>44</v>
-      </c>
-      <c r="J10">
-        <v>43</v>
-      </c>
-      <c r="K10">
-        <v>57</v>
-      </c>
-      <c r="L10">
-        <v>40</v>
-      </c>
-      <c r="M10">
-        <v>18</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>

--- a/output/cta-index-crime-full-year.xlsx
+++ b/output/cta-index-crime-full-year.xlsx
@@ -9,47 +9,47 @@
   <sheets>
     <sheet name="Citywide Totals" sheetId="1" r:id="rId1"/>
     <sheet name="By Neighborhood" sheetId="2" r:id="rId2"/>
-    <sheet name="Logan Square" sheetId="3" r:id="rId3"/>
-    <sheet name="Grand Crossing" sheetId="4" r:id="rId4"/>
-    <sheet name="South Shore" sheetId="5" r:id="rId5"/>
-    <sheet name="Loop" sheetId="6" r:id="rId6"/>
-    <sheet name="Austin" sheetId="7" r:id="rId7"/>
-    <sheet name="Avondale" sheetId="8" r:id="rId8"/>
-    <sheet name="Rush &amp; Division" sheetId="9" r:id="rId9"/>
-    <sheet name="Chatham" sheetId="10" r:id="rId10"/>
-    <sheet name="Oakland" sheetId="11" r:id="rId11"/>
-    <sheet name="River North" sheetId="12" r:id="rId12"/>
-    <sheet name="Old Town" sheetId="13" r:id="rId13"/>
-    <sheet name="New City" sheetId="14" r:id="rId14"/>
-    <sheet name="Belmont Cragin" sheetId="15" r:id="rId15"/>
-    <sheet name="Woodlawn" sheetId="16" r:id="rId16"/>
-    <sheet name="West Loop" sheetId="17" r:id="rId17"/>
-    <sheet name="Printers Row" sheetId="18" r:id="rId18"/>
-    <sheet name="Uptown" sheetId="19" r:id="rId19"/>
-    <sheet name="Lake View" sheetId="20" r:id="rId20"/>
-    <sheet name="North Lawndale" sheetId="21" r:id="rId21"/>
-    <sheet name="Hyde Park" sheetId="22" r:id="rId22"/>
-    <sheet name="Grand Boulevard" sheetId="23" r:id="rId23"/>
-    <sheet name="West Town" sheetId="24" r:id="rId24"/>
-    <sheet name="Douglas" sheetId="25" r:id="rId25"/>
-    <sheet name="Norwood Park" sheetId="26" r:id="rId26"/>
-    <sheet name="Washington Park" sheetId="27" r:id="rId27"/>
-    <sheet name="Fuller Park" sheetId="28" r:id="rId28"/>
-    <sheet name="Englewood" sheetId="29" r:id="rId29"/>
-    <sheet name="Greektown" sheetId="30" r:id="rId30"/>
-    <sheet name="Rogers Park" sheetId="31" r:id="rId31"/>
-    <sheet name="Garfield Park" sheetId="32" r:id="rId32"/>
-    <sheet name="Lincoln Park" sheetId="33" r:id="rId33"/>
-    <sheet name="Edgewater" sheetId="34" r:id="rId34"/>
-    <sheet name="Little Italy, UIC" sheetId="35" r:id="rId35"/>
-    <sheet name="Albany Park" sheetId="36" r:id="rId36"/>
-    <sheet name="Gage Park" sheetId="37" r:id="rId37"/>
-    <sheet name="Wicker Park" sheetId="38" r:id="rId38"/>
-    <sheet name="Avalon Park" sheetId="39" r:id="rId39"/>
-    <sheet name="Kenwood" sheetId="40" r:id="rId40"/>
-    <sheet name="Humboldt Park" sheetId="41" r:id="rId41"/>
-    <sheet name="Lower West Side" sheetId="42" r:id="rId42"/>
-    <sheet name="Near South Side" sheetId="43" r:id="rId43"/>
+    <sheet name="Near South Side" sheetId="3" r:id="rId3"/>
+    <sheet name="Logan Square" sheetId="4" r:id="rId4"/>
+    <sheet name="Grand Crossing" sheetId="5" r:id="rId5"/>
+    <sheet name="South Shore" sheetId="6" r:id="rId6"/>
+    <sheet name="Loop" sheetId="7" r:id="rId7"/>
+    <sheet name="Austin" sheetId="8" r:id="rId8"/>
+    <sheet name="Avondale" sheetId="9" r:id="rId9"/>
+    <sheet name="Rush &amp; Division" sheetId="10" r:id="rId10"/>
+    <sheet name="Chatham" sheetId="11" r:id="rId11"/>
+    <sheet name="Oakland" sheetId="12" r:id="rId12"/>
+    <sheet name="River North" sheetId="13" r:id="rId13"/>
+    <sheet name="Old Town" sheetId="14" r:id="rId14"/>
+    <sheet name="New City" sheetId="15" r:id="rId15"/>
+    <sheet name="Belmont Cragin" sheetId="16" r:id="rId16"/>
+    <sheet name="Woodlawn" sheetId="17" r:id="rId17"/>
+    <sheet name="West Loop" sheetId="18" r:id="rId18"/>
+    <sheet name="Printers Row" sheetId="19" r:id="rId19"/>
+    <sheet name="Uptown" sheetId="20" r:id="rId20"/>
+    <sheet name="Lake View" sheetId="21" r:id="rId21"/>
+    <sheet name="North Lawndale" sheetId="22" r:id="rId22"/>
+    <sheet name="Hyde Park" sheetId="23" r:id="rId23"/>
+    <sheet name="Grand Boulevard" sheetId="24" r:id="rId24"/>
+    <sheet name="West Town" sheetId="25" r:id="rId25"/>
+    <sheet name="Douglas" sheetId="26" r:id="rId26"/>
+    <sheet name="Norwood Park" sheetId="27" r:id="rId27"/>
+    <sheet name="Washington Park" sheetId="28" r:id="rId28"/>
+    <sheet name="Fuller Park" sheetId="29" r:id="rId29"/>
+    <sheet name="Englewood" sheetId="30" r:id="rId30"/>
+    <sheet name="Greektown" sheetId="31" r:id="rId31"/>
+    <sheet name="Rogers Park" sheetId="32" r:id="rId32"/>
+    <sheet name="Garfield Park" sheetId="33" r:id="rId33"/>
+    <sheet name="Lincoln Park" sheetId="34" r:id="rId34"/>
+    <sheet name="Edgewater" sheetId="35" r:id="rId35"/>
+    <sheet name="Little Italy, UIC" sheetId="36" r:id="rId36"/>
+    <sheet name="Albany Park" sheetId="37" r:id="rId37"/>
+    <sheet name="Gage Park" sheetId="38" r:id="rId38"/>
+    <sheet name="Wicker Park" sheetId="39" r:id="rId39"/>
+    <sheet name="Avalon Park" sheetId="40" r:id="rId40"/>
+    <sheet name="Kenwood" sheetId="41" r:id="rId41"/>
+    <sheet name="Humboldt Park" sheetId="42" r:id="rId42"/>
+    <sheet name="Lower West Side" sheetId="43" r:id="rId43"/>
     <sheet name="North Center" sheetId="44" r:id="rId44"/>
     <sheet name="O'Hare" sheetId="45" r:id="rId45"/>
     <sheet name="Sheffield &amp; DePaul" sheetId="46" r:id="rId46"/>
@@ -1156,7 +1156,7 @@
         <v>467</v>
       </c>
       <c r="M9">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -1238,7 +1238,7 @@
         <v>1604</v>
       </c>
       <c r="M11">
-        <v>816</v>
+        <v>817</v>
       </c>
     </row>
   </sheetData>
@@ -1247,6 +1247,264 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:M7"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+    <col min="13" max="13" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="M1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>2</v>
+      </c>
+      <c r="D2">
+        <v>2</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
+      <c r="H2">
+        <v>2</v>
+      </c>
+      <c r="I2">
+        <v>1</v>
+      </c>
+      <c r="J2">
+        <v>1</v>
+      </c>
+      <c r="K2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>1</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
+      <c r="E3">
+        <v>3</v>
+      </c>
+      <c r="F3">
+        <v>4</v>
+      </c>
+      <c r="G3">
+        <v>2</v>
+      </c>
+      <c r="H3">
+        <v>2</v>
+      </c>
+      <c r="I3">
+        <v>4</v>
+      </c>
+      <c r="K3">
+        <v>1</v>
+      </c>
+      <c r="L3">
+        <v>2</v>
+      </c>
+      <c r="M3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="M4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5">
+        <v>5</v>
+      </c>
+      <c r="C5">
+        <v>4</v>
+      </c>
+      <c r="D5">
+        <v>3</v>
+      </c>
+      <c r="E5">
+        <v>7</v>
+      </c>
+      <c r="F5">
+        <v>9</v>
+      </c>
+      <c r="G5">
+        <v>14</v>
+      </c>
+      <c r="H5">
+        <v>7</v>
+      </c>
+      <c r="I5">
+        <v>9</v>
+      </c>
+      <c r="J5">
+        <v>5</v>
+      </c>
+      <c r="K5">
+        <v>3</v>
+      </c>
+      <c r="L5">
+        <v>5</v>
+      </c>
+      <c r="M5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6">
+        <v>34</v>
+      </c>
+      <c r="C6">
+        <v>33</v>
+      </c>
+      <c r="D6">
+        <v>64</v>
+      </c>
+      <c r="E6">
+        <v>44</v>
+      </c>
+      <c r="F6">
+        <v>45</v>
+      </c>
+      <c r="G6">
+        <v>11</v>
+      </c>
+      <c r="H6">
+        <v>7</v>
+      </c>
+      <c r="I6">
+        <v>7</v>
+      </c>
+      <c r="J6">
+        <v>15</v>
+      </c>
+      <c r="K6">
+        <v>9</v>
+      </c>
+      <c r="L6">
+        <v>12</v>
+      </c>
+      <c r="M6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7">
+        <v>42</v>
+      </c>
+      <c r="C7">
+        <v>37</v>
+      </c>
+      <c r="D7">
+        <v>70</v>
+      </c>
+      <c r="E7">
+        <v>55</v>
+      </c>
+      <c r="F7">
+        <v>58</v>
+      </c>
+      <c r="G7">
+        <v>27</v>
+      </c>
+      <c r="H7">
+        <v>18</v>
+      </c>
+      <c r="I7">
+        <v>21</v>
+      </c>
+      <c r="J7">
+        <v>21</v>
+      </c>
+      <c r="K7">
+        <v>14</v>
+      </c>
+      <c r="L7">
+        <v>19</v>
+      </c>
+      <c r="M7">
+        <v>5</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M10"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -1561,7 +1819,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:K6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -1719,7 +1977,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -1986,7 +2244,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M8"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -2252,7 +2510,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -2477,219 +2735,6 @@
       </c>
       <c r="M6">
         <v>2</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M7"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" customWidth="1"/>
-    <col min="13" max="13" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="M1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D2">
-        <v>1</v>
-      </c>
-      <c r="J2">
-        <v>1</v>
-      </c>
-      <c r="M2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="E3">
-        <v>2</v>
-      </c>
-      <c r="G3">
-        <v>1</v>
-      </c>
-      <c r="J3">
-        <v>1</v>
-      </c>
-      <c r="L3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5">
-        <v>5</v>
-      </c>
-      <c r="C5">
-        <v>6</v>
-      </c>
-      <c r="E5">
-        <v>1</v>
-      </c>
-      <c r="H5">
-        <v>2</v>
-      </c>
-      <c r="J5">
-        <v>4</v>
-      </c>
-      <c r="K5">
-        <v>2</v>
-      </c>
-      <c r="M5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B6">
-        <v>6</v>
-      </c>
-      <c r="C6">
-        <v>2</v>
-      </c>
-      <c r="D6">
-        <v>6</v>
-      </c>
-      <c r="E6">
-        <v>8</v>
-      </c>
-      <c r="F6">
-        <v>7</v>
-      </c>
-      <c r="G6">
-        <v>2</v>
-      </c>
-      <c r="H6">
-        <v>1</v>
-      </c>
-      <c r="I6">
-        <v>1</v>
-      </c>
-      <c r="J6">
-        <v>3</v>
-      </c>
-      <c r="K6">
-        <v>1</v>
-      </c>
-      <c r="L6">
-        <v>2</v>
-      </c>
-      <c r="M6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
-      <c r="A7" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B7">
-        <v>11</v>
-      </c>
-      <c r="C7">
-        <v>9</v>
-      </c>
-      <c r="D7">
-        <v>7</v>
-      </c>
-      <c r="E7">
-        <v>11</v>
-      </c>
-      <c r="F7">
-        <v>7</v>
-      </c>
-      <c r="G7">
-        <v>3</v>
-      </c>
-      <c r="H7">
-        <v>3</v>
-      </c>
-      <c r="I7">
-        <v>1</v>
-      </c>
-      <c r="J7">
-        <v>9</v>
-      </c>
-      <c r="K7">
-        <v>3</v>
-      </c>
-      <c r="L7">
-        <v>3</v>
-      </c>
-      <c r="M7">
-        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -2762,22 +2807,13 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2">
-        <v>3</v>
-      </c>
-      <c r="E2">
-        <v>2</v>
-      </c>
-      <c r="F2">
-        <v>1</v>
-      </c>
-      <c r="G2">
-        <v>2</v>
-      </c>
-      <c r="I2">
-        <v>2</v>
-      </c>
-      <c r="L2">
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="J2">
+        <v>1</v>
+      </c>
+      <c r="M2">
         <v>1</v>
       </c>
     </row>
@@ -2785,45 +2821,24 @@
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B3">
-        <v>2</v>
-      </c>
-      <c r="C3">
-        <v>1</v>
-      </c>
-      <c r="D3">
-        <v>5</v>
-      </c>
-      <c r="F3">
+      <c r="E3">
         <v>2</v>
       </c>
       <c r="G3">
-        <v>3</v>
-      </c>
-      <c r="H3">
-        <v>3</v>
-      </c>
-      <c r="I3">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J3">
-        <v>5</v>
-      </c>
-      <c r="K3">
-        <v>5</v>
-      </c>
-      <c r="M3">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="L3">
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F4">
-        <v>1</v>
-      </c>
-      <c r="H4">
+      <c r="C4">
         <v>1</v>
       </c>
     </row>
@@ -2832,37 +2847,22 @@
         <v>8</v>
       </c>
       <c r="B5">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="C5">
-        <v>12</v>
-      </c>
-      <c r="D5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E5">
-        <v>9</v>
-      </c>
-      <c r="F5">
-        <v>3</v>
-      </c>
-      <c r="G5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H5">
-        <v>4</v>
-      </c>
-      <c r="I5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J5">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K5">
-        <v>7</v>
-      </c>
-      <c r="L5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M5">
         <v>1</v>
@@ -2873,40 +2873,40 @@
         <v>9</v>
       </c>
       <c r="B6">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="C6">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D6">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="E6">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F6">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="G6">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H6">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I6">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="J6">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="K6">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M6">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -2914,40 +2914,40 @@
         <v>10</v>
       </c>
       <c r="B7">
-        <v>33</v>
+        <v>11</v>
       </c>
       <c r="C7">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="D7">
-        <v>27</v>
+        <v>7</v>
       </c>
       <c r="E7">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="F7">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="G7">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="H7">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="I7">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="J7">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="K7">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="L7">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="M7">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -2956,6 +2956,264 @@
 </file>
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:M7"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+    <col min="13" max="13" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="M1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>3</v>
+      </c>
+      <c r="E2">
+        <v>2</v>
+      </c>
+      <c r="F2">
+        <v>1</v>
+      </c>
+      <c r="G2">
+        <v>2</v>
+      </c>
+      <c r="I2">
+        <v>2</v>
+      </c>
+      <c r="L2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>2</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
+      <c r="D3">
+        <v>5</v>
+      </c>
+      <c r="F3">
+        <v>2</v>
+      </c>
+      <c r="G3">
+        <v>3</v>
+      </c>
+      <c r="H3">
+        <v>3</v>
+      </c>
+      <c r="I3">
+        <v>5</v>
+      </c>
+      <c r="J3">
+        <v>5</v>
+      </c>
+      <c r="K3">
+        <v>5</v>
+      </c>
+      <c r="M3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F4">
+        <v>1</v>
+      </c>
+      <c r="H4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5">
+        <v>11</v>
+      </c>
+      <c r="C5">
+        <v>12</v>
+      </c>
+      <c r="D5">
+        <v>5</v>
+      </c>
+      <c r="E5">
+        <v>9</v>
+      </c>
+      <c r="F5">
+        <v>3</v>
+      </c>
+      <c r="G5">
+        <v>2</v>
+      </c>
+      <c r="H5">
+        <v>4</v>
+      </c>
+      <c r="I5">
+        <v>4</v>
+      </c>
+      <c r="J5">
+        <v>6</v>
+      </c>
+      <c r="K5">
+        <v>7</v>
+      </c>
+      <c r="L5">
+        <v>4</v>
+      </c>
+      <c r="M5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6">
+        <v>17</v>
+      </c>
+      <c r="C6">
+        <v>10</v>
+      </c>
+      <c r="D6">
+        <v>17</v>
+      </c>
+      <c r="E6">
+        <v>14</v>
+      </c>
+      <c r="F6">
+        <v>15</v>
+      </c>
+      <c r="G6">
+        <v>6</v>
+      </c>
+      <c r="H6">
+        <v>3</v>
+      </c>
+      <c r="I6">
+        <v>6</v>
+      </c>
+      <c r="J6">
+        <v>8</v>
+      </c>
+      <c r="K6">
+        <v>3</v>
+      </c>
+      <c r="L6">
+        <v>1</v>
+      </c>
+      <c r="M6">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7">
+        <v>33</v>
+      </c>
+      <c r="C7">
+        <v>23</v>
+      </c>
+      <c r="D7">
+        <v>27</v>
+      </c>
+      <c r="E7">
+        <v>25</v>
+      </c>
+      <c r="F7">
+        <v>22</v>
+      </c>
+      <c r="G7">
+        <v>13</v>
+      </c>
+      <c r="H7">
+        <v>11</v>
+      </c>
+      <c r="I7">
+        <v>17</v>
+      </c>
+      <c r="J7">
+        <v>19</v>
+      </c>
+      <c r="K7">
+        <v>15</v>
+      </c>
+      <c r="L7">
+        <v>6</v>
+      </c>
+      <c r="M7">
+        <v>9</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M9"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -3241,7 +3499,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -3463,298 +3721,6 @@
       </c>
       <c r="M6">
         <v>4</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M9"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" customWidth="1"/>
-    <col min="13" max="13" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="M1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2">
-        <v>2</v>
-      </c>
-      <c r="C2">
-        <v>4</v>
-      </c>
-      <c r="D2">
-        <v>1</v>
-      </c>
-      <c r="E2">
-        <v>2</v>
-      </c>
-      <c r="F2">
-        <v>1</v>
-      </c>
-      <c r="G2">
-        <v>2</v>
-      </c>
-      <c r="H2">
-        <v>5</v>
-      </c>
-      <c r="I2">
-        <v>2</v>
-      </c>
-      <c r="J2">
-        <v>4</v>
-      </c>
-      <c r="K2">
-        <v>5</v>
-      </c>
-      <c r="L2">
-        <v>2</v>
-      </c>
-      <c r="M2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C3">
-        <v>1</v>
-      </c>
-      <c r="D3">
-        <v>2</v>
-      </c>
-      <c r="E3">
-        <v>3</v>
-      </c>
-      <c r="F3">
-        <v>3</v>
-      </c>
-      <c r="G3">
-        <v>6</v>
-      </c>
-      <c r="H3">
-        <v>2</v>
-      </c>
-      <c r="I3">
-        <v>4</v>
-      </c>
-      <c r="J3">
-        <v>7</v>
-      </c>
-      <c r="K3">
-        <v>7</v>
-      </c>
-      <c r="L3">
-        <v>3</v>
-      </c>
-      <c r="M3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
-      <c r="A7" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B7">
-        <v>5</v>
-      </c>
-      <c r="C7">
-        <v>9</v>
-      </c>
-      <c r="D7">
-        <v>1</v>
-      </c>
-      <c r="E7">
-        <v>6</v>
-      </c>
-      <c r="F7">
-        <v>6</v>
-      </c>
-      <c r="G7">
-        <v>14</v>
-      </c>
-      <c r="H7">
-        <v>7</v>
-      </c>
-      <c r="I7">
-        <v>4</v>
-      </c>
-      <c r="J7">
-        <v>5</v>
-      </c>
-      <c r="K7">
-        <v>11</v>
-      </c>
-      <c r="L7">
-        <v>8</v>
-      </c>
-      <c r="M7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13">
-      <c r="A8" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B8">
-        <v>30</v>
-      </c>
-      <c r="C8">
-        <v>26</v>
-      </c>
-      <c r="D8">
-        <v>15</v>
-      </c>
-      <c r="E8">
-        <v>24</v>
-      </c>
-      <c r="F8">
-        <v>18</v>
-      </c>
-      <c r="G8">
-        <v>16</v>
-      </c>
-      <c r="H8">
-        <v>14</v>
-      </c>
-      <c r="I8">
-        <v>13</v>
-      </c>
-      <c r="J8">
-        <v>15</v>
-      </c>
-      <c r="K8">
-        <v>12</v>
-      </c>
-      <c r="L8">
-        <v>20</v>
-      </c>
-      <c r="M8">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13">
-      <c r="A9" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B9">
-        <v>38</v>
-      </c>
-      <c r="C9">
-        <v>41</v>
-      </c>
-      <c r="D9">
-        <v>19</v>
-      </c>
-      <c r="E9">
-        <v>36</v>
-      </c>
-      <c r="F9">
-        <v>28</v>
-      </c>
-      <c r="G9">
-        <v>38</v>
-      </c>
-      <c r="H9">
-        <v>28</v>
-      </c>
-      <c r="I9">
-        <v>23</v>
-      </c>
-      <c r="J9">
-        <v>31</v>
-      </c>
-      <c r="K9">
-        <v>35</v>
-      </c>
-      <c r="L9">
-        <v>33</v>
-      </c>
-      <c r="M9">
-        <v>15</v>
       </c>
     </row>
   </sheetData>
@@ -6093,7 +6059,7 @@
         <v>14</v>
       </c>
       <c r="M62">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="63" spans="1:13">
@@ -7550,7 +7516,7 @@
         <v>1604</v>
       </c>
       <c r="M99">
-        <v>816</v>
+        <v>817</v>
       </c>
     </row>
   </sheetData>
@@ -7660,7 +7626,7 @@
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M8"/>
+  <dimension ref="A1:M9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="23.7109375" customWidth="1"/>
@@ -7723,6 +7689,9 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
+      <c r="B2">
+        <v>2</v>
+      </c>
       <c r="C2">
         <v>4</v>
       </c>
@@ -7730,79 +7699,76 @@
         <v>1</v>
       </c>
       <c r="E2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H2">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L2">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M2">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B3">
-        <v>2</v>
-      </c>
       <c r="C3">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F3">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G3">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H3">
+        <v>2</v>
+      </c>
+      <c r="I3">
+        <v>4</v>
+      </c>
+      <c r="J3">
         <v>7</v>
       </c>
-      <c r="I3">
-        <v>2</v>
-      </c>
-      <c r="J3">
-        <v>11</v>
-      </c>
       <c r="K3">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L3">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="M3">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="H4">
+        <v>3</v>
+      </c>
+      <c r="E4">
         <v>1</v>
       </c>
     </row>
@@ -7810,143 +7776,139 @@
       <c r="A5" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C5">
-        <v>1</v>
-      </c>
-      <c r="H5">
-        <v>1</v>
-      </c>
-      <c r="I5">
-        <v>1</v>
-      </c>
-      <c r="K5">
-        <v>3</v>
-      </c>
-      <c r="L5">
-        <v>2</v>
-      </c>
-      <c r="M5">
-        <v>2</v>
+      <c r="B5">
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C6">
-        <v>14</v>
-      </c>
-      <c r="D6">
-        <v>12</v>
-      </c>
-      <c r="E6">
-        <v>10</v>
-      </c>
-      <c r="F6">
-        <v>11</v>
-      </c>
-      <c r="G6">
-        <v>11</v>
-      </c>
-      <c r="H6">
-        <v>17</v>
-      </c>
-      <c r="I6">
-        <v>20</v>
-      </c>
-      <c r="J6">
-        <v>3</v>
-      </c>
-      <c r="K6">
-        <v>10</v>
-      </c>
-      <c r="L6">
-        <v>5</v>
-      </c>
-      <c r="M6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7">
+        <v>5</v>
+      </c>
+      <c r="C7">
         <v>9</v>
       </c>
-      <c r="B7">
-        <v>58</v>
-      </c>
-      <c r="C7">
-        <v>53</v>
-      </c>
       <c r="D7">
-        <v>43</v>
+        <v>1</v>
       </c>
       <c r="E7">
-        <v>56</v>
+        <v>6</v>
       </c>
       <c r="F7">
-        <v>53</v>
+        <v>6</v>
       </c>
       <c r="G7">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="H7">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="I7">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="J7">
-        <v>27</v>
+        <v>5</v>
       </c>
       <c r="K7">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="L7">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="M7">
-        <v>13</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:13">
       <c r="A8" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B8">
+        <v>30</v>
+      </c>
+      <c r="C8">
+        <v>26</v>
+      </c>
+      <c r="D8">
+        <v>15</v>
+      </c>
+      <c r="E8">
+        <v>24</v>
+      </c>
+      <c r="F8">
+        <v>18</v>
+      </c>
+      <c r="G8">
+        <v>16</v>
+      </c>
+      <c r="H8">
+        <v>14</v>
+      </c>
+      <c r="I8">
+        <v>13</v>
+      </c>
+      <c r="J8">
+        <v>15</v>
+      </c>
+      <c r="K8">
+        <v>12</v>
+      </c>
+      <c r="L8">
+        <v>20</v>
+      </c>
+      <c r="M8">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13">
+      <c r="A9" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B8">
-        <v>60</v>
-      </c>
-      <c r="C8">
-        <v>76</v>
-      </c>
-      <c r="D8">
-        <v>57</v>
-      </c>
-      <c r="E8">
-        <v>74</v>
-      </c>
-      <c r="F8">
-        <v>71</v>
-      </c>
-      <c r="G8">
-        <v>52</v>
-      </c>
-      <c r="H8">
-        <v>51</v>
-      </c>
-      <c r="I8">
-        <v>52</v>
-      </c>
-      <c r="J8">
-        <v>43</v>
-      </c>
-      <c r="K8">
+      <c r="B9">
+        <v>38</v>
+      </c>
+      <c r="C9">
         <v>41</v>
       </c>
-      <c r="L8">
-        <v>39</v>
-      </c>
-      <c r="M8">
-        <v>25</v>
+      <c r="D9">
+        <v>19</v>
+      </c>
+      <c r="E9">
+        <v>36</v>
+      </c>
+      <c r="F9">
+        <v>28</v>
+      </c>
+      <c r="G9">
+        <v>38</v>
+      </c>
+      <c r="H9">
+        <v>28</v>
+      </c>
+      <c r="I9">
+        <v>23</v>
+      </c>
+      <c r="J9">
+        <v>31</v>
+      </c>
+      <c r="K9">
+        <v>35</v>
+      </c>
+      <c r="L9">
+        <v>33</v>
+      </c>
+      <c r="M9">
+        <v>15</v>
       </c>
     </row>
   </sheetData>
@@ -8019,41 +7981,38 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2">
-        <v>1</v>
-      </c>
       <c r="C2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D2">
         <v>1</v>
       </c>
       <c r="E2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F2">
         <v>2</v>
       </c>
       <c r="G2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K2">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="L2">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M2">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -8061,47 +8020,47 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C3">
-        <v>2</v>
+        <v>4</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
       </c>
       <c r="E3">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F3">
         <v>5</v>
       </c>
       <c r="G3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H3">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="I3">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J3">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="K3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L3">
         <v>7</v>
       </c>
       <c r="M3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4">
-        <v>1</v>
-      </c>
-      <c r="I4">
+        <v>4</v>
+      </c>
+      <c r="H4">
         <v>1</v>
       </c>
     </row>
@@ -8109,52 +8068,61 @@
       <c r="A5" s="1" t="s">
         <v>5</v>
       </c>
+      <c r="C5">
+        <v>1</v>
+      </c>
       <c r="H5">
         <v>1</v>
       </c>
-      <c r="J5">
-        <v>1</v>
+      <c r="I5">
+        <v>1</v>
+      </c>
+      <c r="K5">
+        <v>3</v>
+      </c>
+      <c r="L5">
+        <v>2</v>
+      </c>
+      <c r="M5">
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B6">
+      <c r="C6">
+        <v>14</v>
+      </c>
+      <c r="D6">
         <v>12</v>
       </c>
-      <c r="C6">
-        <v>21</v>
-      </c>
-      <c r="D6">
-        <v>28</v>
-      </c>
       <c r="E6">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="F6">
-        <v>35</v>
+        <v>11</v>
       </c>
       <c r="G6">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H6">
+        <v>17</v>
+      </c>
+      <c r="I6">
+        <v>20</v>
+      </c>
+      <c r="J6">
+        <v>3</v>
+      </c>
+      <c r="K6">
         <v>10</v>
       </c>
-      <c r="I6">
-        <v>15</v>
-      </c>
-      <c r="J6">
-        <v>5</v>
-      </c>
-      <c r="K6">
-        <v>9</v>
-      </c>
       <c r="L6">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="M6">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -8162,40 +8130,40 @@
         <v>9</v>
       </c>
       <c r="B7">
+        <v>58</v>
+      </c>
+      <c r="C7">
+        <v>53</v>
+      </c>
+      <c r="D7">
+        <v>43</v>
+      </c>
+      <c r="E7">
+        <v>56</v>
+      </c>
+      <c r="F7">
+        <v>53</v>
+      </c>
+      <c r="G7">
+        <v>33</v>
+      </c>
+      <c r="H7">
+        <v>23</v>
+      </c>
+      <c r="I7">
+        <v>26</v>
+      </c>
+      <c r="J7">
+        <v>27</v>
+      </c>
+      <c r="K7">
         <v>17</v>
       </c>
-      <c r="C7">
-        <v>35</v>
-      </c>
-      <c r="D7">
-        <v>49</v>
-      </c>
-      <c r="E7">
-        <v>44</v>
-      </c>
-      <c r="F7">
-        <v>58</v>
-      </c>
-      <c r="G7">
-        <v>25</v>
-      </c>
-      <c r="H7">
-        <v>8</v>
-      </c>
-      <c r="I7">
-        <v>10</v>
-      </c>
-      <c r="J7">
-        <v>8</v>
-      </c>
-      <c r="K7">
-        <v>11</v>
-      </c>
       <c r="L7">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="M7">
-        <v>4</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -8203,40 +8171,40 @@
         <v>10</v>
       </c>
       <c r="B8">
-        <v>32</v>
+        <v>60</v>
       </c>
       <c r="C8">
-        <v>61</v>
+        <v>76</v>
       </c>
       <c r="D8">
-        <v>78</v>
+        <v>57</v>
       </c>
       <c r="E8">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="F8">
-        <v>100</v>
+        <v>71</v>
       </c>
       <c r="G8">
+        <v>52</v>
+      </c>
+      <c r="H8">
+        <v>51</v>
+      </c>
+      <c r="I8">
+        <v>52</v>
+      </c>
+      <c r="J8">
         <v>43</v>
       </c>
-      <c r="H8">
-        <v>26</v>
-      </c>
-      <c r="I8">
-        <v>32</v>
-      </c>
-      <c r="J8">
-        <v>20</v>
-      </c>
       <c r="K8">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="L8">
+        <v>39</v>
+      </c>
+      <c r="M8">
         <v>25</v>
-      </c>
-      <c r="M8">
-        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -8245,6 +8213,296 @@
 </file>
 
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:M8"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+    <col min="13" max="13" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="M1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>3</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
+      <c r="F2">
+        <v>2</v>
+      </c>
+      <c r="G2">
+        <v>3</v>
+      </c>
+      <c r="H2">
+        <v>5</v>
+      </c>
+      <c r="I2">
+        <v>2</v>
+      </c>
+      <c r="J2">
+        <v>1</v>
+      </c>
+      <c r="K2">
+        <v>3</v>
+      </c>
+      <c r="L2">
+        <v>4</v>
+      </c>
+      <c r="M2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>1</v>
+      </c>
+      <c r="C3">
+        <v>2</v>
+      </c>
+      <c r="E3">
+        <v>2</v>
+      </c>
+      <c r="F3">
+        <v>5</v>
+      </c>
+      <c r="G3">
+        <v>3</v>
+      </c>
+      <c r="H3">
+        <v>2</v>
+      </c>
+      <c r="I3">
+        <v>4</v>
+      </c>
+      <c r="J3">
+        <v>5</v>
+      </c>
+      <c r="K3">
+        <v>6</v>
+      </c>
+      <c r="L3">
+        <v>7</v>
+      </c>
+      <c r="M3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4">
+        <v>1</v>
+      </c>
+      <c r="I4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H5">
+        <v>1</v>
+      </c>
+      <c r="J5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6">
+        <v>12</v>
+      </c>
+      <c r="C6">
+        <v>21</v>
+      </c>
+      <c r="D6">
+        <v>28</v>
+      </c>
+      <c r="E6">
+        <v>21</v>
+      </c>
+      <c r="F6">
+        <v>35</v>
+      </c>
+      <c r="G6">
+        <v>12</v>
+      </c>
+      <c r="H6">
+        <v>10</v>
+      </c>
+      <c r="I6">
+        <v>15</v>
+      </c>
+      <c r="J6">
+        <v>5</v>
+      </c>
+      <c r="K6">
+        <v>9</v>
+      </c>
+      <c r="L6">
+        <v>7</v>
+      </c>
+      <c r="M6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7">
+        <v>17</v>
+      </c>
+      <c r="C7">
+        <v>35</v>
+      </c>
+      <c r="D7">
+        <v>49</v>
+      </c>
+      <c r="E7">
+        <v>44</v>
+      </c>
+      <c r="F7">
+        <v>58</v>
+      </c>
+      <c r="G7">
+        <v>25</v>
+      </c>
+      <c r="H7">
+        <v>8</v>
+      </c>
+      <c r="I7">
+        <v>10</v>
+      </c>
+      <c r="J7">
+        <v>8</v>
+      </c>
+      <c r="K7">
+        <v>11</v>
+      </c>
+      <c r="L7">
+        <v>7</v>
+      </c>
+      <c r="M7">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13">
+      <c r="A8" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B8">
+        <v>32</v>
+      </c>
+      <c r="C8">
+        <v>61</v>
+      </c>
+      <c r="D8">
+        <v>78</v>
+      </c>
+      <c r="E8">
+        <v>68</v>
+      </c>
+      <c r="F8">
+        <v>100</v>
+      </c>
+      <c r="G8">
+        <v>43</v>
+      </c>
+      <c r="H8">
+        <v>26</v>
+      </c>
+      <c r="I8">
+        <v>32</v>
+      </c>
+      <c r="J8">
+        <v>20</v>
+      </c>
+      <c r="K8">
+        <v>29</v>
+      </c>
+      <c r="L8">
+        <v>25</v>
+      </c>
+      <c r="M8">
+        <v>11</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -8467,7 +8725,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -8725,7 +8983,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -8988,260 +9246,6 @@
       </c>
       <c r="M7">
         <v>16</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M8"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" customWidth="1"/>
-    <col min="13" max="13" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="M1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2">
-        <v>2</v>
-      </c>
-      <c r="D2">
-        <v>1</v>
-      </c>
-      <c r="H2">
-        <v>1</v>
-      </c>
-      <c r="I2">
-        <v>1</v>
-      </c>
-      <c r="J2">
-        <v>2</v>
-      </c>
-      <c r="L2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3">
-        <v>1</v>
-      </c>
-      <c r="D3">
-        <v>2</v>
-      </c>
-      <c r="F3">
-        <v>3</v>
-      </c>
-      <c r="G3">
-        <v>1</v>
-      </c>
-      <c r="H3">
-        <v>2</v>
-      </c>
-      <c r="I3">
-        <v>2</v>
-      </c>
-      <c r="K3">
-        <v>2</v>
-      </c>
-      <c r="M3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="J4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="K5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B6">
-        <v>7</v>
-      </c>
-      <c r="C6">
-        <v>5</v>
-      </c>
-      <c r="D6">
-        <v>5</v>
-      </c>
-      <c r="E6">
-        <v>5</v>
-      </c>
-      <c r="F6">
-        <v>5</v>
-      </c>
-      <c r="G6">
-        <v>1</v>
-      </c>
-      <c r="H6">
-        <v>5</v>
-      </c>
-      <c r="I6">
-        <v>4</v>
-      </c>
-      <c r="J6">
-        <v>1</v>
-      </c>
-      <c r="K6">
-        <v>4</v>
-      </c>
-      <c r="L6">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
-      <c r="A7" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B7">
-        <v>14</v>
-      </c>
-      <c r="C7">
-        <v>13</v>
-      </c>
-      <c r="D7">
-        <v>13</v>
-      </c>
-      <c r="E7">
-        <v>15</v>
-      </c>
-      <c r="F7">
-        <v>11</v>
-      </c>
-      <c r="G7">
-        <v>4</v>
-      </c>
-      <c r="H7">
-        <v>2</v>
-      </c>
-      <c r="I7">
-        <v>7</v>
-      </c>
-      <c r="J7">
-        <v>7</v>
-      </c>
-      <c r="K7">
-        <v>9</v>
-      </c>
-      <c r="L7">
-        <v>8</v>
-      </c>
-      <c r="M7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13">
-      <c r="A8" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B8">
-        <v>22</v>
-      </c>
-      <c r="C8">
-        <v>20</v>
-      </c>
-      <c r="D8">
-        <v>21</v>
-      </c>
-      <c r="E8">
-        <v>20</v>
-      </c>
-      <c r="F8">
-        <v>19</v>
-      </c>
-      <c r="G8">
-        <v>6</v>
-      </c>
-      <c r="H8">
-        <v>10</v>
-      </c>
-      <c r="I8">
-        <v>14</v>
-      </c>
-      <c r="J8">
-        <v>11</v>
-      </c>
-      <c r="K8">
-        <v>16</v>
-      </c>
-      <c r="L8">
-        <v>15</v>
-      </c>
-      <c r="M8">
-        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -9314,16 +9318,22 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="F2">
-        <v>1</v>
-      </c>
-      <c r="K2">
+      <c r="C2">
+        <v>2</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="H2">
+        <v>1</v>
+      </c>
+      <c r="I2">
+        <v>1</v>
+      </c>
+      <c r="J2">
         <v>2</v>
       </c>
       <c r="L2">
-        <v>2</v>
-      </c>
-      <c r="M2">
         <v>1</v>
       </c>
     </row>
@@ -9331,36 +9341,36 @@
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
+      <c r="B3">
+        <v>1</v>
+      </c>
+      <c r="D3">
+        <v>2</v>
+      </c>
       <c r="F3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G3">
         <v>1</v>
       </c>
       <c r="H3">
-        <v>1</v>
-      </c>
-      <c r="J3">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="I3">
+        <v>2</v>
       </c>
       <c r="K3">
         <v>2</v>
       </c>
-      <c r="L3">
-        <v>1</v>
-      </c>
       <c r="M3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D4">
-        <v>1</v>
-      </c>
-      <c r="I4">
+      <c r="J4">
         <v>1</v>
       </c>
     </row>
@@ -9368,7 +9378,7 @@
       <c r="A5" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="I5">
+      <c r="K5">
         <v>1</v>
       </c>
     </row>
@@ -9376,29 +9386,38 @@
       <c r="A6" s="1" t="s">
         <v>8</v>
       </c>
+      <c r="B6">
+        <v>7</v>
+      </c>
+      <c r="C6">
+        <v>5</v>
+      </c>
       <c r="D6">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E6">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F6">
-        <v>2</v>
+        <v>5</v>
+      </c>
+      <c r="G6">
+        <v>1</v>
       </c>
       <c r="H6">
+        <v>5</v>
+      </c>
+      <c r="I6">
+        <v>4</v>
+      </c>
+      <c r="J6">
+        <v>1</v>
+      </c>
+      <c r="K6">
+        <v>4</v>
+      </c>
+      <c r="L6">
         <v>6</v>
-      </c>
-      <c r="J6">
-        <v>1</v>
-      </c>
-      <c r="K6">
-        <v>1</v>
-      </c>
-      <c r="L6">
-        <v>1</v>
-      </c>
-      <c r="M6">
-        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -9406,40 +9425,40 @@
         <v>9</v>
       </c>
       <c r="B7">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C7">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D7">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E7">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F7">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="G7">
+        <v>4</v>
+      </c>
+      <c r="H7">
+        <v>2</v>
+      </c>
+      <c r="I7">
+        <v>7</v>
+      </c>
+      <c r="J7">
+        <v>7</v>
+      </c>
+      <c r="K7">
+        <v>9</v>
+      </c>
+      <c r="L7">
         <v>8</v>
       </c>
-      <c r="H7">
-        <v>4</v>
-      </c>
-      <c r="I7">
-        <v>2</v>
-      </c>
-      <c r="J7">
-        <v>2</v>
-      </c>
-      <c r="K7">
-        <v>3</v>
-      </c>
-      <c r="L7">
-        <v>6</v>
-      </c>
       <c r="M7">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -9447,40 +9466,40 @@
         <v>10</v>
       </c>
       <c r="B8">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="C8">
+        <v>20</v>
+      </c>
+      <c r="D8">
+        <v>21</v>
+      </c>
+      <c r="E8">
+        <v>20</v>
+      </c>
+      <c r="F8">
+        <v>19</v>
+      </c>
+      <c r="G8">
+        <v>6</v>
+      </c>
+      <c r="H8">
         <v>10</v>
       </c>
-      <c r="D8">
-        <v>12</v>
-      </c>
-      <c r="E8">
-        <v>19</v>
-      </c>
-      <c r="F8">
-        <v>21</v>
-      </c>
-      <c r="G8">
-        <v>9</v>
-      </c>
-      <c r="H8">
+      <c r="I8">
+        <v>14</v>
+      </c>
+      <c r="J8">
         <v>11</v>
       </c>
-      <c r="I8">
-        <v>4</v>
-      </c>
-      <c r="J8">
-        <v>4</v>
-      </c>
       <c r="K8">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="L8">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="M8">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -9553,32 +9572,14 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C2">
-        <v>1</v>
-      </c>
-      <c r="D2">
-        <v>2</v>
-      </c>
-      <c r="E2">
-        <v>2</v>
-      </c>
       <c r="F2">
         <v>1</v>
       </c>
-      <c r="G2">
-        <v>2</v>
-      </c>
-      <c r="I2">
-        <v>1</v>
-      </c>
-      <c r="J2">
-        <v>3</v>
-      </c>
       <c r="K2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M2">
         <v>1</v>
@@ -9588,15 +9589,6 @@
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C3">
-        <v>2</v>
-      </c>
-      <c r="D3">
-        <v>2</v>
-      </c>
-      <c r="E3">
-        <v>2</v>
-      </c>
       <c r="F3">
         <v>1</v>
       </c>
@@ -9604,37 +9596,37 @@
         <v>1</v>
       </c>
       <c r="H3">
-        <v>3</v>
-      </c>
-      <c r="I3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J3">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L3">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="M3">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="L4">
+      <c r="D4">
+        <v>1</v>
+      </c>
+      <c r="I4">
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="K5">
+        <v>6</v>
+      </c>
+      <c r="I5">
         <v>1</v>
       </c>
     </row>
@@ -9642,32 +9634,20 @@
       <c r="A6" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B6">
-        <v>7</v>
-      </c>
-      <c r="C6">
-        <v>7</v>
-      </c>
       <c r="D6">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E6">
+        <v>2</v>
+      </c>
+      <c r="F6">
+        <v>2</v>
+      </c>
+      <c r="H6">
         <v>6</v>
       </c>
-      <c r="F6">
-        <v>5</v>
-      </c>
-      <c r="G6">
-        <v>7</v>
-      </c>
-      <c r="H6">
-        <v>4</v>
-      </c>
-      <c r="I6">
-        <v>8</v>
-      </c>
       <c r="J6">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K6">
         <v>1</v>
@@ -9676,7 +9656,7 @@
         <v>1</v>
       </c>
       <c r="M6">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -9684,40 +9664,40 @@
         <v>9</v>
       </c>
       <c r="B7">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="C7">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="D7">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E7">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F7">
         <v>17</v>
       </c>
       <c r="G7">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="H7">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I7">
+        <v>2</v>
+      </c>
+      <c r="J7">
+        <v>2</v>
+      </c>
+      <c r="K7">
+        <v>3</v>
+      </c>
+      <c r="L7">
         <v>6</v>
       </c>
-      <c r="J7">
-        <v>5</v>
-      </c>
-      <c r="K7">
-        <v>8</v>
-      </c>
-      <c r="L7">
-        <v>3</v>
-      </c>
       <c r="M7">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -9725,40 +9705,40 @@
         <v>10</v>
       </c>
       <c r="B8">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="C8">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="D8">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="E8">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="F8">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="G8">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="H8">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I8">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="J8">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="K8">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="L8">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="M8">
-        <v>14</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -9767,6 +9747,284 @@
 </file>
 
 <file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:M8"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+    <col min="13" max="13" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="M1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>2</v>
+      </c>
+      <c r="E2">
+        <v>2</v>
+      </c>
+      <c r="F2">
+        <v>1</v>
+      </c>
+      <c r="G2">
+        <v>2</v>
+      </c>
+      <c r="I2">
+        <v>1</v>
+      </c>
+      <c r="J2">
+        <v>3</v>
+      </c>
+      <c r="K2">
+        <v>1</v>
+      </c>
+      <c r="L2">
+        <v>1</v>
+      </c>
+      <c r="M2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3">
+        <v>2</v>
+      </c>
+      <c r="D3">
+        <v>2</v>
+      </c>
+      <c r="E3">
+        <v>2</v>
+      </c>
+      <c r="F3">
+        <v>1</v>
+      </c>
+      <c r="G3">
+        <v>1</v>
+      </c>
+      <c r="H3">
+        <v>3</v>
+      </c>
+      <c r="I3">
+        <v>3</v>
+      </c>
+      <c r="J3">
+        <v>4</v>
+      </c>
+      <c r="K3">
+        <v>1</v>
+      </c>
+      <c r="L3">
+        <v>5</v>
+      </c>
+      <c r="M3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="L4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="K5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6">
+        <v>7</v>
+      </c>
+      <c r="C6">
+        <v>7</v>
+      </c>
+      <c r="D6">
+        <v>7</v>
+      </c>
+      <c r="E6">
+        <v>6</v>
+      </c>
+      <c r="F6">
+        <v>5</v>
+      </c>
+      <c r="G6">
+        <v>7</v>
+      </c>
+      <c r="H6">
+        <v>4</v>
+      </c>
+      <c r="I6">
+        <v>8</v>
+      </c>
+      <c r="J6">
+        <v>5</v>
+      </c>
+      <c r="K6">
+        <v>1</v>
+      </c>
+      <c r="L6">
+        <v>1</v>
+      </c>
+      <c r="M6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7">
+        <v>21</v>
+      </c>
+      <c r="C7">
+        <v>18</v>
+      </c>
+      <c r="D7">
+        <v>11</v>
+      </c>
+      <c r="E7">
+        <v>14</v>
+      </c>
+      <c r="F7">
+        <v>17</v>
+      </c>
+      <c r="G7">
+        <v>3</v>
+      </c>
+      <c r="H7">
+        <v>5</v>
+      </c>
+      <c r="I7">
+        <v>6</v>
+      </c>
+      <c r="J7">
+        <v>5</v>
+      </c>
+      <c r="K7">
+        <v>8</v>
+      </c>
+      <c r="L7">
+        <v>3</v>
+      </c>
+      <c r="M7">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13">
+      <c r="A8" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B8">
+        <v>28</v>
+      </c>
+      <c r="C8">
+        <v>28</v>
+      </c>
+      <c r="D8">
+        <v>22</v>
+      </c>
+      <c r="E8">
+        <v>24</v>
+      </c>
+      <c r="F8">
+        <v>24</v>
+      </c>
+      <c r="G8">
+        <v>13</v>
+      </c>
+      <c r="H8">
+        <v>12</v>
+      </c>
+      <c r="I8">
+        <v>18</v>
+      </c>
+      <c r="J8">
+        <v>17</v>
+      </c>
+      <c r="K8">
+        <v>12</v>
+      </c>
+      <c r="L8">
+        <v>11</v>
+      </c>
+      <c r="M8">
+        <v>14</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M9"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -10039,322 +10297,6 @@
       </c>
       <c r="M9">
         <v>11</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M9"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" customWidth="1"/>
-    <col min="13" max="13" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="M1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2">
-        <v>1</v>
-      </c>
-      <c r="D2">
-        <v>6</v>
-      </c>
-      <c r="E2">
-        <v>1</v>
-      </c>
-      <c r="F2">
-        <v>9</v>
-      </c>
-      <c r="G2">
-        <v>7</v>
-      </c>
-      <c r="H2">
-        <v>11</v>
-      </c>
-      <c r="I2">
-        <v>10</v>
-      </c>
-      <c r="J2">
-        <v>9</v>
-      </c>
-      <c r="K2">
-        <v>3</v>
-      </c>
-      <c r="L2">
-        <v>6</v>
-      </c>
-      <c r="M2">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3">
-        <v>5</v>
-      </c>
-      <c r="C3">
-        <v>5</v>
-      </c>
-      <c r="D3">
-        <v>18</v>
-      </c>
-      <c r="E3">
-        <v>10</v>
-      </c>
-      <c r="F3">
-        <v>12</v>
-      </c>
-      <c r="G3">
-        <v>11</v>
-      </c>
-      <c r="H3">
-        <v>7</v>
-      </c>
-      <c r="I3">
-        <v>13</v>
-      </c>
-      <c r="J3">
-        <v>12</v>
-      </c>
-      <c r="K3">
-        <v>20</v>
-      </c>
-      <c r="L3">
-        <v>20</v>
-      </c>
-      <c r="M3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B4">
-        <v>1</v>
-      </c>
-      <c r="D4">
-        <v>1</v>
-      </c>
-      <c r="H4">
-        <v>2</v>
-      </c>
-      <c r="J4">
-        <v>1</v>
-      </c>
-      <c r="K4">
-        <v>1</v>
-      </c>
-      <c r="L4">
-        <v>1</v>
-      </c>
-      <c r="M4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H5">
-        <v>1</v>
-      </c>
-      <c r="I5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="G6">
-        <v>1</v>
-      </c>
-      <c r="J6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
-      <c r="A7" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B7">
-        <v>34</v>
-      </c>
-      <c r="C7">
-        <v>45</v>
-      </c>
-      <c r="D7">
-        <v>25</v>
-      </c>
-      <c r="E7">
-        <v>22</v>
-      </c>
-      <c r="F7">
-        <v>42</v>
-      </c>
-      <c r="G7">
-        <v>32</v>
-      </c>
-      <c r="H7">
-        <v>26</v>
-      </c>
-      <c r="I7">
-        <v>21</v>
-      </c>
-      <c r="J7">
-        <v>15</v>
-      </c>
-      <c r="K7">
-        <v>44</v>
-      </c>
-      <c r="L7">
-        <v>44</v>
-      </c>
-      <c r="M7">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13">
-      <c r="A8" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B8">
-        <v>71</v>
-      </c>
-      <c r="C8">
-        <v>91</v>
-      </c>
-      <c r="D8">
-        <v>57</v>
-      </c>
-      <c r="E8">
-        <v>65</v>
-      </c>
-      <c r="F8">
-        <v>75</v>
-      </c>
-      <c r="G8">
-        <v>41</v>
-      </c>
-      <c r="H8">
-        <v>29</v>
-      </c>
-      <c r="I8">
-        <v>45</v>
-      </c>
-      <c r="J8">
-        <v>31</v>
-      </c>
-      <c r="K8">
-        <v>27</v>
-      </c>
-      <c r="L8">
-        <v>32</v>
-      </c>
-      <c r="M8">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13">
-      <c r="A9" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B9">
-        <v>111</v>
-      </c>
-      <c r="C9">
-        <v>142</v>
-      </c>
-      <c r="D9">
-        <v>107</v>
-      </c>
-      <c r="E9">
-        <v>98</v>
-      </c>
-      <c r="F9">
-        <v>138</v>
-      </c>
-      <c r="G9">
-        <v>92</v>
-      </c>
-      <c r="H9">
-        <v>76</v>
-      </c>
-      <c r="I9">
-        <v>90</v>
-      </c>
-      <c r="J9">
-        <v>69</v>
-      </c>
-      <c r="K9">
-        <v>95</v>
-      </c>
-      <c r="L9">
-        <v>103</v>
-      </c>
-      <c r="M9">
-        <v>34</v>
       </c>
     </row>
   </sheetData>
@@ -10427,35 +10369,35 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C2">
-        <v>1</v>
-      </c>
-      <c r="D2">
-        <v>2</v>
+      <c r="F2">
+        <v>1</v>
       </c>
       <c r="G2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H2">
         <v>1</v>
       </c>
       <c r="I2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K2">
-        <v>2</v>
-      </c>
-      <c r="L2">
-        <v>5</v>
+        <v>3</v>
+      </c>
+      <c r="M2">
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
+      <c r="B3">
+        <v>1</v>
+      </c>
       <c r="C3">
         <v>1</v>
       </c>
@@ -10463,21 +10405,24 @@
         <v>1</v>
       </c>
       <c r="E3">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="G3">
+        <v>2</v>
       </c>
       <c r="H3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K3">
         <v>1</v>
       </c>
-      <c r="L3">
+      <c r="M3">
         <v>1</v>
       </c>
     </row>
@@ -10485,27 +10430,15 @@
       <c r="A4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D4">
-        <v>1</v>
-      </c>
-      <c r="E4">
-        <v>1</v>
-      </c>
       <c r="J4">
-        <v>1</v>
-      </c>
-      <c r="L4">
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C5">
-        <v>1</v>
-      </c>
-      <c r="J5">
+        <v>6</v>
+      </c>
+      <c r="K5">
         <v>1</v>
       </c>
     </row>
@@ -10514,40 +10447,40 @@
         <v>8</v>
       </c>
       <c r="B6">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C6">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D6">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E6">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F6">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G6">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H6">
+        <v>6</v>
+      </c>
+      <c r="I6">
         <v>8</v>
       </c>
-      <c r="I6">
-        <v>5</v>
-      </c>
       <c r="J6">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="K6">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="L6">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="M6">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -10555,40 +10488,40 @@
         <v>9</v>
       </c>
       <c r="B7">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="C7">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="D7">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="E7">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="F7">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="G7">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="H7">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I7">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="J7">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="K7">
+        <v>12</v>
+      </c>
+      <c r="L7">
         <v>10</v>
       </c>
-      <c r="L7">
-        <v>12</v>
-      </c>
       <c r="M7">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -10596,40 +10529,40 @@
         <v>10</v>
       </c>
       <c r="B8">
+        <v>29</v>
+      </c>
+      <c r="C8">
+        <v>30</v>
+      </c>
+      <c r="D8">
+        <v>29</v>
+      </c>
+      <c r="E8">
+        <v>26</v>
+      </c>
+      <c r="F8">
+        <v>28</v>
+      </c>
+      <c r="G8">
+        <v>17</v>
+      </c>
+      <c r="H8">
+        <v>15</v>
+      </c>
+      <c r="I8">
+        <v>27</v>
+      </c>
+      <c r="J8">
         <v>19</v>
-      </c>
-      <c r="C8">
-        <v>32</v>
-      </c>
-      <c r="D8">
-        <v>42</v>
-      </c>
-      <c r="E8">
-        <v>37</v>
-      </c>
-      <c r="F8">
-        <v>23</v>
-      </c>
-      <c r="G8">
-        <v>26</v>
-      </c>
-      <c r="H8">
-        <v>18</v>
-      </c>
-      <c r="I8">
-        <v>23</v>
-      </c>
-      <c r="J8">
-        <v>31</v>
       </c>
       <c r="K8">
         <v>20</v>
       </c>
       <c r="L8">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="M8">
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -10638,6 +10571,322 @@
 </file>
 
 <file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:M9"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+    <col min="13" max="13" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="M1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>6</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
+      <c r="F2">
+        <v>9</v>
+      </c>
+      <c r="G2">
+        <v>7</v>
+      </c>
+      <c r="H2">
+        <v>11</v>
+      </c>
+      <c r="I2">
+        <v>10</v>
+      </c>
+      <c r="J2">
+        <v>9</v>
+      </c>
+      <c r="K2">
+        <v>3</v>
+      </c>
+      <c r="L2">
+        <v>6</v>
+      </c>
+      <c r="M2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>5</v>
+      </c>
+      <c r="C3">
+        <v>5</v>
+      </c>
+      <c r="D3">
+        <v>18</v>
+      </c>
+      <c r="E3">
+        <v>10</v>
+      </c>
+      <c r="F3">
+        <v>12</v>
+      </c>
+      <c r="G3">
+        <v>11</v>
+      </c>
+      <c r="H3">
+        <v>7</v>
+      </c>
+      <c r="I3">
+        <v>13</v>
+      </c>
+      <c r="J3">
+        <v>12</v>
+      </c>
+      <c r="K3">
+        <v>20</v>
+      </c>
+      <c r="L3">
+        <v>20</v>
+      </c>
+      <c r="M3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4">
+        <v>1</v>
+      </c>
+      <c r="D4">
+        <v>1</v>
+      </c>
+      <c r="H4">
+        <v>2</v>
+      </c>
+      <c r="J4">
+        <v>1</v>
+      </c>
+      <c r="K4">
+        <v>1</v>
+      </c>
+      <c r="L4">
+        <v>1</v>
+      </c>
+      <c r="M4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H5">
+        <v>1</v>
+      </c>
+      <c r="I5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G6">
+        <v>1</v>
+      </c>
+      <c r="J6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7">
+        <v>34</v>
+      </c>
+      <c r="C7">
+        <v>45</v>
+      </c>
+      <c r="D7">
+        <v>25</v>
+      </c>
+      <c r="E7">
+        <v>22</v>
+      </c>
+      <c r="F7">
+        <v>42</v>
+      </c>
+      <c r="G7">
+        <v>32</v>
+      </c>
+      <c r="H7">
+        <v>26</v>
+      </c>
+      <c r="I7">
+        <v>21</v>
+      </c>
+      <c r="J7">
+        <v>15</v>
+      </c>
+      <c r="K7">
+        <v>44</v>
+      </c>
+      <c r="L7">
+        <v>44</v>
+      </c>
+      <c r="M7">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13">
+      <c r="A8" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B8">
+        <v>71</v>
+      </c>
+      <c r="C8">
+        <v>91</v>
+      </c>
+      <c r="D8">
+        <v>57</v>
+      </c>
+      <c r="E8">
+        <v>65</v>
+      </c>
+      <c r="F8">
+        <v>75</v>
+      </c>
+      <c r="G8">
+        <v>41</v>
+      </c>
+      <c r="H8">
+        <v>29</v>
+      </c>
+      <c r="I8">
+        <v>45</v>
+      </c>
+      <c r="J8">
+        <v>31</v>
+      </c>
+      <c r="K8">
+        <v>27</v>
+      </c>
+      <c r="L8">
+        <v>32</v>
+      </c>
+      <c r="M8">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13">
+      <c r="A9" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B9">
+        <v>111</v>
+      </c>
+      <c r="C9">
+        <v>142</v>
+      </c>
+      <c r="D9">
+        <v>107</v>
+      </c>
+      <c r="E9">
+        <v>98</v>
+      </c>
+      <c r="F9">
+        <v>138</v>
+      </c>
+      <c r="G9">
+        <v>92</v>
+      </c>
+      <c r="H9">
+        <v>76</v>
+      </c>
+      <c r="I9">
+        <v>90</v>
+      </c>
+      <c r="J9">
+        <v>69</v>
+      </c>
+      <c r="K9">
+        <v>95</v>
+      </c>
+      <c r="L9">
+        <v>103</v>
+      </c>
+      <c r="M9">
+        <v>34</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -10862,7 +11111,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M10"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -11174,7 +11423,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M9"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -11487,7 +11736,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -11727,7 +11976,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M9"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -11997,285 +12246,6 @@
       </c>
       <c r="M9">
         <v>15</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M7"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" customWidth="1"/>
-    <col min="13" max="13" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="M1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2">
-        <v>3</v>
-      </c>
-      <c r="D2">
-        <v>1</v>
-      </c>
-      <c r="F2">
-        <v>2</v>
-      </c>
-      <c r="H2">
-        <v>1</v>
-      </c>
-      <c r="I2">
-        <v>4</v>
-      </c>
-      <c r="J2">
-        <v>1</v>
-      </c>
-      <c r="K2">
-        <v>5</v>
-      </c>
-      <c r="L2">
-        <v>4</v>
-      </c>
-      <c r="M2">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3">
-        <v>4</v>
-      </c>
-      <c r="D3">
-        <v>2</v>
-      </c>
-      <c r="E3">
-        <v>2</v>
-      </c>
-      <c r="F3">
-        <v>1</v>
-      </c>
-      <c r="G3">
-        <v>1</v>
-      </c>
-      <c r="H3">
-        <v>1</v>
-      </c>
-      <c r="I3">
-        <v>4</v>
-      </c>
-      <c r="J3">
-        <v>4</v>
-      </c>
-      <c r="K3">
-        <v>5</v>
-      </c>
-      <c r="L3">
-        <v>6</v>
-      </c>
-      <c r="M3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B4">
-        <v>1</v>
-      </c>
-      <c r="H4">
-        <v>2</v>
-      </c>
-      <c r="K4">
-        <v>3</v>
-      </c>
-      <c r="L4">
-        <v>1</v>
-      </c>
-      <c r="M4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5">
-        <v>5</v>
-      </c>
-      <c r="C5">
-        <v>7</v>
-      </c>
-      <c r="D5">
-        <v>11</v>
-      </c>
-      <c r="E5">
-        <v>21</v>
-      </c>
-      <c r="F5">
-        <v>25</v>
-      </c>
-      <c r="G5">
-        <v>15</v>
-      </c>
-      <c r="H5">
-        <v>10</v>
-      </c>
-      <c r="I5">
-        <v>9</v>
-      </c>
-      <c r="J5">
-        <v>11</v>
-      </c>
-      <c r="K5">
-        <v>18</v>
-      </c>
-      <c r="L5">
-        <v>11</v>
-      </c>
-      <c r="M5">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B6">
-        <v>17</v>
-      </c>
-      <c r="C6">
-        <v>12</v>
-      </c>
-      <c r="D6">
-        <v>19</v>
-      </c>
-      <c r="E6">
-        <v>30</v>
-      </c>
-      <c r="F6">
-        <v>34</v>
-      </c>
-      <c r="G6">
-        <v>9</v>
-      </c>
-      <c r="H6">
-        <v>10</v>
-      </c>
-      <c r="I6">
-        <v>7</v>
-      </c>
-      <c r="J6">
-        <v>20</v>
-      </c>
-      <c r="K6">
-        <v>11</v>
-      </c>
-      <c r="L6">
-        <v>21</v>
-      </c>
-      <c r="M6">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
-      <c r="A7" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B7">
-        <v>27</v>
-      </c>
-      <c r="C7">
-        <v>22</v>
-      </c>
-      <c r="D7">
-        <v>33</v>
-      </c>
-      <c r="E7">
-        <v>53</v>
-      </c>
-      <c r="F7">
-        <v>62</v>
-      </c>
-      <c r="G7">
-        <v>25</v>
-      </c>
-      <c r="H7">
-        <v>24</v>
-      </c>
-      <c r="I7">
-        <v>24</v>
-      </c>
-      <c r="J7">
-        <v>36</v>
-      </c>
-      <c r="K7">
-        <v>42</v>
-      </c>
-      <c r="L7">
-        <v>43</v>
-      </c>
-      <c r="M7">
-        <v>18</v>
       </c>
     </row>
   </sheetData>
@@ -12348,29 +12318,32 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
+      <c r="C2">
+        <v>3</v>
+      </c>
       <c r="D2">
         <v>1</v>
       </c>
       <c r="F2">
-        <v>1</v>
-      </c>
-      <c r="G2">
+        <v>2</v>
+      </c>
+      <c r="H2">
         <v>1</v>
       </c>
       <c r="I2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K2">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="L2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M2">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -12378,38 +12351,56 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>1</v>
-      </c>
-      <c r="C3">
+        <v>4</v>
+      </c>
+      <c r="D3">
+        <v>2</v>
+      </c>
+      <c r="E3">
+        <v>2</v>
+      </c>
+      <c r="F3">
         <v>1</v>
       </c>
       <c r="G3">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="H3">
+        <v>1</v>
       </c>
       <c r="I3">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J3">
-        <v>1</v>
+        <v>4</v>
+      </c>
+      <c r="K3">
+        <v>5</v>
       </c>
       <c r="L3">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="M3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="E4">
-        <v>2</v>
-      </c>
-      <c r="J4">
-        <v>1</v>
+      <c r="B4">
+        <v>1</v>
+      </c>
+      <c r="H4">
+        <v>2</v>
       </c>
       <c r="K4">
+        <v>3</v>
+      </c>
+      <c r="L4">
+        <v>1</v>
+      </c>
+      <c r="M4">
         <v>1</v>
       </c>
     </row>
@@ -12418,31 +12409,40 @@
         <v>8</v>
       </c>
       <c r="B5">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C5">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D5">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="E5">
-        <v>2</v>
+        <v>21</v>
+      </c>
+      <c r="F5">
+        <v>25</v>
       </c>
       <c r="G5">
-        <v>1</v>
+        <v>15</v>
+      </c>
+      <c r="H5">
+        <v>10</v>
       </c>
       <c r="I5">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="J5">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="K5">
-        <v>4</v>
+        <v>18</v>
+      </c>
+      <c r="L5">
+        <v>11</v>
       </c>
       <c r="M5">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -12450,40 +12450,40 @@
         <v>9</v>
       </c>
       <c r="B6">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="C6">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D6">
+        <v>19</v>
+      </c>
+      <c r="E6">
+        <v>30</v>
+      </c>
+      <c r="F6">
+        <v>34</v>
+      </c>
+      <c r="G6">
+        <v>9</v>
+      </c>
+      <c r="H6">
         <v>10</v>
       </c>
-      <c r="E6">
-        <v>9</v>
-      </c>
-      <c r="F6">
-        <v>9</v>
-      </c>
-      <c r="G6">
-        <v>8</v>
-      </c>
-      <c r="H6">
-        <v>1</v>
-      </c>
       <c r="I6">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="J6">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="K6">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="L6">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="M6">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -12491,40 +12491,40 @@
         <v>10</v>
       </c>
       <c r="B7">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="C7">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="D7">
-        <v>13</v>
+        <v>33</v>
       </c>
       <c r="E7">
-        <v>13</v>
+        <v>53</v>
       </c>
       <c r="F7">
-        <v>10</v>
+        <v>62</v>
       </c>
       <c r="G7">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="H7">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="I7">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="J7">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="K7">
-        <v>15</v>
+        <v>42</v>
       </c>
       <c r="L7">
-        <v>6</v>
+        <v>43</v>
       </c>
       <c r="M7">
-        <v>5</v>
+        <v>18</v>
       </c>
     </row>
   </sheetData>
@@ -12534,7 +12534,7 @@
 
 <file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M9"/>
+  <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="23.7109375" customWidth="1"/>
@@ -12597,26 +12597,29 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C2">
-        <v>1</v>
-      </c>
       <c r="D2">
         <v>1</v>
       </c>
-      <c r="E2">
-        <v>1</v>
-      </c>
       <c r="F2">
         <v>1</v>
       </c>
+      <c r="G2">
+        <v>1</v>
+      </c>
+      <c r="I2">
+        <v>2</v>
+      </c>
       <c r="J2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K2">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="L2">
-        <v>5</v>
+        <v>2</v>
+      </c>
+      <c r="M2">
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -12624,31 +12627,22 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C3">
-        <v>2</v>
-      </c>
-      <c r="D3">
-        <v>1</v>
-      </c>
-      <c r="E3">
-        <v>3</v>
-      </c>
-      <c r="H3">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="G3">
+        <v>2</v>
       </c>
       <c r="I3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J3">
         <v>1</v>
       </c>
-      <c r="K3">
-        <v>3</v>
-      </c>
       <c r="L3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M3">
         <v>1</v>
@@ -12658,147 +12652,128 @@
       <c r="A4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D4">
-        <v>1</v>
-      </c>
-      <c r="L4">
+      <c r="E4">
+        <v>2</v>
+      </c>
+      <c r="J4">
+        <v>1</v>
+      </c>
+      <c r="K4">
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>6</v>
+        <v>8</v>
+      </c>
+      <c r="B5">
+        <v>1</v>
+      </c>
+      <c r="C5">
+        <v>1</v>
+      </c>
+      <c r="D5">
+        <v>2</v>
+      </c>
+      <c r="E5">
+        <v>2</v>
       </c>
       <c r="G5">
+        <v>1</v>
+      </c>
+      <c r="I5">
+        <v>1</v>
+      </c>
+      <c r="J5">
+        <v>3</v>
+      </c>
+      <c r="K5">
+        <v>4</v>
+      </c>
+      <c r="M5">
         <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
-        <v>7</v>
+        <v>9</v>
+      </c>
+      <c r="B6">
+        <v>8</v>
+      </c>
+      <c r="C6">
+        <v>13</v>
+      </c>
+      <c r="D6">
+        <v>10</v>
+      </c>
+      <c r="E6">
+        <v>9</v>
+      </c>
+      <c r="F6">
+        <v>9</v>
+      </c>
+      <c r="G6">
+        <v>8</v>
+      </c>
+      <c r="H6">
+        <v>1</v>
+      </c>
+      <c r="I6">
+        <v>4</v>
       </c>
       <c r="J6">
-        <v>1</v>
+        <v>5</v>
+      </c>
+      <c r="K6">
+        <v>8</v>
+      </c>
+      <c r="L6">
+        <v>3</v>
+      </c>
+      <c r="M6">
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7">
+        <v>10</v>
+      </c>
+      <c r="C7">
+        <v>15</v>
+      </c>
+      <c r="D7">
+        <v>13</v>
+      </c>
+      <c r="E7">
+        <v>13</v>
+      </c>
+      <c r="F7">
+        <v>10</v>
+      </c>
+      <c r="G7">
+        <v>12</v>
+      </c>
+      <c r="H7">
+        <v>1</v>
+      </c>
+      <c r="I7">
         <v>8</v>
       </c>
-      <c r="B7">
-        <v>4</v>
-      </c>
-      <c r="C7">
-        <v>2</v>
-      </c>
-      <c r="D7">
-        <v>8</v>
-      </c>
-      <c r="E7">
-        <v>5</v>
-      </c>
-      <c r="F7">
-        <v>4</v>
-      </c>
-      <c r="G7">
-        <v>4</v>
-      </c>
-      <c r="I7">
-        <v>3</v>
-      </c>
       <c r="J7">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="K7">
+        <v>15</v>
+      </c>
+      <c r="L7">
         <v>6</v>
       </c>
-      <c r="L7">
-        <v>5</v>
-      </c>
       <c r="M7">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13">
-      <c r="A8" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B8">
-        <v>11</v>
-      </c>
-      <c r="C8">
-        <v>22</v>
-      </c>
-      <c r="D8">
-        <v>24</v>
-      </c>
-      <c r="E8">
-        <v>19</v>
-      </c>
-      <c r="F8">
-        <v>10</v>
-      </c>
-      <c r="G8">
-        <v>4</v>
-      </c>
-      <c r="H8">
-        <v>4</v>
-      </c>
-      <c r="I8">
-        <v>4</v>
-      </c>
-      <c r="J8">
-        <v>4</v>
-      </c>
-      <c r="K8">
-        <v>4</v>
-      </c>
-      <c r="L8">
-        <v>3</v>
-      </c>
-      <c r="M8">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13">
-      <c r="A9" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B9">
-        <v>17</v>
-      </c>
-      <c r="C9">
-        <v>27</v>
-      </c>
-      <c r="D9">
-        <v>35</v>
-      </c>
-      <c r="E9">
-        <v>28</v>
-      </c>
-      <c r="F9">
-        <v>15</v>
-      </c>
-      <c r="G9">
-        <v>9</v>
-      </c>
-      <c r="H9">
-        <v>5</v>
-      </c>
-      <c r="I9">
-        <v>9</v>
-      </c>
-      <c r="J9">
-        <v>11</v>
-      </c>
-      <c r="K9">
-        <v>19</v>
-      </c>
-      <c r="L9">
-        <v>16</v>
-      </c>
-      <c r="M9">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -12871,45 +12846,69 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
       <c r="D2">
         <v>1</v>
       </c>
       <c r="E2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F2">
         <v>1</v>
       </c>
-      <c r="G2">
-        <v>1</v>
-      </c>
-      <c r="M2">
-        <v>1</v>
+      <c r="J2">
+        <v>1</v>
+      </c>
+      <c r="K2">
+        <v>6</v>
+      </c>
+      <c r="L2">
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
+      <c r="B3">
+        <v>2</v>
+      </c>
+      <c r="C3">
+        <v>2</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
       <c r="E3">
-        <v>1</v>
-      </c>
-      <c r="F3">
-        <v>2</v>
+        <v>3</v>
+      </c>
+      <c r="H3">
+        <v>1</v>
       </c>
       <c r="I3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J3">
-        <v>3</v>
+        <v>1</v>
+      </c>
+      <c r="K3">
+        <v>3</v>
+      </c>
+      <c r="L3">
+        <v>2</v>
       </c>
       <c r="M3">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
-        <v>3</v>
+        <v>5</v>
+      </c>
+      <c r="D4">
+        <v>1</v>
       </c>
       <c r="L4">
         <v>1</v>
@@ -12917,9 +12916,9 @@
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="K5">
+        <v>6</v>
+      </c>
+      <c r="G5">
         <v>1</v>
       </c>
     </row>
@@ -12927,7 +12926,7 @@
       <c r="A6" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="H6">
+      <c r="J6">
         <v>1</v>
       </c>
     </row>
@@ -12935,32 +12934,38 @@
       <c r="A7" s="1" t="s">
         <v>8</v>
       </c>
+      <c r="B7">
+        <v>4</v>
+      </c>
       <c r="C7">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D7">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E7">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F7">
-        <v>1</v>
-      </c>
-      <c r="H7">
-        <v>3</v>
+        <v>4</v>
+      </c>
+      <c r="G7">
+        <v>4</v>
       </c>
       <c r="I7">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J7">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K7">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="L7">
-        <v>1</v>
+        <v>5</v>
+      </c>
+      <c r="M7">
+        <v>3</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -12968,40 +12973,40 @@
         <v>9</v>
       </c>
       <c r="B8">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="C8">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="D8">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="E8">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="F8">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="G8">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="H8">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I8">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="J8">
         <v>4</v>
       </c>
       <c r="K8">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="L8">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="M8">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -13009,40 +13014,40 @@
         <v>10</v>
       </c>
       <c r="B9">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C9">
+        <v>27</v>
+      </c>
+      <c r="D9">
+        <v>35</v>
+      </c>
+      <c r="E9">
+        <v>28</v>
+      </c>
+      <c r="F9">
+        <v>15</v>
+      </c>
+      <c r="G9">
+        <v>9</v>
+      </c>
+      <c r="H9">
+        <v>5</v>
+      </c>
+      <c r="I9">
+        <v>9</v>
+      </c>
+      <c r="J9">
+        <v>11</v>
+      </c>
+      <c r="K9">
+        <v>19</v>
+      </c>
+      <c r="L9">
         <v>16</v>
       </c>
-      <c r="D9">
-        <v>32</v>
-      </c>
-      <c r="E9">
-        <v>37</v>
-      </c>
-      <c r="F9">
-        <v>30</v>
-      </c>
-      <c r="G9">
-        <v>8</v>
-      </c>
-      <c r="H9">
-        <v>10</v>
-      </c>
-      <c r="I9">
-        <v>17</v>
-      </c>
-      <c r="J9">
-        <v>8</v>
-      </c>
-      <c r="K9">
-        <v>11</v>
-      </c>
-      <c r="L9">
-        <v>13</v>
-      </c>
       <c r="M9">
-        <v>11</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -13051,6 +13056,525 @@
 </file>
 
 <file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:M9"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+    <col min="13" max="13" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="M1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="E2">
+        <v>2</v>
+      </c>
+      <c r="F2">
+        <v>1</v>
+      </c>
+      <c r="G2">
+        <v>1</v>
+      </c>
+      <c r="M2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E3">
+        <v>1</v>
+      </c>
+      <c r="F3">
+        <v>2</v>
+      </c>
+      <c r="I3">
+        <v>1</v>
+      </c>
+      <c r="J3">
+        <v>3</v>
+      </c>
+      <c r="M3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="L4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="K5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="H6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C7">
+        <v>3</v>
+      </c>
+      <c r="D7">
+        <v>2</v>
+      </c>
+      <c r="E7">
+        <v>3</v>
+      </c>
+      <c r="F7">
+        <v>1</v>
+      </c>
+      <c r="H7">
+        <v>3</v>
+      </c>
+      <c r="I7">
+        <v>5</v>
+      </c>
+      <c r="J7">
+        <v>1</v>
+      </c>
+      <c r="K7">
+        <v>1</v>
+      </c>
+      <c r="L7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13">
+      <c r="A8" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B8">
+        <v>18</v>
+      </c>
+      <c r="C8">
+        <v>13</v>
+      </c>
+      <c r="D8">
+        <v>29</v>
+      </c>
+      <c r="E8">
+        <v>31</v>
+      </c>
+      <c r="F8">
+        <v>26</v>
+      </c>
+      <c r="G8">
+        <v>7</v>
+      </c>
+      <c r="H8">
+        <v>6</v>
+      </c>
+      <c r="I8">
+        <v>11</v>
+      </c>
+      <c r="J8">
+        <v>4</v>
+      </c>
+      <c r="K8">
+        <v>9</v>
+      </c>
+      <c r="L8">
+        <v>11</v>
+      </c>
+      <c r="M8">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13">
+      <c r="A9" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B9">
+        <v>18</v>
+      </c>
+      <c r="C9">
+        <v>16</v>
+      </c>
+      <c r="D9">
+        <v>32</v>
+      </c>
+      <c r="E9">
+        <v>37</v>
+      </c>
+      <c r="F9">
+        <v>30</v>
+      </c>
+      <c r="G9">
+        <v>8</v>
+      </c>
+      <c r="H9">
+        <v>10</v>
+      </c>
+      <c r="I9">
+        <v>17</v>
+      </c>
+      <c r="J9">
+        <v>8</v>
+      </c>
+      <c r="K9">
+        <v>11</v>
+      </c>
+      <c r="L9">
+        <v>13</v>
+      </c>
+      <c r="M9">
+        <v>11</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:M8"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+    <col min="13" max="13" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="M1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>2</v>
+      </c>
+      <c r="G2">
+        <v>4</v>
+      </c>
+      <c r="H2">
+        <v>1</v>
+      </c>
+      <c r="I2">
+        <v>1</v>
+      </c>
+      <c r="J2">
+        <v>3</v>
+      </c>
+      <c r="K2">
+        <v>2</v>
+      </c>
+      <c r="L2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
+      <c r="E3">
+        <v>1</v>
+      </c>
+      <c r="H3">
+        <v>1</v>
+      </c>
+      <c r="I3">
+        <v>1</v>
+      </c>
+      <c r="J3">
+        <v>3</v>
+      </c>
+      <c r="K3">
+        <v>1</v>
+      </c>
+      <c r="L3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D4">
+        <v>1</v>
+      </c>
+      <c r="E4">
+        <v>1</v>
+      </c>
+      <c r="J4">
+        <v>1</v>
+      </c>
+      <c r="L4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5">
+        <v>1</v>
+      </c>
+      <c r="J5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6">
+        <v>2</v>
+      </c>
+      <c r="C6">
+        <v>5</v>
+      </c>
+      <c r="D6">
+        <v>3</v>
+      </c>
+      <c r="E6">
+        <v>4</v>
+      </c>
+      <c r="F6">
+        <v>5</v>
+      </c>
+      <c r="G6">
+        <v>5</v>
+      </c>
+      <c r="H6">
+        <v>8</v>
+      </c>
+      <c r="I6">
+        <v>5</v>
+      </c>
+      <c r="J6">
+        <v>8</v>
+      </c>
+      <c r="K6">
+        <v>7</v>
+      </c>
+      <c r="L6">
+        <v>7</v>
+      </c>
+      <c r="M6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7">
+        <v>17</v>
+      </c>
+      <c r="C7">
+        <v>24</v>
+      </c>
+      <c r="D7">
+        <v>35</v>
+      </c>
+      <c r="E7">
+        <v>31</v>
+      </c>
+      <c r="F7">
+        <v>18</v>
+      </c>
+      <c r="G7">
+        <v>17</v>
+      </c>
+      <c r="H7">
+        <v>8</v>
+      </c>
+      <c r="I7">
+        <v>16</v>
+      </c>
+      <c r="J7">
+        <v>15</v>
+      </c>
+      <c r="K7">
+        <v>10</v>
+      </c>
+      <c r="L7">
+        <v>12</v>
+      </c>
+      <c r="M7">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13">
+      <c r="A8" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B8">
+        <v>19</v>
+      </c>
+      <c r="C8">
+        <v>32</v>
+      </c>
+      <c r="D8">
+        <v>42</v>
+      </c>
+      <c r="E8">
+        <v>37</v>
+      </c>
+      <c r="F8">
+        <v>23</v>
+      </c>
+      <c r="G8">
+        <v>26</v>
+      </c>
+      <c r="H8">
+        <v>18</v>
+      </c>
+      <c r="I8">
+        <v>23</v>
+      </c>
+      <c r="J8">
+        <v>31</v>
+      </c>
+      <c r="K8">
+        <v>20</v>
+      </c>
+      <c r="L8">
+        <v>26</v>
+      </c>
+      <c r="M8">
+        <v>8</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet40.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:L6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -13242,334 +13766,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M10"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" customWidth="1"/>
-    <col min="13" max="13" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="M1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2">
-        <v>5</v>
-      </c>
-      <c r="C2">
-        <v>3</v>
-      </c>
-      <c r="D2">
-        <v>7</v>
-      </c>
-      <c r="E2">
-        <v>5</v>
-      </c>
-      <c r="F2">
-        <v>5</v>
-      </c>
-      <c r="G2">
-        <v>4</v>
-      </c>
-      <c r="H2">
-        <v>6</v>
-      </c>
-      <c r="I2">
-        <v>4</v>
-      </c>
-      <c r="J2">
-        <v>7</v>
-      </c>
-      <c r="K2">
-        <v>7</v>
-      </c>
-      <c r="L2">
-        <v>5</v>
-      </c>
-      <c r="M2">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3">
-        <v>3</v>
-      </c>
-      <c r="C3">
-        <v>2</v>
-      </c>
-      <c r="D3">
-        <v>8</v>
-      </c>
-      <c r="E3">
-        <v>9</v>
-      </c>
-      <c r="F3">
-        <v>19</v>
-      </c>
-      <c r="G3">
-        <v>9</v>
-      </c>
-      <c r="H3">
-        <v>8</v>
-      </c>
-      <c r="I3">
-        <v>13</v>
-      </c>
-      <c r="J3">
-        <v>12</v>
-      </c>
-      <c r="K3">
-        <v>17</v>
-      </c>
-      <c r="L3">
-        <v>13</v>
-      </c>
-      <c r="M3">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="I4">
-        <v>1</v>
-      </c>
-      <c r="M4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="K5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="E6">
-        <v>1</v>
-      </c>
-      <c r="F6">
-        <v>2</v>
-      </c>
-      <c r="J6">
-        <v>2</v>
-      </c>
-      <c r="M6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
-      <c r="A7" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E7">
-        <v>1</v>
-      </c>
-      <c r="I7">
-        <v>1</v>
-      </c>
-      <c r="K7">
-        <v>1</v>
-      </c>
-      <c r="L7">
-        <v>1</v>
-      </c>
-      <c r="M7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13">
-      <c r="A8" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B8">
-        <v>24</v>
-      </c>
-      <c r="C8">
-        <v>37</v>
-      </c>
-      <c r="D8">
-        <v>21</v>
-      </c>
-      <c r="E8">
-        <v>22</v>
-      </c>
-      <c r="F8">
-        <v>27</v>
-      </c>
-      <c r="G8">
-        <v>15</v>
-      </c>
-      <c r="H8">
-        <v>25</v>
-      </c>
-      <c r="I8">
-        <v>21</v>
-      </c>
-      <c r="J8">
-        <v>26</v>
-      </c>
-      <c r="K8">
-        <v>49</v>
-      </c>
-      <c r="L8">
-        <v>44</v>
-      </c>
-      <c r="M8">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13">
-      <c r="A9" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B9">
-        <v>45</v>
-      </c>
-      <c r="C9">
-        <v>64</v>
-      </c>
-      <c r="D9">
-        <v>46</v>
-      </c>
-      <c r="E9">
-        <v>50</v>
-      </c>
-      <c r="F9">
-        <v>38</v>
-      </c>
-      <c r="G9">
-        <v>19</v>
-      </c>
-      <c r="H9">
-        <v>27</v>
-      </c>
-      <c r="I9">
-        <v>37</v>
-      </c>
-      <c r="J9">
-        <v>20</v>
-      </c>
-      <c r="K9">
-        <v>35</v>
-      </c>
-      <c r="L9">
-        <v>35</v>
-      </c>
-      <c r="M9">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13">
-      <c r="A10" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B10">
-        <v>77</v>
-      </c>
-      <c r="C10">
-        <v>106</v>
-      </c>
-      <c r="D10">
-        <v>82</v>
-      </c>
-      <c r="E10">
-        <v>88</v>
-      </c>
-      <c r="F10">
-        <v>91</v>
-      </c>
-      <c r="G10">
-        <v>47</v>
-      </c>
-      <c r="H10">
-        <v>66</v>
-      </c>
-      <c r="I10">
-        <v>77</v>
-      </c>
-      <c r="J10">
-        <v>67</v>
-      </c>
-      <c r="K10">
-        <v>110</v>
-      </c>
-      <c r="L10">
-        <v>98</v>
-      </c>
-      <c r="M10">
-        <v>40</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet40.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet41.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -13764,7 +13961,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet41.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet42.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M9"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -14056,7 +14253,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet42.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet43.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -14290,272 +14487,6 @@
       </c>
       <c r="M6">
         <v>8</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet43.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M8"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" customWidth="1"/>
-    <col min="13" max="13" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="M1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="F2">
-        <v>1</v>
-      </c>
-      <c r="G2">
-        <v>2</v>
-      </c>
-      <c r="H2">
-        <v>1</v>
-      </c>
-      <c r="I2">
-        <v>2</v>
-      </c>
-      <c r="J2">
-        <v>2</v>
-      </c>
-      <c r="K2">
-        <v>3</v>
-      </c>
-      <c r="M2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3">
-        <v>1</v>
-      </c>
-      <c r="C3">
-        <v>1</v>
-      </c>
-      <c r="D3">
-        <v>1</v>
-      </c>
-      <c r="E3">
-        <v>2</v>
-      </c>
-      <c r="G3">
-        <v>2</v>
-      </c>
-      <c r="H3">
-        <v>2</v>
-      </c>
-      <c r="I3">
-        <v>3</v>
-      </c>
-      <c r="J3">
-        <v>1</v>
-      </c>
-      <c r="K3">
-        <v>1</v>
-      </c>
-      <c r="M3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="J4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="K5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B6">
-        <v>6</v>
-      </c>
-      <c r="C6">
-        <v>2</v>
-      </c>
-      <c r="D6">
-        <v>5</v>
-      </c>
-      <c r="E6">
-        <v>5</v>
-      </c>
-      <c r="F6">
-        <v>4</v>
-      </c>
-      <c r="G6">
-        <v>4</v>
-      </c>
-      <c r="H6">
-        <v>6</v>
-      </c>
-      <c r="I6">
-        <v>8</v>
-      </c>
-      <c r="J6">
-        <v>4</v>
-      </c>
-      <c r="K6">
-        <v>3</v>
-      </c>
-      <c r="L6">
-        <v>4</v>
-      </c>
-      <c r="M6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
-      <c r="A7" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B7">
-        <v>22</v>
-      </c>
-      <c r="C7">
-        <v>27</v>
-      </c>
-      <c r="D7">
-        <v>23</v>
-      </c>
-      <c r="E7">
-        <v>19</v>
-      </c>
-      <c r="F7">
-        <v>23</v>
-      </c>
-      <c r="G7">
-        <v>9</v>
-      </c>
-      <c r="H7">
-        <v>6</v>
-      </c>
-      <c r="I7">
-        <v>14</v>
-      </c>
-      <c r="J7">
-        <v>11</v>
-      </c>
-      <c r="K7">
-        <v>12</v>
-      </c>
-      <c r="L7">
-        <v>10</v>
-      </c>
-      <c r="M7">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13">
-      <c r="A8" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B8">
-        <v>29</v>
-      </c>
-      <c r="C8">
-        <v>30</v>
-      </c>
-      <c r="D8">
-        <v>29</v>
-      </c>
-      <c r="E8">
-        <v>26</v>
-      </c>
-      <c r="F8">
-        <v>28</v>
-      </c>
-      <c r="G8">
-        <v>17</v>
-      </c>
-      <c r="H8">
-        <v>15</v>
-      </c>
-      <c r="I8">
-        <v>27</v>
-      </c>
-      <c r="J8">
-        <v>19</v>
-      </c>
-      <c r="K8">
-        <v>20</v>
-      </c>
-      <c r="L8">
-        <v>14</v>
-      </c>
-      <c r="M8">
-        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -15924,10 +15855,10 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:M10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="18.7109375" customWidth="1"/>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
     <col min="2" max="2" width="4.7109375" customWidth="1"/>
     <col min="3" max="3" width="4.7109375" customWidth="1"/>
     <col min="4" max="4" width="4.7109375" customWidth="1"/>
@@ -15988,40 +15919,40 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D2">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F2">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H2">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J2">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="K2">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="L2">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="M2">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -16029,77 +15960,47 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C3">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D3">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E3">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="F3">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="G3">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="H3">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I3">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="J3">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="K3">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="L3">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="M3">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4">
-        <v>11</v>
-      </c>
-      <c r="C4">
-        <v>10</v>
-      </c>
-      <c r="D4">
-        <v>6</v>
-      </c>
-      <c r="E4">
-        <v>7</v>
-      </c>
-      <c r="F4">
-        <v>7</v>
-      </c>
-      <c r="G4">
-        <v>7</v>
-      </c>
-      <c r="H4">
         <v>3</v>
       </c>
       <c r="I4">
-        <v>8</v>
-      </c>
-      <c r="J4">
-        <v>12</v>
-      </c>
-      <c r="K4">
-        <v>4</v>
-      </c>
-      <c r="L4">
         <v>1</v>
       </c>
       <c r="M4">
@@ -16108,84 +16009,170 @@
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B5">
-        <v>15</v>
-      </c>
-      <c r="C5">
-        <v>16</v>
-      </c>
-      <c r="D5">
-        <v>22</v>
-      </c>
-      <c r="E5">
-        <v>14</v>
-      </c>
-      <c r="F5">
-        <v>13</v>
-      </c>
-      <c r="G5">
-        <v>6</v>
-      </c>
-      <c r="H5">
-        <v>11</v>
-      </c>
-      <c r="I5">
-        <v>4</v>
-      </c>
-      <c r="J5">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="K5">
-        <v>8</v>
-      </c>
-      <c r="L5">
-        <v>7</v>
-      </c>
-      <c r="M5">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="E6">
+        <v>1</v>
+      </c>
+      <c r="F6">
+        <v>2</v>
+      </c>
+      <c r="J6">
+        <v>2</v>
+      </c>
+      <c r="M6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E7">
+        <v>1</v>
+      </c>
+      <c r="I7">
+        <v>1</v>
+      </c>
+      <c r="K7">
+        <v>1</v>
+      </c>
+      <c r="L7">
+        <v>1</v>
+      </c>
+      <c r="M7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13">
+      <c r="A8" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8">
+        <v>24</v>
+      </c>
+      <c r="C8">
+        <v>37</v>
+      </c>
+      <c r="D8">
+        <v>21</v>
+      </c>
+      <c r="E8">
+        <v>22</v>
+      </c>
+      <c r="F8">
+        <v>27</v>
+      </c>
+      <c r="G8">
+        <v>15</v>
+      </c>
+      <c r="H8">
+        <v>25</v>
+      </c>
+      <c r="I8">
+        <v>21</v>
+      </c>
+      <c r="J8">
+        <v>26</v>
+      </c>
+      <c r="K8">
+        <v>49</v>
+      </c>
+      <c r="L8">
+        <v>44</v>
+      </c>
+      <c r="M8">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13">
+      <c r="A9" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B9">
+        <v>45</v>
+      </c>
+      <c r="C9">
+        <v>64</v>
+      </c>
+      <c r="D9">
+        <v>46</v>
+      </c>
+      <c r="E9">
+        <v>50</v>
+      </c>
+      <c r="F9">
+        <v>38</v>
+      </c>
+      <c r="G9">
+        <v>19</v>
+      </c>
+      <c r="H9">
+        <v>27</v>
+      </c>
+      <c r="I9">
+        <v>37</v>
+      </c>
+      <c r="J9">
+        <v>20</v>
+      </c>
+      <c r="K9">
+        <v>35</v>
+      </c>
+      <c r="L9">
+        <v>35</v>
+      </c>
+      <c r="M9">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13">
+      <c r="A10" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B6">
-        <v>30</v>
-      </c>
-      <c r="C6">
-        <v>31</v>
-      </c>
-      <c r="D6">
-        <v>34</v>
-      </c>
-      <c r="E6">
-        <v>25</v>
-      </c>
-      <c r="F6">
-        <v>25</v>
-      </c>
-      <c r="G6">
-        <v>15</v>
-      </c>
-      <c r="H6">
-        <v>22</v>
-      </c>
-      <c r="I6">
-        <v>16</v>
-      </c>
-      <c r="J6">
-        <v>28</v>
-      </c>
-      <c r="K6">
-        <v>17</v>
-      </c>
-      <c r="L6">
-        <v>16</v>
-      </c>
-      <c r="M6">
-        <v>12</v>
+      <c r="B10">
+        <v>77</v>
+      </c>
+      <c r="C10">
+        <v>106</v>
+      </c>
+      <c r="D10">
+        <v>82</v>
+      </c>
+      <c r="E10">
+        <v>88</v>
+      </c>
+      <c r="F10">
+        <v>91</v>
+      </c>
+      <c r="G10">
+        <v>47</v>
+      </c>
+      <c r="H10">
+        <v>66</v>
+      </c>
+      <c r="I10">
+        <v>77</v>
+      </c>
+      <c r="J10">
+        <v>67</v>
+      </c>
+      <c r="K10">
+        <v>110</v>
+      </c>
+      <c r="L10">
+        <v>98</v>
+      </c>
+      <c r="M10">
+        <v>40</v>
       </c>
     </row>
   </sheetData>
@@ -18698,10 +18685,10 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M10"/>
+  <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="1" max="1" width="18.7109375" customWidth="1"/>
     <col min="2" max="2" width="4.7109375" customWidth="1"/>
     <col min="3" max="3" width="4.7109375" customWidth="1"/>
     <col min="4" max="4" width="4.7109375" customWidth="1"/>
@@ -18762,40 +18749,40 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D2">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="E2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F2">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="G2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H2">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="I2">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="J2">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="K2">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="L2">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="M2">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -18803,246 +18790,163 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="C3">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="D3">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="E3">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="F3">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="G3">
-        <v>26</v>
+        <v>1</v>
       </c>
       <c r="H3">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="I3">
-        <v>32</v>
+        <v>2</v>
       </c>
       <c r="J3">
-        <v>40</v>
+        <v>2</v>
       </c>
       <c r="K3">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="L3">
-        <v>34</v>
+        <v>6</v>
       </c>
       <c r="M3">
-        <v>17</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
-        <v>3</v>
+        <v>8</v>
+      </c>
+      <c r="B4">
+        <v>11</v>
+      </c>
+      <c r="C4">
+        <v>10</v>
+      </c>
+      <c r="D4">
+        <v>6</v>
+      </c>
+      <c r="E4">
+        <v>7</v>
+      </c>
+      <c r="F4">
+        <v>7</v>
       </c>
       <c r="G4">
-        <v>1</v>
+        <v>7</v>
+      </c>
+      <c r="H4">
+        <v>3</v>
+      </c>
+      <c r="I4">
+        <v>8</v>
       </c>
       <c r="J4">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="K4">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L4">
         <v>1</v>
       </c>
       <c r="M4">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
+      </c>
+      <c r="B5">
+        <v>15</v>
       </c>
       <c r="C5">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="D5">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="E5">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="F5">
-        <v>1</v>
+        <v>13</v>
+      </c>
+      <c r="G5">
+        <v>6</v>
       </c>
       <c r="H5">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="I5">
         <v>4</v>
       </c>
       <c r="J5">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="K5">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="L5">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M5">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
-        <v>6</v>
+        <v>10</v>
+      </c>
+      <c r="B6">
+        <v>30</v>
+      </c>
+      <c r="C6">
+        <v>31</v>
+      </c>
+      <c r="D6">
+        <v>34</v>
+      </c>
+      <c r="E6">
+        <v>25</v>
+      </c>
+      <c r="F6">
+        <v>25</v>
       </c>
       <c r="G6">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="H6">
-        <v>2</v>
+        <v>22</v>
+      </c>
+      <c r="I6">
+        <v>16</v>
       </c>
       <c r="J6">
-        <v>2</v>
+        <v>28</v>
+      </c>
+      <c r="K6">
+        <v>17</v>
       </c>
       <c r="L6">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="M6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
-      <c r="A7" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="K7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13">
-      <c r="A8" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B8">
-        <v>30</v>
-      </c>
-      <c r="C8">
-        <v>44</v>
-      </c>
-      <c r="D8">
-        <v>49</v>
-      </c>
-      <c r="E8">
-        <v>67</v>
-      </c>
-      <c r="F8">
-        <v>69</v>
-      </c>
-      <c r="G8">
-        <v>57</v>
-      </c>
-      <c r="H8">
-        <v>80</v>
-      </c>
-      <c r="I8">
-        <v>80</v>
-      </c>
-      <c r="J8">
-        <v>64</v>
-      </c>
-      <c r="K8">
-        <v>48</v>
-      </c>
-      <c r="L8">
-        <v>44</v>
-      </c>
-      <c r="M8">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13">
-      <c r="A9" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B9">
-        <v>233</v>
-      </c>
-      <c r="C9">
-        <v>354</v>
-      </c>
-      <c r="D9">
-        <v>538</v>
-      </c>
-      <c r="E9">
-        <v>705</v>
-      </c>
-      <c r="F9">
-        <v>568</v>
-      </c>
-      <c r="G9">
-        <v>168</v>
-      </c>
-      <c r="H9">
-        <v>116</v>
-      </c>
-      <c r="I9">
-        <v>194</v>
-      </c>
-      <c r="J9">
-        <v>122</v>
-      </c>
-      <c r="K9">
-        <v>114</v>
-      </c>
-      <c r="L9">
-        <v>95</v>
-      </c>
-      <c r="M9">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13">
-      <c r="A10" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B10">
-        <v>282</v>
-      </c>
-      <c r="C10">
-        <v>416</v>
-      </c>
-      <c r="D10">
-        <v>617</v>
-      </c>
-      <c r="E10">
-        <v>797</v>
-      </c>
-      <c r="F10">
-        <v>660</v>
-      </c>
-      <c r="G10">
-        <v>257</v>
-      </c>
-      <c r="H10">
-        <v>236</v>
-      </c>
-      <c r="I10">
-        <v>324</v>
-      </c>
-      <c r="J10">
-        <v>255</v>
-      </c>
-      <c r="K10">
-        <v>207</v>
-      </c>
-      <c r="L10">
-        <v>196</v>
-      </c>
-      <c r="M10">
-        <v>92</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -21149,40 +21053,40 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D2">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="E2">
         <v>5</v>
       </c>
       <c r="F2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H2">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="I2">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="J2">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="K2">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="L2">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="M2">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -21190,47 +21094,59 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="C3">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="D3">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="E3">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="F3">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="G3">
-        <v>7</v>
+        <v>26</v>
       </c>
       <c r="H3">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="I3">
-        <v>6</v>
+        <v>32</v>
       </c>
       <c r="J3">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="K3">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="L3">
-        <v>14</v>
+        <v>34</v>
       </c>
       <c r="M3">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="I4">
+      <c r="G4">
+        <v>1</v>
+      </c>
+      <c r="J4">
+        <v>2</v>
+      </c>
+      <c r="K4">
+        <v>1</v>
+      </c>
+      <c r="L4">
+        <v>1</v>
+      </c>
+      <c r="M4">
         <v>1</v>
       </c>
     </row>
@@ -21238,14 +21154,23 @@
       <c r="A5" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B5">
-        <v>1</v>
+      <c r="C5">
+        <v>2</v>
       </c>
       <c r="D5">
         <v>1</v>
       </c>
       <c r="E5">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="F5">
+        <v>1</v>
+      </c>
+      <c r="H5">
+        <v>2</v>
+      </c>
+      <c r="I5">
+        <v>4</v>
       </c>
       <c r="J5">
         <v>3</v>
@@ -21253,15 +21178,30 @@
       <c r="K5">
         <v>2</v>
       </c>
+      <c r="L5">
+        <v>5</v>
+      </c>
       <c r="M5">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="K6">
+      <c r="G6">
+        <v>1</v>
+      </c>
+      <c r="H6">
+        <v>2</v>
+      </c>
+      <c r="J6">
+        <v>2</v>
+      </c>
+      <c r="L6">
+        <v>2</v>
+      </c>
+      <c r="M6">
         <v>1</v>
       </c>
     </row>
@@ -21269,7 +21209,7 @@
       <c r="A7" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="L7">
+      <c r="K7">
         <v>1</v>
       </c>
     </row>
@@ -21278,40 +21218,40 @@
         <v>8</v>
       </c>
       <c r="B8">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="C8">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="D8">
-        <v>22</v>
+        <v>49</v>
       </c>
       <c r="E8">
+        <v>67</v>
+      </c>
+      <c r="F8">
+        <v>69</v>
+      </c>
+      <c r="G8">
+        <v>57</v>
+      </c>
+      <c r="H8">
+        <v>80</v>
+      </c>
+      <c r="I8">
+        <v>80</v>
+      </c>
+      <c r="J8">
+        <v>64</v>
+      </c>
+      <c r="K8">
+        <v>48</v>
+      </c>
+      <c r="L8">
         <v>44</v>
       </c>
-      <c r="F8">
-        <v>38</v>
-      </c>
-      <c r="G8">
-        <v>24</v>
-      </c>
-      <c r="H8">
-        <v>50</v>
-      </c>
-      <c r="I8">
-        <v>34</v>
-      </c>
-      <c r="J8">
-        <v>26</v>
-      </c>
-      <c r="K8">
-        <v>24</v>
-      </c>
-      <c r="L8">
-        <v>14</v>
-      </c>
       <c r="M8">
-        <v>15</v>
+        <v>20</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -21319,40 +21259,40 @@
         <v>9</v>
       </c>
       <c r="B9">
-        <v>46</v>
+        <v>233</v>
       </c>
       <c r="C9">
-        <v>59</v>
+        <v>354</v>
       </c>
       <c r="D9">
-        <v>33</v>
+        <v>538</v>
       </c>
       <c r="E9">
-        <v>73</v>
+        <v>705</v>
       </c>
       <c r="F9">
+        <v>568</v>
+      </c>
+      <c r="G9">
+        <v>168</v>
+      </c>
+      <c r="H9">
+        <v>116</v>
+      </c>
+      <c r="I9">
+        <v>194</v>
+      </c>
+      <c r="J9">
+        <v>122</v>
+      </c>
+      <c r="K9">
         <v>114</v>
       </c>
-      <c r="G9">
-        <v>58</v>
-      </c>
-      <c r="H9">
-        <v>41</v>
-      </c>
-      <c r="I9">
-        <v>44</v>
-      </c>
-      <c r="J9">
-        <v>20</v>
-      </c>
-      <c r="K9">
-        <v>25</v>
-      </c>
       <c r="L9">
-        <v>27</v>
+        <v>95</v>
       </c>
       <c r="M9">
-        <v>16</v>
+        <v>47</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -21360,40 +21300,40 @@
         <v>10</v>
       </c>
       <c r="B10">
-        <v>78</v>
+        <v>282</v>
       </c>
       <c r="C10">
-        <v>99</v>
+        <v>416</v>
       </c>
       <c r="D10">
-        <v>65</v>
+        <v>617</v>
       </c>
       <c r="E10">
-        <v>130</v>
+        <v>797</v>
       </c>
       <c r="F10">
-        <v>167</v>
+        <v>660</v>
       </c>
       <c r="G10">
+        <v>257</v>
+      </c>
+      <c r="H10">
+        <v>236</v>
+      </c>
+      <c r="I10">
+        <v>324</v>
+      </c>
+      <c r="J10">
+        <v>255</v>
+      </c>
+      <c r="K10">
+        <v>207</v>
+      </c>
+      <c r="L10">
+        <v>196</v>
+      </c>
+      <c r="M10">
         <v>92</v>
-      </c>
-      <c r="H10">
-        <v>104</v>
-      </c>
-      <c r="I10">
-        <v>89</v>
-      </c>
-      <c r="J10">
-        <v>67</v>
-      </c>
-      <c r="K10">
-        <v>71</v>
-      </c>
-      <c r="L10">
-        <v>61</v>
-      </c>
-      <c r="M10">
-        <v>52</v>
       </c>
     </row>
   </sheetData>
@@ -23241,7 +23181,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M7"/>
+  <dimension ref="A1:M10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="23.7109375" customWidth="1"/>
@@ -23305,185 +23245,251 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E2">
-        <v>2</v>
+        <v>5</v>
+      </c>
+      <c r="F2">
+        <v>9</v>
+      </c>
+      <c r="G2">
+        <v>3</v>
       </c>
       <c r="H2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J2">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="K2">
-        <v>2</v>
+        <v>7</v>
+      </c>
+      <c r="L2">
+        <v>5</v>
       </c>
       <c r="M2">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
+      <c r="B3">
+        <v>4</v>
+      </c>
+      <c r="C3">
+        <v>5</v>
+      </c>
+      <c r="D3">
+        <v>6</v>
+      </c>
       <c r="E3">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="F3">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G3">
-        <v>1</v>
+        <v>7</v>
+      </c>
+      <c r="H3">
+        <v>8</v>
+      </c>
+      <c r="I3">
+        <v>6</v>
       </c>
       <c r="J3">
-        <v>2</v>
+        <v>10</v>
+      </c>
+      <c r="K3">
+        <v>12</v>
       </c>
       <c r="L3">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="M3">
-        <v>4</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B4">
-        <v>1</v>
-      </c>
-      <c r="K4">
+        <v>3</v>
+      </c>
+      <c r="I4">
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B5">
-        <v>2</v>
-      </c>
-      <c r="C5">
         <v>1</v>
       </c>
       <c r="D5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E5">
         <v>1</v>
       </c>
-      <c r="F5">
-        <v>3</v>
-      </c>
-      <c r="G5">
-        <v>4</v>
-      </c>
-      <c r="H5">
-        <v>5</v>
-      </c>
-      <c r="I5">
-        <v>3</v>
-      </c>
       <c r="J5">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="K5">
-        <v>3</v>
-      </c>
-      <c r="L5">
-        <v>3</v>
+        <v>2</v>
+      </c>
+      <c r="M5">
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B6">
-        <v>11</v>
-      </c>
-      <c r="C6">
-        <v>12</v>
-      </c>
-      <c r="D6">
-        <v>29</v>
-      </c>
-      <c r="E6">
-        <v>16</v>
-      </c>
-      <c r="F6">
-        <v>16</v>
-      </c>
-      <c r="G6">
-        <v>8</v>
-      </c>
-      <c r="H6">
-        <v>2</v>
-      </c>
-      <c r="I6">
-        <v>10</v>
-      </c>
-      <c r="J6">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="K6">
-        <v>11</v>
-      </c>
-      <c r="L6">
-        <v>15</v>
-      </c>
-      <c r="M6">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="L7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13">
+      <c r="A8" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8">
+        <v>23</v>
+      </c>
+      <c r="C8">
+        <v>31</v>
+      </c>
+      <c r="D8">
+        <v>22</v>
+      </c>
+      <c r="E8">
+        <v>44</v>
+      </c>
+      <c r="F8">
+        <v>38</v>
+      </c>
+      <c r="G8">
+        <v>24</v>
+      </c>
+      <c r="H8">
+        <v>50</v>
+      </c>
+      <c r="I8">
+        <v>34</v>
+      </c>
+      <c r="J8">
+        <v>26</v>
+      </c>
+      <c r="K8">
+        <v>24</v>
+      </c>
+      <c r="L8">
+        <v>14</v>
+      </c>
+      <c r="M8">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13">
+      <c r="A9" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B9">
+        <v>46</v>
+      </c>
+      <c r="C9">
+        <v>59</v>
+      </c>
+      <c r="D9">
+        <v>33</v>
+      </c>
+      <c r="E9">
+        <v>73</v>
+      </c>
+      <c r="F9">
+        <v>114</v>
+      </c>
+      <c r="G9">
+        <v>58</v>
+      </c>
+      <c r="H9">
+        <v>41</v>
+      </c>
+      <c r="I9">
+        <v>44</v>
+      </c>
+      <c r="J9">
+        <v>20</v>
+      </c>
+      <c r="K9">
+        <v>25</v>
+      </c>
+      <c r="L9">
+        <v>27</v>
+      </c>
+      <c r="M9">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13">
+      <c r="A10" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B7">
-        <v>15</v>
-      </c>
-      <c r="C7">
-        <v>14</v>
-      </c>
-      <c r="D7">
-        <v>33</v>
-      </c>
-      <c r="E7">
-        <v>21</v>
-      </c>
-      <c r="F7">
-        <v>21</v>
-      </c>
-      <c r="G7">
-        <v>13</v>
-      </c>
-      <c r="H7">
-        <v>8</v>
-      </c>
-      <c r="I7">
-        <v>15</v>
-      </c>
-      <c r="J7">
-        <v>22</v>
-      </c>
-      <c r="K7">
-        <v>17</v>
-      </c>
-      <c r="L7">
-        <v>20</v>
-      </c>
-      <c r="M7">
-        <v>11</v>
+      <c r="B10">
+        <v>78</v>
+      </c>
+      <c r="C10">
+        <v>99</v>
+      </c>
+      <c r="D10">
+        <v>65</v>
+      </c>
+      <c r="E10">
+        <v>130</v>
+      </c>
+      <c r="F10">
+        <v>167</v>
+      </c>
+      <c r="G10">
+        <v>92</v>
+      </c>
+      <c r="H10">
+        <v>104</v>
+      </c>
+      <c r="I10">
+        <v>89</v>
+      </c>
+      <c r="J10">
+        <v>67</v>
+      </c>
+      <c r="K10">
+        <v>71</v>
+      </c>
+      <c r="L10">
+        <v>61</v>
+      </c>
+      <c r="M10">
+        <v>52</v>
       </c>
     </row>
   </sheetData>
@@ -25338,67 +25344,64 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
       </c>
       <c r="D2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J2">
         <v>1</v>
       </c>
       <c r="K2">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="M2">
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B3">
-        <v>1</v>
-      </c>
-      <c r="D3">
-        <v>1</v>
-      </c>
       <c r="E3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F3">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G3">
-        <v>2</v>
-      </c>
-      <c r="H3">
-        <v>2</v>
-      </c>
-      <c r="I3">
-        <v>4</v>
-      </c>
-      <c r="K3">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="J3">
+        <v>2</v>
       </c>
       <c r="L3">
         <v>2</v>
       </c>
       <c r="M3">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="M4">
+      <c r="B4">
+        <v>1</v>
+      </c>
+      <c r="K4">
         <v>1</v>
       </c>
     </row>
@@ -25407,40 +25410,37 @@
         <v>8</v>
       </c>
       <c r="B5">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D5">
         <v>3</v>
       </c>
       <c r="E5">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="F5">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="G5">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="H5">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="I5">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="J5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K5">
         <v>3</v>
       </c>
       <c r="L5">
-        <v>5</v>
-      </c>
-      <c r="M5">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -25448,40 +25448,40 @@
         <v>9</v>
       </c>
       <c r="B6">
-        <v>34</v>
+        <v>11</v>
       </c>
       <c r="C6">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="D6">
-        <v>64</v>
+        <v>29</v>
       </c>
       <c r="E6">
-        <v>44</v>
+        <v>16</v>
       </c>
       <c r="F6">
-        <v>45</v>
+        <v>16</v>
       </c>
       <c r="G6">
+        <v>8</v>
+      </c>
+      <c r="H6">
+        <v>2</v>
+      </c>
+      <c r="I6">
+        <v>10</v>
+      </c>
+      <c r="J6">
+        <v>13</v>
+      </c>
+      <c r="K6">
         <v>11</v>
       </c>
-      <c r="H6">
-        <v>7</v>
-      </c>
-      <c r="I6">
-        <v>7</v>
-      </c>
-      <c r="J6">
+      <c r="L6">
         <v>15</v>
       </c>
-      <c r="K6">
-        <v>9</v>
-      </c>
-      <c r="L6">
-        <v>12</v>
-      </c>
       <c r="M6">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -25489,40 +25489,40 @@
         <v>10</v>
       </c>
       <c r="B7">
-        <v>42</v>
+        <v>15</v>
       </c>
       <c r="C7">
-        <v>37</v>
+        <v>14</v>
       </c>
       <c r="D7">
-        <v>70</v>
+        <v>33</v>
       </c>
       <c r="E7">
-        <v>55</v>
+        <v>21</v>
       </c>
       <c r="F7">
-        <v>58</v>
+        <v>21</v>
       </c>
       <c r="G7">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="H7">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="I7">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="J7">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K7">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="L7">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="M7">
-        <v>5</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>

--- a/output/cta-index-crime-full-year.xlsx
+++ b/output/cta-index-crime-full-year.xlsx
@@ -9,49 +9,49 @@
   <sheets>
     <sheet name="Citywide Totals" sheetId="1" r:id="rId1"/>
     <sheet name="By Neighborhood" sheetId="2" r:id="rId2"/>
-    <sheet name="Near South Side" sheetId="3" r:id="rId3"/>
-    <sheet name="Logan Square" sheetId="4" r:id="rId4"/>
-    <sheet name="Grand Crossing" sheetId="5" r:id="rId5"/>
-    <sheet name="South Shore" sheetId="6" r:id="rId6"/>
-    <sheet name="Loop" sheetId="7" r:id="rId7"/>
-    <sheet name="Austin" sheetId="8" r:id="rId8"/>
-    <sheet name="Avondale" sheetId="9" r:id="rId9"/>
-    <sheet name="Rush &amp; Division" sheetId="10" r:id="rId10"/>
-    <sheet name="Chatham" sheetId="11" r:id="rId11"/>
-    <sheet name="Oakland" sheetId="12" r:id="rId12"/>
-    <sheet name="River North" sheetId="13" r:id="rId13"/>
-    <sheet name="Old Town" sheetId="14" r:id="rId14"/>
-    <sheet name="New City" sheetId="15" r:id="rId15"/>
-    <sheet name="Belmont Cragin" sheetId="16" r:id="rId16"/>
-    <sheet name="Woodlawn" sheetId="17" r:id="rId17"/>
-    <sheet name="West Loop" sheetId="18" r:id="rId18"/>
-    <sheet name="Printers Row" sheetId="19" r:id="rId19"/>
-    <sheet name="Uptown" sheetId="20" r:id="rId20"/>
-    <sheet name="Lake View" sheetId="21" r:id="rId21"/>
-    <sheet name="North Lawndale" sheetId="22" r:id="rId22"/>
-    <sheet name="Hyde Park" sheetId="23" r:id="rId23"/>
-    <sheet name="Grand Boulevard" sheetId="24" r:id="rId24"/>
-    <sheet name="West Town" sheetId="25" r:id="rId25"/>
-    <sheet name="Douglas" sheetId="26" r:id="rId26"/>
-    <sheet name="Norwood Park" sheetId="27" r:id="rId27"/>
-    <sheet name="Washington Park" sheetId="28" r:id="rId28"/>
-    <sheet name="Fuller Park" sheetId="29" r:id="rId29"/>
-    <sheet name="Englewood" sheetId="30" r:id="rId30"/>
-    <sheet name="Greektown" sheetId="31" r:id="rId31"/>
-    <sheet name="Rogers Park" sheetId="32" r:id="rId32"/>
-    <sheet name="Garfield Park" sheetId="33" r:id="rId33"/>
-    <sheet name="Lincoln Park" sheetId="34" r:id="rId34"/>
-    <sheet name="Edgewater" sheetId="35" r:id="rId35"/>
-    <sheet name="Little Italy, UIC" sheetId="36" r:id="rId36"/>
-    <sheet name="Albany Park" sheetId="37" r:id="rId37"/>
-    <sheet name="Gage Park" sheetId="38" r:id="rId38"/>
-    <sheet name="Wicker Park" sheetId="39" r:id="rId39"/>
-    <sheet name="Avalon Park" sheetId="40" r:id="rId40"/>
-    <sheet name="Kenwood" sheetId="41" r:id="rId41"/>
-    <sheet name="Humboldt Park" sheetId="42" r:id="rId42"/>
-    <sheet name="Lower West Side" sheetId="43" r:id="rId43"/>
-    <sheet name="North Center" sheetId="44" r:id="rId44"/>
-    <sheet name="O'Hare" sheetId="45" r:id="rId45"/>
+    <sheet name="Loop" sheetId="3" r:id="rId3"/>
+    <sheet name="Lincoln Park" sheetId="4" r:id="rId4"/>
+    <sheet name="O'Hare" sheetId="5" r:id="rId5"/>
+    <sheet name="Near South Side" sheetId="6" r:id="rId6"/>
+    <sheet name="Logan Square" sheetId="7" r:id="rId7"/>
+    <sheet name="Grand Crossing" sheetId="8" r:id="rId8"/>
+    <sheet name="South Shore" sheetId="9" r:id="rId9"/>
+    <sheet name="Austin" sheetId="10" r:id="rId10"/>
+    <sheet name="Avondale" sheetId="11" r:id="rId11"/>
+    <sheet name="Rush &amp; Division" sheetId="12" r:id="rId12"/>
+    <sheet name="Chatham" sheetId="13" r:id="rId13"/>
+    <sheet name="Oakland" sheetId="14" r:id="rId14"/>
+    <sheet name="River North" sheetId="15" r:id="rId15"/>
+    <sheet name="Old Town" sheetId="16" r:id="rId16"/>
+    <sheet name="New City" sheetId="17" r:id="rId17"/>
+    <sheet name="Belmont Cragin" sheetId="18" r:id="rId18"/>
+    <sheet name="Woodlawn" sheetId="19" r:id="rId19"/>
+    <sheet name="West Loop" sheetId="20" r:id="rId20"/>
+    <sheet name="Printers Row" sheetId="21" r:id="rId21"/>
+    <sheet name="Uptown" sheetId="22" r:id="rId22"/>
+    <sheet name="Lake View" sheetId="23" r:id="rId23"/>
+    <sheet name="North Lawndale" sheetId="24" r:id="rId24"/>
+    <sheet name="Hyde Park" sheetId="25" r:id="rId25"/>
+    <sheet name="Grand Boulevard" sheetId="26" r:id="rId26"/>
+    <sheet name="West Town" sheetId="27" r:id="rId27"/>
+    <sheet name="Douglas" sheetId="28" r:id="rId28"/>
+    <sheet name="Norwood Park" sheetId="29" r:id="rId29"/>
+    <sheet name="Washington Park" sheetId="30" r:id="rId30"/>
+    <sheet name="Fuller Park" sheetId="31" r:id="rId31"/>
+    <sheet name="Englewood" sheetId="32" r:id="rId32"/>
+    <sheet name="Greektown" sheetId="33" r:id="rId33"/>
+    <sheet name="Rogers Park" sheetId="34" r:id="rId34"/>
+    <sheet name="Garfield Park" sheetId="35" r:id="rId35"/>
+    <sheet name="Edgewater" sheetId="36" r:id="rId36"/>
+    <sheet name="Little Italy, UIC" sheetId="37" r:id="rId37"/>
+    <sheet name="Albany Park" sheetId="38" r:id="rId38"/>
+    <sheet name="Gage Park" sheetId="39" r:id="rId39"/>
+    <sheet name="Wicker Park" sheetId="40" r:id="rId40"/>
+    <sheet name="Avalon Park" sheetId="41" r:id="rId41"/>
+    <sheet name="Kenwood" sheetId="42" r:id="rId42"/>
+    <sheet name="Humboldt Park" sheetId="43" r:id="rId43"/>
+    <sheet name="Lower West Side" sheetId="44" r:id="rId44"/>
+    <sheet name="North Center" sheetId="45" r:id="rId45"/>
     <sheet name="Sheffield &amp; DePaul" sheetId="46" r:id="rId46"/>
     <sheet name="Mckinley Park" sheetId="47" r:id="rId47"/>
     <sheet name="Lincoln Square" sheetId="48" r:id="rId48"/>
@@ -905,7 +905,7 @@
         <v>137</v>
       </c>
       <c r="M2">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -1156,7 +1156,7 @@
         <v>467</v>
       </c>
       <c r="M9">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -1197,7 +1197,7 @@
         <v>703</v>
       </c>
       <c r="M10">
-        <v>364</v>
+        <v>365</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -1238,7 +1238,7 @@
         <v>1604</v>
       </c>
       <c r="M11">
-        <v>817</v>
+        <v>820</v>
       </c>
     </row>
   </sheetData>
@@ -1247,6 +1247,324 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:M10"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+    <col min="13" max="13" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="M1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>4</v>
+      </c>
+      <c r="C2">
+        <v>4</v>
+      </c>
+      <c r="D2">
+        <v>3</v>
+      </c>
+      <c r="E2">
+        <v>5</v>
+      </c>
+      <c r="F2">
+        <v>9</v>
+      </c>
+      <c r="G2">
+        <v>3</v>
+      </c>
+      <c r="H2">
+        <v>5</v>
+      </c>
+      <c r="I2">
+        <v>4</v>
+      </c>
+      <c r="J2">
+        <v>8</v>
+      </c>
+      <c r="K2">
+        <v>7</v>
+      </c>
+      <c r="L2">
+        <v>5</v>
+      </c>
+      <c r="M2">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>4</v>
+      </c>
+      <c r="C3">
+        <v>5</v>
+      </c>
+      <c r="D3">
+        <v>6</v>
+      </c>
+      <c r="E3">
+        <v>7</v>
+      </c>
+      <c r="F3">
+        <v>6</v>
+      </c>
+      <c r="G3">
+        <v>7</v>
+      </c>
+      <c r="H3">
+        <v>8</v>
+      </c>
+      <c r="I3">
+        <v>6</v>
+      </c>
+      <c r="J3">
+        <v>10</v>
+      </c>
+      <c r="K3">
+        <v>12</v>
+      </c>
+      <c r="L3">
+        <v>14</v>
+      </c>
+      <c r="M3">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="I4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5">
+        <v>1</v>
+      </c>
+      <c r="D5">
+        <v>1</v>
+      </c>
+      <c r="E5">
+        <v>1</v>
+      </c>
+      <c r="J5">
+        <v>3</v>
+      </c>
+      <c r="K5">
+        <v>2</v>
+      </c>
+      <c r="M5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="K6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="L7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13">
+      <c r="A8" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8">
+        <v>23</v>
+      </c>
+      <c r="C8">
+        <v>31</v>
+      </c>
+      <c r="D8">
+        <v>22</v>
+      </c>
+      <c r="E8">
+        <v>44</v>
+      </c>
+      <c r="F8">
+        <v>38</v>
+      </c>
+      <c r="G8">
+        <v>24</v>
+      </c>
+      <c r="H8">
+        <v>50</v>
+      </c>
+      <c r="I8">
+        <v>34</v>
+      </c>
+      <c r="J8">
+        <v>26</v>
+      </c>
+      <c r="K8">
+        <v>24</v>
+      </c>
+      <c r="L8">
+        <v>14</v>
+      </c>
+      <c r="M8">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13">
+      <c r="A9" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B9">
+        <v>46</v>
+      </c>
+      <c r="C9">
+        <v>59</v>
+      </c>
+      <c r="D9">
+        <v>33</v>
+      </c>
+      <c r="E9">
+        <v>73</v>
+      </c>
+      <c r="F9">
+        <v>114</v>
+      </c>
+      <c r="G9">
+        <v>58</v>
+      </c>
+      <c r="H9">
+        <v>41</v>
+      </c>
+      <c r="I9">
+        <v>44</v>
+      </c>
+      <c r="J9">
+        <v>20</v>
+      </c>
+      <c r="K9">
+        <v>25</v>
+      </c>
+      <c r="L9">
+        <v>27</v>
+      </c>
+      <c r="M9">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13">
+      <c r="A10" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B10">
+        <v>78</v>
+      </c>
+      <c r="C10">
+        <v>99</v>
+      </c>
+      <c r="D10">
+        <v>65</v>
+      </c>
+      <c r="E10">
+        <v>130</v>
+      </c>
+      <c r="F10">
+        <v>167</v>
+      </c>
+      <c r="G10">
+        <v>92</v>
+      </c>
+      <c r="H10">
+        <v>104</v>
+      </c>
+      <c r="I10">
+        <v>89</v>
+      </c>
+      <c r="J10">
+        <v>67</v>
+      </c>
+      <c r="K10">
+        <v>71</v>
+      </c>
+      <c r="L10">
+        <v>61</v>
+      </c>
+      <c r="M10">
+        <v>52</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -1312,67 +1630,64 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
       </c>
       <c r="D2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J2">
         <v>1</v>
       </c>
       <c r="K2">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="M2">
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B3">
-        <v>1</v>
-      </c>
-      <c r="D3">
-        <v>1</v>
-      </c>
       <c r="E3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F3">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G3">
-        <v>2</v>
-      </c>
-      <c r="H3">
-        <v>2</v>
-      </c>
-      <c r="I3">
-        <v>4</v>
-      </c>
-      <c r="K3">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="J3">
+        <v>2</v>
       </c>
       <c r="L3">
         <v>2</v>
       </c>
       <c r="M3">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="M4">
+      <c r="B4">
+        <v>1</v>
+      </c>
+      <c r="K4">
         <v>1</v>
       </c>
     </row>
@@ -1381,40 +1696,37 @@
         <v>8</v>
       </c>
       <c r="B5">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D5">
         <v>3</v>
       </c>
       <c r="E5">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="F5">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="G5">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="H5">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="I5">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="J5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K5">
         <v>3</v>
       </c>
       <c r="L5">
-        <v>5</v>
-      </c>
-      <c r="M5">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -1422,40 +1734,40 @@
         <v>9</v>
       </c>
       <c r="B6">
-        <v>34</v>
+        <v>11</v>
       </c>
       <c r="C6">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="D6">
-        <v>64</v>
+        <v>29</v>
       </c>
       <c r="E6">
-        <v>44</v>
+        <v>16</v>
       </c>
       <c r="F6">
-        <v>45</v>
+        <v>16</v>
       </c>
       <c r="G6">
+        <v>8</v>
+      </c>
+      <c r="H6">
+        <v>2</v>
+      </c>
+      <c r="I6">
+        <v>10</v>
+      </c>
+      <c r="J6">
+        <v>13</v>
+      </c>
+      <c r="K6">
         <v>11</v>
       </c>
-      <c r="H6">
-        <v>7</v>
-      </c>
-      <c r="I6">
-        <v>7</v>
-      </c>
-      <c r="J6">
+      <c r="L6">
         <v>15</v>
       </c>
-      <c r="K6">
-        <v>9</v>
-      </c>
-      <c r="L6">
-        <v>12</v>
-      </c>
       <c r="M6">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -1463,40 +1775,40 @@
         <v>10</v>
       </c>
       <c r="B7">
-        <v>42</v>
+        <v>15</v>
       </c>
       <c r="C7">
-        <v>37</v>
+        <v>14</v>
       </c>
       <c r="D7">
-        <v>70</v>
+        <v>33</v>
       </c>
       <c r="E7">
-        <v>55</v>
+        <v>21</v>
       </c>
       <c r="F7">
-        <v>58</v>
+        <v>21</v>
       </c>
       <c r="G7">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="H7">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="I7">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="J7">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K7">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="L7">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="M7">
-        <v>5</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -1504,7 +1816,265 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:M7"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+    <col min="13" max="13" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="M1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>2</v>
+      </c>
+      <c r="D2">
+        <v>2</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
+      <c r="H2">
+        <v>2</v>
+      </c>
+      <c r="I2">
+        <v>1</v>
+      </c>
+      <c r="J2">
+        <v>1</v>
+      </c>
+      <c r="K2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>1</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
+      <c r="E3">
+        <v>3</v>
+      </c>
+      <c r="F3">
+        <v>4</v>
+      </c>
+      <c r="G3">
+        <v>2</v>
+      </c>
+      <c r="H3">
+        <v>2</v>
+      </c>
+      <c r="I3">
+        <v>4</v>
+      </c>
+      <c r="K3">
+        <v>1</v>
+      </c>
+      <c r="L3">
+        <v>2</v>
+      </c>
+      <c r="M3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="M4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5">
+        <v>5</v>
+      </c>
+      <c r="C5">
+        <v>4</v>
+      </c>
+      <c r="D5">
+        <v>3</v>
+      </c>
+      <c r="E5">
+        <v>7</v>
+      </c>
+      <c r="F5">
+        <v>9</v>
+      </c>
+      <c r="G5">
+        <v>14</v>
+      </c>
+      <c r="H5">
+        <v>7</v>
+      </c>
+      <c r="I5">
+        <v>9</v>
+      </c>
+      <c r="J5">
+        <v>5</v>
+      </c>
+      <c r="K5">
+        <v>3</v>
+      </c>
+      <c r="L5">
+        <v>5</v>
+      </c>
+      <c r="M5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6">
+        <v>34</v>
+      </c>
+      <c r="C6">
+        <v>33</v>
+      </c>
+      <c r="D6">
+        <v>64</v>
+      </c>
+      <c r="E6">
+        <v>44</v>
+      </c>
+      <c r="F6">
+        <v>45</v>
+      </c>
+      <c r="G6">
+        <v>11</v>
+      </c>
+      <c r="H6">
+        <v>7</v>
+      </c>
+      <c r="I6">
+        <v>7</v>
+      </c>
+      <c r="J6">
+        <v>15</v>
+      </c>
+      <c r="K6">
+        <v>9</v>
+      </c>
+      <c r="L6">
+        <v>12</v>
+      </c>
+      <c r="M6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7">
+        <v>42</v>
+      </c>
+      <c r="C7">
+        <v>37</v>
+      </c>
+      <c r="D7">
+        <v>70</v>
+      </c>
+      <c r="E7">
+        <v>55</v>
+      </c>
+      <c r="F7">
+        <v>58</v>
+      </c>
+      <c r="G7">
+        <v>27</v>
+      </c>
+      <c r="H7">
+        <v>18</v>
+      </c>
+      <c r="I7">
+        <v>21</v>
+      </c>
+      <c r="J7">
+        <v>21</v>
+      </c>
+      <c r="K7">
+        <v>14</v>
+      </c>
+      <c r="L7">
+        <v>19</v>
+      </c>
+      <c r="M7">
+        <v>5</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M10"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -1819,7 +2389,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:K6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -1977,7 +2547,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -2244,7 +2814,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M8"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -2510,7 +3080,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -2742,7 +3312,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -2955,7 +3525,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -3206,521 +3776,6 @@
       </c>
       <c r="M7">
         <v>9</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M9"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" customWidth="1"/>
-    <col min="13" max="13" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="M1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2">
-        <v>1</v>
-      </c>
-      <c r="C2">
-        <v>2</v>
-      </c>
-      <c r="G2">
-        <v>2</v>
-      </c>
-      <c r="H2">
-        <v>4</v>
-      </c>
-      <c r="I2">
-        <v>3</v>
-      </c>
-      <c r="J2">
-        <v>2</v>
-      </c>
-      <c r="K2">
-        <v>2</v>
-      </c>
-      <c r="L2">
-        <v>1</v>
-      </c>
-      <c r="M2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3">
-        <v>1</v>
-      </c>
-      <c r="D3">
-        <v>2</v>
-      </c>
-      <c r="E3">
-        <v>1</v>
-      </c>
-      <c r="F3">
-        <v>1</v>
-      </c>
-      <c r="G3">
-        <v>2</v>
-      </c>
-      <c r="H3">
-        <v>3</v>
-      </c>
-      <c r="I3">
-        <v>2</v>
-      </c>
-      <c r="J3">
-        <v>1</v>
-      </c>
-      <c r="K3">
-        <v>5</v>
-      </c>
-      <c r="L3">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="F4">
-        <v>1</v>
-      </c>
-      <c r="J4">
-        <v>1</v>
-      </c>
-      <c r="L4">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="I5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
-      <c r="A7" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B7">
-        <v>5</v>
-      </c>
-      <c r="C7">
-        <v>1</v>
-      </c>
-      <c r="D7">
-        <v>6</v>
-      </c>
-      <c r="E7">
-        <v>8</v>
-      </c>
-      <c r="F7">
-        <v>10</v>
-      </c>
-      <c r="G7">
-        <v>8</v>
-      </c>
-      <c r="H7">
-        <v>9</v>
-      </c>
-      <c r="I7">
-        <v>7</v>
-      </c>
-      <c r="J7">
-        <v>4</v>
-      </c>
-      <c r="K7">
-        <v>7</v>
-      </c>
-      <c r="L7">
-        <v>5</v>
-      </c>
-      <c r="M7">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13">
-      <c r="A8" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B8">
-        <v>20</v>
-      </c>
-      <c r="C8">
-        <v>23</v>
-      </c>
-      <c r="D8">
-        <v>35</v>
-      </c>
-      <c r="E8">
-        <v>34</v>
-      </c>
-      <c r="F8">
-        <v>40</v>
-      </c>
-      <c r="G8">
-        <v>20</v>
-      </c>
-      <c r="H8">
-        <v>9</v>
-      </c>
-      <c r="I8">
-        <v>27</v>
-      </c>
-      <c r="J8">
-        <v>22</v>
-      </c>
-      <c r="K8">
-        <v>14</v>
-      </c>
-      <c r="L8">
-        <v>11</v>
-      </c>
-      <c r="M8">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13">
-      <c r="A9" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B9">
-        <v>27</v>
-      </c>
-      <c r="C9">
-        <v>26</v>
-      </c>
-      <c r="D9">
-        <v>44</v>
-      </c>
-      <c r="E9">
-        <v>43</v>
-      </c>
-      <c r="F9">
-        <v>52</v>
-      </c>
-      <c r="G9">
-        <v>32</v>
-      </c>
-      <c r="H9">
-        <v>25</v>
-      </c>
-      <c r="I9">
-        <v>40</v>
-      </c>
-      <c r="J9">
-        <v>30</v>
-      </c>
-      <c r="K9">
-        <v>28</v>
-      </c>
-      <c r="L9">
-        <v>26</v>
-      </c>
-      <c r="M9">
-        <v>17</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M6"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="18.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" customWidth="1"/>
-    <col min="13" max="13" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="M1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2">
-        <v>2</v>
-      </c>
-      <c r="G2">
-        <v>1</v>
-      </c>
-      <c r="I2">
-        <v>1</v>
-      </c>
-      <c r="J2">
-        <v>1</v>
-      </c>
-      <c r="L2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3">
-        <v>1</v>
-      </c>
-      <c r="F3">
-        <v>1</v>
-      </c>
-      <c r="H3">
-        <v>1</v>
-      </c>
-      <c r="J3">
-        <v>1</v>
-      </c>
-      <c r="L3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4">
-        <v>3</v>
-      </c>
-      <c r="C4">
-        <v>5</v>
-      </c>
-      <c r="D4">
-        <v>6</v>
-      </c>
-      <c r="E4">
-        <v>2</v>
-      </c>
-      <c r="F4">
-        <v>7</v>
-      </c>
-      <c r="G4">
-        <v>4</v>
-      </c>
-      <c r="H4">
-        <v>1</v>
-      </c>
-      <c r="I4">
-        <v>10</v>
-      </c>
-      <c r="J4">
-        <v>3</v>
-      </c>
-      <c r="K4">
-        <v>6</v>
-      </c>
-      <c r="L4">
-        <v>3</v>
-      </c>
-      <c r="M4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B5">
-        <v>5</v>
-      </c>
-      <c r="C5">
-        <v>9</v>
-      </c>
-      <c r="D5">
-        <v>8</v>
-      </c>
-      <c r="E5">
-        <v>16</v>
-      </c>
-      <c r="F5">
-        <v>26</v>
-      </c>
-      <c r="G5">
-        <v>3</v>
-      </c>
-      <c r="H5">
-        <v>6</v>
-      </c>
-      <c r="I5">
-        <v>5</v>
-      </c>
-      <c r="J5">
-        <v>6</v>
-      </c>
-      <c r="K5">
-        <v>4</v>
-      </c>
-      <c r="L5">
-        <v>1</v>
-      </c>
-      <c r="M5">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B6">
-        <v>9</v>
-      </c>
-      <c r="C6">
-        <v>16</v>
-      </c>
-      <c r="D6">
-        <v>14</v>
-      </c>
-      <c r="E6">
-        <v>18</v>
-      </c>
-      <c r="F6">
-        <v>34</v>
-      </c>
-      <c r="G6">
-        <v>8</v>
-      </c>
-      <c r="H6">
-        <v>8</v>
-      </c>
-      <c r="I6">
-        <v>16</v>
-      </c>
-      <c r="J6">
-        <v>11</v>
-      </c>
-      <c r="K6">
-        <v>10</v>
-      </c>
-      <c r="L6">
-        <v>7</v>
-      </c>
-      <c r="M6">
-        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -5536,7 +5591,7 @@
         <v>8</v>
       </c>
       <c r="M48">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="49" spans="1:13">
@@ -5741,7 +5796,7 @@
         <v>196</v>
       </c>
       <c r="M53">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="54" spans="1:13">
@@ -6305,7 +6360,7 @@
         <v>21</v>
       </c>
       <c r="M68">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="69" spans="1:13">
@@ -7516,7 +7571,7 @@
         <v>1604</v>
       </c>
       <c r="M99">
-        <v>817</v>
+        <v>820</v>
       </c>
     </row>
   </sheetData>
@@ -7690,37 +7745,28 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C2">
-        <v>4</v>
-      </c>
-      <c r="D2">
-        <v>1</v>
-      </c>
-      <c r="E2">
-        <v>2</v>
-      </c>
-      <c r="F2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G2">
         <v>2</v>
       </c>
       <c r="H2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="L2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M2">
         <v>2</v>
@@ -7730,53 +7776,56 @@
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C3">
+      <c r="B3">
         <v>1</v>
       </c>
       <c r="D3">
         <v>2</v>
       </c>
       <c r="E3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G3">
+        <v>2</v>
+      </c>
+      <c r="H3">
+        <v>3</v>
+      </c>
+      <c r="I3">
+        <v>2</v>
+      </c>
+      <c r="J3">
+        <v>1</v>
+      </c>
+      <c r="K3">
+        <v>5</v>
+      </c>
+      <c r="L3">
         <v>6</v>
-      </c>
-      <c r="H3">
-        <v>2</v>
-      </c>
-      <c r="I3">
-        <v>4</v>
-      </c>
-      <c r="J3">
-        <v>7</v>
-      </c>
-      <c r="K3">
-        <v>7</v>
-      </c>
-      <c r="L3">
-        <v>3</v>
-      </c>
-      <c r="M3">
-        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E4">
-        <v>1</v>
+        <v>5</v>
+      </c>
+      <c r="F4">
+        <v>1</v>
+      </c>
+      <c r="J4">
+        <v>1</v>
+      </c>
+      <c r="L4">
+        <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5">
+        <v>6</v>
+      </c>
+      <c r="I5">
         <v>1</v>
       </c>
     </row>
@@ -7784,7 +7833,7 @@
       <c r="A6" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C6">
+      <c r="D6">
         <v>1</v>
       </c>
     </row>
@@ -7796,37 +7845,37 @@
         <v>5</v>
       </c>
       <c r="C7">
+        <v>1</v>
+      </c>
+      <c r="D7">
+        <v>6</v>
+      </c>
+      <c r="E7">
+        <v>8</v>
+      </c>
+      <c r="F7">
+        <v>10</v>
+      </c>
+      <c r="G7">
+        <v>8</v>
+      </c>
+      <c r="H7">
         <v>9</v>
       </c>
-      <c r="D7">
-        <v>1</v>
-      </c>
-      <c r="E7">
-        <v>6</v>
-      </c>
-      <c r="F7">
-        <v>6</v>
-      </c>
-      <c r="G7">
-        <v>14</v>
-      </c>
-      <c r="H7">
+      <c r="I7">
         <v>7</v>
       </c>
-      <c r="I7">
-        <v>4</v>
-      </c>
       <c r="J7">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K7">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="L7">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="M7">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -7834,40 +7883,40 @@
         <v>9</v>
       </c>
       <c r="B8">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="C8">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="D8">
-        <v>15</v>
+        <v>35</v>
       </c>
       <c r="E8">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="F8">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="G8">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="H8">
+        <v>9</v>
+      </c>
+      <c r="I8">
+        <v>27</v>
+      </c>
+      <c r="J8">
+        <v>22</v>
+      </c>
+      <c r="K8">
         <v>14</v>
       </c>
-      <c r="I8">
-        <v>13</v>
-      </c>
-      <c r="J8">
-        <v>15</v>
-      </c>
-      <c r="K8">
-        <v>12</v>
-      </c>
       <c r="L8">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="M8">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -7875,40 +7924,40 @@
         <v>10</v>
       </c>
       <c r="B9">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="C9">
-        <v>41</v>
+        <v>26</v>
       </c>
       <c r="D9">
-        <v>19</v>
+        <v>44</v>
       </c>
       <c r="E9">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="F9">
+        <v>52</v>
+      </c>
+      <c r="G9">
+        <v>32</v>
+      </c>
+      <c r="H9">
+        <v>25</v>
+      </c>
+      <c r="I9">
+        <v>40</v>
+      </c>
+      <c r="J9">
+        <v>30</v>
+      </c>
+      <c r="K9">
         <v>28</v>
       </c>
-      <c r="G9">
-        <v>38</v>
-      </c>
-      <c r="H9">
-        <v>28</v>
-      </c>
-      <c r="I9">
-        <v>23</v>
-      </c>
-      <c r="J9">
-        <v>31</v>
-      </c>
-      <c r="K9">
-        <v>35</v>
-      </c>
       <c r="L9">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="M9">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
   </sheetData>
@@ -7917,6 +7966,527 @@
 </file>
 
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:M6"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="18.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+    <col min="13" max="13" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="M1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>2</v>
+      </c>
+      <c r="G2">
+        <v>1</v>
+      </c>
+      <c r="I2">
+        <v>1</v>
+      </c>
+      <c r="J2">
+        <v>1</v>
+      </c>
+      <c r="L2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>1</v>
+      </c>
+      <c r="F3">
+        <v>1</v>
+      </c>
+      <c r="H3">
+        <v>1</v>
+      </c>
+      <c r="J3">
+        <v>1</v>
+      </c>
+      <c r="L3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4">
+        <v>3</v>
+      </c>
+      <c r="C4">
+        <v>5</v>
+      </c>
+      <c r="D4">
+        <v>6</v>
+      </c>
+      <c r="E4">
+        <v>2</v>
+      </c>
+      <c r="F4">
+        <v>7</v>
+      </c>
+      <c r="G4">
+        <v>4</v>
+      </c>
+      <c r="H4">
+        <v>1</v>
+      </c>
+      <c r="I4">
+        <v>10</v>
+      </c>
+      <c r="J4">
+        <v>3</v>
+      </c>
+      <c r="K4">
+        <v>6</v>
+      </c>
+      <c r="L4">
+        <v>3</v>
+      </c>
+      <c r="M4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5">
+        <v>5</v>
+      </c>
+      <c r="C5">
+        <v>9</v>
+      </c>
+      <c r="D5">
+        <v>8</v>
+      </c>
+      <c r="E5">
+        <v>16</v>
+      </c>
+      <c r="F5">
+        <v>26</v>
+      </c>
+      <c r="G5">
+        <v>3</v>
+      </c>
+      <c r="H5">
+        <v>6</v>
+      </c>
+      <c r="I5">
+        <v>5</v>
+      </c>
+      <c r="J5">
+        <v>6</v>
+      </c>
+      <c r="K5">
+        <v>4</v>
+      </c>
+      <c r="L5">
+        <v>1</v>
+      </c>
+      <c r="M5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6">
+        <v>9</v>
+      </c>
+      <c r="C6">
+        <v>16</v>
+      </c>
+      <c r="D6">
+        <v>14</v>
+      </c>
+      <c r="E6">
+        <v>18</v>
+      </c>
+      <c r="F6">
+        <v>34</v>
+      </c>
+      <c r="G6">
+        <v>8</v>
+      </c>
+      <c r="H6">
+        <v>8</v>
+      </c>
+      <c r="I6">
+        <v>16</v>
+      </c>
+      <c r="J6">
+        <v>11</v>
+      </c>
+      <c r="K6">
+        <v>10</v>
+      </c>
+      <c r="L6">
+        <v>7</v>
+      </c>
+      <c r="M6">
+        <v>4</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:M9"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+    <col min="13" max="13" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="M1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>2</v>
+      </c>
+      <c r="C2">
+        <v>4</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="E2">
+        <v>2</v>
+      </c>
+      <c r="F2">
+        <v>1</v>
+      </c>
+      <c r="G2">
+        <v>2</v>
+      </c>
+      <c r="H2">
+        <v>5</v>
+      </c>
+      <c r="I2">
+        <v>2</v>
+      </c>
+      <c r="J2">
+        <v>4</v>
+      </c>
+      <c r="K2">
+        <v>5</v>
+      </c>
+      <c r="L2">
+        <v>2</v>
+      </c>
+      <c r="M2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
+      <c r="D3">
+        <v>2</v>
+      </c>
+      <c r="E3">
+        <v>3</v>
+      </c>
+      <c r="F3">
+        <v>3</v>
+      </c>
+      <c r="G3">
+        <v>6</v>
+      </c>
+      <c r="H3">
+        <v>2</v>
+      </c>
+      <c r="I3">
+        <v>4</v>
+      </c>
+      <c r="J3">
+        <v>7</v>
+      </c>
+      <c r="K3">
+        <v>7</v>
+      </c>
+      <c r="L3">
+        <v>3</v>
+      </c>
+      <c r="M3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7">
+        <v>5</v>
+      </c>
+      <c r="C7">
+        <v>9</v>
+      </c>
+      <c r="D7">
+        <v>1</v>
+      </c>
+      <c r="E7">
+        <v>6</v>
+      </c>
+      <c r="F7">
+        <v>6</v>
+      </c>
+      <c r="G7">
+        <v>14</v>
+      </c>
+      <c r="H7">
+        <v>7</v>
+      </c>
+      <c r="I7">
+        <v>4</v>
+      </c>
+      <c r="J7">
+        <v>5</v>
+      </c>
+      <c r="K7">
+        <v>11</v>
+      </c>
+      <c r="L7">
+        <v>8</v>
+      </c>
+      <c r="M7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13">
+      <c r="A8" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B8">
+        <v>30</v>
+      </c>
+      <c r="C8">
+        <v>26</v>
+      </c>
+      <c r="D8">
+        <v>15</v>
+      </c>
+      <c r="E8">
+        <v>24</v>
+      </c>
+      <c r="F8">
+        <v>18</v>
+      </c>
+      <c r="G8">
+        <v>16</v>
+      </c>
+      <c r="H8">
+        <v>14</v>
+      </c>
+      <c r="I8">
+        <v>13</v>
+      </c>
+      <c r="J8">
+        <v>15</v>
+      </c>
+      <c r="K8">
+        <v>12</v>
+      </c>
+      <c r="L8">
+        <v>20</v>
+      </c>
+      <c r="M8">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13">
+      <c r="A9" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B9">
+        <v>38</v>
+      </c>
+      <c r="C9">
+        <v>41</v>
+      </c>
+      <c r="D9">
+        <v>19</v>
+      </c>
+      <c r="E9">
+        <v>36</v>
+      </c>
+      <c r="F9">
+        <v>28</v>
+      </c>
+      <c r="G9">
+        <v>38</v>
+      </c>
+      <c r="H9">
+        <v>28</v>
+      </c>
+      <c r="I9">
+        <v>23</v>
+      </c>
+      <c r="J9">
+        <v>31</v>
+      </c>
+      <c r="K9">
+        <v>35</v>
+      </c>
+      <c r="L9">
+        <v>33</v>
+      </c>
+      <c r="M9">
+        <v>15</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M8"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -8212,7 +8782,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M8"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -8502,7 +9072,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -8725,7 +9295,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -8983,7 +9553,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -9246,499 +9816,6 @@
       </c>
       <c r="M7">
         <v>16</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M8"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" customWidth="1"/>
-    <col min="13" max="13" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="M1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2">
-        <v>2</v>
-      </c>
-      <c r="D2">
-        <v>1</v>
-      </c>
-      <c r="H2">
-        <v>1</v>
-      </c>
-      <c r="I2">
-        <v>1</v>
-      </c>
-      <c r="J2">
-        <v>2</v>
-      </c>
-      <c r="L2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3">
-        <v>1</v>
-      </c>
-      <c r="D3">
-        <v>2</v>
-      </c>
-      <c r="F3">
-        <v>3</v>
-      </c>
-      <c r="G3">
-        <v>1</v>
-      </c>
-      <c r="H3">
-        <v>2</v>
-      </c>
-      <c r="I3">
-        <v>2</v>
-      </c>
-      <c r="K3">
-        <v>2</v>
-      </c>
-      <c r="M3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="J4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="K5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B6">
-        <v>7</v>
-      </c>
-      <c r="C6">
-        <v>5</v>
-      </c>
-      <c r="D6">
-        <v>5</v>
-      </c>
-      <c r="E6">
-        <v>5</v>
-      </c>
-      <c r="F6">
-        <v>5</v>
-      </c>
-      <c r="G6">
-        <v>1</v>
-      </c>
-      <c r="H6">
-        <v>5</v>
-      </c>
-      <c r="I6">
-        <v>4</v>
-      </c>
-      <c r="J6">
-        <v>1</v>
-      </c>
-      <c r="K6">
-        <v>4</v>
-      </c>
-      <c r="L6">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
-      <c r="A7" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B7">
-        <v>14</v>
-      </c>
-      <c r="C7">
-        <v>13</v>
-      </c>
-      <c r="D7">
-        <v>13</v>
-      </c>
-      <c r="E7">
-        <v>15</v>
-      </c>
-      <c r="F7">
-        <v>11</v>
-      </c>
-      <c r="G7">
-        <v>4</v>
-      </c>
-      <c r="H7">
-        <v>2</v>
-      </c>
-      <c r="I7">
-        <v>7</v>
-      </c>
-      <c r="J7">
-        <v>7</v>
-      </c>
-      <c r="K7">
-        <v>9</v>
-      </c>
-      <c r="L7">
-        <v>8</v>
-      </c>
-      <c r="M7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13">
-      <c r="A8" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B8">
-        <v>22</v>
-      </c>
-      <c r="C8">
-        <v>20</v>
-      </c>
-      <c r="D8">
-        <v>21</v>
-      </c>
-      <c r="E8">
-        <v>20</v>
-      </c>
-      <c r="F8">
-        <v>19</v>
-      </c>
-      <c r="G8">
-        <v>6</v>
-      </c>
-      <c r="H8">
-        <v>10</v>
-      </c>
-      <c r="I8">
-        <v>14</v>
-      </c>
-      <c r="J8">
-        <v>11</v>
-      </c>
-      <c r="K8">
-        <v>16</v>
-      </c>
-      <c r="L8">
-        <v>15</v>
-      </c>
-      <c r="M8">
-        <v>3</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M8"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" customWidth="1"/>
-    <col min="13" max="13" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="M1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="F2">
-        <v>1</v>
-      </c>
-      <c r="K2">
-        <v>2</v>
-      </c>
-      <c r="L2">
-        <v>2</v>
-      </c>
-      <c r="M2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="F3">
-        <v>1</v>
-      </c>
-      <c r="G3">
-        <v>1</v>
-      </c>
-      <c r="H3">
-        <v>1</v>
-      </c>
-      <c r="J3">
-        <v>1</v>
-      </c>
-      <c r="K3">
-        <v>2</v>
-      </c>
-      <c r="L3">
-        <v>1</v>
-      </c>
-      <c r="M3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D4">
-        <v>1</v>
-      </c>
-      <c r="I4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="I5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D6">
-        <v>1</v>
-      </c>
-      <c r="E6">
-        <v>2</v>
-      </c>
-      <c r="F6">
-        <v>2</v>
-      </c>
-      <c r="H6">
-        <v>6</v>
-      </c>
-      <c r="J6">
-        <v>1</v>
-      </c>
-      <c r="K6">
-        <v>1</v>
-      </c>
-      <c r="L6">
-        <v>1</v>
-      </c>
-      <c r="M6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
-      <c r="A7" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B7">
-        <v>12</v>
-      </c>
-      <c r="C7">
-        <v>10</v>
-      </c>
-      <c r="D7">
-        <v>10</v>
-      </c>
-      <c r="E7">
-        <v>17</v>
-      </c>
-      <c r="F7">
-        <v>17</v>
-      </c>
-      <c r="G7">
-        <v>8</v>
-      </c>
-      <c r="H7">
-        <v>4</v>
-      </c>
-      <c r="I7">
-        <v>2</v>
-      </c>
-      <c r="J7">
-        <v>2</v>
-      </c>
-      <c r="K7">
-        <v>3</v>
-      </c>
-      <c r="L7">
-        <v>6</v>
-      </c>
-      <c r="M7">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13">
-      <c r="A8" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B8">
-        <v>12</v>
-      </c>
-      <c r="C8">
-        <v>10</v>
-      </c>
-      <c r="D8">
-        <v>12</v>
-      </c>
-      <c r="E8">
-        <v>19</v>
-      </c>
-      <c r="F8">
-        <v>21</v>
-      </c>
-      <c r="G8">
-        <v>9</v>
-      </c>
-      <c r="H8">
-        <v>11</v>
-      </c>
-      <c r="I8">
-        <v>4</v>
-      </c>
-      <c r="J8">
-        <v>4</v>
-      </c>
-      <c r="K8">
-        <v>8</v>
-      </c>
-      <c r="L8">
-        <v>10</v>
-      </c>
-      <c r="M8">
-        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -9812,33 +9889,21 @@
         <v>1</v>
       </c>
       <c r="C2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D2">
-        <v>2</v>
-      </c>
-      <c r="E2">
-        <v>2</v>
-      </c>
-      <c r="F2">
-        <v>1</v>
-      </c>
-      <c r="G2">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="H2">
+        <v>1</v>
       </c>
       <c r="I2">
         <v>1</v>
       </c>
       <c r="J2">
-        <v>3</v>
-      </c>
-      <c r="K2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L2">
-        <v>1</v>
-      </c>
-      <c r="M2">
         <v>1</v>
       </c>
     </row>
@@ -9846,51 +9911,42 @@
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C3">
-        <v>2</v>
+      <c r="B3">
+        <v>1</v>
       </c>
       <c r="D3">
         <v>2</v>
       </c>
-      <c r="E3">
-        <v>2</v>
-      </c>
       <c r="F3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G3">
         <v>1</v>
       </c>
       <c r="H3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I3">
-        <v>3</v>
-      </c>
-      <c r="J3">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K3">
-        <v>1</v>
-      </c>
-      <c r="L3">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="M3">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="L4">
+      <c r="J4">
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K5">
         <v>1</v>
@@ -9904,37 +9960,34 @@
         <v>7</v>
       </c>
       <c r="C6">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D6">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E6">
+        <v>5</v>
+      </c>
+      <c r="F6">
+        <v>5</v>
+      </c>
+      <c r="G6">
+        <v>1</v>
+      </c>
+      <c r="H6">
+        <v>5</v>
+      </c>
+      <c r="I6">
+        <v>4</v>
+      </c>
+      <c r="J6">
+        <v>1</v>
+      </c>
+      <c r="K6">
+        <v>4</v>
+      </c>
+      <c r="L6">
         <v>6</v>
-      </c>
-      <c r="F6">
-        <v>5</v>
-      </c>
-      <c r="G6">
-        <v>7</v>
-      </c>
-      <c r="H6">
-        <v>4</v>
-      </c>
-      <c r="I6">
-        <v>8</v>
-      </c>
-      <c r="J6">
-        <v>5</v>
-      </c>
-      <c r="K6">
-        <v>1</v>
-      </c>
-      <c r="L6">
-        <v>1</v>
-      </c>
-      <c r="M6">
-        <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -9942,40 +9995,40 @@
         <v>9</v>
       </c>
       <c r="B7">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="C7">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="D7">
+        <v>13</v>
+      </c>
+      <c r="E7">
+        <v>15</v>
+      </c>
+      <c r="F7">
         <v>11</v>
       </c>
-      <c r="E7">
-        <v>14</v>
-      </c>
-      <c r="F7">
-        <v>17</v>
-      </c>
       <c r="G7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H7">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J7">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K7">
+        <v>9</v>
+      </c>
+      <c r="L7">
         <v>8</v>
       </c>
-      <c r="L7">
-        <v>3</v>
-      </c>
       <c r="M7">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -9983,40 +10036,40 @@
         <v>10</v>
       </c>
       <c r="B8">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C8">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="D8">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E8">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="F8">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="G8">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="H8">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="I8">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="J8">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="K8">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="L8">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="M8">
-        <v>14</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -10025,6 +10078,877 @@
 </file>
 
 <file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:M8"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+    <col min="13" max="13" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="M1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="F2">
+        <v>1</v>
+      </c>
+      <c r="K2">
+        <v>2</v>
+      </c>
+      <c r="L2">
+        <v>2</v>
+      </c>
+      <c r="M2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F3">
+        <v>1</v>
+      </c>
+      <c r="G3">
+        <v>1</v>
+      </c>
+      <c r="H3">
+        <v>1</v>
+      </c>
+      <c r="J3">
+        <v>1</v>
+      </c>
+      <c r="K3">
+        <v>2</v>
+      </c>
+      <c r="L3">
+        <v>1</v>
+      </c>
+      <c r="M3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D4">
+        <v>1</v>
+      </c>
+      <c r="I4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="I5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D6">
+        <v>1</v>
+      </c>
+      <c r="E6">
+        <v>2</v>
+      </c>
+      <c r="F6">
+        <v>2</v>
+      </c>
+      <c r="H6">
+        <v>6</v>
+      </c>
+      <c r="J6">
+        <v>1</v>
+      </c>
+      <c r="K6">
+        <v>1</v>
+      </c>
+      <c r="L6">
+        <v>1</v>
+      </c>
+      <c r="M6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7">
+        <v>12</v>
+      </c>
+      <c r="C7">
+        <v>10</v>
+      </c>
+      <c r="D7">
+        <v>10</v>
+      </c>
+      <c r="E7">
+        <v>17</v>
+      </c>
+      <c r="F7">
+        <v>17</v>
+      </c>
+      <c r="G7">
+        <v>8</v>
+      </c>
+      <c r="H7">
+        <v>4</v>
+      </c>
+      <c r="I7">
+        <v>2</v>
+      </c>
+      <c r="J7">
+        <v>2</v>
+      </c>
+      <c r="K7">
+        <v>3</v>
+      </c>
+      <c r="L7">
+        <v>6</v>
+      </c>
+      <c r="M7">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13">
+      <c r="A8" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B8">
+        <v>12</v>
+      </c>
+      <c r="C8">
+        <v>10</v>
+      </c>
+      <c r="D8">
+        <v>12</v>
+      </c>
+      <c r="E8">
+        <v>19</v>
+      </c>
+      <c r="F8">
+        <v>21</v>
+      </c>
+      <c r="G8">
+        <v>9</v>
+      </c>
+      <c r="H8">
+        <v>11</v>
+      </c>
+      <c r="I8">
+        <v>4</v>
+      </c>
+      <c r="J8">
+        <v>4</v>
+      </c>
+      <c r="K8">
+        <v>8</v>
+      </c>
+      <c r="L8">
+        <v>10</v>
+      </c>
+      <c r="M8">
+        <v>7</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:M10"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+    <col min="13" max="13" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="M1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>6</v>
+      </c>
+      <c r="C2">
+        <v>3</v>
+      </c>
+      <c r="D2">
+        <v>12</v>
+      </c>
+      <c r="E2">
+        <v>5</v>
+      </c>
+      <c r="F2">
+        <v>8</v>
+      </c>
+      <c r="G2">
+        <v>4</v>
+      </c>
+      <c r="H2">
+        <v>13</v>
+      </c>
+      <c r="I2">
+        <v>14</v>
+      </c>
+      <c r="J2">
+        <v>22</v>
+      </c>
+      <c r="K2">
+        <v>15</v>
+      </c>
+      <c r="L2">
+        <v>15</v>
+      </c>
+      <c r="M2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>13</v>
+      </c>
+      <c r="C3">
+        <v>13</v>
+      </c>
+      <c r="D3">
+        <v>17</v>
+      </c>
+      <c r="E3">
+        <v>18</v>
+      </c>
+      <c r="F3">
+        <v>14</v>
+      </c>
+      <c r="G3">
+        <v>26</v>
+      </c>
+      <c r="H3">
+        <v>23</v>
+      </c>
+      <c r="I3">
+        <v>32</v>
+      </c>
+      <c r="J3">
+        <v>40</v>
+      </c>
+      <c r="K3">
+        <v>26</v>
+      </c>
+      <c r="L3">
+        <v>34</v>
+      </c>
+      <c r="M3">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G4">
+        <v>1</v>
+      </c>
+      <c r="J4">
+        <v>2</v>
+      </c>
+      <c r="K4">
+        <v>1</v>
+      </c>
+      <c r="L4">
+        <v>1</v>
+      </c>
+      <c r="M4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C5">
+        <v>2</v>
+      </c>
+      <c r="D5">
+        <v>1</v>
+      </c>
+      <c r="E5">
+        <v>2</v>
+      </c>
+      <c r="F5">
+        <v>1</v>
+      </c>
+      <c r="H5">
+        <v>2</v>
+      </c>
+      <c r="I5">
+        <v>4</v>
+      </c>
+      <c r="J5">
+        <v>3</v>
+      </c>
+      <c r="K5">
+        <v>2</v>
+      </c>
+      <c r="L5">
+        <v>5</v>
+      </c>
+      <c r="M5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G6">
+        <v>1</v>
+      </c>
+      <c r="H6">
+        <v>2</v>
+      </c>
+      <c r="J6">
+        <v>2</v>
+      </c>
+      <c r="L6">
+        <v>2</v>
+      </c>
+      <c r="M6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="K7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13">
+      <c r="A8" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8">
+        <v>30</v>
+      </c>
+      <c r="C8">
+        <v>44</v>
+      </c>
+      <c r="D8">
+        <v>49</v>
+      </c>
+      <c r="E8">
+        <v>67</v>
+      </c>
+      <c r="F8">
+        <v>69</v>
+      </c>
+      <c r="G8">
+        <v>57</v>
+      </c>
+      <c r="H8">
+        <v>80</v>
+      </c>
+      <c r="I8">
+        <v>80</v>
+      </c>
+      <c r="J8">
+        <v>64</v>
+      </c>
+      <c r="K8">
+        <v>48</v>
+      </c>
+      <c r="L8">
+        <v>44</v>
+      </c>
+      <c r="M8">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13">
+      <c r="A9" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B9">
+        <v>233</v>
+      </c>
+      <c r="C9">
+        <v>354</v>
+      </c>
+      <c r="D9">
+        <v>538</v>
+      </c>
+      <c r="E9">
+        <v>705</v>
+      </c>
+      <c r="F9">
+        <v>568</v>
+      </c>
+      <c r="G9">
+        <v>168</v>
+      </c>
+      <c r="H9">
+        <v>116</v>
+      </c>
+      <c r="I9">
+        <v>194</v>
+      </c>
+      <c r="J9">
+        <v>122</v>
+      </c>
+      <c r="K9">
+        <v>114</v>
+      </c>
+      <c r="L9">
+        <v>95</v>
+      </c>
+      <c r="M9">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13">
+      <c r="A10" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B10">
+        <v>282</v>
+      </c>
+      <c r="C10">
+        <v>416</v>
+      </c>
+      <c r="D10">
+        <v>617</v>
+      </c>
+      <c r="E10">
+        <v>797</v>
+      </c>
+      <c r="F10">
+        <v>660</v>
+      </c>
+      <c r="G10">
+        <v>257</v>
+      </c>
+      <c r="H10">
+        <v>236</v>
+      </c>
+      <c r="I10">
+        <v>324</v>
+      </c>
+      <c r="J10">
+        <v>255</v>
+      </c>
+      <c r="K10">
+        <v>207</v>
+      </c>
+      <c r="L10">
+        <v>196</v>
+      </c>
+      <c r="M10">
+        <v>93</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:M8"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+    <col min="13" max="13" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="M1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>2</v>
+      </c>
+      <c r="E2">
+        <v>2</v>
+      </c>
+      <c r="F2">
+        <v>1</v>
+      </c>
+      <c r="G2">
+        <v>2</v>
+      </c>
+      <c r="I2">
+        <v>1</v>
+      </c>
+      <c r="J2">
+        <v>3</v>
+      </c>
+      <c r="K2">
+        <v>1</v>
+      </c>
+      <c r="L2">
+        <v>1</v>
+      </c>
+      <c r="M2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3">
+        <v>2</v>
+      </c>
+      <c r="D3">
+        <v>2</v>
+      </c>
+      <c r="E3">
+        <v>2</v>
+      </c>
+      <c r="F3">
+        <v>1</v>
+      </c>
+      <c r="G3">
+        <v>1</v>
+      </c>
+      <c r="H3">
+        <v>3</v>
+      </c>
+      <c r="I3">
+        <v>3</v>
+      </c>
+      <c r="J3">
+        <v>4</v>
+      </c>
+      <c r="K3">
+        <v>1</v>
+      </c>
+      <c r="L3">
+        <v>5</v>
+      </c>
+      <c r="M3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="L4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="K5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6">
+        <v>7</v>
+      </c>
+      <c r="C6">
+        <v>7</v>
+      </c>
+      <c r="D6">
+        <v>7</v>
+      </c>
+      <c r="E6">
+        <v>6</v>
+      </c>
+      <c r="F6">
+        <v>5</v>
+      </c>
+      <c r="G6">
+        <v>7</v>
+      </c>
+      <c r="H6">
+        <v>4</v>
+      </c>
+      <c r="I6">
+        <v>8</v>
+      </c>
+      <c r="J6">
+        <v>5</v>
+      </c>
+      <c r="K6">
+        <v>1</v>
+      </c>
+      <c r="L6">
+        <v>1</v>
+      </c>
+      <c r="M6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7">
+        <v>21</v>
+      </c>
+      <c r="C7">
+        <v>18</v>
+      </c>
+      <c r="D7">
+        <v>11</v>
+      </c>
+      <c r="E7">
+        <v>14</v>
+      </c>
+      <c r="F7">
+        <v>17</v>
+      </c>
+      <c r="G7">
+        <v>3</v>
+      </c>
+      <c r="H7">
+        <v>5</v>
+      </c>
+      <c r="I7">
+        <v>6</v>
+      </c>
+      <c r="J7">
+        <v>5</v>
+      </c>
+      <c r="K7">
+        <v>8</v>
+      </c>
+      <c r="L7">
+        <v>3</v>
+      </c>
+      <c r="M7">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13">
+      <c r="A8" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B8">
+        <v>28</v>
+      </c>
+      <c r="C8">
+        <v>28</v>
+      </c>
+      <c r="D8">
+        <v>22</v>
+      </c>
+      <c r="E8">
+        <v>24</v>
+      </c>
+      <c r="F8">
+        <v>24</v>
+      </c>
+      <c r="G8">
+        <v>13</v>
+      </c>
+      <c r="H8">
+        <v>12</v>
+      </c>
+      <c r="I8">
+        <v>18</v>
+      </c>
+      <c r="J8">
+        <v>17</v>
+      </c>
+      <c r="K8">
+        <v>12</v>
+      </c>
+      <c r="L8">
+        <v>11</v>
+      </c>
+      <c r="M8">
+        <v>14</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M9"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -10304,273 +11228,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M8"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" customWidth="1"/>
-    <col min="13" max="13" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="M1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="F2">
-        <v>1</v>
-      </c>
-      <c r="G2">
-        <v>2</v>
-      </c>
-      <c r="H2">
-        <v>1</v>
-      </c>
-      <c r="I2">
-        <v>2</v>
-      </c>
-      <c r="J2">
-        <v>2</v>
-      </c>
-      <c r="K2">
-        <v>3</v>
-      </c>
-      <c r="M2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3">
-        <v>1</v>
-      </c>
-      <c r="C3">
-        <v>1</v>
-      </c>
-      <c r="D3">
-        <v>1</v>
-      </c>
-      <c r="E3">
-        <v>2</v>
-      </c>
-      <c r="G3">
-        <v>2</v>
-      </c>
-      <c r="H3">
-        <v>2</v>
-      </c>
-      <c r="I3">
-        <v>3</v>
-      </c>
-      <c r="J3">
-        <v>1</v>
-      </c>
-      <c r="K3">
-        <v>1</v>
-      </c>
-      <c r="M3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="J4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="K5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B6">
-        <v>6</v>
-      </c>
-      <c r="C6">
-        <v>2</v>
-      </c>
-      <c r="D6">
-        <v>5</v>
-      </c>
-      <c r="E6">
-        <v>5</v>
-      </c>
-      <c r="F6">
-        <v>4</v>
-      </c>
-      <c r="G6">
-        <v>4</v>
-      </c>
-      <c r="H6">
-        <v>6</v>
-      </c>
-      <c r="I6">
-        <v>8</v>
-      </c>
-      <c r="J6">
-        <v>4</v>
-      </c>
-      <c r="K6">
-        <v>3</v>
-      </c>
-      <c r="L6">
-        <v>4</v>
-      </c>
-      <c r="M6">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
-      <c r="A7" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B7">
-        <v>22</v>
-      </c>
-      <c r="C7">
-        <v>27</v>
-      </c>
-      <c r="D7">
-        <v>23</v>
-      </c>
-      <c r="E7">
-        <v>19</v>
-      </c>
-      <c r="F7">
-        <v>23</v>
-      </c>
-      <c r="G7">
-        <v>9</v>
-      </c>
-      <c r="H7">
-        <v>6</v>
-      </c>
-      <c r="I7">
-        <v>14</v>
-      </c>
-      <c r="J7">
-        <v>11</v>
-      </c>
-      <c r="K7">
-        <v>12</v>
-      </c>
-      <c r="L7">
-        <v>10</v>
-      </c>
-      <c r="M7">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13">
-      <c r="A8" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B8">
-        <v>29</v>
-      </c>
-      <c r="C8">
-        <v>30</v>
-      </c>
-      <c r="D8">
-        <v>29</v>
-      </c>
-      <c r="E8">
-        <v>26</v>
-      </c>
-      <c r="F8">
-        <v>28</v>
-      </c>
-      <c r="G8">
-        <v>17</v>
-      </c>
-      <c r="H8">
-        <v>15</v>
-      </c>
-      <c r="I8">
-        <v>27</v>
-      </c>
-      <c r="J8">
-        <v>19</v>
-      </c>
-      <c r="K8">
-        <v>20</v>
-      </c>
-      <c r="L8">
-        <v>14</v>
-      </c>
-      <c r="M8">
-        <v>12</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M9"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -10886,7 +11544,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -11111,7 +11769,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M10"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -11416,559 +12074,6 @@
       </c>
       <c r="M10">
         <v>24</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M9"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" customWidth="1"/>
-    <col min="13" max="13" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="M1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2">
-        <v>1</v>
-      </c>
-      <c r="C2">
-        <v>2</v>
-      </c>
-      <c r="D2">
-        <v>7</v>
-      </c>
-      <c r="E2">
-        <v>8</v>
-      </c>
-      <c r="F2">
-        <v>5</v>
-      </c>
-      <c r="G2">
-        <v>4</v>
-      </c>
-      <c r="H2">
-        <v>2</v>
-      </c>
-      <c r="I2">
-        <v>5</v>
-      </c>
-      <c r="J2">
-        <v>3</v>
-      </c>
-      <c r="K2">
-        <v>5</v>
-      </c>
-      <c r="L2">
-        <v>5</v>
-      </c>
-      <c r="M2">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3">
-        <v>1</v>
-      </c>
-      <c r="C3">
-        <v>3</v>
-      </c>
-      <c r="D3">
-        <v>9</v>
-      </c>
-      <c r="E3">
-        <v>4</v>
-      </c>
-      <c r="F3">
-        <v>5</v>
-      </c>
-      <c r="G3">
-        <v>6</v>
-      </c>
-      <c r="H3">
-        <v>8</v>
-      </c>
-      <c r="I3">
-        <v>9</v>
-      </c>
-      <c r="J3">
-        <v>14</v>
-      </c>
-      <c r="K3">
-        <v>16</v>
-      </c>
-      <c r="L3">
-        <v>8</v>
-      </c>
-      <c r="M3">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="F4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5">
-        <v>2</v>
-      </c>
-      <c r="D5">
-        <v>1</v>
-      </c>
-      <c r="E5">
-        <v>1</v>
-      </c>
-      <c r="F5">
-        <v>1</v>
-      </c>
-      <c r="H5">
-        <v>1</v>
-      </c>
-      <c r="I5">
-        <v>2</v>
-      </c>
-      <c r="M5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="I6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
-      <c r="A7" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B7">
-        <v>15</v>
-      </c>
-      <c r="C7">
-        <v>35</v>
-      </c>
-      <c r="D7">
-        <v>34</v>
-      </c>
-      <c r="E7">
-        <v>56</v>
-      </c>
-      <c r="F7">
-        <v>54</v>
-      </c>
-      <c r="G7">
-        <v>37</v>
-      </c>
-      <c r="H7">
-        <v>39</v>
-      </c>
-      <c r="I7">
-        <v>32</v>
-      </c>
-      <c r="J7">
-        <v>34</v>
-      </c>
-      <c r="K7">
-        <v>27</v>
-      </c>
-      <c r="L7">
-        <v>31</v>
-      </c>
-      <c r="M7">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13">
-      <c r="A8" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B8">
-        <v>54</v>
-      </c>
-      <c r="C8">
-        <v>63</v>
-      </c>
-      <c r="D8">
-        <v>50</v>
-      </c>
-      <c r="E8">
-        <v>109</v>
-      </c>
-      <c r="F8">
-        <v>138</v>
-      </c>
-      <c r="G8">
-        <v>53</v>
-      </c>
-      <c r="H8">
-        <v>29</v>
-      </c>
-      <c r="I8">
-        <v>49</v>
-      </c>
-      <c r="J8">
-        <v>34</v>
-      </c>
-      <c r="K8">
-        <v>28</v>
-      </c>
-      <c r="L8">
-        <v>27</v>
-      </c>
-      <c r="M8">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13">
-      <c r="A9" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B9">
-        <v>73</v>
-      </c>
-      <c r="C9">
-        <v>103</v>
-      </c>
-      <c r="D9">
-        <v>101</v>
-      </c>
-      <c r="E9">
-        <v>178</v>
-      </c>
-      <c r="F9">
-        <v>204</v>
-      </c>
-      <c r="G9">
-        <v>100</v>
-      </c>
-      <c r="H9">
-        <v>79</v>
-      </c>
-      <c r="I9">
-        <v>98</v>
-      </c>
-      <c r="J9">
-        <v>85</v>
-      </c>
-      <c r="K9">
-        <v>76</v>
-      </c>
-      <c r="L9">
-        <v>71</v>
-      </c>
-      <c r="M9">
-        <v>46</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M7"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" customWidth="1"/>
-    <col min="13" max="13" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="M1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D2">
-        <v>1</v>
-      </c>
-      <c r="E2">
-        <v>1</v>
-      </c>
-      <c r="H2">
-        <v>1</v>
-      </c>
-      <c r="J2">
-        <v>3</v>
-      </c>
-      <c r="K2">
-        <v>1</v>
-      </c>
-      <c r="L2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="F3">
-        <v>1</v>
-      </c>
-      <c r="G3">
-        <v>1</v>
-      </c>
-      <c r="H3">
-        <v>2</v>
-      </c>
-      <c r="I3">
-        <v>1</v>
-      </c>
-      <c r="J3">
-        <v>1</v>
-      </c>
-      <c r="K3">
-        <v>2</v>
-      </c>
-      <c r="L3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5">
-        <v>1</v>
-      </c>
-      <c r="C5">
-        <v>3</v>
-      </c>
-      <c r="D5">
-        <v>1</v>
-      </c>
-      <c r="E5">
-        <v>6</v>
-      </c>
-      <c r="F5">
-        <v>2</v>
-      </c>
-      <c r="G5">
-        <v>1</v>
-      </c>
-      <c r="H5">
-        <v>2</v>
-      </c>
-      <c r="I5">
-        <v>2</v>
-      </c>
-      <c r="J5">
-        <v>3</v>
-      </c>
-      <c r="M5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B6">
-        <v>13</v>
-      </c>
-      <c r="C6">
-        <v>15</v>
-      </c>
-      <c r="D6">
-        <v>13</v>
-      </c>
-      <c r="E6">
-        <v>9</v>
-      </c>
-      <c r="F6">
-        <v>14</v>
-      </c>
-      <c r="G6">
-        <v>6</v>
-      </c>
-      <c r="H6">
-        <v>2</v>
-      </c>
-      <c r="I6">
-        <v>9</v>
-      </c>
-      <c r="J6">
-        <v>3</v>
-      </c>
-      <c r="K6">
-        <v>3</v>
-      </c>
-      <c r="L6">
-        <v>4</v>
-      </c>
-      <c r="M6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
-      <c r="A7" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B7">
-        <v>15</v>
-      </c>
-      <c r="C7">
-        <v>18</v>
-      </c>
-      <c r="D7">
-        <v>15</v>
-      </c>
-      <c r="E7">
-        <v>16</v>
-      </c>
-      <c r="F7">
-        <v>17</v>
-      </c>
-      <c r="G7">
-        <v>8</v>
-      </c>
-      <c r="H7">
-        <v>7</v>
-      </c>
-      <c r="I7">
-        <v>12</v>
-      </c>
-      <c r="J7">
-        <v>10</v>
-      </c>
-      <c r="K7">
-        <v>6</v>
-      </c>
-      <c r="L7">
-        <v>8</v>
-      </c>
-      <c r="M7">
-        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -12041,87 +12146,123 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
       <c r="C2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D2">
-        <v>2</v>
+        <v>7</v>
+      </c>
+      <c r="E2">
+        <v>8</v>
       </c>
       <c r="F2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G2">
-        <v>3</v>
+        <v>4</v>
+      </c>
+      <c r="H2">
+        <v>2</v>
       </c>
       <c r="I2">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K2">
         <v>5</v>
       </c>
       <c r="L2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M2">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
+      <c r="B3">
+        <v>1</v>
+      </c>
+      <c r="C3">
+        <v>3</v>
+      </c>
       <c r="D3">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="E3">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F3">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G3">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H3">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="I3">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="J3">
-        <v>3</v>
+        <v>14</v>
+      </c>
+      <c r="K3">
+        <v>16</v>
       </c>
       <c r="L3">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="M3">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="I4">
+      <c r="F4">
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="K5">
+        <v>5</v>
+      </c>
+      <c r="B5">
+        <v>2</v>
+      </c>
+      <c r="D5">
+        <v>1</v>
+      </c>
+      <c r="E5">
+        <v>1</v>
+      </c>
+      <c r="F5">
+        <v>1</v>
+      </c>
+      <c r="H5">
+        <v>1</v>
+      </c>
+      <c r="I5">
+        <v>2</v>
+      </c>
+      <c r="M5">
         <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="M6">
+        <v>6</v>
+      </c>
+      <c r="I6">
         <v>1</v>
       </c>
     </row>
@@ -12130,40 +12271,40 @@
         <v>8</v>
       </c>
       <c r="B7">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="C7">
-        <v>5</v>
+        <v>35</v>
       </c>
       <c r="D7">
-        <v>6</v>
+        <v>34</v>
       </c>
       <c r="E7">
-        <v>5</v>
+        <v>56</v>
       </c>
       <c r="F7">
-        <v>6</v>
+        <v>54</v>
       </c>
       <c r="G7">
-        <v>4</v>
+        <v>37</v>
       </c>
       <c r="H7">
+        <v>39</v>
+      </c>
+      <c r="I7">
+        <v>32</v>
+      </c>
+      <c r="J7">
+        <v>34</v>
+      </c>
+      <c r="K7">
+        <v>27</v>
+      </c>
+      <c r="L7">
+        <v>31</v>
+      </c>
+      <c r="M7">
         <v>12</v>
-      </c>
-      <c r="I7">
-        <v>7</v>
-      </c>
-      <c r="J7">
-        <v>6</v>
-      </c>
-      <c r="K7">
-        <v>16</v>
-      </c>
-      <c r="L7">
-        <v>8</v>
-      </c>
-      <c r="M7">
-        <v>2</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -12171,40 +12312,40 @@
         <v>9</v>
       </c>
       <c r="B8">
-        <v>20</v>
+        <v>54</v>
       </c>
       <c r="C8">
-        <v>21</v>
+        <v>63</v>
       </c>
       <c r="D8">
-        <v>21</v>
+        <v>50</v>
       </c>
       <c r="E8">
+        <v>109</v>
+      </c>
+      <c r="F8">
+        <v>138</v>
+      </c>
+      <c r="G8">
+        <v>53</v>
+      </c>
+      <c r="H8">
+        <v>29</v>
+      </c>
+      <c r="I8">
+        <v>49</v>
+      </c>
+      <c r="J8">
+        <v>34</v>
+      </c>
+      <c r="K8">
+        <v>28</v>
+      </c>
+      <c r="L8">
+        <v>27</v>
+      </c>
+      <c r="M8">
         <v>19</v>
-      </c>
-      <c r="F8">
-        <v>19</v>
-      </c>
-      <c r="G8">
-        <v>7</v>
-      </c>
-      <c r="H8">
-        <v>5</v>
-      </c>
-      <c r="I8">
-        <v>10</v>
-      </c>
-      <c r="J8">
-        <v>9</v>
-      </c>
-      <c r="K8">
-        <v>12</v>
-      </c>
-      <c r="L8">
-        <v>12</v>
-      </c>
-      <c r="M8">
-        <v>6</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -12212,40 +12353,40 @@
         <v>10</v>
       </c>
       <c r="B9">
-        <v>24</v>
+        <v>73</v>
       </c>
       <c r="C9">
-        <v>27</v>
+        <v>103</v>
       </c>
       <c r="D9">
-        <v>30</v>
+        <v>101</v>
       </c>
       <c r="E9">
-        <v>25</v>
+        <v>178</v>
       </c>
       <c r="F9">
-        <v>29</v>
+        <v>204</v>
       </c>
       <c r="G9">
-        <v>18</v>
+        <v>100</v>
       </c>
       <c r="H9">
-        <v>18</v>
+        <v>79</v>
       </c>
       <c r="I9">
-        <v>23</v>
+        <v>98</v>
       </c>
       <c r="J9">
-        <v>19</v>
+        <v>85</v>
       </c>
       <c r="K9">
-        <v>34</v>
+        <v>76</v>
       </c>
       <c r="L9">
-        <v>25</v>
+        <v>71</v>
       </c>
       <c r="M9">
-        <v>15</v>
+        <v>46</v>
       </c>
     </row>
   </sheetData>
@@ -12255,7 +12396,7 @@
 
 <file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M7"/>
+  <dimension ref="A1:M9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="23.7109375" customWidth="1"/>
@@ -12319,19 +12460,19 @@
         <v>1</v>
       </c>
       <c r="C2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F2">
-        <v>2</v>
-      </c>
-      <c r="H2">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="G2">
+        <v>3</v>
       </c>
       <c r="I2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J2">
         <v>1</v>
@@ -12340,191 +12481,189 @@
         <v>5</v>
       </c>
       <c r="L2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M2">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B3">
-        <v>4</v>
-      </c>
       <c r="D3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F3">
         <v>1</v>
       </c>
       <c r="G3">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H3">
         <v>1</v>
       </c>
       <c r="I3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J3">
-        <v>4</v>
-      </c>
-      <c r="K3">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L3">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M3">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B4">
-        <v>1</v>
-      </c>
-      <c r="H4">
-        <v>2</v>
-      </c>
-      <c r="K4">
-        <v>3</v>
-      </c>
-      <c r="L4">
-        <v>1</v>
-      </c>
-      <c r="M4">
+        <v>3</v>
+      </c>
+      <c r="I4">
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5">
-        <v>5</v>
-      </c>
-      <c r="C5">
-        <v>7</v>
-      </c>
-      <c r="D5">
-        <v>11</v>
-      </c>
-      <c r="E5">
-        <v>21</v>
-      </c>
-      <c r="F5">
-        <v>25</v>
-      </c>
-      <c r="G5">
-        <v>15</v>
-      </c>
-      <c r="H5">
-        <v>10</v>
-      </c>
-      <c r="I5">
-        <v>9</v>
-      </c>
-      <c r="J5">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="K5">
-        <v>18</v>
-      </c>
-      <c r="L5">
-        <v>11</v>
-      </c>
-      <c r="M5">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B6">
-        <v>17</v>
-      </c>
-      <c r="C6">
-        <v>12</v>
-      </c>
-      <c r="D6">
-        <v>19</v>
-      </c>
-      <c r="E6">
-        <v>30</v>
-      </c>
-      <c r="F6">
-        <v>34</v>
-      </c>
-      <c r="G6">
-        <v>9</v>
-      </c>
-      <c r="H6">
-        <v>10</v>
-      </c>
-      <c r="I6">
-        <v>7</v>
-      </c>
-      <c r="J6">
-        <v>20</v>
-      </c>
-      <c r="K6">
-        <v>11</v>
-      </c>
-      <c r="L6">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="M6">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7">
+        <v>4</v>
+      </c>
+      <c r="C7">
+        <v>5</v>
+      </c>
+      <c r="D7">
+        <v>6</v>
+      </c>
+      <c r="E7">
+        <v>5</v>
+      </c>
+      <c r="F7">
+        <v>6</v>
+      </c>
+      <c r="G7">
+        <v>4</v>
+      </c>
+      <c r="H7">
+        <v>12</v>
+      </c>
+      <c r="I7">
+        <v>7</v>
+      </c>
+      <c r="J7">
+        <v>6</v>
+      </c>
+      <c r="K7">
+        <v>16</v>
+      </c>
+      <c r="L7">
+        <v>8</v>
+      </c>
+      <c r="M7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13">
+      <c r="A8" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B8">
+        <v>20</v>
+      </c>
+      <c r="C8">
+        <v>21</v>
+      </c>
+      <c r="D8">
+        <v>21</v>
+      </c>
+      <c r="E8">
+        <v>19</v>
+      </c>
+      <c r="F8">
+        <v>19</v>
+      </c>
+      <c r="G8">
+        <v>7</v>
+      </c>
+      <c r="H8">
+        <v>5</v>
+      </c>
+      <c r="I8">
         <v>10</v>
       </c>
-      <c r="B7">
+      <c r="J8">
+        <v>9</v>
+      </c>
+      <c r="K8">
+        <v>12</v>
+      </c>
+      <c r="L8">
+        <v>12</v>
+      </c>
+      <c r="M8">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13">
+      <c r="A9" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B9">
+        <v>24</v>
+      </c>
+      <c r="C9">
         <v>27</v>
       </c>
-      <c r="C7">
-        <v>22</v>
-      </c>
-      <c r="D7">
-        <v>33</v>
-      </c>
-      <c r="E7">
-        <v>53</v>
-      </c>
-      <c r="F7">
-        <v>62</v>
-      </c>
-      <c r="G7">
+      <c r="D9">
+        <v>30</v>
+      </c>
+      <c r="E9">
         <v>25</v>
       </c>
-      <c r="H7">
-        <v>24</v>
-      </c>
-      <c r="I7">
-        <v>24</v>
-      </c>
-      <c r="J7">
-        <v>36</v>
-      </c>
-      <c r="K7">
-        <v>42</v>
-      </c>
-      <c r="L7">
-        <v>43</v>
-      </c>
-      <c r="M7">
+      <c r="F9">
+        <v>29</v>
+      </c>
+      <c r="G9">
         <v>18</v>
+      </c>
+      <c r="H9">
+        <v>18</v>
+      </c>
+      <c r="I9">
+        <v>23</v>
+      </c>
+      <c r="J9">
+        <v>19</v>
+      </c>
+      <c r="K9">
+        <v>34</v>
+      </c>
+      <c r="L9">
+        <v>25</v>
+      </c>
+      <c r="M9">
+        <v>15</v>
       </c>
     </row>
   </sheetData>
@@ -12597,29 +12736,32 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
+      <c r="C2">
+        <v>3</v>
+      </c>
       <c r="D2">
         <v>1</v>
       </c>
       <c r="F2">
-        <v>1</v>
-      </c>
-      <c r="G2">
+        <v>2</v>
+      </c>
+      <c r="H2">
         <v>1</v>
       </c>
       <c r="I2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K2">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="L2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M2">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -12627,38 +12769,56 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>1</v>
-      </c>
-      <c r="C3">
+        <v>4</v>
+      </c>
+      <c r="D3">
+        <v>2</v>
+      </c>
+      <c r="E3">
+        <v>2</v>
+      </c>
+      <c r="F3">
         <v>1</v>
       </c>
       <c r="G3">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="H3">
+        <v>1</v>
       </c>
       <c r="I3">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J3">
-        <v>1</v>
+        <v>4</v>
+      </c>
+      <c r="K3">
+        <v>5</v>
       </c>
       <c r="L3">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="M3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="E4">
-        <v>2</v>
-      </c>
-      <c r="J4">
-        <v>1</v>
+      <c r="B4">
+        <v>1</v>
+      </c>
+      <c r="H4">
+        <v>2</v>
       </c>
       <c r="K4">
+        <v>3</v>
+      </c>
+      <c r="L4">
+        <v>1</v>
+      </c>
+      <c r="M4">
         <v>1</v>
       </c>
     </row>
@@ -12667,31 +12827,40 @@
         <v>8</v>
       </c>
       <c r="B5">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C5">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D5">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="E5">
-        <v>2</v>
+        <v>21</v>
+      </c>
+      <c r="F5">
+        <v>25</v>
       </c>
       <c r="G5">
-        <v>1</v>
+        <v>15</v>
+      </c>
+      <c r="H5">
+        <v>10</v>
       </c>
       <c r="I5">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="J5">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="K5">
-        <v>4</v>
+        <v>18</v>
+      </c>
+      <c r="L5">
+        <v>11</v>
       </c>
       <c r="M5">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -12699,40 +12868,40 @@
         <v>9</v>
       </c>
       <c r="B6">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="C6">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D6">
+        <v>19</v>
+      </c>
+      <c r="E6">
+        <v>30</v>
+      </c>
+      <c r="F6">
+        <v>34</v>
+      </c>
+      <c r="G6">
+        <v>9</v>
+      </c>
+      <c r="H6">
         <v>10</v>
       </c>
-      <c r="E6">
-        <v>9</v>
-      </c>
-      <c r="F6">
-        <v>9</v>
-      </c>
-      <c r="G6">
-        <v>8</v>
-      </c>
-      <c r="H6">
-        <v>1</v>
-      </c>
       <c r="I6">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="J6">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="K6">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="L6">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="M6">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -12740,40 +12909,40 @@
         <v>10</v>
       </c>
       <c r="B7">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="C7">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="D7">
-        <v>13</v>
+        <v>33</v>
       </c>
       <c r="E7">
-        <v>13</v>
+        <v>53</v>
       </c>
       <c r="F7">
-        <v>10</v>
+        <v>62</v>
       </c>
       <c r="G7">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="H7">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="I7">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="J7">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="K7">
-        <v>15</v>
+        <v>42</v>
       </c>
       <c r="L7">
-        <v>6</v>
+        <v>43</v>
       </c>
       <c r="M7">
-        <v>5</v>
+        <v>18</v>
       </c>
     </row>
   </sheetData>
@@ -12783,7 +12952,7 @@
 
 <file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M9"/>
+  <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="23.7109375" customWidth="1"/>
@@ -12846,26 +13015,29 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C2">
-        <v>1</v>
-      </c>
       <c r="D2">
         <v>1</v>
       </c>
-      <c r="E2">
-        <v>1</v>
-      </c>
       <c r="F2">
         <v>1</v>
       </c>
+      <c r="G2">
+        <v>1</v>
+      </c>
+      <c r="I2">
+        <v>2</v>
+      </c>
       <c r="J2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K2">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="L2">
-        <v>5</v>
+        <v>2</v>
+      </c>
+      <c r="M2">
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -12873,31 +13045,22 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C3">
-        <v>2</v>
-      </c>
-      <c r="D3">
-        <v>1</v>
-      </c>
-      <c r="E3">
-        <v>3</v>
-      </c>
-      <c r="H3">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="G3">
+        <v>2</v>
       </c>
       <c r="I3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J3">
         <v>1</v>
       </c>
-      <c r="K3">
-        <v>3</v>
-      </c>
       <c r="L3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M3">
         <v>1</v>
@@ -12907,147 +13070,128 @@
       <c r="A4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D4">
-        <v>1</v>
-      </c>
-      <c r="L4">
+      <c r="E4">
+        <v>2</v>
+      </c>
+      <c r="J4">
+        <v>1</v>
+      </c>
+      <c r="K4">
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>6</v>
+        <v>8</v>
+      </c>
+      <c r="B5">
+        <v>1</v>
+      </c>
+      <c r="C5">
+        <v>1</v>
+      </c>
+      <c r="D5">
+        <v>2</v>
+      </c>
+      <c r="E5">
+        <v>2</v>
       </c>
       <c r="G5">
+        <v>1</v>
+      </c>
+      <c r="I5">
+        <v>1</v>
+      </c>
+      <c r="J5">
+        <v>3</v>
+      </c>
+      <c r="K5">
+        <v>4</v>
+      </c>
+      <c r="M5">
         <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
-        <v>7</v>
+        <v>9</v>
+      </c>
+      <c r="B6">
+        <v>8</v>
+      </c>
+      <c r="C6">
+        <v>13</v>
+      </c>
+      <c r="D6">
+        <v>10</v>
+      </c>
+      <c r="E6">
+        <v>9</v>
+      </c>
+      <c r="F6">
+        <v>9</v>
+      </c>
+      <c r="G6">
+        <v>8</v>
+      </c>
+      <c r="H6">
+        <v>1</v>
+      </c>
+      <c r="I6">
+        <v>4</v>
       </c>
       <c r="J6">
-        <v>1</v>
+        <v>5</v>
+      </c>
+      <c r="K6">
+        <v>8</v>
+      </c>
+      <c r="L6">
+        <v>3</v>
+      </c>
+      <c r="M6">
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7">
+        <v>10</v>
+      </c>
+      <c r="C7">
+        <v>15</v>
+      </c>
+      <c r="D7">
+        <v>13</v>
+      </c>
+      <c r="E7">
+        <v>13</v>
+      </c>
+      <c r="F7">
+        <v>10</v>
+      </c>
+      <c r="G7">
+        <v>12</v>
+      </c>
+      <c r="H7">
+        <v>1</v>
+      </c>
+      <c r="I7">
         <v>8</v>
       </c>
-      <c r="B7">
-        <v>4</v>
-      </c>
-      <c r="C7">
-        <v>2</v>
-      </c>
-      <c r="D7">
-        <v>8</v>
-      </c>
-      <c r="E7">
-        <v>5</v>
-      </c>
-      <c r="F7">
-        <v>4</v>
-      </c>
-      <c r="G7">
-        <v>4</v>
-      </c>
-      <c r="I7">
-        <v>3</v>
-      </c>
       <c r="J7">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="K7">
+        <v>15</v>
+      </c>
+      <c r="L7">
         <v>6</v>
       </c>
-      <c r="L7">
-        <v>5</v>
-      </c>
       <c r="M7">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13">
-      <c r="A8" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B8">
-        <v>11</v>
-      </c>
-      <c r="C8">
-        <v>22</v>
-      </c>
-      <c r="D8">
-        <v>24</v>
-      </c>
-      <c r="E8">
-        <v>19</v>
-      </c>
-      <c r="F8">
-        <v>10</v>
-      </c>
-      <c r="G8">
-        <v>4</v>
-      </c>
-      <c r="H8">
-        <v>4</v>
-      </c>
-      <c r="I8">
-        <v>4</v>
-      </c>
-      <c r="J8">
-        <v>4</v>
-      </c>
-      <c r="K8">
-        <v>4</v>
-      </c>
-      <c r="L8">
-        <v>3</v>
-      </c>
-      <c r="M8">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13">
-      <c r="A9" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B9">
-        <v>17</v>
-      </c>
-      <c r="C9">
-        <v>27</v>
-      </c>
-      <c r="D9">
-        <v>35</v>
-      </c>
-      <c r="E9">
-        <v>28</v>
-      </c>
-      <c r="F9">
-        <v>15</v>
-      </c>
-      <c r="G9">
-        <v>9</v>
-      </c>
-      <c r="H9">
-        <v>5</v>
-      </c>
-      <c r="I9">
-        <v>9</v>
-      </c>
-      <c r="J9">
-        <v>11</v>
-      </c>
-      <c r="K9">
-        <v>19</v>
-      </c>
-      <c r="L9">
-        <v>16</v>
-      </c>
-      <c r="M9">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -13120,45 +13264,69 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
       <c r="D2">
         <v>1</v>
       </c>
       <c r="E2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F2">
         <v>1</v>
       </c>
-      <c r="G2">
-        <v>1</v>
-      </c>
-      <c r="M2">
-        <v>1</v>
+      <c r="J2">
+        <v>1</v>
+      </c>
+      <c r="K2">
+        <v>6</v>
+      </c>
+      <c r="L2">
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
+      <c r="B3">
+        <v>2</v>
+      </c>
+      <c r="C3">
+        <v>2</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
       <c r="E3">
-        <v>1</v>
-      </c>
-      <c r="F3">
-        <v>2</v>
+        <v>3</v>
+      </c>
+      <c r="H3">
+        <v>1</v>
       </c>
       <c r="I3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J3">
-        <v>3</v>
+        <v>1</v>
+      </c>
+      <c r="K3">
+        <v>3</v>
+      </c>
+      <c r="L3">
+        <v>2</v>
       </c>
       <c r="M3">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
-        <v>3</v>
+        <v>5</v>
+      </c>
+      <c r="D4">
+        <v>1</v>
       </c>
       <c r="L4">
         <v>1</v>
@@ -13166,9 +13334,9 @@
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="K5">
+        <v>6</v>
+      </c>
+      <c r="G5">
         <v>1</v>
       </c>
     </row>
@@ -13176,7 +13344,7 @@
       <c r="A6" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="H6">
+      <c r="J6">
         <v>1</v>
       </c>
     </row>
@@ -13184,32 +13352,38 @@
       <c r="A7" s="1" t="s">
         <v>8</v>
       </c>
+      <c r="B7">
+        <v>4</v>
+      </c>
       <c r="C7">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D7">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E7">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F7">
-        <v>1</v>
-      </c>
-      <c r="H7">
-        <v>3</v>
+        <v>4</v>
+      </c>
+      <c r="G7">
+        <v>4</v>
       </c>
       <c r="I7">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J7">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K7">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="L7">
-        <v>1</v>
+        <v>5</v>
+      </c>
+      <c r="M7">
+        <v>3</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -13217,40 +13391,40 @@
         <v>9</v>
       </c>
       <c r="B8">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="C8">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="D8">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="E8">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="F8">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="G8">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="H8">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I8">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="J8">
         <v>4</v>
       </c>
       <c r="K8">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="L8">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="M8">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -13258,40 +13432,40 @@
         <v>10</v>
       </c>
       <c r="B9">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C9">
+        <v>27</v>
+      </c>
+      <c r="D9">
+        <v>35</v>
+      </c>
+      <c r="E9">
+        <v>28</v>
+      </c>
+      <c r="F9">
+        <v>15</v>
+      </c>
+      <c r="G9">
+        <v>9</v>
+      </c>
+      <c r="H9">
+        <v>5</v>
+      </c>
+      <c r="I9">
+        <v>9</v>
+      </c>
+      <c r="J9">
+        <v>11</v>
+      </c>
+      <c r="K9">
+        <v>19</v>
+      </c>
+      <c r="L9">
         <v>16</v>
       </c>
-      <c r="D9">
-        <v>32</v>
-      </c>
-      <c r="E9">
-        <v>37</v>
-      </c>
-      <c r="F9">
-        <v>30</v>
-      </c>
-      <c r="G9">
-        <v>8</v>
-      </c>
-      <c r="H9">
-        <v>10</v>
-      </c>
-      <c r="I9">
-        <v>17</v>
-      </c>
-      <c r="J9">
-        <v>8</v>
-      </c>
-      <c r="K9">
-        <v>11</v>
-      </c>
-      <c r="L9">
-        <v>13</v>
-      </c>
       <c r="M9">
-        <v>11</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -13300,473 +13474,6 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M8"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" customWidth="1"/>
-    <col min="13" max="13" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="M1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2">
-        <v>1</v>
-      </c>
-      <c r="D2">
-        <v>2</v>
-      </c>
-      <c r="G2">
-        <v>4</v>
-      </c>
-      <c r="H2">
-        <v>1</v>
-      </c>
-      <c r="I2">
-        <v>1</v>
-      </c>
-      <c r="J2">
-        <v>3</v>
-      </c>
-      <c r="K2">
-        <v>2</v>
-      </c>
-      <c r="L2">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C3">
-        <v>1</v>
-      </c>
-      <c r="D3">
-        <v>1</v>
-      </c>
-      <c r="E3">
-        <v>1</v>
-      </c>
-      <c r="H3">
-        <v>1</v>
-      </c>
-      <c r="I3">
-        <v>1</v>
-      </c>
-      <c r="J3">
-        <v>3</v>
-      </c>
-      <c r="K3">
-        <v>1</v>
-      </c>
-      <c r="L3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D4">
-        <v>1</v>
-      </c>
-      <c r="E4">
-        <v>1</v>
-      </c>
-      <c r="J4">
-        <v>1</v>
-      </c>
-      <c r="L4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C5">
-        <v>1</v>
-      </c>
-      <c r="J5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B6">
-        <v>2</v>
-      </c>
-      <c r="C6">
-        <v>5</v>
-      </c>
-      <c r="D6">
-        <v>3</v>
-      </c>
-      <c r="E6">
-        <v>4</v>
-      </c>
-      <c r="F6">
-        <v>5</v>
-      </c>
-      <c r="G6">
-        <v>5</v>
-      </c>
-      <c r="H6">
-        <v>8</v>
-      </c>
-      <c r="I6">
-        <v>5</v>
-      </c>
-      <c r="J6">
-        <v>8</v>
-      </c>
-      <c r="K6">
-        <v>7</v>
-      </c>
-      <c r="L6">
-        <v>7</v>
-      </c>
-      <c r="M6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
-      <c r="A7" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B7">
-        <v>17</v>
-      </c>
-      <c r="C7">
-        <v>24</v>
-      </c>
-      <c r="D7">
-        <v>35</v>
-      </c>
-      <c r="E7">
-        <v>31</v>
-      </c>
-      <c r="F7">
-        <v>18</v>
-      </c>
-      <c r="G7">
-        <v>17</v>
-      </c>
-      <c r="H7">
-        <v>8</v>
-      </c>
-      <c r="I7">
-        <v>16</v>
-      </c>
-      <c r="J7">
-        <v>15</v>
-      </c>
-      <c r="K7">
-        <v>10</v>
-      </c>
-      <c r="L7">
-        <v>12</v>
-      </c>
-      <c r="M7">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13">
-      <c r="A8" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B8">
-        <v>19</v>
-      </c>
-      <c r="C8">
-        <v>32</v>
-      </c>
-      <c r="D8">
-        <v>42</v>
-      </c>
-      <c r="E8">
-        <v>37</v>
-      </c>
-      <c r="F8">
-        <v>23</v>
-      </c>
-      <c r="G8">
-        <v>26</v>
-      </c>
-      <c r="H8">
-        <v>18</v>
-      </c>
-      <c r="I8">
-        <v>23</v>
-      </c>
-      <c r="J8">
-        <v>31</v>
-      </c>
-      <c r="K8">
-        <v>20</v>
-      </c>
-      <c r="L8">
-        <v>26</v>
-      </c>
-      <c r="M8">
-        <v>8</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet40.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L6"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="18.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:12">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="H2">
-        <v>1</v>
-      </c>
-      <c r="J2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3">
-        <v>1</v>
-      </c>
-      <c r="C3">
-        <v>1</v>
-      </c>
-      <c r="G3">
-        <v>1</v>
-      </c>
-      <c r="H3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12">
-      <c r="A4" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4">
-        <v>2</v>
-      </c>
-      <c r="C4">
-        <v>3</v>
-      </c>
-      <c r="E4">
-        <v>1</v>
-      </c>
-      <c r="F4">
-        <v>1</v>
-      </c>
-      <c r="G4">
-        <v>1</v>
-      </c>
-      <c r="H4">
-        <v>1</v>
-      </c>
-      <c r="K4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12">
-      <c r="A5" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B5">
-        <v>3</v>
-      </c>
-      <c r="C5">
-        <v>2</v>
-      </c>
-      <c r="D5">
-        <v>2</v>
-      </c>
-      <c r="E5">
-        <v>3</v>
-      </c>
-      <c r="F5">
-        <v>1</v>
-      </c>
-      <c r="G5">
-        <v>1</v>
-      </c>
-      <c r="H5">
-        <v>1</v>
-      </c>
-      <c r="I5">
-        <v>3</v>
-      </c>
-      <c r="J5">
-        <v>2</v>
-      </c>
-      <c r="K5">
-        <v>1</v>
-      </c>
-      <c r="L5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12">
-      <c r="A6" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B6">
-        <v>6</v>
-      </c>
-      <c r="C6">
-        <v>6</v>
-      </c>
-      <c r="D6">
-        <v>2</v>
-      </c>
-      <c r="E6">
-        <v>4</v>
-      </c>
-      <c r="F6">
-        <v>2</v>
-      </c>
-      <c r="G6">
-        <v>3</v>
-      </c>
-      <c r="H6">
-        <v>5</v>
-      </c>
-      <c r="I6">
-        <v>3</v>
-      </c>
-      <c r="J6">
-        <v>4</v>
-      </c>
-      <c r="K6">
-        <v>2</v>
-      </c>
-      <c r="L6">
-        <v>1</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet41.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -13831,14 +13538,23 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
       <c r="E2">
-        <v>2</v>
-      </c>
-      <c r="F2">
         <v>1</v>
       </c>
       <c r="H2">
         <v>1</v>
+      </c>
+      <c r="J2">
+        <v>3</v>
+      </c>
+      <c r="K2">
+        <v>1</v>
+      </c>
+      <c r="L2">
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -13849,17 +13565,29 @@
         <v>1</v>
       </c>
       <c r="G3">
+        <v>1</v>
+      </c>
+      <c r="H3">
+        <v>2</v>
+      </c>
+      <c r="I3">
+        <v>1</v>
+      </c>
+      <c r="J3">
+        <v>1</v>
+      </c>
+      <c r="K3">
         <v>2</v>
       </c>
       <c r="L3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="I4">
+      <c r="B4">
         <v>1</v>
       </c>
     </row>
@@ -13867,17 +13595,35 @@
       <c r="A5" s="1" t="s">
         <v>8</v>
       </c>
+      <c r="B5">
+        <v>1</v>
+      </c>
       <c r="C5">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="D5">
+        <v>1</v>
+      </c>
+      <c r="E5">
+        <v>6</v>
+      </c>
+      <c r="F5">
+        <v>2</v>
       </c>
       <c r="G5">
         <v>1</v>
       </c>
-      <c r="K5">
-        <v>1</v>
+      <c r="H5">
+        <v>2</v>
+      </c>
+      <c r="I5">
+        <v>2</v>
+      </c>
+      <c r="J5">
+        <v>3</v>
       </c>
       <c r="M5">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -13885,31 +13631,37 @@
         <v>9</v>
       </c>
       <c r="B6">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="C6">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="D6">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="E6">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F6">
-        <v>3</v>
+        <v>14</v>
+      </c>
+      <c r="G6">
+        <v>6</v>
       </c>
       <c r="H6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I6">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="J6">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K6">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="L6">
+        <v>4</v>
       </c>
       <c r="M6">
         <v>3</v>
@@ -13920,40 +13672,476 @@
         <v>10</v>
       </c>
       <c r="B7">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="C7">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="D7">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="E7">
+        <v>16</v>
+      </c>
+      <c r="F7">
+        <v>17</v>
+      </c>
+      <c r="G7">
+        <v>8</v>
+      </c>
+      <c r="H7">
+        <v>7</v>
+      </c>
+      <c r="I7">
+        <v>12</v>
+      </c>
+      <c r="J7">
+        <v>10</v>
+      </c>
+      <c r="K7">
+        <v>6</v>
+      </c>
+      <c r="L7">
+        <v>8</v>
+      </c>
+      <c r="M7">
+        <v>4</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet40.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:M9"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+    <col min="13" max="13" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="M1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="E2">
+        <v>2</v>
+      </c>
+      <c r="F2">
+        <v>1</v>
+      </c>
+      <c r="G2">
+        <v>1</v>
+      </c>
+      <c r="M2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E3">
+        <v>1</v>
+      </c>
+      <c r="F3">
+        <v>2</v>
+      </c>
+      <c r="I3">
+        <v>1</v>
+      </c>
+      <c r="J3">
+        <v>3</v>
+      </c>
+      <c r="M3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="L4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="K5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="H6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C7">
+        <v>3</v>
+      </c>
+      <c r="D7">
+        <v>2</v>
+      </c>
+      <c r="E7">
+        <v>3</v>
+      </c>
+      <c r="F7">
+        <v>1</v>
+      </c>
+      <c r="H7">
+        <v>3</v>
+      </c>
+      <c r="I7">
+        <v>5</v>
+      </c>
+      <c r="J7">
+        <v>1</v>
+      </c>
+      <c r="K7">
+        <v>1</v>
+      </c>
+      <c r="L7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13">
+      <c r="A8" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="F7">
-        <v>5</v>
-      </c>
-      <c r="G7">
-        <v>3</v>
-      </c>
-      <c r="H7">
-        <v>2</v>
-      </c>
-      <c r="I7">
-        <v>2</v>
-      </c>
-      <c r="J7">
-        <v>5</v>
-      </c>
-      <c r="K7">
-        <v>2</v>
-      </c>
-      <c r="L7">
-        <v>1</v>
-      </c>
-      <c r="M7">
-        <v>5</v>
+      <c r="B8">
+        <v>18</v>
+      </c>
+      <c r="C8">
+        <v>13</v>
+      </c>
+      <c r="D8">
+        <v>29</v>
+      </c>
+      <c r="E8">
+        <v>31</v>
+      </c>
+      <c r="F8">
+        <v>26</v>
+      </c>
+      <c r="G8">
+        <v>7</v>
+      </c>
+      <c r="H8">
+        <v>6</v>
+      </c>
+      <c r="I8">
+        <v>11</v>
+      </c>
+      <c r="J8">
+        <v>4</v>
+      </c>
+      <c r="K8">
+        <v>9</v>
+      </c>
+      <c r="L8">
+        <v>11</v>
+      </c>
+      <c r="M8">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13">
+      <c r="A9" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B9">
+        <v>18</v>
+      </c>
+      <c r="C9">
+        <v>16</v>
+      </c>
+      <c r="D9">
+        <v>32</v>
+      </c>
+      <c r="E9">
+        <v>37</v>
+      </c>
+      <c r="F9">
+        <v>30</v>
+      </c>
+      <c r="G9">
+        <v>8</v>
+      </c>
+      <c r="H9">
+        <v>10</v>
+      </c>
+      <c r="I9">
+        <v>17</v>
+      </c>
+      <c r="J9">
+        <v>8</v>
+      </c>
+      <c r="K9">
+        <v>11</v>
+      </c>
+      <c r="L9">
+        <v>13</v>
+      </c>
+      <c r="M9">
+        <v>11</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet41.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:L6"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="18.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="H2">
+        <v>1</v>
+      </c>
+      <c r="J2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>1</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
+      <c r="G3">
+        <v>1</v>
+      </c>
+      <c r="H3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12">
+      <c r="A4" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4">
+        <v>2</v>
+      </c>
+      <c r="C4">
+        <v>3</v>
+      </c>
+      <c r="E4">
+        <v>1</v>
+      </c>
+      <c r="F4">
+        <v>1</v>
+      </c>
+      <c r="G4">
+        <v>1</v>
+      </c>
+      <c r="H4">
+        <v>1</v>
+      </c>
+      <c r="K4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12">
+      <c r="A5" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5">
+        <v>3</v>
+      </c>
+      <c r="C5">
+        <v>2</v>
+      </c>
+      <c r="D5">
+        <v>2</v>
+      </c>
+      <c r="E5">
+        <v>3</v>
+      </c>
+      <c r="F5">
+        <v>1</v>
+      </c>
+      <c r="G5">
+        <v>1</v>
+      </c>
+      <c r="H5">
+        <v>1</v>
+      </c>
+      <c r="I5">
+        <v>3</v>
+      </c>
+      <c r="J5">
+        <v>2</v>
+      </c>
+      <c r="K5">
+        <v>1</v>
+      </c>
+      <c r="L5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12">
+      <c r="A6" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6">
+        <v>6</v>
+      </c>
+      <c r="C6">
+        <v>6</v>
+      </c>
+      <c r="D6">
+        <v>2</v>
+      </c>
+      <c r="E6">
+        <v>4</v>
+      </c>
+      <c r="F6">
+        <v>2</v>
+      </c>
+      <c r="G6">
+        <v>3</v>
+      </c>
+      <c r="H6">
+        <v>5</v>
+      </c>
+      <c r="I6">
+        <v>3</v>
+      </c>
+      <c r="J6">
+        <v>4</v>
+      </c>
+      <c r="K6">
+        <v>2</v>
+      </c>
+      <c r="L6">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -13962,6 +14150,201 @@
 </file>
 
 <file path=xl/worksheets/sheet42.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:M7"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+    <col min="13" max="13" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="M1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E2">
+        <v>2</v>
+      </c>
+      <c r="F2">
+        <v>1</v>
+      </c>
+      <c r="H2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F3">
+        <v>1</v>
+      </c>
+      <c r="G3">
+        <v>2</v>
+      </c>
+      <c r="L3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="I4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C5">
+        <v>1</v>
+      </c>
+      <c r="G5">
+        <v>1</v>
+      </c>
+      <c r="K5">
+        <v>1</v>
+      </c>
+      <c r="M5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6">
+        <v>1</v>
+      </c>
+      <c r="C6">
+        <v>2</v>
+      </c>
+      <c r="D6">
+        <v>2</v>
+      </c>
+      <c r="E6">
+        <v>7</v>
+      </c>
+      <c r="F6">
+        <v>3</v>
+      </c>
+      <c r="H6">
+        <v>1</v>
+      </c>
+      <c r="I6">
+        <v>1</v>
+      </c>
+      <c r="J6">
+        <v>5</v>
+      </c>
+      <c r="K6">
+        <v>1</v>
+      </c>
+      <c r="M6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7">
+        <v>1</v>
+      </c>
+      <c r="C7">
+        <v>3</v>
+      </c>
+      <c r="D7">
+        <v>2</v>
+      </c>
+      <c r="E7">
+        <v>9</v>
+      </c>
+      <c r="F7">
+        <v>5</v>
+      </c>
+      <c r="G7">
+        <v>3</v>
+      </c>
+      <c r="H7">
+        <v>2</v>
+      </c>
+      <c r="I7">
+        <v>2</v>
+      </c>
+      <c r="J7">
+        <v>5</v>
+      </c>
+      <c r="K7">
+        <v>2</v>
+      </c>
+      <c r="L7">
+        <v>1</v>
+      </c>
+      <c r="M7">
+        <v>5</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet43.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M9"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -14253,7 +14636,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet43.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet44.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -14494,7 +14877,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet44.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet45.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -14688,257 +15071,6 @@
       </c>
       <c r="M7">
         <v>1</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet45.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M8"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" customWidth="1"/>
-    <col min="13" max="13" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="M1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2">
-        <v>1</v>
-      </c>
-      <c r="D2">
-        <v>2</v>
-      </c>
-      <c r="F2">
-        <v>2</v>
-      </c>
-      <c r="I2">
-        <v>3</v>
-      </c>
-      <c r="J2">
-        <v>2</v>
-      </c>
-      <c r="K2">
-        <v>1</v>
-      </c>
-      <c r="L2">
-        <v>5</v>
-      </c>
-      <c r="M2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C3">
-        <v>1</v>
-      </c>
-      <c r="E3">
-        <v>1</v>
-      </c>
-      <c r="H3">
-        <v>2</v>
-      </c>
-      <c r="I3">
-        <v>1</v>
-      </c>
-      <c r="J3">
-        <v>1</v>
-      </c>
-      <c r="K3">
-        <v>2</v>
-      </c>
-      <c r="L3">
-        <v>2</v>
-      </c>
-      <c r="M3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C4">
-        <v>1</v>
-      </c>
-      <c r="I4">
-        <v>1</v>
-      </c>
-      <c r="K4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="L5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B6">
-        <v>1</v>
-      </c>
-      <c r="F6">
-        <v>4</v>
-      </c>
-      <c r="H6">
-        <v>1</v>
-      </c>
-      <c r="I6">
-        <v>2</v>
-      </c>
-      <c r="K6">
-        <v>1</v>
-      </c>
-      <c r="M6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
-      <c r="A7" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B7">
-        <v>10</v>
-      </c>
-      <c r="C7">
-        <v>20</v>
-      </c>
-      <c r="D7">
-        <v>25</v>
-      </c>
-      <c r="E7">
-        <v>30</v>
-      </c>
-      <c r="F7">
-        <v>41</v>
-      </c>
-      <c r="G7">
-        <v>10</v>
-      </c>
-      <c r="H7">
-        <v>5</v>
-      </c>
-      <c r="I7">
-        <v>5</v>
-      </c>
-      <c r="J7">
-        <v>15</v>
-      </c>
-      <c r="K7">
-        <v>17</v>
-      </c>
-      <c r="L7">
-        <v>12</v>
-      </c>
-      <c r="M7">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13">
-      <c r="A8" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B8">
-        <v>12</v>
-      </c>
-      <c r="C8">
-        <v>22</v>
-      </c>
-      <c r="D8">
-        <v>27</v>
-      </c>
-      <c r="E8">
-        <v>31</v>
-      </c>
-      <c r="F8">
-        <v>47</v>
-      </c>
-      <c r="G8">
-        <v>10</v>
-      </c>
-      <c r="H8">
-        <v>8</v>
-      </c>
-      <c r="I8">
-        <v>12</v>
-      </c>
-      <c r="J8">
-        <v>18</v>
-      </c>
-      <c r="K8">
-        <v>22</v>
-      </c>
-      <c r="L8">
-        <v>21</v>
-      </c>
-      <c r="M8">
-        <v>16</v>
       </c>
     </row>
   </sheetData>
@@ -15855,7 +15987,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M10"/>
+  <dimension ref="A1:M8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="23.7109375" customWidth="1"/>
@@ -15919,260 +16051,184 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>5</v>
-      </c>
-      <c r="C2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D2">
-        <v>7</v>
-      </c>
-      <c r="E2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F2">
-        <v>5</v>
-      </c>
-      <c r="G2">
-        <v>4</v>
-      </c>
-      <c r="H2">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="I2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J2">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="K2">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="L2">
         <v>5</v>
       </c>
       <c r="M2">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B3">
-        <v>3</v>
-      </c>
       <c r="C3">
-        <v>2</v>
-      </c>
-      <c r="D3">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E3">
-        <v>9</v>
-      </c>
-      <c r="F3">
-        <v>19</v>
-      </c>
-      <c r="G3">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="H3">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="I3">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="J3">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="K3">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="L3">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="M3">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
-        <v>3</v>
+        <v>5</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
       </c>
       <c r="I4">
         <v>1</v>
       </c>
-      <c r="M4">
-        <v>2</v>
+      <c r="K4">
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="K5">
-        <v>1</v>
+        <v>6</v>
+      </c>
+      <c r="L5">
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="E6">
+        <v>8</v>
+      </c>
+      <c r="B6">
         <v>1</v>
       </c>
       <c r="F6">
-        <v>2</v>
-      </c>
-      <c r="J6">
-        <v>2</v>
+        <v>4</v>
+      </c>
+      <c r="H6">
+        <v>1</v>
+      </c>
+      <c r="I6">
+        <v>2</v>
+      </c>
+      <c r="K6">
+        <v>1</v>
       </c>
       <c r="M6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="1" t="s">
-        <v>6</v>
+        <v>9</v>
+      </c>
+      <c r="B7">
+        <v>10</v>
+      </c>
+      <c r="C7">
+        <v>20</v>
+      </c>
+      <c r="D7">
+        <v>25</v>
       </c>
       <c r="E7">
-        <v>1</v>
+        <v>30</v>
+      </c>
+      <c r="F7">
+        <v>41</v>
+      </c>
+      <c r="G7">
+        <v>10</v>
+      </c>
+      <c r="H7">
+        <v>5</v>
       </c>
       <c r="I7">
-        <v>1</v>
+        <v>5</v>
+      </c>
+      <c r="J7">
+        <v>15</v>
       </c>
       <c r="K7">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="L7">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="M7">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8" spans="1:13">
       <c r="A8" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B8">
+        <v>12</v>
+      </c>
+      <c r="C8">
+        <v>22</v>
+      </c>
+      <c r="D8">
+        <v>27</v>
+      </c>
+      <c r="E8">
+        <v>31</v>
+      </c>
+      <c r="F8">
+        <v>47</v>
+      </c>
+      <c r="G8">
+        <v>10</v>
+      </c>
+      <c r="H8">
         <v>8</v>
       </c>
-      <c r="B8">
-        <v>24</v>
-      </c>
-      <c r="C8">
-        <v>37</v>
-      </c>
-      <c r="D8">
+      <c r="I8">
+        <v>12</v>
+      </c>
+      <c r="J8">
+        <v>18</v>
+      </c>
+      <c r="K8">
+        <v>22</v>
+      </c>
+      <c r="L8">
         <v>21</v>
       </c>
-      <c r="E8">
-        <v>22</v>
-      </c>
-      <c r="F8">
-        <v>27</v>
-      </c>
-      <c r="G8">
-        <v>15</v>
-      </c>
-      <c r="H8">
-        <v>25</v>
-      </c>
-      <c r="I8">
-        <v>21</v>
-      </c>
-      <c r="J8">
-        <v>26</v>
-      </c>
-      <c r="K8">
-        <v>49</v>
-      </c>
-      <c r="L8">
-        <v>44</v>
-      </c>
       <c r="M8">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13">
-      <c r="A9" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B9">
-        <v>45</v>
-      </c>
-      <c r="C9">
-        <v>64</v>
-      </c>
-      <c r="D9">
-        <v>46</v>
-      </c>
-      <c r="E9">
-        <v>50</v>
-      </c>
-      <c r="F9">
-        <v>38</v>
-      </c>
-      <c r="G9">
-        <v>19</v>
-      </c>
-      <c r="H9">
-        <v>27</v>
-      </c>
-      <c r="I9">
-        <v>37</v>
-      </c>
-      <c r="J9">
-        <v>20</v>
-      </c>
-      <c r="K9">
-        <v>35</v>
-      </c>
-      <c r="L9">
-        <v>35</v>
-      </c>
-      <c r="M9">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13">
-      <c r="A10" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B10">
-        <v>77</v>
-      </c>
-      <c r="C10">
-        <v>106</v>
-      </c>
-      <c r="D10">
-        <v>82</v>
-      </c>
-      <c r="E10">
-        <v>88</v>
-      </c>
-      <c r="F10">
-        <v>91</v>
-      </c>
-      <c r="G10">
-        <v>47</v>
-      </c>
-      <c r="H10">
-        <v>66</v>
-      </c>
-      <c r="I10">
-        <v>77</v>
-      </c>
-      <c r="J10">
-        <v>67</v>
-      </c>
-      <c r="K10">
-        <v>110</v>
-      </c>
-      <c r="L10">
-        <v>98</v>
-      </c>
-      <c r="M10">
-        <v>40</v>
+        <v>17</v>
       </c>
     </row>
   </sheetData>
@@ -18685,10 +18741,10 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:M8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="18.7109375" customWidth="1"/>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
     <col min="2" max="2" width="4.7109375" customWidth="1"/>
     <col min="3" max="3" width="4.7109375" customWidth="1"/>
     <col min="4" max="4" width="4.7109375" customWidth="1"/>
@@ -18748,41 +18804,26 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2">
-        <v>2</v>
-      </c>
-      <c r="C2">
-        <v>1</v>
-      </c>
-      <c r="D2">
-        <v>1</v>
-      </c>
-      <c r="E2">
-        <v>1</v>
-      </c>
       <c r="F2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I2">
         <v>2</v>
       </c>
       <c r="J2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K2">
-        <v>1</v>
-      </c>
-      <c r="L2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M2">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -18790,162 +18831,172 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C3">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D3">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E3">
-        <v>3</v>
-      </c>
-      <c r="F3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H3">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="I3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K3">
-        <v>4</v>
-      </c>
-      <c r="L3">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="M3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4">
-        <v>11</v>
-      </c>
-      <c r="C4">
-        <v>10</v>
-      </c>
-      <c r="D4">
-        <v>6</v>
-      </c>
-      <c r="E4">
-        <v>7</v>
-      </c>
-      <c r="F4">
-        <v>7</v>
-      </c>
-      <c r="G4">
-        <v>7</v>
-      </c>
-      <c r="H4">
-        <v>3</v>
-      </c>
-      <c r="I4">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="J4">
-        <v>12</v>
-      </c>
-      <c r="K4">
-        <v>4</v>
-      </c>
-      <c r="L4">
-        <v>1</v>
-      </c>
-      <c r="M4">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B5">
-        <v>15</v>
-      </c>
-      <c r="C5">
-        <v>16</v>
-      </c>
-      <c r="D5">
-        <v>22</v>
-      </c>
-      <c r="E5">
-        <v>14</v>
-      </c>
-      <c r="F5">
-        <v>13</v>
-      </c>
-      <c r="G5">
         <v>6</v>
       </c>
-      <c r="H5">
-        <v>11</v>
-      </c>
-      <c r="I5">
-        <v>4</v>
-      </c>
-      <c r="J5">
-        <v>13</v>
-      </c>
       <c r="K5">
-        <v>8</v>
-      </c>
-      <c r="L5">
-        <v>7</v>
-      </c>
-      <c r="M5">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6">
+        <v>6</v>
+      </c>
+      <c r="C6">
+        <v>2</v>
+      </c>
+      <c r="D6">
+        <v>5</v>
+      </c>
+      <c r="E6">
+        <v>5</v>
+      </c>
+      <c r="F6">
+        <v>4</v>
+      </c>
+      <c r="G6">
+        <v>4</v>
+      </c>
+      <c r="H6">
+        <v>6</v>
+      </c>
+      <c r="I6">
+        <v>8</v>
+      </c>
+      <c r="J6">
+        <v>4</v>
+      </c>
+      <c r="K6">
+        <v>3</v>
+      </c>
+      <c r="L6">
+        <v>4</v>
+      </c>
+      <c r="M6">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7">
+        <v>22</v>
+      </c>
+      <c r="C7">
+        <v>27</v>
+      </c>
+      <c r="D7">
+        <v>23</v>
+      </c>
+      <c r="E7">
+        <v>19</v>
+      </c>
+      <c r="F7">
+        <v>23</v>
+      </c>
+      <c r="G7">
+        <v>9</v>
+      </c>
+      <c r="H7">
+        <v>6</v>
+      </c>
+      <c r="I7">
+        <v>14</v>
+      </c>
+      <c r="J7">
+        <v>11</v>
+      </c>
+      <c r="K7">
+        <v>12</v>
+      </c>
+      <c r="L7">
         <v>10</v>
       </c>
-      <c r="B6">
+      <c r="M7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13">
+      <c r="A8" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B8">
+        <v>29</v>
+      </c>
+      <c r="C8">
         <v>30</v>
       </c>
-      <c r="C6">
-        <v>31</v>
-      </c>
-      <c r="D6">
-        <v>34</v>
-      </c>
-      <c r="E6">
-        <v>25</v>
-      </c>
-      <c r="F6">
-        <v>25</v>
-      </c>
-      <c r="G6">
+      <c r="D8">
+        <v>29</v>
+      </c>
+      <c r="E8">
+        <v>26</v>
+      </c>
+      <c r="F8">
+        <v>28</v>
+      </c>
+      <c r="G8">
+        <v>17</v>
+      </c>
+      <c r="H8">
         <v>15</v>
       </c>
-      <c r="H6">
-        <v>22</v>
-      </c>
-      <c r="I6">
-        <v>16</v>
-      </c>
-      <c r="J6">
-        <v>28</v>
-      </c>
-      <c r="K6">
-        <v>17</v>
-      </c>
-      <c r="L6">
-        <v>16</v>
-      </c>
-      <c r="M6">
+      <c r="I8">
+        <v>27</v>
+      </c>
+      <c r="J8">
+        <v>19</v>
+      </c>
+      <c r="K8">
+        <v>20</v>
+      </c>
+      <c r="L8">
+        <v>14</v>
+      </c>
+      <c r="M8">
         <v>12</v>
       </c>
     </row>
@@ -20989,7 +21040,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M10"/>
+  <dimension ref="A1:M8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="23.7109375" customWidth="1"/>
@@ -21052,154 +21103,124 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2">
-        <v>6</v>
-      </c>
       <c r="C2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D2">
-        <v>12</v>
-      </c>
-      <c r="E2">
-        <v>5</v>
-      </c>
-      <c r="F2">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="G2">
         <v>4</v>
       </c>
       <c r="H2">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="I2">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="J2">
-        <v>22</v>
+        <v>3</v>
       </c>
       <c r="K2">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="L2">
-        <v>15</v>
-      </c>
-      <c r="M2">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B3">
-        <v>13</v>
-      </c>
       <c r="C3">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="D3">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="E3">
-        <v>18</v>
-      </c>
-      <c r="F3">
-        <v>14</v>
-      </c>
-      <c r="G3">
-        <v>26</v>
+        <v>1</v>
       </c>
       <c r="H3">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="I3">
-        <v>32</v>
+        <v>1</v>
       </c>
       <c r="J3">
-        <v>40</v>
+        <v>3</v>
       </c>
       <c r="K3">
-        <v>26</v>
+        <v>1</v>
       </c>
       <c r="L3">
-        <v>34</v>
-      </c>
-      <c r="M3">
-        <v>17</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="G4">
+        <v>5</v>
+      </c>
+      <c r="D4">
+        <v>1</v>
+      </c>
+      <c r="E4">
         <v>1</v>
       </c>
       <c r="J4">
-        <v>2</v>
-      </c>
-      <c r="K4">
         <v>1</v>
       </c>
       <c r="L4">
-        <v>1</v>
-      </c>
-      <c r="M4">
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C5">
-        <v>2</v>
-      </c>
-      <c r="D5">
-        <v>1</v>
-      </c>
-      <c r="E5">
-        <v>2</v>
-      </c>
-      <c r="F5">
-        <v>1</v>
-      </c>
-      <c r="H5">
-        <v>2</v>
-      </c>
-      <c r="I5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J5">
-        <v>3</v>
-      </c>
-      <c r="K5">
-        <v>2</v>
-      </c>
-      <c r="L5">
-        <v>5</v>
-      </c>
-      <c r="M5">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
-        <v>6</v>
+        <v>8</v>
+      </c>
+      <c r="B6">
+        <v>2</v>
+      </c>
+      <c r="C6">
+        <v>5</v>
+      </c>
+      <c r="D6">
+        <v>3</v>
+      </c>
+      <c r="E6">
+        <v>4</v>
+      </c>
+      <c r="F6">
+        <v>5</v>
       </c>
       <c r="G6">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H6">
-        <v>2</v>
+        <v>8</v>
+      </c>
+      <c r="I6">
+        <v>5</v>
       </c>
       <c r="J6">
-        <v>2</v>
+        <v>8</v>
+      </c>
+      <c r="K6">
+        <v>7</v>
       </c>
       <c r="L6">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="M6">
         <v>1</v>
@@ -21207,133 +21228,84 @@
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7">
+        <v>17</v>
+      </c>
+      <c r="C7">
+        <v>24</v>
+      </c>
+      <c r="D7">
+        <v>35</v>
+      </c>
+      <c r="E7">
+        <v>31</v>
+      </c>
+      <c r="F7">
+        <v>18</v>
+      </c>
+      <c r="G7">
+        <v>17</v>
+      </c>
+      <c r="H7">
+        <v>8</v>
+      </c>
+      <c r="I7">
+        <v>16</v>
+      </c>
+      <c r="J7">
+        <v>15</v>
+      </c>
+      <c r="K7">
+        <v>10</v>
+      </c>
+      <c r="L7">
+        <v>12</v>
+      </c>
+      <c r="M7">
         <v>7</v>
-      </c>
-      <c r="K7">
-        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:13">
       <c r="A8" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B8">
+        <v>19</v>
+      </c>
+      <c r="C8">
+        <v>32</v>
+      </c>
+      <c r="D8">
+        <v>42</v>
+      </c>
+      <c r="E8">
+        <v>37</v>
+      </c>
+      <c r="F8">
+        <v>23</v>
+      </c>
+      <c r="G8">
+        <v>26</v>
+      </c>
+      <c r="H8">
+        <v>18</v>
+      </c>
+      <c r="I8">
+        <v>23</v>
+      </c>
+      <c r="J8">
+        <v>31</v>
+      </c>
+      <c r="K8">
+        <v>20</v>
+      </c>
+      <c r="L8">
+        <v>26</v>
+      </c>
+      <c r="M8">
         <v>8</v>
-      </c>
-      <c r="B8">
-        <v>30</v>
-      </c>
-      <c r="C8">
-        <v>44</v>
-      </c>
-      <c r="D8">
-        <v>49</v>
-      </c>
-      <c r="E8">
-        <v>67</v>
-      </c>
-      <c r="F8">
-        <v>69</v>
-      </c>
-      <c r="G8">
-        <v>57</v>
-      </c>
-      <c r="H8">
-        <v>80</v>
-      </c>
-      <c r="I8">
-        <v>80</v>
-      </c>
-      <c r="J8">
-        <v>64</v>
-      </c>
-      <c r="K8">
-        <v>48</v>
-      </c>
-      <c r="L8">
-        <v>44</v>
-      </c>
-      <c r="M8">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13">
-      <c r="A9" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B9">
-        <v>233</v>
-      </c>
-      <c r="C9">
-        <v>354</v>
-      </c>
-      <c r="D9">
-        <v>538</v>
-      </c>
-      <c r="E9">
-        <v>705</v>
-      </c>
-      <c r="F9">
-        <v>568</v>
-      </c>
-      <c r="G9">
-        <v>168</v>
-      </c>
-      <c r="H9">
-        <v>116</v>
-      </c>
-      <c r="I9">
-        <v>194</v>
-      </c>
-      <c r="J9">
-        <v>122</v>
-      </c>
-      <c r="K9">
-        <v>114</v>
-      </c>
-      <c r="L9">
-        <v>95</v>
-      </c>
-      <c r="M9">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13">
-      <c r="A10" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B10">
-        <v>282</v>
-      </c>
-      <c r="C10">
-        <v>416</v>
-      </c>
-      <c r="D10">
-        <v>617</v>
-      </c>
-      <c r="E10">
-        <v>797</v>
-      </c>
-      <c r="F10">
-        <v>660</v>
-      </c>
-      <c r="G10">
-        <v>257</v>
-      </c>
-      <c r="H10">
-        <v>236</v>
-      </c>
-      <c r="I10">
-        <v>324</v>
-      </c>
-      <c r="J10">
-        <v>255</v>
-      </c>
-      <c r="K10">
-        <v>207</v>
-      </c>
-      <c r="L10">
-        <v>196</v>
-      </c>
-      <c r="M10">
-        <v>92</v>
       </c>
     </row>
   </sheetData>
@@ -23245,31 +23217,31 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D2">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E2">
         <v>5</v>
       </c>
       <c r="F2">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="G2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I2">
         <v>4</v>
       </c>
       <c r="J2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K2">
         <v>7</v>
@@ -23278,7 +23250,7 @@
         <v>5</v>
       </c>
       <c r="M2">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -23286,40 +23258,40 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C3">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D3">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E3">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F3">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="G3">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="H3">
         <v>8</v>
       </c>
       <c r="I3">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="J3">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="K3">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="L3">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M3">
-        <v>11</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -23329,43 +23301,52 @@
       <c r="I4">
         <v>1</v>
       </c>
+      <c r="M4">
+        <v>2</v>
+      </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5">
-        <v>1</v>
-      </c>
-      <c r="D5">
-        <v>1</v>
-      </c>
-      <c r="E5">
-        <v>1</v>
-      </c>
-      <c r="J5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K5">
-        <v>2</v>
-      </c>
-      <c r="M5">
         <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="K6">
+        <v>5</v>
+      </c>
+      <c r="E6">
+        <v>1</v>
+      </c>
+      <c r="F6">
+        <v>2</v>
+      </c>
+      <c r="J6">
+        <v>2</v>
+      </c>
+      <c r="M6">
         <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
+      </c>
+      <c r="E7">
+        <v>1</v>
+      </c>
+      <c r="I7">
+        <v>1</v>
+      </c>
+      <c r="K7">
+        <v>1</v>
       </c>
       <c r="L7">
+        <v>1</v>
+      </c>
+      <c r="M7">
         <v>1</v>
       </c>
     </row>
@@ -23374,40 +23355,40 @@
         <v>8</v>
       </c>
       <c r="B8">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C8">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="D8">
+        <v>21</v>
+      </c>
+      <c r="E8">
         <v>22</v>
       </c>
-      <c r="E8">
-        <v>44</v>
-      </c>
       <c r="F8">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="G8">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="H8">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="I8">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="J8">
         <v>26</v>
       </c>
       <c r="K8">
-        <v>24</v>
+        <v>49</v>
       </c>
       <c r="L8">
-        <v>14</v>
+        <v>44</v>
       </c>
       <c r="M8">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -23415,40 +23396,40 @@
         <v>9</v>
       </c>
       <c r="B9">
+        <v>45</v>
+      </c>
+      <c r="C9">
+        <v>64</v>
+      </c>
+      <c r="D9">
         <v>46</v>
       </c>
-      <c r="C9">
-        <v>59</v>
-      </c>
-      <c r="D9">
-        <v>33</v>
-      </c>
       <c r="E9">
-        <v>73</v>
+        <v>50</v>
       </c>
       <c r="F9">
-        <v>114</v>
+        <v>38</v>
       </c>
       <c r="G9">
-        <v>58</v>
+        <v>19</v>
       </c>
       <c r="H9">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="I9">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="J9">
         <v>20</v>
       </c>
       <c r="K9">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="L9">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="M9">
-        <v>16</v>
+        <v>11</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -23456,40 +23437,40 @@
         <v>10</v>
       </c>
       <c r="B10">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C10">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="D10">
-        <v>65</v>
+        <v>82</v>
       </c>
       <c r="E10">
-        <v>130</v>
+        <v>88</v>
       </c>
       <c r="F10">
-        <v>167</v>
+        <v>91</v>
       </c>
       <c r="G10">
-        <v>92</v>
+        <v>47</v>
       </c>
       <c r="H10">
-        <v>104</v>
+        <v>66</v>
       </c>
       <c r="I10">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="J10">
         <v>67</v>
       </c>
       <c r="K10">
-        <v>71</v>
+        <v>110</v>
       </c>
       <c r="L10">
-        <v>61</v>
+        <v>98</v>
       </c>
       <c r="M10">
-        <v>52</v>
+        <v>40</v>
       </c>
     </row>
   </sheetData>
@@ -25280,10 +25261,10 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M7"/>
+  <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="1" max="1" width="18.7109375" customWidth="1"/>
     <col min="2" max="2" width="4.7109375" customWidth="1"/>
     <col min="3" max="3" width="4.7109375" customWidth="1"/>
     <col min="4" max="4" width="4.7109375" customWidth="1"/>
@@ -25344,7 +25325,7 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C2">
         <v>1</v>
@@ -25353,10 +25334,16 @@
         <v>1</v>
       </c>
       <c r="E2">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="F2">
+        <v>2</v>
+      </c>
+      <c r="G2">
+        <v>1</v>
       </c>
       <c r="H2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I2">
         <v>2</v>
@@ -25365,164 +25352,177 @@
         <v>1</v>
       </c>
       <c r="K2">
+        <v>1</v>
+      </c>
+      <c r="L2">
         <v>2</v>
       </c>
       <c r="M2">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
+      <c r="B3">
+        <v>2</v>
+      </c>
+      <c r="C3">
+        <v>4</v>
+      </c>
+      <c r="D3">
+        <v>5</v>
+      </c>
       <c r="E3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G3">
         <v>1</v>
       </c>
+      <c r="H3">
+        <v>6</v>
+      </c>
+      <c r="I3">
+        <v>2</v>
+      </c>
       <c r="J3">
         <v>2</v>
       </c>
+      <c r="K3">
+        <v>4</v>
+      </c>
       <c r="L3">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="M3">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B4">
-        <v>1</v>
+        <v>11</v>
+      </c>
+      <c r="C4">
+        <v>10</v>
+      </c>
+      <c r="D4">
+        <v>6</v>
+      </c>
+      <c r="E4">
+        <v>7</v>
+      </c>
+      <c r="F4">
+        <v>7</v>
+      </c>
+      <c r="G4">
+        <v>7</v>
+      </c>
+      <c r="H4">
+        <v>3</v>
+      </c>
+      <c r="I4">
+        <v>8</v>
+      </c>
+      <c r="J4">
+        <v>12</v>
       </c>
       <c r="K4">
-        <v>1</v>
+        <v>4</v>
+      </c>
+      <c r="L4">
+        <v>1</v>
+      </c>
+      <c r="M4">
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5">
+        <v>15</v>
+      </c>
+      <c r="C5">
+        <v>16</v>
+      </c>
+      <c r="D5">
+        <v>22</v>
+      </c>
+      <c r="E5">
+        <v>14</v>
+      </c>
+      <c r="F5">
+        <v>13</v>
+      </c>
+      <c r="G5">
+        <v>6</v>
+      </c>
+      <c r="H5">
+        <v>11</v>
+      </c>
+      <c r="I5">
+        <v>4</v>
+      </c>
+      <c r="J5">
+        <v>13</v>
+      </c>
+      <c r="K5">
         <v>8</v>
       </c>
-      <c r="B5">
-        <v>2</v>
-      </c>
-      <c r="C5">
-        <v>1</v>
-      </c>
-      <c r="D5">
-        <v>3</v>
-      </c>
-      <c r="E5">
-        <v>1</v>
-      </c>
-      <c r="F5">
-        <v>3</v>
-      </c>
-      <c r="G5">
-        <v>4</v>
-      </c>
-      <c r="H5">
-        <v>5</v>
-      </c>
-      <c r="I5">
-        <v>3</v>
-      </c>
-      <c r="J5">
-        <v>6</v>
-      </c>
-      <c r="K5">
-        <v>3</v>
-      </c>
       <c r="L5">
-        <v>3</v>
+        <v>7</v>
+      </c>
+      <c r="M5">
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B6">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="C6">
+        <v>31</v>
+      </c>
+      <c r="D6">
+        <v>34</v>
+      </c>
+      <c r="E6">
+        <v>25</v>
+      </c>
+      <c r="F6">
+        <v>25</v>
+      </c>
+      <c r="G6">
+        <v>15</v>
+      </c>
+      <c r="H6">
+        <v>22</v>
+      </c>
+      <c r="I6">
+        <v>16</v>
+      </c>
+      <c r="J6">
+        <v>28</v>
+      </c>
+      <c r="K6">
+        <v>17</v>
+      </c>
+      <c r="L6">
+        <v>16</v>
+      </c>
+      <c r="M6">
         <v>12</v>
-      </c>
-      <c r="D6">
-        <v>29</v>
-      </c>
-      <c r="E6">
-        <v>16</v>
-      </c>
-      <c r="F6">
-        <v>16</v>
-      </c>
-      <c r="G6">
-        <v>8</v>
-      </c>
-      <c r="H6">
-        <v>2</v>
-      </c>
-      <c r="I6">
-        <v>10</v>
-      </c>
-      <c r="J6">
-        <v>13</v>
-      </c>
-      <c r="K6">
-        <v>11</v>
-      </c>
-      <c r="L6">
-        <v>15</v>
-      </c>
-      <c r="M6">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
-      <c r="A7" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B7">
-        <v>15</v>
-      </c>
-      <c r="C7">
-        <v>14</v>
-      </c>
-      <c r="D7">
-        <v>33</v>
-      </c>
-      <c r="E7">
-        <v>21</v>
-      </c>
-      <c r="F7">
-        <v>21</v>
-      </c>
-      <c r="G7">
-        <v>13</v>
-      </c>
-      <c r="H7">
-        <v>8</v>
-      </c>
-      <c r="I7">
-        <v>15</v>
-      </c>
-      <c r="J7">
-        <v>22</v>
-      </c>
-      <c r="K7">
-        <v>17</v>
-      </c>
-      <c r="L7">
-        <v>20</v>
-      </c>
-      <c r="M7">
-        <v>11</v>
       </c>
     </row>
   </sheetData>

--- a/output/cta-index-crime-full-year.xlsx
+++ b/output/cta-index-crime-full-year.xlsx
@@ -9,31 +9,31 @@
   <sheets>
     <sheet name="Citywide Totals" sheetId="1" r:id="rId1"/>
     <sheet name="By Neighborhood" sheetId="2" r:id="rId2"/>
-    <sheet name="Englewood" sheetId="3" r:id="rId3"/>
-    <sheet name="Roseland" sheetId="4" r:id="rId4"/>
-    <sheet name="South Shore" sheetId="5" r:id="rId5"/>
-    <sheet name="Albany Park" sheetId="6" r:id="rId6"/>
-    <sheet name="Old Town" sheetId="7" r:id="rId7"/>
-    <sheet name="Loop" sheetId="8" r:id="rId8"/>
-    <sheet name="Lincoln Park" sheetId="9" r:id="rId9"/>
-    <sheet name="O'Hare" sheetId="10" r:id="rId10"/>
-    <sheet name="Near South Side" sheetId="11" r:id="rId11"/>
-    <sheet name="Logan Square" sheetId="12" r:id="rId12"/>
-    <sheet name="Grand Crossing" sheetId="13" r:id="rId13"/>
-    <sheet name="Austin" sheetId="14" r:id="rId14"/>
-    <sheet name="Avondale" sheetId="15" r:id="rId15"/>
-    <sheet name="Rush &amp; Division" sheetId="16" r:id="rId16"/>
-    <sheet name="Chatham" sheetId="17" r:id="rId17"/>
-    <sheet name="Oakland" sheetId="18" r:id="rId18"/>
-    <sheet name="River North" sheetId="19" r:id="rId19"/>
-    <sheet name="New City" sheetId="20" r:id="rId20"/>
-    <sheet name="Belmont Cragin" sheetId="21" r:id="rId21"/>
-    <sheet name="Woodlawn" sheetId="22" r:id="rId22"/>
-    <sheet name="West Loop" sheetId="23" r:id="rId23"/>
-    <sheet name="Printers Row" sheetId="24" r:id="rId24"/>
-    <sheet name="Uptown" sheetId="25" r:id="rId25"/>
-    <sheet name="Lake View" sheetId="26" r:id="rId26"/>
-    <sheet name="North Lawndale" sheetId="27" r:id="rId27"/>
+    <sheet name="Albany Park" sheetId="3" r:id="rId3"/>
+    <sheet name="Woodlawn" sheetId="4" r:id="rId4"/>
+    <sheet name="North Lawndale" sheetId="5" r:id="rId5"/>
+    <sheet name="Englewood" sheetId="6" r:id="rId6"/>
+    <sheet name="Roseland" sheetId="7" r:id="rId7"/>
+    <sheet name="South Shore" sheetId="8" r:id="rId8"/>
+    <sheet name="Old Town" sheetId="9" r:id="rId9"/>
+    <sheet name="Loop" sheetId="10" r:id="rId10"/>
+    <sheet name="Lincoln Park" sheetId="11" r:id="rId11"/>
+    <sheet name="O'Hare" sheetId="12" r:id="rId12"/>
+    <sheet name="Near South Side" sheetId="13" r:id="rId13"/>
+    <sheet name="Logan Square" sheetId="14" r:id="rId14"/>
+    <sheet name="Grand Crossing" sheetId="15" r:id="rId15"/>
+    <sheet name="Austin" sheetId="16" r:id="rId16"/>
+    <sheet name="Avondale" sheetId="17" r:id="rId17"/>
+    <sheet name="Rush &amp; Division" sheetId="18" r:id="rId18"/>
+    <sheet name="Chatham" sheetId="19" r:id="rId19"/>
+    <sheet name="Oakland" sheetId="20" r:id="rId20"/>
+    <sheet name="River North" sheetId="21" r:id="rId21"/>
+    <sheet name="New City" sheetId="22" r:id="rId22"/>
+    <sheet name="Belmont Cragin" sheetId="23" r:id="rId23"/>
+    <sheet name="West Loop" sheetId="24" r:id="rId24"/>
+    <sheet name="Printers Row" sheetId="25" r:id="rId25"/>
+    <sheet name="Uptown" sheetId="26" r:id="rId26"/>
+    <sheet name="Lake View" sheetId="27" r:id="rId27"/>
     <sheet name="Hyde Park" sheetId="28" r:id="rId28"/>
     <sheet name="Grand Boulevard" sheetId="29" r:id="rId29"/>
     <sheet name="West Town" sheetId="30" r:id="rId30"/>
@@ -905,7 +905,7 @@
         <v>137</v>
       </c>
       <c r="M2">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -1156,7 +1156,7 @@
         <v>467</v>
       </c>
       <c r="M9">
-        <v>192</v>
+        <v>194</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -1238,7 +1238,7 @@
         <v>1604</v>
       </c>
       <c r="M11">
-        <v>825</v>
+        <v>828</v>
       </c>
     </row>
   </sheetData>
@@ -1248,7 +1248,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M8"/>
+  <dimension ref="A1:M10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="23.7109375" customWidth="1"/>
@@ -1312,25 +1312,37 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>1</v>
+        <v>6</v>
+      </c>
+      <c r="C2">
+        <v>3</v>
       </c>
       <c r="D2">
-        <v>2</v>
+        <v>12</v>
+      </c>
+      <c r="E2">
+        <v>5</v>
       </c>
       <c r="F2">
-        <v>2</v>
+        <v>8</v>
+      </c>
+      <c r="G2">
+        <v>4</v>
+      </c>
+      <c r="H2">
+        <v>13</v>
       </c>
       <c r="I2">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="J2">
-        <v>2</v>
+        <v>22</v>
       </c>
       <c r="K2">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="L2">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="M2">
         <v>2</v>
@@ -1340,156 +1352,247 @@
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
+      <c r="B3">
+        <v>13</v>
+      </c>
       <c r="C3">
-        <v>1</v>
+        <v>13</v>
+      </c>
+      <c r="D3">
+        <v>17</v>
       </c>
       <c r="E3">
-        <v>1</v>
+        <v>18</v>
+      </c>
+      <c r="F3">
+        <v>14</v>
+      </c>
+      <c r="G3">
+        <v>26</v>
       </c>
       <c r="H3">
-        <v>2</v>
+        <v>23</v>
       </c>
       <c r="I3">
-        <v>1</v>
+        <v>32</v>
       </c>
       <c r="J3">
-        <v>1</v>
+        <v>40</v>
       </c>
       <c r="K3">
-        <v>2</v>
+        <v>26</v>
       </c>
       <c r="L3">
-        <v>2</v>
+        <v>34</v>
       </c>
       <c r="M3">
-        <v>5</v>
+        <v>17</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C4">
-        <v>1</v>
-      </c>
-      <c r="I4">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="G4">
+        <v>1</v>
+      </c>
+      <c r="J4">
+        <v>2</v>
       </c>
       <c r="K4">
+        <v>1</v>
+      </c>
+      <c r="L4">
+        <v>1</v>
+      </c>
+      <c r="M4">
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
+      </c>
+      <c r="C5">
+        <v>2</v>
+      </c>
+      <c r="D5">
+        <v>1</v>
+      </c>
+      <c r="E5">
+        <v>2</v>
+      </c>
+      <c r="F5">
+        <v>1</v>
+      </c>
+      <c r="H5">
+        <v>2</v>
+      </c>
+      <c r="I5">
+        <v>4</v>
+      </c>
+      <c r="J5">
+        <v>3</v>
+      </c>
+      <c r="K5">
+        <v>2</v>
       </c>
       <c r="L5">
-        <v>2</v>
+        <v>5</v>
+      </c>
+      <c r="M5">
+        <v>4</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B6">
-        <v>1</v>
-      </c>
-      <c r="F6">
-        <v>4</v>
+        <v>6</v>
+      </c>
+      <c r="G6">
+        <v>1</v>
       </c>
       <c r="H6">
-        <v>1</v>
-      </c>
-      <c r="I6">
-        <v>2</v>
-      </c>
-      <c r="K6">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="J6">
+        <v>2</v>
+      </c>
+      <c r="L6">
+        <v>2</v>
       </c>
       <c r="M6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B7">
-        <v>10</v>
-      </c>
-      <c r="C7">
-        <v>20</v>
-      </c>
-      <c r="D7">
-        <v>25</v>
-      </c>
-      <c r="E7">
-        <v>30</v>
-      </c>
-      <c r="F7">
-        <v>41</v>
-      </c>
-      <c r="G7">
-        <v>10</v>
-      </c>
-      <c r="H7">
-        <v>5</v>
-      </c>
-      <c r="I7">
-        <v>5</v>
-      </c>
-      <c r="J7">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="K7">
-        <v>17</v>
-      </c>
-      <c r="L7">
-        <v>12</v>
-      </c>
-      <c r="M7">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:13">
       <c r="A8" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8">
+        <v>30</v>
+      </c>
+      <c r="C8">
+        <v>44</v>
+      </c>
+      <c r="D8">
+        <v>49</v>
+      </c>
+      <c r="E8">
+        <v>67</v>
+      </c>
+      <c r="F8">
+        <v>69</v>
+      </c>
+      <c r="G8">
+        <v>57</v>
+      </c>
+      <c r="H8">
+        <v>80</v>
+      </c>
+      <c r="I8">
+        <v>80</v>
+      </c>
+      <c r="J8">
+        <v>64</v>
+      </c>
+      <c r="K8">
+        <v>48</v>
+      </c>
+      <c r="L8">
+        <v>44</v>
+      </c>
+      <c r="M8">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13">
+      <c r="A9" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B9">
+        <v>233</v>
+      </c>
+      <c r="C9">
+        <v>354</v>
+      </c>
+      <c r="D9">
+        <v>538</v>
+      </c>
+      <c r="E9">
+        <v>705</v>
+      </c>
+      <c r="F9">
+        <v>568</v>
+      </c>
+      <c r="G9">
+        <v>168</v>
+      </c>
+      <c r="H9">
+        <v>116</v>
+      </c>
+      <c r="I9">
+        <v>194</v>
+      </c>
+      <c r="J9">
+        <v>122</v>
+      </c>
+      <c r="K9">
+        <v>114</v>
+      </c>
+      <c r="L9">
+        <v>95</v>
+      </c>
+      <c r="M9">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13">
+      <c r="A10" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B8">
-        <v>12</v>
-      </c>
-      <c r="C8">
-        <v>22</v>
-      </c>
-      <c r="D8">
-        <v>27</v>
-      </c>
-      <c r="E8">
-        <v>31</v>
-      </c>
-      <c r="F8">
-        <v>47</v>
-      </c>
-      <c r="G8">
-        <v>10</v>
-      </c>
-      <c r="H8">
-        <v>8</v>
-      </c>
-      <c r="I8">
-        <v>12</v>
-      </c>
-      <c r="J8">
-        <v>18</v>
-      </c>
-      <c r="K8">
-        <v>22</v>
-      </c>
-      <c r="L8">
-        <v>21</v>
-      </c>
-      <c r="M8">
-        <v>17</v>
+      <c r="B10">
+        <v>282</v>
+      </c>
+      <c r="C10">
+        <v>416</v>
+      </c>
+      <c r="D10">
+        <v>617</v>
+      </c>
+      <c r="E10">
+        <v>797</v>
+      </c>
+      <c r="F10">
+        <v>660</v>
+      </c>
+      <c r="G10">
+        <v>257</v>
+      </c>
+      <c r="H10">
+        <v>236</v>
+      </c>
+      <c r="I10">
+        <v>324</v>
+      </c>
+      <c r="J10">
+        <v>255</v>
+      </c>
+      <c r="K10">
+        <v>207</v>
+      </c>
+      <c r="L10">
+        <v>196</v>
+      </c>
+      <c r="M10">
+        <v>93</v>
       </c>
     </row>
   </sheetData>
@@ -1499,7 +1602,7 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M8"/>
+  <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="23.7109375" customWidth="1"/>
@@ -1562,25 +1665,22 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="F2">
-        <v>1</v>
-      </c>
-      <c r="G2">
-        <v>2</v>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
       </c>
       <c r="H2">
         <v>1</v>
       </c>
-      <c r="I2">
-        <v>2</v>
-      </c>
       <c r="J2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K2">
-        <v>3</v>
-      </c>
-      <c r="M2">
+        <v>1</v>
+      </c>
+      <c r="L2">
         <v>2</v>
       </c>
     </row>
@@ -1588,83 +1688,101 @@
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B3">
-        <v>1</v>
-      </c>
-      <c r="C3">
-        <v>1</v>
-      </c>
-      <c r="D3">
-        <v>1</v>
-      </c>
-      <c r="E3">
-        <v>2</v>
+      <c r="F3">
+        <v>1</v>
       </c>
       <c r="G3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H3">
         <v>2</v>
       </c>
       <c r="I3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J3">
         <v>1</v>
       </c>
       <c r="K3">
-        <v>1</v>
-      </c>
-      <c r="M3">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="L3">
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="J4">
+      <c r="B4">
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5">
+        <v>1</v>
+      </c>
+      <c r="C5">
+        <v>3</v>
+      </c>
+      <c r="D5">
+        <v>1</v>
+      </c>
+      <c r="E5">
         <v>6</v>
       </c>
-      <c r="K5">
+      <c r="F5">
+        <v>2</v>
+      </c>
+      <c r="G5">
+        <v>1</v>
+      </c>
+      <c r="H5">
+        <v>2</v>
+      </c>
+      <c r="I5">
+        <v>2</v>
+      </c>
+      <c r="J5">
+        <v>3</v>
+      </c>
+      <c r="M5">
         <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B6">
+        <v>13</v>
+      </c>
+      <c r="C6">
+        <v>15</v>
+      </c>
+      <c r="D6">
+        <v>13</v>
+      </c>
+      <c r="E6">
+        <v>9</v>
+      </c>
+      <c r="F6">
+        <v>14</v>
+      </c>
+      <c r="G6">
         <v>6</v>
       </c>
-      <c r="C6">
-        <v>2</v>
-      </c>
-      <c r="D6">
-        <v>5</v>
-      </c>
-      <c r="E6">
-        <v>5</v>
-      </c>
-      <c r="F6">
-        <v>4</v>
-      </c>
-      <c r="G6">
-        <v>4</v>
-      </c>
       <c r="H6">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="I6">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J6">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K6">
         <v>3</v>
@@ -1673,89 +1791,48 @@
         <v>4</v>
       </c>
       <c r="M6">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B7">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="C7">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="D7">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="E7">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="F7">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="G7">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H7">
+        <v>7</v>
+      </c>
+      <c r="I7">
+        <v>12</v>
+      </c>
+      <c r="J7">
+        <v>10</v>
+      </c>
+      <c r="K7">
         <v>6</v>
       </c>
-      <c r="I7">
-        <v>14</v>
-      </c>
-      <c r="J7">
-        <v>11</v>
-      </c>
-      <c r="K7">
-        <v>12</v>
-      </c>
       <c r="L7">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="M7">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13">
-      <c r="A8" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B8">
-        <v>29</v>
-      </c>
-      <c r="C8">
-        <v>30</v>
-      </c>
-      <c r="D8">
-        <v>29</v>
-      </c>
-      <c r="E8">
-        <v>26</v>
-      </c>
-      <c r="F8">
-        <v>28</v>
-      </c>
-      <c r="G8">
-        <v>17</v>
-      </c>
-      <c r="H8">
-        <v>15</v>
-      </c>
-      <c r="I8">
-        <v>27</v>
-      </c>
-      <c r="J8">
-        <v>19</v>
-      </c>
-      <c r="K8">
-        <v>20</v>
-      </c>
-      <c r="L8">
-        <v>14</v>
-      </c>
-      <c r="M8">
-        <v>12</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -1828,29 +1905,29 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C2">
+      <c r="B2">
         <v>1</v>
       </c>
       <c r="D2">
         <v>2</v>
       </c>
-      <c r="G2">
-        <v>4</v>
-      </c>
-      <c r="H2">
-        <v>1</v>
+      <c r="F2">
+        <v>2</v>
       </c>
       <c r="I2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L2">
         <v>5</v>
+      </c>
+      <c r="M2">
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -1860,54 +1937,48 @@
       <c r="C3">
         <v>1</v>
       </c>
-      <c r="D3">
-        <v>1</v>
-      </c>
       <c r="E3">
         <v>1</v>
       </c>
       <c r="H3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I3">
         <v>1</v>
       </c>
       <c r="J3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L3">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="M3">
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D4">
-        <v>1</v>
-      </c>
-      <c r="E4">
-        <v>1</v>
-      </c>
-      <c r="J4">
-        <v>1</v>
-      </c>
-      <c r="L4">
+      <c r="C4">
+        <v>1</v>
+      </c>
+      <c r="I4">
+        <v>1</v>
+      </c>
+      <c r="K4">
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C5">
-        <v>1</v>
-      </c>
-      <c r="J5">
-        <v>1</v>
+        <v>6</v>
+      </c>
+      <c r="L5">
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -1915,40 +1986,22 @@
         <v>8</v>
       </c>
       <c r="B6">
-        <v>2</v>
-      </c>
-      <c r="C6">
-        <v>5</v>
-      </c>
-      <c r="D6">
-        <v>3</v>
-      </c>
-      <c r="E6">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F6">
-        <v>5</v>
-      </c>
-      <c r="G6">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H6">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="I6">
-        <v>5</v>
-      </c>
-      <c r="J6">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="K6">
-        <v>7</v>
-      </c>
-      <c r="L6">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="M6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -1956,40 +2009,40 @@
         <v>9</v>
       </c>
       <c r="B7">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C7">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="D7">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="E7">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F7">
-        <v>18</v>
+        <v>41</v>
       </c>
       <c r="G7">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="H7">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="I7">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="J7">
         <v>15</v>
       </c>
       <c r="K7">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="L7">
         <v>12</v>
       </c>
       <c r="M7">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -1997,40 +2050,40 @@
         <v>10</v>
       </c>
       <c r="B8">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="C8">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="D8">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="E8">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="F8">
-        <v>23</v>
+        <v>47</v>
       </c>
       <c r="G8">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="H8">
+        <v>8</v>
+      </c>
+      <c r="I8">
+        <v>12</v>
+      </c>
+      <c r="J8">
         <v>18</v>
       </c>
-      <c r="I8">
-        <v>23</v>
-      </c>
-      <c r="J8">
-        <v>31</v>
-      </c>
       <c r="K8">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="L8">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="M8">
-        <v>8</v>
+        <v>17</v>
       </c>
     </row>
   </sheetData>
@@ -2039,6 +2092,547 @@
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:M8"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+    <col min="13" max="13" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="M1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="F2">
+        <v>1</v>
+      </c>
+      <c r="G2">
+        <v>2</v>
+      </c>
+      <c r="H2">
+        <v>1</v>
+      </c>
+      <c r="I2">
+        <v>2</v>
+      </c>
+      <c r="J2">
+        <v>2</v>
+      </c>
+      <c r="K2">
+        <v>3</v>
+      </c>
+      <c r="M2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>1</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
+      <c r="E3">
+        <v>2</v>
+      </c>
+      <c r="G3">
+        <v>2</v>
+      </c>
+      <c r="H3">
+        <v>2</v>
+      </c>
+      <c r="I3">
+        <v>3</v>
+      </c>
+      <c r="J3">
+        <v>1</v>
+      </c>
+      <c r="K3">
+        <v>1</v>
+      </c>
+      <c r="M3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="J4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="K5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6">
+        <v>6</v>
+      </c>
+      <c r="C6">
+        <v>2</v>
+      </c>
+      <c r="D6">
+        <v>5</v>
+      </c>
+      <c r="E6">
+        <v>5</v>
+      </c>
+      <c r="F6">
+        <v>4</v>
+      </c>
+      <c r="G6">
+        <v>4</v>
+      </c>
+      <c r="H6">
+        <v>6</v>
+      </c>
+      <c r="I6">
+        <v>8</v>
+      </c>
+      <c r="J6">
+        <v>4</v>
+      </c>
+      <c r="K6">
+        <v>3</v>
+      </c>
+      <c r="L6">
+        <v>4</v>
+      </c>
+      <c r="M6">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7">
+        <v>22</v>
+      </c>
+      <c r="C7">
+        <v>27</v>
+      </c>
+      <c r="D7">
+        <v>23</v>
+      </c>
+      <c r="E7">
+        <v>19</v>
+      </c>
+      <c r="F7">
+        <v>23</v>
+      </c>
+      <c r="G7">
+        <v>9</v>
+      </c>
+      <c r="H7">
+        <v>6</v>
+      </c>
+      <c r="I7">
+        <v>14</v>
+      </c>
+      <c r="J7">
+        <v>11</v>
+      </c>
+      <c r="K7">
+        <v>12</v>
+      </c>
+      <c r="L7">
+        <v>10</v>
+      </c>
+      <c r="M7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13">
+      <c r="A8" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B8">
+        <v>29</v>
+      </c>
+      <c r="C8">
+        <v>30</v>
+      </c>
+      <c r="D8">
+        <v>29</v>
+      </c>
+      <c r="E8">
+        <v>26</v>
+      </c>
+      <c r="F8">
+        <v>28</v>
+      </c>
+      <c r="G8">
+        <v>17</v>
+      </c>
+      <c r="H8">
+        <v>15</v>
+      </c>
+      <c r="I8">
+        <v>27</v>
+      </c>
+      <c r="J8">
+        <v>19</v>
+      </c>
+      <c r="K8">
+        <v>20</v>
+      </c>
+      <c r="L8">
+        <v>14</v>
+      </c>
+      <c r="M8">
+        <v>12</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:M8"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+    <col min="13" max="13" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="M1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>2</v>
+      </c>
+      <c r="G2">
+        <v>4</v>
+      </c>
+      <c r="H2">
+        <v>1</v>
+      </c>
+      <c r="I2">
+        <v>1</v>
+      </c>
+      <c r="J2">
+        <v>3</v>
+      </c>
+      <c r="K2">
+        <v>2</v>
+      </c>
+      <c r="L2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
+      <c r="E3">
+        <v>1</v>
+      </c>
+      <c r="H3">
+        <v>1</v>
+      </c>
+      <c r="I3">
+        <v>1</v>
+      </c>
+      <c r="J3">
+        <v>3</v>
+      </c>
+      <c r="K3">
+        <v>1</v>
+      </c>
+      <c r="L3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D4">
+        <v>1</v>
+      </c>
+      <c r="E4">
+        <v>1</v>
+      </c>
+      <c r="J4">
+        <v>1</v>
+      </c>
+      <c r="L4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5">
+        <v>1</v>
+      </c>
+      <c r="J5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6">
+        <v>2</v>
+      </c>
+      <c r="C6">
+        <v>5</v>
+      </c>
+      <c r="D6">
+        <v>3</v>
+      </c>
+      <c r="E6">
+        <v>4</v>
+      </c>
+      <c r="F6">
+        <v>5</v>
+      </c>
+      <c r="G6">
+        <v>5</v>
+      </c>
+      <c r="H6">
+        <v>8</v>
+      </c>
+      <c r="I6">
+        <v>5</v>
+      </c>
+      <c r="J6">
+        <v>8</v>
+      </c>
+      <c r="K6">
+        <v>7</v>
+      </c>
+      <c r="L6">
+        <v>7</v>
+      </c>
+      <c r="M6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7">
+        <v>17</v>
+      </c>
+      <c r="C7">
+        <v>24</v>
+      </c>
+      <c r="D7">
+        <v>35</v>
+      </c>
+      <c r="E7">
+        <v>31</v>
+      </c>
+      <c r="F7">
+        <v>18</v>
+      </c>
+      <c r="G7">
+        <v>17</v>
+      </c>
+      <c r="H7">
+        <v>8</v>
+      </c>
+      <c r="I7">
+        <v>16</v>
+      </c>
+      <c r="J7">
+        <v>15</v>
+      </c>
+      <c r="K7">
+        <v>10</v>
+      </c>
+      <c r="L7">
+        <v>12</v>
+      </c>
+      <c r="M7">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13">
+      <c r="A8" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B8">
+        <v>19</v>
+      </c>
+      <c r="C8">
+        <v>32</v>
+      </c>
+      <c r="D8">
+        <v>42</v>
+      </c>
+      <c r="E8">
+        <v>37</v>
+      </c>
+      <c r="F8">
+        <v>23</v>
+      </c>
+      <c r="G8">
+        <v>26</v>
+      </c>
+      <c r="H8">
+        <v>18</v>
+      </c>
+      <c r="I8">
+        <v>23</v>
+      </c>
+      <c r="J8">
+        <v>31</v>
+      </c>
+      <c r="K8">
+        <v>20</v>
+      </c>
+      <c r="L8">
+        <v>26</v>
+      </c>
+      <c r="M8">
+        <v>8</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M10"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -2365,7 +2959,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M10"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -2683,7 +3277,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -2935,7 +3529,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -3193,7 +3787,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M10"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -3501,431 +4095,6 @@
       </c>
       <c r="M10">
         <v>20</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K6"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="18.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:11">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="G2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="E3">
-        <v>1</v>
-      </c>
-      <c r="F3">
-        <v>2</v>
-      </c>
-      <c r="G3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11">
-      <c r="A4" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C4">
-        <v>1</v>
-      </c>
-      <c r="F4">
-        <v>1</v>
-      </c>
-      <c r="K4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11">
-      <c r="A5" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B5">
-        <v>1</v>
-      </c>
-      <c r="C5">
-        <v>1</v>
-      </c>
-      <c r="D5">
-        <v>1</v>
-      </c>
-      <c r="E5">
-        <v>1</v>
-      </c>
-      <c r="F5">
-        <v>3</v>
-      </c>
-      <c r="H5">
-        <v>1</v>
-      </c>
-      <c r="I5">
-        <v>1</v>
-      </c>
-      <c r="J5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11">
-      <c r="A6" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B6">
-        <v>1</v>
-      </c>
-      <c r="C6">
-        <v>2</v>
-      </c>
-      <c r="D6">
-        <v>1</v>
-      </c>
-      <c r="E6">
-        <v>2</v>
-      </c>
-      <c r="F6">
-        <v>6</v>
-      </c>
-      <c r="G6">
-        <v>3</v>
-      </c>
-      <c r="H6">
-        <v>1</v>
-      </c>
-      <c r="I6">
-        <v>1</v>
-      </c>
-      <c r="J6">
-        <v>1</v>
-      </c>
-      <c r="K6">
-        <v>2</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M7"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" customWidth="1"/>
-    <col min="13" max="13" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="M1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2">
-        <v>1</v>
-      </c>
-      <c r="D2">
-        <v>1</v>
-      </c>
-      <c r="E2">
-        <v>1</v>
-      </c>
-      <c r="F2">
-        <v>1</v>
-      </c>
-      <c r="H2">
-        <v>2</v>
-      </c>
-      <c r="I2">
-        <v>4</v>
-      </c>
-      <c r="J2">
-        <v>3</v>
-      </c>
-      <c r="K2">
-        <v>2</v>
-      </c>
-      <c r="M2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C3">
-        <v>3</v>
-      </c>
-      <c r="D3">
-        <v>4</v>
-      </c>
-      <c r="E3">
-        <v>1</v>
-      </c>
-      <c r="G3">
-        <v>1</v>
-      </c>
-      <c r="H3">
-        <v>2</v>
-      </c>
-      <c r="I3">
-        <v>3</v>
-      </c>
-      <c r="J3">
-        <v>5</v>
-      </c>
-      <c r="K3">
-        <v>4</v>
-      </c>
-      <c r="L3">
-        <v>8</v>
-      </c>
-      <c r="M3">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G4">
-        <v>1</v>
-      </c>
-      <c r="J4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5">
-        <v>3</v>
-      </c>
-      <c r="C5">
-        <v>3</v>
-      </c>
-      <c r="D5">
-        <v>7</v>
-      </c>
-      <c r="E5">
-        <v>5</v>
-      </c>
-      <c r="F5">
-        <v>12</v>
-      </c>
-      <c r="G5">
-        <v>13</v>
-      </c>
-      <c r="H5">
-        <v>11</v>
-      </c>
-      <c r="I5">
-        <v>14</v>
-      </c>
-      <c r="J5">
-        <v>12</v>
-      </c>
-      <c r="K5">
-        <v>9</v>
-      </c>
-      <c r="L5">
-        <v>6</v>
-      </c>
-      <c r="M5">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B6">
-        <v>47</v>
-      </c>
-      <c r="C6">
-        <v>37</v>
-      </c>
-      <c r="D6">
-        <v>85</v>
-      </c>
-      <c r="E6">
-        <v>75</v>
-      </c>
-      <c r="F6">
-        <v>80</v>
-      </c>
-      <c r="G6">
-        <v>22</v>
-      </c>
-      <c r="H6">
-        <v>6</v>
-      </c>
-      <c r="I6">
-        <v>26</v>
-      </c>
-      <c r="J6">
-        <v>12</v>
-      </c>
-      <c r="K6">
-        <v>19</v>
-      </c>
-      <c r="L6">
-        <v>11</v>
-      </c>
-      <c r="M6">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
-      <c r="A7" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B7">
-        <v>50</v>
-      </c>
-      <c r="C7">
-        <v>44</v>
-      </c>
-      <c r="D7">
-        <v>97</v>
-      </c>
-      <c r="E7">
-        <v>82</v>
-      </c>
-      <c r="F7">
-        <v>93</v>
-      </c>
-      <c r="G7">
-        <v>37</v>
-      </c>
-      <c r="H7">
-        <v>21</v>
-      </c>
-      <c r="I7">
-        <v>47</v>
-      </c>
-      <c r="J7">
-        <v>33</v>
-      </c>
-      <c r="K7">
-        <v>34</v>
-      </c>
-      <c r="L7">
-        <v>25</v>
-      </c>
-      <c r="M7">
-        <v>19</v>
       </c>
     </row>
   </sheetData>
@@ -4032,7 +4201,7 @@
         <v>6</v>
       </c>
       <c r="M2">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -6387,7 +6556,7 @@
         <v>25</v>
       </c>
       <c r="M65">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="66" spans="1:13">
@@ -7639,7 +7808,7 @@
         <v>6</v>
       </c>
       <c r="M97">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="98" spans="1:13">
@@ -7721,7 +7890,7 @@
         <v>1604</v>
       </c>
       <c r="M99">
-        <v>825</v>
+        <v>828</v>
       </c>
     </row>
   </sheetData>
@@ -7831,7 +8000,7 @@
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:K6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="18.7109375" customWidth="1"/>
@@ -7845,214 +8014,140 @@
     <col min="9" max="9" width="4.7109375" customWidth="1"/>
     <col min="10" max="10" width="4.7109375" customWidth="1"/>
     <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" customWidth="1"/>
-    <col min="13" max="13" width="4.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1">
-        <v>2015</v>
+        <v>2016</v>
       </c>
       <c r="C1" s="1">
-        <v>2016</v>
+        <v>2017</v>
       </c>
       <c r="D1" s="1">
-        <v>2017</v>
+        <v>2018</v>
       </c>
       <c r="E1" s="1">
-        <v>2018</v>
+        <v>2019</v>
       </c>
       <c r="F1" s="1">
-        <v>2019</v>
+        <v>2020</v>
       </c>
       <c r="G1" s="1">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="H1" s="1">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="I1" s="1">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="J1" s="1">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="K1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="M1" s="1">
         <v>2026</v>
       </c>
     </row>
-    <row r="2" spans="1:13">
+    <row r="2" spans="1:11">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2">
-        <v>1</v>
-      </c>
-      <c r="C2">
-        <v>1</v>
-      </c>
-      <c r="D2">
-        <v>2</v>
-      </c>
-      <c r="H2">
-        <v>2</v>
-      </c>
-      <c r="I2">
-        <v>1</v>
-      </c>
-      <c r="K2">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
+      <c r="G2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B3">
-        <v>1</v>
-      </c>
-      <c r="D3">
-        <v>2</v>
-      </c>
       <c r="E3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F3">
-        <v>1</v>
-      </c>
-      <c r="I3">
-        <v>2</v>
-      </c>
-      <c r="J3">
-        <v>4</v>
-      </c>
-      <c r="K3">
-        <v>5</v>
-      </c>
-      <c r="L3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
+        <v>2</v>
+      </c>
+      <c r="G3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11">
       <c r="A4" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B4">
-        <v>6</v>
-      </c>
       <c r="C4">
-        <v>6</v>
-      </c>
-      <c r="D4">
-        <v>1</v>
-      </c>
-      <c r="E4">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F4">
-        <v>4</v>
-      </c>
-      <c r="I4">
-        <v>1</v>
-      </c>
-      <c r="J4">
         <v>1</v>
       </c>
       <c r="K4">
         <v>2</v>
       </c>
-      <c r="M4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
+    </row>
+    <row r="5" spans="1:11">
       <c r="A5" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B5">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="C5">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D5">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E5">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="F5">
-        <v>8</v>
-      </c>
-      <c r="G5">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J5">
         <v>1</v>
       </c>
-      <c r="K5">
-        <v>2</v>
-      </c>
-      <c r="L5">
-        <v>2</v>
-      </c>
-      <c r="M5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
+    </row>
+    <row r="6" spans="1:11">
       <c r="A6" s="1" t="s">
         <v>10</v>
       </c>
       <c r="B6">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="C6">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="D6">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E6">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="F6">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="G6">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H6">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I6">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="J6">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="K6">
-        <v>12</v>
-      </c>
-      <c r="L6">
-        <v>4</v>
-      </c>
-      <c r="M6">
         <v>2</v>
       </c>
     </row>
@@ -8126,11 +8221,29 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
       <c r="D2">
         <v>1</v>
       </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
+      <c r="F2">
+        <v>1</v>
+      </c>
+      <c r="H2">
+        <v>2</v>
+      </c>
+      <c r="I2">
+        <v>4</v>
+      </c>
       <c r="J2">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="K2">
+        <v>2</v>
       </c>
       <c r="M2">
         <v>1</v>
@@ -8140,24 +8253,45 @@
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
+      <c r="C3">
+        <v>3</v>
+      </c>
+      <c r="D3">
+        <v>4</v>
+      </c>
       <c r="E3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G3">
         <v>1</v>
       </c>
+      <c r="H3">
+        <v>2</v>
+      </c>
+      <c r="I3">
+        <v>3</v>
+      </c>
       <c r="J3">
-        <v>1</v>
+        <v>5</v>
+      </c>
+      <c r="K3">
+        <v>4</v>
       </c>
       <c r="L3">
-        <v>1</v>
+        <v>8</v>
+      </c>
+      <c r="M3">
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C4">
+      <c r="G4">
+        <v>1</v>
+      </c>
+      <c r="J4">
         <v>1</v>
       </c>
     </row>
@@ -8166,25 +8300,40 @@
         <v>8</v>
       </c>
       <c r="B5">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C5">
+        <v>3</v>
+      </c>
+      <c r="D5">
+        <v>7</v>
+      </c>
+      <c r="E5">
+        <v>5</v>
+      </c>
+      <c r="F5">
+        <v>12</v>
+      </c>
+      <c r="G5">
+        <v>13</v>
+      </c>
+      <c r="H5">
+        <v>11</v>
+      </c>
+      <c r="I5">
+        <v>14</v>
+      </c>
+      <c r="J5">
+        <v>12</v>
+      </c>
+      <c r="K5">
+        <v>9</v>
+      </c>
+      <c r="L5">
         <v>6</v>
       </c>
-      <c r="E5">
-        <v>1</v>
-      </c>
-      <c r="H5">
-        <v>2</v>
-      </c>
-      <c r="J5">
-        <v>4</v>
-      </c>
-      <c r="K5">
-        <v>2</v>
-      </c>
       <c r="M5">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -8192,40 +8341,40 @@
         <v>9</v>
       </c>
       <c r="B6">
+        <v>47</v>
+      </c>
+      <c r="C6">
+        <v>37</v>
+      </c>
+      <c r="D6">
+        <v>85</v>
+      </c>
+      <c r="E6">
+        <v>75</v>
+      </c>
+      <c r="F6">
+        <v>80</v>
+      </c>
+      <c r="G6">
+        <v>22</v>
+      </c>
+      <c r="H6">
         <v>6</v>
       </c>
-      <c r="C6">
-        <v>2</v>
-      </c>
-      <c r="D6">
-        <v>6</v>
-      </c>
-      <c r="E6">
-        <v>8</v>
-      </c>
-      <c r="F6">
-        <v>7</v>
-      </c>
-      <c r="G6">
-        <v>2</v>
-      </c>
-      <c r="H6">
-        <v>1</v>
-      </c>
       <c r="I6">
-        <v>1</v>
+        <v>26</v>
       </c>
       <c r="J6">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="K6">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="L6">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="M6">
-        <v>1</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -8233,40 +8382,40 @@
         <v>10</v>
       </c>
       <c r="B7">
-        <v>11</v>
+        <v>50</v>
       </c>
       <c r="C7">
-        <v>9</v>
+        <v>44</v>
       </c>
       <c r="D7">
-        <v>7</v>
+        <v>97</v>
       </c>
       <c r="E7">
-        <v>11</v>
+        <v>82</v>
       </c>
       <c r="F7">
-        <v>7</v>
+        <v>93</v>
       </c>
       <c r="G7">
-        <v>3</v>
+        <v>37</v>
       </c>
       <c r="H7">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="I7">
-        <v>1</v>
+        <v>47</v>
       </c>
       <c r="J7">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="K7">
-        <v>3</v>
+        <v>34</v>
       </c>
       <c r="L7">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="M7">
-        <v>3</v>
+        <v>19</v>
       </c>
     </row>
   </sheetData>
@@ -8275,6 +8424,238 @@
 </file>
 
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:M6"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="18.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+    <col min="13" max="13" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="M1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>2</v>
+      </c>
+      <c r="H2">
+        <v>2</v>
+      </c>
+      <c r="I2">
+        <v>1</v>
+      </c>
+      <c r="K2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>1</v>
+      </c>
+      <c r="D3">
+        <v>2</v>
+      </c>
+      <c r="E3">
+        <v>2</v>
+      </c>
+      <c r="F3">
+        <v>1</v>
+      </c>
+      <c r="I3">
+        <v>2</v>
+      </c>
+      <c r="J3">
+        <v>4</v>
+      </c>
+      <c r="K3">
+        <v>5</v>
+      </c>
+      <c r="L3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4">
+        <v>6</v>
+      </c>
+      <c r="C4">
+        <v>6</v>
+      </c>
+      <c r="D4">
+        <v>1</v>
+      </c>
+      <c r="E4">
+        <v>4</v>
+      </c>
+      <c r="F4">
+        <v>4</v>
+      </c>
+      <c r="I4">
+        <v>1</v>
+      </c>
+      <c r="J4">
+        <v>1</v>
+      </c>
+      <c r="K4">
+        <v>2</v>
+      </c>
+      <c r="M4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5">
+        <v>9</v>
+      </c>
+      <c r="C5">
+        <v>5</v>
+      </c>
+      <c r="D5">
+        <v>5</v>
+      </c>
+      <c r="E5">
+        <v>7</v>
+      </c>
+      <c r="F5">
+        <v>8</v>
+      </c>
+      <c r="G5">
+        <v>6</v>
+      </c>
+      <c r="H5">
+        <v>2</v>
+      </c>
+      <c r="I5">
+        <v>4</v>
+      </c>
+      <c r="J5">
+        <v>1</v>
+      </c>
+      <c r="K5">
+        <v>2</v>
+      </c>
+      <c r="L5">
+        <v>2</v>
+      </c>
+      <c r="M5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6">
+        <v>17</v>
+      </c>
+      <c r="C6">
+        <v>12</v>
+      </c>
+      <c r="D6">
+        <v>10</v>
+      </c>
+      <c r="E6">
+        <v>13</v>
+      </c>
+      <c r="F6">
+        <v>13</v>
+      </c>
+      <c r="G6">
+        <v>6</v>
+      </c>
+      <c r="H6">
+        <v>4</v>
+      </c>
+      <c r="I6">
+        <v>8</v>
+      </c>
+      <c r="J6">
+        <v>6</v>
+      </c>
+      <c r="K6">
+        <v>12</v>
+      </c>
+      <c r="L6">
+        <v>4</v>
+      </c>
+      <c r="M6">
+        <v>2</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -8339,22 +8720,13 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2">
-        <v>3</v>
-      </c>
-      <c r="E2">
-        <v>2</v>
-      </c>
-      <c r="F2">
-        <v>1</v>
-      </c>
-      <c r="G2">
-        <v>2</v>
-      </c>
-      <c r="I2">
-        <v>2</v>
-      </c>
-      <c r="L2">
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="J2">
+        <v>1</v>
+      </c>
+      <c r="M2">
         <v>1</v>
       </c>
     </row>
@@ -8362,45 +8734,24 @@
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B3">
-        <v>2</v>
-      </c>
-      <c r="C3">
-        <v>1</v>
-      </c>
-      <c r="D3">
-        <v>5</v>
-      </c>
-      <c r="F3">
+      <c r="E3">
         <v>2</v>
       </c>
       <c r="G3">
-        <v>3</v>
-      </c>
-      <c r="H3">
-        <v>3</v>
-      </c>
-      <c r="I3">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J3">
-        <v>5</v>
-      </c>
-      <c r="K3">
-        <v>5</v>
-      </c>
-      <c r="M3">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="L3">
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F4">
-        <v>1</v>
-      </c>
-      <c r="H4">
+      <c r="C4">
         <v>1</v>
       </c>
     </row>
@@ -8409,37 +8760,22 @@
         <v>8</v>
       </c>
       <c r="B5">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="C5">
-        <v>12</v>
-      </c>
-      <c r="D5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E5">
-        <v>9</v>
-      </c>
-      <c r="F5">
-        <v>3</v>
-      </c>
-      <c r="G5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H5">
-        <v>4</v>
-      </c>
-      <c r="I5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J5">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K5">
-        <v>7</v>
-      </c>
-      <c r="L5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M5">
         <v>1</v>
@@ -8450,40 +8786,40 @@
         <v>9</v>
       </c>
       <c r="B6">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="C6">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D6">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="E6">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F6">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="G6">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H6">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I6">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="J6">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="K6">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M6">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -8491,40 +8827,40 @@
         <v>10</v>
       </c>
       <c r="B7">
-        <v>33</v>
+        <v>11</v>
       </c>
       <c r="C7">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="D7">
-        <v>27</v>
+        <v>7</v>
       </c>
       <c r="E7">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="F7">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="G7">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="H7">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="I7">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="J7">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="K7">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="L7">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="M7">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -8532,7 +8868,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M9"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -8818,7 +9154,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -9047,7 +9383,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M9"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -9332,302 +9668,6 @@
       </c>
       <c r="M9">
         <v>15</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M8"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" customWidth="1"/>
-    <col min="13" max="13" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="M1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2">
-        <v>4</v>
-      </c>
-      <c r="D2">
-        <v>1</v>
-      </c>
-      <c r="E2">
-        <v>4</v>
-      </c>
-      <c r="F2">
-        <v>2</v>
-      </c>
-      <c r="G2">
-        <v>4</v>
-      </c>
-      <c r="H2">
-        <v>2</v>
-      </c>
-      <c r="I2">
-        <v>3</v>
-      </c>
-      <c r="J2">
-        <v>2</v>
-      </c>
-      <c r="K2">
-        <v>6</v>
-      </c>
-      <c r="L2">
-        <v>6</v>
-      </c>
-      <c r="M2">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3">
-        <v>2</v>
-      </c>
-      <c r="C3">
-        <v>4</v>
-      </c>
-      <c r="D3">
-        <v>1</v>
-      </c>
-      <c r="E3">
-        <v>4</v>
-      </c>
-      <c r="F3">
-        <v>5</v>
-      </c>
-      <c r="G3">
-        <v>4</v>
-      </c>
-      <c r="H3">
-        <v>7</v>
-      </c>
-      <c r="I3">
-        <v>2</v>
-      </c>
-      <c r="J3">
-        <v>11</v>
-      </c>
-      <c r="K3">
-        <v>5</v>
-      </c>
-      <c r="L3">
-        <v>7</v>
-      </c>
-      <c r="M3">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="H4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C5">
-        <v>1</v>
-      </c>
-      <c r="H5">
-        <v>1</v>
-      </c>
-      <c r="I5">
-        <v>1</v>
-      </c>
-      <c r="K5">
-        <v>3</v>
-      </c>
-      <c r="L5">
-        <v>2</v>
-      </c>
-      <c r="M5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C6">
-        <v>14</v>
-      </c>
-      <c r="D6">
-        <v>12</v>
-      </c>
-      <c r="E6">
-        <v>10</v>
-      </c>
-      <c r="F6">
-        <v>11</v>
-      </c>
-      <c r="G6">
-        <v>11</v>
-      </c>
-      <c r="H6">
-        <v>17</v>
-      </c>
-      <c r="I6">
-        <v>20</v>
-      </c>
-      <c r="J6">
-        <v>3</v>
-      </c>
-      <c r="K6">
-        <v>10</v>
-      </c>
-      <c r="L6">
-        <v>5</v>
-      </c>
-      <c r="M6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
-      <c r="A7" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B7">
-        <v>58</v>
-      </c>
-      <c r="C7">
-        <v>53</v>
-      </c>
-      <c r="D7">
-        <v>43</v>
-      </c>
-      <c r="E7">
-        <v>56</v>
-      </c>
-      <c r="F7">
-        <v>53</v>
-      </c>
-      <c r="G7">
-        <v>33</v>
-      </c>
-      <c r="H7">
-        <v>23</v>
-      </c>
-      <c r="I7">
-        <v>26</v>
-      </c>
-      <c r="J7">
-        <v>27</v>
-      </c>
-      <c r="K7">
-        <v>17</v>
-      </c>
-      <c r="L7">
-        <v>19</v>
-      </c>
-      <c r="M7">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13">
-      <c r="A8" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B8">
-        <v>60</v>
-      </c>
-      <c r="C8">
-        <v>76</v>
-      </c>
-      <c r="D8">
-        <v>57</v>
-      </c>
-      <c r="E8">
-        <v>74</v>
-      </c>
-      <c r="F8">
-        <v>71</v>
-      </c>
-      <c r="G8">
-        <v>52</v>
-      </c>
-      <c r="H8">
-        <v>51</v>
-      </c>
-      <c r="I8">
-        <v>52</v>
-      </c>
-      <c r="J8">
-        <v>43</v>
-      </c>
-      <c r="K8">
-        <v>41</v>
-      </c>
-      <c r="L8">
-        <v>39</v>
-      </c>
-      <c r="M8">
-        <v>25</v>
       </c>
     </row>
   </sheetData>
@@ -9700,41 +9740,38 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2">
-        <v>1</v>
-      </c>
       <c r="C2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D2">
         <v>1</v>
       </c>
       <c r="E2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F2">
         <v>2</v>
       </c>
       <c r="G2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K2">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="L2">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M2">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -9742,47 +9779,47 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C3">
-        <v>2</v>
+        <v>4</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
       </c>
       <c r="E3">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F3">
         <v>5</v>
       </c>
       <c r="G3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H3">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="I3">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J3">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="K3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L3">
         <v>7</v>
       </c>
       <c r="M3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4">
-        <v>1</v>
-      </c>
-      <c r="I4">
+        <v>4</v>
+      </c>
+      <c r="H4">
         <v>1</v>
       </c>
     </row>
@@ -9790,52 +9827,61 @@
       <c r="A5" s="1" t="s">
         <v>5</v>
       </c>
+      <c r="C5">
+        <v>1</v>
+      </c>
       <c r="H5">
         <v>1</v>
       </c>
-      <c r="J5">
-        <v>1</v>
+      <c r="I5">
+        <v>1</v>
+      </c>
+      <c r="K5">
+        <v>3</v>
+      </c>
+      <c r="L5">
+        <v>2</v>
+      </c>
+      <c r="M5">
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B6">
+      <c r="C6">
+        <v>14</v>
+      </c>
+      <c r="D6">
         <v>12</v>
       </c>
-      <c r="C6">
-        <v>21</v>
-      </c>
-      <c r="D6">
-        <v>28</v>
-      </c>
       <c r="E6">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="F6">
-        <v>35</v>
+        <v>11</v>
       </c>
       <c r="G6">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H6">
+        <v>17</v>
+      </c>
+      <c r="I6">
+        <v>20</v>
+      </c>
+      <c r="J6">
+        <v>3</v>
+      </c>
+      <c r="K6">
         <v>10</v>
       </c>
-      <c r="I6">
-        <v>15</v>
-      </c>
-      <c r="J6">
-        <v>5</v>
-      </c>
-      <c r="K6">
-        <v>9</v>
-      </c>
       <c r="L6">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="M6">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -9843,40 +9889,40 @@
         <v>9</v>
       </c>
       <c r="B7">
+        <v>58</v>
+      </c>
+      <c r="C7">
+        <v>53</v>
+      </c>
+      <c r="D7">
+        <v>43</v>
+      </c>
+      <c r="E7">
+        <v>56</v>
+      </c>
+      <c r="F7">
+        <v>53</v>
+      </c>
+      <c r="G7">
+        <v>33</v>
+      </c>
+      <c r="H7">
+        <v>23</v>
+      </c>
+      <c r="I7">
+        <v>26</v>
+      </c>
+      <c r="J7">
+        <v>27</v>
+      </c>
+      <c r="K7">
         <v>17</v>
       </c>
-      <c r="C7">
-        <v>35</v>
-      </c>
-      <c r="D7">
-        <v>49</v>
-      </c>
-      <c r="E7">
-        <v>44</v>
-      </c>
-      <c r="F7">
-        <v>58</v>
-      </c>
-      <c r="G7">
-        <v>25</v>
-      </c>
-      <c r="H7">
-        <v>8</v>
-      </c>
-      <c r="I7">
-        <v>10</v>
-      </c>
-      <c r="J7">
-        <v>8</v>
-      </c>
-      <c r="K7">
-        <v>11</v>
-      </c>
       <c r="L7">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="M7">
-        <v>4</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -9884,40 +9930,40 @@
         <v>10</v>
       </c>
       <c r="B8">
-        <v>32</v>
+        <v>60</v>
       </c>
       <c r="C8">
-        <v>61</v>
+        <v>76</v>
       </c>
       <c r="D8">
-        <v>78</v>
+        <v>57</v>
       </c>
       <c r="E8">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="F8">
-        <v>100</v>
+        <v>71</v>
       </c>
       <c r="G8">
+        <v>52</v>
+      </c>
+      <c r="H8">
+        <v>51</v>
+      </c>
+      <c r="I8">
+        <v>52</v>
+      </c>
+      <c r="J8">
         <v>43</v>
       </c>
-      <c r="H8">
-        <v>26</v>
-      </c>
-      <c r="I8">
-        <v>32</v>
-      </c>
-      <c r="J8">
-        <v>20</v>
-      </c>
       <c r="K8">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="L8">
+        <v>39</v>
+      </c>
+      <c r="M8">
         <v>25</v>
-      </c>
-      <c r="M8">
-        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -10408,7 +10454,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M9"/>
+  <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="23.7109375" customWidth="1"/>
@@ -10471,38 +10517,29 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C2">
-        <v>1</v>
-      </c>
       <c r="D2">
-        <v>6</v>
-      </c>
-      <c r="E2">
         <v>1</v>
       </c>
       <c r="F2">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="G2">
-        <v>7</v>
-      </c>
-      <c r="H2">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="I2">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="J2">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="K2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L2">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M2">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -10510,53 +10547,32 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C3">
-        <v>5</v>
-      </c>
-      <c r="D3">
-        <v>18</v>
-      </c>
-      <c r="E3">
-        <v>10</v>
-      </c>
-      <c r="F3">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="G3">
-        <v>11</v>
-      </c>
-      <c r="H3">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="I3">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="J3">
-        <v>12</v>
-      </c>
-      <c r="K3">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="L3">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="M3">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B4">
-        <v>1</v>
-      </c>
-      <c r="D4">
-        <v>1</v>
-      </c>
-      <c r="H4">
+      <c r="E4">
         <v>2</v>
       </c>
       <c r="J4">
@@ -10564,157 +10580,120 @@
       </c>
       <c r="K4">
         <v>1</v>
-      </c>
-      <c r="L4">
-        <v>1</v>
-      </c>
-      <c r="M4">
-        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H5">
+        <v>8</v>
+      </c>
+      <c r="B5">
+        <v>1</v>
+      </c>
+      <c r="C5">
+        <v>1</v>
+      </c>
+      <c r="D5">
+        <v>2</v>
+      </c>
+      <c r="E5">
+        <v>2</v>
+      </c>
+      <c r="G5">
         <v>1</v>
       </c>
       <c r="I5">
         <v>1</v>
+      </c>
+      <c r="J5">
+        <v>3</v>
+      </c>
+      <c r="K5">
+        <v>4</v>
+      </c>
+      <c r="M5">
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
-        <v>7</v>
+        <v>9</v>
+      </c>
+      <c r="B6">
+        <v>8</v>
+      </c>
+      <c r="C6">
+        <v>13</v>
+      </c>
+      <c r="D6">
+        <v>10</v>
+      </c>
+      <c r="E6">
+        <v>9</v>
+      </c>
+      <c r="F6">
+        <v>9</v>
       </c>
       <c r="G6">
-        <v>1</v>
+        <v>8</v>
+      </c>
+      <c r="H6">
+        <v>1</v>
+      </c>
+      <c r="I6">
+        <v>4</v>
       </c>
       <c r="J6">
-        <v>1</v>
+        <v>5</v>
+      </c>
+      <c r="K6">
+        <v>8</v>
+      </c>
+      <c r="L6">
+        <v>3</v>
+      </c>
+      <c r="M6">
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7">
+        <v>10</v>
+      </c>
+      <c r="C7">
+        <v>15</v>
+      </c>
+      <c r="D7">
+        <v>13</v>
+      </c>
+      <c r="E7">
+        <v>13</v>
+      </c>
+      <c r="F7">
+        <v>10</v>
+      </c>
+      <c r="G7">
+        <v>12</v>
+      </c>
+      <c r="H7">
+        <v>1</v>
+      </c>
+      <c r="I7">
         <v>8</v>
       </c>
-      <c r="B7">
-        <v>34</v>
-      </c>
-      <c r="C7">
-        <v>45</v>
-      </c>
-      <c r="D7">
-        <v>25</v>
-      </c>
-      <c r="E7">
-        <v>22</v>
-      </c>
-      <c r="F7">
-        <v>42</v>
-      </c>
-      <c r="G7">
-        <v>32</v>
-      </c>
-      <c r="H7">
-        <v>26</v>
-      </c>
-      <c r="I7">
-        <v>21</v>
-      </c>
       <c r="J7">
+        <v>14</v>
+      </c>
+      <c r="K7">
         <v>15</v>
       </c>
-      <c r="K7">
-        <v>44</v>
-      </c>
       <c r="L7">
-        <v>44</v>
+        <v>6</v>
       </c>
       <c r="M7">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13">
-      <c r="A8" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B8">
-        <v>71</v>
-      </c>
-      <c r="C8">
-        <v>91</v>
-      </c>
-      <c r="D8">
-        <v>57</v>
-      </c>
-      <c r="E8">
-        <v>65</v>
-      </c>
-      <c r="F8">
-        <v>75</v>
-      </c>
-      <c r="G8">
-        <v>41</v>
-      </c>
-      <c r="H8">
-        <v>29</v>
-      </c>
-      <c r="I8">
-        <v>45</v>
-      </c>
-      <c r="J8">
-        <v>31</v>
-      </c>
-      <c r="K8">
-        <v>27</v>
-      </c>
-      <c r="L8">
-        <v>32</v>
-      </c>
-      <c r="M8">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13">
-      <c r="A9" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B9">
-        <v>111</v>
-      </c>
-      <c r="C9">
-        <v>142</v>
-      </c>
-      <c r="D9">
-        <v>107</v>
-      </c>
-      <c r="E9">
-        <v>98</v>
-      </c>
-      <c r="F9">
-        <v>138</v>
-      </c>
-      <c r="G9">
-        <v>92</v>
-      </c>
-      <c r="H9">
-        <v>76</v>
-      </c>
-      <c r="I9">
-        <v>90</v>
-      </c>
-      <c r="J9">
-        <v>69</v>
-      </c>
-      <c r="K9">
-        <v>95</v>
-      </c>
-      <c r="L9">
-        <v>103</v>
-      </c>
-      <c r="M9">
-        <v>35</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -13451,7 +13430,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M10"/>
+  <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="23.7109375" customWidth="1"/>
@@ -13515,39 +13494,21 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>2</v>
-      </c>
-      <c r="C2">
-        <v>4</v>
-      </c>
-      <c r="D2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G2">
-        <v>3</v>
-      </c>
-      <c r="H2">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="I2">
-        <v>7</v>
-      </c>
-      <c r="J2">
-        <v>1</v>
-      </c>
-      <c r="K2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L2">
-        <v>3</v>
-      </c>
-      <c r="M2">
         <v>1</v>
       </c>
     </row>
@@ -13556,213 +13517,168 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C3">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D3">
-        <v>2</v>
-      </c>
-      <c r="E3">
         <v>5</v>
       </c>
       <c r="F3">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="G3">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H3">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I3">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="J3">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="K3">
-        <v>7</v>
-      </c>
-      <c r="L3">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="M3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="D4">
+        <v>5</v>
+      </c>
+      <c r="F4">
+        <v>1</v>
+      </c>
+      <c r="H4">
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>5</v>
+        <v>8</v>
+      </c>
+      <c r="B5">
+        <v>11</v>
       </c>
       <c r="C5">
-        <v>1</v>
+        <v>12</v>
+      </c>
+      <c r="D5">
+        <v>5</v>
+      </c>
+      <c r="E5">
+        <v>9</v>
+      </c>
+      <c r="F5">
+        <v>3</v>
       </c>
       <c r="G5">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="H5">
+        <v>4</v>
       </c>
       <c r="I5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J5">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="K5">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="L5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M5">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6">
+        <v>17</v>
+      </c>
+      <c r="C6">
+        <v>10</v>
+      </c>
+      <c r="D6">
+        <v>17</v>
+      </c>
+      <c r="E6">
+        <v>14</v>
+      </c>
+      <c r="F6">
+        <v>15</v>
+      </c>
+      <c r="G6">
         <v>6</v>
       </c>
-      <c r="D6">
-        <v>1</v>
+      <c r="H6">
+        <v>3</v>
+      </c>
+      <c r="I6">
+        <v>6</v>
+      </c>
+      <c r="J6">
+        <v>8</v>
+      </c>
+      <c r="K6">
+        <v>3</v>
+      </c>
+      <c r="L6">
+        <v>1</v>
+      </c>
+      <c r="M6">
+        <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="1" t="s">
-        <v>7</v>
+        <v>10</v>
+      </c>
+      <c r="B7">
+        <v>33</v>
+      </c>
+      <c r="C7">
+        <v>23</v>
+      </c>
+      <c r="D7">
+        <v>27</v>
+      </c>
+      <c r="E7">
+        <v>25</v>
+      </c>
+      <c r="F7">
+        <v>22</v>
+      </c>
+      <c r="G7">
+        <v>13</v>
+      </c>
+      <c r="H7">
+        <v>11</v>
+      </c>
+      <c r="I7">
+        <v>17</v>
       </c>
       <c r="J7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13">
-      <c r="A8" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B8">
         <v>19</v>
       </c>
-      <c r="C8">
-        <v>16</v>
-      </c>
-      <c r="D8">
-        <v>11</v>
-      </c>
-      <c r="E8">
-        <v>14</v>
-      </c>
-      <c r="F8">
-        <v>12</v>
-      </c>
-      <c r="G8">
-        <v>14</v>
-      </c>
-      <c r="H8">
-        <v>19</v>
-      </c>
-      <c r="I8">
-        <v>29</v>
-      </c>
-      <c r="J8">
-        <v>19</v>
-      </c>
-      <c r="K8">
-        <v>20</v>
-      </c>
-      <c r="L8">
-        <v>26</v>
-      </c>
-      <c r="M8">
+      <c r="K7">
+        <v>15</v>
+      </c>
+      <c r="L7">
         <v>6</v>
       </c>
-    </row>
-    <row r="9" spans="1:13">
-      <c r="A9" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B9">
-        <v>56</v>
-      </c>
-      <c r="C9">
-        <v>45</v>
-      </c>
-      <c r="D9">
-        <v>42</v>
-      </c>
-      <c r="E9">
-        <v>51</v>
-      </c>
-      <c r="F9">
-        <v>54</v>
-      </c>
-      <c r="G9">
-        <v>32</v>
-      </c>
-      <c r="H9">
-        <v>29</v>
-      </c>
-      <c r="I9">
-        <v>35</v>
-      </c>
-      <c r="J9">
-        <v>40</v>
-      </c>
-      <c r="K9">
-        <v>37</v>
-      </c>
-      <c r="L9">
-        <v>25</v>
-      </c>
-      <c r="M9">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13">
-      <c r="A10" s="1" t="s">
+      <c r="M7">
         <v>10</v>
-      </c>
-      <c r="B10">
-        <v>82</v>
-      </c>
-      <c r="C10">
-        <v>70</v>
-      </c>
-      <c r="D10">
-        <v>59</v>
-      </c>
-      <c r="E10">
-        <v>74</v>
-      </c>
-      <c r="F10">
-        <v>77</v>
-      </c>
-      <c r="G10">
-        <v>56</v>
-      </c>
-      <c r="H10">
-        <v>60</v>
-      </c>
-      <c r="I10">
-        <v>82</v>
-      </c>
-      <c r="J10">
-        <v>76</v>
-      </c>
-      <c r="K10">
-        <v>68</v>
-      </c>
-      <c r="L10">
-        <v>62</v>
-      </c>
-      <c r="M10">
-        <v>26</v>
       </c>
     </row>
   </sheetData>
@@ -16131,10 +16047,10 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:M8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="18.7109375" customWidth="1"/>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
     <col min="2" max="2" width="4.7109375" customWidth="1"/>
     <col min="3" max="3" width="4.7109375" customWidth="1"/>
     <col min="4" max="4" width="4.7109375" customWidth="1"/>
@@ -16195,10 +16111,10 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D2">
         <v>1</v>
@@ -16210,10 +16126,10 @@
         <v>2</v>
       </c>
       <c r="G2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H2">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I2">
         <v>2</v>
@@ -16222,13 +16138,13 @@
         <v>1</v>
       </c>
       <c r="K2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M2">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -16236,37 +16152,34 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C3">
-        <v>4</v>
-      </c>
-      <c r="D3">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F3">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H3">
+        <v>2</v>
+      </c>
+      <c r="I3">
+        <v>4</v>
+      </c>
+      <c r="J3">
+        <v>5</v>
+      </c>
+      <c r="K3">
         <v>6</v>
       </c>
-      <c r="I3">
-        <v>2</v>
-      </c>
-      <c r="J3">
-        <v>2</v>
-      </c>
-      <c r="K3">
-        <v>4</v>
-      </c>
       <c r="L3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M3">
         <v>3</v>
@@ -16274,125 +16187,147 @@
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="B4">
-        <v>11</v>
-      </c>
-      <c r="C4">
-        <v>10</v>
-      </c>
-      <c r="D4">
-        <v>6</v>
-      </c>
-      <c r="E4">
-        <v>7</v>
-      </c>
-      <c r="F4">
-        <v>7</v>
-      </c>
-      <c r="G4">
-        <v>7</v>
-      </c>
-      <c r="H4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I4">
-        <v>8</v>
-      </c>
-      <c r="J4">
-        <v>12</v>
-      </c>
-      <c r="K4">
-        <v>4</v>
-      </c>
-      <c r="L4">
-        <v>1</v>
-      </c>
-      <c r="M4">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B5">
-        <v>15</v>
-      </c>
-      <c r="C5">
-        <v>16</v>
-      </c>
-      <c r="D5">
-        <v>22</v>
-      </c>
-      <c r="E5">
-        <v>14</v>
-      </c>
-      <c r="F5">
-        <v>13</v>
-      </c>
-      <c r="G5">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H5">
-        <v>11</v>
-      </c>
-      <c r="I5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J5">
-        <v>13</v>
-      </c>
-      <c r="K5">
-        <v>8</v>
-      </c>
-      <c r="L5">
-        <v>7</v>
-      </c>
-      <c r="M5">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6">
+        <v>12</v>
+      </c>
+      <c r="C6">
+        <v>21</v>
+      </c>
+      <c r="D6">
+        <v>28</v>
+      </c>
+      <c r="E6">
+        <v>21</v>
+      </c>
+      <c r="F6">
+        <v>35</v>
+      </c>
+      <c r="G6">
+        <v>12</v>
+      </c>
+      <c r="H6">
         <v>10</v>
       </c>
-      <c r="B6">
-        <v>30</v>
-      </c>
-      <c r="C6">
-        <v>31</v>
-      </c>
-      <c r="D6">
-        <v>34</v>
-      </c>
-      <c r="E6">
+      <c r="I6">
+        <v>15</v>
+      </c>
+      <c r="J6">
+        <v>5</v>
+      </c>
+      <c r="K6">
+        <v>9</v>
+      </c>
+      <c r="L6">
+        <v>7</v>
+      </c>
+      <c r="M6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7">
+        <v>17</v>
+      </c>
+      <c r="C7">
+        <v>35</v>
+      </c>
+      <c r="D7">
+        <v>49</v>
+      </c>
+      <c r="E7">
+        <v>44</v>
+      </c>
+      <c r="F7">
+        <v>58</v>
+      </c>
+      <c r="G7">
         <v>25</v>
       </c>
-      <c r="F6">
+      <c r="H7">
+        <v>8</v>
+      </c>
+      <c r="I7">
+        <v>10</v>
+      </c>
+      <c r="J7">
+        <v>8</v>
+      </c>
+      <c r="K7">
+        <v>11</v>
+      </c>
+      <c r="L7">
+        <v>7</v>
+      </c>
+      <c r="M7">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13">
+      <c r="A8" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B8">
+        <v>32</v>
+      </c>
+      <c r="C8">
+        <v>61</v>
+      </c>
+      <c r="D8">
+        <v>78</v>
+      </c>
+      <c r="E8">
+        <v>68</v>
+      </c>
+      <c r="F8">
+        <v>100</v>
+      </c>
+      <c r="G8">
+        <v>43</v>
+      </c>
+      <c r="H8">
+        <v>26</v>
+      </c>
+      <c r="I8">
+        <v>32</v>
+      </c>
+      <c r="J8">
+        <v>20</v>
+      </c>
+      <c r="K8">
+        <v>29</v>
+      </c>
+      <c r="L8">
         <v>25</v>
       </c>
-      <c r="G6">
-        <v>15</v>
-      </c>
-      <c r="H6">
-        <v>22</v>
-      </c>
-      <c r="I6">
-        <v>16</v>
-      </c>
-      <c r="J6">
-        <v>28</v>
-      </c>
-      <c r="K6">
-        <v>17</v>
-      </c>
-      <c r="L6">
-        <v>16</v>
-      </c>
-      <c r="M6">
-        <v>13</v>
+      <c r="M8">
+        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -18771,7 +18706,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M7"/>
+  <dimension ref="A1:M9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="23.7109375" customWidth="1"/>
@@ -18834,29 +18769,38 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
       <c r="D2">
+        <v>6</v>
+      </c>
+      <c r="E2">
         <v>1</v>
       </c>
       <c r="F2">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="G2">
-        <v>1</v>
+        <v>7</v>
+      </c>
+      <c r="H2">
+        <v>11</v>
       </c>
       <c r="I2">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="J2">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="K2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L2">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="M2">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -18864,32 +18808,53 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C3">
-        <v>1</v>
+        <v>5</v>
+      </c>
+      <c r="D3">
+        <v>18</v>
+      </c>
+      <c r="E3">
+        <v>10</v>
+      </c>
+      <c r="F3">
+        <v>12</v>
       </c>
       <c r="G3">
-        <v>2</v>
+        <v>11</v>
+      </c>
+      <c r="H3">
+        <v>7</v>
       </c>
       <c r="I3">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="J3">
-        <v>1</v>
+        <v>12</v>
+      </c>
+      <c r="K3">
+        <v>20</v>
       </c>
       <c r="L3">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="M3">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="E4">
+      <c r="B4">
+        <v>1</v>
+      </c>
+      <c r="D4">
+        <v>1</v>
+      </c>
+      <c r="H4">
         <v>2</v>
       </c>
       <c r="J4">
@@ -18897,120 +18862,157 @@
       </c>
       <c r="K4">
         <v>1</v>
+      </c>
+      <c r="L4">
+        <v>1</v>
+      </c>
+      <c r="M4">
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5">
-        <v>1</v>
-      </c>
-      <c r="C5">
-        <v>1</v>
-      </c>
-      <c r="D5">
-        <v>2</v>
-      </c>
-      <c r="E5">
-        <v>2</v>
-      </c>
-      <c r="G5">
+        <v>6</v>
+      </c>
+      <c r="H5">
         <v>1</v>
       </c>
       <c r="I5">
-        <v>1</v>
-      </c>
-      <c r="J5">
-        <v>3</v>
-      </c>
-      <c r="K5">
-        <v>4</v>
-      </c>
-      <c r="M5">
         <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B6">
-        <v>8</v>
-      </c>
-      <c r="C6">
-        <v>13</v>
-      </c>
-      <c r="D6">
-        <v>10</v>
-      </c>
-      <c r="E6">
-        <v>9</v>
-      </c>
-      <c r="F6">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G6">
-        <v>8</v>
-      </c>
-      <c r="H6">
-        <v>1</v>
-      </c>
-      <c r="I6">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J6">
-        <v>5</v>
-      </c>
-      <c r="K6">
-        <v>8</v>
-      </c>
-      <c r="L6">
-        <v>3</v>
-      </c>
-      <c r="M6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7">
+        <v>34</v>
+      </c>
+      <c r="C7">
+        <v>45</v>
+      </c>
+      <c r="D7">
+        <v>25</v>
+      </c>
+      <c r="E7">
+        <v>22</v>
+      </c>
+      <c r="F7">
+        <v>42</v>
+      </c>
+      <c r="G7">
+        <v>32</v>
+      </c>
+      <c r="H7">
+        <v>26</v>
+      </c>
+      <c r="I7">
+        <v>21</v>
+      </c>
+      <c r="J7">
+        <v>15</v>
+      </c>
+      <c r="K7">
+        <v>44</v>
+      </c>
+      <c r="L7">
+        <v>44</v>
+      </c>
+      <c r="M7">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13">
+      <c r="A8" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B8">
+        <v>71</v>
+      </c>
+      <c r="C8">
+        <v>91</v>
+      </c>
+      <c r="D8">
+        <v>57</v>
+      </c>
+      <c r="E8">
+        <v>65</v>
+      </c>
+      <c r="F8">
+        <v>75</v>
+      </c>
+      <c r="G8">
+        <v>41</v>
+      </c>
+      <c r="H8">
+        <v>29</v>
+      </c>
+      <c r="I8">
+        <v>45</v>
+      </c>
+      <c r="J8">
+        <v>31</v>
+      </c>
+      <c r="K8">
+        <v>27</v>
+      </c>
+      <c r="L8">
+        <v>32</v>
+      </c>
+      <c r="M8">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13">
+      <c r="A9" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B7">
-        <v>10</v>
-      </c>
-      <c r="C7">
-        <v>15</v>
-      </c>
-      <c r="D7">
-        <v>13</v>
-      </c>
-      <c r="E7">
-        <v>13</v>
-      </c>
-      <c r="F7">
-        <v>10</v>
-      </c>
-      <c r="G7">
-        <v>12</v>
-      </c>
-      <c r="H7">
-        <v>1</v>
-      </c>
-      <c r="I7">
-        <v>8</v>
-      </c>
-      <c r="J7">
-        <v>14</v>
-      </c>
-      <c r="K7">
-        <v>15</v>
-      </c>
-      <c r="L7">
-        <v>6</v>
-      </c>
-      <c r="M7">
-        <v>6</v>
+      <c r="B9">
+        <v>111</v>
+      </c>
+      <c r="C9">
+        <v>142</v>
+      </c>
+      <c r="D9">
+        <v>107</v>
+      </c>
+      <c r="E9">
+        <v>98</v>
+      </c>
+      <c r="F9">
+        <v>138</v>
+      </c>
+      <c r="G9">
+        <v>92</v>
+      </c>
+      <c r="H9">
+        <v>76</v>
+      </c>
+      <c r="I9">
+        <v>90</v>
+      </c>
+      <c r="J9">
+        <v>69</v>
+      </c>
+      <c r="K9">
+        <v>95</v>
+      </c>
+      <c r="L9">
+        <v>103</v>
+      </c>
+      <c r="M9">
+        <v>35</v>
       </c>
     </row>
   </sheetData>
@@ -21053,7 +21055,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M8"/>
+  <dimension ref="A1:M10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="23.7109375" customWidth="1"/>
@@ -21116,26 +21118,41 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
+      <c r="B2">
+        <v>2</v>
+      </c>
+      <c r="C2">
+        <v>4</v>
+      </c>
       <c r="D2">
         <v>2</v>
       </c>
+      <c r="E2">
+        <v>4</v>
+      </c>
       <c r="F2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H2">
-        <v>1</v>
+        <v>6</v>
+      </c>
+      <c r="I2">
+        <v>7</v>
       </c>
       <c r="J2">
         <v>1</v>
       </c>
       <c r="K2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L2">
-        <v>2</v>
+        <v>3</v>
+      </c>
+      <c r="M2">
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -21143,41 +21160,47 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>1</v>
+        <v>5</v>
+      </c>
+      <c r="C3">
+        <v>4</v>
       </c>
       <c r="D3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E3">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F3">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G3">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H3">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I3">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="J3">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="K3">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="L3">
+        <v>7</v>
+      </c>
+      <c r="M3">
         <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4">
+        <v>4</v>
+      </c>
+      <c r="D4">
         <v>1</v>
       </c>
     </row>
@@ -21185,131 +21208,165 @@
       <c r="A5" s="1" t="s">
         <v>5</v>
       </c>
+      <c r="C5">
+        <v>1</v>
+      </c>
+      <c r="G5">
+        <v>1</v>
+      </c>
+      <c r="I5">
+        <v>2</v>
+      </c>
       <c r="J5">
+        <v>1</v>
+      </c>
+      <c r="K5">
+        <v>1</v>
+      </c>
+      <c r="L5">
+        <v>1</v>
+      </c>
+      <c r="M5">
         <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B6">
-        <v>1</v>
-      </c>
-      <c r="C6">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="D6">
-        <v>4</v>
-      </c>
-      <c r="E6">
-        <v>17</v>
-      </c>
-      <c r="F6">
-        <v>18</v>
-      </c>
-      <c r="G6">
-        <v>12</v>
-      </c>
-      <c r="H6">
-        <v>12</v>
-      </c>
-      <c r="I6">
-        <v>17</v>
-      </c>
-      <c r="J6">
-        <v>6</v>
-      </c>
-      <c r="K6">
-        <v>17</v>
-      </c>
-      <c r="L6">
-        <v>5</v>
-      </c>
-      <c r="M6">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B7">
-        <v>24</v>
-      </c>
-      <c r="C7">
-        <v>26</v>
-      </c>
-      <c r="D7">
-        <v>44</v>
-      </c>
-      <c r="E7">
-        <v>57</v>
-      </c>
-      <c r="F7">
-        <v>79</v>
-      </c>
-      <c r="G7">
-        <v>24</v>
-      </c>
-      <c r="H7">
-        <v>13</v>
-      </c>
-      <c r="I7">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="J7">
-        <v>15</v>
-      </c>
-      <c r="K7">
-        <v>9</v>
-      </c>
-      <c r="L7">
-        <v>7</v>
-      </c>
-      <c r="M7">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:13">
       <c r="A8" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8">
+        <v>19</v>
+      </c>
+      <c r="C8">
+        <v>16</v>
+      </c>
+      <c r="D8">
+        <v>11</v>
+      </c>
+      <c r="E8">
+        <v>14</v>
+      </c>
+      <c r="F8">
+        <v>12</v>
+      </c>
+      <c r="G8">
+        <v>14</v>
+      </c>
+      <c r="H8">
+        <v>19</v>
+      </c>
+      <c r="I8">
+        <v>29</v>
+      </c>
+      <c r="J8">
+        <v>19</v>
+      </c>
+      <c r="K8">
+        <v>20</v>
+      </c>
+      <c r="L8">
+        <v>26</v>
+      </c>
+      <c r="M8">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13">
+      <c r="A9" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B9">
+        <v>56</v>
+      </c>
+      <c r="C9">
+        <v>45</v>
+      </c>
+      <c r="D9">
+        <v>42</v>
+      </c>
+      <c r="E9">
+        <v>51</v>
+      </c>
+      <c r="F9">
+        <v>54</v>
+      </c>
+      <c r="G9">
+        <v>32</v>
+      </c>
+      <c r="H9">
+        <v>29</v>
+      </c>
+      <c r="I9">
+        <v>35</v>
+      </c>
+      <c r="J9">
+        <v>40</v>
+      </c>
+      <c r="K9">
+        <v>37</v>
+      </c>
+      <c r="L9">
+        <v>25</v>
+      </c>
+      <c r="M9">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13">
+      <c r="A10" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B8">
-        <v>27</v>
-      </c>
-      <c r="C8">
-        <v>37</v>
-      </c>
-      <c r="D8">
-        <v>53</v>
-      </c>
-      <c r="E8">
+      <c r="B10">
+        <v>82</v>
+      </c>
+      <c r="C10">
+        <v>70</v>
+      </c>
+      <c r="D10">
+        <v>59</v>
+      </c>
+      <c r="E10">
+        <v>74</v>
+      </c>
+      <c r="F10">
+        <v>77</v>
+      </c>
+      <c r="G10">
+        <v>56</v>
+      </c>
+      <c r="H10">
+        <v>60</v>
+      </c>
+      <c r="I10">
+        <v>82</v>
+      </c>
+      <c r="J10">
         <v>76</v>
       </c>
-      <c r="F8">
-        <v>103</v>
-      </c>
-      <c r="G8">
-        <v>39</v>
-      </c>
-      <c r="H8">
-        <v>30</v>
-      </c>
-      <c r="I8">
-        <v>34</v>
-      </c>
-      <c r="J8">
-        <v>29</v>
-      </c>
-      <c r="K8">
-        <v>33</v>
-      </c>
-      <c r="L8">
-        <v>17</v>
-      </c>
-      <c r="M8">
-        <v>8</v>
+      <c r="K10">
+        <v>68</v>
+      </c>
+      <c r="L10">
+        <v>62</v>
+      </c>
+      <c r="M10">
+        <v>26</v>
       </c>
     </row>
   </sheetData>
@@ -23157,10 +23214,10 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M10"/>
+  <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="1" max="1" width="18.7109375" customWidth="1"/>
     <col min="2" max="2" width="4.7109375" customWidth="1"/>
     <col min="3" max="3" width="4.7109375" customWidth="1"/>
     <col min="4" max="4" width="4.7109375" customWidth="1"/>
@@ -23221,40 +23278,40 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D2">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="E2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F2">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="G2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H2">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="I2">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="J2">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="K2">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="L2">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="M2">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -23262,246 +23319,163 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="C3">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="D3">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="E3">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="F3">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="G3">
-        <v>26</v>
+        <v>1</v>
       </c>
       <c r="H3">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="I3">
-        <v>32</v>
+        <v>2</v>
       </c>
       <c r="J3">
-        <v>40</v>
+        <v>2</v>
       </c>
       <c r="K3">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="L3">
-        <v>34</v>
+        <v>6</v>
       </c>
       <c r="M3">
-        <v>17</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
-        <v>3</v>
+        <v>8</v>
+      </c>
+      <c r="B4">
+        <v>11</v>
+      </c>
+      <c r="C4">
+        <v>10</v>
+      </c>
+      <c r="D4">
+        <v>6</v>
+      </c>
+      <c r="E4">
+        <v>7</v>
+      </c>
+      <c r="F4">
+        <v>7</v>
       </c>
       <c r="G4">
-        <v>1</v>
+        <v>7</v>
+      </c>
+      <c r="H4">
+        <v>3</v>
+      </c>
+      <c r="I4">
+        <v>8</v>
       </c>
       <c r="J4">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="K4">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L4">
         <v>1</v>
       </c>
       <c r="M4">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
+      </c>
+      <c r="B5">
+        <v>15</v>
       </c>
       <c r="C5">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="D5">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="E5">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="F5">
-        <v>1</v>
+        <v>13</v>
+      </c>
+      <c r="G5">
+        <v>6</v>
       </c>
       <c r="H5">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="I5">
         <v>4</v>
       </c>
       <c r="J5">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="K5">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="L5">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M5">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
-        <v>6</v>
+        <v>10</v>
+      </c>
+      <c r="B6">
+        <v>30</v>
+      </c>
+      <c r="C6">
+        <v>31</v>
+      </c>
+      <c r="D6">
+        <v>34</v>
+      </c>
+      <c r="E6">
+        <v>25</v>
+      </c>
+      <c r="F6">
+        <v>25</v>
       </c>
       <c r="G6">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="H6">
-        <v>2</v>
+        <v>22</v>
+      </c>
+      <c r="I6">
+        <v>16</v>
       </c>
       <c r="J6">
-        <v>2</v>
+        <v>28</v>
+      </c>
+      <c r="K6">
+        <v>17</v>
       </c>
       <c r="L6">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="M6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
-      <c r="A7" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="K7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13">
-      <c r="A8" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B8">
-        <v>30</v>
-      </c>
-      <c r="C8">
-        <v>44</v>
-      </c>
-      <c r="D8">
-        <v>49</v>
-      </c>
-      <c r="E8">
-        <v>67</v>
-      </c>
-      <c r="F8">
-        <v>69</v>
-      </c>
-      <c r="G8">
-        <v>57</v>
-      </c>
-      <c r="H8">
-        <v>80</v>
-      </c>
-      <c r="I8">
-        <v>80</v>
-      </c>
-      <c r="J8">
-        <v>64</v>
-      </c>
-      <c r="K8">
-        <v>48</v>
-      </c>
-      <c r="L8">
-        <v>44</v>
-      </c>
-      <c r="M8">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13">
-      <c r="A9" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B9">
-        <v>233</v>
-      </c>
-      <c r="C9">
-        <v>354</v>
-      </c>
-      <c r="D9">
-        <v>538</v>
-      </c>
-      <c r="E9">
-        <v>705</v>
-      </c>
-      <c r="F9">
-        <v>568</v>
-      </c>
-      <c r="G9">
-        <v>168</v>
-      </c>
-      <c r="H9">
-        <v>116</v>
-      </c>
-      <c r="I9">
-        <v>194</v>
-      </c>
-      <c r="J9">
-        <v>122</v>
-      </c>
-      <c r="K9">
-        <v>114</v>
-      </c>
-      <c r="L9">
-        <v>95</v>
-      </c>
-      <c r="M9">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13">
-      <c r="A10" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B10">
-        <v>282</v>
-      </c>
-      <c r="C10">
-        <v>416</v>
-      </c>
-      <c r="D10">
-        <v>617</v>
-      </c>
-      <c r="E10">
-        <v>797</v>
-      </c>
-      <c r="F10">
-        <v>660</v>
-      </c>
-      <c r="G10">
-        <v>257</v>
-      </c>
-      <c r="H10">
-        <v>236</v>
-      </c>
-      <c r="I10">
-        <v>324</v>
-      </c>
-      <c r="J10">
-        <v>255</v>
-      </c>
-      <c r="K10">
-        <v>207</v>
-      </c>
-      <c r="L10">
-        <v>196</v>
-      </c>
-      <c r="M10">
-        <v>93</v>
+        <v>13</v>
       </c>
     </row>
   </sheetData>
@@ -25292,7 +25266,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M7"/>
+  <dimension ref="A1:M8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="23.7109375" customWidth="1"/>
@@ -25356,19 +25330,22 @@
         <v>1</v>
       </c>
       <c r="D2">
-        <v>1</v>
-      </c>
-      <c r="E2">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="F2">
+        <v>2</v>
+      </c>
+      <c r="G2">
+        <v>2</v>
       </c>
       <c r="H2">
         <v>1</v>
       </c>
       <c r="J2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L2">
         <v>2</v>
@@ -25378,31 +25355,40 @@
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
+      <c r="B3">
+        <v>1</v>
+      </c>
+      <c r="D3">
+        <v>3</v>
+      </c>
+      <c r="E3">
+        <v>2</v>
+      </c>
       <c r="F3">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G3">
         <v>1</v>
       </c>
       <c r="H3">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J3">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="K3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B4">
         <v>1</v>
@@ -25410,119 +25396,133 @@
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5">
-        <v>1</v>
-      </c>
-      <c r="C5">
-        <v>3</v>
-      </c>
-      <c r="D5">
-        <v>1</v>
-      </c>
-      <c r="E5">
-        <v>6</v>
-      </c>
-      <c r="F5">
-        <v>2</v>
-      </c>
-      <c r="G5">
-        <v>1</v>
-      </c>
-      <c r="H5">
-        <v>2</v>
-      </c>
-      <c r="I5">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J5">
-        <v>3</v>
-      </c>
-      <c r="M5">
         <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B6">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="C6">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D6">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="E6">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="F6">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="G6">
+        <v>12</v>
+      </c>
+      <c r="H6">
+        <v>12</v>
+      </c>
+      <c r="I6">
+        <v>17</v>
+      </c>
+      <c r="J6">
         <v>6</v>
       </c>
-      <c r="H6">
-        <v>2</v>
-      </c>
-      <c r="I6">
-        <v>9</v>
-      </c>
-      <c r="J6">
-        <v>3</v>
-      </c>
       <c r="K6">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="L6">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M6">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7">
+        <v>24</v>
+      </c>
+      <c r="C7">
+        <v>26</v>
+      </c>
+      <c r="D7">
+        <v>44</v>
+      </c>
+      <c r="E7">
+        <v>57</v>
+      </c>
+      <c r="F7">
+        <v>79</v>
+      </c>
+      <c r="G7">
+        <v>24</v>
+      </c>
+      <c r="H7">
+        <v>13</v>
+      </c>
+      <c r="I7">
+        <v>15</v>
+      </c>
+      <c r="J7">
+        <v>15</v>
+      </c>
+      <c r="K7">
+        <v>9</v>
+      </c>
+      <c r="L7">
+        <v>7</v>
+      </c>
+      <c r="M7">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13">
+      <c r="A8" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B7">
-        <v>15</v>
-      </c>
-      <c r="C7">
-        <v>18</v>
-      </c>
-      <c r="D7">
-        <v>15</v>
-      </c>
-      <c r="E7">
-        <v>16</v>
-      </c>
-      <c r="F7">
+      <c r="B8">
+        <v>27</v>
+      </c>
+      <c r="C8">
+        <v>37</v>
+      </c>
+      <c r="D8">
+        <v>53</v>
+      </c>
+      <c r="E8">
+        <v>76</v>
+      </c>
+      <c r="F8">
+        <v>103</v>
+      </c>
+      <c r="G8">
+        <v>39</v>
+      </c>
+      <c r="H8">
+        <v>30</v>
+      </c>
+      <c r="I8">
+        <v>34</v>
+      </c>
+      <c r="J8">
+        <v>29</v>
+      </c>
+      <c r="K8">
+        <v>33</v>
+      </c>
+      <c r="L8">
         <v>17</v>
       </c>
-      <c r="G7">
+      <c r="M8">
         <v>8</v>
-      </c>
-      <c r="H7">
-        <v>7</v>
-      </c>
-      <c r="I7">
-        <v>12</v>
-      </c>
-      <c r="J7">
-        <v>10</v>
-      </c>
-      <c r="K7">
-        <v>6</v>
-      </c>
-      <c r="L7">
-        <v>8</v>
-      </c>
-      <c r="M7">
-        <v>4</v>
       </c>
     </row>
   </sheetData>

--- a/output/cta-index-crime-full-year.xlsx
+++ b/output/cta-index-crime-full-year.xlsx
@@ -9,20 +9,20 @@
   <sheets>
     <sheet name="Citywide Totals" sheetId="1" r:id="rId1"/>
     <sheet name="By Neighborhood" sheetId="2" r:id="rId2"/>
-    <sheet name="Albany Park" sheetId="3" r:id="rId3"/>
-    <sheet name="Woodlawn" sheetId="4" r:id="rId4"/>
+    <sheet name="Austin" sheetId="3" r:id="rId3"/>
+    <sheet name="Roseland" sheetId="4" r:id="rId4"/>
     <sheet name="North Lawndale" sheetId="5" r:id="rId5"/>
-    <sheet name="Englewood" sheetId="6" r:id="rId6"/>
-    <sheet name="Roseland" sheetId="7" r:id="rId7"/>
-    <sheet name="South Shore" sheetId="8" r:id="rId8"/>
-    <sheet name="Old Town" sheetId="9" r:id="rId9"/>
-    <sheet name="Loop" sheetId="10" r:id="rId10"/>
-    <sheet name="Lincoln Park" sheetId="11" r:id="rId11"/>
-    <sheet name="O'Hare" sheetId="12" r:id="rId12"/>
-    <sheet name="Near South Side" sheetId="13" r:id="rId13"/>
-    <sheet name="Logan Square" sheetId="14" r:id="rId14"/>
-    <sheet name="Grand Crossing" sheetId="15" r:id="rId15"/>
-    <sheet name="Austin" sheetId="16" r:id="rId16"/>
+    <sheet name="Albany Park" sheetId="6" r:id="rId6"/>
+    <sheet name="Woodlawn" sheetId="7" r:id="rId7"/>
+    <sheet name="Englewood" sheetId="8" r:id="rId8"/>
+    <sheet name="South Shore" sheetId="9" r:id="rId9"/>
+    <sheet name="Old Town" sheetId="10" r:id="rId10"/>
+    <sheet name="Loop" sheetId="11" r:id="rId11"/>
+    <sheet name="Lincoln Park" sheetId="12" r:id="rId12"/>
+    <sheet name="O'Hare" sheetId="13" r:id="rId13"/>
+    <sheet name="Near South Side" sheetId="14" r:id="rId14"/>
+    <sheet name="Logan Square" sheetId="15" r:id="rId15"/>
+    <sheet name="Grand Crossing" sheetId="16" r:id="rId16"/>
     <sheet name="Avondale" sheetId="17" r:id="rId17"/>
     <sheet name="Rush &amp; Division" sheetId="18" r:id="rId18"/>
     <sheet name="Chatham" sheetId="19" r:id="rId19"/>
@@ -946,7 +946,7 @@
         <v>262</v>
       </c>
       <c r="M3">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -1039,7 +1039,7 @@
         <v>25</v>
       </c>
       <c r="M6">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -1197,7 +1197,7 @@
         <v>703</v>
       </c>
       <c r="M10">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -1238,7 +1238,7 @@
         <v>1604</v>
       </c>
       <c r="M11">
-        <v>828</v>
+        <v>831</v>
       </c>
     </row>
   </sheetData>
@@ -1247,6 +1247,272 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:M8"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+    <col min="13" max="13" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="M1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>2</v>
+      </c>
+      <c r="F2">
+        <v>2</v>
+      </c>
+      <c r="G2">
+        <v>2</v>
+      </c>
+      <c r="H2">
+        <v>1</v>
+      </c>
+      <c r="J2">
+        <v>1</v>
+      </c>
+      <c r="K2">
+        <v>4</v>
+      </c>
+      <c r="L2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>1</v>
+      </c>
+      <c r="D3">
+        <v>3</v>
+      </c>
+      <c r="E3">
+        <v>2</v>
+      </c>
+      <c r="F3">
+        <v>4</v>
+      </c>
+      <c r="G3">
+        <v>1</v>
+      </c>
+      <c r="H3">
+        <v>4</v>
+      </c>
+      <c r="I3">
+        <v>2</v>
+      </c>
+      <c r="J3">
+        <v>6</v>
+      </c>
+      <c r="K3">
+        <v>3</v>
+      </c>
+      <c r="L3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="J5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6">
+        <v>1</v>
+      </c>
+      <c r="C6">
+        <v>11</v>
+      </c>
+      <c r="D6">
+        <v>4</v>
+      </c>
+      <c r="E6">
+        <v>17</v>
+      </c>
+      <c r="F6">
+        <v>18</v>
+      </c>
+      <c r="G6">
+        <v>12</v>
+      </c>
+      <c r="H6">
+        <v>12</v>
+      </c>
+      <c r="I6">
+        <v>17</v>
+      </c>
+      <c r="J6">
+        <v>6</v>
+      </c>
+      <c r="K6">
+        <v>17</v>
+      </c>
+      <c r="L6">
+        <v>5</v>
+      </c>
+      <c r="M6">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7">
+        <v>24</v>
+      </c>
+      <c r="C7">
+        <v>26</v>
+      </c>
+      <c r="D7">
+        <v>44</v>
+      </c>
+      <c r="E7">
+        <v>57</v>
+      </c>
+      <c r="F7">
+        <v>79</v>
+      </c>
+      <c r="G7">
+        <v>24</v>
+      </c>
+      <c r="H7">
+        <v>13</v>
+      </c>
+      <c r="I7">
+        <v>15</v>
+      </c>
+      <c r="J7">
+        <v>15</v>
+      </c>
+      <c r="K7">
+        <v>9</v>
+      </c>
+      <c r="L7">
+        <v>7</v>
+      </c>
+      <c r="M7">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13">
+      <c r="A8" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B8">
+        <v>27</v>
+      </c>
+      <c r="C8">
+        <v>37</v>
+      </c>
+      <c r="D8">
+        <v>53</v>
+      </c>
+      <c r="E8">
+        <v>76</v>
+      </c>
+      <c r="F8">
+        <v>103</v>
+      </c>
+      <c r="G8">
+        <v>39</v>
+      </c>
+      <c r="H8">
+        <v>30</v>
+      </c>
+      <c r="I8">
+        <v>34</v>
+      </c>
+      <c r="J8">
+        <v>29</v>
+      </c>
+      <c r="K8">
+        <v>33</v>
+      </c>
+      <c r="L8">
+        <v>17</v>
+      </c>
+      <c r="M8">
+        <v>8</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M10"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -1600,7 +1866,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -1833,257 +2099,6 @@
       </c>
       <c r="M7">
         <v>4</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M8"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" customWidth="1"/>
-    <col min="13" max="13" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="M1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2">
-        <v>1</v>
-      </c>
-      <c r="D2">
-        <v>2</v>
-      </c>
-      <c r="F2">
-        <v>2</v>
-      </c>
-      <c r="I2">
-        <v>3</v>
-      </c>
-      <c r="J2">
-        <v>2</v>
-      </c>
-      <c r="K2">
-        <v>1</v>
-      </c>
-      <c r="L2">
-        <v>5</v>
-      </c>
-      <c r="M2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C3">
-        <v>1</v>
-      </c>
-      <c r="E3">
-        <v>1</v>
-      </c>
-      <c r="H3">
-        <v>2</v>
-      </c>
-      <c r="I3">
-        <v>1</v>
-      </c>
-      <c r="J3">
-        <v>1</v>
-      </c>
-      <c r="K3">
-        <v>2</v>
-      </c>
-      <c r="L3">
-        <v>2</v>
-      </c>
-      <c r="M3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C4">
-        <v>1</v>
-      </c>
-      <c r="I4">
-        <v>1</v>
-      </c>
-      <c r="K4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="L5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B6">
-        <v>1</v>
-      </c>
-      <c r="F6">
-        <v>4</v>
-      </c>
-      <c r="H6">
-        <v>1</v>
-      </c>
-      <c r="I6">
-        <v>2</v>
-      </c>
-      <c r="K6">
-        <v>1</v>
-      </c>
-      <c r="M6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
-      <c r="A7" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B7">
-        <v>10</v>
-      </c>
-      <c r="C7">
-        <v>20</v>
-      </c>
-      <c r="D7">
-        <v>25</v>
-      </c>
-      <c r="E7">
-        <v>30</v>
-      </c>
-      <c r="F7">
-        <v>41</v>
-      </c>
-      <c r="G7">
-        <v>10</v>
-      </c>
-      <c r="H7">
-        <v>5</v>
-      </c>
-      <c r="I7">
-        <v>5</v>
-      </c>
-      <c r="J7">
-        <v>15</v>
-      </c>
-      <c r="K7">
-        <v>17</v>
-      </c>
-      <c r="L7">
-        <v>12</v>
-      </c>
-      <c r="M7">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13">
-      <c r="A8" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B8">
-        <v>12</v>
-      </c>
-      <c r="C8">
-        <v>22</v>
-      </c>
-      <c r="D8">
-        <v>27</v>
-      </c>
-      <c r="E8">
-        <v>31</v>
-      </c>
-      <c r="F8">
-        <v>47</v>
-      </c>
-      <c r="G8">
-        <v>10</v>
-      </c>
-      <c r="H8">
-        <v>8</v>
-      </c>
-      <c r="I8">
-        <v>12</v>
-      </c>
-      <c r="J8">
-        <v>18</v>
-      </c>
-      <c r="K8">
-        <v>22</v>
-      </c>
-      <c r="L8">
-        <v>21</v>
-      </c>
-      <c r="M8">
-        <v>17</v>
       </c>
     </row>
   </sheetData>
@@ -2156,23 +2171,26 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>2</v>
+      </c>
       <c r="F2">
-        <v>1</v>
-      </c>
-      <c r="G2">
-        <v>2</v>
-      </c>
-      <c r="H2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J2">
         <v>2</v>
       </c>
       <c r="K2">
-        <v>3</v>
+        <v>1</v>
+      </c>
+      <c r="L2">
+        <v>5</v>
       </c>
       <c r="M2">
         <v>2</v>
@@ -2182,42 +2200,42 @@
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B3">
-        <v>1</v>
-      </c>
       <c r="C3">
         <v>1</v>
       </c>
-      <c r="D3">
-        <v>1</v>
-      </c>
       <c r="E3">
-        <v>2</v>
-      </c>
-      <c r="G3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H3">
         <v>2</v>
       </c>
       <c r="I3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J3">
         <v>1</v>
       </c>
       <c r="K3">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="L3">
+        <v>2</v>
       </c>
       <c r="M3">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="J4">
+      <c r="C4">
+        <v>1</v>
+      </c>
+      <c r="I4">
+        <v>1</v>
+      </c>
+      <c r="K4">
         <v>1</v>
       </c>
     </row>
@@ -2225,8 +2243,8 @@
       <c r="A5" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="K5">
-        <v>1</v>
+      <c r="L5">
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -2234,40 +2252,22 @@
         <v>8</v>
       </c>
       <c r="B6">
-        <v>6</v>
-      </c>
-      <c r="C6">
-        <v>2</v>
-      </c>
-      <c r="D6">
-        <v>5</v>
-      </c>
-      <c r="E6">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F6">
         <v>4</v>
       </c>
-      <c r="G6">
-        <v>4</v>
-      </c>
       <c r="H6">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="I6">
-        <v>8</v>
-      </c>
-      <c r="J6">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K6">
-        <v>3</v>
-      </c>
-      <c r="L6">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M6">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -2275,40 +2275,40 @@
         <v>9</v>
       </c>
       <c r="B7">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="C7">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="D7">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E7">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="F7">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="G7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H7">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I7">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="J7">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="K7">
+        <v>17</v>
+      </c>
+      <c r="L7">
         <v>12</v>
       </c>
-      <c r="L7">
-        <v>10</v>
-      </c>
       <c r="M7">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -2316,40 +2316,40 @@
         <v>10</v>
       </c>
       <c r="B8">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="C8">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="D8">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="E8">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="F8">
-        <v>28</v>
+        <v>47</v>
       </c>
       <c r="G8">
+        <v>10</v>
+      </c>
+      <c r="H8">
+        <v>8</v>
+      </c>
+      <c r="I8">
+        <v>12</v>
+      </c>
+      <c r="J8">
+        <v>18</v>
+      </c>
+      <c r="K8">
+        <v>22</v>
+      </c>
+      <c r="L8">
+        <v>21</v>
+      </c>
+      <c r="M8">
         <v>17</v>
-      </c>
-      <c r="H8">
-        <v>15</v>
-      </c>
-      <c r="I8">
-        <v>27</v>
-      </c>
-      <c r="J8">
-        <v>19</v>
-      </c>
-      <c r="K8">
-        <v>20</v>
-      </c>
-      <c r="L8">
-        <v>14</v>
-      </c>
-      <c r="M8">
-        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -2422,35 +2422,35 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C2">
-        <v>1</v>
-      </c>
-      <c r="D2">
-        <v>2</v>
+      <c r="F2">
+        <v>1</v>
       </c>
       <c r="G2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H2">
         <v>1</v>
       </c>
       <c r="I2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K2">
-        <v>2</v>
-      </c>
-      <c r="L2">
-        <v>5</v>
+        <v>3</v>
+      </c>
+      <c r="M2">
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
+      <c r="B3">
+        <v>1</v>
+      </c>
       <c r="C3">
         <v>1</v>
       </c>
@@ -2458,21 +2458,24 @@
         <v>1</v>
       </c>
       <c r="E3">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="G3">
+        <v>2</v>
       </c>
       <c r="H3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K3">
         <v>1</v>
       </c>
-      <c r="L3">
+      <c r="M3">
         <v>1</v>
       </c>
     </row>
@@ -2480,27 +2483,15 @@
       <c r="A4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D4">
-        <v>1</v>
-      </c>
-      <c r="E4">
-        <v>1</v>
-      </c>
       <c r="J4">
-        <v>1</v>
-      </c>
-      <c r="L4">
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C5">
-        <v>1</v>
-      </c>
-      <c r="J5">
+        <v>6</v>
+      </c>
+      <c r="K5">
         <v>1</v>
       </c>
     </row>
@@ -2509,40 +2500,40 @@
         <v>8</v>
       </c>
       <c r="B6">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C6">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D6">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E6">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F6">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G6">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H6">
+        <v>6</v>
+      </c>
+      <c r="I6">
         <v>8</v>
       </c>
-      <c r="I6">
-        <v>5</v>
-      </c>
       <c r="J6">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="K6">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="L6">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="M6">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -2550,40 +2541,40 @@
         <v>9</v>
       </c>
       <c r="B7">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="C7">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="D7">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="E7">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="F7">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="G7">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="H7">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I7">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="J7">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="K7">
+        <v>12</v>
+      </c>
+      <c r="L7">
         <v>10</v>
       </c>
-      <c r="L7">
-        <v>12</v>
-      </c>
       <c r="M7">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -2591,40 +2582,40 @@
         <v>10</v>
       </c>
       <c r="B8">
+        <v>29</v>
+      </c>
+      <c r="C8">
+        <v>30</v>
+      </c>
+      <c r="D8">
+        <v>29</v>
+      </c>
+      <c r="E8">
+        <v>26</v>
+      </c>
+      <c r="F8">
+        <v>28</v>
+      </c>
+      <c r="G8">
+        <v>17</v>
+      </c>
+      <c r="H8">
+        <v>15</v>
+      </c>
+      <c r="I8">
+        <v>27</v>
+      </c>
+      <c r="J8">
         <v>19</v>
-      </c>
-      <c r="C8">
-        <v>32</v>
-      </c>
-      <c r="D8">
-        <v>42</v>
-      </c>
-      <c r="E8">
-        <v>37</v>
-      </c>
-      <c r="F8">
-        <v>23</v>
-      </c>
-      <c r="G8">
-        <v>26</v>
-      </c>
-      <c r="H8">
-        <v>18</v>
-      </c>
-      <c r="I8">
-        <v>23</v>
-      </c>
-      <c r="J8">
-        <v>31</v>
       </c>
       <c r="K8">
         <v>20</v>
       </c>
       <c r="L8">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="M8">
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -2634,7 +2625,7 @@
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M10"/>
+  <dimension ref="A1:M8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="23.7109375" customWidth="1"/>
@@ -2697,40 +2688,28 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2">
-        <v>5</v>
-      </c>
       <c r="C2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D2">
-        <v>7</v>
-      </c>
-      <c r="E2">
-        <v>5</v>
-      </c>
-      <c r="F2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G2">
         <v>4</v>
       </c>
       <c r="H2">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="I2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J2">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="K2">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="L2">
-        <v>5</v>
-      </c>
-      <c r="M2">
         <v>5</v>
       </c>
     </row>
@@ -2738,74 +2717,95 @@
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B3">
-        <v>3</v>
-      </c>
       <c r="C3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D3">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E3">
-        <v>9</v>
-      </c>
-      <c r="F3">
-        <v>19</v>
-      </c>
-      <c r="G3">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="H3">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="I3">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="J3">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="K3">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="L3">
-        <v>13</v>
-      </c>
-      <c r="M3">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="I4">
-        <v>1</v>
-      </c>
-      <c r="M4">
-        <v>2</v>
+        <v>5</v>
+      </c>
+      <c r="D4">
+        <v>1</v>
+      </c>
+      <c r="E4">
+        <v>1</v>
+      </c>
+      <c r="J4">
+        <v>1</v>
+      </c>
+      <c r="L4">
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="K5">
+        <v>7</v>
+      </c>
+      <c r="C5">
+        <v>1</v>
+      </c>
+      <c r="J5">
         <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
-        <v>5</v>
+        <v>8</v>
+      </c>
+      <c r="B6">
+        <v>2</v>
+      </c>
+      <c r="C6">
+        <v>5</v>
+      </c>
+      <c r="D6">
+        <v>3</v>
       </c>
       <c r="E6">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F6">
-        <v>2</v>
+        <v>5</v>
+      </c>
+      <c r="G6">
+        <v>5</v>
+      </c>
+      <c r="H6">
+        <v>8</v>
+      </c>
+      <c r="I6">
+        <v>5</v>
       </c>
       <c r="J6">
-        <v>2</v>
+        <v>8</v>
+      </c>
+      <c r="K6">
+        <v>7</v>
+      </c>
+      <c r="L6">
+        <v>7</v>
       </c>
       <c r="M6">
         <v>1</v>
@@ -2813,145 +2813,84 @@
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="1" t="s">
-        <v>6</v>
+        <v>9</v>
+      </c>
+      <c r="B7">
+        <v>17</v>
+      </c>
+      <c r="C7">
+        <v>24</v>
+      </c>
+      <c r="D7">
+        <v>35</v>
       </c>
       <c r="E7">
-        <v>1</v>
+        <v>31</v>
+      </c>
+      <c r="F7">
+        <v>18</v>
+      </c>
+      <c r="G7">
+        <v>17</v>
+      </c>
+      <c r="H7">
+        <v>8</v>
       </c>
       <c r="I7">
-        <v>1</v>
+        <v>16</v>
+      </c>
+      <c r="J7">
+        <v>15</v>
       </c>
       <c r="K7">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="L7">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="M7">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8" spans="1:13">
       <c r="A8" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B8">
+        <v>19</v>
+      </c>
+      <c r="C8">
+        <v>32</v>
+      </c>
+      <c r="D8">
+        <v>42</v>
+      </c>
+      <c r="E8">
+        <v>37</v>
+      </c>
+      <c r="F8">
+        <v>23</v>
+      </c>
+      <c r="G8">
+        <v>26</v>
+      </c>
+      <c r="H8">
+        <v>18</v>
+      </c>
+      <c r="I8">
+        <v>23</v>
+      </c>
+      <c r="J8">
+        <v>31</v>
+      </c>
+      <c r="K8">
+        <v>20</v>
+      </c>
+      <c r="L8">
+        <v>26</v>
+      </c>
+      <c r="M8">
         <v>8</v>
-      </c>
-      <c r="B8">
-        <v>24</v>
-      </c>
-      <c r="C8">
-        <v>37</v>
-      </c>
-      <c r="D8">
-        <v>21</v>
-      </c>
-      <c r="E8">
-        <v>22</v>
-      </c>
-      <c r="F8">
-        <v>27</v>
-      </c>
-      <c r="G8">
-        <v>15</v>
-      </c>
-      <c r="H8">
-        <v>25</v>
-      </c>
-      <c r="I8">
-        <v>21</v>
-      </c>
-      <c r="J8">
-        <v>26</v>
-      </c>
-      <c r="K8">
-        <v>49</v>
-      </c>
-      <c r="L8">
-        <v>44</v>
-      </c>
-      <c r="M8">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13">
-      <c r="A9" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B9">
-        <v>45</v>
-      </c>
-      <c r="C9">
-        <v>64</v>
-      </c>
-      <c r="D9">
-        <v>46</v>
-      </c>
-      <c r="E9">
-        <v>50</v>
-      </c>
-      <c r="F9">
-        <v>38</v>
-      </c>
-      <c r="G9">
-        <v>19</v>
-      </c>
-      <c r="H9">
-        <v>27</v>
-      </c>
-      <c r="I9">
-        <v>37</v>
-      </c>
-      <c r="J9">
-        <v>20</v>
-      </c>
-      <c r="K9">
-        <v>35</v>
-      </c>
-      <c r="L9">
-        <v>35</v>
-      </c>
-      <c r="M9">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13">
-      <c r="A10" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B10">
-        <v>77</v>
-      </c>
-      <c r="C10">
-        <v>106</v>
-      </c>
-      <c r="D10">
-        <v>82</v>
-      </c>
-      <c r="E10">
-        <v>88</v>
-      </c>
-      <c r="F10">
-        <v>91</v>
-      </c>
-      <c r="G10">
-        <v>47</v>
-      </c>
-      <c r="H10">
-        <v>66</v>
-      </c>
-      <c r="I10">
-        <v>77</v>
-      </c>
-      <c r="J10">
-        <v>67</v>
-      </c>
-      <c r="K10">
-        <v>110</v>
-      </c>
-      <c r="L10">
-        <v>98</v>
-      </c>
-      <c r="M10">
-        <v>40</v>
       </c>
     </row>
   </sheetData>
@@ -3025,31 +2964,31 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D2">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E2">
         <v>5</v>
       </c>
       <c r="F2">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="G2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I2">
         <v>4</v>
       </c>
       <c r="J2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K2">
         <v>7</v>
@@ -3058,7 +2997,7 @@
         <v>5</v>
       </c>
       <c r="M2">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -3066,40 +3005,40 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C3">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D3">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E3">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F3">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="G3">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="H3">
         <v>8</v>
       </c>
       <c r="I3">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="J3">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="K3">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="L3">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M3">
-        <v>11</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -3109,43 +3048,52 @@
       <c r="I4">
         <v>1</v>
       </c>
+      <c r="M4">
+        <v>2</v>
+      </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5">
-        <v>1</v>
-      </c>
-      <c r="D5">
-        <v>1</v>
-      </c>
-      <c r="E5">
-        <v>1</v>
-      </c>
-      <c r="J5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K5">
-        <v>2</v>
-      </c>
-      <c r="M5">
         <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="K6">
+        <v>5</v>
+      </c>
+      <c r="E6">
+        <v>1</v>
+      </c>
+      <c r="F6">
+        <v>2</v>
+      </c>
+      <c r="J6">
+        <v>2</v>
+      </c>
+      <c r="M6">
         <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
+      </c>
+      <c r="E7">
+        <v>1</v>
+      </c>
+      <c r="I7">
+        <v>1</v>
+      </c>
+      <c r="K7">
+        <v>1</v>
       </c>
       <c r="L7">
+        <v>1</v>
+      </c>
+      <c r="M7">
         <v>1</v>
       </c>
     </row>
@@ -3154,40 +3102,40 @@
         <v>8</v>
       </c>
       <c r="B8">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C8">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="D8">
+        <v>21</v>
+      </c>
+      <c r="E8">
         <v>22</v>
       </c>
-      <c r="E8">
-        <v>44</v>
-      </c>
       <c r="F8">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="G8">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="H8">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="I8">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="J8">
         <v>26</v>
       </c>
       <c r="K8">
-        <v>24</v>
+        <v>49</v>
       </c>
       <c r="L8">
-        <v>14</v>
+        <v>44</v>
       </c>
       <c r="M8">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -3195,40 +3143,40 @@
         <v>9</v>
       </c>
       <c r="B9">
+        <v>45</v>
+      </c>
+      <c r="C9">
+        <v>64</v>
+      </c>
+      <c r="D9">
         <v>46</v>
       </c>
-      <c r="C9">
-        <v>59</v>
-      </c>
-      <c r="D9">
-        <v>33</v>
-      </c>
       <c r="E9">
-        <v>73</v>
+        <v>50</v>
       </c>
       <c r="F9">
-        <v>114</v>
+        <v>38</v>
       </c>
       <c r="G9">
-        <v>58</v>
+        <v>19</v>
       </c>
       <c r="H9">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="I9">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="J9">
         <v>20</v>
       </c>
       <c r="K9">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="L9">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="M9">
-        <v>16</v>
+        <v>11</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -3236,40 +3184,40 @@
         <v>10</v>
       </c>
       <c r="B10">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C10">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="D10">
-        <v>65</v>
+        <v>82</v>
       </c>
       <c r="E10">
-        <v>130</v>
+        <v>88</v>
       </c>
       <c r="F10">
-        <v>167</v>
+        <v>91</v>
       </c>
       <c r="G10">
-        <v>92</v>
+        <v>47</v>
       </c>
       <c r="H10">
-        <v>104</v>
+        <v>66</v>
       </c>
       <c r="I10">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="J10">
         <v>67</v>
       </c>
       <c r="K10">
-        <v>71</v>
+        <v>110</v>
       </c>
       <c r="L10">
-        <v>61</v>
+        <v>98</v>
       </c>
       <c r="M10">
-        <v>52</v>
+        <v>40</v>
       </c>
     </row>
   </sheetData>
@@ -4423,7 +4371,7 @@
         <v>61</v>
       </c>
       <c r="M8">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -6556,7 +6504,7 @@
         <v>25</v>
       </c>
       <c r="M65">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="66" spans="1:13">
@@ -7027,7 +6975,7 @@
         <v>62</v>
       </c>
       <c r="M77">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="78" spans="1:13">
@@ -7890,7 +7838,7 @@
         <v>1604</v>
       </c>
       <c r="M99">
-        <v>828</v>
+        <v>831</v>
       </c>
     </row>
   </sheetData>
@@ -10454,7 +10402,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M7"/>
+  <dimension ref="A1:M10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="23.7109375" customWidth="1"/>
@@ -10517,29 +10465,41 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
+      <c r="B2">
+        <v>4</v>
+      </c>
+      <c r="C2">
+        <v>4</v>
+      </c>
       <c r="D2">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="E2">
+        <v>5</v>
       </c>
       <c r="F2">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="G2">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="H2">
+        <v>5</v>
       </c>
       <c r="I2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J2">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="K2">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="L2">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="M2">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -10547,68 +10507,68 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C3">
-        <v>1</v>
+        <v>5</v>
+      </c>
+      <c r="D3">
+        <v>6</v>
+      </c>
+      <c r="E3">
+        <v>7</v>
+      </c>
+      <c r="F3">
+        <v>6</v>
       </c>
       <c r="G3">
-        <v>2</v>
+        <v>7</v>
+      </c>
+      <c r="H3">
+        <v>8</v>
       </c>
       <c r="I3">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="J3">
-        <v>1</v>
+        <v>10</v>
+      </c>
+      <c r="K3">
+        <v>12</v>
       </c>
       <c r="L3">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="M3">
-        <v>1</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="E4">
-        <v>2</v>
-      </c>
-      <c r="J4">
-        <v>1</v>
-      </c>
-      <c r="K4">
+        <v>3</v>
+      </c>
+      <c r="I4">
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B5">
         <v>1</v>
       </c>
-      <c r="C5">
-        <v>1</v>
-      </c>
       <c r="D5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E5">
-        <v>2</v>
-      </c>
-      <c r="G5">
-        <v>1</v>
-      </c>
-      <c r="I5">
         <v>1</v>
       </c>
       <c r="J5">
         <v>3</v>
       </c>
       <c r="K5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M5">
         <v>2</v>
@@ -10616,84 +10576,141 @@
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B6">
-        <v>8</v>
-      </c>
-      <c r="C6">
-        <v>13</v>
-      </c>
-      <c r="D6">
-        <v>10</v>
-      </c>
-      <c r="E6">
-        <v>9</v>
-      </c>
-      <c r="F6">
-        <v>9</v>
-      </c>
-      <c r="G6">
-        <v>8</v>
-      </c>
-      <c r="H6">
-        <v>1</v>
-      </c>
-      <c r="I6">
-        <v>4</v>
-      </c>
-      <c r="J6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K6">
-        <v>8</v>
-      </c>
-      <c r="L6">
-        <v>3</v>
-      </c>
-      <c r="M6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="L7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13">
+      <c r="A8" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8">
+        <v>23</v>
+      </c>
+      <c r="C8">
+        <v>31</v>
+      </c>
+      <c r="D8">
+        <v>22</v>
+      </c>
+      <c r="E8">
+        <v>44</v>
+      </c>
+      <c r="F8">
+        <v>38</v>
+      </c>
+      <c r="G8">
+        <v>24</v>
+      </c>
+      <c r="H8">
+        <v>50</v>
+      </c>
+      <c r="I8">
+        <v>34</v>
+      </c>
+      <c r="J8">
+        <v>26</v>
+      </c>
+      <c r="K8">
+        <v>24</v>
+      </c>
+      <c r="L8">
+        <v>14</v>
+      </c>
+      <c r="M8">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13">
+      <c r="A9" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B9">
+        <v>46</v>
+      </c>
+      <c r="C9">
+        <v>59</v>
+      </c>
+      <c r="D9">
+        <v>33</v>
+      </c>
+      <c r="E9">
+        <v>73</v>
+      </c>
+      <c r="F9">
+        <v>114</v>
+      </c>
+      <c r="G9">
+        <v>58</v>
+      </c>
+      <c r="H9">
+        <v>41</v>
+      </c>
+      <c r="I9">
+        <v>44</v>
+      </c>
+      <c r="J9">
+        <v>20</v>
+      </c>
+      <c r="K9">
+        <v>25</v>
+      </c>
+      <c r="L9">
+        <v>27</v>
+      </c>
+      <c r="M9">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13">
+      <c r="A10" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B7">
-        <v>10</v>
-      </c>
-      <c r="C7">
-        <v>15</v>
-      </c>
-      <c r="D7">
-        <v>13</v>
-      </c>
-      <c r="E7">
-        <v>13</v>
-      </c>
-      <c r="F7">
-        <v>10</v>
-      </c>
-      <c r="G7">
-        <v>12</v>
-      </c>
-      <c r="H7">
-        <v>1</v>
-      </c>
-      <c r="I7">
-        <v>8</v>
-      </c>
-      <c r="J7">
-        <v>14</v>
-      </c>
-      <c r="K7">
-        <v>15</v>
-      </c>
-      <c r="L7">
-        <v>6</v>
-      </c>
-      <c r="M7">
-        <v>7</v>
+      <c r="B10">
+        <v>78</v>
+      </c>
+      <c r="C10">
+        <v>99</v>
+      </c>
+      <c r="D10">
+        <v>65</v>
+      </c>
+      <c r="E10">
+        <v>130</v>
+      </c>
+      <c r="F10">
+        <v>167</v>
+      </c>
+      <c r="G10">
+        <v>92</v>
+      </c>
+      <c r="H10">
+        <v>104</v>
+      </c>
+      <c r="I10">
+        <v>89</v>
+      </c>
+      <c r="J10">
+        <v>67</v>
+      </c>
+      <c r="K10">
+        <v>71</v>
+      </c>
+      <c r="L10">
+        <v>61</v>
+      </c>
+      <c r="M10">
+        <v>53</v>
       </c>
     </row>
   </sheetData>
@@ -13430,7 +13447,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M7"/>
+  <dimension ref="A1:M10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="23.7109375" customWidth="1"/>
@@ -13494,21 +13511,39 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>3</v>
+        <v>2</v>
+      </c>
+      <c r="C2">
+        <v>4</v>
+      </c>
+      <c r="D2">
+        <v>2</v>
       </c>
       <c r="E2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G2">
-        <v>2</v>
+        <v>3</v>
+      </c>
+      <c r="H2">
+        <v>6</v>
       </c>
       <c r="I2">
-        <v>2</v>
+        <v>7</v>
+      </c>
+      <c r="J2">
+        <v>1</v>
+      </c>
+      <c r="K2">
+        <v>3</v>
       </c>
       <c r="L2">
+        <v>3</v>
+      </c>
+      <c r="M2">
         <v>1</v>
       </c>
     </row>
@@ -13517,168 +13552,213 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C3">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D3">
+        <v>2</v>
+      </c>
+      <c r="E3">
         <v>5</v>
       </c>
       <c r="F3">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="G3">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H3">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I3">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="J3">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="K3">
-        <v>5</v>
+        <v>7</v>
+      </c>
+      <c r="L3">
+        <v>7</v>
       </c>
       <c r="M3">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="F4">
-        <v>1</v>
-      </c>
-      <c r="H4">
+        <v>4</v>
+      </c>
+      <c r="D4">
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="C5">
-        <v>12</v>
-      </c>
-      <c r="D5">
-        <v>5</v>
-      </c>
-      <c r="E5">
-        <v>9</v>
-      </c>
-      <c r="F5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G5">
-        <v>2</v>
-      </c>
-      <c r="H5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J5">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="K5">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="L5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M5">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B6">
-        <v>17</v>
-      </c>
-      <c r="C6">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D6">
-        <v>17</v>
-      </c>
-      <c r="E6">
-        <v>14</v>
-      </c>
-      <c r="F6">
-        <v>15</v>
-      </c>
-      <c r="G6">
-        <v>6</v>
-      </c>
-      <c r="H6">
-        <v>3</v>
-      </c>
-      <c r="I6">
-        <v>6</v>
-      </c>
-      <c r="J6">
-        <v>8</v>
-      </c>
-      <c r="K6">
-        <v>3</v>
-      </c>
-      <c r="L6">
-        <v>1</v>
-      </c>
-      <c r="M6">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="J7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13">
+      <c r="A8" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8">
+        <v>19</v>
+      </c>
+      <c r="C8">
+        <v>16</v>
+      </c>
+      <c r="D8">
+        <v>11</v>
+      </c>
+      <c r="E8">
+        <v>14</v>
+      </c>
+      <c r="F8">
+        <v>12</v>
+      </c>
+      <c r="G8">
+        <v>14</v>
+      </c>
+      <c r="H8">
+        <v>19</v>
+      </c>
+      <c r="I8">
+        <v>29</v>
+      </c>
+      <c r="J8">
+        <v>19</v>
+      </c>
+      <c r="K8">
+        <v>20</v>
+      </c>
+      <c r="L8">
+        <v>26</v>
+      </c>
+      <c r="M8">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13">
+      <c r="A9" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B9">
+        <v>56</v>
+      </c>
+      <c r="C9">
+        <v>45</v>
+      </c>
+      <c r="D9">
+        <v>42</v>
+      </c>
+      <c r="E9">
+        <v>51</v>
+      </c>
+      <c r="F9">
+        <v>54</v>
+      </c>
+      <c r="G9">
+        <v>32</v>
+      </c>
+      <c r="H9">
+        <v>29</v>
+      </c>
+      <c r="I9">
+        <v>35</v>
+      </c>
+      <c r="J9">
+        <v>40</v>
+      </c>
+      <c r="K9">
+        <v>37</v>
+      </c>
+      <c r="L9">
+        <v>25</v>
+      </c>
+      <c r="M9">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13">
+      <c r="A10" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B7">
-        <v>33</v>
-      </c>
-      <c r="C7">
-        <v>23</v>
-      </c>
-      <c r="D7">
+      <c r="B10">
+        <v>82</v>
+      </c>
+      <c r="C10">
+        <v>70</v>
+      </c>
+      <c r="D10">
+        <v>59</v>
+      </c>
+      <c r="E10">
+        <v>74</v>
+      </c>
+      <c r="F10">
+        <v>77</v>
+      </c>
+      <c r="G10">
+        <v>56</v>
+      </c>
+      <c r="H10">
+        <v>60</v>
+      </c>
+      <c r="I10">
+        <v>82</v>
+      </c>
+      <c r="J10">
+        <v>76</v>
+      </c>
+      <c r="K10">
+        <v>68</v>
+      </c>
+      <c r="L10">
+        <v>62</v>
+      </c>
+      <c r="M10">
         <v>27</v>
-      </c>
-      <c r="E7">
-        <v>25</v>
-      </c>
-      <c r="F7">
-        <v>22</v>
-      </c>
-      <c r="G7">
-        <v>13</v>
-      </c>
-      <c r="H7">
-        <v>11</v>
-      </c>
-      <c r="I7">
-        <v>17</v>
-      </c>
-      <c r="J7">
-        <v>19</v>
-      </c>
-      <c r="K7">
-        <v>15</v>
-      </c>
-      <c r="L7">
-        <v>6</v>
-      </c>
-      <c r="M7">
-        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -16286,7 +16366,7 @@
         <v>7</v>
       </c>
       <c r="M7">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -16327,7 +16407,7 @@
         <v>25</v>
       </c>
       <c r="M8">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
   </sheetData>
@@ -18706,7 +18786,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M9"/>
+  <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="23.7109375" customWidth="1"/>
@@ -18769,38 +18849,29 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C2">
-        <v>1</v>
-      </c>
       <c r="D2">
-        <v>6</v>
-      </c>
-      <c r="E2">
         <v>1</v>
       </c>
       <c r="F2">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="G2">
-        <v>7</v>
-      </c>
-      <c r="H2">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="I2">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="J2">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="K2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L2">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M2">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -18808,53 +18879,32 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C3">
-        <v>5</v>
-      </c>
-      <c r="D3">
-        <v>18</v>
-      </c>
-      <c r="E3">
-        <v>10</v>
-      </c>
-      <c r="F3">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="G3">
-        <v>11</v>
-      </c>
-      <c r="H3">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="I3">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="J3">
-        <v>12</v>
-      </c>
-      <c r="K3">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="L3">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="M3">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B4">
-        <v>1</v>
-      </c>
-      <c r="D4">
-        <v>1</v>
-      </c>
-      <c r="H4">
+      <c r="E4">
         <v>2</v>
       </c>
       <c r="J4">
@@ -18862,157 +18912,120 @@
       </c>
       <c r="K4">
         <v>1</v>
-      </c>
-      <c r="L4">
-        <v>1</v>
-      </c>
-      <c r="M4">
-        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H5">
+        <v>8</v>
+      </c>
+      <c r="B5">
+        <v>1</v>
+      </c>
+      <c r="C5">
+        <v>1</v>
+      </c>
+      <c r="D5">
+        <v>2</v>
+      </c>
+      <c r="E5">
+        <v>2</v>
+      </c>
+      <c r="G5">
         <v>1</v>
       </c>
       <c r="I5">
         <v>1</v>
+      </c>
+      <c r="J5">
+        <v>3</v>
+      </c>
+      <c r="K5">
+        <v>4</v>
+      </c>
+      <c r="M5">
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
-        <v>7</v>
+        <v>9</v>
+      </c>
+      <c r="B6">
+        <v>8</v>
+      </c>
+      <c r="C6">
+        <v>13</v>
+      </c>
+      <c r="D6">
+        <v>10</v>
+      </c>
+      <c r="E6">
+        <v>9</v>
+      </c>
+      <c r="F6">
+        <v>9</v>
       </c>
       <c r="G6">
-        <v>1</v>
+        <v>8</v>
+      </c>
+      <c r="H6">
+        <v>1</v>
+      </c>
+      <c r="I6">
+        <v>4</v>
       </c>
       <c r="J6">
-        <v>1</v>
+        <v>5</v>
+      </c>
+      <c r="K6">
+        <v>8</v>
+      </c>
+      <c r="L6">
+        <v>3</v>
+      </c>
+      <c r="M6">
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7">
+        <v>10</v>
+      </c>
+      <c r="C7">
+        <v>15</v>
+      </c>
+      <c r="D7">
+        <v>13</v>
+      </c>
+      <c r="E7">
+        <v>13</v>
+      </c>
+      <c r="F7">
+        <v>10</v>
+      </c>
+      <c r="G7">
+        <v>12</v>
+      </c>
+      <c r="H7">
+        <v>1</v>
+      </c>
+      <c r="I7">
         <v>8</v>
       </c>
-      <c r="B7">
-        <v>34</v>
-      </c>
-      <c r="C7">
-        <v>45</v>
-      </c>
-      <c r="D7">
-        <v>25</v>
-      </c>
-      <c r="E7">
-        <v>22</v>
-      </c>
-      <c r="F7">
-        <v>42</v>
-      </c>
-      <c r="G7">
-        <v>32</v>
-      </c>
-      <c r="H7">
-        <v>26</v>
-      </c>
-      <c r="I7">
-        <v>21</v>
-      </c>
       <c r="J7">
+        <v>14</v>
+      </c>
+      <c r="K7">
         <v>15</v>
       </c>
-      <c r="K7">
-        <v>44</v>
-      </c>
       <c r="L7">
-        <v>44</v>
+        <v>6</v>
       </c>
       <c r="M7">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13">
-      <c r="A8" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B8">
-        <v>71</v>
-      </c>
-      <c r="C8">
-        <v>91</v>
-      </c>
-      <c r="D8">
-        <v>57</v>
-      </c>
-      <c r="E8">
-        <v>65</v>
-      </c>
-      <c r="F8">
-        <v>75</v>
-      </c>
-      <c r="G8">
-        <v>41</v>
-      </c>
-      <c r="H8">
-        <v>29</v>
-      </c>
-      <c r="I8">
-        <v>45</v>
-      </c>
-      <c r="J8">
-        <v>31</v>
-      </c>
-      <c r="K8">
-        <v>27</v>
-      </c>
-      <c r="L8">
-        <v>32</v>
-      </c>
-      <c r="M8">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13">
-      <c r="A9" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B9">
-        <v>111</v>
-      </c>
-      <c r="C9">
-        <v>142</v>
-      </c>
-      <c r="D9">
-        <v>107</v>
-      </c>
-      <c r="E9">
-        <v>98</v>
-      </c>
-      <c r="F9">
-        <v>138</v>
-      </c>
-      <c r="G9">
-        <v>92</v>
-      </c>
-      <c r="H9">
-        <v>76</v>
-      </c>
-      <c r="I9">
-        <v>90</v>
-      </c>
-      <c r="J9">
-        <v>69</v>
-      </c>
-      <c r="K9">
-        <v>95</v>
-      </c>
-      <c r="L9">
-        <v>103</v>
-      </c>
-      <c r="M9">
-        <v>35</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -21055,7 +21068,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M10"/>
+  <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="23.7109375" customWidth="1"/>
@@ -21119,39 +21132,21 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>2</v>
-      </c>
-      <c r="C2">
-        <v>4</v>
-      </c>
-      <c r="D2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G2">
-        <v>3</v>
-      </c>
-      <c r="H2">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="I2">
-        <v>7</v>
-      </c>
-      <c r="J2">
-        <v>1</v>
-      </c>
-      <c r="K2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L2">
-        <v>3</v>
-      </c>
-      <c r="M2">
         <v>1</v>
       </c>
     </row>
@@ -21160,213 +21155,168 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C3">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D3">
-        <v>2</v>
-      </c>
-      <c r="E3">
         <v>5</v>
       </c>
       <c r="F3">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="G3">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H3">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I3">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="J3">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="K3">
-        <v>7</v>
-      </c>
-      <c r="L3">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="M3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="D4">
+        <v>5</v>
+      </c>
+      <c r="F4">
+        <v>1</v>
+      </c>
+      <c r="H4">
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>5</v>
+        <v>8</v>
+      </c>
+      <c r="B5">
+        <v>11</v>
       </c>
       <c r="C5">
-        <v>1</v>
+        <v>12</v>
+      </c>
+      <c r="D5">
+        <v>5</v>
+      </c>
+      <c r="E5">
+        <v>9</v>
+      </c>
+      <c r="F5">
+        <v>3</v>
       </c>
       <c r="G5">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="H5">
+        <v>4</v>
       </c>
       <c r="I5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J5">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="K5">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="L5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M5">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6">
+        <v>17</v>
+      </c>
+      <c r="C6">
+        <v>10</v>
+      </c>
+      <c r="D6">
+        <v>17</v>
+      </c>
+      <c r="E6">
+        <v>14</v>
+      </c>
+      <c r="F6">
+        <v>15</v>
+      </c>
+      <c r="G6">
         <v>6</v>
       </c>
-      <c r="D6">
-        <v>1</v>
+      <c r="H6">
+        <v>3</v>
+      </c>
+      <c r="I6">
+        <v>6</v>
+      </c>
+      <c r="J6">
+        <v>8</v>
+      </c>
+      <c r="K6">
+        <v>3</v>
+      </c>
+      <c r="L6">
+        <v>1</v>
+      </c>
+      <c r="M6">
+        <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="1" t="s">
-        <v>7</v>
+        <v>10</v>
+      </c>
+      <c r="B7">
+        <v>33</v>
+      </c>
+      <c r="C7">
+        <v>23</v>
+      </c>
+      <c r="D7">
+        <v>27</v>
+      </c>
+      <c r="E7">
+        <v>25</v>
+      </c>
+      <c r="F7">
+        <v>22</v>
+      </c>
+      <c r="G7">
+        <v>13</v>
+      </c>
+      <c r="H7">
+        <v>11</v>
+      </c>
+      <c r="I7">
+        <v>17</v>
       </c>
       <c r="J7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13">
-      <c r="A8" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B8">
         <v>19</v>
       </c>
-      <c r="C8">
-        <v>16</v>
-      </c>
-      <c r="D8">
-        <v>11</v>
-      </c>
-      <c r="E8">
-        <v>14</v>
-      </c>
-      <c r="F8">
-        <v>12</v>
-      </c>
-      <c r="G8">
-        <v>14</v>
-      </c>
-      <c r="H8">
-        <v>19</v>
-      </c>
-      <c r="I8">
-        <v>29</v>
-      </c>
-      <c r="J8">
-        <v>19</v>
-      </c>
-      <c r="K8">
-        <v>20</v>
-      </c>
-      <c r="L8">
-        <v>26</v>
-      </c>
-      <c r="M8">
+      <c r="K7">
+        <v>15</v>
+      </c>
+      <c r="L7">
         <v>6</v>
       </c>
-    </row>
-    <row r="9" spans="1:13">
-      <c r="A9" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B9">
-        <v>56</v>
-      </c>
-      <c r="C9">
-        <v>45</v>
-      </c>
-      <c r="D9">
-        <v>42</v>
-      </c>
-      <c r="E9">
-        <v>51</v>
-      </c>
-      <c r="F9">
-        <v>54</v>
-      </c>
-      <c r="G9">
-        <v>32</v>
-      </c>
-      <c r="H9">
-        <v>29</v>
-      </c>
-      <c r="I9">
-        <v>35</v>
-      </c>
-      <c r="J9">
-        <v>40</v>
-      </c>
-      <c r="K9">
-        <v>37</v>
-      </c>
-      <c r="L9">
-        <v>25</v>
-      </c>
-      <c r="M9">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13">
-      <c r="A10" s="1" t="s">
+      <c r="M7">
         <v>10</v>
-      </c>
-      <c r="B10">
-        <v>82</v>
-      </c>
-      <c r="C10">
-        <v>70</v>
-      </c>
-      <c r="D10">
-        <v>59</v>
-      </c>
-      <c r="E10">
-        <v>74</v>
-      </c>
-      <c r="F10">
-        <v>77</v>
-      </c>
-      <c r="G10">
-        <v>56</v>
-      </c>
-      <c r="H10">
-        <v>60</v>
-      </c>
-      <c r="I10">
-        <v>82</v>
-      </c>
-      <c r="J10">
-        <v>76</v>
-      </c>
-      <c r="K10">
-        <v>68</v>
-      </c>
-      <c r="L10">
-        <v>62</v>
-      </c>
-      <c r="M10">
-        <v>26</v>
       </c>
     </row>
   </sheetData>
@@ -23214,10 +23164,10 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:M9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="18.7109375" customWidth="1"/>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
     <col min="2" max="2" width="4.7109375" customWidth="1"/>
     <col min="3" max="3" width="4.7109375" customWidth="1"/>
     <col min="4" max="4" width="4.7109375" customWidth="1"/>
@@ -23277,41 +23227,38 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2">
-        <v>2</v>
-      </c>
       <c r="C2">
         <v>1</v>
       </c>
       <c r="D2">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E2">
         <v>1</v>
       </c>
       <c r="F2">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="G2">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="H2">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="I2">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="J2">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="K2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L2">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="M2">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -23319,75 +23266,60 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D3">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="E3">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="F3">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="G3">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="H3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I3">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="J3">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="K3">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="L3">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="M3">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B4">
-        <v>11</v>
-      </c>
-      <c r="C4">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D4">
-        <v>6</v>
-      </c>
-      <c r="E4">
-        <v>7</v>
-      </c>
-      <c r="F4">
-        <v>7</v>
-      </c>
-      <c r="G4">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="H4">
-        <v>3</v>
-      </c>
-      <c r="I4">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="J4">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="K4">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L4">
         <v>1</v>
@@ -23398,84 +23330,147 @@
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B5">
-        <v>15</v>
-      </c>
-      <c r="C5">
-        <v>16</v>
-      </c>
-      <c r="D5">
-        <v>22</v>
-      </c>
-      <c r="E5">
-        <v>14</v>
-      </c>
-      <c r="F5">
-        <v>13</v>
-      </c>
-      <c r="G5">
         <v>6</v>
       </c>
       <c r="H5">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="I5">
-        <v>4</v>
-      </c>
-      <c r="J5">
-        <v>13</v>
-      </c>
-      <c r="K5">
-        <v>8</v>
-      </c>
-      <c r="L5">
-        <v>7</v>
-      </c>
-      <c r="M5">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G6">
+        <v>1</v>
+      </c>
+      <c r="J6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7">
+        <v>34</v>
+      </c>
+      <c r="C7">
+        <v>45</v>
+      </c>
+      <c r="D7">
+        <v>25</v>
+      </c>
+      <c r="E7">
+        <v>22</v>
+      </c>
+      <c r="F7">
+        <v>42</v>
+      </c>
+      <c r="G7">
+        <v>32</v>
+      </c>
+      <c r="H7">
+        <v>26</v>
+      </c>
+      <c r="I7">
+        <v>21</v>
+      </c>
+      <c r="J7">
+        <v>15</v>
+      </c>
+      <c r="K7">
+        <v>44</v>
+      </c>
+      <c r="L7">
+        <v>44</v>
+      </c>
+      <c r="M7">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13">
+      <c r="A8" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B8">
+        <v>71</v>
+      </c>
+      <c r="C8">
+        <v>91</v>
+      </c>
+      <c r="D8">
+        <v>57</v>
+      </c>
+      <c r="E8">
+        <v>65</v>
+      </c>
+      <c r="F8">
+        <v>75</v>
+      </c>
+      <c r="G8">
+        <v>41</v>
+      </c>
+      <c r="H8">
+        <v>29</v>
+      </c>
+      <c r="I8">
+        <v>45</v>
+      </c>
+      <c r="J8">
+        <v>31</v>
+      </c>
+      <c r="K8">
+        <v>27</v>
+      </c>
+      <c r="L8">
+        <v>32</v>
+      </c>
+      <c r="M8">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13">
+      <c r="A9" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B6">
-        <v>30</v>
-      </c>
-      <c r="C6">
-        <v>31</v>
-      </c>
-      <c r="D6">
-        <v>34</v>
-      </c>
-      <c r="E6">
-        <v>25</v>
-      </c>
-      <c r="F6">
-        <v>25</v>
-      </c>
-      <c r="G6">
-        <v>15</v>
-      </c>
-      <c r="H6">
-        <v>22</v>
-      </c>
-      <c r="I6">
-        <v>16</v>
-      </c>
-      <c r="J6">
-        <v>28</v>
-      </c>
-      <c r="K6">
-        <v>17</v>
-      </c>
-      <c r="L6">
-        <v>16</v>
-      </c>
-      <c r="M6">
-        <v>13</v>
+      <c r="B9">
+        <v>111</v>
+      </c>
+      <c r="C9">
+        <v>142</v>
+      </c>
+      <c r="D9">
+        <v>107</v>
+      </c>
+      <c r="E9">
+        <v>98</v>
+      </c>
+      <c r="F9">
+        <v>138</v>
+      </c>
+      <c r="G9">
+        <v>92</v>
+      </c>
+      <c r="H9">
+        <v>76</v>
+      </c>
+      <c r="I9">
+        <v>90</v>
+      </c>
+      <c r="J9">
+        <v>69</v>
+      </c>
+      <c r="K9">
+        <v>95</v>
+      </c>
+      <c r="L9">
+        <v>103</v>
+      </c>
+      <c r="M9">
+        <v>35</v>
       </c>
     </row>
   </sheetData>
@@ -25266,10 +25261,10 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M8"/>
+  <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="1" max="1" width="18.7109375" customWidth="1"/>
     <col min="2" max="2" width="4.7109375" customWidth="1"/>
     <col min="3" max="3" width="4.7109375" customWidth="1"/>
     <col min="4" max="4" width="4.7109375" customWidth="1"/>
@@ -25329,26 +25324,41 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
+      <c r="B2">
+        <v>2</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
       <c r="D2">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
       </c>
       <c r="F2">
         <v>2</v>
       </c>
       <c r="G2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H2">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="I2">
+        <v>2</v>
       </c>
       <c r="J2">
         <v>1</v>
       </c>
       <c r="K2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L2">
         <v>2</v>
+      </c>
+      <c r="M2">
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -25356,173 +25366,163 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="C3">
+        <v>4</v>
       </c>
       <c r="D3">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G3">
         <v>1</v>
       </c>
       <c r="H3">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I3">
         <v>2</v>
       </c>
       <c r="J3">
+        <v>2</v>
+      </c>
+      <c r="K3">
+        <v>4</v>
+      </c>
+      <c r="L3">
         <v>6</v>
       </c>
-      <c r="K3">
-        <v>3</v>
-      </c>
-      <c r="L3">
+      <c r="M3">
         <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="B4">
-        <v>1</v>
+        <v>11</v>
+      </c>
+      <c r="C4">
+        <v>10</v>
+      </c>
+      <c r="D4">
+        <v>6</v>
+      </c>
+      <c r="E4">
+        <v>7</v>
+      </c>
+      <c r="F4">
+        <v>7</v>
+      </c>
+      <c r="G4">
+        <v>7</v>
+      </c>
+      <c r="H4">
+        <v>3</v>
+      </c>
+      <c r="I4">
+        <v>8</v>
+      </c>
+      <c r="J4">
+        <v>12</v>
+      </c>
+      <c r="K4">
+        <v>4</v>
+      </c>
+      <c r="L4">
+        <v>1</v>
+      </c>
+      <c r="M4">
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
+      </c>
+      <c r="B5">
+        <v>15</v>
+      </c>
+      <c r="C5">
+        <v>16</v>
+      </c>
+      <c r="D5">
+        <v>22</v>
+      </c>
+      <c r="E5">
+        <v>14</v>
+      </c>
+      <c r="F5">
+        <v>13</v>
+      </c>
+      <c r="G5">
+        <v>6</v>
+      </c>
+      <c r="H5">
+        <v>11</v>
+      </c>
+      <c r="I5">
+        <v>4</v>
       </c>
       <c r="J5">
-        <v>1</v>
+        <v>13</v>
+      </c>
+      <c r="K5">
+        <v>8</v>
+      </c>
+      <c r="L5">
+        <v>7</v>
+      </c>
+      <c r="M5">
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B6">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C6">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="D6">
-        <v>4</v>
+        <v>34</v>
       </c>
       <c r="E6">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="F6">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="G6">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="H6">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="I6">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J6">
-        <v>6</v>
+        <v>28</v>
       </c>
       <c r="K6">
         <v>17</v>
       </c>
       <c r="L6">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="M6">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
-      <c r="A7" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B7">
-        <v>24</v>
-      </c>
-      <c r="C7">
-        <v>26</v>
-      </c>
-      <c r="D7">
-        <v>44</v>
-      </c>
-      <c r="E7">
-        <v>57</v>
-      </c>
-      <c r="F7">
-        <v>79</v>
-      </c>
-      <c r="G7">
-        <v>24</v>
-      </c>
-      <c r="H7">
         <v>13</v>
-      </c>
-      <c r="I7">
-        <v>15</v>
-      </c>
-      <c r="J7">
-        <v>15</v>
-      </c>
-      <c r="K7">
-        <v>9</v>
-      </c>
-      <c r="L7">
-        <v>7</v>
-      </c>
-      <c r="M7">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13">
-      <c r="A8" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B8">
-        <v>27</v>
-      </c>
-      <c r="C8">
-        <v>37</v>
-      </c>
-      <c r="D8">
-        <v>53</v>
-      </c>
-      <c r="E8">
-        <v>76</v>
-      </c>
-      <c r="F8">
-        <v>103</v>
-      </c>
-      <c r="G8">
-        <v>39</v>
-      </c>
-      <c r="H8">
-        <v>30</v>
-      </c>
-      <c r="I8">
-        <v>34</v>
-      </c>
-      <c r="J8">
-        <v>29</v>
-      </c>
-      <c r="K8">
-        <v>33</v>
-      </c>
-      <c r="L8">
-        <v>17</v>
-      </c>
-      <c r="M8">
-        <v>8</v>
       </c>
     </row>
   </sheetData>

--- a/output/cta-index-crime-full-year.xlsx
+++ b/output/cta-index-crime-full-year.xlsx
@@ -9,28 +9,28 @@
   <sheets>
     <sheet name="Citywide Totals" sheetId="1" r:id="rId1"/>
     <sheet name="By Neighborhood" sheetId="2" r:id="rId2"/>
-    <sheet name="Uptown" sheetId="3" r:id="rId3"/>
-    <sheet name="Riverdale" sheetId="4" r:id="rId4"/>
-    <sheet name="Fuller Park" sheetId="5" r:id="rId5"/>
-    <sheet name="North Lawndale" sheetId="6" r:id="rId6"/>
-    <sheet name="Little Village" sheetId="7" r:id="rId7"/>
-    <sheet name="Chatham" sheetId="8" r:id="rId8"/>
-    <sheet name="West Loop" sheetId="9" r:id="rId9"/>
-    <sheet name="Auburn Gresham" sheetId="10" r:id="rId10"/>
-    <sheet name="Lake View" sheetId="11" r:id="rId11"/>
-    <sheet name="Humboldt Park" sheetId="12" r:id="rId12"/>
-    <sheet name="Austin" sheetId="13" r:id="rId13"/>
-    <sheet name="Roseland" sheetId="14" r:id="rId14"/>
-    <sheet name="Albany Park" sheetId="15" r:id="rId15"/>
-    <sheet name="Woodlawn" sheetId="16" r:id="rId16"/>
-    <sheet name="Englewood" sheetId="17" r:id="rId17"/>
-    <sheet name="South Shore" sheetId="18" r:id="rId18"/>
-    <sheet name="Old Town" sheetId="19" r:id="rId19"/>
-    <sheet name="Loop" sheetId="20" r:id="rId20"/>
-    <sheet name="Lincoln Park" sheetId="21" r:id="rId21"/>
-    <sheet name="O'Hare" sheetId="22" r:id="rId22"/>
-    <sheet name="Near South Side" sheetId="23" r:id="rId23"/>
-    <sheet name="Logan Square" sheetId="24" r:id="rId24"/>
+    <sheet name="Englewood" sheetId="3" r:id="rId3"/>
+    <sheet name="Uptown" sheetId="4" r:id="rId4"/>
+    <sheet name="Loop" sheetId="5" r:id="rId5"/>
+    <sheet name="Logan Square" sheetId="6" r:id="rId6"/>
+    <sheet name="Riverdale" sheetId="7" r:id="rId7"/>
+    <sheet name="Fuller Park" sheetId="8" r:id="rId8"/>
+    <sheet name="North Lawndale" sheetId="9" r:id="rId9"/>
+    <sheet name="Little Village" sheetId="10" r:id="rId10"/>
+    <sheet name="Chatham" sheetId="11" r:id="rId11"/>
+    <sheet name="West Loop" sheetId="12" r:id="rId12"/>
+    <sheet name="Auburn Gresham" sheetId="13" r:id="rId13"/>
+    <sheet name="Lake View" sheetId="14" r:id="rId14"/>
+    <sheet name="Humboldt Park" sheetId="15" r:id="rId15"/>
+    <sheet name="Austin" sheetId="16" r:id="rId16"/>
+    <sheet name="Roseland" sheetId="17" r:id="rId17"/>
+    <sheet name="Albany Park" sheetId="18" r:id="rId18"/>
+    <sheet name="Woodlawn" sheetId="19" r:id="rId19"/>
+    <sheet name="South Shore" sheetId="20" r:id="rId20"/>
+    <sheet name="Old Town" sheetId="21" r:id="rId21"/>
+    <sheet name="Lincoln Park" sheetId="22" r:id="rId22"/>
+    <sheet name="O'Hare" sheetId="23" r:id="rId23"/>
+    <sheet name="Near South Side" sheetId="24" r:id="rId24"/>
     <sheet name="Grand Crossing" sheetId="25" r:id="rId25"/>
     <sheet name="Avondale" sheetId="26" r:id="rId26"/>
     <sheet name="Rush &amp; Division" sheetId="27" r:id="rId27"/>
@@ -905,7 +905,7 @@
         <v>137</v>
       </c>
       <c r="M2">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -1156,7 +1156,7 @@
         <v>467</v>
       </c>
       <c r="M9">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -1197,7 +1197,7 @@
         <v>703</v>
       </c>
       <c r="M10">
-        <v>373</v>
+        <v>375</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -1238,7 +1238,7 @@
         <v>1604</v>
       </c>
       <c r="M11">
-        <v>842</v>
+        <v>846</v>
       </c>
     </row>
   </sheetData>
@@ -1312,36 +1312,15 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>2</v>
-      </c>
-      <c r="C2">
-        <v>1</v>
-      </c>
-      <c r="E2">
-        <v>2</v>
-      </c>
-      <c r="F2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G2">
         <v>1</v>
       </c>
-      <c r="H2">
-        <v>1</v>
-      </c>
       <c r="I2">
         <v>1</v>
       </c>
-      <c r="J2">
-        <v>1</v>
-      </c>
       <c r="K2">
-        <v>1</v>
-      </c>
-      <c r="L2">
-        <v>3</v>
-      </c>
-      <c r="M2">
         <v>2</v>
       </c>
     </row>
@@ -1353,41 +1332,35 @@
         <v>1</v>
       </c>
       <c r="C3">
-        <v>3</v>
-      </c>
-      <c r="D3">
-        <v>3</v>
-      </c>
-      <c r="E3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G3">
         <v>2</v>
       </c>
       <c r="H3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I3">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J3">
-        <v>3</v>
-      </c>
-      <c r="K3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L3">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="M3">
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C4">
+      <c r="K4">
         <v>1</v>
       </c>
     </row>
@@ -1396,40 +1369,37 @@
         <v>8</v>
       </c>
       <c r="B5">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="C5">
+        <v>4</v>
+      </c>
+      <c r="D5">
+        <v>3</v>
+      </c>
+      <c r="E5">
+        <v>2</v>
+      </c>
+      <c r="F5">
         <v>6</v>
       </c>
-      <c r="D5">
-        <v>7</v>
-      </c>
-      <c r="E5">
-        <v>12</v>
-      </c>
-      <c r="F5">
-        <v>8</v>
-      </c>
       <c r="G5">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="H5">
-        <v>4</v>
-      </c>
-      <c r="I5">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J5">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K5">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="L5">
         <v>2</v>
       </c>
       <c r="M5">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -1437,40 +1407,40 @@
         <v>9</v>
       </c>
       <c r="B6">
-        <v>34</v>
+        <v>6</v>
       </c>
       <c r="C6">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="D6">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="E6">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="F6">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="G6">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="H6">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="I6">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="J6">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="K6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L6">
         <v>8</v>
       </c>
       <c r="M6">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -1478,40 +1448,40 @@
         <v>10</v>
       </c>
       <c r="B7">
-        <v>56</v>
+        <v>11</v>
       </c>
       <c r="C7">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="D7">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="E7">
-        <v>33</v>
+        <v>6</v>
       </c>
       <c r="F7">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="G7">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="H7">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="I7">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="J7">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="K7">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="L7">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="M7">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -1520,6 +1490,880 @@
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:M10"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+    <col min="13" max="13" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="M1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>5</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
+      <c r="F2">
+        <v>3</v>
+      </c>
+      <c r="G2">
+        <v>1</v>
+      </c>
+      <c r="H2">
+        <v>3</v>
+      </c>
+      <c r="I2">
+        <v>2</v>
+      </c>
+      <c r="J2">
+        <v>5</v>
+      </c>
+      <c r="K2">
+        <v>8</v>
+      </c>
+      <c r="L2">
+        <v>3</v>
+      </c>
+      <c r="M2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>2</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
+      <c r="D3">
+        <v>7</v>
+      </c>
+      <c r="E3">
+        <v>3</v>
+      </c>
+      <c r="F3">
+        <v>4</v>
+      </c>
+      <c r="G3">
+        <v>8</v>
+      </c>
+      <c r="H3">
+        <v>4</v>
+      </c>
+      <c r="I3">
+        <v>6</v>
+      </c>
+      <c r="J3">
+        <v>4</v>
+      </c>
+      <c r="K3">
+        <v>10</v>
+      </c>
+      <c r="L3">
+        <v>5</v>
+      </c>
+      <c r="M3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="H4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5">
+        <v>1</v>
+      </c>
+      <c r="K5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G6">
+        <v>1</v>
+      </c>
+      <c r="H6">
+        <v>1</v>
+      </c>
+      <c r="I6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D7">
+        <v>1</v>
+      </c>
+      <c r="E7">
+        <v>1</v>
+      </c>
+      <c r="J7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13">
+      <c r="A8" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8">
+        <v>5</v>
+      </c>
+      <c r="C8">
+        <v>9</v>
+      </c>
+      <c r="D8">
+        <v>17</v>
+      </c>
+      <c r="E8">
+        <v>13</v>
+      </c>
+      <c r="F8">
+        <v>19</v>
+      </c>
+      <c r="G8">
+        <v>15</v>
+      </c>
+      <c r="H8">
+        <v>5</v>
+      </c>
+      <c r="I8">
+        <v>15</v>
+      </c>
+      <c r="J8">
+        <v>12</v>
+      </c>
+      <c r="K8">
+        <v>18</v>
+      </c>
+      <c r="L8">
+        <v>19</v>
+      </c>
+      <c r="M8">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13">
+      <c r="A9" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B9">
+        <v>43</v>
+      </c>
+      <c r="C9">
+        <v>46</v>
+      </c>
+      <c r="D9">
+        <v>32</v>
+      </c>
+      <c r="E9">
+        <v>30</v>
+      </c>
+      <c r="F9">
+        <v>34</v>
+      </c>
+      <c r="G9">
+        <v>15</v>
+      </c>
+      <c r="H9">
+        <v>17</v>
+      </c>
+      <c r="I9">
+        <v>20</v>
+      </c>
+      <c r="J9">
+        <v>20</v>
+      </c>
+      <c r="K9">
+        <v>20</v>
+      </c>
+      <c r="L9">
+        <v>13</v>
+      </c>
+      <c r="M9">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13">
+      <c r="A10" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B10">
+        <v>51</v>
+      </c>
+      <c r="C10">
+        <v>57</v>
+      </c>
+      <c r="D10">
+        <v>62</v>
+      </c>
+      <c r="E10">
+        <v>48</v>
+      </c>
+      <c r="F10">
+        <v>60</v>
+      </c>
+      <c r="G10">
+        <v>40</v>
+      </c>
+      <c r="H10">
+        <v>31</v>
+      </c>
+      <c r="I10">
+        <v>44</v>
+      </c>
+      <c r="J10">
+        <v>43</v>
+      </c>
+      <c r="K10">
+        <v>57</v>
+      </c>
+      <c r="L10">
+        <v>40</v>
+      </c>
+      <c r="M10">
+        <v>21</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:M9"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+    <col min="13" max="13" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="M1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>2</v>
+      </c>
+      <c r="G2">
+        <v>2</v>
+      </c>
+      <c r="H2">
+        <v>4</v>
+      </c>
+      <c r="I2">
+        <v>3</v>
+      </c>
+      <c r="J2">
+        <v>2</v>
+      </c>
+      <c r="K2">
+        <v>2</v>
+      </c>
+      <c r="L2">
+        <v>1</v>
+      </c>
+      <c r="M2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>1</v>
+      </c>
+      <c r="D3">
+        <v>2</v>
+      </c>
+      <c r="E3">
+        <v>1</v>
+      </c>
+      <c r="F3">
+        <v>1</v>
+      </c>
+      <c r="G3">
+        <v>2</v>
+      </c>
+      <c r="H3">
+        <v>3</v>
+      </c>
+      <c r="I3">
+        <v>2</v>
+      </c>
+      <c r="J3">
+        <v>1</v>
+      </c>
+      <c r="K3">
+        <v>5</v>
+      </c>
+      <c r="L3">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F4">
+        <v>1</v>
+      </c>
+      <c r="J4">
+        <v>1</v>
+      </c>
+      <c r="L4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="I5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7">
+        <v>5</v>
+      </c>
+      <c r="C7">
+        <v>1</v>
+      </c>
+      <c r="D7">
+        <v>6</v>
+      </c>
+      <c r="E7">
+        <v>8</v>
+      </c>
+      <c r="F7">
+        <v>10</v>
+      </c>
+      <c r="G7">
+        <v>8</v>
+      </c>
+      <c r="H7">
+        <v>9</v>
+      </c>
+      <c r="I7">
+        <v>7</v>
+      </c>
+      <c r="J7">
+        <v>4</v>
+      </c>
+      <c r="K7">
+        <v>7</v>
+      </c>
+      <c r="L7">
+        <v>5</v>
+      </c>
+      <c r="M7">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13">
+      <c r="A8" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B8">
+        <v>20</v>
+      </c>
+      <c r="C8">
+        <v>23</v>
+      </c>
+      <c r="D8">
+        <v>35</v>
+      </c>
+      <c r="E8">
+        <v>34</v>
+      </c>
+      <c r="F8">
+        <v>40</v>
+      </c>
+      <c r="G8">
+        <v>20</v>
+      </c>
+      <c r="H8">
+        <v>9</v>
+      </c>
+      <c r="I8">
+        <v>27</v>
+      </c>
+      <c r="J8">
+        <v>22</v>
+      </c>
+      <c r="K8">
+        <v>14</v>
+      </c>
+      <c r="L8">
+        <v>11</v>
+      </c>
+      <c r="M8">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13">
+      <c r="A9" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B9">
+        <v>27</v>
+      </c>
+      <c r="C9">
+        <v>26</v>
+      </c>
+      <c r="D9">
+        <v>44</v>
+      </c>
+      <c r="E9">
+        <v>43</v>
+      </c>
+      <c r="F9">
+        <v>52</v>
+      </c>
+      <c r="G9">
+        <v>32</v>
+      </c>
+      <c r="H9">
+        <v>25</v>
+      </c>
+      <c r="I9">
+        <v>40</v>
+      </c>
+      <c r="J9">
+        <v>30</v>
+      </c>
+      <c r="K9">
+        <v>28</v>
+      </c>
+      <c r="L9">
+        <v>26</v>
+      </c>
+      <c r="M9">
+        <v>18</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:M7"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+    <col min="13" max="13" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="M1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>2</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="E2">
+        <v>2</v>
+      </c>
+      <c r="F2">
+        <v>2</v>
+      </c>
+      <c r="G2">
+        <v>1</v>
+      </c>
+      <c r="H2">
+        <v>1</v>
+      </c>
+      <c r="I2">
+        <v>1</v>
+      </c>
+      <c r="J2">
+        <v>1</v>
+      </c>
+      <c r="K2">
+        <v>1</v>
+      </c>
+      <c r="L2">
+        <v>3</v>
+      </c>
+      <c r="M2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>1</v>
+      </c>
+      <c r="C3">
+        <v>3</v>
+      </c>
+      <c r="D3">
+        <v>3</v>
+      </c>
+      <c r="E3">
+        <v>2</v>
+      </c>
+      <c r="F3">
+        <v>2</v>
+      </c>
+      <c r="G3">
+        <v>2</v>
+      </c>
+      <c r="H3">
+        <v>3</v>
+      </c>
+      <c r="I3">
+        <v>4</v>
+      </c>
+      <c r="J3">
+        <v>3</v>
+      </c>
+      <c r="K3">
+        <v>3</v>
+      </c>
+      <c r="L3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5">
+        <v>19</v>
+      </c>
+      <c r="C5">
+        <v>6</v>
+      </c>
+      <c r="D5">
+        <v>7</v>
+      </c>
+      <c r="E5">
+        <v>12</v>
+      </c>
+      <c r="F5">
+        <v>8</v>
+      </c>
+      <c r="G5">
+        <v>7</v>
+      </c>
+      <c r="H5">
+        <v>4</v>
+      </c>
+      <c r="I5">
+        <v>5</v>
+      </c>
+      <c r="J5">
+        <v>5</v>
+      </c>
+      <c r="K5">
+        <v>6</v>
+      </c>
+      <c r="L5">
+        <v>2</v>
+      </c>
+      <c r="M5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6">
+        <v>34</v>
+      </c>
+      <c r="C6">
+        <v>17</v>
+      </c>
+      <c r="D6">
+        <v>13</v>
+      </c>
+      <c r="E6">
+        <v>17</v>
+      </c>
+      <c r="F6">
+        <v>17</v>
+      </c>
+      <c r="G6">
+        <v>20</v>
+      </c>
+      <c r="H6">
+        <v>7</v>
+      </c>
+      <c r="I6">
+        <v>13</v>
+      </c>
+      <c r="J6">
+        <v>7</v>
+      </c>
+      <c r="K6">
+        <v>3</v>
+      </c>
+      <c r="L6">
+        <v>8</v>
+      </c>
+      <c r="M6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7">
+        <v>56</v>
+      </c>
+      <c r="C7">
+        <v>28</v>
+      </c>
+      <c r="D7">
+        <v>23</v>
+      </c>
+      <c r="E7">
+        <v>33</v>
+      </c>
+      <c r="F7">
+        <v>29</v>
+      </c>
+      <c r="G7">
+        <v>30</v>
+      </c>
+      <c r="H7">
+        <v>15</v>
+      </c>
+      <c r="I7">
+        <v>23</v>
+      </c>
+      <c r="J7">
+        <v>16</v>
+      </c>
+      <c r="K7">
+        <v>13</v>
+      </c>
+      <c r="L7">
+        <v>14</v>
+      </c>
+      <c r="M7">
+        <v>6</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M8"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -1815,7 +2659,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M9"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -2107,7 +2951,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M10"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -2425,7 +3269,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M10"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -2746,7 +3590,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -2995,7 +3839,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -3246,859 +4090,6 @@
       </c>
       <c r="M7">
         <v>10</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M9"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" customWidth="1"/>
-    <col min="13" max="13" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="M1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2">
-        <v>1</v>
-      </c>
-      <c r="D2">
-        <v>6</v>
-      </c>
-      <c r="E2">
-        <v>1</v>
-      </c>
-      <c r="F2">
-        <v>9</v>
-      </c>
-      <c r="G2">
-        <v>7</v>
-      </c>
-      <c r="H2">
-        <v>11</v>
-      </c>
-      <c r="I2">
-        <v>10</v>
-      </c>
-      <c r="J2">
-        <v>9</v>
-      </c>
-      <c r="K2">
-        <v>3</v>
-      </c>
-      <c r="L2">
-        <v>6</v>
-      </c>
-      <c r="M2">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3">
-        <v>5</v>
-      </c>
-      <c r="C3">
-        <v>5</v>
-      </c>
-      <c r="D3">
-        <v>18</v>
-      </c>
-      <c r="E3">
-        <v>10</v>
-      </c>
-      <c r="F3">
-        <v>12</v>
-      </c>
-      <c r="G3">
-        <v>11</v>
-      </c>
-      <c r="H3">
-        <v>7</v>
-      </c>
-      <c r="I3">
-        <v>13</v>
-      </c>
-      <c r="J3">
-        <v>12</v>
-      </c>
-      <c r="K3">
-        <v>20</v>
-      </c>
-      <c r="L3">
-        <v>20</v>
-      </c>
-      <c r="M3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B4">
-        <v>1</v>
-      </c>
-      <c r="D4">
-        <v>1</v>
-      </c>
-      <c r="H4">
-        <v>2</v>
-      </c>
-      <c r="J4">
-        <v>1</v>
-      </c>
-      <c r="K4">
-        <v>1</v>
-      </c>
-      <c r="L4">
-        <v>1</v>
-      </c>
-      <c r="M4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H5">
-        <v>1</v>
-      </c>
-      <c r="I5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="G6">
-        <v>1</v>
-      </c>
-      <c r="J6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
-      <c r="A7" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B7">
-        <v>34</v>
-      </c>
-      <c r="C7">
-        <v>45</v>
-      </c>
-      <c r="D7">
-        <v>25</v>
-      </c>
-      <c r="E7">
-        <v>22</v>
-      </c>
-      <c r="F7">
-        <v>42</v>
-      </c>
-      <c r="G7">
-        <v>32</v>
-      </c>
-      <c r="H7">
-        <v>26</v>
-      </c>
-      <c r="I7">
-        <v>21</v>
-      </c>
-      <c r="J7">
-        <v>15</v>
-      </c>
-      <c r="K7">
-        <v>44</v>
-      </c>
-      <c r="L7">
-        <v>44</v>
-      </c>
-      <c r="M7">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13">
-      <c r="A8" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B8">
-        <v>71</v>
-      </c>
-      <c r="C8">
-        <v>91</v>
-      </c>
-      <c r="D8">
-        <v>57</v>
-      </c>
-      <c r="E8">
-        <v>65</v>
-      </c>
-      <c r="F8">
-        <v>75</v>
-      </c>
-      <c r="G8">
-        <v>41</v>
-      </c>
-      <c r="H8">
-        <v>29</v>
-      </c>
-      <c r="I8">
-        <v>45</v>
-      </c>
-      <c r="J8">
-        <v>31</v>
-      </c>
-      <c r="K8">
-        <v>27</v>
-      </c>
-      <c r="L8">
-        <v>32</v>
-      </c>
-      <c r="M8">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13">
-      <c r="A9" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B9">
-        <v>111</v>
-      </c>
-      <c r="C9">
-        <v>142</v>
-      </c>
-      <c r="D9">
-        <v>107</v>
-      </c>
-      <c r="E9">
-        <v>98</v>
-      </c>
-      <c r="F9">
-        <v>138</v>
-      </c>
-      <c r="G9">
-        <v>92</v>
-      </c>
-      <c r="H9">
-        <v>76</v>
-      </c>
-      <c r="I9">
-        <v>90</v>
-      </c>
-      <c r="J9">
-        <v>69</v>
-      </c>
-      <c r="K9">
-        <v>95</v>
-      </c>
-      <c r="L9">
-        <v>103</v>
-      </c>
-      <c r="M9">
-        <v>35</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M6"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="18.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" customWidth="1"/>
-    <col min="13" max="13" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="M1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2">
-        <v>2</v>
-      </c>
-      <c r="C2">
-        <v>1</v>
-      </c>
-      <c r="D2">
-        <v>1</v>
-      </c>
-      <c r="E2">
-        <v>1</v>
-      </c>
-      <c r="F2">
-        <v>2</v>
-      </c>
-      <c r="G2">
-        <v>1</v>
-      </c>
-      <c r="H2">
-        <v>2</v>
-      </c>
-      <c r="I2">
-        <v>2</v>
-      </c>
-      <c r="J2">
-        <v>1</v>
-      </c>
-      <c r="K2">
-        <v>1</v>
-      </c>
-      <c r="L2">
-        <v>2</v>
-      </c>
-      <c r="M2">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3">
-        <v>2</v>
-      </c>
-      <c r="C3">
-        <v>4</v>
-      </c>
-      <c r="D3">
-        <v>5</v>
-      </c>
-      <c r="E3">
-        <v>3</v>
-      </c>
-      <c r="F3">
-        <v>3</v>
-      </c>
-      <c r="G3">
-        <v>1</v>
-      </c>
-      <c r="H3">
-        <v>6</v>
-      </c>
-      <c r="I3">
-        <v>2</v>
-      </c>
-      <c r="J3">
-        <v>2</v>
-      </c>
-      <c r="K3">
-        <v>4</v>
-      </c>
-      <c r="L3">
-        <v>6</v>
-      </c>
-      <c r="M3">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4">
-        <v>11</v>
-      </c>
-      <c r="C4">
-        <v>10</v>
-      </c>
-      <c r="D4">
-        <v>6</v>
-      </c>
-      <c r="E4">
-        <v>7</v>
-      </c>
-      <c r="F4">
-        <v>7</v>
-      </c>
-      <c r="G4">
-        <v>7</v>
-      </c>
-      <c r="H4">
-        <v>3</v>
-      </c>
-      <c r="I4">
-        <v>8</v>
-      </c>
-      <c r="J4">
-        <v>12</v>
-      </c>
-      <c r="K4">
-        <v>4</v>
-      </c>
-      <c r="L4">
-        <v>1</v>
-      </c>
-      <c r="M4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B5">
-        <v>15</v>
-      </c>
-      <c r="C5">
-        <v>16</v>
-      </c>
-      <c r="D5">
-        <v>22</v>
-      </c>
-      <c r="E5">
-        <v>14</v>
-      </c>
-      <c r="F5">
-        <v>13</v>
-      </c>
-      <c r="G5">
-        <v>6</v>
-      </c>
-      <c r="H5">
-        <v>11</v>
-      </c>
-      <c r="I5">
-        <v>4</v>
-      </c>
-      <c r="J5">
-        <v>13</v>
-      </c>
-      <c r="K5">
-        <v>8</v>
-      </c>
-      <c r="L5">
-        <v>7</v>
-      </c>
-      <c r="M5">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B6">
-        <v>30</v>
-      </c>
-      <c r="C6">
-        <v>31</v>
-      </c>
-      <c r="D6">
-        <v>34</v>
-      </c>
-      <c r="E6">
-        <v>25</v>
-      </c>
-      <c r="F6">
-        <v>25</v>
-      </c>
-      <c r="G6">
-        <v>15</v>
-      </c>
-      <c r="H6">
-        <v>22</v>
-      </c>
-      <c r="I6">
-        <v>16</v>
-      </c>
-      <c r="J6">
-        <v>28</v>
-      </c>
-      <c r="K6">
-        <v>17</v>
-      </c>
-      <c r="L6">
-        <v>16</v>
-      </c>
-      <c r="M6">
-        <v>13</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M8"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" customWidth="1"/>
-    <col min="13" max="13" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="M1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D2">
-        <v>2</v>
-      </c>
-      <c r="F2">
-        <v>2</v>
-      </c>
-      <c r="G2">
-        <v>2</v>
-      </c>
-      <c r="H2">
-        <v>1</v>
-      </c>
-      <c r="J2">
-        <v>1</v>
-      </c>
-      <c r="K2">
-        <v>4</v>
-      </c>
-      <c r="L2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3">
-        <v>1</v>
-      </c>
-      <c r="D3">
-        <v>3</v>
-      </c>
-      <c r="E3">
-        <v>2</v>
-      </c>
-      <c r="F3">
-        <v>4</v>
-      </c>
-      <c r="G3">
-        <v>1</v>
-      </c>
-      <c r="H3">
-        <v>4</v>
-      </c>
-      <c r="I3">
-        <v>2</v>
-      </c>
-      <c r="J3">
-        <v>6</v>
-      </c>
-      <c r="K3">
-        <v>3</v>
-      </c>
-      <c r="L3">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="J5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B6">
-        <v>1</v>
-      </c>
-      <c r="C6">
-        <v>11</v>
-      </c>
-      <c r="D6">
-        <v>4</v>
-      </c>
-      <c r="E6">
-        <v>17</v>
-      </c>
-      <c r="F6">
-        <v>18</v>
-      </c>
-      <c r="G6">
-        <v>12</v>
-      </c>
-      <c r="H6">
-        <v>12</v>
-      </c>
-      <c r="I6">
-        <v>17</v>
-      </c>
-      <c r="J6">
-        <v>6</v>
-      </c>
-      <c r="K6">
-        <v>17</v>
-      </c>
-      <c r="L6">
-        <v>5</v>
-      </c>
-      <c r="M6">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
-      <c r="A7" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B7">
-        <v>24</v>
-      </c>
-      <c r="C7">
-        <v>26</v>
-      </c>
-      <c r="D7">
-        <v>44</v>
-      </c>
-      <c r="E7">
-        <v>57</v>
-      </c>
-      <c r="F7">
-        <v>79</v>
-      </c>
-      <c r="G7">
-        <v>24</v>
-      </c>
-      <c r="H7">
-        <v>13</v>
-      </c>
-      <c r="I7">
-        <v>15</v>
-      </c>
-      <c r="J7">
-        <v>15</v>
-      </c>
-      <c r="K7">
-        <v>9</v>
-      </c>
-      <c r="L7">
-        <v>7</v>
-      </c>
-      <c r="M7">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13">
-      <c r="A8" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B8">
-        <v>27</v>
-      </c>
-      <c r="C8">
-        <v>37</v>
-      </c>
-      <c r="D8">
-        <v>53</v>
-      </c>
-      <c r="E8">
-        <v>76</v>
-      </c>
-      <c r="F8">
-        <v>103</v>
-      </c>
-      <c r="G8">
-        <v>39</v>
-      </c>
-      <c r="H8">
-        <v>30</v>
-      </c>
-      <c r="I8">
-        <v>34</v>
-      </c>
-      <c r="J8">
-        <v>29</v>
-      </c>
-      <c r="K8">
-        <v>33</v>
-      </c>
-      <c r="L8">
-        <v>17</v>
-      </c>
-      <c r="M8">
-        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -5163,7 +5154,7 @@
         <v>103</v>
       </c>
       <c r="M28">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="29" spans="1:13">
@@ -6081,7 +6072,7 @@
         <v>26</v>
       </c>
       <c r="M52">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="53" spans="1:13">
@@ -6122,7 +6113,7 @@
         <v>196</v>
       </c>
       <c r="M53">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="54" spans="1:13">
@@ -7420,7 +7411,7 @@
         <v>33</v>
       </c>
       <c r="M87">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="88" spans="1:13">
@@ -7900,7 +7891,7 @@
         <v>1604</v>
       </c>
       <c r="M99">
-        <v>842</v>
+        <v>846</v>
       </c>
     </row>
   </sheetData>
@@ -8010,7 +8001,278 @@
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M10"/>
+  <dimension ref="A1:M6"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="18.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+    <col min="13" max="13" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="M1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>2</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
+      <c r="F2">
+        <v>2</v>
+      </c>
+      <c r="G2">
+        <v>1</v>
+      </c>
+      <c r="H2">
+        <v>2</v>
+      </c>
+      <c r="I2">
+        <v>2</v>
+      </c>
+      <c r="J2">
+        <v>1</v>
+      </c>
+      <c r="K2">
+        <v>1</v>
+      </c>
+      <c r="L2">
+        <v>2</v>
+      </c>
+      <c r="M2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>2</v>
+      </c>
+      <c r="C3">
+        <v>4</v>
+      </c>
+      <c r="D3">
+        <v>5</v>
+      </c>
+      <c r="E3">
+        <v>3</v>
+      </c>
+      <c r="F3">
+        <v>3</v>
+      </c>
+      <c r="G3">
+        <v>1</v>
+      </c>
+      <c r="H3">
+        <v>6</v>
+      </c>
+      <c r="I3">
+        <v>2</v>
+      </c>
+      <c r="J3">
+        <v>2</v>
+      </c>
+      <c r="K3">
+        <v>4</v>
+      </c>
+      <c r="L3">
+        <v>6</v>
+      </c>
+      <c r="M3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4">
+        <v>11</v>
+      </c>
+      <c r="C4">
+        <v>10</v>
+      </c>
+      <c r="D4">
+        <v>6</v>
+      </c>
+      <c r="E4">
+        <v>7</v>
+      </c>
+      <c r="F4">
+        <v>7</v>
+      </c>
+      <c r="G4">
+        <v>7</v>
+      </c>
+      <c r="H4">
+        <v>3</v>
+      </c>
+      <c r="I4">
+        <v>8</v>
+      </c>
+      <c r="J4">
+        <v>12</v>
+      </c>
+      <c r="K4">
+        <v>4</v>
+      </c>
+      <c r="L4">
+        <v>1</v>
+      </c>
+      <c r="M4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5">
+        <v>15</v>
+      </c>
+      <c r="C5">
+        <v>16</v>
+      </c>
+      <c r="D5">
+        <v>22</v>
+      </c>
+      <c r="E5">
+        <v>14</v>
+      </c>
+      <c r="F5">
+        <v>13</v>
+      </c>
+      <c r="G5">
+        <v>6</v>
+      </c>
+      <c r="H5">
+        <v>11</v>
+      </c>
+      <c r="I5">
+        <v>4</v>
+      </c>
+      <c r="J5">
+        <v>13</v>
+      </c>
+      <c r="K5">
+        <v>8</v>
+      </c>
+      <c r="L5">
+        <v>7</v>
+      </c>
+      <c r="M5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6">
+        <v>30</v>
+      </c>
+      <c r="C6">
+        <v>31</v>
+      </c>
+      <c r="D6">
+        <v>34</v>
+      </c>
+      <c r="E6">
+        <v>25</v>
+      </c>
+      <c r="F6">
+        <v>25</v>
+      </c>
+      <c r="G6">
+        <v>15</v>
+      </c>
+      <c r="H6">
+        <v>22</v>
+      </c>
+      <c r="I6">
+        <v>16</v>
+      </c>
+      <c r="J6">
+        <v>28</v>
+      </c>
+      <c r="K6">
+        <v>17</v>
+      </c>
+      <c r="L6">
+        <v>16</v>
+      </c>
+      <c r="M6">
+        <v>13</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:M8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="23.7109375" customWidth="1"/>
@@ -8073,40 +8335,25 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2">
-        <v>6</v>
-      </c>
-      <c r="C2">
-        <v>3</v>
-      </c>
       <c r="D2">
-        <v>12</v>
-      </c>
-      <c r="E2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F2">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="G2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H2">
-        <v>13</v>
-      </c>
-      <c r="I2">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="J2">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="K2">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="L2">
-        <v>15</v>
-      </c>
-      <c r="M2">
         <v>2</v>
       </c>
     </row>
@@ -8115,59 +8362,41 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>13</v>
-      </c>
-      <c r="C3">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="D3">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="E3">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="F3">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="G3">
-        <v>26</v>
+        <v>1</v>
       </c>
       <c r="H3">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="I3">
-        <v>32</v>
+        <v>2</v>
       </c>
       <c r="J3">
-        <v>40</v>
+        <v>6</v>
       </c>
       <c r="K3">
-        <v>26</v>
+        <v>3</v>
       </c>
       <c r="L3">
-        <v>34</v>
-      </c>
-      <c r="M3">
-        <v>17</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="G4">
-        <v>1</v>
-      </c>
-      <c r="J4">
-        <v>2</v>
-      </c>
-      <c r="K4">
-        <v>1</v>
-      </c>
-      <c r="L4">
-        <v>1</v>
-      </c>
-      <c r="M4">
+      <c r="B4">
         <v>1</v>
       </c>
     </row>
@@ -8175,186 +8404,131 @@
       <c r="A5" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C5">
-        <v>2</v>
-      </c>
-      <c r="D5">
-        <v>1</v>
-      </c>
-      <c r="E5">
-        <v>2</v>
-      </c>
-      <c r="F5">
-        <v>1</v>
-      </c>
-      <c r="H5">
-        <v>2</v>
-      </c>
-      <c r="I5">
-        <v>4</v>
-      </c>
       <c r="J5">
-        <v>3</v>
-      </c>
-      <c r="K5">
-        <v>2</v>
-      </c>
-      <c r="L5">
-        <v>5</v>
-      </c>
-      <c r="M5">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6">
+        <v>1</v>
+      </c>
+      <c r="C6">
+        <v>11</v>
+      </c>
+      <c r="D6">
+        <v>4</v>
+      </c>
+      <c r="E6">
+        <v>17</v>
+      </c>
+      <c r="F6">
+        <v>18</v>
+      </c>
+      <c r="G6">
+        <v>12</v>
+      </c>
+      <c r="H6">
+        <v>12</v>
+      </c>
+      <c r="I6">
+        <v>17</v>
+      </c>
+      <c r="J6">
         <v>6</v>
       </c>
-      <c r="G6">
-        <v>1</v>
-      </c>
-      <c r="H6">
-        <v>2</v>
-      </c>
-      <c r="J6">
-        <v>2</v>
+      <c r="K6">
+        <v>17</v>
       </c>
       <c r="L6">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="M6">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7">
+        <v>24</v>
+      </c>
+      <c r="C7">
+        <v>26</v>
+      </c>
+      <c r="D7">
+        <v>44</v>
+      </c>
+      <c r="E7">
+        <v>57</v>
+      </c>
+      <c r="F7">
+        <v>79</v>
+      </c>
+      <c r="G7">
+        <v>24</v>
+      </c>
+      <c r="H7">
+        <v>13</v>
+      </c>
+      <c r="I7">
+        <v>15</v>
+      </c>
+      <c r="J7">
+        <v>15</v>
+      </c>
+      <c r="K7">
+        <v>9</v>
+      </c>
+      <c r="L7">
         <v>7</v>
       </c>
-      <c r="K7">
-        <v>1</v>
+      <c r="M7">
+        <v>4</v>
       </c>
     </row>
     <row r="8" spans="1:13">
       <c r="A8" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B8">
+        <v>27</v>
+      </c>
+      <c r="C8">
+        <v>37</v>
+      </c>
+      <c r="D8">
+        <v>53</v>
+      </c>
+      <c r="E8">
+        <v>76</v>
+      </c>
+      <c r="F8">
+        <v>103</v>
+      </c>
+      <c r="G8">
+        <v>39</v>
+      </c>
+      <c r="H8">
+        <v>30</v>
+      </c>
+      <c r="I8">
+        <v>34</v>
+      </c>
+      <c r="J8">
+        <v>29</v>
+      </c>
+      <c r="K8">
+        <v>33</v>
+      </c>
+      <c r="L8">
+        <v>17</v>
+      </c>
+      <c r="M8">
         <v>8</v>
-      </c>
-      <c r="B8">
-        <v>30</v>
-      </c>
-      <c r="C8">
-        <v>44</v>
-      </c>
-      <c r="D8">
-        <v>49</v>
-      </c>
-      <c r="E8">
-        <v>67</v>
-      </c>
-      <c r="F8">
-        <v>69</v>
-      </c>
-      <c r="G8">
-        <v>57</v>
-      </c>
-      <c r="H8">
-        <v>80</v>
-      </c>
-      <c r="I8">
-        <v>80</v>
-      </c>
-      <c r="J8">
-        <v>64</v>
-      </c>
-      <c r="K8">
-        <v>48</v>
-      </c>
-      <c r="L8">
-        <v>44</v>
-      </c>
-      <c r="M8">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13">
-      <c r="A9" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B9">
-        <v>233</v>
-      </c>
-      <c r="C9">
-        <v>354</v>
-      </c>
-      <c r="D9">
-        <v>538</v>
-      </c>
-      <c r="E9">
-        <v>705</v>
-      </c>
-      <c r="F9">
-        <v>568</v>
-      </c>
-      <c r="G9">
-        <v>168</v>
-      </c>
-      <c r="H9">
-        <v>116</v>
-      </c>
-      <c r="I9">
-        <v>194</v>
-      </c>
-      <c r="J9">
-        <v>122</v>
-      </c>
-      <c r="K9">
-        <v>114</v>
-      </c>
-      <c r="L9">
-        <v>95</v>
-      </c>
-      <c r="M9">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13">
-      <c r="A10" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B10">
-        <v>282</v>
-      </c>
-      <c r="C10">
-        <v>416</v>
-      </c>
-      <c r="D10">
-        <v>617</v>
-      </c>
-      <c r="E10">
-        <v>797</v>
-      </c>
-      <c r="F10">
-        <v>660</v>
-      </c>
-      <c r="G10">
-        <v>257</v>
-      </c>
-      <c r="H10">
-        <v>236</v>
-      </c>
-      <c r="I10">
-        <v>324</v>
-      </c>
-      <c r="J10">
-        <v>255</v>
-      </c>
-      <c r="K10">
-        <v>207</v>
-      </c>
-      <c r="L10">
-        <v>196</v>
-      </c>
-      <c r="M10">
-        <v>93</v>
       </c>
     </row>
   </sheetData>
@@ -8362,7 +8536,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -8595,257 +8769,6 @@
       </c>
       <c r="M7">
         <v>4</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M8"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" customWidth="1"/>
-    <col min="13" max="13" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="M1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2">
-        <v>1</v>
-      </c>
-      <c r="D2">
-        <v>2</v>
-      </c>
-      <c r="F2">
-        <v>2</v>
-      </c>
-      <c r="I2">
-        <v>3</v>
-      </c>
-      <c r="J2">
-        <v>2</v>
-      </c>
-      <c r="K2">
-        <v>1</v>
-      </c>
-      <c r="L2">
-        <v>5</v>
-      </c>
-      <c r="M2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C3">
-        <v>1</v>
-      </c>
-      <c r="E3">
-        <v>1</v>
-      </c>
-      <c r="H3">
-        <v>2</v>
-      </c>
-      <c r="I3">
-        <v>1</v>
-      </c>
-      <c r="J3">
-        <v>1</v>
-      </c>
-      <c r="K3">
-        <v>2</v>
-      </c>
-      <c r="L3">
-        <v>2</v>
-      </c>
-      <c r="M3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C4">
-        <v>1</v>
-      </c>
-      <c r="I4">
-        <v>1</v>
-      </c>
-      <c r="K4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="L5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B6">
-        <v>1</v>
-      </c>
-      <c r="F6">
-        <v>4</v>
-      </c>
-      <c r="H6">
-        <v>1</v>
-      </c>
-      <c r="I6">
-        <v>2</v>
-      </c>
-      <c r="K6">
-        <v>1</v>
-      </c>
-      <c r="M6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
-      <c r="A7" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B7">
-        <v>10</v>
-      </c>
-      <c r="C7">
-        <v>20</v>
-      </c>
-      <c r="D7">
-        <v>25</v>
-      </c>
-      <c r="E7">
-        <v>30</v>
-      </c>
-      <c r="F7">
-        <v>41</v>
-      </c>
-      <c r="G7">
-        <v>10</v>
-      </c>
-      <c r="H7">
-        <v>5</v>
-      </c>
-      <c r="I7">
-        <v>5</v>
-      </c>
-      <c r="J7">
-        <v>15</v>
-      </c>
-      <c r="K7">
-        <v>17</v>
-      </c>
-      <c r="L7">
-        <v>12</v>
-      </c>
-      <c r="M7">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13">
-      <c r="A8" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B8">
-        <v>12</v>
-      </c>
-      <c r="C8">
-        <v>22</v>
-      </c>
-      <c r="D8">
-        <v>27</v>
-      </c>
-      <c r="E8">
-        <v>31</v>
-      </c>
-      <c r="F8">
-        <v>47</v>
-      </c>
-      <c r="G8">
-        <v>10</v>
-      </c>
-      <c r="H8">
-        <v>8</v>
-      </c>
-      <c r="I8">
-        <v>12</v>
-      </c>
-      <c r="J8">
-        <v>18</v>
-      </c>
-      <c r="K8">
-        <v>22</v>
-      </c>
-      <c r="L8">
-        <v>21</v>
-      </c>
-      <c r="M8">
-        <v>17</v>
       </c>
     </row>
   </sheetData>
@@ -8918,23 +8841,26 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>2</v>
+      </c>
       <c r="F2">
-        <v>1</v>
-      </c>
-      <c r="G2">
-        <v>2</v>
-      </c>
-      <c r="H2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J2">
         <v>2</v>
       </c>
       <c r="K2">
-        <v>3</v>
+        <v>1</v>
+      </c>
+      <c r="L2">
+        <v>5</v>
       </c>
       <c r="M2">
         <v>2</v>
@@ -8944,42 +8870,42 @@
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B3">
-        <v>1</v>
-      </c>
       <c r="C3">
         <v>1</v>
       </c>
-      <c r="D3">
-        <v>1</v>
-      </c>
       <c r="E3">
-        <v>2</v>
-      </c>
-      <c r="G3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H3">
         <v>2</v>
       </c>
       <c r="I3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J3">
         <v>1</v>
       </c>
       <c r="K3">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="L3">
+        <v>2</v>
       </c>
       <c r="M3">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="J4">
+      <c r="C4">
+        <v>1</v>
+      </c>
+      <c r="I4">
+        <v>1</v>
+      </c>
+      <c r="K4">
         <v>1</v>
       </c>
     </row>
@@ -8987,8 +8913,8 @@
       <c r="A5" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="K5">
-        <v>1</v>
+      <c r="L5">
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -8996,40 +8922,22 @@
         <v>8</v>
       </c>
       <c r="B6">
-        <v>6</v>
-      </c>
-      <c r="C6">
-        <v>2</v>
-      </c>
-      <c r="D6">
-        <v>5</v>
-      </c>
-      <c r="E6">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F6">
         <v>4</v>
       </c>
-      <c r="G6">
-        <v>4</v>
-      </c>
       <c r="H6">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="I6">
-        <v>8</v>
-      </c>
-      <c r="J6">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K6">
-        <v>3</v>
-      </c>
-      <c r="L6">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M6">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -9037,40 +8945,40 @@
         <v>9</v>
       </c>
       <c r="B7">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="C7">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="D7">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E7">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="F7">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="G7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H7">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I7">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="J7">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="K7">
+        <v>17</v>
+      </c>
+      <c r="L7">
         <v>12</v>
       </c>
-      <c r="L7">
-        <v>10</v>
-      </c>
       <c r="M7">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -9078,40 +8986,40 @@
         <v>10</v>
       </c>
       <c r="B8">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="C8">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="D8">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="E8">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="F8">
-        <v>28</v>
+        <v>47</v>
       </c>
       <c r="G8">
+        <v>10</v>
+      </c>
+      <c r="H8">
+        <v>8</v>
+      </c>
+      <c r="I8">
+        <v>12</v>
+      </c>
+      <c r="J8">
+        <v>18</v>
+      </c>
+      <c r="K8">
+        <v>22</v>
+      </c>
+      <c r="L8">
+        <v>21</v>
+      </c>
+      <c r="M8">
         <v>17</v>
-      </c>
-      <c r="H8">
-        <v>15</v>
-      </c>
-      <c r="I8">
-        <v>27</v>
-      </c>
-      <c r="J8">
-        <v>19</v>
-      </c>
-      <c r="K8">
-        <v>20</v>
-      </c>
-      <c r="L8">
-        <v>14</v>
-      </c>
-      <c r="M8">
-        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -9184,35 +9092,35 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C2">
-        <v>1</v>
-      </c>
-      <c r="D2">
-        <v>2</v>
+      <c r="F2">
+        <v>1</v>
       </c>
       <c r="G2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H2">
         <v>1</v>
       </c>
       <c r="I2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K2">
-        <v>2</v>
-      </c>
-      <c r="L2">
-        <v>5</v>
+        <v>3</v>
+      </c>
+      <c r="M2">
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
+      <c r="B3">
+        <v>1</v>
+      </c>
       <c r="C3">
         <v>1</v>
       </c>
@@ -9220,21 +9128,24 @@
         <v>1</v>
       </c>
       <c r="E3">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="G3">
+        <v>2</v>
       </c>
       <c r="H3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K3">
         <v>1</v>
       </c>
-      <c r="L3">
+      <c r="M3">
         <v>1</v>
       </c>
     </row>
@@ -9242,27 +9153,15 @@
       <c r="A4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D4">
-        <v>1</v>
-      </c>
-      <c r="E4">
-        <v>1</v>
-      </c>
       <c r="J4">
-        <v>1</v>
-      </c>
-      <c r="L4">
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C5">
-        <v>1</v>
-      </c>
-      <c r="J5">
+        <v>6</v>
+      </c>
+      <c r="K5">
         <v>1</v>
       </c>
     </row>
@@ -9271,40 +9170,40 @@
         <v>8</v>
       </c>
       <c r="B6">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C6">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D6">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E6">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F6">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G6">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H6">
+        <v>6</v>
+      </c>
+      <c r="I6">
         <v>8</v>
       </c>
-      <c r="I6">
-        <v>5</v>
-      </c>
       <c r="J6">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="K6">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="L6">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="M6">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -9312,40 +9211,40 @@
         <v>9</v>
       </c>
       <c r="B7">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="C7">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="D7">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="E7">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="F7">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="G7">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="H7">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I7">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="J7">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="K7">
+        <v>12</v>
+      </c>
+      <c r="L7">
         <v>10</v>
       </c>
-      <c r="L7">
-        <v>12</v>
-      </c>
       <c r="M7">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -9353,40 +9252,40 @@
         <v>10</v>
       </c>
       <c r="B8">
+        <v>29</v>
+      </c>
+      <c r="C8">
+        <v>30</v>
+      </c>
+      <c r="D8">
+        <v>29</v>
+      </c>
+      <c r="E8">
+        <v>26</v>
+      </c>
+      <c r="F8">
+        <v>28</v>
+      </c>
+      <c r="G8">
+        <v>17</v>
+      </c>
+      <c r="H8">
+        <v>15</v>
+      </c>
+      <c r="I8">
+        <v>27</v>
+      </c>
+      <c r="J8">
         <v>19</v>
-      </c>
-      <c r="C8">
-        <v>32</v>
-      </c>
-      <c r="D8">
-        <v>42</v>
-      </c>
-      <c r="E8">
-        <v>37</v>
-      </c>
-      <c r="F8">
-        <v>23</v>
-      </c>
-      <c r="G8">
-        <v>26</v>
-      </c>
-      <c r="H8">
-        <v>18</v>
-      </c>
-      <c r="I8">
-        <v>23</v>
-      </c>
-      <c r="J8">
-        <v>31</v>
       </c>
       <c r="K8">
         <v>20</v>
       </c>
       <c r="L8">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="M8">
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -10721,76 +10620,76 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2">
-        <v>2</v>
-      </c>
       <c r="C2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D2">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F2">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="G2">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="H2">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="I2">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="J2">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="K2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L2">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="M2">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
+      <c r="B3">
+        <v>5</v>
+      </c>
       <c r="C3">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D3">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="E3">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="F3">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="G3">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="H3">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="I3">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="J3">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="K3">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="L3">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="M3">
         <v>5</v>
@@ -10798,17 +10697,38 @@
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E4">
-        <v>1</v>
+        <v>5</v>
+      </c>
+      <c r="B4">
+        <v>1</v>
+      </c>
+      <c r="D4">
+        <v>1</v>
+      </c>
+      <c r="H4">
+        <v>2</v>
+      </c>
+      <c r="J4">
+        <v>1</v>
+      </c>
+      <c r="K4">
+        <v>1</v>
+      </c>
+      <c r="L4">
+        <v>1</v>
+      </c>
+      <c r="M4">
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5">
+        <v>6</v>
+      </c>
+      <c r="H5">
+        <v>1</v>
+      </c>
+      <c r="I5">
         <v>1</v>
       </c>
     </row>
@@ -10816,7 +10736,10 @@
       <c r="A6" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C6">
+      <c r="G6">
+        <v>1</v>
+      </c>
+      <c r="J6">
         <v>1</v>
       </c>
     </row>
@@ -10825,40 +10748,40 @@
         <v>8</v>
       </c>
       <c r="B7">
-        <v>5</v>
+        <v>34</v>
       </c>
       <c r="C7">
-        <v>9</v>
+        <v>45</v>
       </c>
       <c r="D7">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="E7">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="F7">
-        <v>6</v>
+        <v>42</v>
       </c>
       <c r="G7">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="H7">
-        <v>7</v>
+        <v>26</v>
       </c>
       <c r="I7">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="J7">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="K7">
-        <v>11</v>
+        <v>44</v>
       </c>
       <c r="L7">
-        <v>8</v>
+        <v>44</v>
       </c>
       <c r="M7">
-        <v>1</v>
+        <v>16</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -10866,40 +10789,40 @@
         <v>9</v>
       </c>
       <c r="B8">
-        <v>30</v>
+        <v>71</v>
       </c>
       <c r="C8">
-        <v>26</v>
+        <v>91</v>
       </c>
       <c r="D8">
-        <v>15</v>
+        <v>57</v>
       </c>
       <c r="E8">
-        <v>24</v>
+        <v>65</v>
       </c>
       <c r="F8">
-        <v>18</v>
+        <v>75</v>
       </c>
       <c r="G8">
-        <v>16</v>
+        <v>41</v>
       </c>
       <c r="H8">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="I8">
-        <v>13</v>
+        <v>45</v>
       </c>
       <c r="J8">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="K8">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="L8">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="M8">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -10907,40 +10830,40 @@
         <v>10</v>
       </c>
       <c r="B9">
-        <v>38</v>
+        <v>111</v>
       </c>
       <c r="C9">
-        <v>41</v>
+        <v>142</v>
       </c>
       <c r="D9">
-        <v>19</v>
+        <v>107</v>
       </c>
       <c r="E9">
+        <v>98</v>
+      </c>
+      <c r="F9">
+        <v>138</v>
+      </c>
+      <c r="G9">
+        <v>92</v>
+      </c>
+      <c r="H9">
+        <v>76</v>
+      </c>
+      <c r="I9">
+        <v>90</v>
+      </c>
+      <c r="J9">
+        <v>69</v>
+      </c>
+      <c r="K9">
+        <v>95</v>
+      </c>
+      <c r="L9">
+        <v>103</v>
+      </c>
+      <c r="M9">
         <v>36</v>
-      </c>
-      <c r="F9">
-        <v>28</v>
-      </c>
-      <c r="G9">
-        <v>38</v>
-      </c>
-      <c r="H9">
-        <v>28</v>
-      </c>
-      <c r="I9">
-        <v>23</v>
-      </c>
-      <c r="J9">
-        <v>31</v>
-      </c>
-      <c r="K9">
-        <v>35</v>
-      </c>
-      <c r="L9">
-        <v>33</v>
-      </c>
-      <c r="M9">
-        <v>16</v>
       </c>
     </row>
   </sheetData>
@@ -13252,10 +13175,10 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L6"/>
+  <dimension ref="A1:M9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="18.7109375" customWidth="1"/>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
     <col min="2" max="2" width="4.7109375" customWidth="1"/>
     <col min="3" max="3" width="4.7109375" customWidth="1"/>
     <col min="4" max="4" width="4.7109375" customWidth="1"/>
@@ -13267,9 +13190,10 @@
     <col min="10" max="10" width="4.7109375" customWidth="1"/>
     <col min="11" max="11" width="4.7109375" customWidth="1"/>
     <col min="12" max="12" width="4.7109375" customWidth="1"/>
+    <col min="13" max="13" width="4.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:13">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -13292,33 +13216,66 @@
         <v>2020</v>
       </c>
       <c r="H1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="I1" s="1">
         <v>2022</v>
       </c>
-      <c r="I1" s="1">
+      <c r="J1" s="1">
         <v>2023</v>
       </c>
-      <c r="J1" s="1">
+      <c r="K1" s="1">
         <v>2024</v>
       </c>
-      <c r="K1" s="1">
+      <c r="L1" s="1">
         <v>2025</v>
       </c>
-      <c r="L1" s="1">
+      <c r="M1" s="1">
         <v>2026</v>
       </c>
     </row>
-    <row r="2" spans="1:12">
+    <row r="2" spans="1:13">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
+      <c r="B2">
+        <v>2</v>
+      </c>
+      <c r="C2">
+        <v>4</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="E2">
+        <v>2</v>
+      </c>
       <c r="F2">
         <v>1</v>
       </c>
+      <c r="G2">
+        <v>2</v>
+      </c>
+      <c r="H2">
+        <v>5</v>
+      </c>
       <c r="I2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12">
+        <v>2</v>
+      </c>
+      <c r="J2">
+        <v>4</v>
+      </c>
+      <c r="K2">
+        <v>5</v>
+      </c>
+      <c r="L2">
+        <v>2</v>
+      </c>
+      <c r="M2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
@@ -13326,100 +13283,181 @@
         <v>1</v>
       </c>
       <c r="D3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E3">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="F3">
+        <v>3</v>
       </c>
       <c r="G3">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H3">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="I3">
+        <v>4</v>
+      </c>
+      <c r="J3">
+        <v>7</v>
+      </c>
+      <c r="K3">
+        <v>7</v>
       </c>
       <c r="L3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12">
+        <v>3</v>
+      </c>
+      <c r="M3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B4">
-        <v>4</v>
-      </c>
-      <c r="D4">
-        <v>2</v>
-      </c>
-      <c r="E4">
-        <v>2</v>
-      </c>
-      <c r="G4">
-        <v>2</v>
-      </c>
-      <c r="H4">
-        <v>1</v>
-      </c>
-      <c r="I4">
-        <v>3</v>
-      </c>
-      <c r="J4">
-        <v>3</v>
-      </c>
-      <c r="K4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12">
-      <c r="A5" s="1" t="s">
+      <c r="B7">
+        <v>5</v>
+      </c>
+      <c r="C7">
         <v>9</v>
       </c>
-      <c r="F5">
-        <v>2</v>
-      </c>
-      <c r="I5">
-        <v>3</v>
-      </c>
-      <c r="K5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12">
-      <c r="A6" s="1" t="s">
+      <c r="D7">
+        <v>1</v>
+      </c>
+      <c r="E7">
+        <v>6</v>
+      </c>
+      <c r="F7">
+        <v>6</v>
+      </c>
+      <c r="G7">
+        <v>14</v>
+      </c>
+      <c r="H7">
+        <v>7</v>
+      </c>
+      <c r="I7">
+        <v>4</v>
+      </c>
+      <c r="J7">
+        <v>5</v>
+      </c>
+      <c r="K7">
+        <v>11</v>
+      </c>
+      <c r="L7">
+        <v>8</v>
+      </c>
+      <c r="M7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13">
+      <c r="A8" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B8">
+        <v>30</v>
+      </c>
+      <c r="C8">
+        <v>26</v>
+      </c>
+      <c r="D8">
+        <v>15</v>
+      </c>
+      <c r="E8">
+        <v>24</v>
+      </c>
+      <c r="F8">
+        <v>18</v>
+      </c>
+      <c r="G8">
+        <v>16</v>
+      </c>
+      <c r="H8">
+        <v>14</v>
+      </c>
+      <c r="I8">
+        <v>13</v>
+      </c>
+      <c r="J8">
+        <v>15</v>
+      </c>
+      <c r="K8">
+        <v>12</v>
+      </c>
+      <c r="L8">
+        <v>20</v>
+      </c>
+      <c r="M8">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13">
+      <c r="A9" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B6">
-        <v>4</v>
-      </c>
-      <c r="C6">
-        <v>1</v>
-      </c>
-      <c r="D6">
-        <v>5</v>
-      </c>
-      <c r="E6">
-        <v>3</v>
-      </c>
-      <c r="F6">
-        <v>3</v>
-      </c>
-      <c r="G6">
-        <v>3</v>
-      </c>
-      <c r="H6">
-        <v>2</v>
-      </c>
-      <c r="I6">
-        <v>7</v>
-      </c>
-      <c r="J6">
-        <v>3</v>
-      </c>
-      <c r="K6">
-        <v>2</v>
-      </c>
-      <c r="L6">
-        <v>1</v>
+      <c r="B9">
+        <v>38</v>
+      </c>
+      <c r="C9">
+        <v>41</v>
+      </c>
+      <c r="D9">
+        <v>19</v>
+      </c>
+      <c r="E9">
+        <v>36</v>
+      </c>
+      <c r="F9">
+        <v>28</v>
+      </c>
+      <c r="G9">
+        <v>38</v>
+      </c>
+      <c r="H9">
+        <v>28</v>
+      </c>
+      <c r="I9">
+        <v>23</v>
+      </c>
+      <c r="J9">
+        <v>31</v>
+      </c>
+      <c r="K9">
+        <v>35</v>
+      </c>
+      <c r="L9">
+        <v>33</v>
+      </c>
+      <c r="M9">
+        <v>17</v>
       </c>
     </row>
   </sheetData>
@@ -15981,10 +16019,10 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M9"/>
+  <dimension ref="A1:M10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="19.7109375" customWidth="1"/>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
     <col min="2" max="2" width="4.7109375" customWidth="1"/>
     <col min="3" max="3" width="4.7109375" customWidth="1"/>
     <col min="4" max="4" width="4.7109375" customWidth="1"/>
@@ -16044,26 +16082,41 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
+      <c r="B2">
+        <v>6</v>
+      </c>
+      <c r="C2">
+        <v>3</v>
+      </c>
       <c r="D2">
-        <v>2</v>
+        <v>12</v>
+      </c>
+      <c r="E2">
+        <v>5</v>
+      </c>
+      <c r="F2">
+        <v>8</v>
+      </c>
+      <c r="G2">
+        <v>4</v>
       </c>
       <c r="H2">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="I2">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="J2">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="K2">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="L2">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="M2">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -16071,187 +16124,246 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="C3">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="D3">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="E3">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="F3">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="G3">
-        <v>2</v>
+        <v>26</v>
       </c>
       <c r="H3">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="I3">
-        <v>2</v>
+        <v>32</v>
       </c>
       <c r="J3">
-        <v>7</v>
+        <v>40</v>
       </c>
       <c r="K3">
-        <v>3</v>
+        <v>26</v>
       </c>
       <c r="L3">
-        <v>5</v>
+        <v>34</v>
       </c>
       <c r="M3">
-        <v>2</v>
+        <v>17</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B4">
+      <c r="G4">
+        <v>1</v>
+      </c>
+      <c r="J4">
+        <v>2</v>
+      </c>
+      <c r="K4">
+        <v>1</v>
+      </c>
+      <c r="L4">
+        <v>1</v>
+      </c>
+      <c r="M4">
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C5">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="D5">
+        <v>1</v>
+      </c>
+      <c r="E5">
+        <v>2</v>
+      </c>
+      <c r="F5">
+        <v>1</v>
+      </c>
+      <c r="H5">
+        <v>2</v>
+      </c>
+      <c r="I5">
+        <v>4</v>
+      </c>
+      <c r="J5">
+        <v>3</v>
+      </c>
+      <c r="K5">
+        <v>2</v>
+      </c>
+      <c r="L5">
+        <v>5</v>
+      </c>
+      <c r="M5">
+        <v>4</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
+      </c>
+      <c r="G6">
+        <v>1</v>
       </c>
       <c r="H6">
+        <v>2</v>
+      </c>
+      <c r="J6">
+        <v>2</v>
+      </c>
+      <c r="L6">
+        <v>2</v>
+      </c>
+      <c r="M6">
         <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B7">
-        <v>6</v>
-      </c>
-      <c r="C7">
-        <v>4</v>
-      </c>
-      <c r="D7">
-        <v>5</v>
-      </c>
-      <c r="E7">
-        <v>4</v>
-      </c>
-      <c r="F7">
-        <v>13</v>
-      </c>
-      <c r="G7">
-        <v>8</v>
-      </c>
-      <c r="H7">
-        <v>4</v>
-      </c>
-      <c r="I7">
-        <v>9</v>
-      </c>
-      <c r="J7">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K7">
-        <v>22</v>
-      </c>
-      <c r="L7">
-        <v>22</v>
-      </c>
-      <c r="M7">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:13">
       <c r="A8" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B8">
-        <v>7</v>
+        <v>30</v>
       </c>
       <c r="C8">
-        <v>11</v>
+        <v>44</v>
       </c>
       <c r="D8">
+        <v>49</v>
+      </c>
+      <c r="E8">
+        <v>67</v>
+      </c>
+      <c r="F8">
+        <v>69</v>
+      </c>
+      <c r="G8">
+        <v>57</v>
+      </c>
+      <c r="H8">
+        <v>80</v>
+      </c>
+      <c r="I8">
+        <v>80</v>
+      </c>
+      <c r="J8">
+        <v>64</v>
+      </c>
+      <c r="K8">
+        <v>48</v>
+      </c>
+      <c r="L8">
+        <v>44</v>
+      </c>
+      <c r="M8">
         <v>21</v>
-      </c>
-      <c r="E8">
-        <v>19</v>
-      </c>
-      <c r="F8">
-        <v>15</v>
-      </c>
-      <c r="G8">
-        <v>4</v>
-      </c>
-      <c r="H8">
-        <v>3</v>
-      </c>
-      <c r="I8">
-        <v>3</v>
-      </c>
-      <c r="J8">
-        <v>12</v>
-      </c>
-      <c r="K8">
-        <v>7</v>
-      </c>
-      <c r="L8">
-        <v>9</v>
-      </c>
-      <c r="M8">
-        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:13">
       <c r="A9" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B9">
+        <v>233</v>
+      </c>
+      <c r="C9">
+        <v>354</v>
+      </c>
+      <c r="D9">
+        <v>538</v>
+      </c>
+      <c r="E9">
+        <v>705</v>
+      </c>
+      <c r="F9">
+        <v>568</v>
+      </c>
+      <c r="G9">
+        <v>168</v>
+      </c>
+      <c r="H9">
+        <v>116</v>
+      </c>
+      <c r="I9">
+        <v>194</v>
+      </c>
+      <c r="J9">
+        <v>122</v>
+      </c>
+      <c r="K9">
+        <v>114</v>
+      </c>
+      <c r="L9">
+        <v>95</v>
+      </c>
+      <c r="M9">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13">
+      <c r="A10" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B9">
-        <v>16</v>
-      </c>
-      <c r="C9">
-        <v>19</v>
-      </c>
-      <c r="D9">
-        <v>29</v>
-      </c>
-      <c r="E9">
-        <v>27</v>
-      </c>
-      <c r="F9">
-        <v>29</v>
-      </c>
-      <c r="G9">
-        <v>14</v>
-      </c>
-      <c r="H9">
-        <v>10</v>
-      </c>
-      <c r="I9">
-        <v>15</v>
-      </c>
-      <c r="J9">
-        <v>25</v>
-      </c>
-      <c r="K9">
-        <v>35</v>
-      </c>
-      <c r="L9">
-        <v>37</v>
-      </c>
-      <c r="M9">
-        <v>12</v>
+      <c r="B10">
+        <v>282</v>
+      </c>
+      <c r="C10">
+        <v>416</v>
+      </c>
+      <c r="D10">
+        <v>617</v>
+      </c>
+      <c r="E10">
+        <v>797</v>
+      </c>
+      <c r="F10">
+        <v>660</v>
+      </c>
+      <c r="G10">
+        <v>257</v>
+      </c>
+      <c r="H10">
+        <v>236</v>
+      </c>
+      <c r="I10">
+        <v>324</v>
+      </c>
+      <c r="J10">
+        <v>255</v>
+      </c>
+      <c r="K10">
+        <v>207</v>
+      </c>
+      <c r="L10">
+        <v>196</v>
+      </c>
+      <c r="M10">
+        <v>94</v>
       </c>
     </row>
   </sheetData>
@@ -18541,97 +18653,82 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2">
-        <v>1</v>
-      </c>
       <c r="C2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D2">
-        <v>1</v>
-      </c>
-      <c r="E2">
-        <v>1</v>
-      </c>
-      <c r="F2">
         <v>2</v>
       </c>
       <c r="G2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L2">
-        <v>4</v>
-      </c>
-      <c r="M2">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B3">
-        <v>1</v>
-      </c>
       <c r="C3">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
       </c>
       <c r="E3">
-        <v>2</v>
-      </c>
-      <c r="F3">
-        <v>5</v>
-      </c>
-      <c r="G3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I3">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J3">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K3">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="L3">
-        <v>7</v>
-      </c>
-      <c r="M3">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4">
-        <v>1</v>
-      </c>
-      <c r="I4">
+        <v>5</v>
+      </c>
+      <c r="D4">
+        <v>1</v>
+      </c>
+      <c r="E4">
+        <v>1</v>
+      </c>
+      <c r="J4">
+        <v>1</v>
+      </c>
+      <c r="L4">
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="H5">
+        <v>7</v>
+      </c>
+      <c r="C5">
         <v>1</v>
       </c>
       <c r="J5">
@@ -18643,40 +18740,40 @@
         <v>8</v>
       </c>
       <c r="B6">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="C6">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="D6">
-        <v>28</v>
+        <v>3</v>
       </c>
       <c r="E6">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="F6">
-        <v>35</v>
+        <v>5</v>
       </c>
       <c r="G6">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="H6">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I6">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="J6">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="K6">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="L6">
         <v>7</v>
       </c>
       <c r="M6">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -18687,37 +18784,37 @@
         <v>17</v>
       </c>
       <c r="C7">
+        <v>24</v>
+      </c>
+      <c r="D7">
         <v>35</v>
       </c>
-      <c r="D7">
-        <v>49</v>
-      </c>
       <c r="E7">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="F7">
-        <v>58</v>
+        <v>18</v>
       </c>
       <c r="G7">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="H7">
         <v>8</v>
       </c>
       <c r="I7">
+        <v>16</v>
+      </c>
+      <c r="J7">
+        <v>15</v>
+      </c>
+      <c r="K7">
         <v>10</v>
       </c>
-      <c r="J7">
+      <c r="L7">
+        <v>12</v>
+      </c>
+      <c r="M7">
         <v>8</v>
-      </c>
-      <c r="K7">
-        <v>11</v>
-      </c>
-      <c r="L7">
-        <v>7</v>
-      </c>
-      <c r="M7">
-        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -18725,40 +18822,40 @@
         <v>10</v>
       </c>
       <c r="B8">
+        <v>19</v>
+      </c>
+      <c r="C8">
         <v>32</v>
       </c>
-      <c r="C8">
-        <v>61</v>
-      </c>
       <c r="D8">
-        <v>78</v>
+        <v>42</v>
       </c>
       <c r="E8">
-        <v>68</v>
+        <v>37</v>
       </c>
       <c r="F8">
-        <v>100</v>
+        <v>23</v>
       </c>
       <c r="G8">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="H8">
+        <v>18</v>
+      </c>
+      <c r="I8">
+        <v>23</v>
+      </c>
+      <c r="J8">
+        <v>31</v>
+      </c>
+      <c r="K8">
+        <v>20</v>
+      </c>
+      <c r="L8">
         <v>26</v>
       </c>
-      <c r="I8">
-        <v>32</v>
-      </c>
-      <c r="J8">
-        <v>20</v>
-      </c>
-      <c r="K8">
-        <v>29</v>
-      </c>
-      <c r="L8">
-        <v>25</v>
-      </c>
       <c r="M8">
-        <v>14</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -21082,10 +21179,10 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M7"/>
+  <dimension ref="A1:L6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="1" max="1" width="18.7109375" customWidth="1"/>
     <col min="2" max="2" width="4.7109375" customWidth="1"/>
     <col min="3" max="3" width="4.7109375" customWidth="1"/>
     <col min="4" max="4" width="4.7109375" customWidth="1"/>
@@ -21097,10 +21194,9 @@
     <col min="10" max="10" width="4.7109375" customWidth="1"/>
     <col min="11" max="11" width="4.7109375" customWidth="1"/>
     <col min="12" max="12" width="4.7109375" customWidth="1"/>
-    <col min="13" max="13" width="4.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:12">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -21123,146 +21219,125 @@
         <v>2020</v>
       </c>
       <c r="H1" s="1">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="I1" s="1">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="J1" s="1">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="K1" s="1">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="L1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="M1" s="1">
         <v>2026</v>
       </c>
     </row>
-    <row r="2" spans="1:13">
+    <row r="2" spans="1:12">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2">
-        <v>1</v>
-      </c>
-      <c r="G2">
+      <c r="F2">
         <v>1</v>
       </c>
       <c r="I2">
         <v>1</v>
       </c>
-      <c r="K2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
+    </row>
+    <row r="3" spans="1:12">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B3">
-        <v>1</v>
-      </c>
       <c r="C3">
         <v>1</v>
       </c>
-      <c r="F3">
+      <c r="D3">
+        <v>3</v>
+      </c>
+      <c r="E3">
         <v>1</v>
       </c>
       <c r="G3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H3">
         <v>1</v>
       </c>
-      <c r="I3">
-        <v>1</v>
-      </c>
-      <c r="J3">
-        <v>1</v>
-      </c>
       <c r="L3">
-        <v>2</v>
-      </c>
-      <c r="M3">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12">
       <c r="A4" s="1" t="s">
-        <v>5</v>
+        <v>8</v>
+      </c>
+      <c r="B4">
+        <v>4</v>
+      </c>
+      <c r="D4">
+        <v>2</v>
+      </c>
+      <c r="E4">
+        <v>2</v>
+      </c>
+      <c r="G4">
+        <v>2</v>
+      </c>
+      <c r="H4">
+        <v>1</v>
+      </c>
+      <c r="I4">
+        <v>3</v>
+      </c>
+      <c r="J4">
+        <v>3</v>
       </c>
       <c r="K4">
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:13">
+    <row r="5" spans="1:12">
       <c r="A5" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5">
-        <v>3</v>
-      </c>
-      <c r="C5">
-        <v>4</v>
-      </c>
-      <c r="D5">
-        <v>3</v>
-      </c>
-      <c r="E5">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="F5">
-        <v>6</v>
-      </c>
-      <c r="G5">
-        <v>1</v>
-      </c>
-      <c r="H5">
-        <v>1</v>
-      </c>
-      <c r="J5">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="I5">
+        <v>3</v>
       </c>
       <c r="K5">
         <v>1</v>
       </c>
-      <c r="L5">
-        <v>2</v>
-      </c>
-      <c r="M5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
+    </row>
+    <row r="6" spans="1:12">
       <c r="A6" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B6">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C6">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="D6">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E6">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F6">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="G6">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I6">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J6">
         <v>3</v>
@@ -21271,51 +21346,7 @@
         <v>2</v>
       </c>
       <c r="L6">
-        <v>8</v>
-      </c>
-      <c r="M6">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
-      <c r="A7" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B7">
-        <v>11</v>
-      </c>
-      <c r="C7">
-        <v>16</v>
-      </c>
-      <c r="D7">
-        <v>9</v>
-      </c>
-      <c r="E7">
-        <v>6</v>
-      </c>
-      <c r="F7">
-        <v>18</v>
-      </c>
-      <c r="G7">
-        <v>9</v>
-      </c>
-      <c r="H7">
-        <v>3</v>
-      </c>
-      <c r="I7">
-        <v>7</v>
-      </c>
-      <c r="J7">
-        <v>5</v>
-      </c>
-      <c r="K7">
-        <v>6</v>
-      </c>
-      <c r="L7">
-        <v>12</v>
-      </c>
-      <c r="M7">
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -23059,10 +23090,10 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M10"/>
+  <dimension ref="A1:M9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="1" max="1" width="19.7109375" customWidth="1"/>
     <col min="2" max="2" width="4.7109375" customWidth="1"/>
     <col min="3" max="3" width="4.7109375" customWidth="1"/>
     <col min="4" max="4" width="4.7109375" customWidth="1"/>
@@ -23122,38 +23153,26 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C2">
-        <v>1</v>
-      </c>
       <c r="D2">
-        <v>5</v>
-      </c>
-      <c r="E2">
-        <v>1</v>
-      </c>
-      <c r="F2">
-        <v>3</v>
-      </c>
-      <c r="G2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K2">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="L2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M2">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -23164,31 +23183,31 @@
         <v>2</v>
       </c>
       <c r="C3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D3">
+        <v>1</v>
+      </c>
+      <c r="E3">
+        <v>4</v>
+      </c>
+      <c r="F3">
+        <v>1</v>
+      </c>
+      <c r="G3">
+        <v>2</v>
+      </c>
+      <c r="H3">
+        <v>1</v>
+      </c>
+      <c r="I3">
+        <v>2</v>
+      </c>
+      <c r="J3">
         <v>7</v>
       </c>
-      <c r="E3">
-        <v>3</v>
-      </c>
-      <c r="F3">
-        <v>4</v>
-      </c>
-      <c r="G3">
-        <v>8</v>
-      </c>
-      <c r="H3">
-        <v>4</v>
-      </c>
-      <c r="I3">
-        <v>6</v>
-      </c>
-      <c r="J3">
-        <v>4</v>
-      </c>
       <c r="K3">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="L3">
         <v>5</v>
@@ -23201,170 +23220,147 @@
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="H4">
+      <c r="B4">
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5">
-        <v>1</v>
-      </c>
-      <c r="K5">
+        <v>6</v>
+      </c>
+      <c r="C5">
         <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="G6">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="H6">
-        <v>1</v>
-      </c>
-      <c r="I6">
         <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="B7">
+        <v>6</v>
+      </c>
+      <c r="C7">
+        <v>4</v>
       </c>
       <c r="D7">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E7">
-        <v>1</v>
+        <v>4</v>
+      </c>
+      <c r="F7">
+        <v>13</v>
+      </c>
+      <c r="G7">
+        <v>8</v>
+      </c>
+      <c r="H7">
+        <v>4</v>
+      </c>
+      <c r="I7">
+        <v>9</v>
       </c>
       <c r="J7">
-        <v>2</v>
+        <v>5</v>
+      </c>
+      <c r="K7">
+        <v>22</v>
+      </c>
+      <c r="L7">
+        <v>22</v>
+      </c>
+      <c r="M7">
+        <v>8</v>
       </c>
     </row>
     <row r="8" spans="1:13">
       <c r="A8" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B8">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C8">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D8">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E8">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="F8">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="G8">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="H8">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I8">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="J8">
         <v>12</v>
       </c>
       <c r="K8">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="L8">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="M8">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:13">
       <c r="A9" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B9">
-        <v>43</v>
+        <v>16</v>
       </c>
       <c r="C9">
-        <v>46</v>
+        <v>19</v>
       </c>
       <c r="D9">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="E9">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="F9">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="G9">
+        <v>14</v>
+      </c>
+      <c r="H9">
+        <v>10</v>
+      </c>
+      <c r="I9">
         <v>15</v>
       </c>
-      <c r="H9">
-        <v>17</v>
-      </c>
-      <c r="I9">
-        <v>20</v>
-      </c>
       <c r="J9">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="K9">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="L9">
-        <v>13</v>
+        <v>37</v>
       </c>
       <c r="M9">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13">
-      <c r="A10" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B10">
-        <v>51</v>
-      </c>
-      <c r="C10">
-        <v>57</v>
-      </c>
-      <c r="D10">
-        <v>62</v>
-      </c>
-      <c r="E10">
-        <v>48</v>
-      </c>
-      <c r="F10">
-        <v>60</v>
-      </c>
-      <c r="G10">
-        <v>40</v>
-      </c>
-      <c r="H10">
-        <v>31</v>
-      </c>
-      <c r="I10">
-        <v>44</v>
-      </c>
-      <c r="J10">
-        <v>43</v>
-      </c>
-      <c r="K10">
-        <v>57</v>
-      </c>
-      <c r="L10">
-        <v>40</v>
-      </c>
-      <c r="M10">
-        <v>21</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -25258,7 +25254,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M9"/>
+  <dimension ref="A1:M8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="23.7109375" customWidth="1"/>
@@ -25325,28 +25321,37 @@
         <v>1</v>
       </c>
       <c r="C2">
+        <v>3</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
+      <c r="F2">
         <v>2</v>
       </c>
       <c r="G2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M2">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -25356,185 +25361,180 @@
       <c r="B3">
         <v>1</v>
       </c>
-      <c r="D3">
+      <c r="C3">
         <v>2</v>
       </c>
       <c r="E3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F3">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I3">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J3">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L3">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="M3">
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="F4">
-        <v>1</v>
-      </c>
-      <c r="J4">
-        <v>1</v>
-      </c>
-      <c r="L4">
-        <v>3</v>
+        <v>3</v>
+      </c>
+      <c r="B4">
+        <v>1</v>
+      </c>
+      <c r="I4">
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="I5">
+        <v>5</v>
+      </c>
+      <c r="H5">
+        <v>1</v>
+      </c>
+      <c r="J5">
         <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6">
+        <v>12</v>
+      </c>
+      <c r="C6">
+        <v>21</v>
+      </c>
+      <c r="D6">
+        <v>28</v>
+      </c>
+      <c r="E6">
+        <v>21</v>
+      </c>
+      <c r="F6">
+        <v>35</v>
+      </c>
+      <c r="G6">
+        <v>12</v>
+      </c>
+      <c r="H6">
+        <v>10</v>
+      </c>
+      <c r="I6">
+        <v>15</v>
+      </c>
+      <c r="J6">
+        <v>5</v>
+      </c>
+      <c r="K6">
+        <v>9</v>
+      </c>
+      <c r="L6">
         <v>7</v>
       </c>
-      <c r="D6">
-        <v>1</v>
+      <c r="M6">
+        <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7">
+        <v>17</v>
+      </c>
+      <c r="C7">
+        <v>35</v>
+      </c>
+      <c r="D7">
+        <v>49</v>
+      </c>
+      <c r="E7">
+        <v>44</v>
+      </c>
+      <c r="F7">
+        <v>58</v>
+      </c>
+      <c r="G7">
+        <v>25</v>
+      </c>
+      <c r="H7">
         <v>8</v>
       </c>
-      <c r="B7">
-        <v>5</v>
-      </c>
-      <c r="C7">
-        <v>1</v>
-      </c>
-      <c r="D7">
-        <v>6</v>
-      </c>
-      <c r="E7">
+      <c r="I7">
+        <v>10</v>
+      </c>
+      <c r="J7">
         <v>8</v>
       </c>
-      <c r="F7">
-        <v>10</v>
-      </c>
-      <c r="G7">
-        <v>8</v>
-      </c>
-      <c r="H7">
-        <v>9</v>
-      </c>
-      <c r="I7">
+      <c r="K7">
+        <v>11</v>
+      </c>
+      <c r="L7">
         <v>7</v>
       </c>
-      <c r="J7">
-        <v>4</v>
-      </c>
-      <c r="K7">
-        <v>7</v>
-      </c>
-      <c r="L7">
-        <v>5</v>
-      </c>
       <c r="M7">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:13">
       <c r="A8" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B8">
+        <v>32</v>
+      </c>
+      <c r="C8">
+        <v>61</v>
+      </c>
+      <c r="D8">
+        <v>78</v>
+      </c>
+      <c r="E8">
+        <v>68</v>
+      </c>
+      <c r="F8">
+        <v>100</v>
+      </c>
+      <c r="G8">
+        <v>43</v>
+      </c>
+      <c r="H8">
+        <v>26</v>
+      </c>
+      <c r="I8">
+        <v>32</v>
+      </c>
+      <c r="J8">
         <v>20</v>
       </c>
-      <c r="C8">
-        <v>23</v>
-      </c>
-      <c r="D8">
-        <v>35</v>
-      </c>
-      <c r="E8">
-        <v>34</v>
-      </c>
-      <c r="F8">
-        <v>40</v>
-      </c>
-      <c r="G8">
-        <v>20</v>
-      </c>
-      <c r="H8">
-        <v>9</v>
-      </c>
-      <c r="I8">
-        <v>27</v>
-      </c>
-      <c r="J8">
-        <v>22</v>
-      </c>
       <c r="K8">
+        <v>29</v>
+      </c>
+      <c r="L8">
+        <v>25</v>
+      </c>
+      <c r="M8">
         <v>14</v>
-      </c>
-      <c r="L8">
-        <v>11</v>
-      </c>
-      <c r="M8">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13">
-      <c r="A9" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B9">
-        <v>27</v>
-      </c>
-      <c r="C9">
-        <v>26</v>
-      </c>
-      <c r="D9">
-        <v>44</v>
-      </c>
-      <c r="E9">
-        <v>43</v>
-      </c>
-      <c r="F9">
-        <v>52</v>
-      </c>
-      <c r="G9">
-        <v>32</v>
-      </c>
-      <c r="H9">
-        <v>25</v>
-      </c>
-      <c r="I9">
-        <v>40</v>
-      </c>
-      <c r="J9">
-        <v>30</v>
-      </c>
-      <c r="K9">
-        <v>28</v>
-      </c>
-      <c r="L9">
-        <v>26</v>
-      </c>
-      <c r="M9">
-        <v>18</v>
       </c>
     </row>
   </sheetData>

--- a/output/cta-index-crime-full-year.xlsx
+++ b/output/cta-index-crime-full-year.xlsx
@@ -9,28 +9,28 @@
   <sheets>
     <sheet name="Citywide Totals" sheetId="1" r:id="rId1"/>
     <sheet name="By Neighborhood" sheetId="2" r:id="rId2"/>
-    <sheet name="River North" sheetId="3" r:id="rId3"/>
-    <sheet name="North Lawndale" sheetId="4" r:id="rId4"/>
-    <sheet name="Englewood" sheetId="5" r:id="rId5"/>
-    <sheet name="Uptown" sheetId="6" r:id="rId6"/>
-    <sheet name="Loop" sheetId="7" r:id="rId7"/>
-    <sheet name="Logan Square" sheetId="8" r:id="rId8"/>
-    <sheet name="Riverdale" sheetId="9" r:id="rId9"/>
-    <sheet name="Fuller Park" sheetId="10" r:id="rId10"/>
-    <sheet name="Little Village" sheetId="11" r:id="rId11"/>
-    <sheet name="Chatham" sheetId="12" r:id="rId12"/>
-    <sheet name="West Loop" sheetId="13" r:id="rId13"/>
-    <sheet name="Auburn Gresham" sheetId="14" r:id="rId14"/>
-    <sheet name="Lake View" sheetId="15" r:id="rId15"/>
-    <sheet name="Humboldt Park" sheetId="16" r:id="rId16"/>
-    <sheet name="Austin" sheetId="17" r:id="rId17"/>
-    <sheet name="Roseland" sheetId="18" r:id="rId18"/>
-    <sheet name="Albany Park" sheetId="19" r:id="rId19"/>
-    <sheet name="Woodlawn" sheetId="20" r:id="rId20"/>
-    <sheet name="South Shore" sheetId="21" r:id="rId21"/>
-    <sheet name="Old Town" sheetId="22" r:id="rId22"/>
-    <sheet name="Lincoln Park" sheetId="23" r:id="rId23"/>
-    <sheet name="O'Hare" sheetId="24" r:id="rId24"/>
+    <sheet name="O'Hare" sheetId="3" r:id="rId3"/>
+    <sheet name="River North" sheetId="4" r:id="rId4"/>
+    <sheet name="North Lawndale" sheetId="5" r:id="rId5"/>
+    <sheet name="Englewood" sheetId="6" r:id="rId6"/>
+    <sheet name="Uptown" sheetId="7" r:id="rId7"/>
+    <sheet name="Loop" sheetId="8" r:id="rId8"/>
+    <sheet name="Logan Square" sheetId="9" r:id="rId9"/>
+    <sheet name="Riverdale" sheetId="10" r:id="rId10"/>
+    <sheet name="Fuller Park" sheetId="11" r:id="rId11"/>
+    <sheet name="Little Village" sheetId="12" r:id="rId12"/>
+    <sheet name="Chatham" sheetId="13" r:id="rId13"/>
+    <sheet name="West Loop" sheetId="14" r:id="rId14"/>
+    <sheet name="Auburn Gresham" sheetId="15" r:id="rId15"/>
+    <sheet name="Lake View" sheetId="16" r:id="rId16"/>
+    <sheet name="Humboldt Park" sheetId="17" r:id="rId17"/>
+    <sheet name="Austin" sheetId="18" r:id="rId18"/>
+    <sheet name="Roseland" sheetId="19" r:id="rId19"/>
+    <sheet name="Albany Park" sheetId="20" r:id="rId20"/>
+    <sheet name="Woodlawn" sheetId="21" r:id="rId21"/>
+    <sheet name="South Shore" sheetId="22" r:id="rId22"/>
+    <sheet name="Old Town" sheetId="23" r:id="rId23"/>
+    <sheet name="Lincoln Park" sheetId="24" r:id="rId24"/>
     <sheet name="Near South Side" sheetId="25" r:id="rId25"/>
     <sheet name="Grand Crossing" sheetId="26" r:id="rId26"/>
     <sheet name="Avondale" sheetId="27" r:id="rId27"/>
@@ -1039,7 +1039,7 @@
         <v>25</v>
       </c>
       <c r="M6">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -1197,7 +1197,7 @@
         <v>703</v>
       </c>
       <c r="M10">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -1247,6 +1247,183 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:L6"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="18.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="F2">
+        <v>1</v>
+      </c>
+      <c r="I2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
+      <c r="D3">
+        <v>3</v>
+      </c>
+      <c r="E3">
+        <v>1</v>
+      </c>
+      <c r="G3">
+        <v>1</v>
+      </c>
+      <c r="H3">
+        <v>1</v>
+      </c>
+      <c r="L3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12">
+      <c r="A4" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4">
+        <v>4</v>
+      </c>
+      <c r="D4">
+        <v>2</v>
+      </c>
+      <c r="E4">
+        <v>2</v>
+      </c>
+      <c r="G4">
+        <v>2</v>
+      </c>
+      <c r="H4">
+        <v>1</v>
+      </c>
+      <c r="I4">
+        <v>3</v>
+      </c>
+      <c r="J4">
+        <v>3</v>
+      </c>
+      <c r="K4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12">
+      <c r="A5" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F5">
+        <v>2</v>
+      </c>
+      <c r="I5">
+        <v>3</v>
+      </c>
+      <c r="K5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12">
+      <c r="A6" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6">
+        <v>4</v>
+      </c>
+      <c r="C6">
+        <v>1</v>
+      </c>
+      <c r="D6">
+        <v>5</v>
+      </c>
+      <c r="E6">
+        <v>3</v>
+      </c>
+      <c r="F6">
+        <v>3</v>
+      </c>
+      <c r="G6">
+        <v>3</v>
+      </c>
+      <c r="H6">
+        <v>2</v>
+      </c>
+      <c r="I6">
+        <v>7</v>
+      </c>
+      <c r="J6">
+        <v>3</v>
+      </c>
+      <c r="K6">
+        <v>2</v>
+      </c>
+      <c r="L6">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M9"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -1526,7 +1703,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -1769,7 +1946,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M10"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -2084,7 +2261,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M9"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -2370,7 +2547,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -2643,7 +2820,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M8"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -2939,7 +3116,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M9"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -3224,324 +3401,6 @@
       </c>
       <c r="M9">
         <v>15</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M10"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" customWidth="1"/>
-    <col min="13" max="13" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="M1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2">
-        <v>4</v>
-      </c>
-      <c r="C2">
-        <v>4</v>
-      </c>
-      <c r="D2">
-        <v>3</v>
-      </c>
-      <c r="E2">
-        <v>5</v>
-      </c>
-      <c r="F2">
-        <v>9</v>
-      </c>
-      <c r="G2">
-        <v>3</v>
-      </c>
-      <c r="H2">
-        <v>5</v>
-      </c>
-      <c r="I2">
-        <v>4</v>
-      </c>
-      <c r="J2">
-        <v>8</v>
-      </c>
-      <c r="K2">
-        <v>7</v>
-      </c>
-      <c r="L2">
-        <v>5</v>
-      </c>
-      <c r="M2">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3">
-        <v>4</v>
-      </c>
-      <c r="C3">
-        <v>5</v>
-      </c>
-      <c r="D3">
-        <v>6</v>
-      </c>
-      <c r="E3">
-        <v>7</v>
-      </c>
-      <c r="F3">
-        <v>6</v>
-      </c>
-      <c r="G3">
-        <v>7</v>
-      </c>
-      <c r="H3">
-        <v>8</v>
-      </c>
-      <c r="I3">
-        <v>6</v>
-      </c>
-      <c r="J3">
-        <v>10</v>
-      </c>
-      <c r="K3">
-        <v>12</v>
-      </c>
-      <c r="L3">
-        <v>14</v>
-      </c>
-      <c r="M3">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="I4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5">
-        <v>1</v>
-      </c>
-      <c r="D5">
-        <v>1</v>
-      </c>
-      <c r="E5">
-        <v>1</v>
-      </c>
-      <c r="J5">
-        <v>3</v>
-      </c>
-      <c r="K5">
-        <v>2</v>
-      </c>
-      <c r="M5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="K6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
-      <c r="A7" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="L7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13">
-      <c r="A8" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B8">
-        <v>23</v>
-      </c>
-      <c r="C8">
-        <v>31</v>
-      </c>
-      <c r="D8">
-        <v>22</v>
-      </c>
-      <c r="E8">
-        <v>44</v>
-      </c>
-      <c r="F8">
-        <v>38</v>
-      </c>
-      <c r="G8">
-        <v>24</v>
-      </c>
-      <c r="H8">
-        <v>50</v>
-      </c>
-      <c r="I8">
-        <v>34</v>
-      </c>
-      <c r="J8">
-        <v>26</v>
-      </c>
-      <c r="K8">
-        <v>24</v>
-      </c>
-      <c r="L8">
-        <v>14</v>
-      </c>
-      <c r="M8">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13">
-      <c r="A9" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B9">
-        <v>46</v>
-      </c>
-      <c r="C9">
-        <v>59</v>
-      </c>
-      <c r="D9">
-        <v>33</v>
-      </c>
-      <c r="E9">
-        <v>73</v>
-      </c>
-      <c r="F9">
-        <v>114</v>
-      </c>
-      <c r="G9">
-        <v>58</v>
-      </c>
-      <c r="H9">
-        <v>41</v>
-      </c>
-      <c r="I9">
-        <v>44</v>
-      </c>
-      <c r="J9">
-        <v>20</v>
-      </c>
-      <c r="K9">
-        <v>25</v>
-      </c>
-      <c r="L9">
-        <v>27</v>
-      </c>
-      <c r="M9">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13">
-      <c r="A10" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B10">
-        <v>78</v>
-      </c>
-      <c r="C10">
-        <v>99</v>
-      </c>
-      <c r="D10">
-        <v>65</v>
-      </c>
-      <c r="E10">
-        <v>130</v>
-      </c>
-      <c r="F10">
-        <v>167</v>
-      </c>
-      <c r="G10">
-        <v>92</v>
-      </c>
-      <c r="H10">
-        <v>104</v>
-      </c>
-      <c r="I10">
-        <v>89</v>
-      </c>
-      <c r="J10">
-        <v>67</v>
-      </c>
-      <c r="K10">
-        <v>71</v>
-      </c>
-      <c r="L10">
-        <v>61</v>
-      </c>
-      <c r="M10">
-        <v>53</v>
       </c>
     </row>
   </sheetData>
@@ -3615,40 +3474,40 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C2">
         <v>4</v>
       </c>
       <c r="D2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F2">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="G2">
         <v>3</v>
       </c>
       <c r="H2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I2">
+        <v>4</v>
+      </c>
+      <c r="J2">
+        <v>8</v>
+      </c>
+      <c r="K2">
         <v>7</v>
       </c>
-      <c r="J2">
-        <v>1</v>
-      </c>
-      <c r="K2">
-        <v>3</v>
-      </c>
       <c r="L2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M2">
-        <v>1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -3656,47 +3515,47 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D3">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E3">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F3">
+        <v>6</v>
+      </c>
+      <c r="G3">
         <v>7</v>
       </c>
-      <c r="G3">
+      <c r="H3">
+        <v>8</v>
+      </c>
+      <c r="I3">
         <v>6</v>
       </c>
-      <c r="H3">
-        <v>6</v>
-      </c>
-      <c r="I3">
-        <v>9</v>
-      </c>
       <c r="J3">
+        <v>10</v>
+      </c>
+      <c r="K3">
+        <v>12</v>
+      </c>
+      <c r="L3">
         <v>14</v>
       </c>
-      <c r="K3">
-        <v>7</v>
-      </c>
-      <c r="L3">
-        <v>7</v>
-      </c>
       <c r="M3">
-        <v>4</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="D4">
+        <v>3</v>
+      </c>
+      <c r="I4">
         <v>1</v>
       </c>
     </row>
@@ -3704,33 +3563,30 @@
       <c r="A5" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C5">
-        <v>1</v>
-      </c>
-      <c r="G5">
-        <v>1</v>
-      </c>
-      <c r="I5">
-        <v>2</v>
+      <c r="B5">
+        <v>1</v>
+      </c>
+      <c r="D5">
+        <v>1</v>
+      </c>
+      <c r="E5">
+        <v>1</v>
       </c>
       <c r="J5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K5">
-        <v>1</v>
-      </c>
-      <c r="L5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M5">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D6">
+      <c r="K6">
         <v>1</v>
       </c>
     </row>
@@ -3738,7 +3594,7 @@
       <c r="A7" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="J7">
+      <c r="L7">
         <v>1</v>
       </c>
     </row>
@@ -3747,40 +3603,40 @@
         <v>8</v>
       </c>
       <c r="B8">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="C8">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="D8">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="E8">
+        <v>44</v>
+      </c>
+      <c r="F8">
+        <v>38</v>
+      </c>
+      <c r="G8">
+        <v>24</v>
+      </c>
+      <c r="H8">
+        <v>50</v>
+      </c>
+      <c r="I8">
+        <v>34</v>
+      </c>
+      <c r="J8">
+        <v>26</v>
+      </c>
+      <c r="K8">
+        <v>24</v>
+      </c>
+      <c r="L8">
         <v>14</v>
       </c>
-      <c r="F8">
-        <v>12</v>
-      </c>
-      <c r="G8">
-        <v>14</v>
-      </c>
-      <c r="H8">
-        <v>19</v>
-      </c>
-      <c r="I8">
-        <v>29</v>
-      </c>
-      <c r="J8">
-        <v>19</v>
-      </c>
-      <c r="K8">
-        <v>20</v>
-      </c>
-      <c r="L8">
-        <v>26</v>
-      </c>
       <c r="M8">
-        <v>6</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -3788,40 +3644,40 @@
         <v>9</v>
       </c>
       <c r="B9">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="C9">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="D9">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="E9">
-        <v>51</v>
+        <v>73</v>
       </c>
       <c r="F9">
-        <v>54</v>
+        <v>114</v>
       </c>
       <c r="G9">
-        <v>32</v>
+        <v>58</v>
       </c>
       <c r="H9">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="I9">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="J9">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="K9">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="L9">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="M9">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -3829,40 +3685,40 @@
         <v>10</v>
       </c>
       <c r="B10">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="C10">
-        <v>70</v>
+        <v>99</v>
       </c>
       <c r="D10">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="E10">
-        <v>74</v>
+        <v>130</v>
       </c>
       <c r="F10">
-        <v>77</v>
+        <v>167</v>
       </c>
       <c r="G10">
-        <v>56</v>
+        <v>92</v>
       </c>
       <c r="H10">
-        <v>60</v>
+        <v>104</v>
       </c>
       <c r="I10">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="J10">
-        <v>76</v>
+        <v>67</v>
       </c>
       <c r="K10">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="L10">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="M10">
-        <v>27</v>
+        <v>53</v>
       </c>
     </row>
   </sheetData>
@@ -3872,7 +3728,7 @@
 
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M7"/>
+  <dimension ref="A1:M10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="23.7109375" customWidth="1"/>
@@ -3935,29 +3791,41 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
+      <c r="B2">
+        <v>2</v>
+      </c>
+      <c r="C2">
+        <v>4</v>
+      </c>
       <c r="D2">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="E2">
+        <v>4</v>
       </c>
       <c r="F2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G2">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="H2">
+        <v>6</v>
       </c>
       <c r="I2">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="J2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -3965,153 +3833,213 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C3">
-        <v>1</v>
+        <v>4</v>
+      </c>
+      <c r="D3">
+        <v>2</v>
+      </c>
+      <c r="E3">
+        <v>5</v>
+      </c>
+      <c r="F3">
+        <v>7</v>
       </c>
       <c r="G3">
-        <v>2</v>
+        <v>6</v>
+      </c>
+      <c r="H3">
+        <v>6</v>
       </c>
       <c r="I3">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="J3">
-        <v>1</v>
+        <v>14</v>
+      </c>
+      <c r="K3">
+        <v>7</v>
       </c>
       <c r="L3">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="M3">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="E4">
-        <v>2</v>
-      </c>
-      <c r="J4">
-        <v>1</v>
-      </c>
-      <c r="K4">
+        <v>4</v>
+      </c>
+      <c r="D4">
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C5">
         <v>1</v>
       </c>
-      <c r="D5">
-        <v>2</v>
-      </c>
-      <c r="E5">
-        <v>2</v>
-      </c>
       <c r="G5">
         <v>1</v>
       </c>
       <c r="I5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K5">
-        <v>4</v>
+        <v>1</v>
+      </c>
+      <c r="L5">
+        <v>1</v>
       </c>
       <c r="M5">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B6">
-        <v>8</v>
-      </c>
-      <c r="C6">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="D6">
-        <v>10</v>
-      </c>
-      <c r="E6">
-        <v>9</v>
-      </c>
-      <c r="F6">
-        <v>9</v>
-      </c>
-      <c r="G6">
-        <v>8</v>
-      </c>
-      <c r="H6">
-        <v>1</v>
-      </c>
-      <c r="I6">
-        <v>4</v>
-      </c>
-      <c r="J6">
-        <v>5</v>
-      </c>
-      <c r="K6">
-        <v>8</v>
-      </c>
-      <c r="L6">
-        <v>3</v>
-      </c>
-      <c r="M6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="J7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13">
+      <c r="A8" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8">
+        <v>19</v>
+      </c>
+      <c r="C8">
+        <v>16</v>
+      </c>
+      <c r="D8">
+        <v>11</v>
+      </c>
+      <c r="E8">
+        <v>14</v>
+      </c>
+      <c r="F8">
+        <v>12</v>
+      </c>
+      <c r="G8">
+        <v>14</v>
+      </c>
+      <c r="H8">
+        <v>19</v>
+      </c>
+      <c r="I8">
+        <v>29</v>
+      </c>
+      <c r="J8">
+        <v>19</v>
+      </c>
+      <c r="K8">
+        <v>20</v>
+      </c>
+      <c r="L8">
+        <v>26</v>
+      </c>
+      <c r="M8">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13">
+      <c r="A9" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B9">
+        <v>56</v>
+      </c>
+      <c r="C9">
+        <v>45</v>
+      </c>
+      <c r="D9">
+        <v>42</v>
+      </c>
+      <c r="E9">
+        <v>51</v>
+      </c>
+      <c r="F9">
+        <v>54</v>
+      </c>
+      <c r="G9">
+        <v>32</v>
+      </c>
+      <c r="H9">
+        <v>29</v>
+      </c>
+      <c r="I9">
+        <v>35</v>
+      </c>
+      <c r="J9">
+        <v>40</v>
+      </c>
+      <c r="K9">
+        <v>37</v>
+      </c>
+      <c r="L9">
+        <v>25</v>
+      </c>
+      <c r="M9">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13">
+      <c r="A10" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B7">
-        <v>10</v>
-      </c>
-      <c r="C7">
-        <v>15</v>
-      </c>
-      <c r="D7">
-        <v>13</v>
-      </c>
-      <c r="E7">
-        <v>13</v>
-      </c>
-      <c r="F7">
-        <v>10</v>
-      </c>
-      <c r="G7">
-        <v>12</v>
-      </c>
-      <c r="H7">
-        <v>1</v>
-      </c>
-      <c r="I7">
-        <v>8</v>
-      </c>
-      <c r="J7">
-        <v>14</v>
-      </c>
-      <c r="K7">
-        <v>15</v>
-      </c>
-      <c r="L7">
-        <v>6</v>
-      </c>
-      <c r="M7">
-        <v>7</v>
+      <c r="B10">
+        <v>82</v>
+      </c>
+      <c r="C10">
+        <v>70</v>
+      </c>
+      <c r="D10">
+        <v>59</v>
+      </c>
+      <c r="E10">
+        <v>74</v>
+      </c>
+      <c r="F10">
+        <v>77</v>
+      </c>
+      <c r="G10">
+        <v>56</v>
+      </c>
+      <c r="H10">
+        <v>60</v>
+      </c>
+      <c r="I10">
+        <v>82</v>
+      </c>
+      <c r="J10">
+        <v>76</v>
+      </c>
+      <c r="K10">
+        <v>68</v>
+      </c>
+      <c r="L10">
+        <v>62</v>
+      </c>
+      <c r="M10">
+        <v>28</v>
       </c>
     </row>
   </sheetData>
@@ -4560,7 +4488,7 @@
         <v>3</v>
       </c>
       <c r="M11">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="12" spans="1:13">
@@ -6135,7 +6063,7 @@
         <v>196</v>
       </c>
       <c r="M53">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="54" spans="1:13">
@@ -6412,7 +6340,7 @@
         <v>16</v>
       </c>
       <c r="M61">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="62" spans="1:13">
@@ -6699,7 +6627,7 @@
         <v>21</v>
       </c>
       <c r="M68">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="69" spans="1:13">
@@ -7050,7 +6978,7 @@
         <v>62</v>
       </c>
       <c r="M77">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="78" spans="1:13">
@@ -8086,23 +8014,29 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2">
-        <v>3</v>
-      </c>
-      <c r="E2">
-        <v>2</v>
+      <c r="D2">
+        <v>1</v>
       </c>
       <c r="F2">
         <v>1</v>
       </c>
       <c r="G2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I2">
         <v>2</v>
       </c>
+      <c r="J2">
+        <v>4</v>
+      </c>
+      <c r="K2">
+        <v>2</v>
+      </c>
       <c r="L2">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="M2">
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -8110,44 +8044,38 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C3">
         <v>1</v>
       </c>
-      <c r="D3">
-        <v>5</v>
-      </c>
-      <c r="F3">
-        <v>2</v>
-      </c>
       <c r="G3">
-        <v>3</v>
-      </c>
-      <c r="H3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I3">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J3">
-        <v>5</v>
-      </c>
-      <c r="K3">
-        <v>5</v>
+        <v>1</v>
+      </c>
+      <c r="L3">
+        <v>1</v>
       </c>
       <c r="M3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F4">
-        <v>1</v>
-      </c>
-      <c r="H4">
+      <c r="E4">
+        <v>2</v>
+      </c>
+      <c r="J4">
+        <v>1</v>
+      </c>
+      <c r="K4">
         <v>1</v>
       </c>
     </row>
@@ -8156,36 +8084,27 @@
         <v>8</v>
       </c>
       <c r="B5">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="C5">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="D5">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E5">
-        <v>9</v>
-      </c>
-      <c r="F5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G5">
-        <v>2</v>
-      </c>
-      <c r="H5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J5">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="K5">
-        <v>7</v>
-      </c>
-      <c r="L5">
         <v>4</v>
       </c>
       <c r="M5">
@@ -8197,40 +8116,40 @@
         <v>9</v>
       </c>
       <c r="B6">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="C6">
+        <v>13</v>
+      </c>
+      <c r="D6">
         <v>10</v>
       </c>
-      <c r="D6">
-        <v>17</v>
-      </c>
       <c r="E6">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="F6">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="G6">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H6">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I6">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J6">
+        <v>5</v>
+      </c>
+      <c r="K6">
         <v>8</v>
       </c>
-      <c r="K6">
-        <v>3</v>
-      </c>
       <c r="L6">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M6">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -8238,31 +8157,31 @@
         <v>10</v>
       </c>
       <c r="B7">
-        <v>33</v>
+        <v>10</v>
       </c>
       <c r="C7">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="D7">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="E7">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="F7">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="G7">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H7">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="I7">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="J7">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="K7">
         <v>15</v>
@@ -8271,7 +8190,7 @@
         <v>6</v>
       </c>
       <c r="M7">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -8280,6 +8199,264 @@
 </file>
 
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:M7"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+    <col min="13" max="13" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="M1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>3</v>
+      </c>
+      <c r="E2">
+        <v>2</v>
+      </c>
+      <c r="F2">
+        <v>1</v>
+      </c>
+      <c r="G2">
+        <v>2</v>
+      </c>
+      <c r="I2">
+        <v>2</v>
+      </c>
+      <c r="L2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>2</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
+      <c r="D3">
+        <v>5</v>
+      </c>
+      <c r="F3">
+        <v>2</v>
+      </c>
+      <c r="G3">
+        <v>3</v>
+      </c>
+      <c r="H3">
+        <v>3</v>
+      </c>
+      <c r="I3">
+        <v>5</v>
+      </c>
+      <c r="J3">
+        <v>5</v>
+      </c>
+      <c r="K3">
+        <v>5</v>
+      </c>
+      <c r="M3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F4">
+        <v>1</v>
+      </c>
+      <c r="H4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5">
+        <v>11</v>
+      </c>
+      <c r="C5">
+        <v>12</v>
+      </c>
+      <c r="D5">
+        <v>5</v>
+      </c>
+      <c r="E5">
+        <v>9</v>
+      </c>
+      <c r="F5">
+        <v>3</v>
+      </c>
+      <c r="G5">
+        <v>2</v>
+      </c>
+      <c r="H5">
+        <v>4</v>
+      </c>
+      <c r="I5">
+        <v>4</v>
+      </c>
+      <c r="J5">
+        <v>6</v>
+      </c>
+      <c r="K5">
+        <v>7</v>
+      </c>
+      <c r="L5">
+        <v>4</v>
+      </c>
+      <c r="M5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6">
+        <v>17</v>
+      </c>
+      <c r="C6">
+        <v>10</v>
+      </c>
+      <c r="D6">
+        <v>17</v>
+      </c>
+      <c r="E6">
+        <v>14</v>
+      </c>
+      <c r="F6">
+        <v>15</v>
+      </c>
+      <c r="G6">
+        <v>6</v>
+      </c>
+      <c r="H6">
+        <v>3</v>
+      </c>
+      <c r="I6">
+        <v>6</v>
+      </c>
+      <c r="J6">
+        <v>8</v>
+      </c>
+      <c r="K6">
+        <v>3</v>
+      </c>
+      <c r="L6">
+        <v>1</v>
+      </c>
+      <c r="M6">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7">
+        <v>33</v>
+      </c>
+      <c r="C7">
+        <v>23</v>
+      </c>
+      <c r="D7">
+        <v>27</v>
+      </c>
+      <c r="E7">
+        <v>25</v>
+      </c>
+      <c r="F7">
+        <v>22</v>
+      </c>
+      <c r="G7">
+        <v>13</v>
+      </c>
+      <c r="H7">
+        <v>11</v>
+      </c>
+      <c r="I7">
+        <v>17</v>
+      </c>
+      <c r="J7">
+        <v>19</v>
+      </c>
+      <c r="K7">
+        <v>15</v>
+      </c>
+      <c r="L7">
+        <v>6</v>
+      </c>
+      <c r="M7">
+        <v>10</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -8550,7 +8727,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M8"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -8816,7 +8993,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -9049,257 +9226,6 @@
       </c>
       <c r="M7">
         <v>4</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M8"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" customWidth="1"/>
-    <col min="13" max="13" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="M1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2">
-        <v>1</v>
-      </c>
-      <c r="D2">
-        <v>2</v>
-      </c>
-      <c r="F2">
-        <v>2</v>
-      </c>
-      <c r="I2">
-        <v>3</v>
-      </c>
-      <c r="J2">
-        <v>2</v>
-      </c>
-      <c r="K2">
-        <v>1</v>
-      </c>
-      <c r="L2">
-        <v>5</v>
-      </c>
-      <c r="M2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C3">
-        <v>1</v>
-      </c>
-      <c r="E3">
-        <v>1</v>
-      </c>
-      <c r="H3">
-        <v>2</v>
-      </c>
-      <c r="I3">
-        <v>1</v>
-      </c>
-      <c r="J3">
-        <v>1</v>
-      </c>
-      <c r="K3">
-        <v>2</v>
-      </c>
-      <c r="L3">
-        <v>2</v>
-      </c>
-      <c r="M3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C4">
-        <v>1</v>
-      </c>
-      <c r="I4">
-        <v>1</v>
-      </c>
-      <c r="K4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="L5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B6">
-        <v>1</v>
-      </c>
-      <c r="F6">
-        <v>4</v>
-      </c>
-      <c r="H6">
-        <v>1</v>
-      </c>
-      <c r="I6">
-        <v>2</v>
-      </c>
-      <c r="K6">
-        <v>1</v>
-      </c>
-      <c r="M6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
-      <c r="A7" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B7">
-        <v>10</v>
-      </c>
-      <c r="C7">
-        <v>20</v>
-      </c>
-      <c r="D7">
-        <v>25</v>
-      </c>
-      <c r="E7">
-        <v>30</v>
-      </c>
-      <c r="F7">
-        <v>41</v>
-      </c>
-      <c r="G7">
-        <v>10</v>
-      </c>
-      <c r="H7">
-        <v>5</v>
-      </c>
-      <c r="I7">
-        <v>5</v>
-      </c>
-      <c r="J7">
-        <v>15</v>
-      </c>
-      <c r="K7">
-        <v>17</v>
-      </c>
-      <c r="L7">
-        <v>12</v>
-      </c>
-      <c r="M7">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13">
-      <c r="A8" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B8">
-        <v>12</v>
-      </c>
-      <c r="C8">
-        <v>22</v>
-      </c>
-      <c r="D8">
-        <v>27</v>
-      </c>
-      <c r="E8">
-        <v>31</v>
-      </c>
-      <c r="F8">
-        <v>47</v>
-      </c>
-      <c r="G8">
-        <v>10</v>
-      </c>
-      <c r="H8">
-        <v>8</v>
-      </c>
-      <c r="I8">
-        <v>12</v>
-      </c>
-      <c r="J8">
-        <v>18</v>
-      </c>
-      <c r="K8">
-        <v>22</v>
-      </c>
-      <c r="L8">
-        <v>21</v>
-      </c>
-      <c r="M8">
-        <v>17</v>
       </c>
     </row>
   </sheetData>
@@ -10570,7 +10496,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M7"/>
+  <dimension ref="A1:M8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="23.7109375" customWidth="1"/>
@@ -10633,32 +10559,29 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C2">
+      <c r="B2">
         <v>1</v>
       </c>
       <c r="D2">
-        <v>1</v>
-      </c>
-      <c r="E2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F2">
-        <v>1</v>
-      </c>
-      <c r="H2">
         <v>2</v>
       </c>
       <c r="I2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K2">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="L2">
+        <v>5</v>
       </c>
       <c r="M2">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -10666,168 +10589,155 @@
         <v>2</v>
       </c>
       <c r="C3">
-        <v>3</v>
-      </c>
-      <c r="D3">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E3">
         <v>1</v>
       </c>
-      <c r="G3">
-        <v>1</v>
-      </c>
       <c r="H3">
         <v>2</v>
       </c>
       <c r="I3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J3">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K3">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L3">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="M3">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G4">
-        <v>1</v>
-      </c>
-      <c r="J4">
+      <c r="C4">
+        <v>1</v>
+      </c>
+      <c r="I4">
+        <v>1</v>
+      </c>
+      <c r="K4">
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5">
-        <v>3</v>
-      </c>
-      <c r="C5">
-        <v>3</v>
-      </c>
-      <c r="D5">
-        <v>7</v>
-      </c>
-      <c r="E5">
-        <v>5</v>
-      </c>
-      <c r="F5">
-        <v>12</v>
-      </c>
-      <c r="G5">
-        <v>13</v>
-      </c>
-      <c r="H5">
-        <v>11</v>
-      </c>
-      <c r="I5">
-        <v>14</v>
-      </c>
-      <c r="J5">
-        <v>12</v>
-      </c>
-      <c r="K5">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="L5">
-        <v>6</v>
-      </c>
-      <c r="M5">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B6">
-        <v>47</v>
-      </c>
-      <c r="C6">
-        <v>37</v>
-      </c>
-      <c r="D6">
-        <v>85</v>
-      </c>
-      <c r="E6">
-        <v>75</v>
+        <v>1</v>
       </c>
       <c r="F6">
-        <v>80</v>
-      </c>
-      <c r="G6">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="H6">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="I6">
-        <v>26</v>
-      </c>
-      <c r="J6">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="K6">
-        <v>19</v>
-      </c>
-      <c r="L6">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="M6">
-        <v>12</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7">
         <v>10</v>
       </c>
-      <c r="B7">
-        <v>50</v>
-      </c>
       <c r="C7">
-        <v>44</v>
+        <v>20</v>
       </c>
       <c r="D7">
-        <v>97</v>
+        <v>25</v>
       </c>
       <c r="E7">
-        <v>82</v>
+        <v>30</v>
       </c>
       <c r="F7">
-        <v>93</v>
+        <v>41</v>
       </c>
       <c r="G7">
-        <v>37</v>
+        <v>10</v>
       </c>
       <c r="H7">
+        <v>5</v>
+      </c>
+      <c r="I7">
+        <v>5</v>
+      </c>
+      <c r="J7">
+        <v>15</v>
+      </c>
+      <c r="K7">
+        <v>17</v>
+      </c>
+      <c r="L7">
+        <v>12</v>
+      </c>
+      <c r="M7">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13">
+      <c r="A8" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B8">
+        <v>12</v>
+      </c>
+      <c r="C8">
+        <v>22</v>
+      </c>
+      <c r="D8">
+        <v>27</v>
+      </c>
+      <c r="E8">
+        <v>31</v>
+      </c>
+      <c r="F8">
+        <v>47</v>
+      </c>
+      <c r="G8">
+        <v>10</v>
+      </c>
+      <c r="H8">
+        <v>8</v>
+      </c>
+      <c r="I8">
+        <v>12</v>
+      </c>
+      <c r="J8">
+        <v>18</v>
+      </c>
+      <c r="K8">
+        <v>22</v>
+      </c>
+      <c r="L8">
         <v>21</v>
       </c>
-      <c r="I7">
-        <v>47</v>
-      </c>
-      <c r="J7">
-        <v>33</v>
-      </c>
-      <c r="K7">
-        <v>34</v>
-      </c>
-      <c r="L7">
-        <v>25</v>
-      </c>
-      <c r="M7">
-        <v>20</v>
+      <c r="M8">
+        <v>18</v>
       </c>
     </row>
   </sheetData>
@@ -11231,7 +11141,7 @@
         <v>2</v>
       </c>
       <c r="M6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -11272,7 +11182,7 @@
         <v>3</v>
       </c>
       <c r="M7">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -13139,7 +13049,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M8"/>
+  <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="23.7109375" customWidth="1"/>
@@ -13202,11 +13112,8 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2">
-        <v>1</v>
-      </c>
       <c r="C2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D2">
         <v>1</v>
@@ -13215,63 +13122,54 @@
         <v>1</v>
       </c>
       <c r="F2">
-        <v>2</v>
-      </c>
-      <c r="G2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K2">
-        <v>3</v>
-      </c>
-      <c r="L2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M2">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B3">
-        <v>1</v>
-      </c>
       <c r="C3">
-        <v>2</v>
+        <v>3</v>
+      </c>
+      <c r="D3">
+        <v>4</v>
       </c>
       <c r="E3">
-        <v>2</v>
-      </c>
-      <c r="F3">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H3">
         <v>2</v>
       </c>
       <c r="I3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J3">
         <v>5</v>
       </c>
       <c r="K3">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L3">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M3">
         <v>3</v>
@@ -13279,147 +13177,136 @@
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4">
-        <v>1</v>
-      </c>
-      <c r="I4">
+        <v>5</v>
+      </c>
+      <c r="G4">
+        <v>1</v>
+      </c>
+      <c r="J4">
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>5</v>
+        <v>8</v>
+      </c>
+      <c r="B5">
+        <v>3</v>
+      </c>
+      <c r="C5">
+        <v>3</v>
+      </c>
+      <c r="D5">
+        <v>7</v>
+      </c>
+      <c r="E5">
+        <v>5</v>
+      </c>
+      <c r="F5">
+        <v>12</v>
+      </c>
+      <c r="G5">
+        <v>13</v>
       </c>
       <c r="H5">
-        <v>1</v>
+        <v>11</v>
+      </c>
+      <c r="I5">
+        <v>14</v>
       </c>
       <c r="J5">
-        <v>1</v>
+        <v>12</v>
+      </c>
+      <c r="K5">
+        <v>9</v>
+      </c>
+      <c r="L5">
+        <v>6</v>
+      </c>
+      <c r="M5">
+        <v>4</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B6">
+        <v>47</v>
+      </c>
+      <c r="C6">
+        <v>37</v>
+      </c>
+      <c r="D6">
+        <v>85</v>
+      </c>
+      <c r="E6">
+        <v>75</v>
+      </c>
+      <c r="F6">
+        <v>80</v>
+      </c>
+      <c r="G6">
+        <v>22</v>
+      </c>
+      <c r="H6">
+        <v>6</v>
+      </c>
+      <c r="I6">
+        <v>26</v>
+      </c>
+      <c r="J6">
         <v>12</v>
       </c>
-      <c r="C6">
-        <v>21</v>
-      </c>
-      <c r="D6">
-        <v>28</v>
-      </c>
-      <c r="E6">
-        <v>21</v>
-      </c>
-      <c r="F6">
-        <v>35</v>
-      </c>
-      <c r="G6">
+      <c r="K6">
+        <v>19</v>
+      </c>
+      <c r="L6">
+        <v>11</v>
+      </c>
+      <c r="M6">
         <v>12</v>
-      </c>
-      <c r="H6">
-        <v>10</v>
-      </c>
-      <c r="I6">
-        <v>15</v>
-      </c>
-      <c r="J6">
-        <v>5</v>
-      </c>
-      <c r="K6">
-        <v>9</v>
-      </c>
-      <c r="L6">
-        <v>7</v>
-      </c>
-      <c r="M6">
-        <v>4</v>
       </c>
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B7">
-        <v>17</v>
+        <v>50</v>
       </c>
       <c r="C7">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="D7">
-        <v>49</v>
+        <v>97</v>
       </c>
       <c r="E7">
-        <v>44</v>
+        <v>82</v>
       </c>
       <c r="F7">
-        <v>58</v>
+        <v>93</v>
       </c>
       <c r="G7">
+        <v>37</v>
+      </c>
+      <c r="H7">
+        <v>21</v>
+      </c>
+      <c r="I7">
+        <v>47</v>
+      </c>
+      <c r="J7">
+        <v>33</v>
+      </c>
+      <c r="K7">
+        <v>34</v>
+      </c>
+      <c r="L7">
         <v>25</v>
       </c>
-      <c r="H7">
-        <v>8</v>
-      </c>
-      <c r="I7">
-        <v>10</v>
-      </c>
-      <c r="J7">
-        <v>8</v>
-      </c>
-      <c r="K7">
-        <v>11</v>
-      </c>
-      <c r="L7">
-        <v>7</v>
-      </c>
       <c r="M7">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13">
-      <c r="A8" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B8">
-        <v>32</v>
-      </c>
-      <c r="C8">
-        <v>61</v>
-      </c>
-      <c r="D8">
-        <v>78</v>
-      </c>
-      <c r="E8">
-        <v>68</v>
-      </c>
-      <c r="F8">
-        <v>100</v>
-      </c>
-      <c r="G8">
-        <v>43</v>
-      </c>
-      <c r="H8">
-        <v>26</v>
-      </c>
-      <c r="I8">
-        <v>32</v>
-      </c>
-      <c r="J8">
         <v>20</v>
-      </c>
-      <c r="K8">
-        <v>29</v>
-      </c>
-      <c r="L8">
-        <v>25</v>
-      </c>
-      <c r="M8">
-        <v>15</v>
       </c>
     </row>
   </sheetData>
@@ -15981,7 +15868,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M9"/>
+  <dimension ref="A1:M8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="23.7109375" customWidth="1"/>
@@ -16044,38 +15931,41 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
       <c r="C2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D2">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E2">
         <v>1</v>
       </c>
       <c r="F2">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="G2">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="H2">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="I2">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="J2">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="K2">
         <v>3</v>
       </c>
       <c r="L2">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M2">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -16083,211 +15973,182 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C3">
-        <v>5</v>
-      </c>
-      <c r="D3">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="E3">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="F3">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="G3">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="H3">
+        <v>2</v>
+      </c>
+      <c r="I3">
+        <v>4</v>
+      </c>
+      <c r="J3">
+        <v>5</v>
+      </c>
+      <c r="K3">
+        <v>6</v>
+      </c>
+      <c r="L3">
         <v>7</v>
       </c>
-      <c r="I3">
-        <v>13</v>
-      </c>
-      <c r="J3">
-        <v>12</v>
-      </c>
-      <c r="K3">
-        <v>20</v>
-      </c>
-      <c r="L3">
-        <v>20</v>
-      </c>
       <c r="M3">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B4">
         <v>1</v>
       </c>
-      <c r="D4">
-        <v>1</v>
-      </c>
-      <c r="H4">
-        <v>2</v>
-      </c>
-      <c r="J4">
-        <v>1</v>
-      </c>
-      <c r="K4">
-        <v>1</v>
-      </c>
-      <c r="L4">
-        <v>1</v>
-      </c>
-      <c r="M4">
-        <v>2</v>
+      <c r="I4">
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H5">
         <v>1</v>
       </c>
-      <c r="I5">
+      <c r="J5">
         <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6">
+        <v>12</v>
+      </c>
+      <c r="C6">
+        <v>21</v>
+      </c>
+      <c r="D6">
+        <v>28</v>
+      </c>
+      <c r="E6">
+        <v>21</v>
+      </c>
+      <c r="F6">
+        <v>35</v>
+      </c>
+      <c r="G6">
+        <v>12</v>
+      </c>
+      <c r="H6">
+        <v>10</v>
+      </c>
+      <c r="I6">
+        <v>15</v>
+      </c>
+      <c r="J6">
+        <v>5</v>
+      </c>
+      <c r="K6">
+        <v>9</v>
+      </c>
+      <c r="L6">
         <v>7</v>
       </c>
-      <c r="G6">
-        <v>1</v>
-      </c>
-      <c r="J6">
-        <v>1</v>
+      <c r="M6">
+        <v>4</v>
       </c>
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7">
+        <v>17</v>
+      </c>
+      <c r="C7">
+        <v>35</v>
+      </c>
+      <c r="D7">
+        <v>49</v>
+      </c>
+      <c r="E7">
+        <v>44</v>
+      </c>
+      <c r="F7">
+        <v>58</v>
+      </c>
+      <c r="G7">
+        <v>25</v>
+      </c>
+      <c r="H7">
         <v>8</v>
       </c>
-      <c r="B7">
-        <v>34</v>
-      </c>
-      <c r="C7">
-        <v>45</v>
-      </c>
-      <c r="D7">
-        <v>25</v>
-      </c>
-      <c r="E7">
-        <v>22</v>
-      </c>
-      <c r="F7">
-        <v>42</v>
-      </c>
-      <c r="G7">
-        <v>32</v>
-      </c>
-      <c r="H7">
-        <v>26</v>
-      </c>
       <c r="I7">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="J7">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="K7">
-        <v>44</v>
+        <v>11</v>
       </c>
       <c r="L7">
-        <v>43</v>
+        <v>7</v>
       </c>
       <c r="M7">
-        <v>16</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:13">
       <c r="A8" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B8">
-        <v>71</v>
+        <v>32</v>
       </c>
       <c r="C8">
-        <v>91</v>
+        <v>61</v>
       </c>
       <c r="D8">
-        <v>57</v>
+        <v>78</v>
       </c>
       <c r="E8">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="F8">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="G8">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="H8">
+        <v>26</v>
+      </c>
+      <c r="I8">
+        <v>32</v>
+      </c>
+      <c r="J8">
+        <v>20</v>
+      </c>
+      <c r="K8">
         <v>29</v>
       </c>
-      <c r="I8">
-        <v>45</v>
-      </c>
-      <c r="J8">
-        <v>31</v>
-      </c>
-      <c r="K8">
-        <v>27</v>
-      </c>
       <c r="L8">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="M8">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13">
-      <c r="A9" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B9">
-        <v>111</v>
-      </c>
-      <c r="C9">
-        <v>142</v>
-      </c>
-      <c r="D9">
-        <v>107</v>
-      </c>
-      <c r="E9">
-        <v>98</v>
-      </c>
-      <c r="F9">
-        <v>138</v>
-      </c>
-      <c r="G9">
-        <v>92</v>
-      </c>
-      <c r="H9">
-        <v>76</v>
-      </c>
-      <c r="I9">
-        <v>90</v>
-      </c>
-      <c r="J9">
-        <v>69</v>
-      </c>
-      <c r="K9">
-        <v>95</v>
-      </c>
-      <c r="L9">
-        <v>102</v>
-      </c>
-      <c r="M9">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
   </sheetData>
@@ -18577,76 +18438,76 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2">
-        <v>2</v>
-      </c>
       <c r="C2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D2">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F2">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="G2">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="H2">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="I2">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="J2">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="K2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L2">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="M2">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
+      <c r="B3">
+        <v>5</v>
+      </c>
       <c r="C3">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D3">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="E3">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="F3">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="G3">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="H3">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="I3">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="J3">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="K3">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="L3">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="M3">
         <v>5</v>
@@ -18654,17 +18515,38 @@
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E4">
-        <v>1</v>
+        <v>5</v>
+      </c>
+      <c r="B4">
+        <v>1</v>
+      </c>
+      <c r="D4">
+        <v>1</v>
+      </c>
+      <c r="H4">
+        <v>2</v>
+      </c>
+      <c r="J4">
+        <v>1</v>
+      </c>
+      <c r="K4">
+        <v>1</v>
+      </c>
+      <c r="L4">
+        <v>1</v>
+      </c>
+      <c r="M4">
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5">
+        <v>6</v>
+      </c>
+      <c r="H5">
+        <v>1</v>
+      </c>
+      <c r="I5">
         <v>1</v>
       </c>
     </row>
@@ -18672,7 +18554,10 @@
       <c r="A6" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C6">
+      <c r="G6">
+        <v>1</v>
+      </c>
+      <c r="J6">
         <v>1</v>
       </c>
     </row>
@@ -18681,40 +18566,40 @@
         <v>8</v>
       </c>
       <c r="B7">
-        <v>5</v>
+        <v>34</v>
       </c>
       <c r="C7">
-        <v>9</v>
+        <v>45</v>
       </c>
       <c r="D7">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="E7">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="F7">
-        <v>6</v>
+        <v>42</v>
       </c>
       <c r="G7">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="H7">
-        <v>7</v>
+        <v>26</v>
       </c>
       <c r="I7">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="J7">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="K7">
-        <v>11</v>
+        <v>44</v>
       </c>
       <c r="L7">
-        <v>8</v>
+        <v>43</v>
       </c>
       <c r="M7">
-        <v>1</v>
+        <v>16</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -18722,40 +18607,40 @@
         <v>9</v>
       </c>
       <c r="B8">
-        <v>30</v>
+        <v>71</v>
       </c>
       <c r="C8">
-        <v>26</v>
+        <v>91</v>
       </c>
       <c r="D8">
-        <v>15</v>
+        <v>57</v>
       </c>
       <c r="E8">
-        <v>24</v>
+        <v>65</v>
       </c>
       <c r="F8">
-        <v>18</v>
+        <v>75</v>
       </c>
       <c r="G8">
-        <v>16</v>
+        <v>41</v>
       </c>
       <c r="H8">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="I8">
-        <v>13</v>
+        <v>45</v>
       </c>
       <c r="J8">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="K8">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="L8">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="M8">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -18763,40 +18648,40 @@
         <v>10</v>
       </c>
       <c r="B9">
-        <v>38</v>
+        <v>111</v>
       </c>
       <c r="C9">
-        <v>41</v>
+        <v>142</v>
       </c>
       <c r="D9">
-        <v>19</v>
+        <v>107</v>
       </c>
       <c r="E9">
+        <v>98</v>
+      </c>
+      <c r="F9">
+        <v>138</v>
+      </c>
+      <c r="G9">
+        <v>92</v>
+      </c>
+      <c r="H9">
+        <v>76</v>
+      </c>
+      <c r="I9">
+        <v>90</v>
+      </c>
+      <c r="J9">
+        <v>69</v>
+      </c>
+      <c r="K9">
+        <v>95</v>
+      </c>
+      <c r="L9">
+        <v>102</v>
+      </c>
+      <c r="M9">
         <v>36</v>
-      </c>
-      <c r="F9">
-        <v>28</v>
-      </c>
-      <c r="G9">
-        <v>38</v>
-      </c>
-      <c r="H9">
-        <v>28</v>
-      </c>
-      <c r="I9">
-        <v>23</v>
-      </c>
-      <c r="J9">
-        <v>31</v>
-      </c>
-      <c r="K9">
-        <v>35</v>
-      </c>
-      <c r="L9">
-        <v>33</v>
-      </c>
-      <c r="M9">
-        <v>17</v>
       </c>
     </row>
   </sheetData>
@@ -21120,7 +21005,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M10"/>
+  <dimension ref="A1:M9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="23.7109375" customWidth="1"/>
@@ -21184,100 +21069,85 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D2">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="E2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F2">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="G2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H2">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="I2">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="J2">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="K2">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="L2">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="M2">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B3">
-        <v>13</v>
-      </c>
       <c r="C3">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="D3">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="E3">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="F3">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="G3">
-        <v>26</v>
+        <v>6</v>
       </c>
       <c r="H3">
-        <v>23</v>
+        <v>2</v>
       </c>
       <c r="I3">
-        <v>32</v>
+        <v>4</v>
       </c>
       <c r="J3">
-        <v>40</v>
+        <v>7</v>
       </c>
       <c r="K3">
-        <v>26</v>
+        <v>7</v>
       </c>
       <c r="L3">
-        <v>34</v>
+        <v>3</v>
       </c>
       <c r="M3">
-        <v>17</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="G4">
-        <v>1</v>
-      </c>
-      <c r="J4">
-        <v>2</v>
-      </c>
-      <c r="K4">
-        <v>1</v>
-      </c>
-      <c r="L4">
-        <v>1</v>
-      </c>
-      <c r="M4">
+      <c r="E4">
         <v>1</v>
       </c>
     </row>
@@ -21285,186 +21155,139 @@
       <c r="A5" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C5">
-        <v>2</v>
-      </c>
-      <c r="D5">
-        <v>1</v>
-      </c>
-      <c r="E5">
-        <v>2</v>
-      </c>
-      <c r="F5">
-        <v>1</v>
-      </c>
-      <c r="H5">
-        <v>2</v>
-      </c>
-      <c r="I5">
-        <v>4</v>
-      </c>
-      <c r="J5">
-        <v>3</v>
-      </c>
-      <c r="K5">
-        <v>2</v>
-      </c>
-      <c r="L5">
-        <v>5</v>
-      </c>
-      <c r="M5">
-        <v>4</v>
+      <c r="B5">
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="G6">
-        <v>1</v>
-      </c>
-      <c r="H6">
-        <v>2</v>
-      </c>
-      <c r="J6">
-        <v>2</v>
-      </c>
-      <c r="L6">
-        <v>2</v>
-      </c>
-      <c r="M6">
+        <v>7</v>
+      </c>
+      <c r="C6">
         <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7">
+        <v>5</v>
+      </c>
+      <c r="C7">
+        <v>9</v>
+      </c>
+      <c r="D7">
+        <v>1</v>
+      </c>
+      <c r="E7">
+        <v>6</v>
+      </c>
+      <c r="F7">
+        <v>6</v>
+      </c>
+      <c r="G7">
+        <v>14</v>
+      </c>
+      <c r="H7">
         <v>7</v>
       </c>
+      <c r="I7">
+        <v>4</v>
+      </c>
+      <c r="J7">
+        <v>5</v>
+      </c>
       <c r="K7">
+        <v>11</v>
+      </c>
+      <c r="L7">
+        <v>8</v>
+      </c>
+      <c r="M7">
         <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:13">
       <c r="A8" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B8">
         <v>30</v>
       </c>
       <c r="C8">
-        <v>44</v>
+        <v>26</v>
       </c>
       <c r="D8">
-        <v>49</v>
+        <v>15</v>
       </c>
       <c r="E8">
-        <v>67</v>
+        <v>24</v>
       </c>
       <c r="F8">
-        <v>69</v>
+        <v>18</v>
       </c>
       <c r="G8">
-        <v>57</v>
+        <v>16</v>
       </c>
       <c r="H8">
-        <v>80</v>
+        <v>14</v>
       </c>
       <c r="I8">
-        <v>80</v>
+        <v>13</v>
       </c>
       <c r="J8">
-        <v>64</v>
+        <v>15</v>
       </c>
       <c r="K8">
-        <v>48</v>
+        <v>12</v>
       </c>
       <c r="L8">
-        <v>44</v>
+        <v>20</v>
       </c>
       <c r="M8">
-        <v>21</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9" spans="1:13">
       <c r="A9" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B9">
-        <v>233</v>
+        <v>38</v>
       </c>
       <c r="C9">
-        <v>354</v>
+        <v>41</v>
       </c>
       <c r="D9">
-        <v>538</v>
+        <v>19</v>
       </c>
       <c r="E9">
-        <v>705</v>
+        <v>36</v>
       </c>
       <c r="F9">
-        <v>568</v>
+        <v>28</v>
       </c>
       <c r="G9">
-        <v>168</v>
+        <v>38</v>
       </c>
       <c r="H9">
-        <v>116</v>
+        <v>28</v>
       </c>
       <c r="I9">
-        <v>194</v>
+        <v>23</v>
       </c>
       <c r="J9">
-        <v>122</v>
+        <v>31</v>
       </c>
       <c r="K9">
-        <v>114</v>
+        <v>35</v>
       </c>
       <c r="L9">
-        <v>95</v>
+        <v>33</v>
       </c>
       <c r="M9">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13">
-      <c r="A10" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B10">
-        <v>282</v>
-      </c>
-      <c r="C10">
-        <v>416</v>
-      </c>
-      <c r="D10">
-        <v>617</v>
-      </c>
-      <c r="E10">
-        <v>797</v>
-      </c>
-      <c r="F10">
-        <v>660</v>
-      </c>
-      <c r="G10">
-        <v>257</v>
-      </c>
-      <c r="H10">
-        <v>236</v>
-      </c>
-      <c r="I10">
-        <v>324</v>
-      </c>
-      <c r="J10">
-        <v>255</v>
-      </c>
-      <c r="K10">
-        <v>207</v>
-      </c>
-      <c r="L10">
-        <v>196</v>
-      </c>
-      <c r="M10">
-        <v>94</v>
+        <v>17</v>
       </c>
     </row>
   </sheetData>
@@ -23208,7 +23031,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M8"/>
+  <dimension ref="A1:M10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="23.7109375" customWidth="1"/>
@@ -23271,124 +23094,154 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
+      <c r="B2">
+        <v>6</v>
+      </c>
       <c r="C2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D2">
-        <v>2</v>
+        <v>12</v>
+      </c>
+      <c r="E2">
+        <v>5</v>
+      </c>
+      <c r="F2">
+        <v>8</v>
       </c>
       <c r="G2">
         <v>4</v>
       </c>
       <c r="H2">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="I2">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="J2">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="K2">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="L2">
-        <v>5</v>
+        <v>15</v>
+      </c>
+      <c r="M2">
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
+      <c r="B3">
+        <v>13</v>
+      </c>
       <c r="C3">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="D3">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="E3">
-        <v>1</v>
+        <v>18</v>
+      </c>
+      <c r="F3">
+        <v>14</v>
+      </c>
+      <c r="G3">
+        <v>26</v>
       </c>
       <c r="H3">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="I3">
-        <v>1</v>
+        <v>32</v>
       </c>
       <c r="J3">
-        <v>3</v>
+        <v>40</v>
       </c>
       <c r="K3">
-        <v>1</v>
+        <v>26</v>
       </c>
       <c r="L3">
-        <v>1</v>
+        <v>34</v>
+      </c>
+      <c r="M3">
+        <v>17</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D4">
-        <v>1</v>
-      </c>
-      <c r="E4">
+        <v>3</v>
+      </c>
+      <c r="G4">
         <v>1</v>
       </c>
       <c r="J4">
+        <v>2</v>
+      </c>
+      <c r="K4">
         <v>1</v>
       </c>
       <c r="L4">
+        <v>1</v>
+      </c>
+      <c r="M4">
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C5">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="D5">
+        <v>1</v>
+      </c>
+      <c r="E5">
+        <v>2</v>
+      </c>
+      <c r="F5">
+        <v>1</v>
+      </c>
+      <c r="H5">
+        <v>2</v>
+      </c>
+      <c r="I5">
+        <v>4</v>
       </c>
       <c r="J5">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="K5">
+        <v>2</v>
+      </c>
+      <c r="L5">
+        <v>5</v>
+      </c>
+      <c r="M5">
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B6">
-        <v>2</v>
-      </c>
-      <c r="C6">
-        <v>5</v>
-      </c>
-      <c r="D6">
-        <v>3</v>
-      </c>
-      <c r="E6">
-        <v>4</v>
-      </c>
-      <c r="F6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G6">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H6">
-        <v>8</v>
-      </c>
-      <c r="I6">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J6">
-        <v>8</v>
-      </c>
-      <c r="K6">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="L6">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="M6">
         <v>1</v>
@@ -23396,84 +23249,133 @@
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B7">
-        <v>17</v>
-      </c>
-      <c r="C7">
-        <v>24</v>
-      </c>
-      <c r="D7">
-        <v>35</v>
-      </c>
-      <c r="E7">
-        <v>31</v>
-      </c>
-      <c r="F7">
-        <v>18</v>
-      </c>
-      <c r="G7">
-        <v>17</v>
-      </c>
-      <c r="H7">
-        <v>8</v>
-      </c>
-      <c r="I7">
-        <v>16</v>
-      </c>
-      <c r="J7">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="K7">
-        <v>10</v>
-      </c>
-      <c r="L7">
-        <v>12</v>
-      </c>
-      <c r="M7">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:13">
       <c r="A8" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8">
+        <v>30</v>
+      </c>
+      <c r="C8">
+        <v>44</v>
+      </c>
+      <c r="D8">
+        <v>49</v>
+      </c>
+      <c r="E8">
+        <v>67</v>
+      </c>
+      <c r="F8">
+        <v>69</v>
+      </c>
+      <c r="G8">
+        <v>57</v>
+      </c>
+      <c r="H8">
+        <v>80</v>
+      </c>
+      <c r="I8">
+        <v>80</v>
+      </c>
+      <c r="J8">
+        <v>64</v>
+      </c>
+      <c r="K8">
+        <v>48</v>
+      </c>
+      <c r="L8">
+        <v>44</v>
+      </c>
+      <c r="M8">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13">
+      <c r="A9" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B9">
+        <v>233</v>
+      </c>
+      <c r="C9">
+        <v>354</v>
+      </c>
+      <c r="D9">
+        <v>538</v>
+      </c>
+      <c r="E9">
+        <v>705</v>
+      </c>
+      <c r="F9">
+        <v>568</v>
+      </c>
+      <c r="G9">
+        <v>168</v>
+      </c>
+      <c r="H9">
+        <v>116</v>
+      </c>
+      <c r="I9">
+        <v>194</v>
+      </c>
+      <c r="J9">
+        <v>122</v>
+      </c>
+      <c r="K9">
+        <v>114</v>
+      </c>
+      <c r="L9">
+        <v>95</v>
+      </c>
+      <c r="M9">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13">
+      <c r="A10" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B8">
-        <v>19</v>
-      </c>
-      <c r="C8">
-        <v>32</v>
-      </c>
-      <c r="D8">
-        <v>42</v>
-      </c>
-      <c r="E8">
-        <v>37</v>
-      </c>
-      <c r="F8">
-        <v>23</v>
-      </c>
-      <c r="G8">
-        <v>26</v>
-      </c>
-      <c r="H8">
-        <v>18</v>
-      </c>
-      <c r="I8">
-        <v>23</v>
-      </c>
-      <c r="J8">
-        <v>31</v>
-      </c>
-      <c r="K8">
-        <v>20</v>
-      </c>
-      <c r="L8">
-        <v>26</v>
-      </c>
-      <c r="M8">
-        <v>9</v>
+      <c r="B10">
+        <v>282</v>
+      </c>
+      <c r="C10">
+        <v>416</v>
+      </c>
+      <c r="D10">
+        <v>617</v>
+      </c>
+      <c r="E10">
+        <v>797</v>
+      </c>
+      <c r="F10">
+        <v>660</v>
+      </c>
+      <c r="G10">
+        <v>257</v>
+      </c>
+      <c r="H10">
+        <v>236</v>
+      </c>
+      <c r="I10">
+        <v>324</v>
+      </c>
+      <c r="J10">
+        <v>255</v>
+      </c>
+      <c r="K10">
+        <v>207</v>
+      </c>
+      <c r="L10">
+        <v>196</v>
+      </c>
+      <c r="M10">
+        <v>93</v>
       </c>
     </row>
   </sheetData>
@@ -25367,10 +25269,10 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L6"/>
+  <dimension ref="A1:M8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="18.7109375" customWidth="1"/>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
     <col min="2" max="2" width="4.7109375" customWidth="1"/>
     <col min="3" max="3" width="4.7109375" customWidth="1"/>
     <col min="4" max="4" width="4.7109375" customWidth="1"/>
@@ -25382,9 +25284,10 @@
     <col min="10" max="10" width="4.7109375" customWidth="1"/>
     <col min="11" max="11" width="4.7109375" customWidth="1"/>
     <col min="12" max="12" width="4.7109375" customWidth="1"/>
+    <col min="13" max="13" width="4.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:13">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -25407,33 +25310,54 @@
         <v>2020</v>
       </c>
       <c r="H1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="I1" s="1">
         <v>2022</v>
       </c>
-      <c r="I1" s="1">
+      <c r="J1" s="1">
         <v>2023</v>
       </c>
-      <c r="J1" s="1">
+      <c r="K1" s="1">
         <v>2024</v>
       </c>
-      <c r="K1" s="1">
+      <c r="L1" s="1">
         <v>2025</v>
       </c>
-      <c r="L1" s="1">
+      <c r="M1" s="1">
         <v>2026</v>
       </c>
     </row>
-    <row r="2" spans="1:12">
+    <row r="2" spans="1:13">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="F2">
+      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>2</v>
+      </c>
+      <c r="G2">
+        <v>4</v>
+      </c>
+      <c r="H2">
         <v>1</v>
       </c>
       <c r="I2">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="1:12">
+      <c r="J2">
+        <v>3</v>
+      </c>
+      <c r="K2">
+        <v>2</v>
+      </c>
+      <c r="L2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
@@ -25441,100 +25365,176 @@
         <v>1</v>
       </c>
       <c r="D3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E3">
         <v>1</v>
       </c>
-      <c r="G3">
-        <v>1</v>
-      </c>
       <c r="H3">
         <v>1</v>
       </c>
+      <c r="I3">
+        <v>1</v>
+      </c>
+      <c r="J3">
+        <v>3</v>
+      </c>
+      <c r="K3">
+        <v>1</v>
+      </c>
       <c r="L3">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:12">
+    <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D4">
+        <v>1</v>
+      </c>
+      <c r="E4">
+        <v>1</v>
+      </c>
+      <c r="J4">
+        <v>1</v>
+      </c>
+      <c r="L4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5">
+        <v>1</v>
+      </c>
+      <c r="J5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B4">
-        <v>4</v>
-      </c>
-      <c r="D4">
-        <v>2</v>
-      </c>
-      <c r="E4">
-        <v>2</v>
-      </c>
-      <c r="G4">
-        <v>2</v>
-      </c>
-      <c r="H4">
-        <v>1</v>
-      </c>
-      <c r="I4">
-        <v>3</v>
-      </c>
-      <c r="J4">
-        <v>3</v>
-      </c>
-      <c r="K4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12">
-      <c r="A5" s="1" t="s">
+      <c r="B6">
+        <v>2</v>
+      </c>
+      <c r="C6">
+        <v>5</v>
+      </c>
+      <c r="D6">
+        <v>3</v>
+      </c>
+      <c r="E6">
+        <v>4</v>
+      </c>
+      <c r="F6">
+        <v>5</v>
+      </c>
+      <c r="G6">
+        <v>5</v>
+      </c>
+      <c r="H6">
+        <v>8</v>
+      </c>
+      <c r="I6">
+        <v>5</v>
+      </c>
+      <c r="J6">
+        <v>8</v>
+      </c>
+      <c r="K6">
+        <v>7</v>
+      </c>
+      <c r="L6">
+        <v>7</v>
+      </c>
+      <c r="M6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="F5">
-        <v>2</v>
-      </c>
-      <c r="I5">
-        <v>3</v>
-      </c>
-      <c r="K5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12">
-      <c r="A6" s="1" t="s">
+      <c r="B7">
+        <v>17</v>
+      </c>
+      <c r="C7">
+        <v>24</v>
+      </c>
+      <c r="D7">
+        <v>35</v>
+      </c>
+      <c r="E7">
+        <v>31</v>
+      </c>
+      <c r="F7">
+        <v>18</v>
+      </c>
+      <c r="G7">
+        <v>17</v>
+      </c>
+      <c r="H7">
+        <v>8</v>
+      </c>
+      <c r="I7">
+        <v>16</v>
+      </c>
+      <c r="J7">
+        <v>15</v>
+      </c>
+      <c r="K7">
         <v>10</v>
       </c>
-      <c r="B6">
-        <v>4</v>
-      </c>
-      <c r="C6">
-        <v>1</v>
-      </c>
-      <c r="D6">
-        <v>5</v>
-      </c>
-      <c r="E6">
-        <v>3</v>
-      </c>
-      <c r="F6">
-        <v>3</v>
-      </c>
-      <c r="G6">
-        <v>3</v>
-      </c>
-      <c r="H6">
-        <v>2</v>
-      </c>
-      <c r="I6">
-        <v>7</v>
-      </c>
-      <c r="J6">
-        <v>3</v>
-      </c>
-      <c r="K6">
-        <v>2</v>
-      </c>
-      <c r="L6">
-        <v>1</v>
+      <c r="L7">
+        <v>12</v>
+      </c>
+      <c r="M7">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13">
+      <c r="A8" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B8">
+        <v>19</v>
+      </c>
+      <c r="C8">
+        <v>32</v>
+      </c>
+      <c r="D8">
+        <v>42</v>
+      </c>
+      <c r="E8">
+        <v>37</v>
+      </c>
+      <c r="F8">
+        <v>23</v>
+      </c>
+      <c r="G8">
+        <v>26</v>
+      </c>
+      <c r="H8">
+        <v>18</v>
+      </c>
+      <c r="I8">
+        <v>23</v>
+      </c>
+      <c r="J8">
+        <v>31</v>
+      </c>
+      <c r="K8">
+        <v>20</v>
+      </c>
+      <c r="L8">
+        <v>26</v>
+      </c>
+      <c r="M8">
+        <v>9</v>
       </c>
     </row>
   </sheetData>

--- a/output/cta-index-crime-full-year.xlsx
+++ b/output/cta-index-crime-full-year.xlsx
@@ -9,46 +9,46 @@
   <sheets>
     <sheet name="Citywide Totals" sheetId="1" r:id="rId1"/>
     <sheet name="By Neighborhood" sheetId="2" r:id="rId2"/>
-    <sheet name="O'Hare" sheetId="3" r:id="rId3"/>
-    <sheet name="River North" sheetId="4" r:id="rId4"/>
-    <sheet name="North Lawndale" sheetId="5" r:id="rId5"/>
-    <sheet name="Englewood" sheetId="6" r:id="rId6"/>
-    <sheet name="Uptown" sheetId="7" r:id="rId7"/>
-    <sheet name="Loop" sheetId="8" r:id="rId8"/>
-    <sheet name="Logan Square" sheetId="9" r:id="rId9"/>
-    <sheet name="Riverdale" sheetId="10" r:id="rId10"/>
-    <sheet name="Fuller Park" sheetId="11" r:id="rId11"/>
-    <sheet name="Little Village" sheetId="12" r:id="rId12"/>
-    <sheet name="Chatham" sheetId="13" r:id="rId13"/>
-    <sheet name="West Loop" sheetId="14" r:id="rId14"/>
-    <sheet name="Auburn Gresham" sheetId="15" r:id="rId15"/>
-    <sheet name="Lake View" sheetId="16" r:id="rId16"/>
-    <sheet name="Humboldt Park" sheetId="17" r:id="rId17"/>
-    <sheet name="Austin" sheetId="18" r:id="rId18"/>
-    <sheet name="Roseland" sheetId="19" r:id="rId19"/>
-    <sheet name="Albany Park" sheetId="20" r:id="rId20"/>
-    <sheet name="Woodlawn" sheetId="21" r:id="rId21"/>
-    <sheet name="South Shore" sheetId="22" r:id="rId22"/>
-    <sheet name="Old Town" sheetId="23" r:id="rId23"/>
-    <sheet name="Lincoln Park" sheetId="24" r:id="rId24"/>
-    <sheet name="Near South Side" sheetId="25" r:id="rId25"/>
-    <sheet name="Grand Crossing" sheetId="26" r:id="rId26"/>
-    <sheet name="Avondale" sheetId="27" r:id="rId27"/>
-    <sheet name="Rush &amp; Division" sheetId="28" r:id="rId28"/>
-    <sheet name="Oakland" sheetId="29" r:id="rId29"/>
-    <sheet name="New City" sheetId="30" r:id="rId30"/>
-    <sheet name="Belmont Cragin" sheetId="31" r:id="rId31"/>
-    <sheet name="Printers Row" sheetId="32" r:id="rId32"/>
-    <sheet name="Hegewisch" sheetId="33" r:id="rId33"/>
-    <sheet name="Hyde Park" sheetId="34" r:id="rId34"/>
-    <sheet name="Grand Boulevard" sheetId="35" r:id="rId35"/>
-    <sheet name="West Town" sheetId="36" r:id="rId36"/>
-    <sheet name="Douglas" sheetId="37" r:id="rId37"/>
-    <sheet name="Norwood Park" sheetId="38" r:id="rId38"/>
-    <sheet name="Washington Park" sheetId="39" r:id="rId39"/>
-    <sheet name="Greektown" sheetId="40" r:id="rId40"/>
-    <sheet name="Rogers Park" sheetId="41" r:id="rId41"/>
-    <sheet name="Garfield Park" sheetId="42" r:id="rId42"/>
+    <sheet name="Garfield Park" sheetId="3" r:id="rId3"/>
+    <sheet name="O'Hare" sheetId="4" r:id="rId4"/>
+    <sheet name="River North" sheetId="5" r:id="rId5"/>
+    <sheet name="North Lawndale" sheetId="6" r:id="rId6"/>
+    <sheet name="Englewood" sheetId="7" r:id="rId7"/>
+    <sheet name="Uptown" sheetId="8" r:id="rId8"/>
+    <sheet name="Loop" sheetId="9" r:id="rId9"/>
+    <sheet name="Logan Square" sheetId="10" r:id="rId10"/>
+    <sheet name="Riverdale" sheetId="11" r:id="rId11"/>
+    <sheet name="Fuller Park" sheetId="12" r:id="rId12"/>
+    <sheet name="Little Village" sheetId="13" r:id="rId13"/>
+    <sheet name="Chatham" sheetId="14" r:id="rId14"/>
+    <sheet name="West Loop" sheetId="15" r:id="rId15"/>
+    <sheet name="Auburn Gresham" sheetId="16" r:id="rId16"/>
+    <sheet name="Lake View" sheetId="17" r:id="rId17"/>
+    <sheet name="Humboldt Park" sheetId="18" r:id="rId18"/>
+    <sheet name="Austin" sheetId="19" r:id="rId19"/>
+    <sheet name="Roseland" sheetId="20" r:id="rId20"/>
+    <sheet name="Albany Park" sheetId="21" r:id="rId21"/>
+    <sheet name="Woodlawn" sheetId="22" r:id="rId22"/>
+    <sheet name="South Shore" sheetId="23" r:id="rId23"/>
+    <sheet name="Old Town" sheetId="24" r:id="rId24"/>
+    <sheet name="Lincoln Park" sheetId="25" r:id="rId25"/>
+    <sheet name="Near South Side" sheetId="26" r:id="rId26"/>
+    <sheet name="Grand Crossing" sheetId="27" r:id="rId27"/>
+    <sheet name="Avondale" sheetId="28" r:id="rId28"/>
+    <sheet name="Rush &amp; Division" sheetId="29" r:id="rId29"/>
+    <sheet name="Oakland" sheetId="30" r:id="rId30"/>
+    <sheet name="New City" sheetId="31" r:id="rId31"/>
+    <sheet name="Belmont Cragin" sheetId="32" r:id="rId32"/>
+    <sheet name="Printers Row" sheetId="33" r:id="rId33"/>
+    <sheet name="Hegewisch" sheetId="34" r:id="rId34"/>
+    <sheet name="Hyde Park" sheetId="35" r:id="rId35"/>
+    <sheet name="Grand Boulevard" sheetId="36" r:id="rId36"/>
+    <sheet name="West Town" sheetId="37" r:id="rId37"/>
+    <sheet name="Douglas" sheetId="38" r:id="rId38"/>
+    <sheet name="Norwood Park" sheetId="39" r:id="rId39"/>
+    <sheet name="Washington Park" sheetId="40" r:id="rId40"/>
+    <sheet name="Greektown" sheetId="41" r:id="rId41"/>
+    <sheet name="Rogers Park" sheetId="42" r:id="rId42"/>
     <sheet name="Edgewater" sheetId="43" r:id="rId43"/>
     <sheet name="Little Italy, UIC" sheetId="44" r:id="rId44"/>
     <sheet name="Gage Park" sheetId="45" r:id="rId45"/>
@@ -946,7 +946,7 @@
         <v>262</v>
       </c>
       <c r="M3">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -1197,7 +1197,7 @@
         <v>703</v>
       </c>
       <c r="M10">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -1238,7 +1238,7 @@
         <v>1604</v>
       </c>
       <c r="M11">
-        <v>850</v>
+        <v>852</v>
       </c>
     </row>
   </sheetData>
@@ -1247,6 +1247,281 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:M8"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+    <col min="13" max="13" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="M1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>2</v>
+      </c>
+      <c r="G2">
+        <v>4</v>
+      </c>
+      <c r="H2">
+        <v>1</v>
+      </c>
+      <c r="I2">
+        <v>1</v>
+      </c>
+      <c r="J2">
+        <v>3</v>
+      </c>
+      <c r="K2">
+        <v>2</v>
+      </c>
+      <c r="L2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
+      <c r="E3">
+        <v>1</v>
+      </c>
+      <c r="H3">
+        <v>1</v>
+      </c>
+      <c r="I3">
+        <v>1</v>
+      </c>
+      <c r="J3">
+        <v>3</v>
+      </c>
+      <c r="K3">
+        <v>1</v>
+      </c>
+      <c r="L3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D4">
+        <v>1</v>
+      </c>
+      <c r="E4">
+        <v>1</v>
+      </c>
+      <c r="J4">
+        <v>1</v>
+      </c>
+      <c r="L4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5">
+        <v>1</v>
+      </c>
+      <c r="J5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6">
+        <v>2</v>
+      </c>
+      <c r="C6">
+        <v>5</v>
+      </c>
+      <c r="D6">
+        <v>3</v>
+      </c>
+      <c r="E6">
+        <v>4</v>
+      </c>
+      <c r="F6">
+        <v>5</v>
+      </c>
+      <c r="G6">
+        <v>5</v>
+      </c>
+      <c r="H6">
+        <v>8</v>
+      </c>
+      <c r="I6">
+        <v>5</v>
+      </c>
+      <c r="J6">
+        <v>8</v>
+      </c>
+      <c r="K6">
+        <v>7</v>
+      </c>
+      <c r="L6">
+        <v>7</v>
+      </c>
+      <c r="M6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7">
+        <v>17</v>
+      </c>
+      <c r="C7">
+        <v>24</v>
+      </c>
+      <c r="D7">
+        <v>35</v>
+      </c>
+      <c r="E7">
+        <v>31</v>
+      </c>
+      <c r="F7">
+        <v>18</v>
+      </c>
+      <c r="G7">
+        <v>17</v>
+      </c>
+      <c r="H7">
+        <v>8</v>
+      </c>
+      <c r="I7">
+        <v>16</v>
+      </c>
+      <c r="J7">
+        <v>15</v>
+      </c>
+      <c r="K7">
+        <v>10</v>
+      </c>
+      <c r="L7">
+        <v>12</v>
+      </c>
+      <c r="M7">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13">
+      <c r="A8" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B8">
+        <v>19</v>
+      </c>
+      <c r="C8">
+        <v>32</v>
+      </c>
+      <c r="D8">
+        <v>42</v>
+      </c>
+      <c r="E8">
+        <v>37</v>
+      </c>
+      <c r="F8">
+        <v>23</v>
+      </c>
+      <c r="G8">
+        <v>26</v>
+      </c>
+      <c r="H8">
+        <v>18</v>
+      </c>
+      <c r="I8">
+        <v>23</v>
+      </c>
+      <c r="J8">
+        <v>31</v>
+      </c>
+      <c r="K8">
+        <v>20</v>
+      </c>
+      <c r="L8">
+        <v>26</v>
+      </c>
+      <c r="M8">
+        <v>9</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:L6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -1423,7 +1698,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M9"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -1703,7 +1978,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -1946,7 +2221,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M10"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -2261,7 +2536,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M9"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -2547,7 +2822,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -2820,7 +3095,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M8"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -3116,7 +3391,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M9"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -3401,324 +3676,6 @@
       </c>
       <c r="M9">
         <v>15</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M10"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" customWidth="1"/>
-    <col min="13" max="13" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="M1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2">
-        <v>4</v>
-      </c>
-      <c r="C2">
-        <v>4</v>
-      </c>
-      <c r="D2">
-        <v>3</v>
-      </c>
-      <c r="E2">
-        <v>5</v>
-      </c>
-      <c r="F2">
-        <v>9</v>
-      </c>
-      <c r="G2">
-        <v>3</v>
-      </c>
-      <c r="H2">
-        <v>5</v>
-      </c>
-      <c r="I2">
-        <v>4</v>
-      </c>
-      <c r="J2">
-        <v>8</v>
-      </c>
-      <c r="K2">
-        <v>7</v>
-      </c>
-      <c r="L2">
-        <v>5</v>
-      </c>
-      <c r="M2">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3">
-        <v>4</v>
-      </c>
-      <c r="C3">
-        <v>5</v>
-      </c>
-      <c r="D3">
-        <v>6</v>
-      </c>
-      <c r="E3">
-        <v>7</v>
-      </c>
-      <c r="F3">
-        <v>6</v>
-      </c>
-      <c r="G3">
-        <v>7</v>
-      </c>
-      <c r="H3">
-        <v>8</v>
-      </c>
-      <c r="I3">
-        <v>6</v>
-      </c>
-      <c r="J3">
-        <v>10</v>
-      </c>
-      <c r="K3">
-        <v>12</v>
-      </c>
-      <c r="L3">
-        <v>14</v>
-      </c>
-      <c r="M3">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="I4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5">
-        <v>1</v>
-      </c>
-      <c r="D5">
-        <v>1</v>
-      </c>
-      <c r="E5">
-        <v>1</v>
-      </c>
-      <c r="J5">
-        <v>3</v>
-      </c>
-      <c r="K5">
-        <v>2</v>
-      </c>
-      <c r="M5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="K6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
-      <c r="A7" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="L7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13">
-      <c r="A8" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B8">
-        <v>23</v>
-      </c>
-      <c r="C8">
-        <v>31</v>
-      </c>
-      <c r="D8">
-        <v>22</v>
-      </c>
-      <c r="E8">
-        <v>44</v>
-      </c>
-      <c r="F8">
-        <v>38</v>
-      </c>
-      <c r="G8">
-        <v>24</v>
-      </c>
-      <c r="H8">
-        <v>50</v>
-      </c>
-      <c r="I8">
-        <v>34</v>
-      </c>
-      <c r="J8">
-        <v>26</v>
-      </c>
-      <c r="K8">
-        <v>24</v>
-      </c>
-      <c r="L8">
-        <v>14</v>
-      </c>
-      <c r="M8">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13">
-      <c r="A9" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B9">
-        <v>46</v>
-      </c>
-      <c r="C9">
-        <v>59</v>
-      </c>
-      <c r="D9">
-        <v>33</v>
-      </c>
-      <c r="E9">
-        <v>73</v>
-      </c>
-      <c r="F9">
-        <v>114</v>
-      </c>
-      <c r="G9">
-        <v>58</v>
-      </c>
-      <c r="H9">
-        <v>41</v>
-      </c>
-      <c r="I9">
-        <v>44</v>
-      </c>
-      <c r="J9">
-        <v>20</v>
-      </c>
-      <c r="K9">
-        <v>25</v>
-      </c>
-      <c r="L9">
-        <v>27</v>
-      </c>
-      <c r="M9">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13">
-      <c r="A10" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B10">
-        <v>78</v>
-      </c>
-      <c r="C10">
-        <v>99</v>
-      </c>
-      <c r="D10">
-        <v>65</v>
-      </c>
-      <c r="E10">
-        <v>130</v>
-      </c>
-      <c r="F10">
-        <v>167</v>
-      </c>
-      <c r="G10">
-        <v>92</v>
-      </c>
-      <c r="H10">
-        <v>104</v>
-      </c>
-      <c r="I10">
-        <v>89</v>
-      </c>
-      <c r="J10">
-        <v>67</v>
-      </c>
-      <c r="K10">
-        <v>71</v>
-      </c>
-      <c r="L10">
-        <v>61</v>
-      </c>
-      <c r="M10">
-        <v>53</v>
       </c>
     </row>
   </sheetData>
@@ -3792,40 +3749,40 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C2">
         <v>4</v>
       </c>
       <c r="D2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F2">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="G2">
         <v>3</v>
       </c>
       <c r="H2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I2">
+        <v>4</v>
+      </c>
+      <c r="J2">
+        <v>8</v>
+      </c>
+      <c r="K2">
         <v>7</v>
       </c>
-      <c r="J2">
-        <v>1</v>
-      </c>
-      <c r="K2">
-        <v>3</v>
-      </c>
       <c r="L2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M2">
-        <v>1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -3833,47 +3790,47 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D3">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E3">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F3">
+        <v>6</v>
+      </c>
+      <c r="G3">
         <v>7</v>
       </c>
-      <c r="G3">
+      <c r="H3">
+        <v>8</v>
+      </c>
+      <c r="I3">
         <v>6</v>
       </c>
-      <c r="H3">
-        <v>6</v>
-      </c>
-      <c r="I3">
-        <v>9</v>
-      </c>
       <c r="J3">
+        <v>10</v>
+      </c>
+      <c r="K3">
+        <v>12</v>
+      </c>
+      <c r="L3">
         <v>14</v>
       </c>
-      <c r="K3">
-        <v>7</v>
-      </c>
-      <c r="L3">
-        <v>7</v>
-      </c>
       <c r="M3">
-        <v>4</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="D4">
+        <v>3</v>
+      </c>
+      <c r="I4">
         <v>1</v>
       </c>
     </row>
@@ -3881,33 +3838,30 @@
       <c r="A5" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C5">
-        <v>1</v>
-      </c>
-      <c r="G5">
-        <v>1</v>
-      </c>
-      <c r="I5">
-        <v>2</v>
+      <c r="B5">
+        <v>1</v>
+      </c>
+      <c r="D5">
+        <v>1</v>
+      </c>
+      <c r="E5">
+        <v>1</v>
       </c>
       <c r="J5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K5">
-        <v>1</v>
-      </c>
-      <c r="L5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M5">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D6">
+      <c r="K6">
         <v>1</v>
       </c>
     </row>
@@ -3915,7 +3869,7 @@
       <c r="A7" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="J7">
+      <c r="L7">
         <v>1</v>
       </c>
     </row>
@@ -3924,40 +3878,40 @@
         <v>8</v>
       </c>
       <c r="B8">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="C8">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="D8">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="E8">
+        <v>44</v>
+      </c>
+      <c r="F8">
+        <v>38</v>
+      </c>
+      <c r="G8">
+        <v>24</v>
+      </c>
+      <c r="H8">
+        <v>50</v>
+      </c>
+      <c r="I8">
+        <v>34</v>
+      </c>
+      <c r="J8">
+        <v>26</v>
+      </c>
+      <c r="K8">
+        <v>24</v>
+      </c>
+      <c r="L8">
         <v>14</v>
       </c>
-      <c r="F8">
-        <v>12</v>
-      </c>
-      <c r="G8">
-        <v>14</v>
-      </c>
-      <c r="H8">
-        <v>19</v>
-      </c>
-      <c r="I8">
-        <v>29</v>
-      </c>
-      <c r="J8">
-        <v>19</v>
-      </c>
-      <c r="K8">
-        <v>20</v>
-      </c>
-      <c r="L8">
-        <v>26</v>
-      </c>
       <c r="M8">
-        <v>6</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -3965,37 +3919,37 @@
         <v>9</v>
       </c>
       <c r="B9">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="C9">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="D9">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="E9">
-        <v>51</v>
+        <v>73</v>
       </c>
       <c r="F9">
-        <v>54</v>
+        <v>114</v>
       </c>
       <c r="G9">
-        <v>32</v>
+        <v>58</v>
       </c>
       <c r="H9">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="I9">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="J9">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="K9">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="L9">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="M9">
         <v>16</v>
@@ -4006,40 +3960,40 @@
         <v>10</v>
       </c>
       <c r="B10">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="C10">
-        <v>70</v>
+        <v>99</v>
       </c>
       <c r="D10">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="E10">
-        <v>74</v>
+        <v>130</v>
       </c>
       <c r="F10">
-        <v>77</v>
+        <v>167</v>
       </c>
       <c r="G10">
-        <v>56</v>
+        <v>92</v>
       </c>
       <c r="H10">
-        <v>60</v>
+        <v>104</v>
       </c>
       <c r="I10">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="J10">
-        <v>76</v>
+        <v>67</v>
       </c>
       <c r="K10">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="L10">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="M10">
-        <v>28</v>
+        <v>53</v>
       </c>
     </row>
   </sheetData>
@@ -5253,7 +5207,7 @@
         <v>71</v>
       </c>
       <c r="M32">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="33" spans="1:13">
@@ -7841,7 +7795,7 @@
         <v>1604</v>
       </c>
       <c r="M99">
-        <v>850</v>
+        <v>852</v>
       </c>
     </row>
   </sheetData>
@@ -7951,7 +7905,7 @@
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M7"/>
+  <dimension ref="A1:M10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="23.7109375" customWidth="1"/>
@@ -8014,29 +7968,41 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
+      <c r="B2">
+        <v>2</v>
+      </c>
+      <c r="C2">
+        <v>4</v>
+      </c>
       <c r="D2">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="E2">
+        <v>4</v>
       </c>
       <c r="F2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G2">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="H2">
+        <v>6</v>
       </c>
       <c r="I2">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="J2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -8044,153 +8010,213 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C3">
-        <v>1</v>
+        <v>4</v>
+      </c>
+      <c r="D3">
+        <v>2</v>
+      </c>
+      <c r="E3">
+        <v>5</v>
+      </c>
+      <c r="F3">
+        <v>7</v>
       </c>
       <c r="G3">
-        <v>2</v>
+        <v>6</v>
+      </c>
+      <c r="H3">
+        <v>6</v>
       </c>
       <c r="I3">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="J3">
-        <v>1</v>
+        <v>14</v>
+      </c>
+      <c r="K3">
+        <v>7</v>
       </c>
       <c r="L3">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="M3">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="E4">
-        <v>2</v>
-      </c>
-      <c r="J4">
-        <v>1</v>
-      </c>
-      <c r="K4">
+        <v>4</v>
+      </c>
+      <c r="D4">
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C5">
         <v>1</v>
       </c>
-      <c r="D5">
-        <v>2</v>
-      </c>
-      <c r="E5">
-        <v>2</v>
-      </c>
       <c r="G5">
         <v>1</v>
       </c>
       <c r="I5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K5">
-        <v>4</v>
+        <v>1</v>
+      </c>
+      <c r="L5">
+        <v>1</v>
       </c>
       <c r="M5">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B6">
-        <v>8</v>
-      </c>
-      <c r="C6">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="D6">
-        <v>10</v>
-      </c>
-      <c r="E6">
-        <v>9</v>
-      </c>
-      <c r="F6">
-        <v>9</v>
-      </c>
-      <c r="G6">
-        <v>8</v>
-      </c>
-      <c r="H6">
-        <v>1</v>
-      </c>
-      <c r="I6">
-        <v>4</v>
-      </c>
-      <c r="J6">
-        <v>5</v>
-      </c>
-      <c r="K6">
-        <v>8</v>
-      </c>
-      <c r="L6">
-        <v>3</v>
-      </c>
-      <c r="M6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="J7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13">
+      <c r="A8" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8">
+        <v>19</v>
+      </c>
+      <c r="C8">
+        <v>16</v>
+      </c>
+      <c r="D8">
+        <v>11</v>
+      </c>
+      <c r="E8">
+        <v>14</v>
+      </c>
+      <c r="F8">
+        <v>12</v>
+      </c>
+      <c r="G8">
+        <v>14</v>
+      </c>
+      <c r="H8">
+        <v>19</v>
+      </c>
+      <c r="I8">
+        <v>29</v>
+      </c>
+      <c r="J8">
+        <v>19</v>
+      </c>
+      <c r="K8">
+        <v>20</v>
+      </c>
+      <c r="L8">
+        <v>26</v>
+      </c>
+      <c r="M8">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13">
+      <c r="A9" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B9">
+        <v>56</v>
+      </c>
+      <c r="C9">
+        <v>45</v>
+      </c>
+      <c r="D9">
+        <v>42</v>
+      </c>
+      <c r="E9">
+        <v>51</v>
+      </c>
+      <c r="F9">
+        <v>54</v>
+      </c>
+      <c r="G9">
+        <v>32</v>
+      </c>
+      <c r="H9">
+        <v>29</v>
+      </c>
+      <c r="I9">
+        <v>35</v>
+      </c>
+      <c r="J9">
+        <v>40</v>
+      </c>
+      <c r="K9">
+        <v>37</v>
+      </c>
+      <c r="L9">
+        <v>25</v>
+      </c>
+      <c r="M9">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13">
+      <c r="A10" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B7">
-        <v>10</v>
-      </c>
-      <c r="C7">
-        <v>15</v>
-      </c>
-      <c r="D7">
-        <v>13</v>
-      </c>
-      <c r="E7">
-        <v>13</v>
-      </c>
-      <c r="F7">
-        <v>10</v>
-      </c>
-      <c r="G7">
-        <v>12</v>
-      </c>
-      <c r="H7">
-        <v>1</v>
-      </c>
-      <c r="I7">
-        <v>8</v>
-      </c>
-      <c r="J7">
-        <v>14</v>
-      </c>
-      <c r="K7">
-        <v>15</v>
-      </c>
-      <c r="L7">
-        <v>6</v>
-      </c>
-      <c r="M7">
-        <v>7</v>
+      <c r="B10">
+        <v>82</v>
+      </c>
+      <c r="C10">
+        <v>70</v>
+      </c>
+      <c r="D10">
+        <v>59</v>
+      </c>
+      <c r="E10">
+        <v>74</v>
+      </c>
+      <c r="F10">
+        <v>77</v>
+      </c>
+      <c r="G10">
+        <v>56</v>
+      </c>
+      <c r="H10">
+        <v>60</v>
+      </c>
+      <c r="I10">
+        <v>82</v>
+      </c>
+      <c r="J10">
+        <v>76</v>
+      </c>
+      <c r="K10">
+        <v>68</v>
+      </c>
+      <c r="L10">
+        <v>62</v>
+      </c>
+      <c r="M10">
+        <v>28</v>
       </c>
     </row>
   </sheetData>
@@ -8263,23 +8289,29 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2">
-        <v>3</v>
-      </c>
-      <c r="E2">
-        <v>2</v>
+      <c r="D2">
+        <v>1</v>
       </c>
       <c r="F2">
         <v>1</v>
       </c>
       <c r="G2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I2">
         <v>2</v>
       </c>
+      <c r="J2">
+        <v>4</v>
+      </c>
+      <c r="K2">
+        <v>2</v>
+      </c>
       <c r="L2">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="M2">
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -8287,44 +8319,38 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C3">
         <v>1</v>
       </c>
-      <c r="D3">
-        <v>5</v>
-      </c>
-      <c r="F3">
-        <v>2</v>
-      </c>
       <c r="G3">
-        <v>3</v>
-      </c>
-      <c r="H3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I3">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J3">
-        <v>5</v>
-      </c>
-      <c r="K3">
-        <v>5</v>
+        <v>1</v>
+      </c>
+      <c r="L3">
+        <v>1</v>
       </c>
       <c r="M3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F4">
-        <v>1</v>
-      </c>
-      <c r="H4">
+      <c r="E4">
+        <v>2</v>
+      </c>
+      <c r="J4">
+        <v>1</v>
+      </c>
+      <c r="K4">
         <v>1</v>
       </c>
     </row>
@@ -8333,36 +8359,27 @@
         <v>8</v>
       </c>
       <c r="B5">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="C5">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="D5">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E5">
-        <v>9</v>
-      </c>
-      <c r="F5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G5">
-        <v>2</v>
-      </c>
-      <c r="H5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J5">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="K5">
-        <v>7</v>
-      </c>
-      <c r="L5">
         <v>4</v>
       </c>
       <c r="M5">
@@ -8374,40 +8391,40 @@
         <v>9</v>
       </c>
       <c r="B6">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="C6">
+        <v>13</v>
+      </c>
+      <c r="D6">
         <v>10</v>
       </c>
-      <c r="D6">
-        <v>17</v>
-      </c>
       <c r="E6">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="F6">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="G6">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H6">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I6">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J6">
+        <v>5</v>
+      </c>
+      <c r="K6">
         <v>8</v>
       </c>
-      <c r="K6">
-        <v>3</v>
-      </c>
       <c r="L6">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M6">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -8415,31 +8432,31 @@
         <v>10</v>
       </c>
       <c r="B7">
-        <v>33</v>
+        <v>10</v>
       </c>
       <c r="C7">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="D7">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="E7">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="F7">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="G7">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H7">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="I7">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="J7">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="K7">
         <v>15</v>
@@ -8448,7 +8465,7 @@
         <v>6</v>
       </c>
       <c r="M7">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -8457,6 +8474,264 @@
 </file>
 
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:M7"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+    <col min="13" max="13" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="M1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>3</v>
+      </c>
+      <c r="E2">
+        <v>2</v>
+      </c>
+      <c r="F2">
+        <v>1</v>
+      </c>
+      <c r="G2">
+        <v>2</v>
+      </c>
+      <c r="I2">
+        <v>2</v>
+      </c>
+      <c r="L2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>2</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
+      <c r="D3">
+        <v>5</v>
+      </c>
+      <c r="F3">
+        <v>2</v>
+      </c>
+      <c r="G3">
+        <v>3</v>
+      </c>
+      <c r="H3">
+        <v>3</v>
+      </c>
+      <c r="I3">
+        <v>5</v>
+      </c>
+      <c r="J3">
+        <v>5</v>
+      </c>
+      <c r="K3">
+        <v>5</v>
+      </c>
+      <c r="M3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F4">
+        <v>1</v>
+      </c>
+      <c r="H4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5">
+        <v>11</v>
+      </c>
+      <c r="C5">
+        <v>12</v>
+      </c>
+      <c r="D5">
+        <v>5</v>
+      </c>
+      <c r="E5">
+        <v>9</v>
+      </c>
+      <c r="F5">
+        <v>3</v>
+      </c>
+      <c r="G5">
+        <v>2</v>
+      </c>
+      <c r="H5">
+        <v>4</v>
+      </c>
+      <c r="I5">
+        <v>4</v>
+      </c>
+      <c r="J5">
+        <v>6</v>
+      </c>
+      <c r="K5">
+        <v>7</v>
+      </c>
+      <c r="L5">
+        <v>4</v>
+      </c>
+      <c r="M5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6">
+        <v>17</v>
+      </c>
+      <c r="C6">
+        <v>10</v>
+      </c>
+      <c r="D6">
+        <v>17</v>
+      </c>
+      <c r="E6">
+        <v>14</v>
+      </c>
+      <c r="F6">
+        <v>15</v>
+      </c>
+      <c r="G6">
+        <v>6</v>
+      </c>
+      <c r="H6">
+        <v>3</v>
+      </c>
+      <c r="I6">
+        <v>6</v>
+      </c>
+      <c r="J6">
+        <v>8</v>
+      </c>
+      <c r="K6">
+        <v>3</v>
+      </c>
+      <c r="L6">
+        <v>1</v>
+      </c>
+      <c r="M6">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7">
+        <v>33</v>
+      </c>
+      <c r="C7">
+        <v>23</v>
+      </c>
+      <c r="D7">
+        <v>27</v>
+      </c>
+      <c r="E7">
+        <v>25</v>
+      </c>
+      <c r="F7">
+        <v>22</v>
+      </c>
+      <c r="G7">
+        <v>13</v>
+      </c>
+      <c r="H7">
+        <v>11</v>
+      </c>
+      <c r="I7">
+        <v>17</v>
+      </c>
+      <c r="J7">
+        <v>19</v>
+      </c>
+      <c r="K7">
+        <v>15</v>
+      </c>
+      <c r="L7">
+        <v>6</v>
+      </c>
+      <c r="M7">
+        <v>10</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -8727,7 +9002,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M8"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -8993,7 +9268,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -9233,7 +9508,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M8"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -9499,7 +9774,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M10"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -9819,258 +10094,6 @@
       </c>
       <c r="M10">
         <v>40</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M7"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" customWidth="1"/>
-    <col min="13" max="13" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="M1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2">
-        <v>1</v>
-      </c>
-      <c r="C2">
-        <v>1</v>
-      </c>
-      <c r="D2">
-        <v>1</v>
-      </c>
-      <c r="E2">
-        <v>2</v>
-      </c>
-      <c r="H2">
-        <v>1</v>
-      </c>
-      <c r="I2">
-        <v>2</v>
-      </c>
-      <c r="J2">
-        <v>1</v>
-      </c>
-      <c r="K2">
-        <v>2</v>
-      </c>
-      <c r="M2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="E3">
-        <v>2</v>
-      </c>
-      <c r="F3">
-        <v>2</v>
-      </c>
-      <c r="G3">
-        <v>1</v>
-      </c>
-      <c r="J3">
-        <v>2</v>
-      </c>
-      <c r="L3">
-        <v>2</v>
-      </c>
-      <c r="M3">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B4">
-        <v>1</v>
-      </c>
-      <c r="K4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5">
-        <v>2</v>
-      </c>
-      <c r="C5">
-        <v>1</v>
-      </c>
-      <c r="D5">
-        <v>3</v>
-      </c>
-      <c r="E5">
-        <v>1</v>
-      </c>
-      <c r="F5">
-        <v>3</v>
-      </c>
-      <c r="G5">
-        <v>4</v>
-      </c>
-      <c r="H5">
-        <v>5</v>
-      </c>
-      <c r="I5">
-        <v>3</v>
-      </c>
-      <c r="J5">
-        <v>6</v>
-      </c>
-      <c r="K5">
-        <v>3</v>
-      </c>
-      <c r="L5">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B6">
-        <v>11</v>
-      </c>
-      <c r="C6">
-        <v>12</v>
-      </c>
-      <c r="D6">
-        <v>29</v>
-      </c>
-      <c r="E6">
-        <v>16</v>
-      </c>
-      <c r="F6">
-        <v>16</v>
-      </c>
-      <c r="G6">
-        <v>8</v>
-      </c>
-      <c r="H6">
-        <v>2</v>
-      </c>
-      <c r="I6">
-        <v>10</v>
-      </c>
-      <c r="J6">
-        <v>13</v>
-      </c>
-      <c r="K6">
-        <v>11</v>
-      </c>
-      <c r="L6">
-        <v>15</v>
-      </c>
-      <c r="M6">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
-      <c r="A7" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B7">
-        <v>15</v>
-      </c>
-      <c r="C7">
-        <v>14</v>
-      </c>
-      <c r="D7">
-        <v>33</v>
-      </c>
-      <c r="E7">
-        <v>21</v>
-      </c>
-      <c r="F7">
-        <v>21</v>
-      </c>
-      <c r="G7">
-        <v>13</v>
-      </c>
-      <c r="H7">
-        <v>8</v>
-      </c>
-      <c r="I7">
-        <v>15</v>
-      </c>
-      <c r="J7">
-        <v>22</v>
-      </c>
-      <c r="K7">
-        <v>17</v>
-      </c>
-      <c r="L7">
-        <v>20</v>
-      </c>
-      <c r="M7">
-        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -10144,67 +10167,64 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
       </c>
       <c r="D2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J2">
         <v>1</v>
       </c>
       <c r="K2">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="M2">
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B3">
-        <v>1</v>
-      </c>
-      <c r="D3">
-        <v>1</v>
-      </c>
       <c r="E3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F3">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G3">
-        <v>2</v>
-      </c>
-      <c r="H3">
-        <v>2</v>
-      </c>
-      <c r="I3">
-        <v>4</v>
-      </c>
-      <c r="K3">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="J3">
+        <v>2</v>
       </c>
       <c r="L3">
         <v>2</v>
       </c>
       <c r="M3">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="M4">
+      <c r="B4">
+        <v>1</v>
+      </c>
+      <c r="K4">
         <v>1</v>
       </c>
     </row>
@@ -10213,40 +10233,37 @@
         <v>8</v>
       </c>
       <c r="B5">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D5">
         <v>3</v>
       </c>
       <c r="E5">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="F5">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="G5">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="H5">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="I5">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="J5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K5">
         <v>3</v>
       </c>
       <c r="L5">
-        <v>5</v>
-      </c>
-      <c r="M5">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -10254,40 +10271,40 @@
         <v>9</v>
       </c>
       <c r="B6">
-        <v>34</v>
+        <v>11</v>
       </c>
       <c r="C6">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="D6">
-        <v>64</v>
+        <v>29</v>
       </c>
       <c r="E6">
-        <v>44</v>
+        <v>16</v>
       </c>
       <c r="F6">
-        <v>45</v>
+        <v>16</v>
       </c>
       <c r="G6">
+        <v>8</v>
+      </c>
+      <c r="H6">
+        <v>2</v>
+      </c>
+      <c r="I6">
+        <v>10</v>
+      </c>
+      <c r="J6">
+        <v>13</v>
+      </c>
+      <c r="K6">
         <v>11</v>
       </c>
-      <c r="H6">
-        <v>7</v>
-      </c>
-      <c r="I6">
-        <v>7</v>
-      </c>
-      <c r="J6">
+      <c r="L6">
         <v>15</v>
       </c>
-      <c r="K6">
-        <v>9</v>
-      </c>
-      <c r="L6">
-        <v>12</v>
-      </c>
       <c r="M6">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -10295,40 +10312,40 @@
         <v>10</v>
       </c>
       <c r="B7">
-        <v>42</v>
+        <v>15</v>
       </c>
       <c r="C7">
-        <v>37</v>
+        <v>14</v>
       </c>
       <c r="D7">
-        <v>70</v>
+        <v>33</v>
       </c>
       <c r="E7">
-        <v>55</v>
+        <v>21</v>
       </c>
       <c r="F7">
-        <v>58</v>
+        <v>21</v>
       </c>
       <c r="G7">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="H7">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="I7">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="J7">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K7">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="L7">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="M7">
-        <v>5</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -10337,6 +10354,577 @@
 </file>
 
 <file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:M7"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+    <col min="13" max="13" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="M1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>2</v>
+      </c>
+      <c r="D2">
+        <v>2</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
+      <c r="H2">
+        <v>2</v>
+      </c>
+      <c r="I2">
+        <v>1</v>
+      </c>
+      <c r="J2">
+        <v>1</v>
+      </c>
+      <c r="K2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>1</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
+      <c r="E3">
+        <v>3</v>
+      </c>
+      <c r="F3">
+        <v>4</v>
+      </c>
+      <c r="G3">
+        <v>2</v>
+      </c>
+      <c r="H3">
+        <v>2</v>
+      </c>
+      <c r="I3">
+        <v>4</v>
+      </c>
+      <c r="K3">
+        <v>1</v>
+      </c>
+      <c r="L3">
+        <v>2</v>
+      </c>
+      <c r="M3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="M4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5">
+        <v>5</v>
+      </c>
+      <c r="C5">
+        <v>4</v>
+      </c>
+      <c r="D5">
+        <v>3</v>
+      </c>
+      <c r="E5">
+        <v>7</v>
+      </c>
+      <c r="F5">
+        <v>9</v>
+      </c>
+      <c r="G5">
+        <v>14</v>
+      </c>
+      <c r="H5">
+        <v>7</v>
+      </c>
+      <c r="I5">
+        <v>9</v>
+      </c>
+      <c r="J5">
+        <v>5</v>
+      </c>
+      <c r="K5">
+        <v>3</v>
+      </c>
+      <c r="L5">
+        <v>5</v>
+      </c>
+      <c r="M5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6">
+        <v>34</v>
+      </c>
+      <c r="C6">
+        <v>33</v>
+      </c>
+      <c r="D6">
+        <v>64</v>
+      </c>
+      <c r="E6">
+        <v>44</v>
+      </c>
+      <c r="F6">
+        <v>45</v>
+      </c>
+      <c r="G6">
+        <v>11</v>
+      </c>
+      <c r="H6">
+        <v>7</v>
+      </c>
+      <c r="I6">
+        <v>7</v>
+      </c>
+      <c r="J6">
+        <v>15</v>
+      </c>
+      <c r="K6">
+        <v>9</v>
+      </c>
+      <c r="L6">
+        <v>12</v>
+      </c>
+      <c r="M6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7">
+        <v>42</v>
+      </c>
+      <c r="C7">
+        <v>37</v>
+      </c>
+      <c r="D7">
+        <v>70</v>
+      </c>
+      <c r="E7">
+        <v>55</v>
+      </c>
+      <c r="F7">
+        <v>58</v>
+      </c>
+      <c r="G7">
+        <v>27</v>
+      </c>
+      <c r="H7">
+        <v>18</v>
+      </c>
+      <c r="I7">
+        <v>21</v>
+      </c>
+      <c r="J7">
+        <v>21</v>
+      </c>
+      <c r="K7">
+        <v>14</v>
+      </c>
+      <c r="L7">
+        <v>19</v>
+      </c>
+      <c r="M7">
+        <v>5</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:M9"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+    <col min="13" max="13" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="M1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>2</v>
+      </c>
+      <c r="D2">
+        <v>7</v>
+      </c>
+      <c r="E2">
+        <v>8</v>
+      </c>
+      <c r="F2">
+        <v>5</v>
+      </c>
+      <c r="G2">
+        <v>4</v>
+      </c>
+      <c r="H2">
+        <v>2</v>
+      </c>
+      <c r="I2">
+        <v>5</v>
+      </c>
+      <c r="J2">
+        <v>3</v>
+      </c>
+      <c r="K2">
+        <v>5</v>
+      </c>
+      <c r="L2">
+        <v>5</v>
+      </c>
+      <c r="M2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>1</v>
+      </c>
+      <c r="C3">
+        <v>3</v>
+      </c>
+      <c r="D3">
+        <v>9</v>
+      </c>
+      <c r="E3">
+        <v>4</v>
+      </c>
+      <c r="F3">
+        <v>5</v>
+      </c>
+      <c r="G3">
+        <v>6</v>
+      </c>
+      <c r="H3">
+        <v>8</v>
+      </c>
+      <c r="I3">
+        <v>9</v>
+      </c>
+      <c r="J3">
+        <v>14</v>
+      </c>
+      <c r="K3">
+        <v>16</v>
+      </c>
+      <c r="L3">
+        <v>8</v>
+      </c>
+      <c r="M3">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5">
+        <v>2</v>
+      </c>
+      <c r="D5">
+        <v>1</v>
+      </c>
+      <c r="E5">
+        <v>1</v>
+      </c>
+      <c r="F5">
+        <v>1</v>
+      </c>
+      <c r="H5">
+        <v>1</v>
+      </c>
+      <c r="I5">
+        <v>2</v>
+      </c>
+      <c r="M5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="I6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7">
+        <v>15</v>
+      </c>
+      <c r="C7">
+        <v>35</v>
+      </c>
+      <c r="D7">
+        <v>34</v>
+      </c>
+      <c r="E7">
+        <v>56</v>
+      </c>
+      <c r="F7">
+        <v>54</v>
+      </c>
+      <c r="G7">
+        <v>37</v>
+      </c>
+      <c r="H7">
+        <v>39</v>
+      </c>
+      <c r="I7">
+        <v>32</v>
+      </c>
+      <c r="J7">
+        <v>34</v>
+      </c>
+      <c r="K7">
+        <v>27</v>
+      </c>
+      <c r="L7">
+        <v>31</v>
+      </c>
+      <c r="M7">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13">
+      <c r="A8" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B8">
+        <v>54</v>
+      </c>
+      <c r="C8">
+        <v>63</v>
+      </c>
+      <c r="D8">
+        <v>50</v>
+      </c>
+      <c r="E8">
+        <v>109</v>
+      </c>
+      <c r="F8">
+        <v>138</v>
+      </c>
+      <c r="G8">
+        <v>53</v>
+      </c>
+      <c r="H8">
+        <v>29</v>
+      </c>
+      <c r="I8">
+        <v>49</v>
+      </c>
+      <c r="J8">
+        <v>34</v>
+      </c>
+      <c r="K8">
+        <v>28</v>
+      </c>
+      <c r="L8">
+        <v>27</v>
+      </c>
+      <c r="M8">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13">
+      <c r="A9" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B9">
+        <v>73</v>
+      </c>
+      <c r="C9">
+        <v>103</v>
+      </c>
+      <c r="D9">
+        <v>101</v>
+      </c>
+      <c r="E9">
+        <v>178</v>
+      </c>
+      <c r="F9">
+        <v>204</v>
+      </c>
+      <c r="G9">
+        <v>100</v>
+      </c>
+      <c r="H9">
+        <v>79</v>
+      </c>
+      <c r="I9">
+        <v>98</v>
+      </c>
+      <c r="J9">
+        <v>85</v>
+      </c>
+      <c r="K9">
+        <v>76</v>
+      </c>
+      <c r="L9">
+        <v>71</v>
+      </c>
+      <c r="M9">
+        <v>48</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:K6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -10494,258 +11082,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M8"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" customWidth="1"/>
-    <col min="13" max="13" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="M1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2">
-        <v>1</v>
-      </c>
-      <c r="D2">
-        <v>2</v>
-      </c>
-      <c r="F2">
-        <v>2</v>
-      </c>
-      <c r="I2">
-        <v>3</v>
-      </c>
-      <c r="J2">
-        <v>2</v>
-      </c>
-      <c r="K2">
-        <v>1</v>
-      </c>
-      <c r="L2">
-        <v>5</v>
-      </c>
-      <c r="M2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C3">
-        <v>1</v>
-      </c>
-      <c r="E3">
-        <v>1</v>
-      </c>
-      <c r="H3">
-        <v>2</v>
-      </c>
-      <c r="I3">
-        <v>1</v>
-      </c>
-      <c r="J3">
-        <v>1</v>
-      </c>
-      <c r="K3">
-        <v>2</v>
-      </c>
-      <c r="L3">
-        <v>2</v>
-      </c>
-      <c r="M3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C4">
-        <v>1</v>
-      </c>
-      <c r="I4">
-        <v>1</v>
-      </c>
-      <c r="K4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="L5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B6">
-        <v>1</v>
-      </c>
-      <c r="F6">
-        <v>4</v>
-      </c>
-      <c r="H6">
-        <v>1</v>
-      </c>
-      <c r="I6">
-        <v>2</v>
-      </c>
-      <c r="K6">
-        <v>1</v>
-      </c>
-      <c r="M6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
-      <c r="A7" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B7">
-        <v>10</v>
-      </c>
-      <c r="C7">
-        <v>20</v>
-      </c>
-      <c r="D7">
-        <v>25</v>
-      </c>
-      <c r="E7">
-        <v>30</v>
-      </c>
-      <c r="F7">
-        <v>41</v>
-      </c>
-      <c r="G7">
-        <v>10</v>
-      </c>
-      <c r="H7">
-        <v>5</v>
-      </c>
-      <c r="I7">
-        <v>5</v>
-      </c>
-      <c r="J7">
-        <v>15</v>
-      </c>
-      <c r="K7">
-        <v>17</v>
-      </c>
-      <c r="L7">
-        <v>12</v>
-      </c>
-      <c r="M7">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13">
-      <c r="A8" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B8">
-        <v>12</v>
-      </c>
-      <c r="C8">
-        <v>22</v>
-      </c>
-      <c r="D8">
-        <v>27</v>
-      </c>
-      <c r="E8">
-        <v>31</v>
-      </c>
-      <c r="F8">
-        <v>47</v>
-      </c>
-      <c r="G8">
-        <v>10</v>
-      </c>
-      <c r="H8">
-        <v>8</v>
-      </c>
-      <c r="I8">
-        <v>12</v>
-      </c>
-      <c r="J8">
-        <v>18</v>
-      </c>
-      <c r="K8">
-        <v>22</v>
-      </c>
-      <c r="L8">
-        <v>21</v>
-      </c>
-      <c r="M8">
-        <v>18</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -10977,7 +11314,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -11190,7 +11527,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -11419,7 +11756,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:G6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -11525,7 +11862,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -11748,7 +12085,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -12006,7 +12343,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -12269,260 +12606,6 @@
       </c>
       <c r="M7">
         <v>16</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M8"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" customWidth="1"/>
-    <col min="13" max="13" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="M1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2">
-        <v>2</v>
-      </c>
-      <c r="D2">
-        <v>1</v>
-      </c>
-      <c r="H2">
-        <v>1</v>
-      </c>
-      <c r="I2">
-        <v>1</v>
-      </c>
-      <c r="J2">
-        <v>2</v>
-      </c>
-      <c r="L2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3">
-        <v>1</v>
-      </c>
-      <c r="D3">
-        <v>2</v>
-      </c>
-      <c r="F3">
-        <v>3</v>
-      </c>
-      <c r="G3">
-        <v>1</v>
-      </c>
-      <c r="H3">
-        <v>2</v>
-      </c>
-      <c r="I3">
-        <v>2</v>
-      </c>
-      <c r="K3">
-        <v>2</v>
-      </c>
-      <c r="M3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="J4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="K5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B6">
-        <v>7</v>
-      </c>
-      <c r="C6">
-        <v>5</v>
-      </c>
-      <c r="D6">
-        <v>5</v>
-      </c>
-      <c r="E6">
-        <v>5</v>
-      </c>
-      <c r="F6">
-        <v>5</v>
-      </c>
-      <c r="G6">
-        <v>1</v>
-      </c>
-      <c r="H6">
-        <v>5</v>
-      </c>
-      <c r="I6">
-        <v>4</v>
-      </c>
-      <c r="J6">
-        <v>1</v>
-      </c>
-      <c r="K6">
-        <v>4</v>
-      </c>
-      <c r="L6">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
-      <c r="A7" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B7">
-        <v>14</v>
-      </c>
-      <c r="C7">
-        <v>13</v>
-      </c>
-      <c r="D7">
-        <v>13</v>
-      </c>
-      <c r="E7">
-        <v>15</v>
-      </c>
-      <c r="F7">
-        <v>11</v>
-      </c>
-      <c r="G7">
-        <v>4</v>
-      </c>
-      <c r="H7">
-        <v>2</v>
-      </c>
-      <c r="I7">
-        <v>7</v>
-      </c>
-      <c r="J7">
-        <v>7</v>
-      </c>
-      <c r="K7">
-        <v>9</v>
-      </c>
-      <c r="L7">
-        <v>8</v>
-      </c>
-      <c r="M7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13">
-      <c r="A8" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B8">
-        <v>22</v>
-      </c>
-      <c r="C8">
-        <v>20</v>
-      </c>
-      <c r="D8">
-        <v>21</v>
-      </c>
-      <c r="E8">
-        <v>20</v>
-      </c>
-      <c r="F8">
-        <v>19</v>
-      </c>
-      <c r="G8">
-        <v>6</v>
-      </c>
-      <c r="H8">
-        <v>10</v>
-      </c>
-      <c r="I8">
-        <v>14</v>
-      </c>
-      <c r="J8">
-        <v>11</v>
-      </c>
-      <c r="K8">
-        <v>16</v>
-      </c>
-      <c r="L8">
-        <v>15</v>
-      </c>
-      <c r="M8">
-        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -12595,16 +12678,22 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="F2">
-        <v>1</v>
-      </c>
-      <c r="K2">
+      <c r="C2">
+        <v>2</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="H2">
+        <v>1</v>
+      </c>
+      <c r="I2">
+        <v>1</v>
+      </c>
+      <c r="J2">
         <v>2</v>
       </c>
       <c r="L2">
-        <v>2</v>
-      </c>
-      <c r="M2">
         <v>1</v>
       </c>
     </row>
@@ -12612,36 +12701,36 @@
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
+      <c r="B3">
+        <v>1</v>
+      </c>
+      <c r="D3">
+        <v>2</v>
+      </c>
       <c r="F3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G3">
         <v>1</v>
       </c>
       <c r="H3">
-        <v>1</v>
-      </c>
-      <c r="J3">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="I3">
+        <v>2</v>
       </c>
       <c r="K3">
         <v>2</v>
       </c>
-      <c r="L3">
-        <v>1</v>
-      </c>
       <c r="M3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D4">
-        <v>1</v>
-      </c>
-      <c r="I4">
+      <c r="J4">
         <v>1</v>
       </c>
     </row>
@@ -12649,7 +12738,7 @@
       <c r="A5" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="I5">
+      <c r="K5">
         <v>1</v>
       </c>
     </row>
@@ -12657,29 +12746,38 @@
       <c r="A6" s="1" t="s">
         <v>8</v>
       </c>
+      <c r="B6">
+        <v>7</v>
+      </c>
+      <c r="C6">
+        <v>5</v>
+      </c>
       <c r="D6">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E6">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F6">
-        <v>2</v>
+        <v>5</v>
+      </c>
+      <c r="G6">
+        <v>1</v>
       </c>
       <c r="H6">
+        <v>5</v>
+      </c>
+      <c r="I6">
+        <v>4</v>
+      </c>
+      <c r="J6">
+        <v>1</v>
+      </c>
+      <c r="K6">
+        <v>4</v>
+      </c>
+      <c r="L6">
         <v>6</v>
-      </c>
-      <c r="J6">
-        <v>1</v>
-      </c>
-      <c r="K6">
-        <v>1</v>
-      </c>
-      <c r="L6">
-        <v>1</v>
-      </c>
-      <c r="M6">
-        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -12687,40 +12785,40 @@
         <v>9</v>
       </c>
       <c r="B7">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C7">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D7">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E7">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F7">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="G7">
+        <v>4</v>
+      </c>
+      <c r="H7">
+        <v>2</v>
+      </c>
+      <c r="I7">
+        <v>7</v>
+      </c>
+      <c r="J7">
+        <v>7</v>
+      </c>
+      <c r="K7">
+        <v>9</v>
+      </c>
+      <c r="L7">
         <v>8</v>
       </c>
-      <c r="H7">
-        <v>4</v>
-      </c>
-      <c r="I7">
-        <v>2</v>
-      </c>
-      <c r="J7">
-        <v>2</v>
-      </c>
-      <c r="K7">
-        <v>3</v>
-      </c>
-      <c r="L7">
-        <v>6</v>
-      </c>
       <c r="M7">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -12728,40 +12826,40 @@
         <v>10</v>
       </c>
       <c r="B8">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="C8">
+        <v>20</v>
+      </c>
+      <c r="D8">
+        <v>21</v>
+      </c>
+      <c r="E8">
+        <v>20</v>
+      </c>
+      <c r="F8">
+        <v>19</v>
+      </c>
+      <c r="G8">
+        <v>6</v>
+      </c>
+      <c r="H8">
         <v>10</v>
       </c>
-      <c r="D8">
-        <v>12</v>
-      </c>
-      <c r="E8">
-        <v>19</v>
-      </c>
-      <c r="F8">
-        <v>21</v>
-      </c>
-      <c r="G8">
-        <v>9</v>
-      </c>
-      <c r="H8">
+      <c r="I8">
+        <v>14</v>
+      </c>
+      <c r="J8">
         <v>11</v>
       </c>
-      <c r="I8">
-        <v>4</v>
-      </c>
-      <c r="J8">
-        <v>4</v>
-      </c>
       <c r="K8">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="L8">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="M8">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -12834,32 +12932,14 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C2">
-        <v>1</v>
-      </c>
-      <c r="D2">
-        <v>2</v>
-      </c>
-      <c r="E2">
-        <v>2</v>
-      </c>
       <c r="F2">
         <v>1</v>
       </c>
-      <c r="G2">
-        <v>2</v>
-      </c>
-      <c r="I2">
-        <v>1</v>
-      </c>
-      <c r="J2">
-        <v>3</v>
-      </c>
       <c r="K2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M2">
         <v>1</v>
@@ -12869,15 +12949,6 @@
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C3">
-        <v>2</v>
-      </c>
-      <c r="D3">
-        <v>2</v>
-      </c>
-      <c r="E3">
-        <v>2</v>
-      </c>
       <c r="F3">
         <v>1</v>
       </c>
@@ -12885,37 +12956,37 @@
         <v>1</v>
       </c>
       <c r="H3">
-        <v>3</v>
-      </c>
-      <c r="I3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J3">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L3">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="M3">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="L4">
+      <c r="D4">
+        <v>1</v>
+      </c>
+      <c r="I4">
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="K5">
+        <v>6</v>
+      </c>
+      <c r="I5">
         <v>1</v>
       </c>
     </row>
@@ -12923,32 +12994,20 @@
       <c r="A6" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B6">
-        <v>7</v>
-      </c>
-      <c r="C6">
-        <v>7</v>
-      </c>
       <c r="D6">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E6">
+        <v>2</v>
+      </c>
+      <c r="F6">
+        <v>2</v>
+      </c>
+      <c r="H6">
         <v>6</v>
       </c>
-      <c r="F6">
-        <v>5</v>
-      </c>
-      <c r="G6">
-        <v>7</v>
-      </c>
-      <c r="H6">
-        <v>4</v>
-      </c>
-      <c r="I6">
-        <v>8</v>
-      </c>
       <c r="J6">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K6">
         <v>1</v>
@@ -12957,7 +13016,7 @@
         <v>1</v>
       </c>
       <c r="M6">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -12965,40 +13024,40 @@
         <v>9</v>
       </c>
       <c r="B7">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="C7">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="D7">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E7">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F7">
         <v>17</v>
       </c>
       <c r="G7">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="H7">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I7">
+        <v>2</v>
+      </c>
+      <c r="J7">
+        <v>2</v>
+      </c>
+      <c r="K7">
+        <v>3</v>
+      </c>
+      <c r="L7">
         <v>6</v>
       </c>
-      <c r="J7">
-        <v>5</v>
-      </c>
-      <c r="K7">
-        <v>8</v>
-      </c>
-      <c r="L7">
-        <v>3</v>
-      </c>
       <c r="M7">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -13006,40 +13065,40 @@
         <v>10</v>
       </c>
       <c r="B8">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="C8">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="D8">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="E8">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="F8">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="G8">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="H8">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I8">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="J8">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="K8">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="L8">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="M8">
-        <v>14</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -13048,6 +13107,535 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:M8"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+    <col min="13" max="13" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="M1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>2</v>
+      </c>
+      <c r="F2">
+        <v>2</v>
+      </c>
+      <c r="I2">
+        <v>3</v>
+      </c>
+      <c r="J2">
+        <v>2</v>
+      </c>
+      <c r="K2">
+        <v>1</v>
+      </c>
+      <c r="L2">
+        <v>5</v>
+      </c>
+      <c r="M2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
+      <c r="E3">
+        <v>1</v>
+      </c>
+      <c r="H3">
+        <v>2</v>
+      </c>
+      <c r="I3">
+        <v>1</v>
+      </c>
+      <c r="J3">
+        <v>1</v>
+      </c>
+      <c r="K3">
+        <v>2</v>
+      </c>
+      <c r="L3">
+        <v>2</v>
+      </c>
+      <c r="M3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
+      <c r="I4">
+        <v>1</v>
+      </c>
+      <c r="K4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="L5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6">
+        <v>1</v>
+      </c>
+      <c r="F6">
+        <v>4</v>
+      </c>
+      <c r="H6">
+        <v>1</v>
+      </c>
+      <c r="I6">
+        <v>2</v>
+      </c>
+      <c r="K6">
+        <v>1</v>
+      </c>
+      <c r="M6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7">
+        <v>10</v>
+      </c>
+      <c r="C7">
+        <v>20</v>
+      </c>
+      <c r="D7">
+        <v>25</v>
+      </c>
+      <c r="E7">
+        <v>30</v>
+      </c>
+      <c r="F7">
+        <v>41</v>
+      </c>
+      <c r="G7">
+        <v>10</v>
+      </c>
+      <c r="H7">
+        <v>5</v>
+      </c>
+      <c r="I7">
+        <v>5</v>
+      </c>
+      <c r="J7">
+        <v>15</v>
+      </c>
+      <c r="K7">
+        <v>17</v>
+      </c>
+      <c r="L7">
+        <v>12</v>
+      </c>
+      <c r="M7">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13">
+      <c r="A8" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B8">
+        <v>12</v>
+      </c>
+      <c r="C8">
+        <v>22</v>
+      </c>
+      <c r="D8">
+        <v>27</v>
+      </c>
+      <c r="E8">
+        <v>31</v>
+      </c>
+      <c r="F8">
+        <v>47</v>
+      </c>
+      <c r="G8">
+        <v>10</v>
+      </c>
+      <c r="H8">
+        <v>8</v>
+      </c>
+      <c r="I8">
+        <v>12</v>
+      </c>
+      <c r="J8">
+        <v>18</v>
+      </c>
+      <c r="K8">
+        <v>22</v>
+      </c>
+      <c r="L8">
+        <v>21</v>
+      </c>
+      <c r="M8">
+        <v>18</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet40.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:M8"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+    <col min="13" max="13" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="M1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>2</v>
+      </c>
+      <c r="E2">
+        <v>2</v>
+      </c>
+      <c r="F2">
+        <v>1</v>
+      </c>
+      <c r="G2">
+        <v>2</v>
+      </c>
+      <c r="I2">
+        <v>1</v>
+      </c>
+      <c r="J2">
+        <v>3</v>
+      </c>
+      <c r="K2">
+        <v>1</v>
+      </c>
+      <c r="L2">
+        <v>1</v>
+      </c>
+      <c r="M2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3">
+        <v>2</v>
+      </c>
+      <c r="D3">
+        <v>2</v>
+      </c>
+      <c r="E3">
+        <v>2</v>
+      </c>
+      <c r="F3">
+        <v>1</v>
+      </c>
+      <c r="G3">
+        <v>1</v>
+      </c>
+      <c r="H3">
+        <v>3</v>
+      </c>
+      <c r="I3">
+        <v>3</v>
+      </c>
+      <c r="J3">
+        <v>4</v>
+      </c>
+      <c r="K3">
+        <v>1</v>
+      </c>
+      <c r="L3">
+        <v>5</v>
+      </c>
+      <c r="M3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="L4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="K5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6">
+        <v>7</v>
+      </c>
+      <c r="C6">
+        <v>7</v>
+      </c>
+      <c r="D6">
+        <v>7</v>
+      </c>
+      <c r="E6">
+        <v>6</v>
+      </c>
+      <c r="F6">
+        <v>5</v>
+      </c>
+      <c r="G6">
+        <v>7</v>
+      </c>
+      <c r="H6">
+        <v>4</v>
+      </c>
+      <c r="I6">
+        <v>8</v>
+      </c>
+      <c r="J6">
+        <v>5</v>
+      </c>
+      <c r="K6">
+        <v>1</v>
+      </c>
+      <c r="L6">
+        <v>1</v>
+      </c>
+      <c r="M6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7">
+        <v>21</v>
+      </c>
+      <c r="C7">
+        <v>18</v>
+      </c>
+      <c r="D7">
+        <v>11</v>
+      </c>
+      <c r="E7">
+        <v>14</v>
+      </c>
+      <c r="F7">
+        <v>17</v>
+      </c>
+      <c r="G7">
+        <v>3</v>
+      </c>
+      <c r="H7">
+        <v>5</v>
+      </c>
+      <c r="I7">
+        <v>6</v>
+      </c>
+      <c r="J7">
+        <v>5</v>
+      </c>
+      <c r="K7">
+        <v>8</v>
+      </c>
+      <c r="L7">
+        <v>3</v>
+      </c>
+      <c r="M7">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13">
+      <c r="A8" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B8">
+        <v>28</v>
+      </c>
+      <c r="C8">
+        <v>28</v>
+      </c>
+      <c r="D8">
+        <v>22</v>
+      </c>
+      <c r="E8">
+        <v>24</v>
+      </c>
+      <c r="F8">
+        <v>24</v>
+      </c>
+      <c r="G8">
+        <v>13</v>
+      </c>
+      <c r="H8">
+        <v>12</v>
+      </c>
+      <c r="I8">
+        <v>18</v>
+      </c>
+      <c r="J8">
+        <v>17</v>
+      </c>
+      <c r="K8">
+        <v>12</v>
+      </c>
+      <c r="L8">
+        <v>11</v>
+      </c>
+      <c r="M8">
+        <v>14</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet41.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -13118,25 +13706,7 @@
       <c r="D2">
         <v>1</v>
       </c>
-      <c r="E2">
-        <v>1</v>
-      </c>
-      <c r="F2">
-        <v>1</v>
-      </c>
-      <c r="H2">
-        <v>2</v>
-      </c>
-      <c r="I2">
-        <v>4</v>
-      </c>
-      <c r="J2">
-        <v>3</v>
-      </c>
       <c r="K2">
-        <v>2</v>
-      </c>
-      <c r="M2">
         <v>1</v>
       </c>
     </row>
@@ -13145,44 +13715,26 @@
         <v>2</v>
       </c>
       <c r="C3">
-        <v>3</v>
-      </c>
-      <c r="D3">
-        <v>4</v>
-      </c>
-      <c r="E3">
         <v>1</v>
       </c>
       <c r="G3">
         <v>1</v>
       </c>
       <c r="H3">
-        <v>2</v>
-      </c>
-      <c r="I3">
-        <v>3</v>
-      </c>
-      <c r="J3">
-        <v>5</v>
-      </c>
-      <c r="K3">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L3">
-        <v>8</v>
-      </c>
-      <c r="M3">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G4">
-        <v>1</v>
-      </c>
-      <c r="J4">
+      <c r="E4">
+        <v>1</v>
+      </c>
+      <c r="K4">
         <v>1</v>
       </c>
     </row>
@@ -13190,41 +13742,35 @@
       <c r="A5" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B5">
-        <v>3</v>
-      </c>
-      <c r="C5">
-        <v>3</v>
-      </c>
       <c r="D5">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F5">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="G5">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="H5">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="I5">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="J5">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="K5">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="L5">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="M5">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -13232,40 +13778,40 @@
         <v>9</v>
       </c>
       <c r="B6">
-        <v>47</v>
+        <v>4</v>
       </c>
       <c r="C6">
-        <v>37</v>
+        <v>6</v>
       </c>
       <c r="D6">
-        <v>85</v>
+        <v>5</v>
       </c>
       <c r="E6">
-        <v>75</v>
+        <v>10</v>
       </c>
       <c r="F6">
-        <v>80</v>
+        <v>6</v>
       </c>
       <c r="G6">
-        <v>22</v>
+        <v>2</v>
       </c>
       <c r="H6">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I6">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="J6">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="K6">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="L6">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="M6">
-        <v>12</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -13273,40 +13819,40 @@
         <v>10</v>
       </c>
       <c r="B7">
-        <v>50</v>
+        <v>4</v>
       </c>
       <c r="C7">
-        <v>44</v>
+        <v>8</v>
       </c>
       <c r="D7">
-        <v>97</v>
+        <v>7</v>
       </c>
       <c r="E7">
-        <v>82</v>
+        <v>15</v>
       </c>
       <c r="F7">
-        <v>93</v>
+        <v>11</v>
       </c>
       <c r="G7">
-        <v>37</v>
+        <v>6</v>
       </c>
       <c r="H7">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="I7">
-        <v>47</v>
+        <v>9</v>
       </c>
       <c r="J7">
-        <v>33</v>
+        <v>4</v>
       </c>
       <c r="K7">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="L7">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="M7">
-        <v>20</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -13314,232 +13860,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet40.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M7"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" customWidth="1"/>
-    <col min="13" max="13" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="M1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2">
-        <v>1</v>
-      </c>
-      <c r="D2">
-        <v>1</v>
-      </c>
-      <c r="K2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C3">
-        <v>1</v>
-      </c>
-      <c r="G3">
-        <v>1</v>
-      </c>
-      <c r="H3">
-        <v>1</v>
-      </c>
-      <c r="L3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="E4">
-        <v>1</v>
-      </c>
-      <c r="K4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D5">
-        <v>1</v>
-      </c>
-      <c r="E5">
-        <v>4</v>
-      </c>
-      <c r="F5">
-        <v>5</v>
-      </c>
-      <c r="G5">
-        <v>3</v>
-      </c>
-      <c r="H5">
-        <v>1</v>
-      </c>
-      <c r="I5">
-        <v>5</v>
-      </c>
-      <c r="J5">
-        <v>1</v>
-      </c>
-      <c r="K5">
-        <v>2</v>
-      </c>
-      <c r="L5">
-        <v>1</v>
-      </c>
-      <c r="M5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B6">
-        <v>4</v>
-      </c>
-      <c r="C6">
-        <v>6</v>
-      </c>
-      <c r="D6">
-        <v>5</v>
-      </c>
-      <c r="E6">
-        <v>10</v>
-      </c>
-      <c r="F6">
-        <v>6</v>
-      </c>
-      <c r="G6">
-        <v>2</v>
-      </c>
-      <c r="H6">
-        <v>4</v>
-      </c>
-      <c r="I6">
-        <v>4</v>
-      </c>
-      <c r="J6">
-        <v>3</v>
-      </c>
-      <c r="K6">
-        <v>5</v>
-      </c>
-      <c r="L6">
-        <v>3</v>
-      </c>
-      <c r="M6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
-      <c r="A7" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B7">
-        <v>4</v>
-      </c>
-      <c r="C7">
-        <v>8</v>
-      </c>
-      <c r="D7">
-        <v>7</v>
-      </c>
-      <c r="E7">
-        <v>15</v>
-      </c>
-      <c r="F7">
-        <v>11</v>
-      </c>
-      <c r="G7">
-        <v>6</v>
-      </c>
-      <c r="H7">
-        <v>6</v>
-      </c>
-      <c r="I7">
-        <v>9</v>
-      </c>
-      <c r="J7">
-        <v>4</v>
-      </c>
-      <c r="K7">
-        <v>9</v>
-      </c>
-      <c r="L7">
-        <v>5</v>
-      </c>
-      <c r="M7">
-        <v>4</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet41.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet42.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M10"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -13844,319 +14165,6 @@
       </c>
       <c r="M10">
         <v>24</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet42.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M9"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" customWidth="1"/>
-    <col min="13" max="13" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="M1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2">
-        <v>1</v>
-      </c>
-      <c r="C2">
-        <v>2</v>
-      </c>
-      <c r="D2">
-        <v>7</v>
-      </c>
-      <c r="E2">
-        <v>8</v>
-      </c>
-      <c r="F2">
-        <v>5</v>
-      </c>
-      <c r="G2">
-        <v>4</v>
-      </c>
-      <c r="H2">
-        <v>2</v>
-      </c>
-      <c r="I2">
-        <v>5</v>
-      </c>
-      <c r="J2">
-        <v>3</v>
-      </c>
-      <c r="K2">
-        <v>5</v>
-      </c>
-      <c r="L2">
-        <v>5</v>
-      </c>
-      <c r="M2">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3">
-        <v>1</v>
-      </c>
-      <c r="C3">
-        <v>3</v>
-      </c>
-      <c r="D3">
-        <v>9</v>
-      </c>
-      <c r="E3">
-        <v>4</v>
-      </c>
-      <c r="F3">
-        <v>5</v>
-      </c>
-      <c r="G3">
-        <v>6</v>
-      </c>
-      <c r="H3">
-        <v>8</v>
-      </c>
-      <c r="I3">
-        <v>9</v>
-      </c>
-      <c r="J3">
-        <v>14</v>
-      </c>
-      <c r="K3">
-        <v>16</v>
-      </c>
-      <c r="L3">
-        <v>8</v>
-      </c>
-      <c r="M3">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="F4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5">
-        <v>2</v>
-      </c>
-      <c r="D5">
-        <v>1</v>
-      </c>
-      <c r="E5">
-        <v>1</v>
-      </c>
-      <c r="F5">
-        <v>1</v>
-      </c>
-      <c r="H5">
-        <v>1</v>
-      </c>
-      <c r="I5">
-        <v>2</v>
-      </c>
-      <c r="M5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="I6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
-      <c r="A7" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B7">
-        <v>15</v>
-      </c>
-      <c r="C7">
-        <v>35</v>
-      </c>
-      <c r="D7">
-        <v>34</v>
-      </c>
-      <c r="E7">
-        <v>56</v>
-      </c>
-      <c r="F7">
-        <v>54</v>
-      </c>
-      <c r="G7">
-        <v>37</v>
-      </c>
-      <c r="H7">
-        <v>39</v>
-      </c>
-      <c r="I7">
-        <v>32</v>
-      </c>
-      <c r="J7">
-        <v>34</v>
-      </c>
-      <c r="K7">
-        <v>27</v>
-      </c>
-      <c r="L7">
-        <v>31</v>
-      </c>
-      <c r="M7">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13">
-      <c r="A8" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B8">
-        <v>54</v>
-      </c>
-      <c r="C8">
-        <v>63</v>
-      </c>
-      <c r="D8">
-        <v>50</v>
-      </c>
-      <c r="E8">
-        <v>109</v>
-      </c>
-      <c r="F8">
-        <v>138</v>
-      </c>
-      <c r="G8">
-        <v>53</v>
-      </c>
-      <c r="H8">
-        <v>29</v>
-      </c>
-      <c r="I8">
-        <v>49</v>
-      </c>
-      <c r="J8">
-        <v>34</v>
-      </c>
-      <c r="K8">
-        <v>28</v>
-      </c>
-      <c r="L8">
-        <v>27</v>
-      </c>
-      <c r="M8">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13">
-      <c r="A9" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B9">
-        <v>73</v>
-      </c>
-      <c r="C9">
-        <v>103</v>
-      </c>
-      <c r="D9">
-        <v>101</v>
-      </c>
-      <c r="E9">
-        <v>178</v>
-      </c>
-      <c r="F9">
-        <v>204</v>
-      </c>
-      <c r="G9">
-        <v>100</v>
-      </c>
-      <c r="H9">
-        <v>79</v>
-      </c>
-      <c r="I9">
-        <v>98</v>
-      </c>
-      <c r="J9">
-        <v>85</v>
-      </c>
-      <c r="K9">
-        <v>76</v>
-      </c>
-      <c r="L9">
-        <v>71</v>
-      </c>
-      <c r="M9">
-        <v>46</v>
       </c>
     </row>
   </sheetData>
@@ -15868,7 +15876,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M8"/>
+  <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="23.7109375" customWidth="1"/>
@@ -15931,11 +15939,8 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2">
-        <v>1</v>
-      </c>
       <c r="C2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D2">
         <v>1</v>
@@ -15944,63 +15949,54 @@
         <v>1</v>
       </c>
       <c r="F2">
-        <v>2</v>
-      </c>
-      <c r="G2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K2">
-        <v>3</v>
-      </c>
-      <c r="L2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M2">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B3">
-        <v>1</v>
-      </c>
       <c r="C3">
-        <v>2</v>
+        <v>3</v>
+      </c>
+      <c r="D3">
+        <v>4</v>
       </c>
       <c r="E3">
-        <v>2</v>
-      </c>
-      <c r="F3">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H3">
         <v>2</v>
       </c>
       <c r="I3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J3">
         <v>5</v>
       </c>
       <c r="K3">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L3">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M3">
         <v>3</v>
@@ -16008,147 +16004,136 @@
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4">
-        <v>1</v>
-      </c>
-      <c r="I4">
+        <v>5</v>
+      </c>
+      <c r="G4">
+        <v>1</v>
+      </c>
+      <c r="J4">
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>5</v>
+        <v>8</v>
+      </c>
+      <c r="B5">
+        <v>3</v>
+      </c>
+      <c r="C5">
+        <v>3</v>
+      </c>
+      <c r="D5">
+        <v>7</v>
+      </c>
+      <c r="E5">
+        <v>5</v>
+      </c>
+      <c r="F5">
+        <v>12</v>
+      </c>
+      <c r="G5">
+        <v>13</v>
       </c>
       <c r="H5">
-        <v>1</v>
+        <v>11</v>
+      </c>
+      <c r="I5">
+        <v>14</v>
       </c>
       <c r="J5">
-        <v>1</v>
+        <v>12</v>
+      </c>
+      <c r="K5">
+        <v>9</v>
+      </c>
+      <c r="L5">
+        <v>6</v>
+      </c>
+      <c r="M5">
+        <v>4</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B6">
+        <v>47</v>
+      </c>
+      <c r="C6">
+        <v>37</v>
+      </c>
+      <c r="D6">
+        <v>85</v>
+      </c>
+      <c r="E6">
+        <v>75</v>
+      </c>
+      <c r="F6">
+        <v>80</v>
+      </c>
+      <c r="G6">
+        <v>22</v>
+      </c>
+      <c r="H6">
+        <v>6</v>
+      </c>
+      <c r="I6">
+        <v>26</v>
+      </c>
+      <c r="J6">
         <v>12</v>
       </c>
-      <c r="C6">
-        <v>21</v>
-      </c>
-      <c r="D6">
-        <v>28</v>
-      </c>
-      <c r="E6">
-        <v>21</v>
-      </c>
-      <c r="F6">
-        <v>35</v>
-      </c>
-      <c r="G6">
+      <c r="K6">
+        <v>19</v>
+      </c>
+      <c r="L6">
+        <v>11</v>
+      </c>
+      <c r="M6">
         <v>12</v>
-      </c>
-      <c r="H6">
-        <v>10</v>
-      </c>
-      <c r="I6">
-        <v>15</v>
-      </c>
-      <c r="J6">
-        <v>5</v>
-      </c>
-      <c r="K6">
-        <v>9</v>
-      </c>
-      <c r="L6">
-        <v>7</v>
-      </c>
-      <c r="M6">
-        <v>4</v>
       </c>
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B7">
-        <v>17</v>
+        <v>50</v>
       </c>
       <c r="C7">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="D7">
-        <v>49</v>
+        <v>97</v>
       </c>
       <c r="E7">
-        <v>44</v>
+        <v>82</v>
       </c>
       <c r="F7">
-        <v>58</v>
+        <v>93</v>
       </c>
       <c r="G7">
+        <v>37</v>
+      </c>
+      <c r="H7">
+        <v>21</v>
+      </c>
+      <c r="I7">
+        <v>47</v>
+      </c>
+      <c r="J7">
+        <v>33</v>
+      </c>
+      <c r="K7">
+        <v>34</v>
+      </c>
+      <c r="L7">
         <v>25</v>
       </c>
-      <c r="H7">
-        <v>8</v>
-      </c>
-      <c r="I7">
-        <v>10</v>
-      </c>
-      <c r="J7">
-        <v>8</v>
-      </c>
-      <c r="K7">
-        <v>11</v>
-      </c>
-      <c r="L7">
-        <v>7</v>
-      </c>
       <c r="M7">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13">
-      <c r="A8" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B8">
-        <v>32</v>
-      </c>
-      <c r="C8">
-        <v>61</v>
-      </c>
-      <c r="D8">
-        <v>78</v>
-      </c>
-      <c r="E8">
-        <v>68</v>
-      </c>
-      <c r="F8">
-        <v>100</v>
-      </c>
-      <c r="G8">
-        <v>43</v>
-      </c>
-      <c r="H8">
-        <v>26</v>
-      </c>
-      <c r="I8">
-        <v>32</v>
-      </c>
-      <c r="J8">
         <v>20</v>
-      </c>
-      <c r="K8">
-        <v>29</v>
-      </c>
-      <c r="L8">
-        <v>25</v>
-      </c>
-      <c r="M8">
-        <v>15</v>
       </c>
     </row>
   </sheetData>
@@ -18375,7 +18360,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M9"/>
+  <dimension ref="A1:M8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="23.7109375" customWidth="1"/>
@@ -18438,38 +18423,41 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
       <c r="C2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D2">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E2">
         <v>1</v>
       </c>
       <c r="F2">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="G2">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="H2">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="I2">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="J2">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="K2">
         <v>3</v>
       </c>
       <c r="L2">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M2">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -18477,211 +18465,182 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C3">
-        <v>5</v>
-      </c>
-      <c r="D3">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="E3">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="F3">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="G3">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="H3">
+        <v>2</v>
+      </c>
+      <c r="I3">
+        <v>4</v>
+      </c>
+      <c r="J3">
+        <v>5</v>
+      </c>
+      <c r="K3">
+        <v>6</v>
+      </c>
+      <c r="L3">
         <v>7</v>
       </c>
-      <c r="I3">
-        <v>13</v>
-      </c>
-      <c r="J3">
-        <v>12</v>
-      </c>
-      <c r="K3">
-        <v>20</v>
-      </c>
-      <c r="L3">
-        <v>20</v>
-      </c>
       <c r="M3">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B4">
         <v>1</v>
       </c>
-      <c r="D4">
-        <v>1</v>
-      </c>
-      <c r="H4">
-        <v>2</v>
-      </c>
-      <c r="J4">
-        <v>1</v>
-      </c>
-      <c r="K4">
-        <v>1</v>
-      </c>
-      <c r="L4">
-        <v>1</v>
-      </c>
-      <c r="M4">
-        <v>2</v>
+      <c r="I4">
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H5">
         <v>1</v>
       </c>
-      <c r="I5">
+      <c r="J5">
         <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6">
+        <v>12</v>
+      </c>
+      <c r="C6">
+        <v>21</v>
+      </c>
+      <c r="D6">
+        <v>28</v>
+      </c>
+      <c r="E6">
+        <v>21</v>
+      </c>
+      <c r="F6">
+        <v>35</v>
+      </c>
+      <c r="G6">
+        <v>12</v>
+      </c>
+      <c r="H6">
+        <v>10</v>
+      </c>
+      <c r="I6">
+        <v>15</v>
+      </c>
+      <c r="J6">
+        <v>5</v>
+      </c>
+      <c r="K6">
+        <v>9</v>
+      </c>
+      <c r="L6">
         <v>7</v>
       </c>
-      <c r="G6">
-        <v>1</v>
-      </c>
-      <c r="J6">
-        <v>1</v>
+      <c r="M6">
+        <v>4</v>
       </c>
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7">
+        <v>17</v>
+      </c>
+      <c r="C7">
+        <v>35</v>
+      </c>
+      <c r="D7">
+        <v>49</v>
+      </c>
+      <c r="E7">
+        <v>44</v>
+      </c>
+      <c r="F7">
+        <v>58</v>
+      </c>
+      <c r="G7">
+        <v>25</v>
+      </c>
+      <c r="H7">
         <v>8</v>
       </c>
-      <c r="B7">
-        <v>34</v>
-      </c>
-      <c r="C7">
-        <v>45</v>
-      </c>
-      <c r="D7">
-        <v>25</v>
-      </c>
-      <c r="E7">
-        <v>22</v>
-      </c>
-      <c r="F7">
-        <v>42</v>
-      </c>
-      <c r="G7">
-        <v>32</v>
-      </c>
-      <c r="H7">
-        <v>26</v>
-      </c>
       <c r="I7">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="J7">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="K7">
-        <v>44</v>
+        <v>11</v>
       </c>
       <c r="L7">
-        <v>43</v>
+        <v>7</v>
       </c>
       <c r="M7">
-        <v>16</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:13">
       <c r="A8" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B8">
-        <v>71</v>
+        <v>32</v>
       </c>
       <c r="C8">
-        <v>91</v>
+        <v>61</v>
       </c>
       <c r="D8">
-        <v>57</v>
+        <v>78</v>
       </c>
       <c r="E8">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="F8">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="G8">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="H8">
+        <v>26</v>
+      </c>
+      <c r="I8">
+        <v>32</v>
+      </c>
+      <c r="J8">
+        <v>20</v>
+      </c>
+      <c r="K8">
         <v>29</v>
       </c>
-      <c r="I8">
-        <v>45</v>
-      </c>
-      <c r="J8">
-        <v>31</v>
-      </c>
-      <c r="K8">
-        <v>27</v>
-      </c>
       <c r="L8">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="M8">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13">
-      <c r="A9" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B9">
-        <v>111</v>
-      </c>
-      <c r="C9">
-        <v>142</v>
-      </c>
-      <c r="D9">
-        <v>107</v>
-      </c>
-      <c r="E9">
-        <v>98</v>
-      </c>
-      <c r="F9">
-        <v>138</v>
-      </c>
-      <c r="G9">
-        <v>92</v>
-      </c>
-      <c r="H9">
-        <v>76</v>
-      </c>
-      <c r="I9">
-        <v>90</v>
-      </c>
-      <c r="J9">
-        <v>69</v>
-      </c>
-      <c r="K9">
-        <v>95</v>
-      </c>
-      <c r="L9">
-        <v>102</v>
-      </c>
-      <c r="M9">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
   </sheetData>
@@ -21068,76 +21027,76 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2">
-        <v>2</v>
-      </c>
       <c r="C2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D2">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F2">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="G2">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="H2">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="I2">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="J2">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="K2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L2">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="M2">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
+      <c r="B3">
+        <v>5</v>
+      </c>
       <c r="C3">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D3">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="E3">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="F3">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="G3">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="H3">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="I3">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="J3">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="K3">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="L3">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="M3">
         <v>5</v>
@@ -21145,17 +21104,38 @@
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E4">
-        <v>1</v>
+        <v>5</v>
+      </c>
+      <c r="B4">
+        <v>1</v>
+      </c>
+      <c r="D4">
+        <v>1</v>
+      </c>
+      <c r="H4">
+        <v>2</v>
+      </c>
+      <c r="J4">
+        <v>1</v>
+      </c>
+      <c r="K4">
+        <v>1</v>
+      </c>
+      <c r="L4">
+        <v>1</v>
+      </c>
+      <c r="M4">
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5">
+        <v>6</v>
+      </c>
+      <c r="H5">
+        <v>1</v>
+      </c>
+      <c r="I5">
         <v>1</v>
       </c>
     </row>
@@ -21163,7 +21143,10 @@
       <c r="A6" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C6">
+      <c r="G6">
+        <v>1</v>
+      </c>
+      <c r="J6">
         <v>1</v>
       </c>
     </row>
@@ -21172,40 +21155,40 @@
         <v>8</v>
       </c>
       <c r="B7">
-        <v>5</v>
+        <v>34</v>
       </c>
       <c r="C7">
-        <v>9</v>
+        <v>45</v>
       </c>
       <c r="D7">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="E7">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="F7">
-        <v>6</v>
+        <v>42</v>
       </c>
       <c r="G7">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="H7">
-        <v>7</v>
+        <v>26</v>
       </c>
       <c r="I7">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="J7">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="K7">
-        <v>11</v>
+        <v>44</v>
       </c>
       <c r="L7">
-        <v>8</v>
+        <v>43</v>
       </c>
       <c r="M7">
-        <v>1</v>
+        <v>16</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -21213,40 +21196,40 @@
         <v>9</v>
       </c>
       <c r="B8">
-        <v>30</v>
+        <v>71</v>
       </c>
       <c r="C8">
-        <v>26</v>
+        <v>91</v>
       </c>
       <c r="D8">
-        <v>15</v>
+        <v>57</v>
       </c>
       <c r="E8">
-        <v>24</v>
+        <v>65</v>
       </c>
       <c r="F8">
-        <v>18</v>
+        <v>75</v>
       </c>
       <c r="G8">
-        <v>16</v>
+        <v>41</v>
       </c>
       <c r="H8">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="I8">
-        <v>13</v>
+        <v>45</v>
       </c>
       <c r="J8">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="K8">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="L8">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="M8">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -21254,40 +21237,40 @@
         <v>10</v>
       </c>
       <c r="B9">
-        <v>38</v>
+        <v>111</v>
       </c>
       <c r="C9">
-        <v>41</v>
+        <v>142</v>
       </c>
       <c r="D9">
-        <v>19</v>
+        <v>107</v>
       </c>
       <c r="E9">
+        <v>98</v>
+      </c>
+      <c r="F9">
+        <v>138</v>
+      </c>
+      <c r="G9">
+        <v>92</v>
+      </c>
+      <c r="H9">
+        <v>76</v>
+      </c>
+      <c r="I9">
+        <v>90</v>
+      </c>
+      <c r="J9">
+        <v>69</v>
+      </c>
+      <c r="K9">
+        <v>95</v>
+      </c>
+      <c r="L9">
+        <v>102</v>
+      </c>
+      <c r="M9">
         <v>36</v>
-      </c>
-      <c r="F9">
-        <v>28</v>
-      </c>
-      <c r="G9">
-        <v>38</v>
-      </c>
-      <c r="H9">
-        <v>28</v>
-      </c>
-      <c r="I9">
-        <v>23</v>
-      </c>
-      <c r="J9">
-        <v>31</v>
-      </c>
-      <c r="K9">
-        <v>35</v>
-      </c>
-      <c r="L9">
-        <v>33</v>
-      </c>
-      <c r="M9">
-        <v>17</v>
       </c>
     </row>
   </sheetData>
@@ -23031,7 +23014,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M10"/>
+  <dimension ref="A1:M9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="23.7109375" customWidth="1"/>
@@ -23095,100 +23078,85 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D2">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="E2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F2">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="G2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H2">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="I2">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="J2">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="K2">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="L2">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="M2">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B3">
-        <v>13</v>
-      </c>
       <c r="C3">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="D3">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="E3">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="F3">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="G3">
-        <v>26</v>
+        <v>6</v>
       </c>
       <c r="H3">
-        <v>23</v>
+        <v>2</v>
       </c>
       <c r="I3">
-        <v>32</v>
+        <v>4</v>
       </c>
       <c r="J3">
-        <v>40</v>
+        <v>7</v>
       </c>
       <c r="K3">
-        <v>26</v>
+        <v>7</v>
       </c>
       <c r="L3">
-        <v>34</v>
+        <v>3</v>
       </c>
       <c r="M3">
-        <v>17</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="G4">
-        <v>1</v>
-      </c>
-      <c r="J4">
-        <v>2</v>
-      </c>
-      <c r="K4">
-        <v>1</v>
-      </c>
-      <c r="L4">
-        <v>1</v>
-      </c>
-      <c r="M4">
+      <c r="E4">
         <v>1</v>
       </c>
     </row>
@@ -23196,186 +23164,139 @@
       <c r="A5" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C5">
-        <v>2</v>
-      </c>
-      <c r="D5">
-        <v>1</v>
-      </c>
-      <c r="E5">
-        <v>2</v>
-      </c>
-      <c r="F5">
-        <v>1</v>
-      </c>
-      <c r="H5">
-        <v>2</v>
-      </c>
-      <c r="I5">
-        <v>4</v>
-      </c>
-      <c r="J5">
-        <v>3</v>
-      </c>
-      <c r="K5">
-        <v>2</v>
-      </c>
-      <c r="L5">
-        <v>5</v>
-      </c>
-      <c r="M5">
-        <v>3</v>
+      <c r="B5">
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="G6">
-        <v>1</v>
-      </c>
-      <c r="H6">
-        <v>2</v>
-      </c>
-      <c r="J6">
-        <v>2</v>
-      </c>
-      <c r="L6">
-        <v>2</v>
-      </c>
-      <c r="M6">
+        <v>7</v>
+      </c>
+      <c r="C6">
         <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7">
+        <v>5</v>
+      </c>
+      <c r="C7">
+        <v>9</v>
+      </c>
+      <c r="D7">
+        <v>1</v>
+      </c>
+      <c r="E7">
+        <v>6</v>
+      </c>
+      <c r="F7">
+        <v>6</v>
+      </c>
+      <c r="G7">
+        <v>14</v>
+      </c>
+      <c r="H7">
         <v>7</v>
       </c>
+      <c r="I7">
+        <v>4</v>
+      </c>
+      <c r="J7">
+        <v>5</v>
+      </c>
       <c r="K7">
+        <v>11</v>
+      </c>
+      <c r="L7">
+        <v>8</v>
+      </c>
+      <c r="M7">
         <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:13">
       <c r="A8" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B8">
         <v>30</v>
       </c>
       <c r="C8">
-        <v>44</v>
+        <v>26</v>
       </c>
       <c r="D8">
-        <v>49</v>
+        <v>15</v>
       </c>
       <c r="E8">
-        <v>67</v>
+        <v>24</v>
       </c>
       <c r="F8">
-        <v>69</v>
+        <v>18</v>
       </c>
       <c r="G8">
-        <v>57</v>
+        <v>16</v>
       </c>
       <c r="H8">
-        <v>80</v>
+        <v>14</v>
       </c>
       <c r="I8">
-        <v>80</v>
+        <v>13</v>
       </c>
       <c r="J8">
-        <v>64</v>
+        <v>15</v>
       </c>
       <c r="K8">
-        <v>48</v>
+        <v>12</v>
       </c>
       <c r="L8">
-        <v>44</v>
+        <v>20</v>
       </c>
       <c r="M8">
-        <v>21</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9" spans="1:13">
       <c r="A9" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B9">
-        <v>233</v>
+        <v>38</v>
       </c>
       <c r="C9">
-        <v>354</v>
+        <v>41</v>
       </c>
       <c r="D9">
-        <v>538</v>
+        <v>19</v>
       </c>
       <c r="E9">
-        <v>705</v>
+        <v>36</v>
       </c>
       <c r="F9">
-        <v>568</v>
+        <v>28</v>
       </c>
       <c r="G9">
-        <v>168</v>
+        <v>38</v>
       </c>
       <c r="H9">
-        <v>116</v>
+        <v>28</v>
       </c>
       <c r="I9">
-        <v>194</v>
+        <v>23</v>
       </c>
       <c r="J9">
-        <v>122</v>
+        <v>31</v>
       </c>
       <c r="K9">
-        <v>114</v>
+        <v>35</v>
       </c>
       <c r="L9">
-        <v>95</v>
+        <v>33</v>
       </c>
       <c r="M9">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13">
-      <c r="A10" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B10">
-        <v>282</v>
-      </c>
-      <c r="C10">
-        <v>416</v>
-      </c>
-      <c r="D10">
-        <v>617</v>
-      </c>
-      <c r="E10">
-        <v>797</v>
-      </c>
-      <c r="F10">
-        <v>660</v>
-      </c>
-      <c r="G10">
-        <v>257</v>
-      </c>
-      <c r="H10">
-        <v>236</v>
-      </c>
-      <c r="I10">
-        <v>324</v>
-      </c>
-      <c r="J10">
-        <v>255</v>
-      </c>
-      <c r="K10">
-        <v>207</v>
-      </c>
-      <c r="L10">
-        <v>196</v>
-      </c>
-      <c r="M10">
-        <v>93</v>
+        <v>17</v>
       </c>
     </row>
   </sheetData>
@@ -25269,7 +25190,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M8"/>
+  <dimension ref="A1:M10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="23.7109375" customWidth="1"/>
@@ -25332,124 +25253,154 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
+      <c r="B2">
+        <v>6</v>
+      </c>
       <c r="C2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D2">
-        <v>2</v>
+        <v>12</v>
+      </c>
+      <c r="E2">
+        <v>5</v>
+      </c>
+      <c r="F2">
+        <v>8</v>
       </c>
       <c r="G2">
         <v>4</v>
       </c>
       <c r="H2">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="I2">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="J2">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="K2">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="L2">
-        <v>5</v>
+        <v>15</v>
+      </c>
+      <c r="M2">
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
+      <c r="B3">
+        <v>13</v>
+      </c>
       <c r="C3">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="D3">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="E3">
-        <v>1</v>
+        <v>18</v>
+      </c>
+      <c r="F3">
+        <v>14</v>
+      </c>
+      <c r="G3">
+        <v>26</v>
       </c>
       <c r="H3">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="I3">
-        <v>1</v>
+        <v>32</v>
       </c>
       <c r="J3">
-        <v>3</v>
+        <v>40</v>
       </c>
       <c r="K3">
-        <v>1</v>
+        <v>26</v>
       </c>
       <c r="L3">
-        <v>1</v>
+        <v>34</v>
+      </c>
+      <c r="M3">
+        <v>17</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D4">
-        <v>1</v>
-      </c>
-      <c r="E4">
+        <v>3</v>
+      </c>
+      <c r="G4">
         <v>1</v>
       </c>
       <c r="J4">
+        <v>2</v>
+      </c>
+      <c r="K4">
         <v>1</v>
       </c>
       <c r="L4">
+        <v>1</v>
+      </c>
+      <c r="M4">
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C5">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="D5">
+        <v>1</v>
+      </c>
+      <c r="E5">
+        <v>2</v>
+      </c>
+      <c r="F5">
+        <v>1</v>
+      </c>
+      <c r="H5">
+        <v>2</v>
+      </c>
+      <c r="I5">
+        <v>4</v>
       </c>
       <c r="J5">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="K5">
+        <v>2</v>
+      </c>
+      <c r="L5">
+        <v>5</v>
+      </c>
+      <c r="M5">
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B6">
-        <v>2</v>
-      </c>
-      <c r="C6">
-        <v>5</v>
-      </c>
-      <c r="D6">
-        <v>3</v>
-      </c>
-      <c r="E6">
-        <v>4</v>
-      </c>
-      <c r="F6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G6">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H6">
-        <v>8</v>
-      </c>
-      <c r="I6">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J6">
-        <v>8</v>
-      </c>
-      <c r="K6">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="L6">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="M6">
         <v>1</v>
@@ -25457,84 +25408,133 @@
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B7">
-        <v>17</v>
-      </c>
-      <c r="C7">
-        <v>24</v>
-      </c>
-      <c r="D7">
-        <v>35</v>
-      </c>
-      <c r="E7">
-        <v>31</v>
-      </c>
-      <c r="F7">
-        <v>18</v>
-      </c>
-      <c r="G7">
-        <v>17</v>
-      </c>
-      <c r="H7">
-        <v>8</v>
-      </c>
-      <c r="I7">
-        <v>16</v>
-      </c>
-      <c r="J7">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="K7">
-        <v>10</v>
-      </c>
-      <c r="L7">
-        <v>12</v>
-      </c>
-      <c r="M7">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:13">
       <c r="A8" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8">
+        <v>30</v>
+      </c>
+      <c r="C8">
+        <v>44</v>
+      </c>
+      <c r="D8">
+        <v>49</v>
+      </c>
+      <c r="E8">
+        <v>67</v>
+      </c>
+      <c r="F8">
+        <v>69</v>
+      </c>
+      <c r="G8">
+        <v>57</v>
+      </c>
+      <c r="H8">
+        <v>80</v>
+      </c>
+      <c r="I8">
+        <v>80</v>
+      </c>
+      <c r="J8">
+        <v>64</v>
+      </c>
+      <c r="K8">
+        <v>48</v>
+      </c>
+      <c r="L8">
+        <v>44</v>
+      </c>
+      <c r="M8">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13">
+      <c r="A9" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B9">
+        <v>233</v>
+      </c>
+      <c r="C9">
+        <v>354</v>
+      </c>
+      <c r="D9">
+        <v>538</v>
+      </c>
+      <c r="E9">
+        <v>705</v>
+      </c>
+      <c r="F9">
+        <v>568</v>
+      </c>
+      <c r="G9">
+        <v>168</v>
+      </c>
+      <c r="H9">
+        <v>116</v>
+      </c>
+      <c r="I9">
+        <v>194</v>
+      </c>
+      <c r="J9">
+        <v>122</v>
+      </c>
+      <c r="K9">
+        <v>114</v>
+      </c>
+      <c r="L9">
+        <v>95</v>
+      </c>
+      <c r="M9">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13">
+      <c r="A10" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B8">
-        <v>19</v>
-      </c>
-      <c r="C8">
-        <v>32</v>
-      </c>
-      <c r="D8">
-        <v>42</v>
-      </c>
-      <c r="E8">
-        <v>37</v>
-      </c>
-      <c r="F8">
-        <v>23</v>
-      </c>
-      <c r="G8">
-        <v>26</v>
-      </c>
-      <c r="H8">
-        <v>18</v>
-      </c>
-      <c r="I8">
-        <v>23</v>
-      </c>
-      <c r="J8">
-        <v>31</v>
-      </c>
-      <c r="K8">
-        <v>20</v>
-      </c>
-      <c r="L8">
-        <v>26</v>
-      </c>
-      <c r="M8">
-        <v>9</v>
+      <c r="B10">
+        <v>282</v>
+      </c>
+      <c r="C10">
+        <v>416</v>
+      </c>
+      <c r="D10">
+        <v>617</v>
+      </c>
+      <c r="E10">
+        <v>797</v>
+      </c>
+      <c r="F10">
+        <v>660</v>
+      </c>
+      <c r="G10">
+        <v>257</v>
+      </c>
+      <c r="H10">
+        <v>236</v>
+      </c>
+      <c r="I10">
+        <v>324</v>
+      </c>
+      <c r="J10">
+        <v>255</v>
+      </c>
+      <c r="K10">
+        <v>207</v>
+      </c>
+      <c r="L10">
+        <v>196</v>
+      </c>
+      <c r="M10">
+        <v>93</v>
       </c>
     </row>
   </sheetData>

--- a/output/cta-index-crime-full-year.xlsx
+++ b/output/cta-index-crime-full-year.xlsx
@@ -14,30 +14,30 @@
     <sheet name="Humboldt Park" sheetId="5" r:id="rId5"/>
     <sheet name="Washington Park" sheetId="6" r:id="rId6"/>
     <sheet name="O'Hare" sheetId="7" r:id="rId7"/>
-    <sheet name="Chatham" sheetId="8" r:id="rId8"/>
-    <sheet name="Englewood" sheetId="9" r:id="rId9"/>
-    <sheet name="Albany Park" sheetId="10" r:id="rId10"/>
-    <sheet name="Grand Boulevard" sheetId="11" r:id="rId11"/>
-    <sheet name="Belmont Cragin" sheetId="12" r:id="rId12"/>
-    <sheet name="West Ridge" sheetId="13" r:id="rId13"/>
-    <sheet name="Loop" sheetId="14" r:id="rId14"/>
-    <sheet name="Lake View" sheetId="15" r:id="rId15"/>
-    <sheet name="South Shore" sheetId="16" r:id="rId16"/>
-    <sheet name="Avondale" sheetId="17" r:id="rId17"/>
-    <sheet name="Mount Greenwood" sheetId="18" r:id="rId18"/>
-    <sheet name="Gage Park" sheetId="19" r:id="rId19"/>
-    <sheet name="Grand Crossing" sheetId="20" r:id="rId20"/>
-    <sheet name="West Loop" sheetId="21" r:id="rId21"/>
-    <sheet name="Rush &amp; Division" sheetId="22" r:id="rId22"/>
-    <sheet name="North Lawndale" sheetId="23" r:id="rId23"/>
-    <sheet name="South Chicago" sheetId="24" r:id="rId24"/>
-    <sheet name="Garfield Park" sheetId="25" r:id="rId25"/>
-    <sheet name="United Center" sheetId="26" r:id="rId26"/>
-    <sheet name="Magnificent Mile" sheetId="27" r:id="rId27"/>
-    <sheet name="Jefferson Park" sheetId="28" r:id="rId28"/>
-    <sheet name="New City" sheetId="29" r:id="rId29"/>
-    <sheet name="Logan Square" sheetId="30" r:id="rId30"/>
-    <sheet name="Ashburn" sheetId="31" r:id="rId31"/>
+    <sheet name="Ashburn" sheetId="8" r:id="rId8"/>
+    <sheet name="Grand Crossing" sheetId="9" r:id="rId9"/>
+    <sheet name="Englewood" sheetId="10" r:id="rId10"/>
+    <sheet name="Chatham" sheetId="11" r:id="rId11"/>
+    <sheet name="Albany Park" sheetId="12" r:id="rId12"/>
+    <sheet name="Grand Boulevard" sheetId="13" r:id="rId13"/>
+    <sheet name="Belmont Cragin" sheetId="14" r:id="rId14"/>
+    <sheet name="West Ridge" sheetId="15" r:id="rId15"/>
+    <sheet name="Loop" sheetId="16" r:id="rId16"/>
+    <sheet name="Lake View" sheetId="17" r:id="rId17"/>
+    <sheet name="South Shore" sheetId="18" r:id="rId18"/>
+    <sheet name="Avondale" sheetId="19" r:id="rId19"/>
+    <sheet name="Mount Greenwood" sheetId="20" r:id="rId20"/>
+    <sheet name="Gage Park" sheetId="21" r:id="rId21"/>
+    <sheet name="West Loop" sheetId="22" r:id="rId22"/>
+    <sheet name="Rush &amp; Division" sheetId="23" r:id="rId23"/>
+    <sheet name="North Lawndale" sheetId="24" r:id="rId24"/>
+    <sheet name="South Chicago" sheetId="25" r:id="rId25"/>
+    <sheet name="Garfield Park" sheetId="26" r:id="rId26"/>
+    <sheet name="United Center" sheetId="27" r:id="rId27"/>
+    <sheet name="Magnificent Mile" sheetId="28" r:id="rId28"/>
+    <sheet name="Jefferson Park" sheetId="29" r:id="rId29"/>
+    <sheet name="New City" sheetId="30" r:id="rId30"/>
+    <sheet name="Logan Square" sheetId="31" r:id="rId31"/>
     <sheet name="Lower West Side" sheetId="32" r:id="rId32"/>
     <sheet name="Bridgeport" sheetId="33" r:id="rId33"/>
     <sheet name="Sheffield &amp; DePaul" sheetId="34" r:id="rId34"/>
@@ -905,7 +905,7 @@
         <v>137</v>
       </c>
       <c r="M2">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -946,7 +946,7 @@
         <v>262</v>
       </c>
       <c r="M3">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -1197,7 +1197,7 @@
         <v>703</v>
       </c>
       <c r="M10">
-        <v>386</v>
+        <v>385</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -1238,7 +1238,7 @@
         <v>1604</v>
       </c>
       <c r="M11">
-        <v>864</v>
+        <v>865</v>
       </c>
     </row>
   </sheetData>
@@ -1248,7 +1248,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M7"/>
+  <dimension ref="A1:M9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="23.7109375" customWidth="1"/>
@@ -1311,29 +1311,38 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
       <c r="D2">
+        <v>6</v>
+      </c>
+      <c r="E2">
         <v>1</v>
       </c>
       <c r="F2">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="G2">
-        <v>1</v>
+        <v>7</v>
+      </c>
+      <c r="H2">
+        <v>11</v>
       </c>
       <c r="I2">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="J2">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="K2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L2">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="M2">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -1341,32 +1350,53 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C3">
-        <v>1</v>
+        <v>5</v>
+      </c>
+      <c r="D3">
+        <v>18</v>
+      </c>
+      <c r="E3">
+        <v>10</v>
+      </c>
+      <c r="F3">
+        <v>12</v>
       </c>
       <c r="G3">
-        <v>2</v>
+        <v>11</v>
+      </c>
+      <c r="H3">
+        <v>7</v>
       </c>
       <c r="I3">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="J3">
-        <v>1</v>
+        <v>12</v>
+      </c>
+      <c r="K3">
+        <v>20</v>
       </c>
       <c r="L3">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="M3">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="E4">
+      <c r="B4">
+        <v>1</v>
+      </c>
+      <c r="D4">
+        <v>1</v>
+      </c>
+      <c r="H4">
         <v>2</v>
       </c>
       <c r="J4">
@@ -1374,120 +1404,157 @@
       </c>
       <c r="K4">
         <v>1</v>
+      </c>
+      <c r="L4">
+        <v>1</v>
+      </c>
+      <c r="M4">
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5">
-        <v>1</v>
-      </c>
-      <c r="C5">
-        <v>1</v>
-      </c>
-      <c r="D5">
-        <v>2</v>
-      </c>
-      <c r="E5">
-        <v>2</v>
-      </c>
-      <c r="G5">
+        <v>6</v>
+      </c>
+      <c r="H5">
         <v>1</v>
       </c>
       <c r="I5">
         <v>1</v>
-      </c>
-      <c r="J5">
-        <v>3</v>
-      </c>
-      <c r="K5">
-        <v>4</v>
-      </c>
-      <c r="M5">
-        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B6">
-        <v>8</v>
-      </c>
-      <c r="C6">
-        <v>13</v>
-      </c>
-      <c r="D6">
-        <v>10</v>
-      </c>
-      <c r="E6">
-        <v>9</v>
-      </c>
-      <c r="F6">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G6">
-        <v>8</v>
-      </c>
-      <c r="H6">
-        <v>1</v>
-      </c>
-      <c r="I6">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J6">
-        <v>5</v>
-      </c>
-      <c r="K6">
-        <v>8</v>
-      </c>
-      <c r="L6">
-        <v>3</v>
-      </c>
-      <c r="M6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7">
+        <v>34</v>
+      </c>
+      <c r="C7">
+        <v>45</v>
+      </c>
+      <c r="D7">
+        <v>25</v>
+      </c>
+      <c r="E7">
+        <v>22</v>
+      </c>
+      <c r="F7">
+        <v>42</v>
+      </c>
+      <c r="G7">
+        <v>32</v>
+      </c>
+      <c r="H7">
+        <v>26</v>
+      </c>
+      <c r="I7">
+        <v>21</v>
+      </c>
+      <c r="J7">
+        <v>15</v>
+      </c>
+      <c r="K7">
+        <v>44</v>
+      </c>
+      <c r="L7">
+        <v>43</v>
+      </c>
+      <c r="M7">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13">
+      <c r="A8" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B8">
+        <v>71</v>
+      </c>
+      <c r="C8">
+        <v>91</v>
+      </c>
+      <c r="D8">
+        <v>57</v>
+      </c>
+      <c r="E8">
+        <v>65</v>
+      </c>
+      <c r="F8">
+        <v>75</v>
+      </c>
+      <c r="G8">
+        <v>41</v>
+      </c>
+      <c r="H8">
+        <v>29</v>
+      </c>
+      <c r="I8">
+        <v>45</v>
+      </c>
+      <c r="J8">
+        <v>31</v>
+      </c>
+      <c r="K8">
+        <v>27</v>
+      </c>
+      <c r="L8">
+        <v>32</v>
+      </c>
+      <c r="M8">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13">
+      <c r="A9" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B7">
-        <v>10</v>
-      </c>
-      <c r="C7">
-        <v>15</v>
-      </c>
-      <c r="D7">
-        <v>13</v>
-      </c>
-      <c r="E7">
-        <v>13</v>
-      </c>
-      <c r="F7">
-        <v>10</v>
-      </c>
-      <c r="G7">
-        <v>12</v>
-      </c>
-      <c r="H7">
-        <v>1</v>
-      </c>
-      <c r="I7">
-        <v>8</v>
-      </c>
-      <c r="J7">
-        <v>14</v>
-      </c>
-      <c r="K7">
-        <v>15</v>
-      </c>
-      <c r="L7">
-        <v>6</v>
-      </c>
-      <c r="M7">
-        <v>7</v>
+      <c r="B9">
+        <v>111</v>
+      </c>
+      <c r="C9">
+        <v>142</v>
+      </c>
+      <c r="D9">
+        <v>107</v>
+      </c>
+      <c r="E9">
+        <v>98</v>
+      </c>
+      <c r="F9">
+        <v>138</v>
+      </c>
+      <c r="G9">
+        <v>92</v>
+      </c>
+      <c r="H9">
+        <v>76</v>
+      </c>
+      <c r="I9">
+        <v>90</v>
+      </c>
+      <c r="J9">
+        <v>69</v>
+      </c>
+      <c r="K9">
+        <v>95</v>
+      </c>
+      <c r="L9">
+        <v>102</v>
+      </c>
+      <c r="M9">
+        <v>38</v>
       </c>
     </row>
   </sheetData>
@@ -1497,10 +1564,10 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M7"/>
+  <dimension ref="A1:M10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="18.7109375" customWidth="1"/>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
     <col min="2" max="2" width="4.7109375" customWidth="1"/>
     <col min="3" max="3" width="4.7109375" customWidth="1"/>
     <col min="4" max="4" width="4.7109375" customWidth="1"/>
@@ -1564,25 +1631,34 @@
         <v>1</v>
       </c>
       <c r="D2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E2">
         <v>1</v>
       </c>
+      <c r="F2">
+        <v>3</v>
+      </c>
+      <c r="G2">
+        <v>1</v>
+      </c>
       <c r="H2">
+        <v>3</v>
+      </c>
+      <c r="I2">
         <v>2</v>
       </c>
       <c r="J2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K2">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="L2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M2">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -1596,33 +1672,39 @@
         <v>1</v>
       </c>
       <c r="D3">
-        <v>1</v>
+        <v>7</v>
+      </c>
+      <c r="E3">
+        <v>3</v>
       </c>
       <c r="F3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G3">
-        <v>1</v>
+        <v>8</v>
+      </c>
+      <c r="H3">
+        <v>4</v>
       </c>
       <c r="I3">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J3">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K3">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="L3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H4">
         <v>1</v>
@@ -1630,122 +1712,164 @@
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B5">
-        <v>7</v>
-      </c>
-      <c r="C5">
-        <v>11</v>
-      </c>
-      <c r="D5">
-        <v>8</v>
-      </c>
-      <c r="E5">
-        <v>5</v>
-      </c>
-      <c r="F5">
-        <v>5</v>
-      </c>
-      <c r="G5">
-        <v>6</v>
-      </c>
-      <c r="H5">
-        <v>2</v>
-      </c>
-      <c r="I5">
-        <v>2</v>
-      </c>
-      <c r="J5">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K5">
-        <v>6</v>
-      </c>
-      <c r="L5">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B6">
-        <v>15</v>
-      </c>
-      <c r="C6">
-        <v>16</v>
-      </c>
-      <c r="D6">
-        <v>15</v>
-      </c>
-      <c r="E6">
-        <v>16</v>
-      </c>
-      <c r="F6">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="G6">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="H6">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I6">
-        <v>5</v>
-      </c>
-      <c r="J6">
-        <v>12</v>
-      </c>
-      <c r="K6">
-        <v>6</v>
-      </c>
-      <c r="L6">
-        <v>4</v>
-      </c>
-      <c r="M6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D7">
+        <v>1</v>
+      </c>
+      <c r="E7">
+        <v>1</v>
+      </c>
+      <c r="J7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13">
+      <c r="A8" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8">
+        <v>5</v>
+      </c>
+      <c r="C8">
+        <v>9</v>
+      </c>
+      <c r="D8">
+        <v>17</v>
+      </c>
+      <c r="E8">
+        <v>13</v>
+      </c>
+      <c r="F8">
+        <v>19</v>
+      </c>
+      <c r="G8">
+        <v>15</v>
+      </c>
+      <c r="H8">
+        <v>5</v>
+      </c>
+      <c r="I8">
+        <v>15</v>
+      </c>
+      <c r="J8">
+        <v>12</v>
+      </c>
+      <c r="K8">
+        <v>18</v>
+      </c>
+      <c r="L8">
+        <v>19</v>
+      </c>
+      <c r="M8">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13">
+      <c r="A9" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B9">
+        <v>43</v>
+      </c>
+      <c r="C9">
+        <v>46</v>
+      </c>
+      <c r="D9">
+        <v>32</v>
+      </c>
+      <c r="E9">
+        <v>30</v>
+      </c>
+      <c r="F9">
+        <v>34</v>
+      </c>
+      <c r="G9">
+        <v>15</v>
+      </c>
+      <c r="H9">
+        <v>17</v>
+      </c>
+      <c r="I9">
+        <v>20</v>
+      </c>
+      <c r="J9">
+        <v>20</v>
+      </c>
+      <c r="K9">
+        <v>20</v>
+      </c>
+      <c r="L9">
+        <v>12</v>
+      </c>
+      <c r="M9">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13">
+      <c r="A10" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B7">
-        <v>24</v>
-      </c>
-      <c r="C7">
-        <v>29</v>
-      </c>
-      <c r="D7">
-        <v>25</v>
-      </c>
-      <c r="E7">
-        <v>22</v>
-      </c>
-      <c r="F7">
-        <v>19</v>
-      </c>
-      <c r="G7">
-        <v>16</v>
-      </c>
-      <c r="H7">
-        <v>10</v>
-      </c>
-      <c r="I7">
-        <v>11</v>
-      </c>
-      <c r="J7">
-        <v>20</v>
-      </c>
-      <c r="K7">
-        <v>15</v>
-      </c>
-      <c r="L7">
-        <v>16</v>
-      </c>
-      <c r="M7">
-        <v>7</v>
+      <c r="B10">
+        <v>51</v>
+      </c>
+      <c r="C10">
+        <v>57</v>
+      </c>
+      <c r="D10">
+        <v>62</v>
+      </c>
+      <c r="E10">
+        <v>48</v>
+      </c>
+      <c r="F10">
+        <v>60</v>
+      </c>
+      <c r="G10">
+        <v>40</v>
+      </c>
+      <c r="H10">
+        <v>31</v>
+      </c>
+      <c r="I10">
+        <v>44</v>
+      </c>
+      <c r="J10">
+        <v>43</v>
+      </c>
+      <c r="K10">
+        <v>57</v>
+      </c>
+      <c r="L10">
+        <v>39</v>
+      </c>
+      <c r="M10">
+        <v>21</v>
       </c>
     </row>
   </sheetData>
@@ -1821,27 +1945,51 @@
       <c r="D2">
         <v>1</v>
       </c>
+      <c r="F2">
+        <v>1</v>
+      </c>
+      <c r="G2">
+        <v>1</v>
+      </c>
+      <c r="I2">
+        <v>2</v>
+      </c>
       <c r="J2">
-        <v>1</v>
+        <v>4</v>
+      </c>
+      <c r="K2">
+        <v>2</v>
+      </c>
+      <c r="L2">
+        <v>2</v>
       </c>
       <c r="M2">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="E3">
-        <v>2</v>
+      <c r="B3">
+        <v>1</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
       </c>
       <c r="G3">
+        <v>2</v>
+      </c>
+      <c r="I3">
         <v>1</v>
       </c>
       <c r="J3">
         <v>1</v>
       </c>
       <c r="L3">
+        <v>1</v>
+      </c>
+      <c r="M3">
         <v>1</v>
       </c>
     </row>
@@ -1849,7 +1997,13 @@
       <c r="A4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C4">
+      <c r="E4">
+        <v>2</v>
+      </c>
+      <c r="J4">
+        <v>1</v>
+      </c>
+      <c r="K4">
         <v>1</v>
       </c>
     </row>
@@ -1858,25 +2012,31 @@
         <v>8</v>
       </c>
       <c r="B5">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C5">
-        <v>6</v>
+        <v>1</v>
+      </c>
+      <c r="D5">
+        <v>2</v>
       </c>
       <c r="E5">
-        <v>1</v>
-      </c>
-      <c r="H5">
-        <v>2</v>
+        <v>2</v>
+      </c>
+      <c r="G5">
+        <v>1</v>
+      </c>
+      <c r="I5">
+        <v>1</v>
       </c>
       <c r="J5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M5">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -1884,37 +2044,37 @@
         <v>9</v>
       </c>
       <c r="B6">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C6">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="D6">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E6">
+        <v>9</v>
+      </c>
+      <c r="F6">
+        <v>9</v>
+      </c>
+      <c r="G6">
         <v>8</v>
       </c>
-      <c r="F6">
-        <v>7</v>
-      </c>
-      <c r="G6">
-        <v>2</v>
-      </c>
       <c r="H6">
         <v>1</v>
       </c>
       <c r="I6">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J6">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K6">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="L6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M6">
         <v>2</v>
@@ -1925,40 +2085,40 @@
         <v>10</v>
       </c>
       <c r="B7">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C7">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D7">
+        <v>13</v>
+      </c>
+      <c r="E7">
+        <v>13</v>
+      </c>
+      <c r="F7">
+        <v>10</v>
+      </c>
+      <c r="G7">
+        <v>12</v>
+      </c>
+      <c r="H7">
+        <v>1</v>
+      </c>
+      <c r="I7">
+        <v>8</v>
+      </c>
+      <c r="J7">
+        <v>14</v>
+      </c>
+      <c r="K7">
+        <v>15</v>
+      </c>
+      <c r="L7">
+        <v>6</v>
+      </c>
+      <c r="M7">
         <v>7</v>
-      </c>
-      <c r="E7">
-        <v>11</v>
-      </c>
-      <c r="F7">
-        <v>7</v>
-      </c>
-      <c r="G7">
-        <v>3</v>
-      </c>
-      <c r="H7">
-        <v>3</v>
-      </c>
-      <c r="I7">
-        <v>1</v>
-      </c>
-      <c r="J7">
-        <v>9</v>
-      </c>
-      <c r="K7">
-        <v>3</v>
-      </c>
-      <c r="L7">
-        <v>3</v>
-      </c>
-      <c r="M7">
-        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -1967,6 +2127,477 @@
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:M7"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="18.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+    <col min="13" max="13" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="M1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
+      <c r="H2">
+        <v>2</v>
+      </c>
+      <c r="J2">
+        <v>1</v>
+      </c>
+      <c r="K2">
+        <v>2</v>
+      </c>
+      <c r="L2">
+        <v>2</v>
+      </c>
+      <c r="M2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>2</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
+      <c r="F3">
+        <v>3</v>
+      </c>
+      <c r="G3">
+        <v>1</v>
+      </c>
+      <c r="I3">
+        <v>4</v>
+      </c>
+      <c r="J3">
+        <v>2</v>
+      </c>
+      <c r="K3">
+        <v>1</v>
+      </c>
+      <c r="L3">
+        <v>4</v>
+      </c>
+      <c r="M3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5">
+        <v>7</v>
+      </c>
+      <c r="C5">
+        <v>11</v>
+      </c>
+      <c r="D5">
+        <v>8</v>
+      </c>
+      <c r="E5">
+        <v>5</v>
+      </c>
+      <c r="F5">
+        <v>5</v>
+      </c>
+      <c r="G5">
+        <v>6</v>
+      </c>
+      <c r="H5">
+        <v>2</v>
+      </c>
+      <c r="I5">
+        <v>2</v>
+      </c>
+      <c r="J5">
+        <v>5</v>
+      </c>
+      <c r="K5">
+        <v>6</v>
+      </c>
+      <c r="L5">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6">
+        <v>15</v>
+      </c>
+      <c r="C6">
+        <v>16</v>
+      </c>
+      <c r="D6">
+        <v>15</v>
+      </c>
+      <c r="E6">
+        <v>16</v>
+      </c>
+      <c r="F6">
+        <v>11</v>
+      </c>
+      <c r="G6">
+        <v>9</v>
+      </c>
+      <c r="H6">
+        <v>5</v>
+      </c>
+      <c r="I6">
+        <v>5</v>
+      </c>
+      <c r="J6">
+        <v>12</v>
+      </c>
+      <c r="K6">
+        <v>6</v>
+      </c>
+      <c r="L6">
+        <v>4</v>
+      </c>
+      <c r="M6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7">
+        <v>24</v>
+      </c>
+      <c r="C7">
+        <v>29</v>
+      </c>
+      <c r="D7">
+        <v>25</v>
+      </c>
+      <c r="E7">
+        <v>22</v>
+      </c>
+      <c r="F7">
+        <v>19</v>
+      </c>
+      <c r="G7">
+        <v>16</v>
+      </c>
+      <c r="H7">
+        <v>10</v>
+      </c>
+      <c r="I7">
+        <v>11</v>
+      </c>
+      <c r="J7">
+        <v>20</v>
+      </c>
+      <c r="K7">
+        <v>15</v>
+      </c>
+      <c r="L7">
+        <v>16</v>
+      </c>
+      <c r="M7">
+        <v>7</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:M7"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+    <col min="13" max="13" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="M1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="J2">
+        <v>1</v>
+      </c>
+      <c r="M2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E3">
+        <v>2</v>
+      </c>
+      <c r="G3">
+        <v>1</v>
+      </c>
+      <c r="J3">
+        <v>1</v>
+      </c>
+      <c r="L3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5">
+        <v>5</v>
+      </c>
+      <c r="C5">
+        <v>6</v>
+      </c>
+      <c r="E5">
+        <v>1</v>
+      </c>
+      <c r="H5">
+        <v>2</v>
+      </c>
+      <c r="J5">
+        <v>4</v>
+      </c>
+      <c r="K5">
+        <v>2</v>
+      </c>
+      <c r="M5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6">
+        <v>6</v>
+      </c>
+      <c r="C6">
+        <v>2</v>
+      </c>
+      <c r="D6">
+        <v>6</v>
+      </c>
+      <c r="E6">
+        <v>8</v>
+      </c>
+      <c r="F6">
+        <v>7</v>
+      </c>
+      <c r="G6">
+        <v>2</v>
+      </c>
+      <c r="H6">
+        <v>1</v>
+      </c>
+      <c r="I6">
+        <v>1</v>
+      </c>
+      <c r="J6">
+        <v>3</v>
+      </c>
+      <c r="K6">
+        <v>1</v>
+      </c>
+      <c r="L6">
+        <v>2</v>
+      </c>
+      <c r="M6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7">
+        <v>11</v>
+      </c>
+      <c r="C7">
+        <v>9</v>
+      </c>
+      <c r="D7">
+        <v>7</v>
+      </c>
+      <c r="E7">
+        <v>11</v>
+      </c>
+      <c r="F7">
+        <v>7</v>
+      </c>
+      <c r="G7">
+        <v>3</v>
+      </c>
+      <c r="H7">
+        <v>3</v>
+      </c>
+      <c r="I7">
+        <v>1</v>
+      </c>
+      <c r="J7">
+        <v>9</v>
+      </c>
+      <c r="K7">
+        <v>3</v>
+      </c>
+      <c r="L7">
+        <v>3</v>
+      </c>
+      <c r="M7">
+        <v>4</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:L8"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -2144,7 +2775,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M10"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -2498,7 +3129,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M8"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -2794,7 +3425,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -3065,7 +3696,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -3310,343 +3941,6 @@
       </c>
       <c r="M7">
         <v>11</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D4"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="18.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:4">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2023</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4">
-      <c r="A3" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B3">
-        <v>1</v>
-      </c>
-      <c r="C3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4">
-      <c r="A4" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B4">
-        <v>1</v>
-      </c>
-      <c r="C4">
-        <v>1</v>
-      </c>
-      <c r="D4">
-        <v>1</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M9"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" customWidth="1"/>
-    <col min="13" max="13" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="M1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2">
-        <v>1</v>
-      </c>
-      <c r="D2">
-        <v>1</v>
-      </c>
-      <c r="E2">
-        <v>1</v>
-      </c>
-      <c r="F2">
-        <v>1</v>
-      </c>
-      <c r="J2">
-        <v>1</v>
-      </c>
-      <c r="K2">
-        <v>6</v>
-      </c>
-      <c r="L2">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3">
-        <v>2</v>
-      </c>
-      <c r="C3">
-        <v>2</v>
-      </c>
-      <c r="D3">
-        <v>1</v>
-      </c>
-      <c r="E3">
-        <v>3</v>
-      </c>
-      <c r="H3">
-        <v>1</v>
-      </c>
-      <c r="I3">
-        <v>2</v>
-      </c>
-      <c r="J3">
-        <v>1</v>
-      </c>
-      <c r="K3">
-        <v>3</v>
-      </c>
-      <c r="L3">
-        <v>2</v>
-      </c>
-      <c r="M3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D4">
-        <v>1</v>
-      </c>
-      <c r="L4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="G5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="J6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
-      <c r="A7" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B7">
-        <v>4</v>
-      </c>
-      <c r="C7">
-        <v>2</v>
-      </c>
-      <c r="D7">
-        <v>8</v>
-      </c>
-      <c r="E7">
-        <v>5</v>
-      </c>
-      <c r="F7">
-        <v>4</v>
-      </c>
-      <c r="G7">
-        <v>4</v>
-      </c>
-      <c r="I7">
-        <v>3</v>
-      </c>
-      <c r="J7">
-        <v>4</v>
-      </c>
-      <c r="K7">
-        <v>6</v>
-      </c>
-      <c r="L7">
-        <v>5</v>
-      </c>
-      <c r="M7">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13">
-      <c r="A8" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B8">
-        <v>11</v>
-      </c>
-      <c r="C8">
-        <v>22</v>
-      </c>
-      <c r="D8">
-        <v>24</v>
-      </c>
-      <c r="E8">
-        <v>19</v>
-      </c>
-      <c r="F8">
-        <v>10</v>
-      </c>
-      <c r="G8">
-        <v>4</v>
-      </c>
-      <c r="H8">
-        <v>4</v>
-      </c>
-      <c r="I8">
-        <v>4</v>
-      </c>
-      <c r="J8">
-        <v>4</v>
-      </c>
-      <c r="K8">
-        <v>4</v>
-      </c>
-      <c r="L8">
-        <v>3</v>
-      </c>
-      <c r="M8">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13">
-      <c r="A9" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B9">
-        <v>17</v>
-      </c>
-      <c r="C9">
-        <v>27</v>
-      </c>
-      <c r="D9">
-        <v>35</v>
-      </c>
-      <c r="E9">
-        <v>28</v>
-      </c>
-      <c r="F9">
-        <v>15</v>
-      </c>
-      <c r="G9">
-        <v>9</v>
-      </c>
-      <c r="H9">
-        <v>5</v>
-      </c>
-      <c r="I9">
-        <v>9</v>
-      </c>
-      <c r="J9">
-        <v>11</v>
-      </c>
-      <c r="K9">
-        <v>19</v>
-      </c>
-      <c r="L9">
-        <v>16</v>
-      </c>
-      <c r="M9">
-        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -4714,7 +5008,7 @@
         <v>102</v>
       </c>
       <c r="M28">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="29" spans="1:13">
@@ -7451,7 +7745,7 @@
         <v>1604</v>
       </c>
       <c r="M99">
-        <v>864</v>
+        <v>865</v>
       </c>
     </row>
   </sheetData>
@@ -7561,324 +7855,60 @@
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M10"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="1" max="1" width="18.7109375" customWidth="1"/>
     <col min="2" max="2" width="4.7109375" customWidth="1"/>
     <col min="3" max="3" width="4.7109375" customWidth="1"/>
     <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" customWidth="1"/>
-    <col min="13" max="13" width="4.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1">
-        <v>2015</v>
+        <v>2016</v>
       </c>
       <c r="C1" s="1">
-        <v>2016</v>
+        <v>2022</v>
       </c>
       <c r="D1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="J1" s="1">
         <v>2023</v>
       </c>
-      <c r="K1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="M1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
+    </row>
+    <row r="2" spans="1:4">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2">
-        <v>5</v>
-      </c>
-      <c r="C2">
-        <v>3</v>
-      </c>
       <c r="D2">
-        <v>7</v>
-      </c>
-      <c r="E2">
-        <v>5</v>
-      </c>
-      <c r="F2">
-        <v>5</v>
-      </c>
-      <c r="G2">
-        <v>4</v>
-      </c>
-      <c r="H2">
-        <v>6</v>
-      </c>
-      <c r="I2">
-        <v>4</v>
-      </c>
-      <c r="J2">
-        <v>7</v>
-      </c>
-      <c r="K2">
-        <v>7</v>
-      </c>
-      <c r="L2">
-        <v>5</v>
-      </c>
-      <c r="M2">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="B3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C3">
-        <v>2</v>
-      </c>
-      <c r="D3">
-        <v>8</v>
-      </c>
-      <c r="E3">
-        <v>9</v>
-      </c>
-      <c r="F3">
-        <v>19</v>
-      </c>
-      <c r="G3">
-        <v>9</v>
-      </c>
-      <c r="H3">
-        <v>8</v>
-      </c>
-      <c r="I3">
-        <v>13</v>
-      </c>
-      <c r="J3">
-        <v>12</v>
-      </c>
-      <c r="K3">
-        <v>17</v>
-      </c>
-      <c r="L3">
-        <v>13</v>
-      </c>
-      <c r="M3">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="I4">
-        <v>1</v>
-      </c>
-      <c r="M4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="K5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="E6">
-        <v>1</v>
-      </c>
-      <c r="F6">
-        <v>2</v>
-      </c>
-      <c r="J6">
-        <v>2</v>
-      </c>
-      <c r="M6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
-      <c r="A7" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E7">
-        <v>1</v>
-      </c>
-      <c r="I7">
-        <v>1</v>
-      </c>
-      <c r="K7">
-        <v>1</v>
-      </c>
-      <c r="L7">
-        <v>1</v>
-      </c>
-      <c r="M7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13">
-      <c r="A8" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B8">
-        <v>24</v>
-      </c>
-      <c r="C8">
-        <v>37</v>
-      </c>
-      <c r="D8">
-        <v>21</v>
-      </c>
-      <c r="E8">
-        <v>22</v>
-      </c>
-      <c r="F8">
-        <v>27</v>
-      </c>
-      <c r="G8">
-        <v>15</v>
-      </c>
-      <c r="H8">
-        <v>25</v>
-      </c>
-      <c r="I8">
-        <v>21</v>
-      </c>
-      <c r="J8">
-        <v>26</v>
-      </c>
-      <c r="K8">
-        <v>49</v>
-      </c>
-      <c r="L8">
-        <v>44</v>
-      </c>
-      <c r="M8">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13">
-      <c r="A9" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B9">
-        <v>45</v>
-      </c>
-      <c r="C9">
-        <v>64</v>
-      </c>
-      <c r="D9">
-        <v>46</v>
-      </c>
-      <c r="E9">
-        <v>50</v>
-      </c>
-      <c r="F9">
-        <v>38</v>
-      </c>
-      <c r="G9">
-        <v>19</v>
-      </c>
-      <c r="H9">
-        <v>27</v>
-      </c>
-      <c r="I9">
-        <v>37</v>
-      </c>
-      <c r="J9">
-        <v>20</v>
-      </c>
-      <c r="K9">
-        <v>35</v>
-      </c>
-      <c r="L9">
-        <v>35</v>
-      </c>
-      <c r="M9">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13">
-      <c r="A10" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B10">
-        <v>77</v>
-      </c>
-      <c r="C10">
-        <v>106</v>
-      </c>
-      <c r="D10">
-        <v>82</v>
-      </c>
-      <c r="E10">
-        <v>88</v>
-      </c>
-      <c r="F10">
-        <v>91</v>
-      </c>
-      <c r="G10">
-        <v>47</v>
-      </c>
-      <c r="H10">
-        <v>66</v>
-      </c>
-      <c r="I10">
-        <v>77</v>
-      </c>
-      <c r="J10">
-        <v>67</v>
-      </c>
-      <c r="K10">
-        <v>110</v>
-      </c>
-      <c r="L10">
-        <v>98</v>
-      </c>
-      <c r="M10">
-        <v>41</v>
+      <c r="B4">
+        <v>1</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
+      <c r="D4">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -7951,32 +7981,26 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2">
-        <v>1</v>
-      </c>
       <c r="C2">
-        <v>2</v>
-      </c>
-      <c r="G2">
-        <v>2</v>
-      </c>
-      <c r="H2">
-        <v>4</v>
-      </c>
-      <c r="I2">
-        <v>3</v>
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
+      <c r="F2">
+        <v>1</v>
       </c>
       <c r="J2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K2">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="L2">
-        <v>1</v>
-      </c>
-      <c r="M2">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -7984,22 +8008,19 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="C3">
+        <v>2</v>
       </c>
       <c r="D3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E3">
-        <v>1</v>
-      </c>
-      <c r="F3">
-        <v>1</v>
-      </c>
-      <c r="G3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I3">
         <v>2</v>
@@ -8008,31 +8029,31 @@
         <v>1</v>
       </c>
       <c r="K3">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L3">
-        <v>6</v>
+        <v>2</v>
+      </c>
+      <c r="M3">
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F4">
-        <v>1</v>
-      </c>
-      <c r="J4">
+      <c r="D4">
         <v>1</v>
       </c>
       <c r="L4">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="I5">
+      <c r="G5">
         <v>1</v>
       </c>
     </row>
@@ -8040,7 +8061,7 @@
       <c r="A6" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D6">
+      <c r="J6">
         <v>1</v>
       </c>
     </row>
@@ -8049,40 +8070,37 @@
         <v>8</v>
       </c>
       <c r="B7">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D7">
+        <v>8</v>
+      </c>
+      <c r="E7">
+        <v>5</v>
+      </c>
+      <c r="F7">
+        <v>4</v>
+      </c>
+      <c r="G7">
+        <v>4</v>
+      </c>
+      <c r="I7">
+        <v>3</v>
+      </c>
+      <c r="J7">
+        <v>4</v>
+      </c>
+      <c r="K7">
         <v>6</v>
       </c>
-      <c r="E7">
-        <v>8</v>
-      </c>
-      <c r="F7">
-        <v>10</v>
-      </c>
-      <c r="G7">
-        <v>8</v>
-      </c>
-      <c r="H7">
-        <v>9</v>
-      </c>
-      <c r="I7">
-        <v>7</v>
-      </c>
-      <c r="J7">
-        <v>4</v>
-      </c>
-      <c r="K7">
-        <v>7</v>
-      </c>
       <c r="L7">
         <v>5</v>
       </c>
       <c r="M7">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -8090,40 +8108,40 @@
         <v>9</v>
       </c>
       <c r="B8">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="C8">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D8">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="E8">
-        <v>34</v>
+        <v>19</v>
       </c>
       <c r="F8">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="G8">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="H8">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="I8">
-        <v>27</v>
+        <v>4</v>
       </c>
       <c r="J8">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="K8">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="L8">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="M8">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -8131,40 +8149,40 @@
         <v>10</v>
       </c>
       <c r="B9">
+        <v>17</v>
+      </c>
+      <c r="C9">
         <v>27</v>
       </c>
-      <c r="C9">
-        <v>26</v>
-      </c>
       <c r="D9">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="E9">
-        <v>43</v>
+        <v>28</v>
       </c>
       <c r="F9">
-        <v>52</v>
+        <v>15</v>
       </c>
       <c r="G9">
-        <v>32</v>
+        <v>9</v>
       </c>
       <c r="H9">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="I9">
-        <v>40</v>
+        <v>9</v>
       </c>
       <c r="J9">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="K9">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="L9">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="M9">
-        <v>18</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -8173,6 +8191,292 @@
 </file>
 
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:M9"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+    <col min="13" max="13" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="M1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>2</v>
+      </c>
+      <c r="G2">
+        <v>2</v>
+      </c>
+      <c r="H2">
+        <v>4</v>
+      </c>
+      <c r="I2">
+        <v>3</v>
+      </c>
+      <c r="J2">
+        <v>2</v>
+      </c>
+      <c r="K2">
+        <v>2</v>
+      </c>
+      <c r="L2">
+        <v>1</v>
+      </c>
+      <c r="M2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>1</v>
+      </c>
+      <c r="D3">
+        <v>2</v>
+      </c>
+      <c r="E3">
+        <v>1</v>
+      </c>
+      <c r="F3">
+        <v>1</v>
+      </c>
+      <c r="G3">
+        <v>2</v>
+      </c>
+      <c r="H3">
+        <v>3</v>
+      </c>
+      <c r="I3">
+        <v>2</v>
+      </c>
+      <c r="J3">
+        <v>1</v>
+      </c>
+      <c r="K3">
+        <v>5</v>
+      </c>
+      <c r="L3">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F4">
+        <v>1</v>
+      </c>
+      <c r="J4">
+        <v>1</v>
+      </c>
+      <c r="L4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="I5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7">
+        <v>5</v>
+      </c>
+      <c r="C7">
+        <v>1</v>
+      </c>
+      <c r="D7">
+        <v>6</v>
+      </c>
+      <c r="E7">
+        <v>8</v>
+      </c>
+      <c r="F7">
+        <v>10</v>
+      </c>
+      <c r="G7">
+        <v>8</v>
+      </c>
+      <c r="H7">
+        <v>9</v>
+      </c>
+      <c r="I7">
+        <v>7</v>
+      </c>
+      <c r="J7">
+        <v>4</v>
+      </c>
+      <c r="K7">
+        <v>7</v>
+      </c>
+      <c r="L7">
+        <v>5</v>
+      </c>
+      <c r="M7">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13">
+      <c r="A8" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B8">
+        <v>20</v>
+      </c>
+      <c r="C8">
+        <v>23</v>
+      </c>
+      <c r="D8">
+        <v>35</v>
+      </c>
+      <c r="E8">
+        <v>34</v>
+      </c>
+      <c r="F8">
+        <v>40</v>
+      </c>
+      <c r="G8">
+        <v>20</v>
+      </c>
+      <c r="H8">
+        <v>9</v>
+      </c>
+      <c r="I8">
+        <v>27</v>
+      </c>
+      <c r="J8">
+        <v>22</v>
+      </c>
+      <c r="K8">
+        <v>14</v>
+      </c>
+      <c r="L8">
+        <v>11</v>
+      </c>
+      <c r="M8">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13">
+      <c r="A9" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B9">
+        <v>27</v>
+      </c>
+      <c r="C9">
+        <v>26</v>
+      </c>
+      <c r="D9">
+        <v>44</v>
+      </c>
+      <c r="E9">
+        <v>43</v>
+      </c>
+      <c r="F9">
+        <v>52</v>
+      </c>
+      <c r="G9">
+        <v>32</v>
+      </c>
+      <c r="H9">
+        <v>25</v>
+      </c>
+      <c r="I9">
+        <v>40</v>
+      </c>
+      <c r="J9">
+        <v>30</v>
+      </c>
+      <c r="K9">
+        <v>28</v>
+      </c>
+      <c r="L9">
+        <v>25</v>
+      </c>
+      <c r="M9">
+        <v>18</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -8430,7 +8734,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M8"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -8720,7 +9024,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -8969,319 +9273,6 @@
       </c>
       <c r="M6">
         <v>5</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M9"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" customWidth="1"/>
-    <col min="13" max="13" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="M1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2">
-        <v>1</v>
-      </c>
-      <c r="C2">
-        <v>2</v>
-      </c>
-      <c r="D2">
-        <v>7</v>
-      </c>
-      <c r="E2">
-        <v>8</v>
-      </c>
-      <c r="F2">
-        <v>5</v>
-      </c>
-      <c r="G2">
-        <v>4</v>
-      </c>
-      <c r="H2">
-        <v>2</v>
-      </c>
-      <c r="I2">
-        <v>5</v>
-      </c>
-      <c r="J2">
-        <v>3</v>
-      </c>
-      <c r="K2">
-        <v>5</v>
-      </c>
-      <c r="L2">
-        <v>5</v>
-      </c>
-      <c r="M2">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3">
-        <v>1</v>
-      </c>
-      <c r="C3">
-        <v>3</v>
-      </c>
-      <c r="D3">
-        <v>9</v>
-      </c>
-      <c r="E3">
-        <v>4</v>
-      </c>
-      <c r="F3">
-        <v>5</v>
-      </c>
-      <c r="G3">
-        <v>6</v>
-      </c>
-      <c r="H3">
-        <v>8</v>
-      </c>
-      <c r="I3">
-        <v>9</v>
-      </c>
-      <c r="J3">
-        <v>14</v>
-      </c>
-      <c r="K3">
-        <v>16</v>
-      </c>
-      <c r="L3">
-        <v>8</v>
-      </c>
-      <c r="M3">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="F4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5">
-        <v>2</v>
-      </c>
-      <c r="D5">
-        <v>1</v>
-      </c>
-      <c r="E5">
-        <v>1</v>
-      </c>
-      <c r="F5">
-        <v>1</v>
-      </c>
-      <c r="H5">
-        <v>1</v>
-      </c>
-      <c r="I5">
-        <v>2</v>
-      </c>
-      <c r="M5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="I6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
-      <c r="A7" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B7">
-        <v>15</v>
-      </c>
-      <c r="C7">
-        <v>35</v>
-      </c>
-      <c r="D7">
-        <v>34</v>
-      </c>
-      <c r="E7">
-        <v>56</v>
-      </c>
-      <c r="F7">
-        <v>54</v>
-      </c>
-      <c r="G7">
-        <v>37</v>
-      </c>
-      <c r="H7">
-        <v>39</v>
-      </c>
-      <c r="I7">
-        <v>32</v>
-      </c>
-      <c r="J7">
-        <v>34</v>
-      </c>
-      <c r="K7">
-        <v>27</v>
-      </c>
-      <c r="L7">
-        <v>31</v>
-      </c>
-      <c r="M7">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13">
-      <c r="A8" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B8">
-        <v>54</v>
-      </c>
-      <c r="C8">
-        <v>63</v>
-      </c>
-      <c r="D8">
-        <v>50</v>
-      </c>
-      <c r="E8">
-        <v>109</v>
-      </c>
-      <c r="F8">
-        <v>138</v>
-      </c>
-      <c r="G8">
-        <v>53</v>
-      </c>
-      <c r="H8">
-        <v>29</v>
-      </c>
-      <c r="I8">
-        <v>49</v>
-      </c>
-      <c r="J8">
-        <v>34</v>
-      </c>
-      <c r="K8">
-        <v>28</v>
-      </c>
-      <c r="L8">
-        <v>27</v>
-      </c>
-      <c r="M8">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13">
-      <c r="A9" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B9">
-        <v>73</v>
-      </c>
-      <c r="C9">
-        <v>103</v>
-      </c>
-      <c r="D9">
-        <v>101</v>
-      </c>
-      <c r="E9">
-        <v>178</v>
-      </c>
-      <c r="F9">
-        <v>204</v>
-      </c>
-      <c r="G9">
-        <v>100</v>
-      </c>
-      <c r="H9">
-        <v>79</v>
-      </c>
-      <c r="I9">
-        <v>98</v>
-      </c>
-      <c r="J9">
-        <v>85</v>
-      </c>
-      <c r="K9">
-        <v>76</v>
-      </c>
-      <c r="L9">
-        <v>71</v>
-      </c>
-      <c r="M9">
-        <v>49</v>
       </c>
     </row>
   </sheetData>
@@ -9354,75 +9345,87 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
       <c r="C2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D2">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E2">
-        <v>2</v>
+        <v>8</v>
+      </c>
+      <c r="F2">
+        <v>5</v>
       </c>
       <c r="G2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I2">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K2">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="L2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M2">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
+      <c r="B3">
+        <v>1</v>
+      </c>
       <c r="C3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D3">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="E3">
-        <v>1</v>
+        <v>4</v>
+      </c>
+      <c r="F3">
+        <v>5</v>
+      </c>
+      <c r="G3">
+        <v>6</v>
       </c>
       <c r="H3">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="I3">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="J3">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="K3">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="L3">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M3">
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="D4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F4">
         <v>1</v>
@@ -9432,15 +9435,33 @@
       <c r="A5" s="1" t="s">
         <v>5</v>
       </c>
+      <c r="B5">
+        <v>2</v>
+      </c>
+      <c r="D5">
+        <v>1</v>
+      </c>
+      <c r="E5">
+        <v>1</v>
+      </c>
+      <c r="F5">
+        <v>1</v>
+      </c>
+      <c r="H5">
+        <v>1</v>
+      </c>
+      <c r="I5">
+        <v>2</v>
+      </c>
       <c r="M5">
         <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="L6">
+        <v>6</v>
+      </c>
+      <c r="I6">
         <v>1</v>
       </c>
     </row>
@@ -9449,40 +9470,40 @@
         <v>8</v>
       </c>
       <c r="B7">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="C7">
-        <v>14</v>
+        <v>35</v>
       </c>
       <c r="D7">
-        <v>4</v>
+        <v>34</v>
       </c>
       <c r="E7">
-        <v>4</v>
+        <v>56</v>
       </c>
       <c r="F7">
-        <v>5</v>
+        <v>54</v>
       </c>
       <c r="G7">
-        <v>5</v>
+        <v>37</v>
       </c>
       <c r="H7">
-        <v>3</v>
+        <v>39</v>
       </c>
       <c r="I7">
-        <v>3</v>
+        <v>32</v>
       </c>
       <c r="J7">
-        <v>7</v>
+        <v>34</v>
       </c>
       <c r="K7">
-        <v>6</v>
+        <v>27</v>
       </c>
       <c r="L7">
-        <v>7</v>
+        <v>31</v>
       </c>
       <c r="M7">
-        <v>2</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -9490,40 +9511,40 @@
         <v>9</v>
       </c>
       <c r="B8">
-        <v>11</v>
+        <v>54</v>
       </c>
       <c r="C8">
-        <v>10</v>
+        <v>63</v>
       </c>
       <c r="D8">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="E8">
-        <v>12</v>
+        <v>109</v>
       </c>
       <c r="F8">
+        <v>138</v>
+      </c>
+      <c r="G8">
+        <v>53</v>
+      </c>
+      <c r="H8">
+        <v>29</v>
+      </c>
+      <c r="I8">
+        <v>49</v>
+      </c>
+      <c r="J8">
+        <v>34</v>
+      </c>
+      <c r="K8">
+        <v>28</v>
+      </c>
+      <c r="L8">
+        <v>27</v>
+      </c>
+      <c r="M8">
         <v>20</v>
-      </c>
-      <c r="G8">
-        <v>8</v>
-      </c>
-      <c r="H8">
-        <v>3</v>
-      </c>
-      <c r="I8">
-        <v>5</v>
-      </c>
-      <c r="J8">
-        <v>6</v>
-      </c>
-      <c r="K8">
-        <v>3</v>
-      </c>
-      <c r="L8">
-        <v>10</v>
-      </c>
-      <c r="M8">
-        <v>2</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -9531,40 +9552,40 @@
         <v>10</v>
       </c>
       <c r="B9">
-        <v>14</v>
+        <v>73</v>
       </c>
       <c r="C9">
-        <v>27</v>
+        <v>103</v>
       </c>
       <c r="D9">
-        <v>17</v>
+        <v>101</v>
       </c>
       <c r="E9">
-        <v>19</v>
+        <v>178</v>
       </c>
       <c r="F9">
-        <v>26</v>
+        <v>204</v>
       </c>
       <c r="G9">
-        <v>14</v>
+        <v>100</v>
       </c>
       <c r="H9">
-        <v>9</v>
+        <v>79</v>
       </c>
       <c r="I9">
-        <v>11</v>
+        <v>98</v>
       </c>
       <c r="J9">
-        <v>20</v>
+        <v>85</v>
       </c>
       <c r="K9">
-        <v>14</v>
+        <v>76</v>
       </c>
       <c r="L9">
-        <v>27</v>
+        <v>71</v>
       </c>
       <c r="M9">
-        <v>9</v>
+        <v>49</v>
       </c>
     </row>
   </sheetData>
@@ -9573,6 +9594,289 @@
 </file>
 
 <file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:M9"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+    <col min="13" max="13" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="M1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="E2">
+        <v>2</v>
+      </c>
+      <c r="G2">
+        <v>1</v>
+      </c>
+      <c r="H2">
+        <v>1</v>
+      </c>
+      <c r="I2">
+        <v>2</v>
+      </c>
+      <c r="J2">
+        <v>2</v>
+      </c>
+      <c r="K2">
+        <v>2</v>
+      </c>
+      <c r="L2">
+        <v>3</v>
+      </c>
+      <c r="M2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3">
+        <v>2</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
+      <c r="E3">
+        <v>1</v>
+      </c>
+      <c r="H3">
+        <v>2</v>
+      </c>
+      <c r="I3">
+        <v>1</v>
+      </c>
+      <c r="J3">
+        <v>5</v>
+      </c>
+      <c r="K3">
+        <v>3</v>
+      </c>
+      <c r="L3">
+        <v>6</v>
+      </c>
+      <c r="M3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D4">
+        <v>1</v>
+      </c>
+      <c r="F4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="M5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="L6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7">
+        <v>3</v>
+      </c>
+      <c r="C7">
+        <v>14</v>
+      </c>
+      <c r="D7">
+        <v>4</v>
+      </c>
+      <c r="E7">
+        <v>4</v>
+      </c>
+      <c r="F7">
+        <v>5</v>
+      </c>
+      <c r="G7">
+        <v>5</v>
+      </c>
+      <c r="H7">
+        <v>3</v>
+      </c>
+      <c r="I7">
+        <v>3</v>
+      </c>
+      <c r="J7">
+        <v>7</v>
+      </c>
+      <c r="K7">
+        <v>6</v>
+      </c>
+      <c r="L7">
+        <v>7</v>
+      </c>
+      <c r="M7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13">
+      <c r="A8" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B8">
+        <v>11</v>
+      </c>
+      <c r="C8">
+        <v>10</v>
+      </c>
+      <c r="D8">
+        <v>10</v>
+      </c>
+      <c r="E8">
+        <v>12</v>
+      </c>
+      <c r="F8">
+        <v>20</v>
+      </c>
+      <c r="G8">
+        <v>8</v>
+      </c>
+      <c r="H8">
+        <v>3</v>
+      </c>
+      <c r="I8">
+        <v>5</v>
+      </c>
+      <c r="J8">
+        <v>6</v>
+      </c>
+      <c r="K8">
+        <v>3</v>
+      </c>
+      <c r="L8">
+        <v>10</v>
+      </c>
+      <c r="M8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13">
+      <c r="A9" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B9">
+        <v>14</v>
+      </c>
+      <c r="C9">
+        <v>27</v>
+      </c>
+      <c r="D9">
+        <v>17</v>
+      </c>
+      <c r="E9">
+        <v>19</v>
+      </c>
+      <c r="F9">
+        <v>26</v>
+      </c>
+      <c r="G9">
+        <v>14</v>
+      </c>
+      <c r="H9">
+        <v>9</v>
+      </c>
+      <c r="I9">
+        <v>11</v>
+      </c>
+      <c r="J9">
+        <v>20</v>
+      </c>
+      <c r="K9">
+        <v>14</v>
+      </c>
+      <c r="L9">
+        <v>27</v>
+      </c>
+      <c r="M9">
+        <v>9</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -9750,7 +10054,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M8"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -10012,238 +10316,6 @@
       </c>
       <c r="M8">
         <v>11</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M6"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="18.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" customWidth="1"/>
-    <col min="13" max="13" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="M1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2">
-        <v>1</v>
-      </c>
-      <c r="C2">
-        <v>1</v>
-      </c>
-      <c r="D2">
-        <v>2</v>
-      </c>
-      <c r="H2">
-        <v>2</v>
-      </c>
-      <c r="I2">
-        <v>1</v>
-      </c>
-      <c r="K2">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3">
-        <v>1</v>
-      </c>
-      <c r="D3">
-        <v>2</v>
-      </c>
-      <c r="E3">
-        <v>2</v>
-      </c>
-      <c r="F3">
-        <v>1</v>
-      </c>
-      <c r="I3">
-        <v>2</v>
-      </c>
-      <c r="J3">
-        <v>4</v>
-      </c>
-      <c r="K3">
-        <v>5</v>
-      </c>
-      <c r="L3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4">
-        <v>6</v>
-      </c>
-      <c r="C4">
-        <v>6</v>
-      </c>
-      <c r="D4">
-        <v>1</v>
-      </c>
-      <c r="E4">
-        <v>4</v>
-      </c>
-      <c r="F4">
-        <v>4</v>
-      </c>
-      <c r="I4">
-        <v>1</v>
-      </c>
-      <c r="J4">
-        <v>1</v>
-      </c>
-      <c r="K4">
-        <v>2</v>
-      </c>
-      <c r="M4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B5">
-        <v>9</v>
-      </c>
-      <c r="C5">
-        <v>5</v>
-      </c>
-      <c r="D5">
-        <v>5</v>
-      </c>
-      <c r="E5">
-        <v>7</v>
-      </c>
-      <c r="F5">
-        <v>8</v>
-      </c>
-      <c r="G5">
-        <v>6</v>
-      </c>
-      <c r="H5">
-        <v>2</v>
-      </c>
-      <c r="I5">
-        <v>4</v>
-      </c>
-      <c r="J5">
-        <v>1</v>
-      </c>
-      <c r="K5">
-        <v>2</v>
-      </c>
-      <c r="L5">
-        <v>2</v>
-      </c>
-      <c r="M5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B6">
-        <v>17</v>
-      </c>
-      <c r="C6">
-        <v>12</v>
-      </c>
-      <c r="D6">
-        <v>10</v>
-      </c>
-      <c r="E6">
-        <v>13</v>
-      </c>
-      <c r="F6">
-        <v>13</v>
-      </c>
-      <c r="G6">
-        <v>6</v>
-      </c>
-      <c r="H6">
-        <v>4</v>
-      </c>
-      <c r="I6">
-        <v>8</v>
-      </c>
-      <c r="J6">
-        <v>6</v>
-      </c>
-      <c r="K6">
-        <v>12</v>
-      </c>
-      <c r="L6">
-        <v>4</v>
-      </c>
-      <c r="M6">
-        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -10492,6 +10564,238 @@
 
 <file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:M6"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="18.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+    <col min="13" max="13" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="M1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>2</v>
+      </c>
+      <c r="H2">
+        <v>2</v>
+      </c>
+      <c r="I2">
+        <v>1</v>
+      </c>
+      <c r="K2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>1</v>
+      </c>
+      <c r="D3">
+        <v>2</v>
+      </c>
+      <c r="E3">
+        <v>2</v>
+      </c>
+      <c r="F3">
+        <v>1</v>
+      </c>
+      <c r="I3">
+        <v>2</v>
+      </c>
+      <c r="J3">
+        <v>4</v>
+      </c>
+      <c r="K3">
+        <v>5</v>
+      </c>
+      <c r="L3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4">
+        <v>6</v>
+      </c>
+      <c r="C4">
+        <v>6</v>
+      </c>
+      <c r="D4">
+        <v>1</v>
+      </c>
+      <c r="E4">
+        <v>4</v>
+      </c>
+      <c r="F4">
+        <v>4</v>
+      </c>
+      <c r="I4">
+        <v>1</v>
+      </c>
+      <c r="J4">
+        <v>1</v>
+      </c>
+      <c r="K4">
+        <v>2</v>
+      </c>
+      <c r="M4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5">
+        <v>9</v>
+      </c>
+      <c r="C5">
+        <v>5</v>
+      </c>
+      <c r="D5">
+        <v>5</v>
+      </c>
+      <c r="E5">
+        <v>7</v>
+      </c>
+      <c r="F5">
+        <v>8</v>
+      </c>
+      <c r="G5">
+        <v>6</v>
+      </c>
+      <c r="H5">
+        <v>2</v>
+      </c>
+      <c r="I5">
+        <v>4</v>
+      </c>
+      <c r="J5">
+        <v>1</v>
+      </c>
+      <c r="K5">
+        <v>2</v>
+      </c>
+      <c r="L5">
+        <v>2</v>
+      </c>
+      <c r="M5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6">
+        <v>17</v>
+      </c>
+      <c r="C6">
+        <v>12</v>
+      </c>
+      <c r="D6">
+        <v>10</v>
+      </c>
+      <c r="E6">
+        <v>13</v>
+      </c>
+      <c r="F6">
+        <v>13</v>
+      </c>
+      <c r="G6">
+        <v>6</v>
+      </c>
+      <c r="H6">
+        <v>4</v>
+      </c>
+      <c r="I6">
+        <v>8</v>
+      </c>
+      <c r="J6">
+        <v>6</v>
+      </c>
+      <c r="K6">
+        <v>12</v>
+      </c>
+      <c r="L6">
+        <v>4</v>
+      </c>
+      <c r="M6">
+        <v>2</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -10758,238 +11062,6 @@
       </c>
       <c r="M8">
         <v>9</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M6"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="18.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" customWidth="1"/>
-    <col min="13" max="13" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="M1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2">
-        <v>2</v>
-      </c>
-      <c r="G2">
-        <v>1</v>
-      </c>
-      <c r="I2">
-        <v>2</v>
-      </c>
-      <c r="L2">
-        <v>2</v>
-      </c>
-      <c r="M2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D3">
-        <v>1</v>
-      </c>
-      <c r="F3">
-        <v>1</v>
-      </c>
-      <c r="G3">
-        <v>1</v>
-      </c>
-      <c r="H3">
-        <v>1</v>
-      </c>
-      <c r="I3">
-        <v>2</v>
-      </c>
-      <c r="J3">
-        <v>1</v>
-      </c>
-      <c r="L3">
-        <v>3</v>
-      </c>
-      <c r="M3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4">
-        <v>1</v>
-      </c>
-      <c r="C4">
-        <v>2</v>
-      </c>
-      <c r="E4">
-        <v>2</v>
-      </c>
-      <c r="F4">
-        <v>3</v>
-      </c>
-      <c r="G4">
-        <v>3</v>
-      </c>
-      <c r="H4">
-        <v>1</v>
-      </c>
-      <c r="I4">
-        <v>4</v>
-      </c>
-      <c r="J4">
-        <v>2</v>
-      </c>
-      <c r="K4">
-        <v>4</v>
-      </c>
-      <c r="L4">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B5">
-        <v>3</v>
-      </c>
-      <c r="C5">
-        <v>3</v>
-      </c>
-      <c r="D5">
-        <v>7</v>
-      </c>
-      <c r="E5">
-        <v>4</v>
-      </c>
-      <c r="F5">
-        <v>7</v>
-      </c>
-      <c r="G5">
-        <v>3</v>
-      </c>
-      <c r="H5">
-        <v>3</v>
-      </c>
-      <c r="I5">
-        <v>3</v>
-      </c>
-      <c r="J5">
-        <v>1</v>
-      </c>
-      <c r="K5">
-        <v>3</v>
-      </c>
-      <c r="L5">
-        <v>4</v>
-      </c>
-      <c r="M5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B6">
-        <v>4</v>
-      </c>
-      <c r="C6">
-        <v>7</v>
-      </c>
-      <c r="D6">
-        <v>8</v>
-      </c>
-      <c r="E6">
-        <v>6</v>
-      </c>
-      <c r="F6">
-        <v>11</v>
-      </c>
-      <c r="G6">
-        <v>8</v>
-      </c>
-      <c r="H6">
-        <v>5</v>
-      </c>
-      <c r="I6">
-        <v>11</v>
-      </c>
-      <c r="J6">
-        <v>4</v>
-      </c>
-      <c r="K6">
-        <v>7</v>
-      </c>
-      <c r="L6">
-        <v>13</v>
-      </c>
-      <c r="M6">
-        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -23152,10 +23224,10 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M10"/>
+  <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="1" max="1" width="18.7109375" customWidth="1"/>
     <col min="2" max="2" width="4.7109375" customWidth="1"/>
     <col min="3" max="3" width="4.7109375" customWidth="1"/>
     <col min="4" max="4" width="4.7109375" customWidth="1"/>
@@ -23216,248 +23288,165 @@
         <v>1</v>
       </c>
       <c r="C2">
-        <v>1</v>
-      </c>
-      <c r="D2">
-        <v>5</v>
-      </c>
-      <c r="E2">
-        <v>1</v>
-      </c>
-      <c r="F2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G2">
         <v>1</v>
       </c>
-      <c r="H2">
-        <v>3</v>
-      </c>
       <c r="I2">
         <v>2</v>
       </c>
-      <c r="J2">
-        <v>5</v>
-      </c>
-      <c r="K2">
-        <v>8</v>
-      </c>
       <c r="L2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M2">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B3">
-        <v>2</v>
-      </c>
-      <c r="C3">
-        <v>1</v>
-      </c>
       <c r="D3">
-        <v>7</v>
-      </c>
-      <c r="E3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F3">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G3">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="H3">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I3">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="J3">
-        <v>4</v>
-      </c>
-      <c r="K3">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="L3">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4">
+        <v>1</v>
+      </c>
+      <c r="C4">
+        <v>2</v>
+      </c>
+      <c r="E4">
+        <v>2</v>
+      </c>
+      <c r="F4">
+        <v>3</v>
+      </c>
+      <c r="G4">
         <v>3</v>
       </c>
       <c r="H4">
         <v>1</v>
+      </c>
+      <c r="I4">
+        <v>4</v>
+      </c>
+      <c r="J4">
+        <v>2</v>
+      </c>
+      <c r="K4">
+        <v>4</v>
+      </c>
+      <c r="L4">
+        <v>4</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B5">
+        <v>3</v>
+      </c>
+      <c r="C5">
+        <v>3</v>
+      </c>
+      <c r="D5">
+        <v>7</v>
+      </c>
+      <c r="E5">
+        <v>4</v>
+      </c>
+      <c r="F5">
+        <v>7</v>
+      </c>
+      <c r="G5">
+        <v>3</v>
+      </c>
+      <c r="H5">
+        <v>3</v>
+      </c>
+      <c r="I5">
+        <v>3</v>
+      </c>
+      <c r="J5">
         <v>1</v>
       </c>
       <c r="K5">
+        <v>3</v>
+      </c>
+      <c r="L5">
+        <v>4</v>
+      </c>
+      <c r="M5">
         <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6">
+        <v>4</v>
+      </c>
+      <c r="C6">
+        <v>7</v>
+      </c>
+      <c r="D6">
+        <v>8</v>
+      </c>
+      <c r="E6">
         <v>6</v>
       </c>
+      <c r="F6">
+        <v>11</v>
+      </c>
       <c r="G6">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="H6">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
-      <c r="A7" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="J6">
+        <v>4</v>
+      </c>
+      <c r="K6">
         <v>7</v>
       </c>
-      <c r="D7">
-        <v>1</v>
-      </c>
-      <c r="E7">
-        <v>1</v>
-      </c>
-      <c r="J7">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13">
-      <c r="A8" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B8">
-        <v>5</v>
-      </c>
-      <c r="C8">
-        <v>9</v>
-      </c>
-      <c r="D8">
-        <v>17</v>
-      </c>
-      <c r="E8">
+      <c r="L6">
         <v>13</v>
       </c>
-      <c r="F8">
-        <v>19</v>
-      </c>
-      <c r="G8">
-        <v>15</v>
-      </c>
-      <c r="H8">
-        <v>5</v>
-      </c>
-      <c r="I8">
-        <v>15</v>
-      </c>
-      <c r="J8">
-        <v>12</v>
-      </c>
-      <c r="K8">
-        <v>18</v>
-      </c>
-      <c r="L8">
-        <v>19</v>
-      </c>
-      <c r="M8">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13">
-      <c r="A9" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B9">
-        <v>43</v>
-      </c>
-      <c r="C9">
-        <v>46</v>
-      </c>
-      <c r="D9">
-        <v>32</v>
-      </c>
-      <c r="E9">
-        <v>30</v>
-      </c>
-      <c r="F9">
-        <v>34</v>
-      </c>
-      <c r="G9">
-        <v>15</v>
-      </c>
-      <c r="H9">
-        <v>17</v>
-      </c>
-      <c r="I9">
-        <v>20</v>
-      </c>
-      <c r="J9">
-        <v>20</v>
-      </c>
-      <c r="K9">
-        <v>20</v>
-      </c>
-      <c r="L9">
-        <v>12</v>
-      </c>
-      <c r="M9">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13">
-      <c r="A10" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B10">
-        <v>51</v>
-      </c>
-      <c r="C10">
-        <v>57</v>
-      </c>
-      <c r="D10">
-        <v>62</v>
-      </c>
-      <c r="E10">
-        <v>48</v>
-      </c>
-      <c r="F10">
-        <v>60</v>
-      </c>
-      <c r="G10">
-        <v>40</v>
-      </c>
-      <c r="H10">
-        <v>31</v>
-      </c>
-      <c r="I10">
-        <v>44</v>
-      </c>
-      <c r="J10">
-        <v>43</v>
-      </c>
-      <c r="K10">
-        <v>57</v>
-      </c>
-      <c r="L10">
-        <v>39</v>
-      </c>
-      <c r="M10">
-        <v>21</v>
+      <c r="M6">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -25150,7 +25139,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M9"/>
+  <dimension ref="A1:M10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="23.7109375" customWidth="1"/>
@@ -25213,38 +25202,41 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
+      <c r="B2">
+        <v>5</v>
+      </c>
       <c r="C2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D2">
+        <v>7</v>
+      </c>
+      <c r="E2">
+        <v>5</v>
+      </c>
+      <c r="F2">
+        <v>5</v>
+      </c>
+      <c r="G2">
+        <v>4</v>
+      </c>
+      <c r="H2">
         <v>6</v>
       </c>
-      <c r="E2">
-        <v>1</v>
-      </c>
-      <c r="F2">
-        <v>9</v>
-      </c>
-      <c r="G2">
+      <c r="I2">
+        <v>4</v>
+      </c>
+      <c r="J2">
         <v>7</v>
       </c>
-      <c r="H2">
-        <v>11</v>
-      </c>
-      <c r="I2">
-        <v>10</v>
-      </c>
-      <c r="J2">
-        <v>9</v>
-      </c>
       <c r="K2">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="L2">
+        <v>5</v>
+      </c>
+      <c r="M2">
         <v>6</v>
-      </c>
-      <c r="M2">
-        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -25252,25 +25244,25 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C3">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D3">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="E3">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F3">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="G3">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H3">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I3">
         <v>13</v>
@@ -25279,35 +25271,20 @@
         <v>12</v>
       </c>
       <c r="K3">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="L3">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="M3">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B4">
-        <v>1</v>
-      </c>
-      <c r="D4">
-        <v>1</v>
-      </c>
-      <c r="H4">
-        <v>2</v>
-      </c>
-      <c r="J4">
-        <v>1</v>
-      </c>
-      <c r="K4">
-        <v>1</v>
-      </c>
-      <c r="L4">
+        <v>3</v>
+      </c>
+      <c r="I4">
         <v>1</v>
       </c>
       <c r="M4">
@@ -25316,147 +25293,170 @@
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H5">
-        <v>1</v>
-      </c>
-      <c r="I5">
+        <v>4</v>
+      </c>
+      <c r="K5">
         <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="G6">
-        <v>1</v>
+        <v>5</v>
+      </c>
+      <c r="E6">
+        <v>1</v>
+      </c>
+      <c r="F6">
+        <v>2</v>
       </c>
       <c r="J6">
+        <v>2</v>
+      </c>
+      <c r="M6">
         <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B7">
-        <v>34</v>
-      </c>
-      <c r="C7">
-        <v>45</v>
-      </c>
-      <c r="D7">
-        <v>25</v>
+        <v>6</v>
       </c>
       <c r="E7">
-        <v>22</v>
-      </c>
-      <c r="F7">
-        <v>42</v>
-      </c>
-      <c r="G7">
-        <v>32</v>
-      </c>
-      <c r="H7">
-        <v>26</v>
+        <v>1</v>
       </c>
       <c r="I7">
-        <v>21</v>
-      </c>
-      <c r="J7">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="K7">
-        <v>44</v>
+        <v>1</v>
       </c>
       <c r="L7">
-        <v>43</v>
+        <v>1</v>
       </c>
       <c r="M7">
-        <v>17</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:13">
       <c r="A8" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B8">
-        <v>71</v>
+        <v>24</v>
       </c>
       <c r="C8">
-        <v>91</v>
+        <v>37</v>
       </c>
       <c r="D8">
-        <v>57</v>
+        <v>21</v>
       </c>
       <c r="E8">
-        <v>65</v>
+        <v>22</v>
       </c>
       <c r="F8">
-        <v>75</v>
+        <v>27</v>
       </c>
       <c r="G8">
-        <v>41</v>
+        <v>15</v>
       </c>
       <c r="H8">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="I8">
-        <v>45</v>
+        <v>21</v>
       </c>
       <c r="J8">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="K8">
-        <v>27</v>
+        <v>49</v>
       </c>
       <c r="L8">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="M8">
-        <v>9</v>
+        <v>13</v>
       </c>
     </row>
     <row r="9" spans="1:13">
       <c r="A9" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B9">
+        <v>45</v>
+      </c>
+      <c r="C9">
+        <v>64</v>
+      </c>
+      <c r="D9">
+        <v>46</v>
+      </c>
+      <c r="E9">
+        <v>50</v>
+      </c>
+      <c r="F9">
+        <v>38</v>
+      </c>
+      <c r="G9">
+        <v>19</v>
+      </c>
+      <c r="H9">
+        <v>27</v>
+      </c>
+      <c r="I9">
+        <v>37</v>
+      </c>
+      <c r="J9">
+        <v>20</v>
+      </c>
+      <c r="K9">
+        <v>35</v>
+      </c>
+      <c r="L9">
+        <v>35</v>
+      </c>
+      <c r="M9">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13">
+      <c r="A10" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B9">
-        <v>111</v>
-      </c>
-      <c r="C9">
-        <v>142</v>
-      </c>
-      <c r="D9">
-        <v>107</v>
-      </c>
-      <c r="E9">
+      <c r="B10">
+        <v>77</v>
+      </c>
+      <c r="C10">
+        <v>106</v>
+      </c>
+      <c r="D10">
+        <v>82</v>
+      </c>
+      <c r="E10">
+        <v>88</v>
+      </c>
+      <c r="F10">
+        <v>91</v>
+      </c>
+      <c r="G10">
+        <v>47</v>
+      </c>
+      <c r="H10">
+        <v>66</v>
+      </c>
+      <c r="I10">
+        <v>77</v>
+      </c>
+      <c r="J10">
+        <v>67</v>
+      </c>
+      <c r="K10">
+        <v>110</v>
+      </c>
+      <c r="L10">
         <v>98</v>
       </c>
-      <c r="F9">
-        <v>138</v>
-      </c>
-      <c r="G9">
-        <v>92</v>
-      </c>
-      <c r="H9">
-        <v>76</v>
-      </c>
-      <c r="I9">
-        <v>90</v>
-      </c>
-      <c r="J9">
-        <v>69</v>
-      </c>
-      <c r="K9">
-        <v>95</v>
-      </c>
-      <c r="L9">
-        <v>102</v>
-      </c>
-      <c r="M9">
-        <v>37</v>
+      <c r="M10">
+        <v>41</v>
       </c>
     </row>
   </sheetData>

--- a/output/cta-index-crime-full-year.xlsx
+++ b/output/cta-index-crime-full-year.xlsx
@@ -41,64 +41,64 @@
     <sheet name="Magnificent Mile" sheetId="32" r:id="rId32"/>
     <sheet name="Jefferson Park" sheetId="33" r:id="rId33"/>
     <sheet name="New City" sheetId="34" r:id="rId34"/>
-    <sheet name="Logan Square" sheetId="35" r:id="rId35"/>
-    <sheet name="Bridgeport" sheetId="36" r:id="rId36"/>
-    <sheet name="Sheffield &amp; DePaul" sheetId="37" r:id="rId37"/>
-    <sheet name="Greektown" sheetId="38" r:id="rId38"/>
-    <sheet name="River North" sheetId="39" r:id="rId39"/>
-    <sheet name="Roseland" sheetId="40" r:id="rId40"/>
-    <sheet name="Chinatown" sheetId="41" r:id="rId41"/>
-    <sheet name="Austin" sheetId="42" r:id="rId42"/>
-    <sheet name="Rogers Park" sheetId="43" r:id="rId43"/>
-    <sheet name="Mckinley Park" sheetId="44" r:id="rId44"/>
-    <sheet name="Irving Park" sheetId="45" r:id="rId45"/>
-    <sheet name="Armour Square" sheetId="46" r:id="rId46"/>
-    <sheet name="Uptown" sheetId="47" r:id="rId47"/>
-    <sheet name="West Elsdon" sheetId="48" r:id="rId48"/>
-    <sheet name="Woodlawn" sheetId="49" r:id="rId49"/>
-    <sheet name="Douglas" sheetId="50" r:id="rId50"/>
-    <sheet name="Edgewater" sheetId="51" r:id="rId51"/>
-    <sheet name="Morgan Park" sheetId="52" r:id="rId52"/>
-    <sheet name="Chicago Lawn" sheetId="53" r:id="rId53"/>
-    <sheet name="South Deering" sheetId="54" r:id="rId54"/>
-    <sheet name="Fuller Park" sheetId="55" r:id="rId55"/>
-    <sheet name="Brighton Park" sheetId="56" r:id="rId56"/>
-    <sheet name="Montclare" sheetId="57" r:id="rId57"/>
-    <sheet name="Near South Side" sheetId="58" r:id="rId58"/>
-    <sheet name="Lincoln Park" sheetId="59" r:id="rId59"/>
-    <sheet name="Riverdale" sheetId="60" r:id="rId60"/>
-    <sheet name="North Center" sheetId="61" r:id="rId61"/>
-    <sheet name="Little Village" sheetId="62" r:id="rId62"/>
-    <sheet name="Lincoln Square" sheetId="63" r:id="rId63"/>
-    <sheet name="Clearing" sheetId="64" r:id="rId64"/>
-    <sheet name="Boystown" sheetId="65" r:id="rId65"/>
-    <sheet name="Auburn Gresham" sheetId="66" r:id="rId66"/>
-    <sheet name="Bucktown" sheetId="67" r:id="rId67"/>
-    <sheet name="Hermosa" sheetId="68" r:id="rId68"/>
-    <sheet name="West Pullman" sheetId="69" r:id="rId69"/>
-    <sheet name="Millenium Park" sheetId="70" r:id="rId70"/>
-    <sheet name="Wrigleyville" sheetId="71" r:id="rId71"/>
-    <sheet name="Garfield Ridge" sheetId="72" r:id="rId72"/>
-    <sheet name="Printers Row" sheetId="73" r:id="rId73"/>
-    <sheet name="Archer Heights" sheetId="74" r:id="rId74"/>
-    <sheet name="East Village" sheetId="75" r:id="rId75"/>
-    <sheet name="Ukrainian Village" sheetId="76" r:id="rId76"/>
-    <sheet name="Hyde Park" sheetId="77" r:id="rId77"/>
-    <sheet name="Calumet Heights" sheetId="78" r:id="rId78"/>
-    <sheet name="Washington Heights" sheetId="79" r:id="rId79"/>
-    <sheet name="Pullman" sheetId="80" r:id="rId80"/>
-    <sheet name="Kenwood" sheetId="81" r:id="rId81"/>
-    <sheet name="North Park" sheetId="82" r:id="rId82"/>
-    <sheet name="Jackson Park" sheetId="83" r:id="rId83"/>
-    <sheet name="Grant Park" sheetId="84" r:id="rId84"/>
-    <sheet name="Beverly" sheetId="85" r:id="rId85"/>
-    <sheet name="Streeterville" sheetId="86" r:id="rId86"/>
-    <sheet name="Andersonville" sheetId="87" r:id="rId87"/>
-    <sheet name="Portage Park" sheetId="88" r:id="rId88"/>
-    <sheet name="Avalon Park" sheetId="89" r:id="rId89"/>
-    <sheet name="Oakland" sheetId="90" r:id="rId90"/>
-    <sheet name="Hegewisch" sheetId="91" r:id="rId91"/>
-    <sheet name="West Lawn" sheetId="92" r:id="rId92"/>
+    <sheet name="West Lawn" sheetId="35" r:id="rId35"/>
+    <sheet name="Logan Square" sheetId="36" r:id="rId36"/>
+    <sheet name="Bridgeport" sheetId="37" r:id="rId37"/>
+    <sheet name="Sheffield &amp; DePaul" sheetId="38" r:id="rId38"/>
+    <sheet name="Greektown" sheetId="39" r:id="rId39"/>
+    <sheet name="River North" sheetId="40" r:id="rId40"/>
+    <sheet name="Roseland" sheetId="41" r:id="rId41"/>
+    <sheet name="Chinatown" sheetId="42" r:id="rId42"/>
+    <sheet name="Austin" sheetId="43" r:id="rId43"/>
+    <sheet name="Rogers Park" sheetId="44" r:id="rId44"/>
+    <sheet name="Mckinley Park" sheetId="45" r:id="rId45"/>
+    <sheet name="Irving Park" sheetId="46" r:id="rId46"/>
+    <sheet name="Armour Square" sheetId="47" r:id="rId47"/>
+    <sheet name="Uptown" sheetId="48" r:id="rId48"/>
+    <sheet name="West Elsdon" sheetId="49" r:id="rId49"/>
+    <sheet name="Woodlawn" sheetId="50" r:id="rId50"/>
+    <sheet name="Douglas" sheetId="51" r:id="rId51"/>
+    <sheet name="Edgewater" sheetId="52" r:id="rId52"/>
+    <sheet name="Morgan Park" sheetId="53" r:id="rId53"/>
+    <sheet name="Chicago Lawn" sheetId="54" r:id="rId54"/>
+    <sheet name="South Deering" sheetId="55" r:id="rId55"/>
+    <sheet name="Fuller Park" sheetId="56" r:id="rId56"/>
+    <sheet name="Brighton Park" sheetId="57" r:id="rId57"/>
+    <sheet name="Montclare" sheetId="58" r:id="rId58"/>
+    <sheet name="Near South Side" sheetId="59" r:id="rId59"/>
+    <sheet name="Lincoln Park" sheetId="60" r:id="rId60"/>
+    <sheet name="Riverdale" sheetId="61" r:id="rId61"/>
+    <sheet name="North Center" sheetId="62" r:id="rId62"/>
+    <sheet name="Little Village" sheetId="63" r:id="rId63"/>
+    <sheet name="Lincoln Square" sheetId="64" r:id="rId64"/>
+    <sheet name="Clearing" sheetId="65" r:id="rId65"/>
+    <sheet name="Boystown" sheetId="66" r:id="rId66"/>
+    <sheet name="Auburn Gresham" sheetId="67" r:id="rId67"/>
+    <sheet name="Bucktown" sheetId="68" r:id="rId68"/>
+    <sheet name="Hermosa" sheetId="69" r:id="rId69"/>
+    <sheet name="West Pullman" sheetId="70" r:id="rId70"/>
+    <sheet name="Millenium Park" sheetId="71" r:id="rId71"/>
+    <sheet name="Wrigleyville" sheetId="72" r:id="rId72"/>
+    <sheet name="Garfield Ridge" sheetId="73" r:id="rId73"/>
+    <sheet name="Printers Row" sheetId="74" r:id="rId74"/>
+    <sheet name="Archer Heights" sheetId="75" r:id="rId75"/>
+    <sheet name="East Village" sheetId="76" r:id="rId76"/>
+    <sheet name="Ukrainian Village" sheetId="77" r:id="rId77"/>
+    <sheet name="Hyde Park" sheetId="78" r:id="rId78"/>
+    <sheet name="Calumet Heights" sheetId="79" r:id="rId79"/>
+    <sheet name="Washington Heights" sheetId="80" r:id="rId80"/>
+    <sheet name="Pullman" sheetId="81" r:id="rId81"/>
+    <sheet name="Kenwood" sheetId="82" r:id="rId82"/>
+    <sheet name="North Park" sheetId="83" r:id="rId83"/>
+    <sheet name="Jackson Park" sheetId="84" r:id="rId84"/>
+    <sheet name="Grant Park" sheetId="85" r:id="rId85"/>
+    <sheet name="Beverly" sheetId="86" r:id="rId86"/>
+    <sheet name="Streeterville" sheetId="87" r:id="rId87"/>
+    <sheet name="Andersonville" sheetId="88" r:id="rId88"/>
+    <sheet name="Portage Park" sheetId="89" r:id="rId89"/>
+    <sheet name="Avalon Park" sheetId="90" r:id="rId90"/>
+    <sheet name="Oakland" sheetId="91" r:id="rId91"/>
+    <sheet name="Hegewisch" sheetId="92" r:id="rId92"/>
     <sheet name="East Side" sheetId="93" r:id="rId93"/>
     <sheet name="Dunning" sheetId="94" r:id="rId94"/>
     <sheet name="Gold Coast" sheetId="95" r:id="rId95"/>
@@ -946,7 +946,7 @@
         <v>262</v>
       </c>
       <c r="M3">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -1238,7 +1238,7 @@
         <v>1604</v>
       </c>
       <c r="M11">
-        <v>876</v>
+        <v>877</v>
       </c>
     </row>
   </sheetData>
@@ -7519,6 +7519,9 @@
       <c r="L91">
         <v>5</v>
       </c>
+      <c r="M91">
+        <v>1</v>
+      </c>
     </row>
     <row r="92" spans="1:13">
       <c r="A92" s="2" t="s">
@@ -7842,7 +7845,7 @@
         <v>1604</v>
       </c>
       <c r="M99">
-        <v>876</v>
+        <v>877</v>
       </c>
     </row>
   </sheetData>
@@ -11829,6 +11832,158 @@
 
 <file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:K6"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="18.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="H2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="H3">
+        <v>1</v>
+      </c>
+      <c r="K3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11">
+      <c r="A4" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D4">
+        <v>4</v>
+      </c>
+      <c r="F4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11">
+      <c r="A5" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5">
+        <v>3</v>
+      </c>
+      <c r="C5">
+        <v>2</v>
+      </c>
+      <c r="D5">
+        <v>2</v>
+      </c>
+      <c r="E5">
+        <v>5</v>
+      </c>
+      <c r="G5">
+        <v>1</v>
+      </c>
+      <c r="H5">
+        <v>1</v>
+      </c>
+      <c r="I5">
+        <v>1</v>
+      </c>
+      <c r="J5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11">
+      <c r="A6" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6">
+        <v>3</v>
+      </c>
+      <c r="C6">
+        <v>2</v>
+      </c>
+      <c r="D6">
+        <v>6</v>
+      </c>
+      <c r="E6">
+        <v>5</v>
+      </c>
+      <c r="F6">
+        <v>1</v>
+      </c>
+      <c r="G6">
+        <v>1</v>
+      </c>
+      <c r="H6">
+        <v>3</v>
+      </c>
+      <c r="I6">
+        <v>1</v>
+      </c>
+      <c r="J6">
+        <v>5</v>
+      </c>
+      <c r="K6">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -12095,240 +12250,6 @@
       </c>
       <c r="M8">
         <v>9</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M7"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" customWidth="1"/>
-    <col min="13" max="13" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="M1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2">
-        <v>1</v>
-      </c>
-      <c r="D2">
-        <v>1</v>
-      </c>
-      <c r="E2">
-        <v>1</v>
-      </c>
-      <c r="H2">
-        <v>1</v>
-      </c>
-      <c r="J2">
-        <v>1</v>
-      </c>
-      <c r="K2">
-        <v>2</v>
-      </c>
-      <c r="L2">
-        <v>2</v>
-      </c>
-      <c r="M2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C3">
-        <v>1</v>
-      </c>
-      <c r="H3">
-        <v>1</v>
-      </c>
-      <c r="I3">
-        <v>1</v>
-      </c>
-      <c r="K3">
-        <v>2</v>
-      </c>
-      <c r="M3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="J4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5">
-        <v>2</v>
-      </c>
-      <c r="C5">
-        <v>4</v>
-      </c>
-      <c r="D5">
-        <v>2</v>
-      </c>
-      <c r="F5">
-        <v>1</v>
-      </c>
-      <c r="G5">
-        <v>2</v>
-      </c>
-      <c r="H5">
-        <v>1</v>
-      </c>
-      <c r="I5">
-        <v>2</v>
-      </c>
-      <c r="K5">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B6">
-        <v>7</v>
-      </c>
-      <c r="C6">
-        <v>5</v>
-      </c>
-      <c r="D6">
-        <v>6</v>
-      </c>
-      <c r="E6">
-        <v>4</v>
-      </c>
-      <c r="F6">
-        <v>9</v>
-      </c>
-      <c r="G6">
-        <v>6</v>
-      </c>
-      <c r="H6">
-        <v>1</v>
-      </c>
-      <c r="I6">
-        <v>4</v>
-      </c>
-      <c r="J6">
-        <v>4</v>
-      </c>
-      <c r="K6">
-        <v>6</v>
-      </c>
-      <c r="L6">
-        <v>1</v>
-      </c>
-      <c r="M6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
-      <c r="A7" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B7">
-        <v>9</v>
-      </c>
-      <c r="C7">
-        <v>11</v>
-      </c>
-      <c r="D7">
-        <v>9</v>
-      </c>
-      <c r="E7">
-        <v>5</v>
-      </c>
-      <c r="F7">
-        <v>10</v>
-      </c>
-      <c r="G7">
-        <v>8</v>
-      </c>
-      <c r="H7">
-        <v>4</v>
-      </c>
-      <c r="I7">
-        <v>7</v>
-      </c>
-      <c r="J7">
-        <v>6</v>
-      </c>
-      <c r="K7">
-        <v>14</v>
-      </c>
-      <c r="L7">
-        <v>3</v>
-      </c>
-      <c r="M7">
-        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -12401,61 +12322,46 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
       <c r="D2">
         <v>1</v>
       </c>
       <c r="E2">
-        <v>2</v>
-      </c>
-      <c r="F2">
         <v>1</v>
       </c>
       <c r="H2">
-        <v>3</v>
-      </c>
-      <c r="I2">
         <v>1</v>
       </c>
       <c r="J2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L2">
         <v>2</v>
       </c>
       <c r="M2">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B3">
-        <v>2</v>
-      </c>
-      <c r="D3">
-        <v>1</v>
-      </c>
-      <c r="F3">
-        <v>2</v>
+      <c r="C3">
+        <v>1</v>
       </c>
       <c r="H3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I3">
-        <v>4</v>
-      </c>
-      <c r="J3">
         <v>1</v>
       </c>
       <c r="K3">
         <v>2</v>
-      </c>
-      <c r="L3">
-        <v>6</v>
       </c>
       <c r="M3">
         <v>1</v>
@@ -12465,11 +12371,8 @@
       <c r="A4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="H4">
-        <v>1</v>
-      </c>
-      <c r="I4">
-        <v>2</v>
+      <c r="J4">
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -12477,40 +12380,28 @@
         <v>8</v>
       </c>
       <c r="B5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D5">
-        <v>5</v>
-      </c>
-      <c r="E5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F5">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="G5">
         <v>2</v>
       </c>
       <c r="H5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I5">
-        <v>8</v>
-      </c>
-      <c r="J5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K5">
-        <v>5</v>
-      </c>
-      <c r="L5">
-        <v>4</v>
-      </c>
-      <c r="M5">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -12518,40 +12409,40 @@
         <v>9</v>
       </c>
       <c r="B6">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C6">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="D6">
-        <v>26</v>
+        <v>6</v>
       </c>
       <c r="E6">
-        <v>31</v>
+        <v>4</v>
       </c>
       <c r="F6">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="G6">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="H6">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="I6">
+        <v>4</v>
+      </c>
+      <c r="J6">
+        <v>4</v>
+      </c>
+      <c r="K6">
         <v>6</v>
       </c>
-      <c r="J6">
-        <v>6</v>
-      </c>
-      <c r="K6">
-        <v>9</v>
-      </c>
       <c r="L6">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="M6">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -12559,40 +12450,40 @@
         <v>10</v>
       </c>
       <c r="B7">
+        <v>9</v>
+      </c>
+      <c r="C7">
+        <v>11</v>
+      </c>
+      <c r="D7">
+        <v>9</v>
+      </c>
+      <c r="E7">
+        <v>5</v>
+      </c>
+      <c r="F7">
+        <v>10</v>
+      </c>
+      <c r="G7">
+        <v>8</v>
+      </c>
+      <c r="H7">
+        <v>4</v>
+      </c>
+      <c r="I7">
+        <v>7</v>
+      </c>
+      <c r="J7">
+        <v>6</v>
+      </c>
+      <c r="K7">
         <v>14</v>
       </c>
-      <c r="C7">
-        <v>27</v>
-      </c>
-      <c r="D7">
-        <v>33</v>
-      </c>
-      <c r="E7">
-        <v>36</v>
-      </c>
-      <c r="F7">
-        <v>38</v>
-      </c>
-      <c r="G7">
-        <v>13</v>
-      </c>
-      <c r="H7">
-        <v>17</v>
-      </c>
-      <c r="I7">
-        <v>21</v>
-      </c>
-      <c r="J7">
-        <v>11</v>
-      </c>
-      <c r="K7">
-        <v>17</v>
-      </c>
       <c r="L7">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="M7">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -12665,13 +12556,31 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C2">
-        <v>1</v>
-      </c>
       <c r="D2">
         <v>1</v>
       </c>
+      <c r="E2">
+        <v>2</v>
+      </c>
+      <c r="F2">
+        <v>1</v>
+      </c>
+      <c r="H2">
+        <v>3</v>
+      </c>
+      <c r="I2">
+        <v>1</v>
+      </c>
+      <c r="J2">
+        <v>3</v>
+      </c>
       <c r="K2">
+        <v>1</v>
+      </c>
+      <c r="L2">
+        <v>2</v>
+      </c>
+      <c r="M2">
         <v>1</v>
       </c>
     </row>
@@ -12679,16 +12588,31 @@
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C3">
-        <v>1</v>
-      </c>
-      <c r="G3">
-        <v>1</v>
+      <c r="B3">
+        <v>2</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
+      <c r="F3">
+        <v>2</v>
       </c>
       <c r="H3">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="I3">
+        <v>4</v>
+      </c>
+      <c r="J3">
+        <v>1</v>
+      </c>
+      <c r="K3">
+        <v>2</v>
       </c>
       <c r="L3">
+        <v>6</v>
+      </c>
+      <c r="M3">
         <v>1</v>
       </c>
     </row>
@@ -12696,46 +12620,52 @@
       <c r="A4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="E4">
-        <v>1</v>
-      </c>
-      <c r="K4">
-        <v>1</v>
+      <c r="H4">
+        <v>1</v>
+      </c>
+      <c r="I4">
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
         <v>8</v>
       </c>
+      <c r="B5">
+        <v>1</v>
+      </c>
+      <c r="C5">
+        <v>5</v>
+      </c>
       <c r="D5">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F5">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I5">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="J5">
         <v>1</v>
       </c>
       <c r="K5">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="L5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M5">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -12743,40 +12673,40 @@
         <v>9</v>
       </c>
       <c r="B6">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="C6">
+        <v>22</v>
+      </c>
+      <c r="D6">
+        <v>26</v>
+      </c>
+      <c r="E6">
+        <v>31</v>
+      </c>
+      <c r="F6">
+        <v>28</v>
+      </c>
+      <c r="G6">
+        <v>11</v>
+      </c>
+      <c r="H6">
+        <v>8</v>
+      </c>
+      <c r="I6">
         <v>6</v>
       </c>
-      <c r="D6">
-        <v>5</v>
-      </c>
-      <c r="E6">
-        <v>10</v>
-      </c>
-      <c r="F6">
+      <c r="J6">
         <v>6</v>
       </c>
-      <c r="G6">
-        <v>2</v>
-      </c>
-      <c r="H6">
-        <v>4</v>
-      </c>
-      <c r="I6">
-        <v>4</v>
-      </c>
-      <c r="J6">
-        <v>3</v>
-      </c>
       <c r="K6">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="L6">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="M6">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -12784,40 +12714,40 @@
         <v>10</v>
       </c>
       <c r="B7">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="C7">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="D7">
-        <v>7</v>
+        <v>33</v>
       </c>
       <c r="E7">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="F7">
+        <v>38</v>
+      </c>
+      <c r="G7">
+        <v>13</v>
+      </c>
+      <c r="H7">
+        <v>17</v>
+      </c>
+      <c r="I7">
+        <v>21</v>
+      </c>
+      <c r="J7">
         <v>11</v>
       </c>
-      <c r="G7">
-        <v>6</v>
-      </c>
-      <c r="H7">
-        <v>6</v>
-      </c>
-      <c r="I7">
+      <c r="K7">
+        <v>17</v>
+      </c>
+      <c r="L7">
+        <v>21</v>
+      </c>
+      <c r="M7">
         <v>9</v>
-      </c>
-      <c r="J7">
-        <v>4</v>
-      </c>
-      <c r="K7">
-        <v>9</v>
-      </c>
-      <c r="L7">
-        <v>5</v>
-      </c>
-      <c r="M7">
-        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -12896,25 +12826,7 @@
       <c r="D2">
         <v>1</v>
       </c>
-      <c r="E2">
-        <v>1</v>
-      </c>
-      <c r="F2">
-        <v>1</v>
-      </c>
-      <c r="H2">
-        <v>2</v>
-      </c>
-      <c r="I2">
-        <v>4</v>
-      </c>
-      <c r="J2">
-        <v>3</v>
-      </c>
       <c r="K2">
-        <v>2</v>
-      </c>
-      <c r="M2">
         <v>1</v>
       </c>
     </row>
@@ -12923,44 +12835,26 @@
         <v>2</v>
       </c>
       <c r="C3">
-        <v>3</v>
-      </c>
-      <c r="D3">
-        <v>4</v>
-      </c>
-      <c r="E3">
         <v>1</v>
       </c>
       <c r="G3">
         <v>1</v>
       </c>
       <c r="H3">
-        <v>2</v>
-      </c>
-      <c r="I3">
-        <v>3</v>
-      </c>
-      <c r="J3">
-        <v>5</v>
-      </c>
-      <c r="K3">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L3">
-        <v>8</v>
-      </c>
-      <c r="M3">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G4">
-        <v>1</v>
-      </c>
-      <c r="J4">
+      <c r="E4">
+        <v>1</v>
+      </c>
+      <c r="K4">
         <v>1</v>
       </c>
     </row>
@@ -12968,41 +12862,35 @@
       <c r="A5" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B5">
-        <v>3</v>
-      </c>
-      <c r="C5">
-        <v>3</v>
-      </c>
       <c r="D5">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F5">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="G5">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="H5">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="I5">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="J5">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="K5">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="L5">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="M5">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -13010,40 +12898,40 @@
         <v>9</v>
       </c>
       <c r="B6">
-        <v>47</v>
+        <v>4</v>
       </c>
       <c r="C6">
-        <v>37</v>
+        <v>6</v>
       </c>
       <c r="D6">
-        <v>85</v>
+        <v>5</v>
       </c>
       <c r="E6">
-        <v>75</v>
+        <v>10</v>
       </c>
       <c r="F6">
-        <v>80</v>
+        <v>6</v>
       </c>
       <c r="G6">
-        <v>22</v>
+        <v>2</v>
       </c>
       <c r="H6">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I6">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="J6">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="K6">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="L6">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="M6">
-        <v>12</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -13051,40 +12939,40 @@
         <v>10</v>
       </c>
       <c r="B7">
-        <v>50</v>
+        <v>4</v>
       </c>
       <c r="C7">
-        <v>44</v>
+        <v>8</v>
       </c>
       <c r="D7">
-        <v>97</v>
+        <v>7</v>
       </c>
       <c r="E7">
-        <v>82</v>
+        <v>15</v>
       </c>
       <c r="F7">
-        <v>93</v>
+        <v>11</v>
       </c>
       <c r="G7">
-        <v>37</v>
+        <v>6</v>
       </c>
       <c r="H7">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="I7">
-        <v>47</v>
+        <v>9</v>
       </c>
       <c r="J7">
-        <v>33</v>
+        <v>4</v>
       </c>
       <c r="K7">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="L7">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="M7">
-        <v>20</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -13364,6 +13252,273 @@
 
 <file path=xl/worksheets/sheet40.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:M7"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+    <col min="13" max="13" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="M1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
+      <c r="F2">
+        <v>1</v>
+      </c>
+      <c r="H2">
+        <v>2</v>
+      </c>
+      <c r="I2">
+        <v>4</v>
+      </c>
+      <c r="J2">
+        <v>3</v>
+      </c>
+      <c r="K2">
+        <v>2</v>
+      </c>
+      <c r="M2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3">
+        <v>3</v>
+      </c>
+      <c r="D3">
+        <v>4</v>
+      </c>
+      <c r="E3">
+        <v>1</v>
+      </c>
+      <c r="G3">
+        <v>1</v>
+      </c>
+      <c r="H3">
+        <v>2</v>
+      </c>
+      <c r="I3">
+        <v>3</v>
+      </c>
+      <c r="J3">
+        <v>5</v>
+      </c>
+      <c r="K3">
+        <v>4</v>
+      </c>
+      <c r="L3">
+        <v>8</v>
+      </c>
+      <c r="M3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G4">
+        <v>1</v>
+      </c>
+      <c r="J4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5">
+        <v>3</v>
+      </c>
+      <c r="C5">
+        <v>3</v>
+      </c>
+      <c r="D5">
+        <v>7</v>
+      </c>
+      <c r="E5">
+        <v>5</v>
+      </c>
+      <c r="F5">
+        <v>12</v>
+      </c>
+      <c r="G5">
+        <v>13</v>
+      </c>
+      <c r="H5">
+        <v>11</v>
+      </c>
+      <c r="I5">
+        <v>14</v>
+      </c>
+      <c r="J5">
+        <v>12</v>
+      </c>
+      <c r="K5">
+        <v>9</v>
+      </c>
+      <c r="L5">
+        <v>6</v>
+      </c>
+      <c r="M5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6">
+        <v>47</v>
+      </c>
+      <c r="C6">
+        <v>37</v>
+      </c>
+      <c r="D6">
+        <v>85</v>
+      </c>
+      <c r="E6">
+        <v>75</v>
+      </c>
+      <c r="F6">
+        <v>80</v>
+      </c>
+      <c r="G6">
+        <v>22</v>
+      </c>
+      <c r="H6">
+        <v>6</v>
+      </c>
+      <c r="I6">
+        <v>26</v>
+      </c>
+      <c r="J6">
+        <v>12</v>
+      </c>
+      <c r="K6">
+        <v>19</v>
+      </c>
+      <c r="L6">
+        <v>11</v>
+      </c>
+      <c r="M6">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7">
+        <v>50</v>
+      </c>
+      <c r="C7">
+        <v>44</v>
+      </c>
+      <c r="D7">
+        <v>97</v>
+      </c>
+      <c r="E7">
+        <v>82</v>
+      </c>
+      <c r="F7">
+        <v>93</v>
+      </c>
+      <c r="G7">
+        <v>37</v>
+      </c>
+      <c r="H7">
+        <v>21</v>
+      </c>
+      <c r="I7">
+        <v>47</v>
+      </c>
+      <c r="J7">
+        <v>33</v>
+      </c>
+      <c r="K7">
+        <v>34</v>
+      </c>
+      <c r="L7">
+        <v>25</v>
+      </c>
+      <c r="M7">
+        <v>20</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet41.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -13683,7 +13838,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet41.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet42.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M9"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -13950,324 +14105,6 @@
       </c>
       <c r="M9">
         <v>7</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet42.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M10"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" customWidth="1"/>
-    <col min="13" max="13" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="M1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2">
-        <v>4</v>
-      </c>
-      <c r="C2">
-        <v>4</v>
-      </c>
-      <c r="D2">
-        <v>3</v>
-      </c>
-      <c r="E2">
-        <v>5</v>
-      </c>
-      <c r="F2">
-        <v>9</v>
-      </c>
-      <c r="G2">
-        <v>3</v>
-      </c>
-      <c r="H2">
-        <v>5</v>
-      </c>
-      <c r="I2">
-        <v>4</v>
-      </c>
-      <c r="J2">
-        <v>8</v>
-      </c>
-      <c r="K2">
-        <v>7</v>
-      </c>
-      <c r="L2">
-        <v>5</v>
-      </c>
-      <c r="M2">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3">
-        <v>4</v>
-      </c>
-      <c r="C3">
-        <v>5</v>
-      </c>
-      <c r="D3">
-        <v>6</v>
-      </c>
-      <c r="E3">
-        <v>7</v>
-      </c>
-      <c r="F3">
-        <v>6</v>
-      </c>
-      <c r="G3">
-        <v>7</v>
-      </c>
-      <c r="H3">
-        <v>8</v>
-      </c>
-      <c r="I3">
-        <v>6</v>
-      </c>
-      <c r="J3">
-        <v>10</v>
-      </c>
-      <c r="K3">
-        <v>12</v>
-      </c>
-      <c r="L3">
-        <v>14</v>
-      </c>
-      <c r="M3">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="I4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5">
-        <v>1</v>
-      </c>
-      <c r="D5">
-        <v>1</v>
-      </c>
-      <c r="E5">
-        <v>1</v>
-      </c>
-      <c r="J5">
-        <v>3</v>
-      </c>
-      <c r="K5">
-        <v>2</v>
-      </c>
-      <c r="M5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="K6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
-      <c r="A7" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="L7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13">
-      <c r="A8" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B8">
-        <v>23</v>
-      </c>
-      <c r="C8">
-        <v>31</v>
-      </c>
-      <c r="D8">
-        <v>22</v>
-      </c>
-      <c r="E8">
-        <v>44</v>
-      </c>
-      <c r="F8">
-        <v>38</v>
-      </c>
-      <c r="G8">
-        <v>24</v>
-      </c>
-      <c r="H8">
-        <v>50</v>
-      </c>
-      <c r="I8">
-        <v>34</v>
-      </c>
-      <c r="J8">
-        <v>26</v>
-      </c>
-      <c r="K8">
-        <v>24</v>
-      </c>
-      <c r="L8">
-        <v>14</v>
-      </c>
-      <c r="M8">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13">
-      <c r="A9" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B9">
-        <v>46</v>
-      </c>
-      <c r="C9">
-        <v>59</v>
-      </c>
-      <c r="D9">
-        <v>33</v>
-      </c>
-      <c r="E9">
-        <v>73</v>
-      </c>
-      <c r="F9">
-        <v>114</v>
-      </c>
-      <c r="G9">
-        <v>58</v>
-      </c>
-      <c r="H9">
-        <v>41</v>
-      </c>
-      <c r="I9">
-        <v>44</v>
-      </c>
-      <c r="J9">
-        <v>20</v>
-      </c>
-      <c r="K9">
-        <v>25</v>
-      </c>
-      <c r="L9">
-        <v>27</v>
-      </c>
-      <c r="M9">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13">
-      <c r="A10" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B10">
-        <v>78</v>
-      </c>
-      <c r="C10">
-        <v>99</v>
-      </c>
-      <c r="D10">
-        <v>65</v>
-      </c>
-      <c r="E10">
-        <v>130</v>
-      </c>
-      <c r="F10">
-        <v>167</v>
-      </c>
-      <c r="G10">
-        <v>92</v>
-      </c>
-      <c r="H10">
-        <v>104</v>
-      </c>
-      <c r="I10">
-        <v>89</v>
-      </c>
-      <c r="J10">
-        <v>67</v>
-      </c>
-      <c r="K10">
-        <v>71</v>
-      </c>
-      <c r="L10">
-        <v>61</v>
-      </c>
-      <c r="M10">
-        <v>53</v>
       </c>
     </row>
   </sheetData>
@@ -14340,73 +14177,82 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
+      <c r="B2">
+        <v>4</v>
+      </c>
       <c r="C2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D2">
         <v>3</v>
       </c>
       <c r="E2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F2">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="G2">
-        <v>6</v>
+        <v>3</v>
+      </c>
+      <c r="H2">
+        <v>5</v>
       </c>
       <c r="I2">
         <v>4</v>
       </c>
       <c r="J2">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="K2">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M2">
-        <v>1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
+      <c r="B3">
+        <v>4</v>
+      </c>
       <c r="C3">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D3">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E3">
+        <v>7</v>
+      </c>
+      <c r="F3">
+        <v>6</v>
+      </c>
+      <c r="G3">
+        <v>7</v>
+      </c>
+      <c r="H3">
         <v>8</v>
       </c>
-      <c r="F3">
-        <v>1</v>
-      </c>
-      <c r="G3">
-        <v>5</v>
-      </c>
-      <c r="H3">
-        <v>3</v>
-      </c>
       <c r="I3">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J3">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="K3">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="L3">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="M3">
-        <v>2</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -14421,23 +14267,20 @@
       <c r="A5" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F5">
-        <v>2</v>
-      </c>
-      <c r="G5">
-        <v>1</v>
-      </c>
-      <c r="H5">
-        <v>1</v>
-      </c>
-      <c r="I5">
-        <v>2</v>
+      <c r="B5">
+        <v>1</v>
+      </c>
+      <c r="D5">
+        <v>1</v>
+      </c>
+      <c r="E5">
+        <v>1</v>
+      </c>
+      <c r="J5">
+        <v>3</v>
       </c>
       <c r="K5">
-        <v>3</v>
-      </c>
-      <c r="L5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M5">
         <v>2</v>
@@ -14447,7 +14290,7 @@
       <c r="A6" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="F6">
+      <c r="K6">
         <v>1</v>
       </c>
     </row>
@@ -14455,7 +14298,7 @@
       <c r="A7" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I7">
+      <c r="L7">
         <v>1</v>
       </c>
     </row>
@@ -14464,40 +14307,40 @@
         <v>8</v>
       </c>
       <c r="B8">
-        <v>3</v>
+        <v>23</v>
       </c>
       <c r="C8">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="D8">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="E8">
-        <v>10</v>
+        <v>44</v>
       </c>
       <c r="F8">
-        <v>15</v>
+        <v>38</v>
       </c>
       <c r="G8">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="H8">
-        <v>14</v>
+        <v>50</v>
       </c>
       <c r="I8">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="J8">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="K8">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="L8">
         <v>14</v>
       </c>
       <c r="M8">
-        <v>4</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -14505,40 +14348,40 @@
         <v>9</v>
       </c>
       <c r="B9">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="C9">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="D9">
-        <v>54</v>
+        <v>33</v>
       </c>
       <c r="E9">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="F9">
-        <v>50</v>
+        <v>114</v>
       </c>
       <c r="G9">
-        <v>32</v>
+        <v>58</v>
       </c>
       <c r="H9">
-        <v>21</v>
+        <v>41</v>
       </c>
       <c r="I9">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="J9">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="K9">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="L9">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="M9">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -14546,40 +14389,40 @@
         <v>10</v>
       </c>
       <c r="B10">
-        <v>59</v>
+        <v>78</v>
       </c>
       <c r="C10">
-        <v>76</v>
+        <v>99</v>
       </c>
       <c r="D10">
+        <v>65</v>
+      </c>
+      <c r="E10">
+        <v>130</v>
+      </c>
+      <c r="F10">
+        <v>167</v>
+      </c>
+      <c r="G10">
+        <v>92</v>
+      </c>
+      <c r="H10">
+        <v>104</v>
+      </c>
+      <c r="I10">
+        <v>89</v>
+      </c>
+      <c r="J10">
+        <v>67</v>
+      </c>
+      <c r="K10">
         <v>71</v>
       </c>
-      <c r="E10">
-        <v>101</v>
-      </c>
-      <c r="F10">
-        <v>70</v>
-      </c>
-      <c r="G10">
+      <c r="L10">
+        <v>61</v>
+      </c>
+      <c r="M10">
         <v>53</v>
-      </c>
-      <c r="H10">
-        <v>39</v>
-      </c>
-      <c r="I10">
-        <v>49</v>
-      </c>
-      <c r="J10">
-        <v>47</v>
-      </c>
-      <c r="K10">
-        <v>54</v>
-      </c>
-      <c r="L10">
-        <v>59</v>
-      </c>
-      <c r="M10">
-        <v>24</v>
       </c>
     </row>
   </sheetData>
@@ -14589,7 +14432,7 @@
 
 <file path=xl/worksheets/sheet44.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M7"/>
+  <dimension ref="A1:M10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="23.7109375" customWidth="1"/>
@@ -14653,19 +14496,31 @@
         <v>1</v>
       </c>
       <c r="C2">
-        <v>2</v>
+        <v>3</v>
+      </c>
+      <c r="D2">
+        <v>3</v>
+      </c>
+      <c r="E2">
+        <v>3</v>
       </c>
       <c r="F2">
         <v>1</v>
       </c>
+      <c r="G2">
+        <v>6</v>
+      </c>
       <c r="I2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J2">
         <v>1</v>
       </c>
       <c r="K2">
-        <v>1</v>
+        <v>5</v>
+      </c>
+      <c r="L2">
+        <v>3</v>
       </c>
       <c r="M2">
         <v>1</v>
@@ -14678,136 +14533,208 @@
       <c r="C3">
         <v>1</v>
       </c>
+      <c r="D3">
+        <v>3</v>
+      </c>
       <c r="E3">
-        <v>1</v>
+        <v>8</v>
+      </c>
+      <c r="F3">
+        <v>1</v>
+      </c>
+      <c r="G3">
+        <v>5</v>
       </c>
       <c r="H3">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="I3">
+        <v>4</v>
       </c>
       <c r="J3">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="K3">
+        <v>8</v>
       </c>
       <c r="L3">
-        <v>1</v>
+        <v>5</v>
+      </c>
+      <c r="M3">
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="L4">
+        <v>3</v>
+      </c>
+      <c r="I4">
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5">
-        <v>1</v>
-      </c>
-      <c r="C5">
-        <v>1</v>
-      </c>
-      <c r="D5">
-        <v>3</v>
-      </c>
-      <c r="E5">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G5">
         <v>1</v>
       </c>
+      <c r="H5">
+        <v>1</v>
+      </c>
+      <c r="I5">
+        <v>2</v>
+      </c>
       <c r="K5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L5">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="M5">
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B6">
         <v>6</v>
       </c>
-      <c r="C6">
-        <v>9</v>
-      </c>
-      <c r="D6">
-        <v>6</v>
-      </c>
-      <c r="E6">
-        <v>7</v>
-      </c>
       <c r="F6">
-        <v>9</v>
-      </c>
-      <c r="G6">
-        <v>3</v>
-      </c>
-      <c r="H6">
-        <v>2</v>
-      </c>
-      <c r="I6">
-        <v>1</v>
-      </c>
-      <c r="J6">
-        <v>3</v>
-      </c>
-      <c r="K6">
-        <v>5</v>
-      </c>
-      <c r="L6">
-        <v>4</v>
-      </c>
-      <c r="M6">
         <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13">
+      <c r="A8" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8">
+        <v>3</v>
+      </c>
+      <c r="C8">
+        <v>11</v>
+      </c>
+      <c r="D8">
+        <v>11</v>
+      </c>
+      <c r="E8">
         <v>10</v>
       </c>
-      <c r="B7">
-        <v>7</v>
-      </c>
-      <c r="C7">
+      <c r="F8">
+        <v>15</v>
+      </c>
+      <c r="G8">
+        <v>9</v>
+      </c>
+      <c r="H8">
+        <v>14</v>
+      </c>
+      <c r="I8">
         <v>13</v>
       </c>
-      <c r="D7">
+      <c r="J8">
+        <v>13</v>
+      </c>
+      <c r="K8">
+        <v>14</v>
+      </c>
+      <c r="L8">
+        <v>14</v>
+      </c>
+      <c r="M8">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13">
+      <c r="A9" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="E7">
-        <v>9</v>
-      </c>
-      <c r="F7">
-        <v>11</v>
-      </c>
-      <c r="G7">
-        <v>4</v>
-      </c>
-      <c r="H7">
-        <v>3</v>
-      </c>
-      <c r="I7">
-        <v>2</v>
-      </c>
-      <c r="J7">
-        <v>5</v>
-      </c>
-      <c r="K7">
+      <c r="B9">
+        <v>56</v>
+      </c>
+      <c r="C9">
+        <v>61</v>
+      </c>
+      <c r="D9">
+        <v>54</v>
+      </c>
+      <c r="E9">
+        <v>80</v>
+      </c>
+      <c r="F9">
+        <v>50</v>
+      </c>
+      <c r="G9">
+        <v>32</v>
+      </c>
+      <c r="H9">
+        <v>21</v>
+      </c>
+      <c r="I9">
+        <v>24</v>
+      </c>
+      <c r="J9">
+        <v>30</v>
+      </c>
+      <c r="K9">
+        <v>24</v>
+      </c>
+      <c r="L9">
+        <v>34</v>
+      </c>
+      <c r="M9">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13">
+      <c r="A10" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L7">
-        <v>7</v>
-      </c>
-      <c r="M7">
-        <v>2</v>
+      <c r="B10">
+        <v>59</v>
+      </c>
+      <c r="C10">
+        <v>76</v>
+      </c>
+      <c r="D10">
+        <v>71</v>
+      </c>
+      <c r="E10">
+        <v>101</v>
+      </c>
+      <c r="F10">
+        <v>70</v>
+      </c>
+      <c r="G10">
+        <v>53</v>
+      </c>
+      <c r="H10">
+        <v>39</v>
+      </c>
+      <c r="I10">
+        <v>49</v>
+      </c>
+      <c r="J10">
+        <v>47</v>
+      </c>
+      <c r="K10">
+        <v>54</v>
+      </c>
+      <c r="L10">
+        <v>59</v>
+      </c>
+      <c r="M10">
+        <v>24</v>
       </c>
     </row>
   </sheetData>
@@ -14881,31 +14808,19 @@
         <v>1</v>
       </c>
       <c r="C2">
-        <v>1</v>
-      </c>
-      <c r="D2">
-        <v>1</v>
-      </c>
-      <c r="E2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F2">
-        <v>2</v>
-      </c>
-      <c r="H2">
         <v>1</v>
       </c>
       <c r="I2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K2">
-        <v>2</v>
-      </c>
-      <c r="L2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M2">
         <v>1</v>
@@ -14915,34 +14830,19 @@
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B3">
-        <v>1</v>
-      </c>
       <c r="C3">
         <v>1</v>
       </c>
-      <c r="D3">
-        <v>1</v>
-      </c>
       <c r="E3">
         <v>1</v>
       </c>
-      <c r="G3">
-        <v>2</v>
-      </c>
       <c r="H3">
         <v>1</v>
       </c>
-      <c r="I3">
-        <v>2</v>
-      </c>
-      <c r="K3">
-        <v>2</v>
+      <c r="J3">
+        <v>1</v>
       </c>
       <c r="L3">
-        <v>3</v>
-      </c>
-      <c r="M3">
         <v>1</v>
       </c>
     </row>
@@ -14950,7 +14850,7 @@
       <c r="A4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C4">
+      <c r="L4">
         <v>1</v>
       </c>
     </row>
@@ -14962,10 +14862,10 @@
         <v>1</v>
       </c>
       <c r="C5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D5">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E5">
         <v>1</v>
@@ -14974,24 +14874,12 @@
         <v>1</v>
       </c>
       <c r="G5">
-        <v>2</v>
-      </c>
-      <c r="H5">
-        <v>3</v>
-      </c>
-      <c r="I5">
-        <v>2</v>
-      </c>
-      <c r="J5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L5">
-        <v>1</v>
-      </c>
-      <c r="M5">
         <v>1</v>
       </c>
     </row>
@@ -15000,40 +14888,40 @@
         <v>9</v>
       </c>
       <c r="B6">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="C6">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D6">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="E6">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="F6">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="G6">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="H6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I6">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="J6">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="K6">
         <v>5</v>
       </c>
       <c r="L6">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="M6">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -15041,40 +14929,40 @@
         <v>10</v>
       </c>
       <c r="B7">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C7">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="D7">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="E7">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="F7">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="G7">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="H7">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="I7">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="J7">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="K7">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="L7">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="M7">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -15151,13 +15039,16 @@
         <v>1</v>
       </c>
       <c r="D2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E2">
         <v>1</v>
       </c>
       <c r="F2">
-        <v>3</v>
+        <v>2</v>
+      </c>
+      <c r="H2">
+        <v>1</v>
       </c>
       <c r="I2">
         <v>2</v>
@@ -15166,10 +15057,10 @@
         <v>4</v>
       </c>
       <c r="K2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M2">
         <v>1</v>
@@ -15189,38 +15080,32 @@
         <v>1</v>
       </c>
       <c r="E3">
-        <v>6</v>
-      </c>
-      <c r="F3">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="G3">
+        <v>2</v>
       </c>
       <c r="H3">
         <v>1</v>
       </c>
       <c r="I3">
-        <v>1</v>
-      </c>
-      <c r="J3">
         <v>2</v>
       </c>
       <c r="K3">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L3">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="M3">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="I4">
-        <v>1</v>
-      </c>
-      <c r="M4">
+      <c r="C4">
         <v>1</v>
       </c>
     </row>
@@ -15229,40 +15114,40 @@
         <v>8</v>
       </c>
       <c r="B5">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C5">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E5">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F5">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="G5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H5">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="I5">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="J5">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="K5">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="L5">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="M5">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -15270,40 +15155,40 @@
         <v>9</v>
       </c>
       <c r="B6">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="C6">
+        <v>12</v>
+      </c>
+      <c r="D6">
         <v>14</v>
       </c>
-      <c r="D6">
-        <v>13</v>
-      </c>
       <c r="E6">
+        <v>14</v>
+      </c>
+      <c r="F6">
+        <v>15</v>
+      </c>
+      <c r="G6">
+        <v>9</v>
+      </c>
+      <c r="H6">
+        <v>3</v>
+      </c>
+      <c r="I6">
+        <v>6</v>
+      </c>
+      <c r="J6">
+        <v>7</v>
+      </c>
+      <c r="K6">
+        <v>5</v>
+      </c>
+      <c r="L6">
         <v>11</v>
       </c>
-      <c r="F6">
-        <v>28</v>
-      </c>
-      <c r="G6">
-        <v>11</v>
-      </c>
-      <c r="H6">
-        <v>8</v>
-      </c>
-      <c r="I6">
-        <v>12</v>
-      </c>
-      <c r="J6">
-        <v>6</v>
-      </c>
-      <c r="K6">
-        <v>9</v>
-      </c>
-      <c r="L6">
-        <v>12</v>
-      </c>
       <c r="M6">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -15311,40 +15196,40 @@
         <v>10</v>
       </c>
       <c r="B7">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="C7">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="D7">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E7">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="F7">
-        <v>47</v>
+        <v>18</v>
       </c>
       <c r="G7">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="H7">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="I7">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="J7">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="K7">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="L7">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="M7">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -15353,6 +15238,276 @@
 </file>
 
 <file path=xl/worksheets/sheet47.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:M7"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+    <col min="13" max="13" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="M1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>2</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
+      <c r="F2">
+        <v>3</v>
+      </c>
+      <c r="I2">
+        <v>2</v>
+      </c>
+      <c r="J2">
+        <v>4</v>
+      </c>
+      <c r="K2">
+        <v>1</v>
+      </c>
+      <c r="L2">
+        <v>3</v>
+      </c>
+      <c r="M2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>1</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
+      <c r="E3">
+        <v>6</v>
+      </c>
+      <c r="F3">
+        <v>1</v>
+      </c>
+      <c r="H3">
+        <v>1</v>
+      </c>
+      <c r="I3">
+        <v>1</v>
+      </c>
+      <c r="J3">
+        <v>2</v>
+      </c>
+      <c r="K3">
+        <v>4</v>
+      </c>
+      <c r="L3">
+        <v>6</v>
+      </c>
+      <c r="M3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="I4">
+        <v>1</v>
+      </c>
+      <c r="M4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5">
+        <v>5</v>
+      </c>
+      <c r="C5">
+        <v>6</v>
+      </c>
+      <c r="D5">
+        <v>4</v>
+      </c>
+      <c r="E5">
+        <v>5</v>
+      </c>
+      <c r="F5">
+        <v>15</v>
+      </c>
+      <c r="G5">
+        <v>4</v>
+      </c>
+      <c r="H5">
+        <v>7</v>
+      </c>
+      <c r="I5">
+        <v>11</v>
+      </c>
+      <c r="J5">
+        <v>15</v>
+      </c>
+      <c r="K5">
+        <v>11</v>
+      </c>
+      <c r="L5">
+        <v>19</v>
+      </c>
+      <c r="M5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6">
+        <v>21</v>
+      </c>
+      <c r="C6">
+        <v>14</v>
+      </c>
+      <c r="D6">
+        <v>13</v>
+      </c>
+      <c r="E6">
+        <v>11</v>
+      </c>
+      <c r="F6">
+        <v>28</v>
+      </c>
+      <c r="G6">
+        <v>11</v>
+      </c>
+      <c r="H6">
+        <v>8</v>
+      </c>
+      <c r="I6">
+        <v>12</v>
+      </c>
+      <c r="J6">
+        <v>6</v>
+      </c>
+      <c r="K6">
+        <v>9</v>
+      </c>
+      <c r="L6">
+        <v>12</v>
+      </c>
+      <c r="M6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7">
+        <v>27</v>
+      </c>
+      <c r="C7">
+        <v>22</v>
+      </c>
+      <c r="D7">
+        <v>20</v>
+      </c>
+      <c r="E7">
+        <v>23</v>
+      </c>
+      <c r="F7">
+        <v>47</v>
+      </c>
+      <c r="G7">
+        <v>15</v>
+      </c>
+      <c r="H7">
+        <v>16</v>
+      </c>
+      <c r="I7">
+        <v>27</v>
+      </c>
+      <c r="J7">
+        <v>27</v>
+      </c>
+      <c r="K7">
+        <v>25</v>
+      </c>
+      <c r="L7">
+        <v>40</v>
+      </c>
+      <c r="M7">
+        <v>10</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet48.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M9"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -15644,7 +15799,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet48.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet49.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -15836,264 +15991,6 @@
       </c>
       <c r="M6">
         <v>2</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet49.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M7"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" customWidth="1"/>
-    <col min="13" max="13" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="M1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2">
-        <v>3</v>
-      </c>
-      <c r="E2">
-        <v>2</v>
-      </c>
-      <c r="F2">
-        <v>1</v>
-      </c>
-      <c r="G2">
-        <v>2</v>
-      </c>
-      <c r="I2">
-        <v>2</v>
-      </c>
-      <c r="L2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3">
-        <v>2</v>
-      </c>
-      <c r="C3">
-        <v>1</v>
-      </c>
-      <c r="D3">
-        <v>5</v>
-      </c>
-      <c r="F3">
-        <v>2</v>
-      </c>
-      <c r="G3">
-        <v>3</v>
-      </c>
-      <c r="H3">
-        <v>3</v>
-      </c>
-      <c r="I3">
-        <v>5</v>
-      </c>
-      <c r="J3">
-        <v>5</v>
-      </c>
-      <c r="K3">
-        <v>5</v>
-      </c>
-      <c r="M3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="F4">
-        <v>1</v>
-      </c>
-      <c r="H4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5">
-        <v>11</v>
-      </c>
-      <c r="C5">
-        <v>12</v>
-      </c>
-      <c r="D5">
-        <v>5</v>
-      </c>
-      <c r="E5">
-        <v>9</v>
-      </c>
-      <c r="F5">
-        <v>3</v>
-      </c>
-      <c r="G5">
-        <v>2</v>
-      </c>
-      <c r="H5">
-        <v>4</v>
-      </c>
-      <c r="I5">
-        <v>4</v>
-      </c>
-      <c r="J5">
-        <v>6</v>
-      </c>
-      <c r="K5">
-        <v>7</v>
-      </c>
-      <c r="L5">
-        <v>4</v>
-      </c>
-      <c r="M5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B6">
-        <v>17</v>
-      </c>
-      <c r="C6">
-        <v>10</v>
-      </c>
-      <c r="D6">
-        <v>17</v>
-      </c>
-      <c r="E6">
-        <v>14</v>
-      </c>
-      <c r="F6">
-        <v>15</v>
-      </c>
-      <c r="G6">
-        <v>6</v>
-      </c>
-      <c r="H6">
-        <v>3</v>
-      </c>
-      <c r="I6">
-        <v>6</v>
-      </c>
-      <c r="J6">
-        <v>8</v>
-      </c>
-      <c r="K6">
-        <v>3</v>
-      </c>
-      <c r="L6">
-        <v>1</v>
-      </c>
-      <c r="M6">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
-      <c r="A7" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B7">
-        <v>33</v>
-      </c>
-      <c r="C7">
-        <v>23</v>
-      </c>
-      <c r="D7">
-        <v>27</v>
-      </c>
-      <c r="E7">
-        <v>25</v>
-      </c>
-      <c r="F7">
-        <v>22</v>
-      </c>
-      <c r="G7">
-        <v>13</v>
-      </c>
-      <c r="H7">
-        <v>11</v>
-      </c>
-      <c r="I7">
-        <v>17</v>
-      </c>
-      <c r="J7">
-        <v>19</v>
-      </c>
-      <c r="K7">
-        <v>15</v>
-      </c>
-      <c r="L7">
-        <v>6</v>
-      </c>
-      <c r="M7">
-        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -16395,6 +16292,264 @@
 
 <file path=xl/worksheets/sheet50.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:M7"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+    <col min="13" max="13" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="M1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>3</v>
+      </c>
+      <c r="E2">
+        <v>2</v>
+      </c>
+      <c r="F2">
+        <v>1</v>
+      </c>
+      <c r="G2">
+        <v>2</v>
+      </c>
+      <c r="I2">
+        <v>2</v>
+      </c>
+      <c r="L2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>2</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
+      <c r="D3">
+        <v>5</v>
+      </c>
+      <c r="F3">
+        <v>2</v>
+      </c>
+      <c r="G3">
+        <v>3</v>
+      </c>
+      <c r="H3">
+        <v>3</v>
+      </c>
+      <c r="I3">
+        <v>5</v>
+      </c>
+      <c r="J3">
+        <v>5</v>
+      </c>
+      <c r="K3">
+        <v>5</v>
+      </c>
+      <c r="M3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F4">
+        <v>1</v>
+      </c>
+      <c r="H4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5">
+        <v>11</v>
+      </c>
+      <c r="C5">
+        <v>12</v>
+      </c>
+      <c r="D5">
+        <v>5</v>
+      </c>
+      <c r="E5">
+        <v>9</v>
+      </c>
+      <c r="F5">
+        <v>3</v>
+      </c>
+      <c r="G5">
+        <v>2</v>
+      </c>
+      <c r="H5">
+        <v>4</v>
+      </c>
+      <c r="I5">
+        <v>4</v>
+      </c>
+      <c r="J5">
+        <v>6</v>
+      </c>
+      <c r="K5">
+        <v>7</v>
+      </c>
+      <c r="L5">
+        <v>4</v>
+      </c>
+      <c r="M5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6">
+        <v>17</v>
+      </c>
+      <c r="C6">
+        <v>10</v>
+      </c>
+      <c r="D6">
+        <v>17</v>
+      </c>
+      <c r="E6">
+        <v>14</v>
+      </c>
+      <c r="F6">
+        <v>15</v>
+      </c>
+      <c r="G6">
+        <v>6</v>
+      </c>
+      <c r="H6">
+        <v>3</v>
+      </c>
+      <c r="I6">
+        <v>6</v>
+      </c>
+      <c r="J6">
+        <v>8</v>
+      </c>
+      <c r="K6">
+        <v>3</v>
+      </c>
+      <c r="L6">
+        <v>1</v>
+      </c>
+      <c r="M6">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7">
+        <v>33</v>
+      </c>
+      <c r="C7">
+        <v>23</v>
+      </c>
+      <c r="D7">
+        <v>27</v>
+      </c>
+      <c r="E7">
+        <v>25</v>
+      </c>
+      <c r="F7">
+        <v>22</v>
+      </c>
+      <c r="G7">
+        <v>13</v>
+      </c>
+      <c r="H7">
+        <v>11</v>
+      </c>
+      <c r="I7">
+        <v>17</v>
+      </c>
+      <c r="J7">
+        <v>19</v>
+      </c>
+      <c r="K7">
+        <v>15</v>
+      </c>
+      <c r="L7">
+        <v>6</v>
+      </c>
+      <c r="M7">
+        <v>10</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet51.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -16647,7 +16802,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet51.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet52.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M9"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -16924,7 +17079,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet52.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet53.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -17113,264 +17268,6 @@
       </c>
       <c r="M6">
         <v>1</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet53.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M7"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" customWidth="1"/>
-    <col min="13" max="13" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="M1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D2">
-        <v>1</v>
-      </c>
-      <c r="G2">
-        <v>4</v>
-      </c>
-      <c r="H2">
-        <v>2</v>
-      </c>
-      <c r="I2">
-        <v>1</v>
-      </c>
-      <c r="L2">
-        <v>1</v>
-      </c>
-      <c r="M2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3">
-        <v>2</v>
-      </c>
-      <c r="C3">
-        <v>1</v>
-      </c>
-      <c r="D3">
-        <v>4</v>
-      </c>
-      <c r="E3">
-        <v>1</v>
-      </c>
-      <c r="F3">
-        <v>4</v>
-      </c>
-      <c r="G3">
-        <v>3</v>
-      </c>
-      <c r="H3">
-        <v>1</v>
-      </c>
-      <c r="I3">
-        <v>4</v>
-      </c>
-      <c r="J3">
-        <v>3</v>
-      </c>
-      <c r="K3">
-        <v>1</v>
-      </c>
-      <c r="L3">
-        <v>2</v>
-      </c>
-      <c r="M3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5">
-        <v>11</v>
-      </c>
-      <c r="C5">
-        <v>4</v>
-      </c>
-      <c r="D5">
-        <v>11</v>
-      </c>
-      <c r="E5">
-        <v>4</v>
-      </c>
-      <c r="F5">
-        <v>4</v>
-      </c>
-      <c r="G5">
-        <v>6</v>
-      </c>
-      <c r="H5">
-        <v>3</v>
-      </c>
-      <c r="I5">
-        <v>1</v>
-      </c>
-      <c r="J5">
-        <v>2</v>
-      </c>
-      <c r="K5">
-        <v>2</v>
-      </c>
-      <c r="L5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B6">
-        <v>9</v>
-      </c>
-      <c r="C6">
-        <v>18</v>
-      </c>
-      <c r="D6">
-        <v>9</v>
-      </c>
-      <c r="E6">
-        <v>6</v>
-      </c>
-      <c r="F6">
-        <v>7</v>
-      </c>
-      <c r="G6">
-        <v>4</v>
-      </c>
-      <c r="H6">
-        <v>1</v>
-      </c>
-      <c r="I6">
-        <v>7</v>
-      </c>
-      <c r="J6">
-        <v>3</v>
-      </c>
-      <c r="K6">
-        <v>3</v>
-      </c>
-      <c r="L6">
-        <v>3</v>
-      </c>
-      <c r="M6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
-      <c r="A7" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B7">
-        <v>23</v>
-      </c>
-      <c r="C7">
-        <v>23</v>
-      </c>
-      <c r="D7">
-        <v>25</v>
-      </c>
-      <c r="E7">
-        <v>11</v>
-      </c>
-      <c r="F7">
-        <v>15</v>
-      </c>
-      <c r="G7">
-        <v>17</v>
-      </c>
-      <c r="H7">
-        <v>7</v>
-      </c>
-      <c r="I7">
-        <v>13</v>
-      </c>
-      <c r="J7">
-        <v>8</v>
-      </c>
-      <c r="K7">
-        <v>6</v>
-      </c>
-      <c r="L7">
-        <v>7</v>
-      </c>
-      <c r="M7">
-        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -17443,46 +17340,64 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2">
-        <v>1</v>
-      </c>
-      <c r="C2">
-        <v>2</v>
-      </c>
       <c r="D2">
         <v>1</v>
       </c>
       <c r="G2">
-        <v>1</v>
-      </c>
-      <c r="J2">
+        <v>4</v>
+      </c>
+      <c r="H2">
+        <v>2</v>
+      </c>
+      <c r="I2">
+        <v>1</v>
+      </c>
+      <c r="L2">
         <v>1</v>
       </c>
       <c r="M2">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
+      <c r="B3">
+        <v>2</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
+      <c r="D3">
+        <v>4</v>
+      </c>
+      <c r="E3">
+        <v>1</v>
+      </c>
       <c r="F3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H3">
         <v>1</v>
       </c>
+      <c r="I3">
+        <v>4</v>
+      </c>
       <c r="J3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K3">
         <v>1</v>
       </c>
       <c r="L3">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="M3">
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -17498,63 +17413,78 @@
         <v>8</v>
       </c>
       <c r="B5">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="C5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D5">
-        <v>3</v>
+        <v>11</v>
+      </c>
+      <c r="E5">
+        <v>4</v>
       </c>
       <c r="F5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G5">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H5">
-        <v>4</v>
+        <v>3</v>
+      </c>
+      <c r="I5">
+        <v>1</v>
       </c>
       <c r="J5">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="K5">
+        <v>2</v>
       </c>
       <c r="L5">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
         <v>9</v>
       </c>
+      <c r="B6">
+        <v>9</v>
+      </c>
       <c r="C6">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="D6">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="E6">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F6">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="G6">
-        <v>2</v>
+        <v>4</v>
+      </c>
+      <c r="H6">
+        <v>1</v>
       </c>
       <c r="I6">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="J6">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K6">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L6">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M6">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -17562,40 +17492,40 @@
         <v>10</v>
       </c>
       <c r="B7">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="C7">
+        <v>23</v>
+      </c>
+      <c r="D7">
+        <v>25</v>
+      </c>
+      <c r="E7">
+        <v>11</v>
+      </c>
+      <c r="F7">
+        <v>15</v>
+      </c>
+      <c r="G7">
+        <v>17</v>
+      </c>
+      <c r="H7">
         <v>7</v>
       </c>
-      <c r="D7">
+      <c r="I7">
+        <v>13</v>
+      </c>
+      <c r="J7">
+        <v>8</v>
+      </c>
+      <c r="K7">
         <v>6</v>
-      </c>
-      <c r="E7">
-        <v>3</v>
-      </c>
-      <c r="F7">
-        <v>6</v>
-      </c>
-      <c r="G7">
-        <v>5</v>
-      </c>
-      <c r="H7">
-        <v>5</v>
-      </c>
-      <c r="I7">
-        <v>1</v>
-      </c>
-      <c r="J7">
-        <v>4</v>
-      </c>
-      <c r="K7">
-        <v>2</v>
       </c>
       <c r="L7">
         <v>7</v>
       </c>
       <c r="M7">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -17604,6 +17534,231 @@
 </file>
 
 <file path=xl/worksheets/sheet55.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:M7"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+    <col min="13" max="13" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="M1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>2</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="G2">
+        <v>1</v>
+      </c>
+      <c r="J2">
+        <v>1</v>
+      </c>
+      <c r="M2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F3">
+        <v>3</v>
+      </c>
+      <c r="G3">
+        <v>1</v>
+      </c>
+      <c r="H3">
+        <v>1</v>
+      </c>
+      <c r="J3">
+        <v>1</v>
+      </c>
+      <c r="K3">
+        <v>1</v>
+      </c>
+      <c r="L3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5">
+        <v>3</v>
+      </c>
+      <c r="C5">
+        <v>2</v>
+      </c>
+      <c r="D5">
+        <v>3</v>
+      </c>
+      <c r="F5">
+        <v>1</v>
+      </c>
+      <c r="G5">
+        <v>1</v>
+      </c>
+      <c r="H5">
+        <v>4</v>
+      </c>
+      <c r="J5">
+        <v>1</v>
+      </c>
+      <c r="L5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C6">
+        <v>3</v>
+      </c>
+      <c r="D6">
+        <v>2</v>
+      </c>
+      <c r="E6">
+        <v>3</v>
+      </c>
+      <c r="F6">
+        <v>2</v>
+      </c>
+      <c r="G6">
+        <v>2</v>
+      </c>
+      <c r="I6">
+        <v>1</v>
+      </c>
+      <c r="J6">
+        <v>1</v>
+      </c>
+      <c r="K6">
+        <v>1</v>
+      </c>
+      <c r="L6">
+        <v>4</v>
+      </c>
+      <c r="M6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7">
+        <v>5</v>
+      </c>
+      <c r="C7">
+        <v>7</v>
+      </c>
+      <c r="D7">
+        <v>6</v>
+      </c>
+      <c r="E7">
+        <v>3</v>
+      </c>
+      <c r="F7">
+        <v>6</v>
+      </c>
+      <c r="G7">
+        <v>5</v>
+      </c>
+      <c r="H7">
+        <v>5</v>
+      </c>
+      <c r="I7">
+        <v>1</v>
+      </c>
+      <c r="J7">
+        <v>4</v>
+      </c>
+      <c r="K7">
+        <v>2</v>
+      </c>
+      <c r="L7">
+        <v>7</v>
+      </c>
+      <c r="M7">
+        <v>2</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet56.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M9"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -17883,7 +18038,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet56.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet57.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:L8"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -18109,7 +18264,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet57.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet58.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:G5"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -18219,7 +18374,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet58.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet59.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M8"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -18478,246 +18633,6 @@
       </c>
       <c r="M8">
         <v>12</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet59.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M7"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" customWidth="1"/>
-    <col min="13" max="13" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="M1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D2">
-        <v>1</v>
-      </c>
-      <c r="E2">
-        <v>1</v>
-      </c>
-      <c r="H2">
-        <v>1</v>
-      </c>
-      <c r="J2">
-        <v>3</v>
-      </c>
-      <c r="K2">
-        <v>1</v>
-      </c>
-      <c r="L2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="F3">
-        <v>1</v>
-      </c>
-      <c r="G3">
-        <v>1</v>
-      </c>
-      <c r="H3">
-        <v>2</v>
-      </c>
-      <c r="I3">
-        <v>1</v>
-      </c>
-      <c r="J3">
-        <v>1</v>
-      </c>
-      <c r="K3">
-        <v>2</v>
-      </c>
-      <c r="L3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5">
-        <v>1</v>
-      </c>
-      <c r="C5">
-        <v>3</v>
-      </c>
-      <c r="D5">
-        <v>1</v>
-      </c>
-      <c r="E5">
-        <v>6</v>
-      </c>
-      <c r="F5">
-        <v>2</v>
-      </c>
-      <c r="G5">
-        <v>1</v>
-      </c>
-      <c r="H5">
-        <v>2</v>
-      </c>
-      <c r="I5">
-        <v>2</v>
-      </c>
-      <c r="J5">
-        <v>3</v>
-      </c>
-      <c r="M5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B6">
-        <v>13</v>
-      </c>
-      <c r="C6">
-        <v>15</v>
-      </c>
-      <c r="D6">
-        <v>13</v>
-      </c>
-      <c r="E6">
-        <v>9</v>
-      </c>
-      <c r="F6">
-        <v>14</v>
-      </c>
-      <c r="G6">
-        <v>6</v>
-      </c>
-      <c r="H6">
-        <v>2</v>
-      </c>
-      <c r="I6">
-        <v>9</v>
-      </c>
-      <c r="J6">
-        <v>3</v>
-      </c>
-      <c r="K6">
-        <v>3</v>
-      </c>
-      <c r="L6">
-        <v>4</v>
-      </c>
-      <c r="M6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
-      <c r="A7" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B7">
-        <v>15</v>
-      </c>
-      <c r="C7">
-        <v>18</v>
-      </c>
-      <c r="D7">
-        <v>15</v>
-      </c>
-      <c r="E7">
-        <v>16</v>
-      </c>
-      <c r="F7">
-        <v>17</v>
-      </c>
-      <c r="G7">
-        <v>8</v>
-      </c>
-      <c r="H7">
-        <v>7</v>
-      </c>
-      <c r="I7">
-        <v>12</v>
-      </c>
-      <c r="J7">
-        <v>10</v>
-      </c>
-      <c r="K7">
-        <v>6</v>
-      </c>
-      <c r="L7">
-        <v>8</v>
-      </c>
-      <c r="M7">
-        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -19005,183 +18920,6 @@
 
 <file path=xl/worksheets/sheet60.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L6"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="18.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:12">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="F2">
-        <v>1</v>
-      </c>
-      <c r="I2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C3">
-        <v>1</v>
-      </c>
-      <c r="D3">
-        <v>3</v>
-      </c>
-      <c r="E3">
-        <v>1</v>
-      </c>
-      <c r="G3">
-        <v>1</v>
-      </c>
-      <c r="H3">
-        <v>1</v>
-      </c>
-      <c r="L3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12">
-      <c r="A4" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4">
-        <v>4</v>
-      </c>
-      <c r="D4">
-        <v>2</v>
-      </c>
-      <c r="E4">
-        <v>2</v>
-      </c>
-      <c r="G4">
-        <v>2</v>
-      </c>
-      <c r="H4">
-        <v>1</v>
-      </c>
-      <c r="I4">
-        <v>3</v>
-      </c>
-      <c r="J4">
-        <v>3</v>
-      </c>
-      <c r="K4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12">
-      <c r="A5" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F5">
-        <v>2</v>
-      </c>
-      <c r="I5">
-        <v>3</v>
-      </c>
-      <c r="K5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12">
-      <c r="A6" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B6">
-        <v>4</v>
-      </c>
-      <c r="C6">
-        <v>1</v>
-      </c>
-      <c r="D6">
-        <v>5</v>
-      </c>
-      <c r="E6">
-        <v>3</v>
-      </c>
-      <c r="F6">
-        <v>3</v>
-      </c>
-      <c r="G6">
-        <v>3</v>
-      </c>
-      <c r="H6">
-        <v>2</v>
-      </c>
-      <c r="I6">
-        <v>7</v>
-      </c>
-      <c r="J6">
-        <v>3</v>
-      </c>
-      <c r="K6">
-        <v>2</v>
-      </c>
-      <c r="L6">
-        <v>1</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet61.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -19245,26 +18983,56 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="F2">
-        <v>1</v>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
+      <c r="H2">
+        <v>1</v>
+      </c>
+      <c r="J2">
+        <v>3</v>
+      </c>
+      <c r="K2">
+        <v>1</v>
+      </c>
+      <c r="L2">
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
+      <c r="F3">
+        <v>1</v>
+      </c>
+      <c r="G3">
+        <v>1</v>
+      </c>
+      <c r="H3">
+        <v>2</v>
+      </c>
+      <c r="I3">
+        <v>1</v>
+      </c>
+      <c r="J3">
+        <v>1</v>
+      </c>
       <c r="K3">
         <v>2</v>
       </c>
       <c r="L3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="I4">
+      <c r="B4">
         <v>1</v>
       </c>
     </row>
@@ -19276,25 +19044,31 @@
         <v>1</v>
       </c>
       <c r="C5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D5">
         <v>1</v>
       </c>
+      <c r="E5">
+        <v>6</v>
+      </c>
       <c r="F5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G5">
         <v>1</v>
       </c>
+      <c r="H5">
+        <v>2</v>
+      </c>
       <c r="I5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J5">
-        <v>1</v>
-      </c>
-      <c r="K5">
-        <v>3</v>
+        <v>3</v>
+      </c>
+      <c r="M5">
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -19302,37 +19076,40 @@
         <v>9</v>
       </c>
       <c r="B6">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="C6">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="D6">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="E6">
+        <v>9</v>
+      </c>
+      <c r="F6">
+        <v>14</v>
+      </c>
+      <c r="G6">
         <v>6</v>
       </c>
-      <c r="F6">
-        <v>4</v>
-      </c>
-      <c r="G6">
-        <v>4</v>
-      </c>
       <c r="H6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I6">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="J6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K6">
         <v>3</v>
       </c>
+      <c r="L6">
+        <v>4</v>
+      </c>
       <c r="M6">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -19340,39 +19117,216 @@
         <v>10</v>
       </c>
       <c r="B7">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="C7">
+        <v>18</v>
+      </c>
+      <c r="D7">
+        <v>15</v>
+      </c>
+      <c r="E7">
+        <v>16</v>
+      </c>
+      <c r="F7">
+        <v>17</v>
+      </c>
+      <c r="G7">
+        <v>8</v>
+      </c>
+      <c r="H7">
+        <v>7</v>
+      </c>
+      <c r="I7">
+        <v>12</v>
+      </c>
+      <c r="J7">
+        <v>10</v>
+      </c>
+      <c r="K7">
+        <v>6</v>
+      </c>
+      <c r="L7">
+        <v>8</v>
+      </c>
+      <c r="M7">
+        <v>4</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet61.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:L6"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="18.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="F2">
+        <v>1</v>
+      </c>
+      <c r="I2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
+      <c r="D3">
+        <v>3</v>
+      </c>
+      <c r="E3">
+        <v>1</v>
+      </c>
+      <c r="G3">
+        <v>1</v>
+      </c>
+      <c r="H3">
+        <v>1</v>
+      </c>
+      <c r="L3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12">
+      <c r="A4" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4">
+        <v>4</v>
+      </c>
+      <c r="D4">
+        <v>2</v>
+      </c>
+      <c r="E4">
+        <v>2</v>
+      </c>
+      <c r="G4">
+        <v>2</v>
+      </c>
+      <c r="H4">
+        <v>1</v>
+      </c>
+      <c r="I4">
+        <v>3</v>
+      </c>
+      <c r="J4">
+        <v>3</v>
+      </c>
+      <c r="K4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12">
+      <c r="A5" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D7">
-        <v>6</v>
-      </c>
-      <c r="E7">
-        <v>6</v>
-      </c>
-      <c r="F7">
-        <v>8</v>
-      </c>
-      <c r="G7">
-        <v>5</v>
-      </c>
-      <c r="H7">
-        <v>1</v>
-      </c>
-      <c r="I7">
+      <c r="F5">
+        <v>2</v>
+      </c>
+      <c r="I5">
+        <v>3</v>
+      </c>
+      <c r="K5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12">
+      <c r="A6" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6">
+        <v>4</v>
+      </c>
+      <c r="C6">
+        <v>1</v>
+      </c>
+      <c r="D6">
+        <v>5</v>
+      </c>
+      <c r="E6">
+        <v>3</v>
+      </c>
+      <c r="F6">
+        <v>3</v>
+      </c>
+      <c r="G6">
+        <v>3</v>
+      </c>
+      <c r="H6">
+        <v>2</v>
+      </c>
+      <c r="I6">
         <v>7</v>
       </c>
-      <c r="J7">
-        <v>3</v>
-      </c>
-      <c r="K7">
-        <v>8</v>
-      </c>
-      <c r="L7">
-        <v>1</v>
-      </c>
-      <c r="M7">
+      <c r="J6">
+        <v>3</v>
+      </c>
+      <c r="K6">
+        <v>2</v>
+      </c>
+      <c r="L6">
         <v>1</v>
       </c>
     </row>
@@ -19446,56 +19400,26 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2">
-        <v>1</v>
-      </c>
-      <c r="G2">
-        <v>1</v>
-      </c>
-      <c r="I2">
-        <v>1</v>
-      </c>
-      <c r="K2">
-        <v>2</v>
+      <c r="F2">
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B3">
-        <v>1</v>
-      </c>
-      <c r="C3">
-        <v>1</v>
-      </c>
-      <c r="F3">
-        <v>1</v>
-      </c>
-      <c r="G3">
-        <v>2</v>
-      </c>
-      <c r="H3">
-        <v>1</v>
-      </c>
-      <c r="I3">
-        <v>1</v>
-      </c>
-      <c r="J3">
-        <v>1</v>
+      <c r="K3">
+        <v>2</v>
       </c>
       <c r="L3">
-        <v>2</v>
-      </c>
-      <c r="M3">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="K4">
+      <c r="I4">
         <v>1</v>
       </c>
     </row>
@@ -19504,37 +19428,28 @@
         <v>8</v>
       </c>
       <c r="B5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D5">
-        <v>3</v>
-      </c>
-      <c r="E5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F5">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G5">
         <v>1</v>
       </c>
-      <c r="H5">
+      <c r="I5">
         <v>1</v>
       </c>
       <c r="J5">
         <v>1</v>
       </c>
       <c r="K5">
-        <v>1</v>
-      </c>
-      <c r="L5">
-        <v>2</v>
-      </c>
-      <c r="M5">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -19542,22 +19457,22 @@
         <v>9</v>
       </c>
       <c r="B6">
+        <v>4</v>
+      </c>
+      <c r="C6">
+        <v>7</v>
+      </c>
+      <c r="D6">
+        <v>5</v>
+      </c>
+      <c r="E6">
         <v>6</v>
       </c>
-      <c r="C6">
-        <v>11</v>
-      </c>
-      <c r="D6">
-        <v>6</v>
-      </c>
-      <c r="E6">
-        <v>4</v>
-      </c>
       <c r="F6">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="G6">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H6">
         <v>1</v>
@@ -19566,16 +19481,13 @@
         <v>5</v>
       </c>
       <c r="J6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K6">
-        <v>2</v>
-      </c>
-      <c r="L6">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="M6">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -19583,40 +19495,40 @@
         <v>10</v>
       </c>
       <c r="B7">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="C7">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="D7">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E7">
         <v>6</v>
       </c>
       <c r="F7">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="G7">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="H7">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I7">
         <v>7</v>
       </c>
       <c r="J7">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K7">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="L7">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="M7">
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -19689,17 +19601,17 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="D2">
-        <v>2</v>
+      <c r="B2">
+        <v>1</v>
       </c>
       <c r="G2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I2">
         <v>1</v>
       </c>
-      <c r="J2">
-        <v>3</v>
+      <c r="K2">
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -19709,22 +19621,28 @@
       <c r="B3">
         <v>1</v>
       </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
       <c r="F3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H3">
         <v>1</v>
       </c>
       <c r="I3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J3">
         <v>1</v>
       </c>
       <c r="L3">
+        <v>2</v>
+      </c>
+      <c r="M3">
         <v>4</v>
       </c>
     </row>
@@ -19740,29 +19658,38 @@
       <c r="A5" s="1" t="s">
         <v>8</v>
       </c>
+      <c r="B5">
+        <v>3</v>
+      </c>
       <c r="C5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F5">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G5">
         <v>1</v>
       </c>
+      <c r="H5">
+        <v>1</v>
+      </c>
       <c r="J5">
         <v>1</v>
       </c>
       <c r="K5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L5">
-        <v>5</v>
+        <v>2</v>
+      </c>
+      <c r="M5">
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -19773,37 +19700,37 @@
         <v>6</v>
       </c>
       <c r="C6">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="D6">
         <v>6</v>
       </c>
       <c r="E6">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="F6">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="G6">
         <v>5</v>
       </c>
       <c r="H6">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I6">
         <v>5</v>
       </c>
       <c r="J6">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="K6">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L6">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="M6">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -19811,7 +19738,7 @@
         <v>10</v>
       </c>
       <c r="B7">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="C7">
         <v>16</v>
@@ -19820,31 +19747,31 @@
         <v>9</v>
       </c>
       <c r="E7">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F7">
+        <v>18</v>
+      </c>
+      <c r="G7">
         <v>9</v>
       </c>
-      <c r="G7">
-        <v>10</v>
-      </c>
       <c r="H7">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I7">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="J7">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="K7">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L7">
         <v>12</v>
       </c>
       <c r="M7">
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -19853,6 +19780,234 @@
 </file>
 
 <file path=xl/worksheets/sheet64.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:M7"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+    <col min="13" max="13" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="M1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>2</v>
+      </c>
+      <c r="G2">
+        <v>3</v>
+      </c>
+      <c r="I2">
+        <v>1</v>
+      </c>
+      <c r="J2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>1</v>
+      </c>
+      <c r="F3">
+        <v>2</v>
+      </c>
+      <c r="G3">
+        <v>1</v>
+      </c>
+      <c r="H3">
+        <v>1</v>
+      </c>
+      <c r="I3">
+        <v>3</v>
+      </c>
+      <c r="J3">
+        <v>1</v>
+      </c>
+      <c r="L3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="K4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C5">
+        <v>2</v>
+      </c>
+      <c r="D5">
+        <v>1</v>
+      </c>
+      <c r="E5">
+        <v>1</v>
+      </c>
+      <c r="F5">
+        <v>1</v>
+      </c>
+      <c r="G5">
+        <v>1</v>
+      </c>
+      <c r="J5">
+        <v>1</v>
+      </c>
+      <c r="K5">
+        <v>2</v>
+      </c>
+      <c r="L5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6">
+        <v>6</v>
+      </c>
+      <c r="C6">
+        <v>14</v>
+      </c>
+      <c r="D6">
+        <v>6</v>
+      </c>
+      <c r="E6">
+        <v>7</v>
+      </c>
+      <c r="F6">
+        <v>6</v>
+      </c>
+      <c r="G6">
+        <v>5</v>
+      </c>
+      <c r="H6">
+        <v>4</v>
+      </c>
+      <c r="I6">
+        <v>5</v>
+      </c>
+      <c r="J6">
+        <v>6</v>
+      </c>
+      <c r="K6">
+        <v>4</v>
+      </c>
+      <c r="L6">
+        <v>3</v>
+      </c>
+      <c r="M6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7">
+        <v>7</v>
+      </c>
+      <c r="C7">
+        <v>16</v>
+      </c>
+      <c r="D7">
+        <v>9</v>
+      </c>
+      <c r="E7">
+        <v>8</v>
+      </c>
+      <c r="F7">
+        <v>9</v>
+      </c>
+      <c r="G7">
+        <v>10</v>
+      </c>
+      <c r="H7">
+        <v>5</v>
+      </c>
+      <c r="I7">
+        <v>9</v>
+      </c>
+      <c r="J7">
+        <v>11</v>
+      </c>
+      <c r="K7">
+        <v>7</v>
+      </c>
+      <c r="L7">
+        <v>12</v>
+      </c>
+      <c r="M7">
+        <v>3</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet65.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M8"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -20079,7 +20234,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet65.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet66.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:H5"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -20190,7 +20345,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet66.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet67.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -20463,7 +20618,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet67.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet68.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -20650,7 +20805,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet68.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet69.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:I5"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -20784,226 +20939,6 @@
         <v>3</v>
       </c>
       <c r="I5">
-        <v>3</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet69.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M6"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="18.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" customWidth="1"/>
-    <col min="13" max="13" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="M1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="H2">
-        <v>1</v>
-      </c>
-      <c r="I2">
-        <v>2</v>
-      </c>
-      <c r="J2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3">
-        <v>2</v>
-      </c>
-      <c r="E3">
-        <v>2</v>
-      </c>
-      <c r="F3">
-        <v>2</v>
-      </c>
-      <c r="J3">
-        <v>4</v>
-      </c>
-      <c r="K3">
-        <v>1</v>
-      </c>
-      <c r="M3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4">
-        <v>8</v>
-      </c>
-      <c r="C4">
-        <v>4</v>
-      </c>
-      <c r="D4">
-        <v>1</v>
-      </c>
-      <c r="E4">
-        <v>2</v>
-      </c>
-      <c r="F4">
-        <v>4</v>
-      </c>
-      <c r="G4">
-        <v>2</v>
-      </c>
-      <c r="H4">
-        <v>3</v>
-      </c>
-      <c r="I4">
-        <v>1</v>
-      </c>
-      <c r="J4">
-        <v>1</v>
-      </c>
-      <c r="K4">
-        <v>5</v>
-      </c>
-      <c r="L4">
-        <v>2</v>
-      </c>
-      <c r="M4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B5">
-        <v>7</v>
-      </c>
-      <c r="C5">
-        <v>6</v>
-      </c>
-      <c r="D5">
-        <v>4</v>
-      </c>
-      <c r="E5">
-        <v>3</v>
-      </c>
-      <c r="F5">
-        <v>4</v>
-      </c>
-      <c r="G5">
-        <v>1</v>
-      </c>
-      <c r="H5">
-        <v>1</v>
-      </c>
-      <c r="K5">
-        <v>2</v>
-      </c>
-      <c r="L5">
-        <v>2</v>
-      </c>
-      <c r="M5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B6">
-        <v>17</v>
-      </c>
-      <c r="C6">
-        <v>10</v>
-      </c>
-      <c r="D6">
-        <v>5</v>
-      </c>
-      <c r="E6">
-        <v>7</v>
-      </c>
-      <c r="F6">
-        <v>10</v>
-      </c>
-      <c r="G6">
-        <v>3</v>
-      </c>
-      <c r="H6">
-        <v>5</v>
-      </c>
-      <c r="I6">
-        <v>3</v>
-      </c>
-      <c r="J6">
-        <v>6</v>
-      </c>
-      <c r="K6">
-        <v>8</v>
-      </c>
-      <c r="L6">
-        <v>4</v>
-      </c>
-      <c r="M6">
         <v>3</v>
       </c>
     </row>
@@ -21265,6 +21200,226 @@
 
 <file path=xl/worksheets/sheet70.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:M6"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="18.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+    <col min="13" max="13" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="M1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="H2">
+        <v>1</v>
+      </c>
+      <c r="I2">
+        <v>2</v>
+      </c>
+      <c r="J2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>2</v>
+      </c>
+      <c r="E3">
+        <v>2</v>
+      </c>
+      <c r="F3">
+        <v>2</v>
+      </c>
+      <c r="J3">
+        <v>4</v>
+      </c>
+      <c r="K3">
+        <v>1</v>
+      </c>
+      <c r="M3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4">
+        <v>8</v>
+      </c>
+      <c r="C4">
+        <v>4</v>
+      </c>
+      <c r="D4">
+        <v>1</v>
+      </c>
+      <c r="E4">
+        <v>2</v>
+      </c>
+      <c r="F4">
+        <v>4</v>
+      </c>
+      <c r="G4">
+        <v>2</v>
+      </c>
+      <c r="H4">
+        <v>3</v>
+      </c>
+      <c r="I4">
+        <v>1</v>
+      </c>
+      <c r="J4">
+        <v>1</v>
+      </c>
+      <c r="K4">
+        <v>5</v>
+      </c>
+      <c r="L4">
+        <v>2</v>
+      </c>
+      <c r="M4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5">
+        <v>7</v>
+      </c>
+      <c r="C5">
+        <v>6</v>
+      </c>
+      <c r="D5">
+        <v>4</v>
+      </c>
+      <c r="E5">
+        <v>3</v>
+      </c>
+      <c r="F5">
+        <v>4</v>
+      </c>
+      <c r="G5">
+        <v>1</v>
+      </c>
+      <c r="H5">
+        <v>1</v>
+      </c>
+      <c r="K5">
+        <v>2</v>
+      </c>
+      <c r="L5">
+        <v>2</v>
+      </c>
+      <c r="M5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6">
+        <v>17</v>
+      </c>
+      <c r="C6">
+        <v>10</v>
+      </c>
+      <c r="D6">
+        <v>5</v>
+      </c>
+      <c r="E6">
+        <v>7</v>
+      </c>
+      <c r="F6">
+        <v>10</v>
+      </c>
+      <c r="G6">
+        <v>3</v>
+      </c>
+      <c r="H6">
+        <v>5</v>
+      </c>
+      <c r="I6">
+        <v>3</v>
+      </c>
+      <c r="J6">
+        <v>6</v>
+      </c>
+      <c r="K6">
+        <v>8</v>
+      </c>
+      <c r="L6">
+        <v>4</v>
+      </c>
+      <c r="M6">
+        <v>3</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet71.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:K5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -21416,7 +21571,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet71.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet72.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -21665,7 +21820,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet72.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet73.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -21834,7 +21989,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet73.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet74.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -22063,7 +22218,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet74.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet75.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:J7"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -22225,7 +22380,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet75.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet76.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:L5"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -22378,190 +22533,6 @@
       </c>
       <c r="L5">
         <v>1</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet76.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M6"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="18.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" customWidth="1"/>
-    <col min="13" max="13" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="M1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="H2">
-        <v>1</v>
-      </c>
-      <c r="J2">
-        <v>1</v>
-      </c>
-      <c r="L2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="L3">
-        <v>2</v>
-      </c>
-      <c r="M3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E4">
-        <v>1</v>
-      </c>
-      <c r="I4">
-        <v>2</v>
-      </c>
-      <c r="L4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B5">
-        <v>3</v>
-      </c>
-      <c r="C5">
-        <v>2</v>
-      </c>
-      <c r="D5">
-        <v>1</v>
-      </c>
-      <c r="E5">
-        <v>2</v>
-      </c>
-      <c r="F5">
-        <v>2</v>
-      </c>
-      <c r="G5">
-        <v>1</v>
-      </c>
-      <c r="H5">
-        <v>2</v>
-      </c>
-      <c r="I5">
-        <v>2</v>
-      </c>
-      <c r="K5">
-        <v>4</v>
-      </c>
-      <c r="L5">
-        <v>1</v>
-      </c>
-      <c r="M5">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B6">
-        <v>3</v>
-      </c>
-      <c r="C6">
-        <v>2</v>
-      </c>
-      <c r="D6">
-        <v>1</v>
-      </c>
-      <c r="E6">
-        <v>3</v>
-      </c>
-      <c r="F6">
-        <v>2</v>
-      </c>
-      <c r="G6">
-        <v>1</v>
-      </c>
-      <c r="H6">
-        <v>3</v>
-      </c>
-      <c r="I6">
-        <v>4</v>
-      </c>
-      <c r="J6">
-        <v>1</v>
-      </c>
-      <c r="K6">
-        <v>4</v>
-      </c>
-      <c r="L6">
-        <v>5</v>
-      </c>
-      <c r="M6">
-        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -22637,10 +22608,10 @@
       <c r="H2">
         <v>1</v>
       </c>
-      <c r="I2">
-        <v>1</v>
-      </c>
-      <c r="K2">
+      <c r="J2">
+        <v>1</v>
+      </c>
+      <c r="L2">
         <v>1</v>
       </c>
     </row>
@@ -22648,23 +22619,8 @@
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="E3">
-        <v>1</v>
-      </c>
-      <c r="H3">
-        <v>1</v>
-      </c>
-      <c r="I3">
-        <v>2</v>
-      </c>
-      <c r="J3">
-        <v>2</v>
-      </c>
-      <c r="K3">
-        <v>1</v>
-      </c>
       <c r="L3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M3">
         <v>1</v>
@@ -22674,34 +22630,13 @@
       <c r="A4" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B4">
-        <v>2</v>
-      </c>
-      <c r="C4">
-        <v>1</v>
-      </c>
       <c r="E4">
-        <v>3</v>
-      </c>
-      <c r="F4">
-        <v>2</v>
-      </c>
-      <c r="H4">
         <v>1</v>
       </c>
       <c r="I4">
         <v>2</v>
       </c>
-      <c r="J4">
-        <v>11</v>
-      </c>
-      <c r="K4">
-        <v>1</v>
-      </c>
       <c r="L4">
-        <v>1</v>
-      </c>
-      <c r="M4">
         <v>1</v>
       </c>
     </row>
@@ -22710,40 +22645,37 @@
         <v>9</v>
       </c>
       <c r="B5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E5">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="F5">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I5">
-        <v>6</v>
-      </c>
-      <c r="J5">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="K5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M5">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -22751,40 +22683,40 @@
         <v>10</v>
       </c>
       <c r="B6">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C6">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D6">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E6">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="F6">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="G6">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H6">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="I6">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="J6">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="K6">
         <v>4</v>
       </c>
       <c r="L6">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="M6">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -22857,16 +22789,13 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C2">
-        <v>1</v>
-      </c>
-      <c r="E2">
-        <v>1</v>
-      </c>
-      <c r="G2">
-        <v>1</v>
-      </c>
-      <c r="J2">
+      <c r="H2">
+        <v>1</v>
+      </c>
+      <c r="I2">
+        <v>1</v>
+      </c>
+      <c r="K2">
         <v>1</v>
       </c>
     </row>
@@ -22874,14 +22803,23 @@
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D3">
-        <v>2</v>
-      </c>
       <c r="E3">
-        <v>2</v>
-      </c>
-      <c r="G3">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="H3">
+        <v>1</v>
+      </c>
+      <c r="I3">
+        <v>2</v>
+      </c>
+      <c r="J3">
+        <v>2</v>
+      </c>
+      <c r="K3">
+        <v>1</v>
+      </c>
+      <c r="L3">
+        <v>3</v>
       </c>
       <c r="M3">
         <v>1</v>
@@ -22892,28 +22830,28 @@
         <v>8</v>
       </c>
       <c r="B4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E4">
         <v>3</v>
       </c>
-      <c r="G4">
+      <c r="F4">
         <v>2</v>
       </c>
       <c r="H4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I4">
         <v>2</v>
       </c>
       <c r="J4">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="K4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L4">
         <v>1</v>
@@ -22927,28 +22865,40 @@
         <v>9</v>
       </c>
       <c r="B5">
-        <v>5</v>
+        <v>2</v>
+      </c>
+      <c r="C5">
+        <v>4</v>
       </c>
       <c r="D5">
         <v>4</v>
       </c>
       <c r="E5">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="F5">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I5">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="J5">
-        <v>3</v>
+        <v>9</v>
+      </c>
+      <c r="K5">
+        <v>1</v>
+      </c>
+      <c r="L5">
+        <v>3</v>
+      </c>
+      <c r="M5">
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -22956,40 +22906,40 @@
         <v>10</v>
       </c>
       <c r="B6">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C6">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D6">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E6">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F6">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="G6">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H6">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="I6">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="J6">
+        <v>22</v>
+      </c>
+      <c r="K6">
+        <v>4</v>
+      </c>
+      <c r="L6">
         <v>7</v>
       </c>
-      <c r="K6">
-        <v>3</v>
-      </c>
-      <c r="L6">
-        <v>1</v>
-      </c>
       <c r="M6">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -22999,10 +22949,10 @@
 
 <file path=xl/worksheets/sheet79.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M7"/>
+  <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="19.7109375" customWidth="1"/>
+    <col min="1" max="1" width="18.7109375" customWidth="1"/>
     <col min="2" max="2" width="4.7109375" customWidth="1"/>
     <col min="3" max="3" width="4.7109375" customWidth="1"/>
     <col min="4" max="4" width="4.7109375" customWidth="1"/>
@@ -23062,25 +23012,16 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2">
-        <v>2</v>
-      </c>
       <c r="C2">
         <v>1</v>
       </c>
-      <c r="D2">
-        <v>1</v>
-      </c>
       <c r="E2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G2">
         <v>1</v>
       </c>
-      <c r="I2">
-        <v>1</v>
-      </c>
-      <c r="L2">
+      <c r="J2">
         <v>1</v>
       </c>
     </row>
@@ -23088,19 +23029,13 @@
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B3">
-        <v>2</v>
-      </c>
-      <c r="C3">
-        <v>2</v>
-      </c>
       <c r="D3">
-        <v>1</v>
-      </c>
-      <c r="J3">
-        <v>1</v>
-      </c>
-      <c r="K3">
+        <v>2</v>
+      </c>
+      <c r="E3">
+        <v>2</v>
+      </c>
+      <c r="G3">
         <v>1</v>
       </c>
       <c r="M3">
@@ -23109,114 +23044,106 @@
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="B4">
+        <v>3</v>
+      </c>
+      <c r="C4">
+        <v>3</v>
+      </c>
+      <c r="E4">
+        <v>3</v>
+      </c>
+      <c r="G4">
+        <v>2</v>
+      </c>
+      <c r="H4">
+        <v>2</v>
       </c>
       <c r="I4">
+        <v>2</v>
+      </c>
+      <c r="J4">
+        <v>3</v>
+      </c>
+      <c r="K4">
+        <v>3</v>
+      </c>
+      <c r="L4">
+        <v>1</v>
+      </c>
+      <c r="M4">
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B5">
-        <v>1</v>
-      </c>
-      <c r="C5">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E5">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="F5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G5">
-        <v>4</v>
+        <v>2</v>
+      </c>
+      <c r="H5">
+        <v>1</v>
       </c>
       <c r="I5">
         <v>1</v>
+      </c>
+      <c r="J5">
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B6">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C6">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D6">
         <v>6</v>
       </c>
       <c r="E6">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F6">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="G6">
         <v>6</v>
       </c>
       <c r="H6">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I6">
-        <v>2</v>
+        <v>3</v>
+      </c>
+      <c r="J6">
+        <v>7</v>
       </c>
       <c r="K6">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L6">
         <v>1</v>
       </c>
       <c r="M6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
-      <c r="A7" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B7">
-        <v>9</v>
-      </c>
-      <c r="C7">
-        <v>19</v>
-      </c>
-      <c r="D7">
-        <v>11</v>
-      </c>
-      <c r="E7">
-        <v>14</v>
-      </c>
-      <c r="F7">
-        <v>11</v>
-      </c>
-      <c r="G7">
-        <v>11</v>
-      </c>
-      <c r="H7">
-        <v>1</v>
-      </c>
-      <c r="I7">
-        <v>5</v>
-      </c>
-      <c r="J7">
-        <v>1</v>
-      </c>
-      <c r="K7">
-        <v>2</v>
-      </c>
-      <c r="L7">
-        <v>2</v>
-      </c>
-      <c r="M7">
         <v>2</v>
       </c>
     </row>
@@ -23459,6 +23386,234 @@
 
 <file path=xl/worksheets/sheet80.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:M7"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="19.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+    <col min="13" max="13" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="M1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>2</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="E2">
+        <v>2</v>
+      </c>
+      <c r="G2">
+        <v>1</v>
+      </c>
+      <c r="I2">
+        <v>1</v>
+      </c>
+      <c r="L2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>2</v>
+      </c>
+      <c r="C3">
+        <v>2</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
+      <c r="J3">
+        <v>1</v>
+      </c>
+      <c r="K3">
+        <v>1</v>
+      </c>
+      <c r="M3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5">
+        <v>1</v>
+      </c>
+      <c r="C5">
+        <v>8</v>
+      </c>
+      <c r="D5">
+        <v>3</v>
+      </c>
+      <c r="E5">
+        <v>7</v>
+      </c>
+      <c r="F5">
+        <v>4</v>
+      </c>
+      <c r="G5">
+        <v>4</v>
+      </c>
+      <c r="I5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6">
+        <v>4</v>
+      </c>
+      <c r="C6">
+        <v>8</v>
+      </c>
+      <c r="D6">
+        <v>6</v>
+      </c>
+      <c r="E6">
+        <v>5</v>
+      </c>
+      <c r="F6">
+        <v>7</v>
+      </c>
+      <c r="G6">
+        <v>6</v>
+      </c>
+      <c r="H6">
+        <v>1</v>
+      </c>
+      <c r="I6">
+        <v>2</v>
+      </c>
+      <c r="K6">
+        <v>1</v>
+      </c>
+      <c r="L6">
+        <v>1</v>
+      </c>
+      <c r="M6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7">
+        <v>9</v>
+      </c>
+      <c r="C7">
+        <v>19</v>
+      </c>
+      <c r="D7">
+        <v>11</v>
+      </c>
+      <c r="E7">
+        <v>14</v>
+      </c>
+      <c r="F7">
+        <v>11</v>
+      </c>
+      <c r="G7">
+        <v>11</v>
+      </c>
+      <c r="H7">
+        <v>1</v>
+      </c>
+      <c r="I7">
+        <v>5</v>
+      </c>
+      <c r="J7">
+        <v>1</v>
+      </c>
+      <c r="K7">
+        <v>2</v>
+      </c>
+      <c r="L7">
+        <v>2</v>
+      </c>
+      <c r="M7">
+        <v>2</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet81.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:J7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -23610,7 +23765,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet81.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet82.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -23805,7 +23960,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet82.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet83.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -23982,177 +24137,6 @@
       </c>
       <c r="M6">
         <v>2</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet83.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L6"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="18.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:12">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="G2">
-        <v>2</v>
-      </c>
-      <c r="I2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="E3">
-        <v>1</v>
-      </c>
-      <c r="J3">
-        <v>1</v>
-      </c>
-      <c r="L3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12">
-      <c r="A4" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4">
-        <v>1</v>
-      </c>
-      <c r="C4">
-        <v>1</v>
-      </c>
-      <c r="D4">
-        <v>1</v>
-      </c>
-      <c r="F4">
-        <v>1</v>
-      </c>
-      <c r="G4">
-        <v>1</v>
-      </c>
-      <c r="I4">
-        <v>3</v>
-      </c>
-      <c r="J4">
-        <v>1</v>
-      </c>
-      <c r="K4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12">
-      <c r="A5" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C5">
-        <v>1</v>
-      </c>
-      <c r="E5">
-        <v>2</v>
-      </c>
-      <c r="G5">
-        <v>1</v>
-      </c>
-      <c r="H5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12">
-      <c r="A6" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B6">
-        <v>1</v>
-      </c>
-      <c r="C6">
-        <v>2</v>
-      </c>
-      <c r="D6">
-        <v>1</v>
-      </c>
-      <c r="E6">
-        <v>3</v>
-      </c>
-      <c r="F6">
-        <v>1</v>
-      </c>
-      <c r="G6">
-        <v>4</v>
-      </c>
-      <c r="H6">
-        <v>1</v>
-      </c>
-      <c r="I6">
-        <v>4</v>
-      </c>
-      <c r="J6">
-        <v>2</v>
-      </c>
-      <c r="K6">
-        <v>2</v>
-      </c>
-      <c r="L6">
-        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -24193,19 +24177,19 @@
         <v>2017</v>
       </c>
       <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
         <v>2019</v>
       </c>
-      <c r="F1" s="1">
+      <c r="G1" s="1">
         <v>2020</v>
       </c>
-      <c r="G1" s="1">
+      <c r="H1" s="1">
         <v>2021</v>
       </c>
-      <c r="H1" s="1">
+      <c r="I1" s="1">
         <v>2022</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2023</v>
       </c>
       <c r="J1" s="1">
         <v>2024</v>
@@ -24222,6 +24206,9 @@
         <v>1</v>
       </c>
       <c r="G2">
+        <v>2</v>
+      </c>
+      <c r="I2">
         <v>1</v>
       </c>
     </row>
@@ -24229,10 +24216,13 @@
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="H3">
+      <c r="E3">
         <v>1</v>
       </c>
       <c r="J3">
+        <v>1</v>
+      </c>
+      <c r="L3">
         <v>1</v>
       </c>
     </row>
@@ -24240,46 +24230,46 @@
       <c r="A4" s="1" t="s">
         <v>8</v>
       </c>
+      <c r="B4">
+        <v>1</v>
+      </c>
       <c r="C4">
         <v>1</v>
       </c>
+      <c r="D4">
+        <v>1</v>
+      </c>
+      <c r="F4">
+        <v>1</v>
+      </c>
       <c r="G4">
         <v>1</v>
       </c>
-      <c r="L4">
-        <v>1</v>
+      <c r="I4">
+        <v>3</v>
+      </c>
+      <c r="J4">
+        <v>1</v>
+      </c>
+      <c r="K4">
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:12">
       <c r="A5" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B5">
-        <v>3</v>
-      </c>
       <c r="C5">
-        <v>3</v>
-      </c>
-      <c r="D5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E5">
-        <v>3</v>
-      </c>
-      <c r="F5">
+        <v>2</v>
+      </c>
+      <c r="G5">
         <v>1</v>
       </c>
       <c r="H5">
         <v>1</v>
-      </c>
-      <c r="I5">
-        <v>2</v>
-      </c>
-      <c r="K5">
-        <v>3</v>
-      </c>
-      <c r="L5">
-        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:12">
@@ -24287,13 +24277,13 @@
         <v>10</v>
       </c>
       <c r="B6">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C6">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D6">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E6">
         <v>3</v>
@@ -24302,22 +24292,22 @@
         <v>1</v>
       </c>
       <c r="G6">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I6">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L6">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -24326,6 +24316,171 @@
 </file>
 
 <file path=xl/worksheets/sheet85.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:L6"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="18.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="G2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="H3">
+        <v>1</v>
+      </c>
+      <c r="J3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12">
+      <c r="A4" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
+      <c r="G4">
+        <v>1</v>
+      </c>
+      <c r="L4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12">
+      <c r="A5" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5">
+        <v>3</v>
+      </c>
+      <c r="C5">
+        <v>3</v>
+      </c>
+      <c r="D5">
+        <v>4</v>
+      </c>
+      <c r="E5">
+        <v>3</v>
+      </c>
+      <c r="F5">
+        <v>1</v>
+      </c>
+      <c r="H5">
+        <v>1</v>
+      </c>
+      <c r="I5">
+        <v>2</v>
+      </c>
+      <c r="K5">
+        <v>3</v>
+      </c>
+      <c r="L5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12">
+      <c r="A6" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6">
+        <v>3</v>
+      </c>
+      <c r="C6">
+        <v>4</v>
+      </c>
+      <c r="D6">
+        <v>4</v>
+      </c>
+      <c r="E6">
+        <v>3</v>
+      </c>
+      <c r="F6">
+        <v>1</v>
+      </c>
+      <c r="G6">
+        <v>2</v>
+      </c>
+      <c r="H6">
+        <v>2</v>
+      </c>
+      <c r="I6">
+        <v>2</v>
+      </c>
+      <c r="J6">
+        <v>1</v>
+      </c>
+      <c r="K6">
+        <v>3</v>
+      </c>
+      <c r="L6">
+        <v>3</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet86.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:I5"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -24446,7 +24601,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet86.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet87.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -24635,7 +24790,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet87.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet88.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:H4"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -24741,7 +24896,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet88.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet89.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -24940,198 +25095,6 @@
         <v>3</v>
       </c>
       <c r="M7">
-        <v>1</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet89.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L6"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="18.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:12">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="H2">
-        <v>1</v>
-      </c>
-      <c r="J2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3">
-        <v>1</v>
-      </c>
-      <c r="C3">
-        <v>1</v>
-      </c>
-      <c r="G3">
-        <v>1</v>
-      </c>
-      <c r="H3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12">
-      <c r="A4" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4">
-        <v>2</v>
-      </c>
-      <c r="C4">
-        <v>3</v>
-      </c>
-      <c r="E4">
-        <v>1</v>
-      </c>
-      <c r="F4">
-        <v>1</v>
-      </c>
-      <c r="G4">
-        <v>1</v>
-      </c>
-      <c r="H4">
-        <v>1</v>
-      </c>
-      <c r="K4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12">
-      <c r="A5" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B5">
-        <v>3</v>
-      </c>
-      <c r="C5">
-        <v>2</v>
-      </c>
-      <c r="D5">
-        <v>2</v>
-      </c>
-      <c r="E5">
-        <v>3</v>
-      </c>
-      <c r="F5">
-        <v>1</v>
-      </c>
-      <c r="G5">
-        <v>1</v>
-      </c>
-      <c r="H5">
-        <v>1</v>
-      </c>
-      <c r="I5">
-        <v>3</v>
-      </c>
-      <c r="J5">
-        <v>2</v>
-      </c>
-      <c r="K5">
-        <v>1</v>
-      </c>
-      <c r="L5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12">
-      <c r="A6" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B6">
-        <v>6</v>
-      </c>
-      <c r="C6">
-        <v>6</v>
-      </c>
-      <c r="D6">
-        <v>2</v>
-      </c>
-      <c r="E6">
-        <v>4</v>
-      </c>
-      <c r="F6">
-        <v>2</v>
-      </c>
-      <c r="G6">
-        <v>3</v>
-      </c>
-      <c r="H6">
-        <v>5</v>
-      </c>
-      <c r="I6">
-        <v>3</v>
-      </c>
-      <c r="J6">
-        <v>4</v>
-      </c>
-      <c r="K6">
-        <v>2</v>
-      </c>
-      <c r="L6">
         <v>1</v>
       </c>
     </row>
@@ -25469,6 +25432,198 @@
 
 <file path=xl/worksheets/sheet90.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:L6"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="18.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="H2">
+        <v>1</v>
+      </c>
+      <c r="J2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>1</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
+      <c r="G3">
+        <v>1</v>
+      </c>
+      <c r="H3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12">
+      <c r="A4" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4">
+        <v>2</v>
+      </c>
+      <c r="C4">
+        <v>3</v>
+      </c>
+      <c r="E4">
+        <v>1</v>
+      </c>
+      <c r="F4">
+        <v>1</v>
+      </c>
+      <c r="G4">
+        <v>1</v>
+      </c>
+      <c r="H4">
+        <v>1</v>
+      </c>
+      <c r="K4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12">
+      <c r="A5" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5">
+        <v>3</v>
+      </c>
+      <c r="C5">
+        <v>2</v>
+      </c>
+      <c r="D5">
+        <v>2</v>
+      </c>
+      <c r="E5">
+        <v>3</v>
+      </c>
+      <c r="F5">
+        <v>1</v>
+      </c>
+      <c r="G5">
+        <v>1</v>
+      </c>
+      <c r="H5">
+        <v>1</v>
+      </c>
+      <c r="I5">
+        <v>3</v>
+      </c>
+      <c r="J5">
+        <v>2</v>
+      </c>
+      <c r="K5">
+        <v>1</v>
+      </c>
+      <c r="L5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12">
+      <c r="A6" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6">
+        <v>6</v>
+      </c>
+      <c r="C6">
+        <v>6</v>
+      </c>
+      <c r="D6">
+        <v>2</v>
+      </c>
+      <c r="E6">
+        <v>4</v>
+      </c>
+      <c r="F6">
+        <v>2</v>
+      </c>
+      <c r="G6">
+        <v>3</v>
+      </c>
+      <c r="H6">
+        <v>5</v>
+      </c>
+      <c r="I6">
+        <v>3</v>
+      </c>
+      <c r="J6">
+        <v>4</v>
+      </c>
+      <c r="K6">
+        <v>2</v>
+      </c>
+      <c r="L6">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet91.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:K6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -25625,7 +25780,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet91.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet92.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:G6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -25724,148 +25879,6 @@
       </c>
       <c r="G6">
         <v>1</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet92.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J6"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="18.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:10">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2025</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="H2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="H3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10">
-      <c r="A4" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D4">
-        <v>4</v>
-      </c>
-      <c r="F4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10">
-      <c r="A5" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B5">
-        <v>3</v>
-      </c>
-      <c r="C5">
-        <v>2</v>
-      </c>
-      <c r="D5">
-        <v>2</v>
-      </c>
-      <c r="E5">
-        <v>5</v>
-      </c>
-      <c r="G5">
-        <v>1</v>
-      </c>
-      <c r="H5">
-        <v>1</v>
-      </c>
-      <c r="I5">
-        <v>1</v>
-      </c>
-      <c r="J5">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10">
-      <c r="A6" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B6">
-        <v>3</v>
-      </c>
-      <c r="C6">
-        <v>2</v>
-      </c>
-      <c r="D6">
-        <v>6</v>
-      </c>
-      <c r="E6">
-        <v>5</v>
-      </c>
-      <c r="F6">
-        <v>1</v>
-      </c>
-      <c r="G6">
-        <v>1</v>
-      </c>
-      <c r="H6">
-        <v>3</v>
-      </c>
-      <c r="I6">
-        <v>1</v>
-      </c>
-      <c r="J6">
-        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/output/cta-index-crime-full-year.xlsx
+++ b/output/cta-index-crime-full-year.xlsx
@@ -47,18 +47,18 @@
     <sheet name="Sheffield &amp; DePaul" sheetId="38" r:id="rId38"/>
     <sheet name="Greektown" sheetId="39" r:id="rId39"/>
     <sheet name="River North" sheetId="40" r:id="rId40"/>
-    <sheet name="Roseland" sheetId="41" r:id="rId41"/>
-    <sheet name="Chinatown" sheetId="42" r:id="rId42"/>
-    <sheet name="Austin" sheetId="43" r:id="rId43"/>
-    <sheet name="Rogers Park" sheetId="44" r:id="rId44"/>
-    <sheet name="Mckinley Park" sheetId="45" r:id="rId45"/>
-    <sheet name="Irving Park" sheetId="46" r:id="rId46"/>
-    <sheet name="Armour Square" sheetId="47" r:id="rId47"/>
-    <sheet name="Uptown" sheetId="48" r:id="rId48"/>
-    <sheet name="West Elsdon" sheetId="49" r:id="rId49"/>
-    <sheet name="Woodlawn" sheetId="50" r:id="rId50"/>
-    <sheet name="Douglas" sheetId="51" r:id="rId51"/>
-    <sheet name="Edgewater" sheetId="52" r:id="rId52"/>
+    <sheet name="Edgewater" sheetId="41" r:id="rId41"/>
+    <sheet name="Roseland" sheetId="42" r:id="rId42"/>
+    <sheet name="Chinatown" sheetId="43" r:id="rId43"/>
+    <sheet name="Austin" sheetId="44" r:id="rId44"/>
+    <sheet name="Rogers Park" sheetId="45" r:id="rId45"/>
+    <sheet name="Mckinley Park" sheetId="46" r:id="rId46"/>
+    <sheet name="Irving Park" sheetId="47" r:id="rId47"/>
+    <sheet name="Armour Square" sheetId="48" r:id="rId48"/>
+    <sheet name="Uptown" sheetId="49" r:id="rId49"/>
+    <sheet name="West Elsdon" sheetId="50" r:id="rId50"/>
+    <sheet name="Woodlawn" sheetId="51" r:id="rId51"/>
+    <sheet name="Douglas" sheetId="52" r:id="rId52"/>
     <sheet name="Morgan Park" sheetId="53" r:id="rId53"/>
     <sheet name="Chicago Lawn" sheetId="54" r:id="rId54"/>
     <sheet name="South Deering" sheetId="55" r:id="rId55"/>
@@ -905,7 +905,7 @@
         <v>137</v>
       </c>
       <c r="M2">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -1156,7 +1156,7 @@
         <v>467</v>
       </c>
       <c r="M9">
-        <v>204</v>
+        <v>206</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -1197,7 +1197,7 @@
         <v>703</v>
       </c>
       <c r="M10">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -1238,7 +1238,7 @@
         <v>1604</v>
       </c>
       <c r="M11">
-        <v>877</v>
+        <v>881</v>
       </c>
     </row>
   </sheetData>
@@ -5064,7 +5064,7 @@
         <v>25</v>
       </c>
       <c r="M27">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="28" spans="1:13">
@@ -6341,7 +6341,7 @@
         <v>16</v>
       </c>
       <c r="M61">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="62" spans="1:13">
@@ -7116,7 +7116,7 @@
         <v>16</v>
       </c>
       <c r="M81">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="82" spans="1:13">
@@ -7845,7 +7845,7 @@
         <v>1604</v>
       </c>
       <c r="M99">
-        <v>877</v>
+        <v>881</v>
       </c>
     </row>
   </sheetData>
@@ -10226,7 +10226,7 @@
         <v>6</v>
       </c>
       <c r="M4">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -10308,7 +10308,7 @@
         <v>16</v>
       </c>
       <c r="M6">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -13519,6 +13519,283 @@
 
 <file path=xl/worksheets/sheet41.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:M9"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+    <col min="13" max="13" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="M1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>2</v>
+      </c>
+      <c r="F2">
+        <v>3</v>
+      </c>
+      <c r="G2">
+        <v>3</v>
+      </c>
+      <c r="I2">
+        <v>2</v>
+      </c>
+      <c r="J2">
+        <v>1</v>
+      </c>
+      <c r="K2">
+        <v>5</v>
+      </c>
+      <c r="L2">
+        <v>3</v>
+      </c>
+      <c r="M2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
+      <c r="E3">
+        <v>1</v>
+      </c>
+      <c r="F3">
+        <v>1</v>
+      </c>
+      <c r="G3">
+        <v>4</v>
+      </c>
+      <c r="H3">
+        <v>1</v>
+      </c>
+      <c r="I3">
+        <v>3</v>
+      </c>
+      <c r="J3">
+        <v>3</v>
+      </c>
+      <c r="L3">
+        <v>2</v>
+      </c>
+      <c r="M3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="I4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="K5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="M6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7">
+        <v>4</v>
+      </c>
+      <c r="C7">
+        <v>5</v>
+      </c>
+      <c r="D7">
+        <v>6</v>
+      </c>
+      <c r="E7">
+        <v>5</v>
+      </c>
+      <c r="F7">
+        <v>6</v>
+      </c>
+      <c r="G7">
+        <v>4</v>
+      </c>
+      <c r="H7">
+        <v>12</v>
+      </c>
+      <c r="I7">
+        <v>7</v>
+      </c>
+      <c r="J7">
+        <v>6</v>
+      </c>
+      <c r="K7">
+        <v>16</v>
+      </c>
+      <c r="L7">
+        <v>8</v>
+      </c>
+      <c r="M7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13">
+      <c r="A8" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B8">
+        <v>20</v>
+      </c>
+      <c r="C8">
+        <v>21</v>
+      </c>
+      <c r="D8">
+        <v>21</v>
+      </c>
+      <c r="E8">
+        <v>19</v>
+      </c>
+      <c r="F8">
+        <v>19</v>
+      </c>
+      <c r="G8">
+        <v>7</v>
+      </c>
+      <c r="H8">
+        <v>5</v>
+      </c>
+      <c r="I8">
+        <v>10</v>
+      </c>
+      <c r="J8">
+        <v>9</v>
+      </c>
+      <c r="K8">
+        <v>12</v>
+      </c>
+      <c r="L8">
+        <v>12</v>
+      </c>
+      <c r="M8">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13">
+      <c r="A9" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B9">
+        <v>24</v>
+      </c>
+      <c r="C9">
+        <v>27</v>
+      </c>
+      <c r="D9">
+        <v>30</v>
+      </c>
+      <c r="E9">
+        <v>25</v>
+      </c>
+      <c r="F9">
+        <v>29</v>
+      </c>
+      <c r="G9">
+        <v>18</v>
+      </c>
+      <c r="H9">
+        <v>18</v>
+      </c>
+      <c r="I9">
+        <v>23</v>
+      </c>
+      <c r="J9">
+        <v>19</v>
+      </c>
+      <c r="K9">
+        <v>34</v>
+      </c>
+      <c r="L9">
+        <v>25</v>
+      </c>
+      <c r="M9">
+        <v>16</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet42.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -13838,7 +14115,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet42.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet43.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M9"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -14105,324 +14382,6 @@
       </c>
       <c r="M9">
         <v>7</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet43.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M10"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" customWidth="1"/>
-    <col min="13" max="13" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="M1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2">
-        <v>4</v>
-      </c>
-      <c r="C2">
-        <v>4</v>
-      </c>
-      <c r="D2">
-        <v>3</v>
-      </c>
-      <c r="E2">
-        <v>5</v>
-      </c>
-      <c r="F2">
-        <v>9</v>
-      </c>
-      <c r="G2">
-        <v>3</v>
-      </c>
-      <c r="H2">
-        <v>5</v>
-      </c>
-      <c r="I2">
-        <v>4</v>
-      </c>
-      <c r="J2">
-        <v>8</v>
-      </c>
-      <c r="K2">
-        <v>7</v>
-      </c>
-      <c r="L2">
-        <v>5</v>
-      </c>
-      <c r="M2">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3">
-        <v>4</v>
-      </c>
-      <c r="C3">
-        <v>5</v>
-      </c>
-      <c r="D3">
-        <v>6</v>
-      </c>
-      <c r="E3">
-        <v>7</v>
-      </c>
-      <c r="F3">
-        <v>6</v>
-      </c>
-      <c r="G3">
-        <v>7</v>
-      </c>
-      <c r="H3">
-        <v>8</v>
-      </c>
-      <c r="I3">
-        <v>6</v>
-      </c>
-      <c r="J3">
-        <v>10</v>
-      </c>
-      <c r="K3">
-        <v>12</v>
-      </c>
-      <c r="L3">
-        <v>14</v>
-      </c>
-      <c r="M3">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="I4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5">
-        <v>1</v>
-      </c>
-      <c r="D5">
-        <v>1</v>
-      </c>
-      <c r="E5">
-        <v>1</v>
-      </c>
-      <c r="J5">
-        <v>3</v>
-      </c>
-      <c r="K5">
-        <v>2</v>
-      </c>
-      <c r="M5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="K6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
-      <c r="A7" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="L7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13">
-      <c r="A8" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B8">
-        <v>23</v>
-      </c>
-      <c r="C8">
-        <v>31</v>
-      </c>
-      <c r="D8">
-        <v>22</v>
-      </c>
-      <c r="E8">
-        <v>44</v>
-      </c>
-      <c r="F8">
-        <v>38</v>
-      </c>
-      <c r="G8">
-        <v>24</v>
-      </c>
-      <c r="H8">
-        <v>50</v>
-      </c>
-      <c r="I8">
-        <v>34</v>
-      </c>
-      <c r="J8">
-        <v>26</v>
-      </c>
-      <c r="K8">
-        <v>24</v>
-      </c>
-      <c r="L8">
-        <v>14</v>
-      </c>
-      <c r="M8">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13">
-      <c r="A9" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B9">
-        <v>46</v>
-      </c>
-      <c r="C9">
-        <v>59</v>
-      </c>
-      <c r="D9">
-        <v>33</v>
-      </c>
-      <c r="E9">
-        <v>73</v>
-      </c>
-      <c r="F9">
-        <v>114</v>
-      </c>
-      <c r="G9">
-        <v>58</v>
-      </c>
-      <c r="H9">
-        <v>41</v>
-      </c>
-      <c r="I9">
-        <v>44</v>
-      </c>
-      <c r="J9">
-        <v>20</v>
-      </c>
-      <c r="K9">
-        <v>25</v>
-      </c>
-      <c r="L9">
-        <v>27</v>
-      </c>
-      <c r="M9">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13">
-      <c r="A10" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B10">
-        <v>78</v>
-      </c>
-      <c r="C10">
-        <v>99</v>
-      </c>
-      <c r="D10">
-        <v>65</v>
-      </c>
-      <c r="E10">
-        <v>130</v>
-      </c>
-      <c r="F10">
-        <v>167</v>
-      </c>
-      <c r="G10">
-        <v>92</v>
-      </c>
-      <c r="H10">
-        <v>104</v>
-      </c>
-      <c r="I10">
-        <v>89</v>
-      </c>
-      <c r="J10">
-        <v>67</v>
-      </c>
-      <c r="K10">
-        <v>71</v>
-      </c>
-      <c r="L10">
-        <v>61</v>
-      </c>
-      <c r="M10">
-        <v>53</v>
       </c>
     </row>
   </sheetData>
@@ -14495,73 +14454,82 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
+      <c r="B2">
+        <v>4</v>
+      </c>
       <c r="C2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D2">
         <v>3</v>
       </c>
       <c r="E2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F2">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="G2">
-        <v>6</v>
+        <v>3</v>
+      </c>
+      <c r="H2">
+        <v>5</v>
       </c>
       <c r="I2">
         <v>4</v>
       </c>
       <c r="J2">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="K2">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M2">
-        <v>1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
+      <c r="B3">
+        <v>4</v>
+      </c>
       <c r="C3">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D3">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E3">
+        <v>7</v>
+      </c>
+      <c r="F3">
+        <v>6</v>
+      </c>
+      <c r="G3">
+        <v>7</v>
+      </c>
+      <c r="H3">
         <v>8</v>
       </c>
-      <c r="F3">
-        <v>1</v>
-      </c>
-      <c r="G3">
-        <v>5</v>
-      </c>
-      <c r="H3">
-        <v>3</v>
-      </c>
       <c r="I3">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J3">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="K3">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="L3">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="M3">
-        <v>2</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -14576,23 +14544,20 @@
       <c r="A5" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F5">
-        <v>2</v>
-      </c>
-      <c r="G5">
-        <v>1</v>
-      </c>
-      <c r="H5">
-        <v>1</v>
-      </c>
-      <c r="I5">
-        <v>2</v>
+      <c r="B5">
+        <v>1</v>
+      </c>
+      <c r="D5">
+        <v>1</v>
+      </c>
+      <c r="E5">
+        <v>1</v>
+      </c>
+      <c r="J5">
+        <v>3</v>
       </c>
       <c r="K5">
-        <v>3</v>
-      </c>
-      <c r="L5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M5">
         <v>2</v>
@@ -14602,7 +14567,7 @@
       <c r="A6" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="F6">
+      <c r="K6">
         <v>1</v>
       </c>
     </row>
@@ -14610,7 +14575,7 @@
       <c r="A7" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I7">
+      <c r="L7">
         <v>1</v>
       </c>
     </row>
@@ -14619,40 +14584,40 @@
         <v>8</v>
       </c>
       <c r="B8">
-        <v>3</v>
+        <v>23</v>
       </c>
       <c r="C8">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="D8">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="E8">
-        <v>10</v>
+        <v>44</v>
       </c>
       <c r="F8">
-        <v>15</v>
+        <v>38</v>
       </c>
       <c r="G8">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="H8">
-        <v>14</v>
+        <v>50</v>
       </c>
       <c r="I8">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="J8">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="K8">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="L8">
         <v>14</v>
       </c>
       <c r="M8">
-        <v>4</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -14660,40 +14625,40 @@
         <v>9</v>
       </c>
       <c r="B9">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="C9">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="D9">
-        <v>54</v>
+        <v>33</v>
       </c>
       <c r="E9">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="F9">
-        <v>50</v>
+        <v>114</v>
       </c>
       <c r="G9">
-        <v>32</v>
+        <v>58</v>
       </c>
       <c r="H9">
-        <v>21</v>
+        <v>41</v>
       </c>
       <c r="I9">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="J9">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="K9">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="L9">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="M9">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -14701,40 +14666,40 @@
         <v>10</v>
       </c>
       <c r="B10">
-        <v>59</v>
+        <v>78</v>
       </c>
       <c r="C10">
-        <v>76</v>
+        <v>99</v>
       </c>
       <c r="D10">
+        <v>65</v>
+      </c>
+      <c r="E10">
+        <v>130</v>
+      </c>
+      <c r="F10">
+        <v>167</v>
+      </c>
+      <c r="G10">
+        <v>92</v>
+      </c>
+      <c r="H10">
+        <v>104</v>
+      </c>
+      <c r="I10">
+        <v>89</v>
+      </c>
+      <c r="J10">
+        <v>67</v>
+      </c>
+      <c r="K10">
         <v>71</v>
       </c>
-      <c r="E10">
-        <v>101</v>
-      </c>
-      <c r="F10">
-        <v>70</v>
-      </c>
-      <c r="G10">
+      <c r="L10">
+        <v>61</v>
+      </c>
+      <c r="M10">
         <v>53</v>
-      </c>
-      <c r="H10">
-        <v>39</v>
-      </c>
-      <c r="I10">
-        <v>49</v>
-      </c>
-      <c r="J10">
-        <v>47</v>
-      </c>
-      <c r="K10">
-        <v>54</v>
-      </c>
-      <c r="L10">
-        <v>59</v>
-      </c>
-      <c r="M10">
-        <v>24</v>
       </c>
     </row>
   </sheetData>
@@ -14744,7 +14709,7 @@
 
 <file path=xl/worksheets/sheet45.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M7"/>
+  <dimension ref="A1:M10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="23.7109375" customWidth="1"/>
@@ -14808,19 +14773,31 @@
         <v>1</v>
       </c>
       <c r="C2">
-        <v>2</v>
+        <v>3</v>
+      </c>
+      <c r="D2">
+        <v>3</v>
+      </c>
+      <c r="E2">
+        <v>3</v>
       </c>
       <c r="F2">
         <v>1</v>
       </c>
+      <c r="G2">
+        <v>6</v>
+      </c>
       <c r="I2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J2">
         <v>1</v>
       </c>
       <c r="K2">
-        <v>1</v>
+        <v>5</v>
+      </c>
+      <c r="L2">
+        <v>3</v>
       </c>
       <c r="M2">
         <v>1</v>
@@ -14833,136 +14810,208 @@
       <c r="C3">
         <v>1</v>
       </c>
+      <c r="D3">
+        <v>3</v>
+      </c>
       <c r="E3">
-        <v>1</v>
+        <v>8</v>
+      </c>
+      <c r="F3">
+        <v>1</v>
+      </c>
+      <c r="G3">
+        <v>5</v>
       </c>
       <c r="H3">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="I3">
+        <v>4</v>
       </c>
       <c r="J3">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="K3">
+        <v>8</v>
       </c>
       <c r="L3">
-        <v>1</v>
+        <v>5</v>
+      </c>
+      <c r="M3">
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="L4">
+        <v>3</v>
+      </c>
+      <c r="I4">
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5">
-        <v>1</v>
-      </c>
-      <c r="C5">
-        <v>1</v>
-      </c>
-      <c r="D5">
-        <v>3</v>
-      </c>
-      <c r="E5">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G5">
         <v>1</v>
       </c>
+      <c r="H5">
+        <v>1</v>
+      </c>
+      <c r="I5">
+        <v>2</v>
+      </c>
       <c r="K5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L5">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="M5">
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B6">
         <v>6</v>
       </c>
-      <c r="C6">
-        <v>9</v>
-      </c>
-      <c r="D6">
-        <v>6</v>
-      </c>
-      <c r="E6">
-        <v>7</v>
-      </c>
       <c r="F6">
-        <v>9</v>
-      </c>
-      <c r="G6">
-        <v>3</v>
-      </c>
-      <c r="H6">
-        <v>2</v>
-      </c>
-      <c r="I6">
-        <v>1</v>
-      </c>
-      <c r="J6">
-        <v>3</v>
-      </c>
-      <c r="K6">
-        <v>5</v>
-      </c>
-      <c r="L6">
-        <v>4</v>
-      </c>
-      <c r="M6">
         <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13">
+      <c r="A8" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8">
+        <v>3</v>
+      </c>
+      <c r="C8">
+        <v>11</v>
+      </c>
+      <c r="D8">
+        <v>11</v>
+      </c>
+      <c r="E8">
         <v>10</v>
       </c>
-      <c r="B7">
-        <v>7</v>
-      </c>
-      <c r="C7">
+      <c r="F8">
+        <v>15</v>
+      </c>
+      <c r="G8">
+        <v>9</v>
+      </c>
+      <c r="H8">
+        <v>14</v>
+      </c>
+      <c r="I8">
         <v>13</v>
       </c>
-      <c r="D7">
+      <c r="J8">
+        <v>13</v>
+      </c>
+      <c r="K8">
+        <v>14</v>
+      </c>
+      <c r="L8">
+        <v>14</v>
+      </c>
+      <c r="M8">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13">
+      <c r="A9" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="E7">
-        <v>9</v>
-      </c>
-      <c r="F7">
-        <v>11</v>
-      </c>
-      <c r="G7">
-        <v>4</v>
-      </c>
-      <c r="H7">
-        <v>3</v>
-      </c>
-      <c r="I7">
-        <v>2</v>
-      </c>
-      <c r="J7">
-        <v>5</v>
-      </c>
-      <c r="K7">
+      <c r="B9">
+        <v>56</v>
+      </c>
+      <c r="C9">
+        <v>61</v>
+      </c>
+      <c r="D9">
+        <v>54</v>
+      </c>
+      <c r="E9">
+        <v>80</v>
+      </c>
+      <c r="F9">
+        <v>50</v>
+      </c>
+      <c r="G9">
+        <v>32</v>
+      </c>
+      <c r="H9">
+        <v>21</v>
+      </c>
+      <c r="I9">
+        <v>24</v>
+      </c>
+      <c r="J9">
+        <v>30</v>
+      </c>
+      <c r="K9">
+        <v>24</v>
+      </c>
+      <c r="L9">
+        <v>34</v>
+      </c>
+      <c r="M9">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13">
+      <c r="A10" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L7">
-        <v>7</v>
-      </c>
-      <c r="M7">
-        <v>2</v>
+      <c r="B10">
+        <v>59</v>
+      </c>
+      <c r="C10">
+        <v>76</v>
+      </c>
+      <c r="D10">
+        <v>71</v>
+      </c>
+      <c r="E10">
+        <v>101</v>
+      </c>
+      <c r="F10">
+        <v>70</v>
+      </c>
+      <c r="G10">
+        <v>53</v>
+      </c>
+      <c r="H10">
+        <v>39</v>
+      </c>
+      <c r="I10">
+        <v>49</v>
+      </c>
+      <c r="J10">
+        <v>47</v>
+      </c>
+      <c r="K10">
+        <v>54</v>
+      </c>
+      <c r="L10">
+        <v>59</v>
+      </c>
+      <c r="M10">
+        <v>24</v>
       </c>
     </row>
   </sheetData>
@@ -15036,31 +15085,19 @@
         <v>1</v>
       </c>
       <c r="C2">
-        <v>1</v>
-      </c>
-      <c r="D2">
-        <v>1</v>
-      </c>
-      <c r="E2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F2">
-        <v>2</v>
-      </c>
-      <c r="H2">
         <v>1</v>
       </c>
       <c r="I2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K2">
-        <v>2</v>
-      </c>
-      <c r="L2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M2">
         <v>1</v>
@@ -15070,34 +15107,19 @@
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B3">
-        <v>1</v>
-      </c>
       <c r="C3">
         <v>1</v>
       </c>
-      <c r="D3">
-        <v>1</v>
-      </c>
       <c r="E3">
         <v>1</v>
       </c>
-      <c r="G3">
-        <v>2</v>
-      </c>
       <c r="H3">
         <v>1</v>
       </c>
-      <c r="I3">
-        <v>2</v>
-      </c>
-      <c r="K3">
-        <v>2</v>
+      <c r="J3">
+        <v>1</v>
       </c>
       <c r="L3">
-        <v>3</v>
-      </c>
-      <c r="M3">
         <v>1</v>
       </c>
     </row>
@@ -15105,7 +15127,7 @@
       <c r="A4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C4">
+      <c r="L4">
         <v>1</v>
       </c>
     </row>
@@ -15117,10 +15139,10 @@
         <v>1</v>
       </c>
       <c r="C5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D5">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E5">
         <v>1</v>
@@ -15129,24 +15151,12 @@
         <v>1</v>
       </c>
       <c r="G5">
-        <v>2</v>
-      </c>
-      <c r="H5">
-        <v>3</v>
-      </c>
-      <c r="I5">
-        <v>2</v>
-      </c>
-      <c r="J5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L5">
-        <v>1</v>
-      </c>
-      <c r="M5">
         <v>1</v>
       </c>
     </row>
@@ -15155,40 +15165,40 @@
         <v>9</v>
       </c>
       <c r="B6">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="C6">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D6">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="E6">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="F6">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="G6">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="H6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I6">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="J6">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="K6">
         <v>5</v>
       </c>
       <c r="L6">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="M6">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -15196,40 +15206,40 @@
         <v>10</v>
       </c>
       <c r="B7">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C7">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="D7">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="E7">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="F7">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="G7">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="H7">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="I7">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="J7">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="K7">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="L7">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="M7">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -15306,13 +15316,16 @@
         <v>1</v>
       </c>
       <c r="D2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E2">
         <v>1</v>
       </c>
       <c r="F2">
-        <v>3</v>
+        <v>2</v>
+      </c>
+      <c r="H2">
+        <v>1</v>
       </c>
       <c r="I2">
         <v>2</v>
@@ -15321,10 +15334,10 @@
         <v>4</v>
       </c>
       <c r="K2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M2">
         <v>1</v>
@@ -15344,38 +15357,32 @@
         <v>1</v>
       </c>
       <c r="E3">
-        <v>6</v>
-      </c>
-      <c r="F3">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="G3">
+        <v>2</v>
       </c>
       <c r="H3">
         <v>1</v>
       </c>
       <c r="I3">
-        <v>1</v>
-      </c>
-      <c r="J3">
         <v>2</v>
       </c>
       <c r="K3">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L3">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="M3">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="I4">
-        <v>1</v>
-      </c>
-      <c r="M4">
+      <c r="C4">
         <v>1</v>
       </c>
     </row>
@@ -15384,40 +15391,40 @@
         <v>8</v>
       </c>
       <c r="B5">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C5">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E5">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F5">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="G5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H5">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="I5">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="J5">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="K5">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="L5">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="M5">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -15425,40 +15432,40 @@
         <v>9</v>
       </c>
       <c r="B6">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="C6">
+        <v>12</v>
+      </c>
+      <c r="D6">
         <v>14</v>
       </c>
-      <c r="D6">
-        <v>13</v>
-      </c>
       <c r="E6">
+        <v>14</v>
+      </c>
+      <c r="F6">
+        <v>15</v>
+      </c>
+      <c r="G6">
+        <v>9</v>
+      </c>
+      <c r="H6">
+        <v>3</v>
+      </c>
+      <c r="I6">
+        <v>6</v>
+      </c>
+      <c r="J6">
+        <v>7</v>
+      </c>
+      <c r="K6">
+        <v>5</v>
+      </c>
+      <c r="L6">
         <v>11</v>
       </c>
-      <c r="F6">
-        <v>28</v>
-      </c>
-      <c r="G6">
-        <v>11</v>
-      </c>
-      <c r="H6">
-        <v>8</v>
-      </c>
-      <c r="I6">
-        <v>12</v>
-      </c>
-      <c r="J6">
-        <v>6</v>
-      </c>
-      <c r="K6">
-        <v>9</v>
-      </c>
-      <c r="L6">
-        <v>12</v>
-      </c>
       <c r="M6">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -15466,40 +15473,40 @@
         <v>10</v>
       </c>
       <c r="B7">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="C7">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="D7">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E7">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="F7">
-        <v>47</v>
+        <v>18</v>
       </c>
       <c r="G7">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="H7">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="I7">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="J7">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="K7">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="L7">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="M7">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -15508,6 +15515,276 @@
 </file>
 
 <file path=xl/worksheets/sheet48.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:M7"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+    <col min="13" max="13" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="M1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>2</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
+      <c r="F2">
+        <v>3</v>
+      </c>
+      <c r="I2">
+        <v>2</v>
+      </c>
+      <c r="J2">
+        <v>4</v>
+      </c>
+      <c r="K2">
+        <v>1</v>
+      </c>
+      <c r="L2">
+        <v>3</v>
+      </c>
+      <c r="M2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>1</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
+      <c r="E3">
+        <v>6</v>
+      </c>
+      <c r="F3">
+        <v>1</v>
+      </c>
+      <c r="H3">
+        <v>1</v>
+      </c>
+      <c r="I3">
+        <v>1</v>
+      </c>
+      <c r="J3">
+        <v>2</v>
+      </c>
+      <c r="K3">
+        <v>4</v>
+      </c>
+      <c r="L3">
+        <v>6</v>
+      </c>
+      <c r="M3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="I4">
+        <v>1</v>
+      </c>
+      <c r="M4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5">
+        <v>5</v>
+      </c>
+      <c r="C5">
+        <v>6</v>
+      </c>
+      <c r="D5">
+        <v>4</v>
+      </c>
+      <c r="E5">
+        <v>5</v>
+      </c>
+      <c r="F5">
+        <v>15</v>
+      </c>
+      <c r="G5">
+        <v>4</v>
+      </c>
+      <c r="H5">
+        <v>7</v>
+      </c>
+      <c r="I5">
+        <v>11</v>
+      </c>
+      <c r="J5">
+        <v>15</v>
+      </c>
+      <c r="K5">
+        <v>11</v>
+      </c>
+      <c r="L5">
+        <v>19</v>
+      </c>
+      <c r="M5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6">
+        <v>21</v>
+      </c>
+      <c r="C6">
+        <v>14</v>
+      </c>
+      <c r="D6">
+        <v>13</v>
+      </c>
+      <c r="E6">
+        <v>11</v>
+      </c>
+      <c r="F6">
+        <v>28</v>
+      </c>
+      <c r="G6">
+        <v>11</v>
+      </c>
+      <c r="H6">
+        <v>8</v>
+      </c>
+      <c r="I6">
+        <v>12</v>
+      </c>
+      <c r="J6">
+        <v>6</v>
+      </c>
+      <c r="K6">
+        <v>9</v>
+      </c>
+      <c r="L6">
+        <v>12</v>
+      </c>
+      <c r="M6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7">
+        <v>27</v>
+      </c>
+      <c r="C7">
+        <v>22</v>
+      </c>
+      <c r="D7">
+        <v>20</v>
+      </c>
+      <c r="E7">
+        <v>23</v>
+      </c>
+      <c r="F7">
+        <v>47</v>
+      </c>
+      <c r="G7">
+        <v>15</v>
+      </c>
+      <c r="H7">
+        <v>16</v>
+      </c>
+      <c r="I7">
+        <v>27</v>
+      </c>
+      <c r="J7">
+        <v>27</v>
+      </c>
+      <c r="K7">
+        <v>25</v>
+      </c>
+      <c r="L7">
+        <v>40</v>
+      </c>
+      <c r="M7">
+        <v>10</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet49.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M9"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -15792,205 +16069,6 @@
       </c>
       <c r="M9">
         <v>17</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet49.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M6"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="18.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" customWidth="1"/>
-    <col min="13" max="13" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="M1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="L2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="J3">
-        <v>1</v>
-      </c>
-      <c r="L3">
-        <v>1</v>
-      </c>
-      <c r="M3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4">
-        <v>3</v>
-      </c>
-      <c r="C4">
-        <v>2</v>
-      </c>
-      <c r="D4">
-        <v>2</v>
-      </c>
-      <c r="F4">
-        <v>1</v>
-      </c>
-      <c r="G4">
-        <v>2</v>
-      </c>
-      <c r="H4">
-        <v>1</v>
-      </c>
-      <c r="I4">
-        <v>1</v>
-      </c>
-      <c r="K4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B5">
-        <v>5</v>
-      </c>
-      <c r="C5">
-        <v>2</v>
-      </c>
-      <c r="D5">
-        <v>2</v>
-      </c>
-      <c r="E5">
-        <v>12</v>
-      </c>
-      <c r="F5">
-        <v>3</v>
-      </c>
-      <c r="G5">
-        <v>2</v>
-      </c>
-      <c r="H5">
-        <v>1</v>
-      </c>
-      <c r="I5">
-        <v>2</v>
-      </c>
-      <c r="J5">
-        <v>9</v>
-      </c>
-      <c r="K5">
-        <v>4</v>
-      </c>
-      <c r="L5">
-        <v>1</v>
-      </c>
-      <c r="M5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B6">
-        <v>8</v>
-      </c>
-      <c r="C6">
-        <v>4</v>
-      </c>
-      <c r="D6">
-        <v>4</v>
-      </c>
-      <c r="E6">
-        <v>12</v>
-      </c>
-      <c r="F6">
-        <v>4</v>
-      </c>
-      <c r="G6">
-        <v>4</v>
-      </c>
-      <c r="H6">
-        <v>2</v>
-      </c>
-      <c r="I6">
-        <v>3</v>
-      </c>
-      <c r="J6">
-        <v>10</v>
-      </c>
-      <c r="K6">
-        <v>5</v>
-      </c>
-      <c r="L6">
-        <v>3</v>
-      </c>
-      <c r="M6">
-        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -16292,6 +16370,205 @@
 
 <file path=xl/worksheets/sheet50.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:M6"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="18.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+    <col min="13" max="13" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="M1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="L2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="J3">
+        <v>1</v>
+      </c>
+      <c r="L3">
+        <v>1</v>
+      </c>
+      <c r="M3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4">
+        <v>3</v>
+      </c>
+      <c r="C4">
+        <v>2</v>
+      </c>
+      <c r="D4">
+        <v>2</v>
+      </c>
+      <c r="F4">
+        <v>1</v>
+      </c>
+      <c r="G4">
+        <v>2</v>
+      </c>
+      <c r="H4">
+        <v>1</v>
+      </c>
+      <c r="I4">
+        <v>1</v>
+      </c>
+      <c r="K4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5">
+        <v>5</v>
+      </c>
+      <c r="C5">
+        <v>2</v>
+      </c>
+      <c r="D5">
+        <v>2</v>
+      </c>
+      <c r="E5">
+        <v>12</v>
+      </c>
+      <c r="F5">
+        <v>3</v>
+      </c>
+      <c r="G5">
+        <v>2</v>
+      </c>
+      <c r="H5">
+        <v>1</v>
+      </c>
+      <c r="I5">
+        <v>2</v>
+      </c>
+      <c r="J5">
+        <v>9</v>
+      </c>
+      <c r="K5">
+        <v>4</v>
+      </c>
+      <c r="L5">
+        <v>1</v>
+      </c>
+      <c r="M5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6">
+        <v>8</v>
+      </c>
+      <c r="C6">
+        <v>4</v>
+      </c>
+      <c r="D6">
+        <v>4</v>
+      </c>
+      <c r="E6">
+        <v>12</v>
+      </c>
+      <c r="F6">
+        <v>4</v>
+      </c>
+      <c r="G6">
+        <v>4</v>
+      </c>
+      <c r="H6">
+        <v>2</v>
+      </c>
+      <c r="I6">
+        <v>3</v>
+      </c>
+      <c r="J6">
+        <v>10</v>
+      </c>
+      <c r="K6">
+        <v>5</v>
+      </c>
+      <c r="L6">
+        <v>3</v>
+      </c>
+      <c r="M6">
+        <v>2</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet51.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -16548,7 +16825,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet51.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet52.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M8"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -16795,283 +17072,6 @@
       </c>
       <c r="M8">
         <v>3</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet52.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M9"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" customWidth="1"/>
-    <col min="13" max="13" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="M1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2">
-        <v>1</v>
-      </c>
-      <c r="D2">
-        <v>2</v>
-      </c>
-      <c r="F2">
-        <v>3</v>
-      </c>
-      <c r="G2">
-        <v>3</v>
-      </c>
-      <c r="I2">
-        <v>2</v>
-      </c>
-      <c r="J2">
-        <v>1</v>
-      </c>
-      <c r="K2">
-        <v>5</v>
-      </c>
-      <c r="L2">
-        <v>3</v>
-      </c>
-      <c r="M2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D3">
-        <v>1</v>
-      </c>
-      <c r="E3">
-        <v>1</v>
-      </c>
-      <c r="F3">
-        <v>1</v>
-      </c>
-      <c r="G3">
-        <v>4</v>
-      </c>
-      <c r="H3">
-        <v>1</v>
-      </c>
-      <c r="I3">
-        <v>3</v>
-      </c>
-      <c r="J3">
-        <v>3</v>
-      </c>
-      <c r="L3">
-        <v>2</v>
-      </c>
-      <c r="M3">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="I4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="K5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="M6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
-      <c r="A7" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B7">
-        <v>4</v>
-      </c>
-      <c r="C7">
-        <v>5</v>
-      </c>
-      <c r="D7">
-        <v>6</v>
-      </c>
-      <c r="E7">
-        <v>5</v>
-      </c>
-      <c r="F7">
-        <v>6</v>
-      </c>
-      <c r="G7">
-        <v>4</v>
-      </c>
-      <c r="H7">
-        <v>12</v>
-      </c>
-      <c r="I7">
-        <v>7</v>
-      </c>
-      <c r="J7">
-        <v>6</v>
-      </c>
-      <c r="K7">
-        <v>16</v>
-      </c>
-      <c r="L7">
-        <v>8</v>
-      </c>
-      <c r="M7">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13">
-      <c r="A8" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B8">
-        <v>20</v>
-      </c>
-      <c r="C8">
-        <v>21</v>
-      </c>
-      <c r="D8">
-        <v>21</v>
-      </c>
-      <c r="E8">
-        <v>19</v>
-      </c>
-      <c r="F8">
-        <v>19</v>
-      </c>
-      <c r="G8">
-        <v>7</v>
-      </c>
-      <c r="H8">
-        <v>5</v>
-      </c>
-      <c r="I8">
-        <v>10</v>
-      </c>
-      <c r="J8">
-        <v>9</v>
-      </c>
-      <c r="K8">
-        <v>12</v>
-      </c>
-      <c r="L8">
-        <v>12</v>
-      </c>
-      <c r="M8">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13">
-      <c r="A9" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B9">
-        <v>24</v>
-      </c>
-      <c r="C9">
-        <v>27</v>
-      </c>
-      <c r="D9">
-        <v>30</v>
-      </c>
-      <c r="E9">
-        <v>25</v>
-      </c>
-      <c r="F9">
-        <v>29</v>
-      </c>
-      <c r="G9">
-        <v>18</v>
-      </c>
-      <c r="H9">
-        <v>18</v>
-      </c>
-      <c r="I9">
-        <v>23</v>
-      </c>
-      <c r="J9">
-        <v>19</v>
-      </c>
-      <c r="K9">
-        <v>34</v>
-      </c>
-      <c r="L9">
-        <v>25</v>
-      </c>
-      <c r="M9">
-        <v>15</v>
       </c>
     </row>
   </sheetData>

--- a/output/cta-index-crime-full-year.xlsx
+++ b/output/cta-index-crime-full-year.xlsx
@@ -9,44 +9,44 @@
   <sheets>
     <sheet name="Citywide Totals" sheetId="1" r:id="rId1"/>
     <sheet name="By Neighborhood" sheetId="2" r:id="rId2"/>
-    <sheet name="Woodlawn" sheetId="3" r:id="rId3"/>
-    <sheet name="Roseland" sheetId="4" r:id="rId4"/>
-    <sheet name="Chatham" sheetId="5" r:id="rId5"/>
-    <sheet name="Loop" sheetId="6" r:id="rId6"/>
-    <sheet name="Rush &amp; Division" sheetId="7" r:id="rId7"/>
-    <sheet name="Near South Side" sheetId="8" r:id="rId8"/>
-    <sheet name="Rogers Park" sheetId="9" r:id="rId9"/>
-    <sheet name="North Lawndale" sheetId="10" r:id="rId10"/>
-    <sheet name="River North" sheetId="11" r:id="rId11"/>
-    <sheet name="O'Hare" sheetId="12" r:id="rId12"/>
-    <sheet name="Wrigleyville" sheetId="13" r:id="rId13"/>
-    <sheet name="Austin" sheetId="14" r:id="rId14"/>
-    <sheet name="Sheffield &amp; DePaul" sheetId="15" r:id="rId15"/>
-    <sheet name="Kenwood" sheetId="16" r:id="rId16"/>
-    <sheet name="South Chicago" sheetId="17" r:id="rId17"/>
-    <sheet name="Jefferson Park" sheetId="18" r:id="rId18"/>
-    <sheet name="Edgewater" sheetId="19" r:id="rId19"/>
-    <sheet name="West Lawn" sheetId="20" r:id="rId20"/>
-    <sheet name="Little Italy, UIC" sheetId="21" r:id="rId21"/>
-    <sheet name="Wicker Park" sheetId="22" r:id="rId22"/>
-    <sheet name="Lower West Side" sheetId="23" r:id="rId23"/>
-    <sheet name="Ashburn" sheetId="24" r:id="rId24"/>
-    <sheet name="Old Town" sheetId="25" r:id="rId25"/>
-    <sheet name="Gage Park" sheetId="26" r:id="rId26"/>
-    <sheet name="Grand Boulevard" sheetId="27" r:id="rId27"/>
-    <sheet name="Lake View" sheetId="28" r:id="rId28"/>
-    <sheet name="Englewood" sheetId="29" r:id="rId29"/>
-    <sheet name="Washington Park" sheetId="30" r:id="rId30"/>
-    <sheet name="West Town" sheetId="31" r:id="rId31"/>
-    <sheet name="East Village" sheetId="32" r:id="rId32"/>
-    <sheet name="Garfield Park" sheetId="33" r:id="rId33"/>
-    <sheet name="Fuller Park" sheetId="34" r:id="rId34"/>
-    <sheet name="Uptown" sheetId="35" r:id="rId35"/>
-    <sheet name="Logan Square" sheetId="36" r:id="rId36"/>
-    <sheet name="Riverdale" sheetId="37" r:id="rId37"/>
-    <sheet name="Little Village" sheetId="38" r:id="rId38"/>
-    <sheet name="West Loop" sheetId="39" r:id="rId39"/>
-    <sheet name="Auburn Gresham" sheetId="40" r:id="rId40"/>
+    <sheet name="Austin" sheetId="3" r:id="rId3"/>
+    <sheet name="Englewood" sheetId="4" r:id="rId4"/>
+    <sheet name="Auburn Gresham" sheetId="5" r:id="rId5"/>
+    <sheet name="Woodlawn" sheetId="6" r:id="rId6"/>
+    <sheet name="Roseland" sheetId="7" r:id="rId7"/>
+    <sheet name="Chatham" sheetId="8" r:id="rId8"/>
+    <sheet name="Loop" sheetId="9" r:id="rId9"/>
+    <sheet name="Rush &amp; Division" sheetId="10" r:id="rId10"/>
+    <sheet name="Near South Side" sheetId="11" r:id="rId11"/>
+    <sheet name="Rogers Park" sheetId="12" r:id="rId12"/>
+    <sheet name="North Lawndale" sheetId="13" r:id="rId13"/>
+    <sheet name="River North" sheetId="14" r:id="rId14"/>
+    <sheet name="O'Hare" sheetId="15" r:id="rId15"/>
+    <sheet name="Wrigleyville" sheetId="16" r:id="rId16"/>
+    <sheet name="Sheffield &amp; DePaul" sheetId="17" r:id="rId17"/>
+    <sheet name="Kenwood" sheetId="18" r:id="rId18"/>
+    <sheet name="South Chicago" sheetId="19" r:id="rId19"/>
+    <sheet name="Jefferson Park" sheetId="20" r:id="rId20"/>
+    <sheet name="Edgewater" sheetId="21" r:id="rId21"/>
+    <sheet name="West Lawn" sheetId="22" r:id="rId22"/>
+    <sheet name="Little Italy, UIC" sheetId="23" r:id="rId23"/>
+    <sheet name="Wicker Park" sheetId="24" r:id="rId24"/>
+    <sheet name="Lower West Side" sheetId="25" r:id="rId25"/>
+    <sheet name="Ashburn" sheetId="26" r:id="rId26"/>
+    <sheet name="Old Town" sheetId="27" r:id="rId27"/>
+    <sheet name="Gage Park" sheetId="28" r:id="rId28"/>
+    <sheet name="Grand Boulevard" sheetId="29" r:id="rId29"/>
+    <sheet name="Lake View" sheetId="30" r:id="rId30"/>
+    <sheet name="Washington Park" sheetId="31" r:id="rId31"/>
+    <sheet name="West Town" sheetId="32" r:id="rId32"/>
+    <sheet name="East Village" sheetId="33" r:id="rId33"/>
+    <sheet name="Garfield Park" sheetId="34" r:id="rId34"/>
+    <sheet name="Fuller Park" sheetId="35" r:id="rId35"/>
+    <sheet name="Uptown" sheetId="36" r:id="rId36"/>
+    <sheet name="Logan Square" sheetId="37" r:id="rId37"/>
+    <sheet name="Riverdale" sheetId="38" r:id="rId38"/>
+    <sheet name="Little Village" sheetId="39" r:id="rId39"/>
+    <sheet name="West Loop" sheetId="40" r:id="rId40"/>
     <sheet name="Humboldt Park" sheetId="41" r:id="rId41"/>
     <sheet name="Albany Park" sheetId="42" r:id="rId42"/>
     <sheet name="South Shore" sheetId="43" r:id="rId43"/>
@@ -905,7 +905,7 @@
         <v>137</v>
       </c>
       <c r="M2">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -946,7 +946,7 @@
         <v>262</v>
       </c>
       <c r="M3">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -1197,7 +1197,7 @@
         <v>703</v>
       </c>
       <c r="M10">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -1238,7 +1238,7 @@
         <v>1604</v>
       </c>
       <c r="M11">
-        <v>898</v>
+        <v>901</v>
       </c>
     </row>
   </sheetData>
@@ -1247,6 +1247,264 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:M7"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+    <col min="13" max="13" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="M1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>2</v>
+      </c>
+      <c r="D2">
+        <v>2</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
+      <c r="H2">
+        <v>2</v>
+      </c>
+      <c r="I2">
+        <v>1</v>
+      </c>
+      <c r="J2">
+        <v>1</v>
+      </c>
+      <c r="K2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>1</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
+      <c r="E3">
+        <v>3</v>
+      </c>
+      <c r="F3">
+        <v>4</v>
+      </c>
+      <c r="G3">
+        <v>2</v>
+      </c>
+      <c r="H3">
+        <v>2</v>
+      </c>
+      <c r="I3">
+        <v>4</v>
+      </c>
+      <c r="K3">
+        <v>1</v>
+      </c>
+      <c r="L3">
+        <v>2</v>
+      </c>
+      <c r="M3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="M4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5">
+        <v>5</v>
+      </c>
+      <c r="C5">
+        <v>4</v>
+      </c>
+      <c r="D5">
+        <v>3</v>
+      </c>
+      <c r="E5">
+        <v>7</v>
+      </c>
+      <c r="F5">
+        <v>9</v>
+      </c>
+      <c r="G5">
+        <v>14</v>
+      </c>
+      <c r="H5">
+        <v>7</v>
+      </c>
+      <c r="I5">
+        <v>9</v>
+      </c>
+      <c r="J5">
+        <v>5</v>
+      </c>
+      <c r="K5">
+        <v>3</v>
+      </c>
+      <c r="L5">
+        <v>5</v>
+      </c>
+      <c r="M5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6">
+        <v>34</v>
+      </c>
+      <c r="C6">
+        <v>33</v>
+      </c>
+      <c r="D6">
+        <v>64</v>
+      </c>
+      <c r="E6">
+        <v>44</v>
+      </c>
+      <c r="F6">
+        <v>45</v>
+      </c>
+      <c r="G6">
+        <v>11</v>
+      </c>
+      <c r="H6">
+        <v>7</v>
+      </c>
+      <c r="I6">
+        <v>7</v>
+      </c>
+      <c r="J6">
+        <v>15</v>
+      </c>
+      <c r="K6">
+        <v>9</v>
+      </c>
+      <c r="L6">
+        <v>12</v>
+      </c>
+      <c r="M6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7">
+        <v>42</v>
+      </c>
+      <c r="C7">
+        <v>37</v>
+      </c>
+      <c r="D7">
+        <v>70</v>
+      </c>
+      <c r="E7">
+        <v>55</v>
+      </c>
+      <c r="F7">
+        <v>58</v>
+      </c>
+      <c r="G7">
+        <v>27</v>
+      </c>
+      <c r="H7">
+        <v>18</v>
+      </c>
+      <c r="I7">
+        <v>21</v>
+      </c>
+      <c r="J7">
+        <v>21</v>
+      </c>
+      <c r="K7">
+        <v>14</v>
+      </c>
+      <c r="L7">
+        <v>19</v>
+      </c>
+      <c r="M7">
+        <v>7</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M8"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -1311,41 +1569,26 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2">
-        <v>1</v>
-      </c>
-      <c r="C2">
-        <v>3</v>
-      </c>
-      <c r="D2">
-        <v>1</v>
-      </c>
-      <c r="E2">
-        <v>1</v>
-      </c>
       <c r="F2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I2">
         <v>2</v>
       </c>
       <c r="J2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K2">
         <v>3</v>
       </c>
-      <c r="L2">
-        <v>4</v>
-      </c>
       <c r="M2">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -1356,55 +1599,46 @@
         <v>1</v>
       </c>
       <c r="C3">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
       </c>
       <c r="E3">
         <v>2</v>
       </c>
-      <c r="F3">
-        <v>5</v>
-      </c>
       <c r="G3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H3">
         <v>2</v>
       </c>
       <c r="I3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J3">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K3">
-        <v>6</v>
-      </c>
-      <c r="L3">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="M3">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4">
-        <v>1</v>
-      </c>
-      <c r="I4">
+        <v>5</v>
+      </c>
+      <c r="J4">
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="H5">
-        <v>1</v>
-      </c>
-      <c r="J5">
+        <v>6</v>
+      </c>
+      <c r="K5">
         <v>1</v>
       </c>
     </row>
@@ -1413,40 +1647,40 @@
         <v>8</v>
       </c>
       <c r="B6">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C6">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="D6">
-        <v>28</v>
+        <v>5</v>
       </c>
       <c r="E6">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="F6">
-        <v>35</v>
+        <v>4</v>
       </c>
       <c r="G6">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="H6">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="I6">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="J6">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K6">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="L6">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="M6">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -1454,40 +1688,40 @@
         <v>9</v>
       </c>
       <c r="B7">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="C7">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="D7">
-        <v>49</v>
+        <v>23</v>
       </c>
       <c r="E7">
-        <v>44</v>
+        <v>19</v>
       </c>
       <c r="F7">
-        <v>58</v>
+        <v>23</v>
       </c>
       <c r="G7">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="H7">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I7">
+        <v>14</v>
+      </c>
+      <c r="J7">
+        <v>11</v>
+      </c>
+      <c r="K7">
+        <v>12</v>
+      </c>
+      <c r="L7">
         <v>10</v>
       </c>
-      <c r="J7">
-        <v>8</v>
-      </c>
-      <c r="K7">
-        <v>11</v>
-      </c>
-      <c r="L7">
-        <v>7</v>
-      </c>
       <c r="M7">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -1495,40 +1729,40 @@
         <v>10</v>
       </c>
       <c r="B8">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C8">
-        <v>61</v>
+        <v>30</v>
       </c>
       <c r="D8">
-        <v>78</v>
+        <v>29</v>
       </c>
       <c r="E8">
-        <v>68</v>
+        <v>26</v>
       </c>
       <c r="F8">
-        <v>100</v>
+        <v>28</v>
       </c>
       <c r="G8">
-        <v>43</v>
+        <v>17</v>
       </c>
       <c r="H8">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="I8">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="J8">
+        <v>19</v>
+      </c>
+      <c r="K8">
         <v>20</v>
       </c>
-      <c r="K8">
-        <v>29</v>
-      </c>
       <c r="L8">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="M8">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
   </sheetData>
@@ -1536,7 +1770,609 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:M10"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+    <col min="13" max="13" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="M1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>3</v>
+      </c>
+      <c r="D2">
+        <v>3</v>
+      </c>
+      <c r="E2">
+        <v>3</v>
+      </c>
+      <c r="F2">
+        <v>1</v>
+      </c>
+      <c r="G2">
+        <v>6</v>
+      </c>
+      <c r="I2">
+        <v>4</v>
+      </c>
+      <c r="J2">
+        <v>1</v>
+      </c>
+      <c r="K2">
+        <v>5</v>
+      </c>
+      <c r="L2">
+        <v>3</v>
+      </c>
+      <c r="M2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
+      <c r="D3">
+        <v>3</v>
+      </c>
+      <c r="E3">
+        <v>8</v>
+      </c>
+      <c r="F3">
+        <v>1</v>
+      </c>
+      <c r="G3">
+        <v>5</v>
+      </c>
+      <c r="H3">
+        <v>3</v>
+      </c>
+      <c r="I3">
+        <v>4</v>
+      </c>
+      <c r="J3">
+        <v>3</v>
+      </c>
+      <c r="K3">
+        <v>8</v>
+      </c>
+      <c r="L3">
+        <v>5</v>
+      </c>
+      <c r="M3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="I4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F5">
+        <v>2</v>
+      </c>
+      <c r="G5">
+        <v>1</v>
+      </c>
+      <c r="H5">
+        <v>1</v>
+      </c>
+      <c r="I5">
+        <v>2</v>
+      </c>
+      <c r="K5">
+        <v>3</v>
+      </c>
+      <c r="L5">
+        <v>3</v>
+      </c>
+      <c r="M5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13">
+      <c r="A8" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8">
+        <v>3</v>
+      </c>
+      <c r="C8">
+        <v>11</v>
+      </c>
+      <c r="D8">
+        <v>11</v>
+      </c>
+      <c r="E8">
+        <v>10</v>
+      </c>
+      <c r="F8">
+        <v>15</v>
+      </c>
+      <c r="G8">
+        <v>9</v>
+      </c>
+      <c r="H8">
+        <v>14</v>
+      </c>
+      <c r="I8">
+        <v>13</v>
+      </c>
+      <c r="J8">
+        <v>13</v>
+      </c>
+      <c r="K8">
+        <v>14</v>
+      </c>
+      <c r="L8">
+        <v>14</v>
+      </c>
+      <c r="M8">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13">
+      <c r="A9" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B9">
+        <v>56</v>
+      </c>
+      <c r="C9">
+        <v>61</v>
+      </c>
+      <c r="D9">
+        <v>54</v>
+      </c>
+      <c r="E9">
+        <v>80</v>
+      </c>
+      <c r="F9">
+        <v>50</v>
+      </c>
+      <c r="G9">
+        <v>32</v>
+      </c>
+      <c r="H9">
+        <v>21</v>
+      </c>
+      <c r="I9">
+        <v>24</v>
+      </c>
+      <c r="J9">
+        <v>30</v>
+      </c>
+      <c r="K9">
+        <v>24</v>
+      </c>
+      <c r="L9">
+        <v>34</v>
+      </c>
+      <c r="M9">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13">
+      <c r="A10" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B10">
+        <v>59</v>
+      </c>
+      <c r="C10">
+        <v>76</v>
+      </c>
+      <c r="D10">
+        <v>71</v>
+      </c>
+      <c r="E10">
+        <v>101</v>
+      </c>
+      <c r="F10">
+        <v>70</v>
+      </c>
+      <c r="G10">
+        <v>53</v>
+      </c>
+      <c r="H10">
+        <v>39</v>
+      </c>
+      <c r="I10">
+        <v>49</v>
+      </c>
+      <c r="J10">
+        <v>47</v>
+      </c>
+      <c r="K10">
+        <v>54</v>
+      </c>
+      <c r="L10">
+        <v>59</v>
+      </c>
+      <c r="M10">
+        <v>25</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:M8"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+    <col min="13" max="13" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="M1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>3</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
+      <c r="F2">
+        <v>2</v>
+      </c>
+      <c r="G2">
+        <v>3</v>
+      </c>
+      <c r="H2">
+        <v>5</v>
+      </c>
+      <c r="I2">
+        <v>2</v>
+      </c>
+      <c r="J2">
+        <v>1</v>
+      </c>
+      <c r="K2">
+        <v>3</v>
+      </c>
+      <c r="L2">
+        <v>4</v>
+      </c>
+      <c r="M2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>1</v>
+      </c>
+      <c r="C3">
+        <v>2</v>
+      </c>
+      <c r="E3">
+        <v>2</v>
+      </c>
+      <c r="F3">
+        <v>5</v>
+      </c>
+      <c r="G3">
+        <v>3</v>
+      </c>
+      <c r="H3">
+        <v>2</v>
+      </c>
+      <c r="I3">
+        <v>4</v>
+      </c>
+      <c r="J3">
+        <v>5</v>
+      </c>
+      <c r="K3">
+        <v>6</v>
+      </c>
+      <c r="L3">
+        <v>7</v>
+      </c>
+      <c r="M3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4">
+        <v>1</v>
+      </c>
+      <c r="I4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H5">
+        <v>1</v>
+      </c>
+      <c r="J5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6">
+        <v>12</v>
+      </c>
+      <c r="C6">
+        <v>21</v>
+      </c>
+      <c r="D6">
+        <v>28</v>
+      </c>
+      <c r="E6">
+        <v>21</v>
+      </c>
+      <c r="F6">
+        <v>35</v>
+      </c>
+      <c r="G6">
+        <v>12</v>
+      </c>
+      <c r="H6">
+        <v>10</v>
+      </c>
+      <c r="I6">
+        <v>15</v>
+      </c>
+      <c r="J6">
+        <v>5</v>
+      </c>
+      <c r="K6">
+        <v>9</v>
+      </c>
+      <c r="L6">
+        <v>7</v>
+      </c>
+      <c r="M6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7">
+        <v>17</v>
+      </c>
+      <c r="C7">
+        <v>35</v>
+      </c>
+      <c r="D7">
+        <v>49</v>
+      </c>
+      <c r="E7">
+        <v>44</v>
+      </c>
+      <c r="F7">
+        <v>58</v>
+      </c>
+      <c r="G7">
+        <v>25</v>
+      </c>
+      <c r="H7">
+        <v>8</v>
+      </c>
+      <c r="I7">
+        <v>10</v>
+      </c>
+      <c r="J7">
+        <v>8</v>
+      </c>
+      <c r="K7">
+        <v>11</v>
+      </c>
+      <c r="L7">
+        <v>7</v>
+      </c>
+      <c r="M7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13">
+      <c r="A8" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B8">
+        <v>32</v>
+      </c>
+      <c r="C8">
+        <v>61</v>
+      </c>
+      <c r="D8">
+        <v>78</v>
+      </c>
+      <c r="E8">
+        <v>68</v>
+      </c>
+      <c r="F8">
+        <v>100</v>
+      </c>
+      <c r="G8">
+        <v>43</v>
+      </c>
+      <c r="H8">
+        <v>26</v>
+      </c>
+      <c r="I8">
+        <v>32</v>
+      </c>
+      <c r="J8">
+        <v>20</v>
+      </c>
+      <c r="K8">
+        <v>29</v>
+      </c>
+      <c r="L8">
+        <v>25</v>
+      </c>
+      <c r="M8">
+        <v>16</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -1803,7 +2639,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M8"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -2047,840 +2883,6 @@
       </c>
       <c r="M8">
         <v>23</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M7"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" customWidth="1"/>
-    <col min="13" max="13" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="M1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2">
-        <v>2</v>
-      </c>
-      <c r="E2">
-        <v>1</v>
-      </c>
-      <c r="F2">
-        <v>2</v>
-      </c>
-      <c r="G2">
-        <v>1</v>
-      </c>
-      <c r="H2">
-        <v>1</v>
-      </c>
-      <c r="J2">
-        <v>1</v>
-      </c>
-      <c r="M2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3">
-        <v>1</v>
-      </c>
-      <c r="D3">
-        <v>1</v>
-      </c>
-      <c r="F3">
-        <v>1</v>
-      </c>
-      <c r="G3">
-        <v>1</v>
-      </c>
-      <c r="H3">
-        <v>1</v>
-      </c>
-      <c r="I3">
-        <v>1</v>
-      </c>
-      <c r="J3">
-        <v>2</v>
-      </c>
-      <c r="K3">
-        <v>1</v>
-      </c>
-      <c r="M3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B4">
-        <v>1</v>
-      </c>
-      <c r="E4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C5">
-        <v>2</v>
-      </c>
-      <c r="D5">
-        <v>1</v>
-      </c>
-      <c r="F5">
-        <v>4</v>
-      </c>
-      <c r="G5">
-        <v>3</v>
-      </c>
-      <c r="H5">
-        <v>2</v>
-      </c>
-      <c r="I5">
-        <v>1</v>
-      </c>
-      <c r="J5">
-        <v>2</v>
-      </c>
-      <c r="K5">
-        <v>2</v>
-      </c>
-      <c r="L5">
-        <v>3</v>
-      </c>
-      <c r="M5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B6">
-        <v>9</v>
-      </c>
-      <c r="C6">
-        <v>10</v>
-      </c>
-      <c r="D6">
-        <v>5</v>
-      </c>
-      <c r="E6">
-        <v>9</v>
-      </c>
-      <c r="F6">
-        <v>7</v>
-      </c>
-      <c r="G6">
-        <v>3</v>
-      </c>
-      <c r="H6">
-        <v>4</v>
-      </c>
-      <c r="I6">
-        <v>3</v>
-      </c>
-      <c r="J6">
-        <v>1</v>
-      </c>
-      <c r="K6">
-        <v>6</v>
-      </c>
-      <c r="L6">
-        <v>2</v>
-      </c>
-      <c r="M6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
-      <c r="A7" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B7">
-        <v>13</v>
-      </c>
-      <c r="C7">
-        <v>12</v>
-      </c>
-      <c r="D7">
-        <v>7</v>
-      </c>
-      <c r="E7">
-        <v>11</v>
-      </c>
-      <c r="F7">
-        <v>14</v>
-      </c>
-      <c r="G7">
-        <v>8</v>
-      </c>
-      <c r="H7">
-        <v>8</v>
-      </c>
-      <c r="I7">
-        <v>5</v>
-      </c>
-      <c r="J7">
-        <v>6</v>
-      </c>
-      <c r="K7">
-        <v>9</v>
-      </c>
-      <c r="L7">
-        <v>5</v>
-      </c>
-      <c r="M7">
-        <v>5</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M10"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" customWidth="1"/>
-    <col min="13" max="13" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="M1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2">
-        <v>4</v>
-      </c>
-      <c r="C2">
-        <v>4</v>
-      </c>
-      <c r="D2">
-        <v>3</v>
-      </c>
-      <c r="E2">
-        <v>5</v>
-      </c>
-      <c r="F2">
-        <v>9</v>
-      </c>
-      <c r="G2">
-        <v>3</v>
-      </c>
-      <c r="H2">
-        <v>5</v>
-      </c>
-      <c r="I2">
-        <v>4</v>
-      </c>
-      <c r="J2">
-        <v>8</v>
-      </c>
-      <c r="K2">
-        <v>7</v>
-      </c>
-      <c r="L2">
-        <v>5</v>
-      </c>
-      <c r="M2">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3">
-        <v>4</v>
-      </c>
-      <c r="C3">
-        <v>5</v>
-      </c>
-      <c r="D3">
-        <v>6</v>
-      </c>
-      <c r="E3">
-        <v>7</v>
-      </c>
-      <c r="F3">
-        <v>6</v>
-      </c>
-      <c r="G3">
-        <v>7</v>
-      </c>
-      <c r="H3">
-        <v>8</v>
-      </c>
-      <c r="I3">
-        <v>6</v>
-      </c>
-      <c r="J3">
-        <v>10</v>
-      </c>
-      <c r="K3">
-        <v>12</v>
-      </c>
-      <c r="L3">
-        <v>14</v>
-      </c>
-      <c r="M3">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="I4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5">
-        <v>1</v>
-      </c>
-      <c r="D5">
-        <v>1</v>
-      </c>
-      <c r="E5">
-        <v>1</v>
-      </c>
-      <c r="J5">
-        <v>3</v>
-      </c>
-      <c r="K5">
-        <v>2</v>
-      </c>
-      <c r="M5">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="K6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
-      <c r="A7" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="L7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13">
-      <c r="A8" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B8">
-        <v>23</v>
-      </c>
-      <c r="C8">
-        <v>31</v>
-      </c>
-      <c r="D8">
-        <v>22</v>
-      </c>
-      <c r="E8">
-        <v>44</v>
-      </c>
-      <c r="F8">
-        <v>38</v>
-      </c>
-      <c r="G8">
-        <v>24</v>
-      </c>
-      <c r="H8">
-        <v>50</v>
-      </c>
-      <c r="I8">
-        <v>34</v>
-      </c>
-      <c r="J8">
-        <v>26</v>
-      </c>
-      <c r="K8">
-        <v>24</v>
-      </c>
-      <c r="L8">
-        <v>14</v>
-      </c>
-      <c r="M8">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13">
-      <c r="A9" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B9">
-        <v>46</v>
-      </c>
-      <c r="C9">
-        <v>59</v>
-      </c>
-      <c r="D9">
-        <v>33</v>
-      </c>
-      <c r="E9">
-        <v>73</v>
-      </c>
-      <c r="F9">
-        <v>114</v>
-      </c>
-      <c r="G9">
-        <v>58</v>
-      </c>
-      <c r="H9">
-        <v>41</v>
-      </c>
-      <c r="I9">
-        <v>44</v>
-      </c>
-      <c r="J9">
-        <v>20</v>
-      </c>
-      <c r="K9">
-        <v>25</v>
-      </c>
-      <c r="L9">
-        <v>27</v>
-      </c>
-      <c r="M9">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13">
-      <c r="A10" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B10">
-        <v>78</v>
-      </c>
-      <c r="C10">
-        <v>99</v>
-      </c>
-      <c r="D10">
-        <v>65</v>
-      </c>
-      <c r="E10">
-        <v>130</v>
-      </c>
-      <c r="F10">
-        <v>167</v>
-      </c>
-      <c r="G10">
-        <v>92</v>
-      </c>
-      <c r="H10">
-        <v>104</v>
-      </c>
-      <c r="I10">
-        <v>89</v>
-      </c>
-      <c r="J10">
-        <v>67</v>
-      </c>
-      <c r="K10">
-        <v>71</v>
-      </c>
-      <c r="L10">
-        <v>61</v>
-      </c>
-      <c r="M10">
-        <v>54</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M7"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" customWidth="1"/>
-    <col min="13" max="13" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="M1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D2">
-        <v>1</v>
-      </c>
-      <c r="E2">
-        <v>2</v>
-      </c>
-      <c r="F2">
-        <v>1</v>
-      </c>
-      <c r="H2">
-        <v>3</v>
-      </c>
-      <c r="I2">
-        <v>1</v>
-      </c>
-      <c r="J2">
-        <v>3</v>
-      </c>
-      <c r="K2">
-        <v>1</v>
-      </c>
-      <c r="L2">
-        <v>2</v>
-      </c>
-      <c r="M2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3">
-        <v>2</v>
-      </c>
-      <c r="D3">
-        <v>1</v>
-      </c>
-      <c r="F3">
-        <v>2</v>
-      </c>
-      <c r="H3">
-        <v>2</v>
-      </c>
-      <c r="I3">
-        <v>4</v>
-      </c>
-      <c r="J3">
-        <v>1</v>
-      </c>
-      <c r="K3">
-        <v>2</v>
-      </c>
-      <c r="L3">
-        <v>6</v>
-      </c>
-      <c r="M3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="H4">
-        <v>1</v>
-      </c>
-      <c r="I4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5">
-        <v>1</v>
-      </c>
-      <c r="C5">
-        <v>5</v>
-      </c>
-      <c r="D5">
-        <v>5</v>
-      </c>
-      <c r="E5">
-        <v>3</v>
-      </c>
-      <c r="F5">
-        <v>7</v>
-      </c>
-      <c r="G5">
-        <v>2</v>
-      </c>
-      <c r="H5">
-        <v>3</v>
-      </c>
-      <c r="I5">
-        <v>8</v>
-      </c>
-      <c r="J5">
-        <v>1</v>
-      </c>
-      <c r="K5">
-        <v>5</v>
-      </c>
-      <c r="L5">
-        <v>4</v>
-      </c>
-      <c r="M5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B6">
-        <v>11</v>
-      </c>
-      <c r="C6">
-        <v>22</v>
-      </c>
-      <c r="D6">
-        <v>26</v>
-      </c>
-      <c r="E6">
-        <v>31</v>
-      </c>
-      <c r="F6">
-        <v>28</v>
-      </c>
-      <c r="G6">
-        <v>11</v>
-      </c>
-      <c r="H6">
-        <v>8</v>
-      </c>
-      <c r="I6">
-        <v>6</v>
-      </c>
-      <c r="J6">
-        <v>6</v>
-      </c>
-      <c r="K6">
-        <v>9</v>
-      </c>
-      <c r="L6">
-        <v>9</v>
-      </c>
-      <c r="M6">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
-      <c r="A7" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B7">
-        <v>14</v>
-      </c>
-      <c r="C7">
-        <v>27</v>
-      </c>
-      <c r="D7">
-        <v>33</v>
-      </c>
-      <c r="E7">
-        <v>36</v>
-      </c>
-      <c r="F7">
-        <v>38</v>
-      </c>
-      <c r="G7">
-        <v>13</v>
-      </c>
-      <c r="H7">
-        <v>17</v>
-      </c>
-      <c r="I7">
-        <v>21</v>
-      </c>
-      <c r="J7">
-        <v>11</v>
-      </c>
-      <c r="K7">
-        <v>17</v>
-      </c>
-      <c r="L7">
-        <v>21</v>
-      </c>
-      <c r="M7">
-        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -2953,13 +2955,22 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
+      <c r="B2">
+        <v>2</v>
+      </c>
       <c r="E2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F2">
+        <v>2</v>
+      </c>
+      <c r="G2">
         <v>1</v>
       </c>
       <c r="H2">
+        <v>1</v>
+      </c>
+      <c r="J2">
         <v>1</v>
       </c>
       <c r="M2">
@@ -2970,21 +2981,42 @@
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
+      <c r="B3">
+        <v>1</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
       <c r="F3">
         <v>1</v>
       </c>
       <c r="G3">
-        <v>2</v>
-      </c>
-      <c r="L3">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="H3">
+        <v>1</v>
+      </c>
+      <c r="I3">
+        <v>1</v>
+      </c>
+      <c r="J3">
+        <v>2</v>
+      </c>
+      <c r="K3">
+        <v>1</v>
+      </c>
+      <c r="M3">
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="I4">
+      <c r="B4">
+        <v>1</v>
+      </c>
+      <c r="E4">
         <v>1</v>
       </c>
     </row>
@@ -2993,16 +3025,34 @@
         <v>8</v>
       </c>
       <c r="C5">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="D5">
+        <v>1</v>
+      </c>
+      <c r="F5">
+        <v>4</v>
       </c>
       <c r="G5">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="H5">
+        <v>2</v>
+      </c>
+      <c r="I5">
+        <v>1</v>
+      </c>
+      <c r="J5">
+        <v>2</v>
       </c>
       <c r="K5">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="L5">
+        <v>3</v>
       </c>
       <c r="M5">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -3010,34 +3060,40 @@
         <v>9</v>
       </c>
       <c r="B6">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C6">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="D6">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E6">
+        <v>9</v>
+      </c>
+      <c r="F6">
         <v>7</v>
       </c>
-      <c r="F6">
+      <c r="G6">
         <v>3</v>
       </c>
       <c r="H6">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I6">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J6">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K6">
-        <v>1</v>
+        <v>6</v>
+      </c>
+      <c r="L6">
+        <v>2</v>
       </c>
       <c r="M6">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -3045,40 +3101,40 @@
         <v>10</v>
       </c>
       <c r="B7">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="C7">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="D7">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E7">
+        <v>11</v>
+      </c>
+      <c r="F7">
+        <v>14</v>
+      </c>
+      <c r="G7">
+        <v>8</v>
+      </c>
+      <c r="H7">
+        <v>8</v>
+      </c>
+      <c r="I7">
+        <v>5</v>
+      </c>
+      <c r="J7">
+        <v>6</v>
+      </c>
+      <c r="K7">
         <v>9</v>
       </c>
-      <c r="F7">
-        <v>5</v>
-      </c>
-      <c r="G7">
-        <v>3</v>
-      </c>
-      <c r="H7">
-        <v>2</v>
-      </c>
-      <c r="I7">
-        <v>2</v>
-      </c>
-      <c r="J7">
-        <v>5</v>
-      </c>
-      <c r="K7">
-        <v>2</v>
-      </c>
       <c r="L7">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M7">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -3087,6 +3143,468 @@
 </file>
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:M7"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+    <col min="13" max="13" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="M1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="E2">
+        <v>2</v>
+      </c>
+      <c r="F2">
+        <v>1</v>
+      </c>
+      <c r="H2">
+        <v>3</v>
+      </c>
+      <c r="I2">
+        <v>1</v>
+      </c>
+      <c r="J2">
+        <v>3</v>
+      </c>
+      <c r="K2">
+        <v>1</v>
+      </c>
+      <c r="L2">
+        <v>2</v>
+      </c>
+      <c r="M2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>2</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
+      <c r="F3">
+        <v>2</v>
+      </c>
+      <c r="H3">
+        <v>2</v>
+      </c>
+      <c r="I3">
+        <v>4</v>
+      </c>
+      <c r="J3">
+        <v>1</v>
+      </c>
+      <c r="K3">
+        <v>2</v>
+      </c>
+      <c r="L3">
+        <v>6</v>
+      </c>
+      <c r="M3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H4">
+        <v>1</v>
+      </c>
+      <c r="I4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5">
+        <v>1</v>
+      </c>
+      <c r="C5">
+        <v>5</v>
+      </c>
+      <c r="D5">
+        <v>5</v>
+      </c>
+      <c r="E5">
+        <v>3</v>
+      </c>
+      <c r="F5">
+        <v>7</v>
+      </c>
+      <c r="G5">
+        <v>2</v>
+      </c>
+      <c r="H5">
+        <v>3</v>
+      </c>
+      <c r="I5">
+        <v>8</v>
+      </c>
+      <c r="J5">
+        <v>1</v>
+      </c>
+      <c r="K5">
+        <v>5</v>
+      </c>
+      <c r="L5">
+        <v>4</v>
+      </c>
+      <c r="M5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6">
+        <v>11</v>
+      </c>
+      <c r="C6">
+        <v>22</v>
+      </c>
+      <c r="D6">
+        <v>26</v>
+      </c>
+      <c r="E6">
+        <v>31</v>
+      </c>
+      <c r="F6">
+        <v>28</v>
+      </c>
+      <c r="G6">
+        <v>11</v>
+      </c>
+      <c r="H6">
+        <v>8</v>
+      </c>
+      <c r="I6">
+        <v>6</v>
+      </c>
+      <c r="J6">
+        <v>6</v>
+      </c>
+      <c r="K6">
+        <v>9</v>
+      </c>
+      <c r="L6">
+        <v>9</v>
+      </c>
+      <c r="M6">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7">
+        <v>14</v>
+      </c>
+      <c r="C7">
+        <v>27</v>
+      </c>
+      <c r="D7">
+        <v>33</v>
+      </c>
+      <c r="E7">
+        <v>36</v>
+      </c>
+      <c r="F7">
+        <v>38</v>
+      </c>
+      <c r="G7">
+        <v>13</v>
+      </c>
+      <c r="H7">
+        <v>17</v>
+      </c>
+      <c r="I7">
+        <v>21</v>
+      </c>
+      <c r="J7">
+        <v>11</v>
+      </c>
+      <c r="K7">
+        <v>17</v>
+      </c>
+      <c r="L7">
+        <v>21</v>
+      </c>
+      <c r="M7">
+        <v>10</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:M7"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+    <col min="13" max="13" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="M1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E2">
+        <v>2</v>
+      </c>
+      <c r="F2">
+        <v>1</v>
+      </c>
+      <c r="H2">
+        <v>1</v>
+      </c>
+      <c r="M2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F3">
+        <v>1</v>
+      </c>
+      <c r="G3">
+        <v>2</v>
+      </c>
+      <c r="L3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="I4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C5">
+        <v>1</v>
+      </c>
+      <c r="G5">
+        <v>1</v>
+      </c>
+      <c r="K5">
+        <v>1</v>
+      </c>
+      <c r="M5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6">
+        <v>1</v>
+      </c>
+      <c r="C6">
+        <v>2</v>
+      </c>
+      <c r="D6">
+        <v>2</v>
+      </c>
+      <c r="E6">
+        <v>7</v>
+      </c>
+      <c r="F6">
+        <v>3</v>
+      </c>
+      <c r="H6">
+        <v>1</v>
+      </c>
+      <c r="I6">
+        <v>1</v>
+      </c>
+      <c r="J6">
+        <v>5</v>
+      </c>
+      <c r="K6">
+        <v>1</v>
+      </c>
+      <c r="M6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7">
+        <v>1</v>
+      </c>
+      <c r="C7">
+        <v>3</v>
+      </c>
+      <c r="D7">
+        <v>2</v>
+      </c>
+      <c r="E7">
+        <v>9</v>
+      </c>
+      <c r="F7">
+        <v>5</v>
+      </c>
+      <c r="G7">
+        <v>3</v>
+      </c>
+      <c r="H7">
+        <v>2</v>
+      </c>
+      <c r="I7">
+        <v>2</v>
+      </c>
+      <c r="J7">
+        <v>5</v>
+      </c>
+      <c r="K7">
+        <v>2</v>
+      </c>
+      <c r="L7">
+        <v>1</v>
+      </c>
+      <c r="M7">
+        <v>6</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -3335,552 +3853,6 @@
       </c>
       <c r="M6">
         <v>6</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M8"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" customWidth="1"/>
-    <col min="13" max="13" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="M1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2">
-        <v>1</v>
-      </c>
-      <c r="E2">
-        <v>1</v>
-      </c>
-      <c r="G2">
-        <v>2</v>
-      </c>
-      <c r="H2">
-        <v>4</v>
-      </c>
-      <c r="I2">
-        <v>3</v>
-      </c>
-      <c r="K2">
-        <v>1</v>
-      </c>
-      <c r="L2">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3">
-        <v>1</v>
-      </c>
-      <c r="C3">
-        <v>1</v>
-      </c>
-      <c r="D3">
-        <v>3</v>
-      </c>
-      <c r="F3">
-        <v>1</v>
-      </c>
-      <c r="G3">
-        <v>3</v>
-      </c>
-      <c r="H3">
-        <v>3</v>
-      </c>
-      <c r="J3">
-        <v>1</v>
-      </c>
-      <c r="K3">
-        <v>2</v>
-      </c>
-      <c r="L3">
-        <v>2</v>
-      </c>
-      <c r="M3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="M4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D5">
-        <v>1</v>
-      </c>
-      <c r="I5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B6">
-        <v>2</v>
-      </c>
-      <c r="C6">
-        <v>1</v>
-      </c>
-      <c r="D6">
-        <v>1</v>
-      </c>
-      <c r="E6">
-        <v>1</v>
-      </c>
-      <c r="F6">
-        <v>2</v>
-      </c>
-      <c r="G6">
-        <v>2</v>
-      </c>
-      <c r="H6">
-        <v>2</v>
-      </c>
-      <c r="I6">
-        <v>2</v>
-      </c>
-      <c r="J6">
-        <v>5</v>
-      </c>
-      <c r="K6">
-        <v>1</v>
-      </c>
-      <c r="L6">
-        <v>3</v>
-      </c>
-      <c r="M6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
-      <c r="A7" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B7">
-        <v>25</v>
-      </c>
-      <c r="C7">
-        <v>19</v>
-      </c>
-      <c r="D7">
-        <v>11</v>
-      </c>
-      <c r="E7">
-        <v>22</v>
-      </c>
-      <c r="F7">
-        <v>20</v>
-      </c>
-      <c r="G7">
-        <v>22</v>
-      </c>
-      <c r="H7">
-        <v>11</v>
-      </c>
-      <c r="I7">
-        <v>7</v>
-      </c>
-      <c r="J7">
-        <v>8</v>
-      </c>
-      <c r="K7">
-        <v>11</v>
-      </c>
-      <c r="L7">
-        <v>12</v>
-      </c>
-      <c r="M7">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13">
-      <c r="A8" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B8">
-        <v>29</v>
-      </c>
-      <c r="C8">
-        <v>21</v>
-      </c>
-      <c r="D8">
-        <v>16</v>
-      </c>
-      <c r="E8">
-        <v>24</v>
-      </c>
-      <c r="F8">
-        <v>23</v>
-      </c>
-      <c r="G8">
-        <v>29</v>
-      </c>
-      <c r="H8">
-        <v>20</v>
-      </c>
-      <c r="I8">
-        <v>13</v>
-      </c>
-      <c r="J8">
-        <v>14</v>
-      </c>
-      <c r="K8">
-        <v>15</v>
-      </c>
-      <c r="L8">
-        <v>20</v>
-      </c>
-      <c r="M8">
-        <v>12</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M9"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" customWidth="1"/>
-    <col min="13" max="13" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="M1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2">
-        <v>1</v>
-      </c>
-      <c r="D2">
-        <v>2</v>
-      </c>
-      <c r="F2">
-        <v>3</v>
-      </c>
-      <c r="G2">
-        <v>3</v>
-      </c>
-      <c r="I2">
-        <v>2</v>
-      </c>
-      <c r="J2">
-        <v>1</v>
-      </c>
-      <c r="K2">
-        <v>5</v>
-      </c>
-      <c r="L2">
-        <v>3</v>
-      </c>
-      <c r="M2">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D3">
-        <v>1</v>
-      </c>
-      <c r="E3">
-        <v>1</v>
-      </c>
-      <c r="F3">
-        <v>1</v>
-      </c>
-      <c r="G3">
-        <v>4</v>
-      </c>
-      <c r="H3">
-        <v>1</v>
-      </c>
-      <c r="I3">
-        <v>3</v>
-      </c>
-      <c r="J3">
-        <v>3</v>
-      </c>
-      <c r="L3">
-        <v>2</v>
-      </c>
-      <c r="M3">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="I4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="K5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="M6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
-      <c r="A7" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B7">
-        <v>4</v>
-      </c>
-      <c r="C7">
-        <v>5</v>
-      </c>
-      <c r="D7">
-        <v>6</v>
-      </c>
-      <c r="E7">
-        <v>5</v>
-      </c>
-      <c r="F7">
-        <v>6</v>
-      </c>
-      <c r="G7">
-        <v>4</v>
-      </c>
-      <c r="H7">
-        <v>12</v>
-      </c>
-      <c r="I7">
-        <v>7</v>
-      </c>
-      <c r="J7">
-        <v>6</v>
-      </c>
-      <c r="K7">
-        <v>16</v>
-      </c>
-      <c r="L7">
-        <v>8</v>
-      </c>
-      <c r="M7">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13">
-      <c r="A8" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B8">
-        <v>20</v>
-      </c>
-      <c r="C8">
-        <v>21</v>
-      </c>
-      <c r="D8">
-        <v>21</v>
-      </c>
-      <c r="E8">
-        <v>19</v>
-      </c>
-      <c r="F8">
-        <v>19</v>
-      </c>
-      <c r="G8">
-        <v>7</v>
-      </c>
-      <c r="H8">
-        <v>5</v>
-      </c>
-      <c r="I8">
-        <v>10</v>
-      </c>
-      <c r="J8">
-        <v>9</v>
-      </c>
-      <c r="K8">
-        <v>12</v>
-      </c>
-      <c r="L8">
-        <v>12</v>
-      </c>
-      <c r="M8">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13">
-      <c r="A9" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B9">
-        <v>24</v>
-      </c>
-      <c r="C9">
-        <v>27</v>
-      </c>
-      <c r="D9">
-        <v>30</v>
-      </c>
-      <c r="E9">
-        <v>25</v>
-      </c>
-      <c r="F9">
-        <v>29</v>
-      </c>
-      <c r="G9">
-    